--- a/data/CV_infolist.xlsx
+++ b/data/CV_infolist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sooyo\Documents\github\sylcv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F396B098-1992-4913-8670-762B8665C341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133D400D-5121-4688-BAC3-0B0B52A7A8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="14496" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="348">
   <si>
     <t>Degree</t>
   </si>
@@ -1089,6 +1089,9 @@
   <si>
     <t>BMC Medical Research Methodology</t>
   </si>
+  <si>
+    <t>Sooyong Lee, Myoungsung Lee, Sehee Hong</t>
+  </si>
 </sst>
 </file>
 
@@ -32957,7 +32960,7 @@
         <v>97</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>251</v>
+        <v>347</v>
       </c>
       <c r="C31" s="30">
         <v>2026</v>

--- a/data/CV_infolist.xlsx
+++ b/data/CV_infolist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sooyo\Documents\github\sylcv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133D400D-5121-4688-BAC3-0B0B52A7A8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9E15CF-B290-47BF-BCA7-23EEB18CC0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="14496" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="352">
   <si>
     <t>Degree</t>
   </si>
@@ -1092,6 +1092,18 @@
   <si>
     <t>Sooyong Lee, Myoungsung Lee, Sehee Hong</t>
   </si>
+  <si>
+    <t>How to Generate Data for Simulation-based Power Analysis</t>
+  </si>
+  <si>
+    <t>Comparison in Scale Development Between CFA and IRT</t>
+  </si>
+  <si>
+    <t>Factor Scores for Multidimensional Latent Growth Curve Modeling</t>
+  </si>
+  <si>
+    <t>Validity Study for AI-generated Sample and Responses</t>
+  </si>
 </sst>
 </file>
 
@@ -31828,7 +31840,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:X1003"/>
+  <dimension ref="A1:X1007"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.44140625" style="33" customWidth="1"/>
@@ -32993,16 +33005,16 @@
     </row>
     <row r="32" spans="1:24" ht="20.25" customHeight="1">
       <c r="A32" s="30" t="s">
-        <v>258</v>
+        <v>97</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>344</v>
+        <v>251</v>
       </c>
       <c r="C32" s="30">
         <v>2026</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E32" s="30"/>
       <c r="F32" s="44"/>
@@ -33027,16 +33039,16 @@
     </row>
     <row r="33" spans="1:24" ht="20.25" customHeight="1">
       <c r="A33" s="30" t="s">
-        <v>258</v>
+        <v>97</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>341</v>
+        <v>251</v>
       </c>
       <c r="C33" s="30">
         <v>2026</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E33" s="30"/>
       <c r="F33" s="44"/>
@@ -33061,7 +33073,7 @@
     </row>
     <row r="34" spans="1:24" ht="20.25" customHeight="1">
       <c r="A34" s="30" t="s">
-        <v>258</v>
+        <v>97</v>
       </c>
       <c r="B34" s="30" t="s">
         <v>251</v>
@@ -33070,7 +33082,7 @@
         <v>2026</v>
       </c>
       <c r="D34" s="53" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="E34" s="30"/>
       <c r="F34" s="44"/>
@@ -33095,24 +33107,22 @@
     </row>
     <row r="35" spans="1:24" ht="20.25" customHeight="1">
       <c r="A35" s="30" t="s">
-        <v>258</v>
+        <v>97</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="C35" s="30">
-        <v>2025</v>
-      </c>
-      <c r="D35" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="F35" s="30"/>
+        <v>2026</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>351</v>
+      </c>
+      <c r="E35" s="30"/>
+      <c r="F35" s="44"/>
       <c r="G35" s="30"/>
       <c r="H35" s="47"/>
-      <c r="I35" s="30"/>
+      <c r="I35" s="22"/>
       <c r="J35" s="30"/>
       <c r="K35" s="30"/>
       <c r="L35" s="30"/>
@@ -33134,24 +33144,20 @@
         <v>258</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>229</v>
+        <v>344</v>
       </c>
       <c r="C36" s="30">
-        <v>2025</v>
-      </c>
-      <c r="D36" s="30" t="s">
-        <v>228</v>
-      </c>
-      <c r="E36" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="F36" s="30"/>
+        <v>2026</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="E36" s="30"/>
+      <c r="F36" s="44"/>
       <c r="G36" s="30"/>
       <c r="H36" s="47"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30" t="s">
-        <v>103</v>
-      </c>
+      <c r="I36" s="22"/>
+      <c r="J36" s="30"/>
       <c r="K36" s="30"/>
       <c r="L36" s="30"/>
       <c r="M36" s="30"/>
@@ -33172,17 +33178,19 @@
         <v>258</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30" t="s">
-        <v>252</v>
+        <v>341</v>
+      </c>
+      <c r="C37" s="30">
+        <v>2026</v>
+      </c>
+      <c r="D37" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
+      <c r="F37" s="44"/>
       <c r="G37" s="30"/>
       <c r="H37" s="47"/>
-      <c r="I37" s="30"/>
+      <c r="I37" s="22"/>
       <c r="J37" s="30"/>
       <c r="K37" s="30"/>
       <c r="L37" s="30"/>
@@ -33206,15 +33214,17 @@
       <c r="B38" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30" t="s">
-        <v>253</v>
+      <c r="C38" s="30">
+        <v>2026</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>340</v>
       </c>
       <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
+      <c r="F38" s="44"/>
       <c r="G38" s="30"/>
       <c r="H38" s="47"/>
-      <c r="I38" s="30"/>
+      <c r="I38" s="22"/>
       <c r="J38" s="30"/>
       <c r="K38" s="30"/>
       <c r="L38" s="30"/>
@@ -33236,13 +33246,17 @@
         <v>258</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="C39" s="30"/>
+        <v>227</v>
+      </c>
+      <c r="C39" s="30">
+        <v>2025</v>
+      </c>
       <c r="D39" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="E39" s="30"/>
+        <v>226</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>225</v>
+      </c>
       <c r="F39" s="30"/>
       <c r="G39" s="30"/>
       <c r="H39" s="47"/>
@@ -33268,18 +33282,24 @@
         <v>258</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="C40" s="30"/>
+        <v>229</v>
+      </c>
+      <c r="C40" s="30">
+        <v>2025</v>
+      </c>
       <c r="D40" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="E40" s="30"/>
+        <v>228</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>225</v>
+      </c>
       <c r="F40" s="30"/>
       <c r="G40" s="30"/>
       <c r="H40" s="47"/>
       <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
+      <c r="J40" s="30" t="s">
+        <v>103</v>
+      </c>
       <c r="K40" s="30"/>
       <c r="L40" s="30"/>
       <c r="M40" s="30"/>
@@ -33304,7 +33324,7 @@
       </c>
       <c r="C41" s="30"/>
       <c r="D41" s="30" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E41" s="30"/>
       <c r="F41" s="30"/>
@@ -33336,7 +33356,7 @@
       </c>
       <c r="C42" s="30"/>
       <c r="D42" s="30" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E42" s="30"/>
       <c r="F42" s="30"/>
@@ -33364,11 +33384,11 @@
         <v>258</v>
       </c>
       <c r="B43" s="30" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C43" s="30"/>
       <c r="D43" s="30" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E43" s="30"/>
       <c r="F43" s="30"/>
@@ -33395,10 +33415,12 @@
       <c r="A44" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="B44" s="30"/>
+      <c r="B44" s="30" t="s">
+        <v>251</v>
+      </c>
       <c r="C44" s="30"/>
       <c r="D44" s="30" t="s">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="E44" s="30"/>
       <c r="F44" s="30"/>
@@ -33425,10 +33447,12 @@
       <c r="A45" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="B45" s="30"/>
+      <c r="B45" s="30" t="s">
+        <v>251</v>
+      </c>
       <c r="C45" s="30"/>
       <c r="D45" s="30" t="s">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="E45" s="30"/>
       <c r="F45" s="30"/>
@@ -33455,10 +33479,12 @@
       <c r="A46" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="B46" s="30"/>
+      <c r="B46" s="30" t="s">
+        <v>251</v>
+      </c>
       <c r="C46" s="30"/>
       <c r="D46" s="30" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="E46" s="30"/>
       <c r="F46" s="30"/>
@@ -33485,10 +33511,12 @@
       <c r="A47" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="B47" s="30"/>
+      <c r="B47" s="30" t="s">
+        <v>259</v>
+      </c>
       <c r="C47" s="30"/>
       <c r="D47" s="30" t="s">
-        <v>319</v>
+        <v>260</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="30"/>
@@ -33518,7 +33546,7 @@
       <c r="B48" s="30"/>
       <c r="C48" s="30"/>
       <c r="D48" s="30" t="s">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="E48" s="30"/>
       <c r="F48" s="30"/>
@@ -33548,7 +33576,7 @@
       <c r="B49" s="30"/>
       <c r="C49" s="30"/>
       <c r="D49" s="30" t="s">
-        <v>321</v>
+        <v>287</v>
       </c>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
@@ -33578,7 +33606,7 @@
       <c r="B50" s="30"/>
       <c r="C50" s="30"/>
       <c r="D50" s="30" t="s">
-        <v>322</v>
+        <v>288</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="30"/>
@@ -33608,7 +33636,7 @@
       <c r="B51" s="30"/>
       <c r="C51" s="30"/>
       <c r="D51" s="30" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="30"/>
@@ -33638,11 +33666,9 @@
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
       <c r="D52" s="30" t="s">
-        <v>334</v>
-      </c>
-      <c r="E52" s="30" t="s">
-        <v>333</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="E52" s="30"/>
       <c r="F52" s="30"/>
       <c r="G52" s="30"/>
       <c r="H52" s="47"/>
@@ -33669,7 +33695,9 @@
       </c>
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="30" t="s">
+        <v>321</v>
+      </c>
       <c r="E53" s="30"/>
       <c r="F53" s="30"/>
       <c r="G53" s="30"/>
@@ -33693,24 +33721,18 @@
     </row>
     <row r="54" spans="1:24" ht="20.25" customHeight="1">
       <c r="A54" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="B54" s="30" t="s">
-        <v>318</v>
-      </c>
-      <c r="C54" s="30">
-        <v>2025</v>
-      </c>
-      <c r="D54" s="50" t="s">
-        <v>311</v>
-      </c>
-      <c r="E54" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="F54" s="44"/>
+        <v>258</v>
+      </c>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
       <c r="G54" s="30"/>
       <c r="H54" s="47"/>
-      <c r="I54" s="22"/>
+      <c r="I54" s="30"/>
       <c r="J54" s="30"/>
       <c r="K54" s="30"/>
       <c r="L54" s="30"/>
@@ -33729,22 +33751,19 @@
     </row>
     <row r="55" spans="1:24" ht="20.25" customHeight="1">
       <c r="A55" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="B55" s="30" t="s">
-        <v>119</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="B55" s="30"/>
       <c r="C55" s="30"/>
       <c r="D55" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="E55" s="30" t="s">
-        <v>152</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="E55" s="30"/>
       <c r="F55" s="30"/>
       <c r="G55" s="30"/>
       <c r="H55" s="47"/>
       <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
       <c r="K55" s="30"/>
       <c r="L55" s="30"/>
       <c r="M55" s="30"/>
@@ -33762,22 +33781,21 @@
     </row>
     <row r="56" spans="1:24" ht="20.25" customHeight="1">
       <c r="A56" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="B56" s="30" t="s">
-        <v>153</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="B56" s="30"/>
       <c r="C56" s="30"/>
-      <c r="D56" s="35" t="s">
-        <v>154</v>
+      <c r="D56" s="30" t="s">
+        <v>334</v>
       </c>
       <c r="E56" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="I56"/>
-      <c r="J56" s="33" t="s">
-        <v>103</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="47"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
       <c r="K56" s="30"/>
       <c r="L56" s="30"/>
       <c r="M56" s="30"/>
@@ -33795,21 +33813,17 @@
     </row>
     <row r="57" spans="1:24" ht="20.25" customHeight="1">
       <c r="A57" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="B57" s="30" t="s">
-        <v>153</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="B57" s="30"/>
       <c r="C57" s="30"/>
-      <c r="D57" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E57" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="J57" s="33" t="s">
-        <v>103</v>
-      </c>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
       <c r="K57" s="30"/>
       <c r="L57" s="30"/>
       <c r="M57" s="30"/>
@@ -33827,25 +33841,25 @@
     </row>
     <row r="58" spans="1:24" ht="20.25" customHeight="1">
       <c r="A58" s="30" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30" t="s">
-        <v>155</v>
+        <v>318</v>
+      </c>
+      <c r="C58" s="30">
+        <v>2025</v>
+      </c>
+      <c r="D58" s="50" t="s">
+        <v>311</v>
       </c>
       <c r="E58" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="F58" s="30"/>
+      <c r="F58" s="44"/>
       <c r="G58" s="30"/>
       <c r="H58" s="47"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="33" t="s">
-        <v>103</v>
-      </c>
+      <c r="I58" s="22"/>
+      <c r="J58" s="30"/>
       <c r="K58" s="30"/>
       <c r="L58" s="30"/>
       <c r="M58" s="30"/>
@@ -33862,16 +33876,23 @@
       <c r="X58" s="30"/>
     </row>
     <row r="59" spans="1:24" ht="20.25" customHeight="1">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="B59" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
+      <c r="D59" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="F59" s="30"/>
       <c r="G59" s="30"/>
       <c r="H59" s="47"/>
       <c r="I59" s="30"/>
-      <c r="J59" s="30"/>
       <c r="K59" s="30"/>
       <c r="L59" s="30"/>
       <c r="M59" s="30"/>
@@ -33888,16 +33909,23 @@
       <c r="X59" s="30"/>
     </row>
     <row r="60" spans="1:24" ht="20.25" customHeight="1">
-      <c r="A60" s="30"/>
-      <c r="B60" s="30"/>
+      <c r="A60" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>153</v>
+      </c>
       <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="30"/>
-      <c r="H60" s="47"/>
-      <c r="I60" s="30"/>
-      <c r="J60" s="30"/>
+      <c r="D60" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="E60" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="I60"/>
+      <c r="J60" s="33" t="s">
+        <v>103</v>
+      </c>
       <c r="K60" s="30"/>
       <c r="L60" s="30"/>
       <c r="M60" s="30"/>
@@ -33914,16 +33942,22 @@
       <c r="X60" s="30"/>
     </row>
     <row r="61" spans="1:24" ht="20.25" customHeight="1">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
+      <c r="A61" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="B61" s="30" t="s">
+        <v>153</v>
+      </c>
       <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="47"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
+      <c r="D61" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E61" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="J61" s="33" t="s">
+        <v>103</v>
+      </c>
       <c r="K61" s="30"/>
       <c r="L61" s="30"/>
       <c r="M61" s="30"/>
@@ -33940,16 +33974,26 @@
       <c r="X61" s="30"/>
     </row>
     <row r="62" spans="1:24" ht="20.25" customHeight="1">
-      <c r="A62" s="30"/>
-      <c r="B62" s="30"/>
+      <c r="A62" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="B62" s="30" t="s">
+        <v>52</v>
+      </c>
       <c r="C62" s="30"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
+      <c r="D62" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E62" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="F62" s="30"/>
       <c r="G62" s="30"/>
       <c r="H62" s="47"/>
       <c r="I62" s="30"/>
-      <c r="J62" s="30"/>
+      <c r="J62" s="33" t="s">
+        <v>103</v>
+      </c>
       <c r="K62" s="30"/>
       <c r="L62" s="30"/>
       <c r="M62" s="30"/>
@@ -58430,6 +58474,110 @@
       <c r="V1003" s="30"/>
       <c r="W1003" s="30"/>
       <c r="X1003" s="30"/>
+    </row>
+    <row r="1004" spans="1:24" ht="20.25" customHeight="1">
+      <c r="A1004" s="30"/>
+      <c r="B1004" s="30"/>
+      <c r="C1004" s="30"/>
+      <c r="D1004" s="30"/>
+      <c r="E1004" s="30"/>
+      <c r="F1004" s="30"/>
+      <c r="G1004" s="30"/>
+      <c r="H1004" s="47"/>
+      <c r="I1004" s="30"/>
+      <c r="J1004" s="30"/>
+      <c r="K1004" s="30"/>
+      <c r="L1004" s="30"/>
+      <c r="M1004" s="30"/>
+      <c r="N1004" s="30"/>
+      <c r="O1004" s="30"/>
+      <c r="P1004" s="30"/>
+      <c r="Q1004" s="30"/>
+      <c r="R1004" s="30"/>
+      <c r="S1004" s="30"/>
+      <c r="T1004" s="30"/>
+      <c r="U1004" s="30"/>
+      <c r="V1004" s="30"/>
+      <c r="W1004" s="30"/>
+      <c r="X1004" s="30"/>
+    </row>
+    <row r="1005" spans="1:24" ht="20.25" customHeight="1">
+      <c r="A1005" s="30"/>
+      <c r="B1005" s="30"/>
+      <c r="C1005" s="30"/>
+      <c r="D1005" s="30"/>
+      <c r="E1005" s="30"/>
+      <c r="F1005" s="30"/>
+      <c r="G1005" s="30"/>
+      <c r="H1005" s="47"/>
+      <c r="I1005" s="30"/>
+      <c r="J1005" s="30"/>
+      <c r="K1005" s="30"/>
+      <c r="L1005" s="30"/>
+      <c r="M1005" s="30"/>
+      <c r="N1005" s="30"/>
+      <c r="O1005" s="30"/>
+      <c r="P1005" s="30"/>
+      <c r="Q1005" s="30"/>
+      <c r="R1005" s="30"/>
+      <c r="S1005" s="30"/>
+      <c r="T1005" s="30"/>
+      <c r="U1005" s="30"/>
+      <c r="V1005" s="30"/>
+      <c r="W1005" s="30"/>
+      <c r="X1005" s="30"/>
+    </row>
+    <row r="1006" spans="1:24" ht="20.25" customHeight="1">
+      <c r="A1006" s="30"/>
+      <c r="B1006" s="30"/>
+      <c r="C1006" s="30"/>
+      <c r="D1006" s="30"/>
+      <c r="E1006" s="30"/>
+      <c r="F1006" s="30"/>
+      <c r="G1006" s="30"/>
+      <c r="H1006" s="47"/>
+      <c r="I1006" s="30"/>
+      <c r="J1006" s="30"/>
+      <c r="K1006" s="30"/>
+      <c r="L1006" s="30"/>
+      <c r="M1006" s="30"/>
+      <c r="N1006" s="30"/>
+      <c r="O1006" s="30"/>
+      <c r="P1006" s="30"/>
+      <c r="Q1006" s="30"/>
+      <c r="R1006" s="30"/>
+      <c r="S1006" s="30"/>
+      <c r="T1006" s="30"/>
+      <c r="U1006" s="30"/>
+      <c r="V1006" s="30"/>
+      <c r="W1006" s="30"/>
+      <c r="X1006" s="30"/>
+    </row>
+    <row r="1007" spans="1:24" ht="20.25" customHeight="1">
+      <c r="A1007" s="30"/>
+      <c r="B1007" s="30"/>
+      <c r="C1007" s="30"/>
+      <c r="D1007" s="30"/>
+      <c r="E1007" s="30"/>
+      <c r="F1007" s="30"/>
+      <c r="G1007" s="30"/>
+      <c r="H1007" s="47"/>
+      <c r="I1007" s="30"/>
+      <c r="J1007" s="30"/>
+      <c r="K1007" s="30"/>
+      <c r="L1007" s="30"/>
+      <c r="M1007" s="30"/>
+      <c r="N1007" s="30"/>
+      <c r="O1007" s="30"/>
+      <c r="P1007" s="30"/>
+      <c r="Q1007" s="30"/>
+      <c r="R1007" s="30"/>
+      <c r="S1007" s="30"/>
+      <c r="T1007" s="30"/>
+      <c r="U1007" s="30"/>
+      <c r="V1007" s="30"/>
+      <c r="W1007" s="30"/>
+      <c r="X1007" s="30"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J21" xr:uid="{00000000-0001-0000-0600-000000000000}">

--- a/data/CV_infolist.xlsx
+++ b/data/CV_infolist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sooyo\Documents\github\sylcv\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lee\Documents\GitHub\sylcv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9E15CF-B290-47BF-BCA7-23EEB18CC0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C05310-94AB-4AE8-ABD6-F654A71B0802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1110" yWindow="0" windowWidth="14430" windowHeight="16200" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
@@ -24,10 +24,23 @@
     <sheet name="Software" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Publication!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Publication!$A$1:$J$20</definedName>
     <definedName name="header" localSheetId="6">Publication!$D$29</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1695,15 +1708,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="29.44140625" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="136.6640625" customWidth="1"/>
+    <col min="1" max="1" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="136.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.2">
+    <row r="1" spans="1:5" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1720,7 +1733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="39.6">
+    <row r="2" spans="1:5" ht="38.25">
       <c r="A2" s="26" t="s">
         <v>165</v>
       </c>
@@ -1737,7 +1750,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="13.8" thickBot="1">
+    <row r="3" spans="1:5" ht="13.5" thickBot="1">
       <c r="A3" s="24" t="s">
         <v>134</v>
       </c>
@@ -1782,9 +1795,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:P18"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="39.109375" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1">
@@ -2218,19 +2231,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1001"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.88671875" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" style="16" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="13.2">
+    <row r="1" spans="1:27" ht="12.75">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -2277,7 +2290,7 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:27" ht="13.2">
+    <row r="2" spans="1:27" ht="12.75">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -2322,7 +2335,7 @@
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
     </row>
-    <row r="3" spans="1:27" ht="13.2">
+    <row r="3" spans="1:27" ht="12.75">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -2367,7 +2380,7 @@
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
     </row>
-    <row r="4" spans="1:27" ht="13.2">
+    <row r="4" spans="1:27" ht="12.75">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -2455,7 +2468,7 @@
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
     </row>
-    <row r="6" spans="1:27" ht="13.2">
+    <row r="6" spans="1:27" ht="12.75">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -2498,7 +2511,7 @@
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
     </row>
-    <row r="7" spans="1:27" ht="16.8">
+    <row r="7" spans="1:27" ht="18">
       <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
@@ -2545,7 +2558,7 @@
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
     </row>
-    <row r="8" spans="1:27" ht="16.8">
+    <row r="8" spans="1:27" ht="18">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -2590,7 +2603,7 @@
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:27" ht="16.8">
+    <row r="9" spans="1:27" ht="18">
       <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
@@ -2635,7 +2648,7 @@
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
     </row>
-    <row r="10" spans="1:27" ht="13.2">
+    <row r="10" spans="1:27" ht="12.75">
       <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
@@ -2678,7 +2691,7 @@
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="1:27" ht="13.2">
+    <row r="11" spans="1:27" ht="12.75">
       <c r="A11" s="21" t="s">
         <v>40</v>
       </c>
@@ -2719,7 +2732,7 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="1:27" ht="15.6">
+    <row r="12" spans="1:27">
       <c r="A12" s="21" t="s">
         <v>19</v>
       </c>
@@ -2760,7 +2773,7 @@
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
     </row>
-    <row r="13" spans="1:27" ht="15.6">
+    <row r="13" spans="1:27">
       <c r="A13" s="21" t="s">
         <v>40</v>
       </c>
@@ -2801,7 +2814,7 @@
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
     </row>
-    <row r="14" spans="1:27" ht="13.2">
+    <row r="14" spans="1:27" ht="12.75">
       <c r="A14" s="21" t="s">
         <v>40</v>
       </c>
@@ -2844,7 +2857,7 @@
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
     </row>
-    <row r="15" spans="1:27" ht="13.2">
+    <row r="15" spans="1:27" ht="12.75">
       <c r="A15" s="21" t="s">
         <v>40</v>
       </c>
@@ -2887,7 +2900,7 @@
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
     </row>
-    <row r="16" spans="1:27" ht="13.2">
+    <row r="16" spans="1:27" ht="12.75">
       <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
@@ -2930,7 +2943,7 @@
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="1:27" ht="13.2">
+    <row r="17" spans="1:27" ht="12.75">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -2973,7 +2986,7 @@
       <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
     </row>
-    <row r="18" spans="1:27" ht="13.2">
+    <row r="18" spans="1:27" ht="12.75">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -3016,7 +3029,7 @@
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
     </row>
-    <row r="19" spans="1:27" ht="13.2">
+    <row r="19" spans="1:27" ht="12.75">
       <c r="A19" s="2" t="s">
         <v>40</v>
       </c>
@@ -3059,7 +3072,7 @@
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" spans="1:27" ht="13.2">
+    <row r="20" spans="1:27" ht="12.75">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -3102,7 +3115,7 @@
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" spans="1:27" ht="13.2">
+    <row r="21" spans="1:27" ht="12.75">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="14"/>
@@ -3131,7 +3144,7 @@
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
     </row>
-    <row r="22" spans="1:27" ht="13.2">
+    <row r="22" spans="1:27" ht="12.75">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="14"/>
@@ -3160,7 +3173,7 @@
       <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="1:27" ht="13.2">
+    <row r="23" spans="1:27" ht="12.75">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="14"/>
@@ -3189,7 +3202,7 @@
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
     </row>
-    <row r="24" spans="1:27" ht="13.2">
+    <row r="24" spans="1:27" ht="12.75">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="14"/>
@@ -3218,7 +3231,7 @@
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" spans="1:27" ht="13.2">
+    <row r="25" spans="1:27" ht="12.75">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="14"/>
@@ -3247,7 +3260,7 @@
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
     </row>
-    <row r="26" spans="1:27" ht="13.2">
+    <row r="26" spans="1:27" ht="12.75">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="14"/>
@@ -3276,7 +3289,7 @@
       <c r="Z26" s="2"/>
       <c r="AA26" s="2"/>
     </row>
-    <row r="27" spans="1:27" ht="13.2">
+    <row r="27" spans="1:27" ht="12.75">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="14"/>
@@ -3305,7 +3318,7 @@
       <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
     </row>
-    <row r="28" spans="1:27" ht="13.2">
+    <row r="28" spans="1:27" ht="12.75">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="14"/>
@@ -3334,7 +3347,7 @@
       <c r="Z28" s="2"/>
       <c r="AA28" s="2"/>
     </row>
-    <row r="29" spans="1:27" ht="13.2">
+    <row r="29" spans="1:27" ht="12.75">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="14"/>
@@ -3363,7 +3376,7 @@
       <c r="Z29" s="2"/>
       <c r="AA29" s="2"/>
     </row>
-    <row r="30" spans="1:27" ht="13.2">
+    <row r="30" spans="1:27" ht="12.75">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="14"/>
@@ -3392,7 +3405,7 @@
       <c r="Z30" s="2"/>
       <c r="AA30" s="2"/>
     </row>
-    <row r="31" spans="1:27" ht="13.2">
+    <row r="31" spans="1:27" ht="12.75">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="14"/>
@@ -3421,7 +3434,7 @@
       <c r="Z31" s="2"/>
       <c r="AA31" s="2"/>
     </row>
-    <row r="32" spans="1:27" ht="13.2">
+    <row r="32" spans="1:27" ht="12.75">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="14"/>
@@ -3450,7 +3463,7 @@
       <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
     </row>
-    <row r="33" spans="1:27" ht="13.2">
+    <row r="33" spans="1:27" ht="12.75">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="14"/>
@@ -3479,7 +3492,7 @@
       <c r="Z33" s="2"/>
       <c r="AA33" s="2"/>
     </row>
-    <row r="34" spans="1:27" ht="13.2">
+    <row r="34" spans="1:27" ht="12.75">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="14"/>
@@ -3508,7 +3521,7 @@
       <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
     </row>
-    <row r="35" spans="1:27" ht="13.2">
+    <row r="35" spans="1:27" ht="12.75">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="14"/>
@@ -3537,7 +3550,7 @@
       <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
     </row>
-    <row r="36" spans="1:27" ht="13.2">
+    <row r="36" spans="1:27" ht="12.75">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="14"/>
@@ -3566,7 +3579,7 @@
       <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
     </row>
-    <row r="37" spans="1:27" ht="13.2">
+    <row r="37" spans="1:27" ht="12.75">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="14"/>
@@ -3595,7 +3608,7 @@
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
     </row>
-    <row r="38" spans="1:27" ht="13.2">
+    <row r="38" spans="1:27" ht="12.75">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="14"/>
@@ -3624,7 +3637,7 @@
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
     </row>
-    <row r="39" spans="1:27" ht="13.2">
+    <row r="39" spans="1:27" ht="12.75">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="14"/>
@@ -3653,7 +3666,7 @@
       <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
     </row>
-    <row r="40" spans="1:27" ht="13.2">
+    <row r="40" spans="1:27" ht="12.75">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="14"/>
@@ -3682,7 +3695,7 @@
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
     </row>
-    <row r="41" spans="1:27" ht="13.2">
+    <row r="41" spans="1:27" ht="12.75">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="14"/>
@@ -3711,7 +3724,7 @@
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="1:27" ht="13.2">
+    <row r="42" spans="1:27" ht="12.75">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="14"/>
@@ -3740,7 +3753,7 @@
       <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
     </row>
-    <row r="43" spans="1:27" ht="13.2">
+    <row r="43" spans="1:27" ht="12.75">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="14"/>
@@ -3769,7 +3782,7 @@
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
     </row>
-    <row r="44" spans="1:27" ht="13.2">
+    <row r="44" spans="1:27" ht="12.75">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="14"/>
@@ -3798,7 +3811,7 @@
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
     </row>
-    <row r="45" spans="1:27" ht="13.2">
+    <row r="45" spans="1:27" ht="12.75">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="14"/>
@@ -3827,7 +3840,7 @@
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="1:27" ht="13.2">
+    <row r="46" spans="1:27" ht="12.75">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="14"/>
@@ -3856,7 +3869,7 @@
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
     </row>
-    <row r="47" spans="1:27" ht="13.2">
+    <row r="47" spans="1:27" ht="12.75">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="14"/>
@@ -3885,7 +3898,7 @@
       <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
     </row>
-    <row r="48" spans="1:27" ht="13.2">
+    <row r="48" spans="1:27" ht="12.75">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="14"/>
@@ -3914,7 +3927,7 @@
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
     </row>
-    <row r="49" spans="1:27" ht="13.2">
+    <row r="49" spans="1:27" ht="12.75">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="14"/>
@@ -3943,7 +3956,7 @@
       <c r="Z49" s="2"/>
       <c r="AA49" s="2"/>
     </row>
-    <row r="50" spans="1:27" ht="13.2">
+    <row r="50" spans="1:27" ht="12.75">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="14"/>
@@ -3972,7 +3985,7 @@
       <c r="Z50" s="2"/>
       <c r="AA50" s="2"/>
     </row>
-    <row r="51" spans="1:27" ht="13.2">
+    <row r="51" spans="1:27" ht="12.75">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="14"/>
@@ -4001,7 +4014,7 @@
       <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
     </row>
-    <row r="52" spans="1:27" ht="13.2">
+    <row r="52" spans="1:27" ht="12.75">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="14"/>
@@ -4030,7 +4043,7 @@
       <c r="Z52" s="2"/>
       <c r="AA52" s="2"/>
     </row>
-    <row r="53" spans="1:27" ht="13.2">
+    <row r="53" spans="1:27" ht="12.75">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="14"/>
@@ -4059,7 +4072,7 @@
       <c r="Z53" s="2"/>
       <c r="AA53" s="2"/>
     </row>
-    <row r="54" spans="1:27" ht="13.2">
+    <row r="54" spans="1:27" ht="12.75">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="14"/>
@@ -4088,7 +4101,7 @@
       <c r="Z54" s="2"/>
       <c r="AA54" s="2"/>
     </row>
-    <row r="55" spans="1:27" ht="13.2">
+    <row r="55" spans="1:27" ht="12.75">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="14"/>
@@ -4117,7 +4130,7 @@
       <c r="Z55" s="2"/>
       <c r="AA55" s="2"/>
     </row>
-    <row r="56" spans="1:27" ht="13.2">
+    <row r="56" spans="1:27" ht="12.75">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="14"/>
@@ -4146,7 +4159,7 @@
       <c r="Z56" s="2"/>
       <c r="AA56" s="2"/>
     </row>
-    <row r="57" spans="1:27" ht="13.2">
+    <row r="57" spans="1:27" ht="12.75">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="14"/>
@@ -4175,7 +4188,7 @@
       <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
     </row>
-    <row r="58" spans="1:27" ht="13.2">
+    <row r="58" spans="1:27" ht="12.75">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="14"/>
@@ -4204,7 +4217,7 @@
       <c r="Z58" s="2"/>
       <c r="AA58" s="2"/>
     </row>
-    <row r="59" spans="1:27" ht="13.2">
+    <row r="59" spans="1:27" ht="12.75">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="14"/>
@@ -4233,7 +4246,7 @@
       <c r="Z59" s="2"/>
       <c r="AA59" s="2"/>
     </row>
-    <row r="60" spans="1:27" ht="13.2">
+    <row r="60" spans="1:27" ht="12.75">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="14"/>
@@ -4262,7 +4275,7 @@
       <c r="Z60" s="2"/>
       <c r="AA60" s="2"/>
     </row>
-    <row r="61" spans="1:27" ht="13.2">
+    <row r="61" spans="1:27" ht="12.75">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="14"/>
@@ -4291,7 +4304,7 @@
       <c r="Z61" s="2"/>
       <c r="AA61" s="2"/>
     </row>
-    <row r="62" spans="1:27" ht="13.2">
+    <row r="62" spans="1:27" ht="12.75">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="14"/>
@@ -4320,7 +4333,7 @@
       <c r="Z62" s="2"/>
       <c r="AA62" s="2"/>
     </row>
-    <row r="63" spans="1:27" ht="13.2">
+    <row r="63" spans="1:27" ht="12.75">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="14"/>
@@ -4349,7 +4362,7 @@
       <c r="Z63" s="2"/>
       <c r="AA63" s="2"/>
     </row>
-    <row r="64" spans="1:27" ht="13.2">
+    <row r="64" spans="1:27" ht="12.75">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="14"/>
@@ -4378,7 +4391,7 @@
       <c r="Z64" s="2"/>
       <c r="AA64" s="2"/>
     </row>
-    <row r="65" spans="1:27" ht="13.2">
+    <row r="65" spans="1:27" ht="12.75">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="14"/>
@@ -4407,7 +4420,7 @@
       <c r="Z65" s="2"/>
       <c r="AA65" s="2"/>
     </row>
-    <row r="66" spans="1:27" ht="13.2">
+    <row r="66" spans="1:27" ht="12.75">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="14"/>
@@ -4436,7 +4449,7 @@
       <c r="Z66" s="2"/>
       <c r="AA66" s="2"/>
     </row>
-    <row r="67" spans="1:27" ht="13.2">
+    <row r="67" spans="1:27" ht="12.75">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="14"/>
@@ -4465,7 +4478,7 @@
       <c r="Z67" s="2"/>
       <c r="AA67" s="2"/>
     </row>
-    <row r="68" spans="1:27" ht="13.2">
+    <row r="68" spans="1:27" ht="12.75">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="14"/>
@@ -4494,7 +4507,7 @@
       <c r="Z68" s="2"/>
       <c r="AA68" s="2"/>
     </row>
-    <row r="69" spans="1:27" ht="13.2">
+    <row r="69" spans="1:27" ht="12.75">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="14"/>
@@ -4523,7 +4536,7 @@
       <c r="Z69" s="2"/>
       <c r="AA69" s="2"/>
     </row>
-    <row r="70" spans="1:27" ht="13.2">
+    <row r="70" spans="1:27" ht="12.75">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="14"/>
@@ -4552,7 +4565,7 @@
       <c r="Z70" s="2"/>
       <c r="AA70" s="2"/>
     </row>
-    <row r="71" spans="1:27" ht="13.2">
+    <row r="71" spans="1:27" ht="12.75">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="14"/>
@@ -4581,7 +4594,7 @@
       <c r="Z71" s="2"/>
       <c r="AA71" s="2"/>
     </row>
-    <row r="72" spans="1:27" ht="13.2">
+    <row r="72" spans="1:27" ht="12.75">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="14"/>
@@ -4610,7 +4623,7 @@
       <c r="Z72" s="2"/>
       <c r="AA72" s="2"/>
     </row>
-    <row r="73" spans="1:27" ht="13.2">
+    <row r="73" spans="1:27" ht="12.75">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="14"/>
@@ -4639,7 +4652,7 @@
       <c r="Z73" s="2"/>
       <c r="AA73" s="2"/>
     </row>
-    <row r="74" spans="1:27" ht="13.2">
+    <row r="74" spans="1:27" ht="12.75">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="14"/>
@@ -4668,7 +4681,7 @@
       <c r="Z74" s="2"/>
       <c r="AA74" s="2"/>
     </row>
-    <row r="75" spans="1:27" ht="13.2">
+    <row r="75" spans="1:27" ht="12.75">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="14"/>
@@ -4697,7 +4710,7 @@
       <c r="Z75" s="2"/>
       <c r="AA75" s="2"/>
     </row>
-    <row r="76" spans="1:27" ht="13.2">
+    <row r="76" spans="1:27" ht="12.75">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="14"/>
@@ -4726,7 +4739,7 @@
       <c r="Z76" s="2"/>
       <c r="AA76" s="2"/>
     </row>
-    <row r="77" spans="1:27" ht="13.2">
+    <row r="77" spans="1:27" ht="12.75">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="14"/>
@@ -4755,7 +4768,7 @@
       <c r="Z77" s="2"/>
       <c r="AA77" s="2"/>
     </row>
-    <row r="78" spans="1:27" ht="13.2">
+    <row r="78" spans="1:27" ht="12.75">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="14"/>
@@ -4784,7 +4797,7 @@
       <c r="Z78" s="2"/>
       <c r="AA78" s="2"/>
     </row>
-    <row r="79" spans="1:27" ht="13.2">
+    <row r="79" spans="1:27" ht="12.75">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="14"/>
@@ -4813,7 +4826,7 @@
       <c r="Z79" s="2"/>
       <c r="AA79" s="2"/>
     </row>
-    <row r="80" spans="1:27" ht="13.2">
+    <row r="80" spans="1:27" ht="12.75">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="14"/>
@@ -4842,7 +4855,7 @@
       <c r="Z80" s="2"/>
       <c r="AA80" s="2"/>
     </row>
-    <row r="81" spans="1:27" ht="13.2">
+    <row r="81" spans="1:27" ht="12.75">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="14"/>
@@ -4871,7 +4884,7 @@
       <c r="Z81" s="2"/>
       <c r="AA81" s="2"/>
     </row>
-    <row r="82" spans="1:27" ht="13.2">
+    <row r="82" spans="1:27" ht="12.75">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="14"/>
@@ -4900,7 +4913,7 @@
       <c r="Z82" s="2"/>
       <c r="AA82" s="2"/>
     </row>
-    <row r="83" spans="1:27" ht="13.2">
+    <row r="83" spans="1:27" ht="12.75">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="14"/>
@@ -4929,7 +4942,7 @@
       <c r="Z83" s="2"/>
       <c r="AA83" s="2"/>
     </row>
-    <row r="84" spans="1:27" ht="13.2">
+    <row r="84" spans="1:27" ht="12.75">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="14"/>
@@ -4958,7 +4971,7 @@
       <c r="Z84" s="2"/>
       <c r="AA84" s="2"/>
     </row>
-    <row r="85" spans="1:27" ht="13.2">
+    <row r="85" spans="1:27" ht="12.75">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="14"/>
@@ -4987,7 +5000,7 @@
       <c r="Z85" s="2"/>
       <c r="AA85" s="2"/>
     </row>
-    <row r="86" spans="1:27" ht="13.2">
+    <row r="86" spans="1:27" ht="12.75">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="14"/>
@@ -5016,7 +5029,7 @@
       <c r="Z86" s="2"/>
       <c r="AA86" s="2"/>
     </row>
-    <row r="87" spans="1:27" ht="13.2">
+    <row r="87" spans="1:27" ht="12.75">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="14"/>
@@ -5045,7 +5058,7 @@
       <c r="Z87" s="2"/>
       <c r="AA87" s="2"/>
     </row>
-    <row r="88" spans="1:27" ht="13.2">
+    <row r="88" spans="1:27" ht="12.75">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="14"/>
@@ -5074,7 +5087,7 @@
       <c r="Z88" s="2"/>
       <c r="AA88" s="2"/>
     </row>
-    <row r="89" spans="1:27" ht="13.2">
+    <row r="89" spans="1:27" ht="12.75">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="14"/>
@@ -5103,7 +5116,7 @@
       <c r="Z89" s="2"/>
       <c r="AA89" s="2"/>
     </row>
-    <row r="90" spans="1:27" ht="13.2">
+    <row r="90" spans="1:27" ht="12.75">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="14"/>
@@ -5132,7 +5145,7 @@
       <c r="Z90" s="2"/>
       <c r="AA90" s="2"/>
     </row>
-    <row r="91" spans="1:27" ht="13.2">
+    <row r="91" spans="1:27" ht="12.75">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="14"/>
@@ -5161,7 +5174,7 @@
       <c r="Z91" s="2"/>
       <c r="AA91" s="2"/>
     </row>
-    <row r="92" spans="1:27" ht="13.2">
+    <row r="92" spans="1:27" ht="12.75">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="14"/>
@@ -5190,7 +5203,7 @@
       <c r="Z92" s="2"/>
       <c r="AA92" s="2"/>
     </row>
-    <row r="93" spans="1:27" ht="13.2">
+    <row r="93" spans="1:27" ht="12.75">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="14"/>
@@ -5219,7 +5232,7 @@
       <c r="Z93" s="2"/>
       <c r="AA93" s="2"/>
     </row>
-    <row r="94" spans="1:27" ht="13.2">
+    <row r="94" spans="1:27" ht="12.75">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="14"/>
@@ -5248,7 +5261,7 @@
       <c r="Z94" s="2"/>
       <c r="AA94" s="2"/>
     </row>
-    <row r="95" spans="1:27" ht="13.2">
+    <row r="95" spans="1:27" ht="12.75">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="14"/>
@@ -5277,7 +5290,7 @@
       <c r="Z95" s="2"/>
       <c r="AA95" s="2"/>
     </row>
-    <row r="96" spans="1:27" ht="13.2">
+    <row r="96" spans="1:27" ht="12.75">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="14"/>
@@ -5306,7 +5319,7 @@
       <c r="Z96" s="2"/>
       <c r="AA96" s="2"/>
     </row>
-    <row r="97" spans="1:27" ht="13.2">
+    <row r="97" spans="1:27" ht="12.75">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="14"/>
@@ -5335,7 +5348,7 @@
       <c r="Z97" s="2"/>
       <c r="AA97" s="2"/>
     </row>
-    <row r="98" spans="1:27" ht="13.2">
+    <row r="98" spans="1:27" ht="12.75">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="14"/>
@@ -5364,7 +5377,7 @@
       <c r="Z98" s="2"/>
       <c r="AA98" s="2"/>
     </row>
-    <row r="99" spans="1:27" ht="13.2">
+    <row r="99" spans="1:27" ht="12.75">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="14"/>
@@ -5393,7 +5406,7 @@
       <c r="Z99" s="2"/>
       <c r="AA99" s="2"/>
     </row>
-    <row r="100" spans="1:27" ht="13.2">
+    <row r="100" spans="1:27" ht="12.75">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="14"/>
@@ -5422,7 +5435,7 @@
       <c r="Z100" s="2"/>
       <c r="AA100" s="2"/>
     </row>
-    <row r="101" spans="1:27" ht="13.2">
+    <row r="101" spans="1:27" ht="12.75">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="14"/>
@@ -5451,7 +5464,7 @@
       <c r="Z101" s="2"/>
       <c r="AA101" s="2"/>
     </row>
-    <row r="102" spans="1:27" ht="13.2">
+    <row r="102" spans="1:27" ht="12.75">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="14"/>
@@ -5480,7 +5493,7 @@
       <c r="Z102" s="2"/>
       <c r="AA102" s="2"/>
     </row>
-    <row r="103" spans="1:27" ht="13.2">
+    <row r="103" spans="1:27" ht="12.75">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="14"/>
@@ -5509,7 +5522,7 @@
       <c r="Z103" s="2"/>
       <c r="AA103" s="2"/>
     </row>
-    <row r="104" spans="1:27" ht="13.2">
+    <row r="104" spans="1:27" ht="12.75">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="14"/>
@@ -5538,7 +5551,7 @@
       <c r="Z104" s="2"/>
       <c r="AA104" s="2"/>
     </row>
-    <row r="105" spans="1:27" ht="13.2">
+    <row r="105" spans="1:27" ht="12.75">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="14"/>
@@ -5567,7 +5580,7 @@
       <c r="Z105" s="2"/>
       <c r="AA105" s="2"/>
     </row>
-    <row r="106" spans="1:27" ht="13.2">
+    <row r="106" spans="1:27" ht="12.75">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="14"/>
@@ -5596,7 +5609,7 @@
       <c r="Z106" s="2"/>
       <c r="AA106" s="2"/>
     </row>
-    <row r="107" spans="1:27" ht="13.2">
+    <row r="107" spans="1:27" ht="12.75">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="14"/>
@@ -5625,7 +5638,7 @@
       <c r="Z107" s="2"/>
       <c r="AA107" s="2"/>
     </row>
-    <row r="108" spans="1:27" ht="13.2">
+    <row r="108" spans="1:27" ht="12.75">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="14"/>
@@ -5654,7 +5667,7 @@
       <c r="Z108" s="2"/>
       <c r="AA108" s="2"/>
     </row>
-    <row r="109" spans="1:27" ht="13.2">
+    <row r="109" spans="1:27" ht="12.75">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="14"/>
@@ -5683,7 +5696,7 @@
       <c r="Z109" s="2"/>
       <c r="AA109" s="2"/>
     </row>
-    <row r="110" spans="1:27" ht="13.2">
+    <row r="110" spans="1:27" ht="12.75">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="14"/>
@@ -5712,7 +5725,7 @@
       <c r="Z110" s="2"/>
       <c r="AA110" s="2"/>
     </row>
-    <row r="111" spans="1:27" ht="13.2">
+    <row r="111" spans="1:27" ht="12.75">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="14"/>
@@ -5741,7 +5754,7 @@
       <c r="Z111" s="2"/>
       <c r="AA111" s="2"/>
     </row>
-    <row r="112" spans="1:27" ht="13.2">
+    <row r="112" spans="1:27" ht="12.75">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="14"/>
@@ -5770,7 +5783,7 @@
       <c r="Z112" s="2"/>
       <c r="AA112" s="2"/>
     </row>
-    <row r="113" spans="1:27" ht="13.2">
+    <row r="113" spans="1:27" ht="12.75">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="14"/>
@@ -5799,7 +5812,7 @@
       <c r="Z113" s="2"/>
       <c r="AA113" s="2"/>
     </row>
-    <row r="114" spans="1:27" ht="13.2">
+    <row r="114" spans="1:27" ht="12.75">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="14"/>
@@ -5828,7 +5841,7 @@
       <c r="Z114" s="2"/>
       <c r="AA114" s="2"/>
     </row>
-    <row r="115" spans="1:27" ht="13.2">
+    <row r="115" spans="1:27" ht="12.75">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="14"/>
@@ -5857,7 +5870,7 @@
       <c r="Z115" s="2"/>
       <c r="AA115" s="2"/>
     </row>
-    <row r="116" spans="1:27" ht="13.2">
+    <row r="116" spans="1:27" ht="12.75">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="14"/>
@@ -5886,7 +5899,7 @@
       <c r="Z116" s="2"/>
       <c r="AA116" s="2"/>
     </row>
-    <row r="117" spans="1:27" ht="13.2">
+    <row r="117" spans="1:27" ht="12.75">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="14"/>
@@ -5915,7 +5928,7 @@
       <c r="Z117" s="2"/>
       <c r="AA117" s="2"/>
     </row>
-    <row r="118" spans="1:27" ht="13.2">
+    <row r="118" spans="1:27" ht="12.75">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="14"/>
@@ -5944,7 +5957,7 @@
       <c r="Z118" s="2"/>
       <c r="AA118" s="2"/>
     </row>
-    <row r="119" spans="1:27" ht="13.2">
+    <row r="119" spans="1:27" ht="12.75">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="14"/>
@@ -5973,7 +5986,7 @@
       <c r="Z119" s="2"/>
       <c r="AA119" s="2"/>
     </row>
-    <row r="120" spans="1:27" ht="13.2">
+    <row r="120" spans="1:27" ht="12.75">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="14"/>
@@ -6002,7 +6015,7 @@
       <c r="Z120" s="2"/>
       <c r="AA120" s="2"/>
     </row>
-    <row r="121" spans="1:27" ht="13.2">
+    <row r="121" spans="1:27" ht="12.75">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="14"/>
@@ -6031,7 +6044,7 @@
       <c r="Z121" s="2"/>
       <c r="AA121" s="2"/>
     </row>
-    <row r="122" spans="1:27" ht="13.2">
+    <row r="122" spans="1:27" ht="12.75">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="14"/>
@@ -6060,7 +6073,7 @@
       <c r="Z122" s="2"/>
       <c r="AA122" s="2"/>
     </row>
-    <row r="123" spans="1:27" ht="13.2">
+    <row r="123" spans="1:27" ht="12.75">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="14"/>
@@ -6089,7 +6102,7 @@
       <c r="Z123" s="2"/>
       <c r="AA123" s="2"/>
     </row>
-    <row r="124" spans="1:27" ht="13.2">
+    <row r="124" spans="1:27" ht="12.75">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="14"/>
@@ -6118,7 +6131,7 @@
       <c r="Z124" s="2"/>
       <c r="AA124" s="2"/>
     </row>
-    <row r="125" spans="1:27" ht="13.2">
+    <row r="125" spans="1:27" ht="12.75">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="14"/>
@@ -6147,7 +6160,7 @@
       <c r="Z125" s="2"/>
       <c r="AA125" s="2"/>
     </row>
-    <row r="126" spans="1:27" ht="13.2">
+    <row r="126" spans="1:27" ht="12.75">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="14"/>
@@ -6176,7 +6189,7 @@
       <c r="Z126" s="2"/>
       <c r="AA126" s="2"/>
     </row>
-    <row r="127" spans="1:27" ht="13.2">
+    <row r="127" spans="1:27" ht="12.75">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="14"/>
@@ -6205,7 +6218,7 @@
       <c r="Z127" s="2"/>
       <c r="AA127" s="2"/>
     </row>
-    <row r="128" spans="1:27" ht="13.2">
+    <row r="128" spans="1:27" ht="12.75">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="14"/>
@@ -6234,7 +6247,7 @@
       <c r="Z128" s="2"/>
       <c r="AA128" s="2"/>
     </row>
-    <row r="129" spans="1:27" ht="13.2">
+    <row r="129" spans="1:27" ht="12.75">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="14"/>
@@ -6263,7 +6276,7 @@
       <c r="Z129" s="2"/>
       <c r="AA129" s="2"/>
     </row>
-    <row r="130" spans="1:27" ht="13.2">
+    <row r="130" spans="1:27" ht="12.75">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="14"/>
@@ -6292,7 +6305,7 @@
       <c r="Z130" s="2"/>
       <c r="AA130" s="2"/>
     </row>
-    <row r="131" spans="1:27" ht="13.2">
+    <row r="131" spans="1:27" ht="12.75">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="14"/>
@@ -6321,7 +6334,7 @@
       <c r="Z131" s="2"/>
       <c r="AA131" s="2"/>
     </row>
-    <row r="132" spans="1:27" ht="13.2">
+    <row r="132" spans="1:27" ht="12.75">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="14"/>
@@ -6350,7 +6363,7 @@
       <c r="Z132" s="2"/>
       <c r="AA132" s="2"/>
     </row>
-    <row r="133" spans="1:27" ht="13.2">
+    <row r="133" spans="1:27" ht="12.75">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="14"/>
@@ -6379,7 +6392,7 @@
       <c r="Z133" s="2"/>
       <c r="AA133" s="2"/>
     </row>
-    <row r="134" spans="1:27" ht="13.2">
+    <row r="134" spans="1:27" ht="12.75">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="14"/>
@@ -6408,7 +6421,7 @@
       <c r="Z134" s="2"/>
       <c r="AA134" s="2"/>
     </row>
-    <row r="135" spans="1:27" ht="13.2">
+    <row r="135" spans="1:27" ht="12.75">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="14"/>
@@ -6437,7 +6450,7 @@
       <c r="Z135" s="2"/>
       <c r="AA135" s="2"/>
     </row>
-    <row r="136" spans="1:27" ht="13.2">
+    <row r="136" spans="1:27" ht="12.75">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="14"/>
@@ -6466,7 +6479,7 @@
       <c r="Z136" s="2"/>
       <c r="AA136" s="2"/>
     </row>
-    <row r="137" spans="1:27" ht="13.2">
+    <row r="137" spans="1:27" ht="12.75">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="14"/>
@@ -6495,7 +6508,7 @@
       <c r="Z137" s="2"/>
       <c r="AA137" s="2"/>
     </row>
-    <row r="138" spans="1:27" ht="13.2">
+    <row r="138" spans="1:27" ht="12.75">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="14"/>
@@ -6524,7 +6537,7 @@
       <c r="Z138" s="2"/>
       <c r="AA138" s="2"/>
     </row>
-    <row r="139" spans="1:27" ht="13.2">
+    <row r="139" spans="1:27" ht="12.75">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="14"/>
@@ -6553,7 +6566,7 @@
       <c r="Z139" s="2"/>
       <c r="AA139" s="2"/>
     </row>
-    <row r="140" spans="1:27" ht="13.2">
+    <row r="140" spans="1:27" ht="12.75">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="14"/>
@@ -6582,7 +6595,7 @@
       <c r="Z140" s="2"/>
       <c r="AA140" s="2"/>
     </row>
-    <row r="141" spans="1:27" ht="13.2">
+    <row r="141" spans="1:27" ht="12.75">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="14"/>
@@ -6611,7 +6624,7 @@
       <c r="Z141" s="2"/>
       <c r="AA141" s="2"/>
     </row>
-    <row r="142" spans="1:27" ht="13.2">
+    <row r="142" spans="1:27" ht="12.75">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="14"/>
@@ -6640,7 +6653,7 @@
       <c r="Z142" s="2"/>
       <c r="AA142" s="2"/>
     </row>
-    <row r="143" spans="1:27" ht="13.2">
+    <row r="143" spans="1:27" ht="12.75">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="14"/>
@@ -6669,7 +6682,7 @@
       <c r="Z143" s="2"/>
       <c r="AA143" s="2"/>
     </row>
-    <row r="144" spans="1:27" ht="13.2">
+    <row r="144" spans="1:27" ht="12.75">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="14"/>
@@ -6698,7 +6711,7 @@
       <c r="Z144" s="2"/>
       <c r="AA144" s="2"/>
     </row>
-    <row r="145" spans="1:27" ht="13.2">
+    <row r="145" spans="1:27" ht="12.75">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="14"/>
@@ -6727,7 +6740,7 @@
       <c r="Z145" s="2"/>
       <c r="AA145" s="2"/>
     </row>
-    <row r="146" spans="1:27" ht="13.2">
+    <row r="146" spans="1:27" ht="12.75">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="14"/>
@@ -6756,7 +6769,7 @@
       <c r="Z146" s="2"/>
       <c r="AA146" s="2"/>
     </row>
-    <row r="147" spans="1:27" ht="13.2">
+    <row r="147" spans="1:27" ht="12.75">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="14"/>
@@ -6785,7 +6798,7 @@
       <c r="Z147" s="2"/>
       <c r="AA147" s="2"/>
     </row>
-    <row r="148" spans="1:27" ht="13.2">
+    <row r="148" spans="1:27" ht="12.75">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="14"/>
@@ -6814,7 +6827,7 @@
       <c r="Z148" s="2"/>
       <c r="AA148" s="2"/>
     </row>
-    <row r="149" spans="1:27" ht="13.2">
+    <row r="149" spans="1:27" ht="12.75">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="14"/>
@@ -6843,7 +6856,7 @@
       <c r="Z149" s="2"/>
       <c r="AA149" s="2"/>
     </row>
-    <row r="150" spans="1:27" ht="13.2">
+    <row r="150" spans="1:27" ht="12.75">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="14"/>
@@ -6872,7 +6885,7 @@
       <c r="Z150" s="2"/>
       <c r="AA150" s="2"/>
     </row>
-    <row r="151" spans="1:27" ht="13.2">
+    <row r="151" spans="1:27" ht="12.75">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="14"/>
@@ -6901,7 +6914,7 @@
       <c r="Z151" s="2"/>
       <c r="AA151" s="2"/>
     </row>
-    <row r="152" spans="1:27" ht="13.2">
+    <row r="152" spans="1:27" ht="12.75">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="14"/>
@@ -6930,7 +6943,7 @@
       <c r="Z152" s="2"/>
       <c r="AA152" s="2"/>
     </row>
-    <row r="153" spans="1:27" ht="13.2">
+    <row r="153" spans="1:27" ht="12.75">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="14"/>
@@ -6959,7 +6972,7 @@
       <c r="Z153" s="2"/>
       <c r="AA153" s="2"/>
     </row>
-    <row r="154" spans="1:27" ht="13.2">
+    <row r="154" spans="1:27" ht="12.75">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="14"/>
@@ -6988,7 +7001,7 @@
       <c r="Z154" s="2"/>
       <c r="AA154" s="2"/>
     </row>
-    <row r="155" spans="1:27" ht="13.2">
+    <row r="155" spans="1:27" ht="12.75">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="14"/>
@@ -7017,7 +7030,7 @@
       <c r="Z155" s="2"/>
       <c r="AA155" s="2"/>
     </row>
-    <row r="156" spans="1:27" ht="13.2">
+    <row r="156" spans="1:27" ht="12.75">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="14"/>
@@ -7046,7 +7059,7 @@
       <c r="Z156" s="2"/>
       <c r="AA156" s="2"/>
     </row>
-    <row r="157" spans="1:27" ht="13.2">
+    <row r="157" spans="1:27" ht="12.75">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="14"/>
@@ -7075,7 +7088,7 @@
       <c r="Z157" s="2"/>
       <c r="AA157" s="2"/>
     </row>
-    <row r="158" spans="1:27" ht="13.2">
+    <row r="158" spans="1:27" ht="12.75">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="14"/>
@@ -7104,7 +7117,7 @@
       <c r="Z158" s="2"/>
       <c r="AA158" s="2"/>
     </row>
-    <row r="159" spans="1:27" ht="13.2">
+    <row r="159" spans="1:27" ht="12.75">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="14"/>
@@ -7133,7 +7146,7 @@
       <c r="Z159" s="2"/>
       <c r="AA159" s="2"/>
     </row>
-    <row r="160" spans="1:27" ht="13.2">
+    <row r="160" spans="1:27" ht="12.75">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="14"/>
@@ -7162,7 +7175,7 @@
       <c r="Z160" s="2"/>
       <c r="AA160" s="2"/>
     </row>
-    <row r="161" spans="1:27" ht="13.2">
+    <row r="161" spans="1:27" ht="12.75">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="14"/>
@@ -7191,7 +7204,7 @@
       <c r="Z161" s="2"/>
       <c r="AA161" s="2"/>
     </row>
-    <row r="162" spans="1:27" ht="13.2">
+    <row r="162" spans="1:27" ht="12.75">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="14"/>
@@ -7220,7 +7233,7 @@
       <c r="Z162" s="2"/>
       <c r="AA162" s="2"/>
     </row>
-    <row r="163" spans="1:27" ht="13.2">
+    <row r="163" spans="1:27" ht="12.75">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="14"/>
@@ -7249,7 +7262,7 @@
       <c r="Z163" s="2"/>
       <c r="AA163" s="2"/>
     </row>
-    <row r="164" spans="1:27" ht="13.2">
+    <row r="164" spans="1:27" ht="12.75">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="14"/>
@@ -7278,7 +7291,7 @@
       <c r="Z164" s="2"/>
       <c r="AA164" s="2"/>
     </row>
-    <row r="165" spans="1:27" ht="13.2">
+    <row r="165" spans="1:27" ht="12.75">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="14"/>
@@ -7307,7 +7320,7 @@
       <c r="Z165" s="2"/>
       <c r="AA165" s="2"/>
     </row>
-    <row r="166" spans="1:27" ht="13.2">
+    <row r="166" spans="1:27" ht="12.75">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="14"/>
@@ -7336,7 +7349,7 @@
       <c r="Z166" s="2"/>
       <c r="AA166" s="2"/>
     </row>
-    <row r="167" spans="1:27" ht="13.2">
+    <row r="167" spans="1:27" ht="12.75">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="14"/>
@@ -7365,7 +7378,7 @@
       <c r="Z167" s="2"/>
       <c r="AA167" s="2"/>
     </row>
-    <row r="168" spans="1:27" ht="13.2">
+    <row r="168" spans="1:27" ht="12.75">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="14"/>
@@ -7394,7 +7407,7 @@
       <c r="Z168" s="2"/>
       <c r="AA168" s="2"/>
     </row>
-    <row r="169" spans="1:27" ht="13.2">
+    <row r="169" spans="1:27" ht="12.75">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="14"/>
@@ -7423,7 +7436,7 @@
       <c r="Z169" s="2"/>
       <c r="AA169" s="2"/>
     </row>
-    <row r="170" spans="1:27" ht="13.2">
+    <row r="170" spans="1:27" ht="12.75">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="14"/>
@@ -7452,7 +7465,7 @@
       <c r="Z170" s="2"/>
       <c r="AA170" s="2"/>
     </row>
-    <row r="171" spans="1:27" ht="13.2">
+    <row r="171" spans="1:27" ht="12.75">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="14"/>
@@ -7481,7 +7494,7 @@
       <c r="Z171" s="2"/>
       <c r="AA171" s="2"/>
     </row>
-    <row r="172" spans="1:27" ht="13.2">
+    <row r="172" spans="1:27" ht="12.75">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="14"/>
@@ -7510,7 +7523,7 @@
       <c r="Z172" s="2"/>
       <c r="AA172" s="2"/>
     </row>
-    <row r="173" spans="1:27" ht="13.2">
+    <row r="173" spans="1:27" ht="12.75">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="14"/>
@@ -7539,7 +7552,7 @@
       <c r="Z173" s="2"/>
       <c r="AA173" s="2"/>
     </row>
-    <row r="174" spans="1:27" ht="13.2">
+    <row r="174" spans="1:27" ht="12.75">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="14"/>
@@ -7568,7 +7581,7 @@
       <c r="Z174" s="2"/>
       <c r="AA174" s="2"/>
     </row>
-    <row r="175" spans="1:27" ht="13.2">
+    <row r="175" spans="1:27" ht="12.75">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="14"/>
@@ -7597,7 +7610,7 @@
       <c r="Z175" s="2"/>
       <c r="AA175" s="2"/>
     </row>
-    <row r="176" spans="1:27" ht="13.2">
+    <row r="176" spans="1:27" ht="12.75">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="14"/>
@@ -7626,7 +7639,7 @@
       <c r="Z176" s="2"/>
       <c r="AA176" s="2"/>
     </row>
-    <row r="177" spans="1:27" ht="13.2">
+    <row r="177" spans="1:27" ht="12.75">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="14"/>
@@ -7655,7 +7668,7 @@
       <c r="Z177" s="2"/>
       <c r="AA177" s="2"/>
     </row>
-    <row r="178" spans="1:27" ht="13.2">
+    <row r="178" spans="1:27" ht="12.75">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="14"/>
@@ -7684,7 +7697,7 @@
       <c r="Z178" s="2"/>
       <c r="AA178" s="2"/>
     </row>
-    <row r="179" spans="1:27" ht="13.2">
+    <row r="179" spans="1:27" ht="12.75">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="14"/>
@@ -7713,7 +7726,7 @@
       <c r="Z179" s="2"/>
       <c r="AA179" s="2"/>
     </row>
-    <row r="180" spans="1:27" ht="13.2">
+    <row r="180" spans="1:27" ht="12.75">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="14"/>
@@ -7742,7 +7755,7 @@
       <c r="Z180" s="2"/>
       <c r="AA180" s="2"/>
     </row>
-    <row r="181" spans="1:27" ht="13.2">
+    <row r="181" spans="1:27" ht="12.75">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="14"/>
@@ -7771,7 +7784,7 @@
       <c r="Z181" s="2"/>
       <c r="AA181" s="2"/>
     </row>
-    <row r="182" spans="1:27" ht="13.2">
+    <row r="182" spans="1:27" ht="12.75">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="14"/>
@@ -7800,7 +7813,7 @@
       <c r="Z182" s="2"/>
       <c r="AA182" s="2"/>
     </row>
-    <row r="183" spans="1:27" ht="13.2">
+    <row r="183" spans="1:27" ht="12.75">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="14"/>
@@ -7829,7 +7842,7 @@
       <c r="Z183" s="2"/>
       <c r="AA183" s="2"/>
     </row>
-    <row r="184" spans="1:27" ht="13.2">
+    <row r="184" spans="1:27" ht="12.75">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="14"/>
@@ -7858,7 +7871,7 @@
       <c r="Z184" s="2"/>
       <c r="AA184" s="2"/>
     </row>
-    <row r="185" spans="1:27" ht="13.2">
+    <row r="185" spans="1:27" ht="12.75">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="14"/>
@@ -7887,7 +7900,7 @@
       <c r="Z185" s="2"/>
       <c r="AA185" s="2"/>
     </row>
-    <row r="186" spans="1:27" ht="13.2">
+    <row r="186" spans="1:27" ht="12.75">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="14"/>
@@ -7916,7 +7929,7 @@
       <c r="Z186" s="2"/>
       <c r="AA186" s="2"/>
     </row>
-    <row r="187" spans="1:27" ht="13.2">
+    <row r="187" spans="1:27" ht="12.75">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="14"/>
@@ -7945,7 +7958,7 @@
       <c r="Z187" s="2"/>
       <c r="AA187" s="2"/>
     </row>
-    <row r="188" spans="1:27" ht="13.2">
+    <row r="188" spans="1:27" ht="12.75">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="14"/>
@@ -7974,7 +7987,7 @@
       <c r="Z188" s="2"/>
       <c r="AA188" s="2"/>
     </row>
-    <row r="189" spans="1:27" ht="13.2">
+    <row r="189" spans="1:27" ht="12.75">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="14"/>
@@ -8003,7 +8016,7 @@
       <c r="Z189" s="2"/>
       <c r="AA189" s="2"/>
     </row>
-    <row r="190" spans="1:27" ht="13.2">
+    <row r="190" spans="1:27" ht="12.75">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="14"/>
@@ -8032,7 +8045,7 @@
       <c r="Z190" s="2"/>
       <c r="AA190" s="2"/>
     </row>
-    <row r="191" spans="1:27" ht="13.2">
+    <row r="191" spans="1:27" ht="12.75">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="14"/>
@@ -8061,7 +8074,7 @@
       <c r="Z191" s="2"/>
       <c r="AA191" s="2"/>
     </row>
-    <row r="192" spans="1:27" ht="13.2">
+    <row r="192" spans="1:27" ht="12.75">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="14"/>
@@ -8090,7 +8103,7 @@
       <c r="Z192" s="2"/>
       <c r="AA192" s="2"/>
     </row>
-    <row r="193" spans="1:27" ht="13.2">
+    <row r="193" spans="1:27" ht="12.75">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="14"/>
@@ -8119,7 +8132,7 @@
       <c r="Z193" s="2"/>
       <c r="AA193" s="2"/>
     </row>
-    <row r="194" spans="1:27" ht="13.2">
+    <row r="194" spans="1:27" ht="12.75">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="14"/>
@@ -8148,7 +8161,7 @@
       <c r="Z194" s="2"/>
       <c r="AA194" s="2"/>
     </row>
-    <row r="195" spans="1:27" ht="13.2">
+    <row r="195" spans="1:27" ht="12.75">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="14"/>
@@ -8177,7 +8190,7 @@
       <c r="Z195" s="2"/>
       <c r="AA195" s="2"/>
     </row>
-    <row r="196" spans="1:27" ht="13.2">
+    <row r="196" spans="1:27" ht="12.75">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="14"/>
@@ -8206,7 +8219,7 @@
       <c r="Z196" s="2"/>
       <c r="AA196" s="2"/>
     </row>
-    <row r="197" spans="1:27" ht="13.2">
+    <row r="197" spans="1:27" ht="12.75">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="14"/>
@@ -8235,7 +8248,7 @@
       <c r="Z197" s="2"/>
       <c r="AA197" s="2"/>
     </row>
-    <row r="198" spans="1:27" ht="13.2">
+    <row r="198" spans="1:27" ht="12.75">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="14"/>
@@ -8264,7 +8277,7 @@
       <c r="Z198" s="2"/>
       <c r="AA198" s="2"/>
     </row>
-    <row r="199" spans="1:27" ht="13.2">
+    <row r="199" spans="1:27" ht="12.75">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="14"/>
@@ -8293,7 +8306,7 @@
       <c r="Z199" s="2"/>
       <c r="AA199" s="2"/>
     </row>
-    <row r="200" spans="1:27" ht="13.2">
+    <row r="200" spans="1:27" ht="12.75">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="14"/>
@@ -8322,7 +8335,7 @@
       <c r="Z200" s="2"/>
       <c r="AA200" s="2"/>
     </row>
-    <row r="201" spans="1:27" ht="13.2">
+    <row r="201" spans="1:27" ht="12.75">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="14"/>
@@ -8351,7 +8364,7 @@
       <c r="Z201" s="2"/>
       <c r="AA201" s="2"/>
     </row>
-    <row r="202" spans="1:27" ht="13.2">
+    <row r="202" spans="1:27" ht="12.75">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="14"/>
@@ -8380,7 +8393,7 @@
       <c r="Z202" s="2"/>
       <c r="AA202" s="2"/>
     </row>
-    <row r="203" spans="1:27" ht="13.2">
+    <row r="203" spans="1:27" ht="12.75">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="14"/>
@@ -8409,7 +8422,7 @@
       <c r="Z203" s="2"/>
       <c r="AA203" s="2"/>
     </row>
-    <row r="204" spans="1:27" ht="13.2">
+    <row r="204" spans="1:27" ht="12.75">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="14"/>
@@ -8438,7 +8451,7 @@
       <c r="Z204" s="2"/>
       <c r="AA204" s="2"/>
     </row>
-    <row r="205" spans="1:27" ht="13.2">
+    <row r="205" spans="1:27" ht="12.75">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="14"/>
@@ -8467,7 +8480,7 @@
       <c r="Z205" s="2"/>
       <c r="AA205" s="2"/>
     </row>
-    <row r="206" spans="1:27" ht="13.2">
+    <row r="206" spans="1:27" ht="12.75">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="14"/>
@@ -8496,7 +8509,7 @@
       <c r="Z206" s="2"/>
       <c r="AA206" s="2"/>
     </row>
-    <row r="207" spans="1:27" ht="13.2">
+    <row r="207" spans="1:27" ht="12.75">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="14"/>
@@ -8525,7 +8538,7 @@
       <c r="Z207" s="2"/>
       <c r="AA207" s="2"/>
     </row>
-    <row r="208" spans="1:27" ht="13.2">
+    <row r="208" spans="1:27" ht="12.75">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="14"/>
@@ -8554,7 +8567,7 @@
       <c r="Z208" s="2"/>
       <c r="AA208" s="2"/>
     </row>
-    <row r="209" spans="1:27" ht="13.2">
+    <row r="209" spans="1:27" ht="12.75">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="14"/>
@@ -8583,7 +8596,7 @@
       <c r="Z209" s="2"/>
       <c r="AA209" s="2"/>
     </row>
-    <row r="210" spans="1:27" ht="13.2">
+    <row r="210" spans="1:27" ht="12.75">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="14"/>
@@ -8612,7 +8625,7 @@
       <c r="Z210" s="2"/>
       <c r="AA210" s="2"/>
     </row>
-    <row r="211" spans="1:27" ht="13.2">
+    <row r="211" spans="1:27" ht="12.75">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="14"/>
@@ -8641,7 +8654,7 @@
       <c r="Z211" s="2"/>
       <c r="AA211" s="2"/>
     </row>
-    <row r="212" spans="1:27" ht="13.2">
+    <row r="212" spans="1:27" ht="12.75">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="14"/>
@@ -8670,7 +8683,7 @@
       <c r="Z212" s="2"/>
       <c r="AA212" s="2"/>
     </row>
-    <row r="213" spans="1:27" ht="13.2">
+    <row r="213" spans="1:27" ht="12.75">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="14"/>
@@ -8699,7 +8712,7 @@
       <c r="Z213" s="2"/>
       <c r="AA213" s="2"/>
     </row>
-    <row r="214" spans="1:27" ht="13.2">
+    <row r="214" spans="1:27" ht="12.75">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="14"/>
@@ -8728,7 +8741,7 @@
       <c r="Z214" s="2"/>
       <c r="AA214" s="2"/>
     </row>
-    <row r="215" spans="1:27" ht="13.2">
+    <row r="215" spans="1:27" ht="12.75">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="14"/>
@@ -8757,7 +8770,7 @@
       <c r="Z215" s="2"/>
       <c r="AA215" s="2"/>
     </row>
-    <row r="216" spans="1:27" ht="13.2">
+    <row r="216" spans="1:27" ht="12.75">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="14"/>
@@ -8786,7 +8799,7 @@
       <c r="Z216" s="2"/>
       <c r="AA216" s="2"/>
     </row>
-    <row r="217" spans="1:27" ht="13.2">
+    <row r="217" spans="1:27" ht="12.75">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="14"/>
@@ -8815,7 +8828,7 @@
       <c r="Z217" s="2"/>
       <c r="AA217" s="2"/>
     </row>
-    <row r="218" spans="1:27" ht="13.2">
+    <row r="218" spans="1:27" ht="12.75">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="14"/>
@@ -8844,7 +8857,7 @@
       <c r="Z218" s="2"/>
       <c r="AA218" s="2"/>
     </row>
-    <row r="219" spans="1:27" ht="13.2">
+    <row r="219" spans="1:27" ht="12.75">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="14"/>
@@ -8873,7 +8886,7 @@
       <c r="Z219" s="2"/>
       <c r="AA219" s="2"/>
     </row>
-    <row r="220" spans="1:27" ht="13.2">
+    <row r="220" spans="1:27" ht="12.75">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="14"/>
@@ -8902,7 +8915,7 @@
       <c r="Z220" s="2"/>
       <c r="AA220" s="2"/>
     </row>
-    <row r="221" spans="1:27" ht="13.2">
+    <row r="221" spans="1:27" ht="12.75">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="14"/>
@@ -8931,7 +8944,7 @@
       <c r="Z221" s="2"/>
       <c r="AA221" s="2"/>
     </row>
-    <row r="222" spans="1:27" ht="13.2">
+    <row r="222" spans="1:27" ht="12.75">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="14"/>
@@ -8960,7 +8973,7 @@
       <c r="Z222" s="2"/>
       <c r="AA222" s="2"/>
     </row>
-    <row r="223" spans="1:27" ht="13.2">
+    <row r="223" spans="1:27" ht="12.75">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="14"/>
@@ -8989,7 +9002,7 @@
       <c r="Z223" s="2"/>
       <c r="AA223" s="2"/>
     </row>
-    <row r="224" spans="1:27" ht="13.2">
+    <row r="224" spans="1:27" ht="12.75">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="14"/>
@@ -9018,7 +9031,7 @@
       <c r="Z224" s="2"/>
       <c r="AA224" s="2"/>
     </row>
-    <row r="225" spans="1:27" ht="13.2">
+    <row r="225" spans="1:27" ht="12.75">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="14"/>
@@ -9047,7 +9060,7 @@
       <c r="Z225" s="2"/>
       <c r="AA225" s="2"/>
     </row>
-    <row r="226" spans="1:27" ht="13.2">
+    <row r="226" spans="1:27" ht="12.75">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="14"/>
@@ -9076,7 +9089,7 @@
       <c r="Z226" s="2"/>
       <c r="AA226" s="2"/>
     </row>
-    <row r="227" spans="1:27" ht="13.2">
+    <row r="227" spans="1:27" ht="12.75">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="14"/>
@@ -9105,7 +9118,7 @@
       <c r="Z227" s="2"/>
       <c r="AA227" s="2"/>
     </row>
-    <row r="228" spans="1:27" ht="13.2">
+    <row r="228" spans="1:27" ht="12.75">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="14"/>
@@ -9134,7 +9147,7 @@
       <c r="Z228" s="2"/>
       <c r="AA228" s="2"/>
     </row>
-    <row r="229" spans="1:27" ht="13.2">
+    <row r="229" spans="1:27" ht="12.75">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="14"/>
@@ -9163,7 +9176,7 @@
       <c r="Z229" s="2"/>
       <c r="AA229" s="2"/>
     </row>
-    <row r="230" spans="1:27" ht="13.2">
+    <row r="230" spans="1:27" ht="12.75">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="14"/>
@@ -9192,7 +9205,7 @@
       <c r="Z230" s="2"/>
       <c r="AA230" s="2"/>
     </row>
-    <row r="231" spans="1:27" ht="13.2">
+    <row r="231" spans="1:27" ht="12.75">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="14"/>
@@ -9221,7 +9234,7 @@
       <c r="Z231" s="2"/>
       <c r="AA231" s="2"/>
     </row>
-    <row r="232" spans="1:27" ht="13.2">
+    <row r="232" spans="1:27" ht="12.75">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="14"/>
@@ -9250,7 +9263,7 @@
       <c r="Z232" s="2"/>
       <c r="AA232" s="2"/>
     </row>
-    <row r="233" spans="1:27" ht="13.2">
+    <row r="233" spans="1:27" ht="12.75">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="14"/>
@@ -9279,7 +9292,7 @@
       <c r="Z233" s="2"/>
       <c r="AA233" s="2"/>
     </row>
-    <row r="234" spans="1:27" ht="13.2">
+    <row r="234" spans="1:27" ht="12.75">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="14"/>
@@ -9308,7 +9321,7 @@
       <c r="Z234" s="2"/>
       <c r="AA234" s="2"/>
     </row>
-    <row r="235" spans="1:27" ht="13.2">
+    <row r="235" spans="1:27" ht="12.75">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="14"/>
@@ -9337,7 +9350,7 @@
       <c r="Z235" s="2"/>
       <c r="AA235" s="2"/>
     </row>
-    <row r="236" spans="1:27" ht="13.2">
+    <row r="236" spans="1:27" ht="12.75">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="14"/>
@@ -9366,7 +9379,7 @@
       <c r="Z236" s="2"/>
       <c r="AA236" s="2"/>
     </row>
-    <row r="237" spans="1:27" ht="13.2">
+    <row r="237" spans="1:27" ht="12.75">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="14"/>
@@ -9395,7 +9408,7 @@
       <c r="Z237" s="2"/>
       <c r="AA237" s="2"/>
     </row>
-    <row r="238" spans="1:27" ht="13.2">
+    <row r="238" spans="1:27" ht="12.75">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="14"/>
@@ -9424,7 +9437,7 @@
       <c r="Z238" s="2"/>
       <c r="AA238" s="2"/>
     </row>
-    <row r="239" spans="1:27" ht="13.2">
+    <row r="239" spans="1:27" ht="12.75">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="14"/>
@@ -9453,7 +9466,7 @@
       <c r="Z239" s="2"/>
       <c r="AA239" s="2"/>
     </row>
-    <row r="240" spans="1:27" ht="13.2">
+    <row r="240" spans="1:27" ht="12.75">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="14"/>
@@ -9482,7 +9495,7 @@
       <c r="Z240" s="2"/>
       <c r="AA240" s="2"/>
     </row>
-    <row r="241" spans="1:27" ht="13.2">
+    <row r="241" spans="1:27" ht="12.75">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="14"/>
@@ -9511,7 +9524,7 @@
       <c r="Z241" s="2"/>
       <c r="AA241" s="2"/>
     </row>
-    <row r="242" spans="1:27" ht="13.2">
+    <row r="242" spans="1:27" ht="12.75">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="14"/>
@@ -9540,7 +9553,7 @@
       <c r="Z242" s="2"/>
       <c r="AA242" s="2"/>
     </row>
-    <row r="243" spans="1:27" ht="13.2">
+    <row r="243" spans="1:27" ht="12.75">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="14"/>
@@ -9569,7 +9582,7 @@
       <c r="Z243" s="2"/>
       <c r="AA243" s="2"/>
     </row>
-    <row r="244" spans="1:27" ht="13.2">
+    <row r="244" spans="1:27" ht="12.75">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="14"/>
@@ -9598,7 +9611,7 @@
       <c r="Z244" s="2"/>
       <c r="AA244" s="2"/>
     </row>
-    <row r="245" spans="1:27" ht="13.2">
+    <row r="245" spans="1:27" ht="12.75">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="14"/>
@@ -9627,7 +9640,7 @@
       <c r="Z245" s="2"/>
       <c r="AA245" s="2"/>
     </row>
-    <row r="246" spans="1:27" ht="13.2">
+    <row r="246" spans="1:27" ht="12.75">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="14"/>
@@ -9656,7 +9669,7 @@
       <c r="Z246" s="2"/>
       <c r="AA246" s="2"/>
     </row>
-    <row r="247" spans="1:27" ht="13.2">
+    <row r="247" spans="1:27" ht="12.75">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="14"/>
@@ -9685,7 +9698,7 @@
       <c r="Z247" s="2"/>
       <c r="AA247" s="2"/>
     </row>
-    <row r="248" spans="1:27" ht="13.2">
+    <row r="248" spans="1:27" ht="12.75">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="14"/>
@@ -9714,7 +9727,7 @@
       <c r="Z248" s="2"/>
       <c r="AA248" s="2"/>
     </row>
-    <row r="249" spans="1:27" ht="13.2">
+    <row r="249" spans="1:27" ht="12.75">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="14"/>
@@ -9743,7 +9756,7 @@
       <c r="Z249" s="2"/>
       <c r="AA249" s="2"/>
     </row>
-    <row r="250" spans="1:27" ht="13.2">
+    <row r="250" spans="1:27" ht="12.75">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="14"/>
@@ -9772,7 +9785,7 @@
       <c r="Z250" s="2"/>
       <c r="AA250" s="2"/>
     </row>
-    <row r="251" spans="1:27" ht="13.2">
+    <row r="251" spans="1:27" ht="12.75">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="14"/>
@@ -9801,7 +9814,7 @@
       <c r="Z251" s="2"/>
       <c r="AA251" s="2"/>
     </row>
-    <row r="252" spans="1:27" ht="13.2">
+    <row r="252" spans="1:27" ht="12.75">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="14"/>
@@ -9830,7 +9843,7 @@
       <c r="Z252" s="2"/>
       <c r="AA252" s="2"/>
     </row>
-    <row r="253" spans="1:27" ht="13.2">
+    <row r="253" spans="1:27" ht="12.75">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="14"/>
@@ -9859,7 +9872,7 @@
       <c r="Z253" s="2"/>
       <c r="AA253" s="2"/>
     </row>
-    <row r="254" spans="1:27" ht="13.2">
+    <row r="254" spans="1:27" ht="12.75">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="14"/>
@@ -9888,7 +9901,7 @@
       <c r="Z254" s="2"/>
       <c r="AA254" s="2"/>
     </row>
-    <row r="255" spans="1:27" ht="13.2">
+    <row r="255" spans="1:27" ht="12.75">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="14"/>
@@ -9917,7 +9930,7 @@
       <c r="Z255" s="2"/>
       <c r="AA255" s="2"/>
     </row>
-    <row r="256" spans="1:27" ht="13.2">
+    <row r="256" spans="1:27" ht="12.75">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="14"/>
@@ -9946,7 +9959,7 @@
       <c r="Z256" s="2"/>
       <c r="AA256" s="2"/>
     </row>
-    <row r="257" spans="1:27" ht="13.2">
+    <row r="257" spans="1:27" ht="12.75">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="14"/>
@@ -9975,7 +9988,7 @@
       <c r="Z257" s="2"/>
       <c r="AA257" s="2"/>
     </row>
-    <row r="258" spans="1:27" ht="13.2">
+    <row r="258" spans="1:27" ht="12.75">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="14"/>
@@ -10004,7 +10017,7 @@
       <c r="Z258" s="2"/>
       <c r="AA258" s="2"/>
     </row>
-    <row r="259" spans="1:27" ht="13.2">
+    <row r="259" spans="1:27" ht="12.75">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="14"/>
@@ -10033,7 +10046,7 @@
       <c r="Z259" s="2"/>
       <c r="AA259" s="2"/>
     </row>
-    <row r="260" spans="1:27" ht="13.2">
+    <row r="260" spans="1:27" ht="12.75">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="14"/>
@@ -10062,7 +10075,7 @@
       <c r="Z260" s="2"/>
       <c r="AA260" s="2"/>
     </row>
-    <row r="261" spans="1:27" ht="13.2">
+    <row r="261" spans="1:27" ht="12.75">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="14"/>
@@ -10091,7 +10104,7 @@
       <c r="Z261" s="2"/>
       <c r="AA261" s="2"/>
     </row>
-    <row r="262" spans="1:27" ht="13.2">
+    <row r="262" spans="1:27" ht="12.75">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="14"/>
@@ -10120,7 +10133,7 @@
       <c r="Z262" s="2"/>
       <c r="AA262" s="2"/>
     </row>
-    <row r="263" spans="1:27" ht="13.2">
+    <row r="263" spans="1:27" ht="12.75">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="14"/>
@@ -10149,7 +10162,7 @@
       <c r="Z263" s="2"/>
       <c r="AA263" s="2"/>
     </row>
-    <row r="264" spans="1:27" ht="13.2">
+    <row r="264" spans="1:27" ht="12.75">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="14"/>
@@ -10178,7 +10191,7 @@
       <c r="Z264" s="2"/>
       <c r="AA264" s="2"/>
     </row>
-    <row r="265" spans="1:27" ht="13.2">
+    <row r="265" spans="1:27" ht="12.75">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="14"/>
@@ -10207,7 +10220,7 @@
       <c r="Z265" s="2"/>
       <c r="AA265" s="2"/>
     </row>
-    <row r="266" spans="1:27" ht="13.2">
+    <row r="266" spans="1:27" ht="12.75">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="14"/>
@@ -10236,7 +10249,7 @@
       <c r="Z266" s="2"/>
       <c r="AA266" s="2"/>
     </row>
-    <row r="267" spans="1:27" ht="13.2">
+    <row r="267" spans="1:27" ht="12.75">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="14"/>
@@ -10265,7 +10278,7 @@
       <c r="Z267" s="2"/>
       <c r="AA267" s="2"/>
     </row>
-    <row r="268" spans="1:27" ht="13.2">
+    <row r="268" spans="1:27" ht="12.75">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="14"/>
@@ -10294,7 +10307,7 @@
       <c r="Z268" s="2"/>
       <c r="AA268" s="2"/>
     </row>
-    <row r="269" spans="1:27" ht="13.2">
+    <row r="269" spans="1:27" ht="12.75">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="14"/>
@@ -10323,7 +10336,7 @@
       <c r="Z269" s="2"/>
       <c r="AA269" s="2"/>
     </row>
-    <row r="270" spans="1:27" ht="13.2">
+    <row r="270" spans="1:27" ht="12.75">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="14"/>
@@ -10352,7 +10365,7 @@
       <c r="Z270" s="2"/>
       <c r="AA270" s="2"/>
     </row>
-    <row r="271" spans="1:27" ht="13.2">
+    <row r="271" spans="1:27" ht="12.75">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="14"/>
@@ -10381,7 +10394,7 @@
       <c r="Z271" s="2"/>
       <c r="AA271" s="2"/>
     </row>
-    <row r="272" spans="1:27" ht="13.2">
+    <row r="272" spans="1:27" ht="12.75">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="14"/>
@@ -10410,7 +10423,7 @@
       <c r="Z272" s="2"/>
       <c r="AA272" s="2"/>
     </row>
-    <row r="273" spans="1:27" ht="13.2">
+    <row r="273" spans="1:27" ht="12.75">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="14"/>
@@ -10439,7 +10452,7 @@
       <c r="Z273" s="2"/>
       <c r="AA273" s="2"/>
     </row>
-    <row r="274" spans="1:27" ht="13.2">
+    <row r="274" spans="1:27" ht="12.75">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="14"/>
@@ -10468,7 +10481,7 @@
       <c r="Z274" s="2"/>
       <c r="AA274" s="2"/>
     </row>
-    <row r="275" spans="1:27" ht="13.2">
+    <row r="275" spans="1:27" ht="12.75">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="14"/>
@@ -10497,7 +10510,7 @@
       <c r="Z275" s="2"/>
       <c r="AA275" s="2"/>
     </row>
-    <row r="276" spans="1:27" ht="13.2">
+    <row r="276" spans="1:27" ht="12.75">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="14"/>
@@ -10526,7 +10539,7 @@
       <c r="Z276" s="2"/>
       <c r="AA276" s="2"/>
     </row>
-    <row r="277" spans="1:27" ht="13.2">
+    <row r="277" spans="1:27" ht="12.75">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="14"/>
@@ -10555,7 +10568,7 @@
       <c r="Z277" s="2"/>
       <c r="AA277" s="2"/>
     </row>
-    <row r="278" spans="1:27" ht="13.2">
+    <row r="278" spans="1:27" ht="12.75">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="14"/>
@@ -10584,7 +10597,7 @@
       <c r="Z278" s="2"/>
       <c r="AA278" s="2"/>
     </row>
-    <row r="279" spans="1:27" ht="13.2">
+    <row r="279" spans="1:27" ht="12.75">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="14"/>
@@ -10613,7 +10626,7 @@
       <c r="Z279" s="2"/>
       <c r="AA279" s="2"/>
     </row>
-    <row r="280" spans="1:27" ht="13.2">
+    <row r="280" spans="1:27" ht="12.75">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="14"/>
@@ -10642,7 +10655,7 @@
       <c r="Z280" s="2"/>
       <c r="AA280" s="2"/>
     </row>
-    <row r="281" spans="1:27" ht="13.2">
+    <row r="281" spans="1:27" ht="12.75">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="14"/>
@@ -10671,7 +10684,7 @@
       <c r="Z281" s="2"/>
       <c r="AA281" s="2"/>
     </row>
-    <row r="282" spans="1:27" ht="13.2">
+    <row r="282" spans="1:27" ht="12.75">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="14"/>
@@ -10700,7 +10713,7 @@
       <c r="Z282" s="2"/>
       <c r="AA282" s="2"/>
     </row>
-    <row r="283" spans="1:27" ht="13.2">
+    <row r="283" spans="1:27" ht="12.75">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="14"/>
@@ -10729,7 +10742,7 @@
       <c r="Z283" s="2"/>
       <c r="AA283" s="2"/>
     </row>
-    <row r="284" spans="1:27" ht="13.2">
+    <row r="284" spans="1:27" ht="12.75">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="14"/>
@@ -10758,7 +10771,7 @@
       <c r="Z284" s="2"/>
       <c r="AA284" s="2"/>
     </row>
-    <row r="285" spans="1:27" ht="13.2">
+    <row r="285" spans="1:27" ht="12.75">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="14"/>
@@ -10787,7 +10800,7 @@
       <c r="Z285" s="2"/>
       <c r="AA285" s="2"/>
     </row>
-    <row r="286" spans="1:27" ht="13.2">
+    <row r="286" spans="1:27" ht="12.75">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="14"/>
@@ -10816,7 +10829,7 @@
       <c r="Z286" s="2"/>
       <c r="AA286" s="2"/>
     </row>
-    <row r="287" spans="1:27" ht="13.2">
+    <row r="287" spans="1:27" ht="12.75">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="14"/>
@@ -10845,7 +10858,7 @@
       <c r="Z287" s="2"/>
       <c r="AA287" s="2"/>
     </row>
-    <row r="288" spans="1:27" ht="13.2">
+    <row r="288" spans="1:27" ht="12.75">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="14"/>
@@ -10874,7 +10887,7 @@
       <c r="Z288" s="2"/>
       <c r="AA288" s="2"/>
     </row>
-    <row r="289" spans="1:27" ht="13.2">
+    <row r="289" spans="1:27" ht="12.75">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="14"/>
@@ -10903,7 +10916,7 @@
       <c r="Z289" s="2"/>
       <c r="AA289" s="2"/>
     </row>
-    <row r="290" spans="1:27" ht="13.2">
+    <row r="290" spans="1:27" ht="12.75">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="14"/>
@@ -10932,7 +10945,7 @@
       <c r="Z290" s="2"/>
       <c r="AA290" s="2"/>
     </row>
-    <row r="291" spans="1:27" ht="13.2">
+    <row r="291" spans="1:27" ht="12.75">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="14"/>
@@ -10961,7 +10974,7 @@
       <c r="Z291" s="2"/>
       <c r="AA291" s="2"/>
     </row>
-    <row r="292" spans="1:27" ht="13.2">
+    <row r="292" spans="1:27" ht="12.75">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="14"/>
@@ -10990,7 +11003,7 @@
       <c r="Z292" s="2"/>
       <c r="AA292" s="2"/>
     </row>
-    <row r="293" spans="1:27" ht="13.2">
+    <row r="293" spans="1:27" ht="12.75">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="14"/>
@@ -11019,7 +11032,7 @@
       <c r="Z293" s="2"/>
       <c r="AA293" s="2"/>
     </row>
-    <row r="294" spans="1:27" ht="13.2">
+    <row r="294" spans="1:27" ht="12.75">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="14"/>
@@ -11048,7 +11061,7 @@
       <c r="Z294" s="2"/>
       <c r="AA294" s="2"/>
     </row>
-    <row r="295" spans="1:27" ht="13.2">
+    <row r="295" spans="1:27" ht="12.75">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="14"/>
@@ -11077,7 +11090,7 @@
       <c r="Z295" s="2"/>
       <c r="AA295" s="2"/>
     </row>
-    <row r="296" spans="1:27" ht="13.2">
+    <row r="296" spans="1:27" ht="12.75">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="14"/>
@@ -11106,7 +11119,7 @@
       <c r="Z296" s="2"/>
       <c r="AA296" s="2"/>
     </row>
-    <row r="297" spans="1:27" ht="13.2">
+    <row r="297" spans="1:27" ht="12.75">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="14"/>
@@ -11135,7 +11148,7 @@
       <c r="Z297" s="2"/>
       <c r="AA297" s="2"/>
     </row>
-    <row r="298" spans="1:27" ht="13.2">
+    <row r="298" spans="1:27" ht="12.75">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="14"/>
@@ -11164,7 +11177,7 @@
       <c r="Z298" s="2"/>
       <c r="AA298" s="2"/>
     </row>
-    <row r="299" spans="1:27" ht="13.2">
+    <row r="299" spans="1:27" ht="12.75">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="14"/>
@@ -11193,7 +11206,7 @@
       <c r="Z299" s="2"/>
       <c r="AA299" s="2"/>
     </row>
-    <row r="300" spans="1:27" ht="13.2">
+    <row r="300" spans="1:27" ht="12.75">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="14"/>
@@ -11222,7 +11235,7 @@
       <c r="Z300" s="2"/>
       <c r="AA300" s="2"/>
     </row>
-    <row r="301" spans="1:27" ht="13.2">
+    <row r="301" spans="1:27" ht="12.75">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="14"/>
@@ -11251,7 +11264,7 @@
       <c r="Z301" s="2"/>
       <c r="AA301" s="2"/>
     </row>
-    <row r="302" spans="1:27" ht="13.2">
+    <row r="302" spans="1:27" ht="12.75">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="14"/>
@@ -11280,7 +11293,7 @@
       <c r="Z302" s="2"/>
       <c r="AA302" s="2"/>
     </row>
-    <row r="303" spans="1:27" ht="13.2">
+    <row r="303" spans="1:27" ht="12.75">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="14"/>
@@ -11309,7 +11322,7 @@
       <c r="Z303" s="2"/>
       <c r="AA303" s="2"/>
     </row>
-    <row r="304" spans="1:27" ht="13.2">
+    <row r="304" spans="1:27" ht="12.75">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="14"/>
@@ -11338,7 +11351,7 @@
       <c r="Z304" s="2"/>
       <c r="AA304" s="2"/>
     </row>
-    <row r="305" spans="1:27" ht="13.2">
+    <row r="305" spans="1:27" ht="12.75">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="14"/>
@@ -11367,7 +11380,7 @@
       <c r="Z305" s="2"/>
       <c r="AA305" s="2"/>
     </row>
-    <row r="306" spans="1:27" ht="13.2">
+    <row r="306" spans="1:27" ht="12.75">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="14"/>
@@ -11396,7 +11409,7 @@
       <c r="Z306" s="2"/>
       <c r="AA306" s="2"/>
     </row>
-    <row r="307" spans="1:27" ht="13.2">
+    <row r="307" spans="1:27" ht="12.75">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="14"/>
@@ -11425,7 +11438,7 @@
       <c r="Z307" s="2"/>
       <c r="AA307" s="2"/>
     </row>
-    <row r="308" spans="1:27" ht="13.2">
+    <row r="308" spans="1:27" ht="12.75">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="14"/>
@@ -11454,7 +11467,7 @@
       <c r="Z308" s="2"/>
       <c r="AA308" s="2"/>
     </row>
-    <row r="309" spans="1:27" ht="13.2">
+    <row r="309" spans="1:27" ht="12.75">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="14"/>
@@ -11483,7 +11496,7 @@
       <c r="Z309" s="2"/>
       <c r="AA309" s="2"/>
     </row>
-    <row r="310" spans="1:27" ht="13.2">
+    <row r="310" spans="1:27" ht="12.75">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="14"/>
@@ -11512,7 +11525,7 @@
       <c r="Z310" s="2"/>
       <c r="AA310" s="2"/>
     </row>
-    <row r="311" spans="1:27" ht="13.2">
+    <row r="311" spans="1:27" ht="12.75">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="14"/>
@@ -11541,7 +11554,7 @@
       <c r="Z311" s="2"/>
       <c r="AA311" s="2"/>
     </row>
-    <row r="312" spans="1:27" ht="13.2">
+    <row r="312" spans="1:27" ht="12.75">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="14"/>
@@ -11570,7 +11583,7 @@
       <c r="Z312" s="2"/>
       <c r="AA312" s="2"/>
     </row>
-    <row r="313" spans="1:27" ht="13.2">
+    <row r="313" spans="1:27" ht="12.75">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="14"/>
@@ -11599,7 +11612,7 @@
       <c r="Z313" s="2"/>
       <c r="AA313" s="2"/>
     </row>
-    <row r="314" spans="1:27" ht="13.2">
+    <row r="314" spans="1:27" ht="12.75">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="14"/>
@@ -11628,7 +11641,7 @@
       <c r="Z314" s="2"/>
       <c r="AA314" s="2"/>
     </row>
-    <row r="315" spans="1:27" ht="13.2">
+    <row r="315" spans="1:27" ht="12.75">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="14"/>
@@ -11657,7 +11670,7 @@
       <c r="Z315" s="2"/>
       <c r="AA315" s="2"/>
     </row>
-    <row r="316" spans="1:27" ht="13.2">
+    <row r="316" spans="1:27" ht="12.75">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="14"/>
@@ -11686,7 +11699,7 @@
       <c r="Z316" s="2"/>
       <c r="AA316" s="2"/>
     </row>
-    <row r="317" spans="1:27" ht="13.2">
+    <row r="317" spans="1:27" ht="12.75">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="14"/>
@@ -11715,7 +11728,7 @@
       <c r="Z317" s="2"/>
       <c r="AA317" s="2"/>
     </row>
-    <row r="318" spans="1:27" ht="13.2">
+    <row r="318" spans="1:27" ht="12.75">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="14"/>
@@ -11744,7 +11757,7 @@
       <c r="Z318" s="2"/>
       <c r="AA318" s="2"/>
     </row>
-    <row r="319" spans="1:27" ht="13.2">
+    <row r="319" spans="1:27" ht="12.75">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="14"/>
@@ -11773,7 +11786,7 @@
       <c r="Z319" s="2"/>
       <c r="AA319" s="2"/>
     </row>
-    <row r="320" spans="1:27" ht="13.2">
+    <row r="320" spans="1:27" ht="12.75">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="14"/>
@@ -11802,7 +11815,7 @@
       <c r="Z320" s="2"/>
       <c r="AA320" s="2"/>
     </row>
-    <row r="321" spans="1:27" ht="13.2">
+    <row r="321" spans="1:27" ht="12.75">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="14"/>
@@ -11831,7 +11844,7 @@
       <c r="Z321" s="2"/>
       <c r="AA321" s="2"/>
     </row>
-    <row r="322" spans="1:27" ht="13.2">
+    <row r="322" spans="1:27" ht="12.75">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="14"/>
@@ -11860,7 +11873,7 @@
       <c r="Z322" s="2"/>
       <c r="AA322" s="2"/>
     </row>
-    <row r="323" spans="1:27" ht="13.2">
+    <row r="323" spans="1:27" ht="12.75">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="14"/>
@@ -11889,7 +11902,7 @@
       <c r="Z323" s="2"/>
       <c r="AA323" s="2"/>
     </row>
-    <row r="324" spans="1:27" ht="13.2">
+    <row r="324" spans="1:27" ht="12.75">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="14"/>
@@ -11918,7 +11931,7 @@
       <c r="Z324" s="2"/>
       <c r="AA324" s="2"/>
     </row>
-    <row r="325" spans="1:27" ht="13.2">
+    <row r="325" spans="1:27" ht="12.75">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="14"/>
@@ -11947,7 +11960,7 @@
       <c r="Z325" s="2"/>
       <c r="AA325" s="2"/>
     </row>
-    <row r="326" spans="1:27" ht="13.2">
+    <row r="326" spans="1:27" ht="12.75">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="14"/>
@@ -11976,7 +11989,7 @@
       <c r="Z326" s="2"/>
       <c r="AA326" s="2"/>
     </row>
-    <row r="327" spans="1:27" ht="13.2">
+    <row r="327" spans="1:27" ht="12.75">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="14"/>
@@ -12005,7 +12018,7 @@
       <c r="Z327" s="2"/>
       <c r="AA327" s="2"/>
     </row>
-    <row r="328" spans="1:27" ht="13.2">
+    <row r="328" spans="1:27" ht="12.75">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="14"/>
@@ -12034,7 +12047,7 @@
       <c r="Z328" s="2"/>
       <c r="AA328" s="2"/>
     </row>
-    <row r="329" spans="1:27" ht="13.2">
+    <row r="329" spans="1:27" ht="12.75">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="14"/>
@@ -12063,7 +12076,7 @@
       <c r="Z329" s="2"/>
       <c r="AA329" s="2"/>
     </row>
-    <row r="330" spans="1:27" ht="13.2">
+    <row r="330" spans="1:27" ht="12.75">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="14"/>
@@ -12092,7 +12105,7 @@
       <c r="Z330" s="2"/>
       <c r="AA330" s="2"/>
     </row>
-    <row r="331" spans="1:27" ht="13.2">
+    <row r="331" spans="1:27" ht="12.75">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="14"/>
@@ -12121,7 +12134,7 @@
       <c r="Z331" s="2"/>
       <c r="AA331" s="2"/>
     </row>
-    <row r="332" spans="1:27" ht="13.2">
+    <row r="332" spans="1:27" ht="12.75">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="14"/>
@@ -12150,7 +12163,7 @@
       <c r="Z332" s="2"/>
       <c r="AA332" s="2"/>
     </row>
-    <row r="333" spans="1:27" ht="13.2">
+    <row r="333" spans="1:27" ht="12.75">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="14"/>
@@ -12179,7 +12192,7 @@
       <c r="Z333" s="2"/>
       <c r="AA333" s="2"/>
     </row>
-    <row r="334" spans="1:27" ht="13.2">
+    <row r="334" spans="1:27" ht="12.75">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="14"/>
@@ -12208,7 +12221,7 @@
       <c r="Z334" s="2"/>
       <c r="AA334" s="2"/>
     </row>
-    <row r="335" spans="1:27" ht="13.2">
+    <row r="335" spans="1:27" ht="12.75">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="14"/>
@@ -12237,7 +12250,7 @@
       <c r="Z335" s="2"/>
       <c r="AA335" s="2"/>
     </row>
-    <row r="336" spans="1:27" ht="13.2">
+    <row r="336" spans="1:27" ht="12.75">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="14"/>
@@ -12266,7 +12279,7 @@
       <c r="Z336" s="2"/>
       <c r="AA336" s="2"/>
     </row>
-    <row r="337" spans="1:27" ht="13.2">
+    <row r="337" spans="1:27" ht="12.75">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="14"/>
@@ -12295,7 +12308,7 @@
       <c r="Z337" s="2"/>
       <c r="AA337" s="2"/>
     </row>
-    <row r="338" spans="1:27" ht="13.2">
+    <row r="338" spans="1:27" ht="12.75">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="14"/>
@@ -12324,7 +12337,7 @@
       <c r="Z338" s="2"/>
       <c r="AA338" s="2"/>
     </row>
-    <row r="339" spans="1:27" ht="13.2">
+    <row r="339" spans="1:27" ht="12.75">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="14"/>
@@ -12353,7 +12366,7 @@
       <c r="Z339" s="2"/>
       <c r="AA339" s="2"/>
     </row>
-    <row r="340" spans="1:27" ht="13.2">
+    <row r="340" spans="1:27" ht="12.75">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="14"/>
@@ -12382,7 +12395,7 @@
       <c r="Z340" s="2"/>
       <c r="AA340" s="2"/>
     </row>
-    <row r="341" spans="1:27" ht="13.2">
+    <row r="341" spans="1:27" ht="12.75">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="14"/>
@@ -12411,7 +12424,7 @@
       <c r="Z341" s="2"/>
       <c r="AA341" s="2"/>
     </row>
-    <row r="342" spans="1:27" ht="13.2">
+    <row r="342" spans="1:27" ht="12.75">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="14"/>
@@ -12440,7 +12453,7 @@
       <c r="Z342" s="2"/>
       <c r="AA342" s="2"/>
     </row>
-    <row r="343" spans="1:27" ht="13.2">
+    <row r="343" spans="1:27" ht="12.75">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="14"/>
@@ -12469,7 +12482,7 @@
       <c r="Z343" s="2"/>
       <c r="AA343" s="2"/>
     </row>
-    <row r="344" spans="1:27" ht="13.2">
+    <row r="344" spans="1:27" ht="12.75">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="14"/>
@@ -12498,7 +12511,7 @@
       <c r="Z344" s="2"/>
       <c r="AA344" s="2"/>
     </row>
-    <row r="345" spans="1:27" ht="13.2">
+    <row r="345" spans="1:27" ht="12.75">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="14"/>
@@ -12527,7 +12540,7 @@
       <c r="Z345" s="2"/>
       <c r="AA345" s="2"/>
     </row>
-    <row r="346" spans="1:27" ht="13.2">
+    <row r="346" spans="1:27" ht="12.75">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="14"/>
@@ -12556,7 +12569,7 @@
       <c r="Z346" s="2"/>
       <c r="AA346" s="2"/>
     </row>
-    <row r="347" spans="1:27" ht="13.2">
+    <row r="347" spans="1:27" ht="12.75">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="14"/>
@@ -12585,7 +12598,7 @@
       <c r="Z347" s="2"/>
       <c r="AA347" s="2"/>
     </row>
-    <row r="348" spans="1:27" ht="13.2">
+    <row r="348" spans="1:27" ht="12.75">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="14"/>
@@ -12614,7 +12627,7 @@
       <c r="Z348" s="2"/>
       <c r="AA348" s="2"/>
     </row>
-    <row r="349" spans="1:27" ht="13.2">
+    <row r="349" spans="1:27" ht="12.75">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="14"/>
@@ -12643,7 +12656,7 @@
       <c r="Z349" s="2"/>
       <c r="AA349" s="2"/>
     </row>
-    <row r="350" spans="1:27" ht="13.2">
+    <row r="350" spans="1:27" ht="12.75">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="14"/>
@@ -12672,7 +12685,7 @@
       <c r="Z350" s="2"/>
       <c r="AA350" s="2"/>
     </row>
-    <row r="351" spans="1:27" ht="13.2">
+    <row r="351" spans="1:27" ht="12.75">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="14"/>
@@ -12701,7 +12714,7 @@
       <c r="Z351" s="2"/>
       <c r="AA351" s="2"/>
     </row>
-    <row r="352" spans="1:27" ht="13.2">
+    <row r="352" spans="1:27" ht="12.75">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="14"/>
@@ -12730,7 +12743,7 @@
       <c r="Z352" s="2"/>
       <c r="AA352" s="2"/>
     </row>
-    <row r="353" spans="1:27" ht="13.2">
+    <row r="353" spans="1:27" ht="12.75">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="14"/>
@@ -12759,7 +12772,7 @@
       <c r="Z353" s="2"/>
       <c r="AA353" s="2"/>
     </row>
-    <row r="354" spans="1:27" ht="13.2">
+    <row r="354" spans="1:27" ht="12.75">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="14"/>
@@ -12788,7 +12801,7 @@
       <c r="Z354" s="2"/>
       <c r="AA354" s="2"/>
     </row>
-    <row r="355" spans="1:27" ht="13.2">
+    <row r="355" spans="1:27" ht="12.75">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="14"/>
@@ -12817,7 +12830,7 @@
       <c r="Z355" s="2"/>
       <c r="AA355" s="2"/>
     </row>
-    <row r="356" spans="1:27" ht="13.2">
+    <row r="356" spans="1:27" ht="12.75">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="14"/>
@@ -12846,7 +12859,7 @@
       <c r="Z356" s="2"/>
       <c r="AA356" s="2"/>
     </row>
-    <row r="357" spans="1:27" ht="13.2">
+    <row r="357" spans="1:27" ht="12.75">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="14"/>
@@ -12875,7 +12888,7 @@
       <c r="Z357" s="2"/>
       <c r="AA357" s="2"/>
     </row>
-    <row r="358" spans="1:27" ht="13.2">
+    <row r="358" spans="1:27" ht="12.75">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="14"/>
@@ -12904,7 +12917,7 @@
       <c r="Z358" s="2"/>
       <c r="AA358" s="2"/>
     </row>
-    <row r="359" spans="1:27" ht="13.2">
+    <row r="359" spans="1:27" ht="12.75">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="14"/>
@@ -12933,7 +12946,7 @@
       <c r="Z359" s="2"/>
       <c r="AA359" s="2"/>
     </row>
-    <row r="360" spans="1:27" ht="13.2">
+    <row r="360" spans="1:27" ht="12.75">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="14"/>
@@ -12962,7 +12975,7 @@
       <c r="Z360" s="2"/>
       <c r="AA360" s="2"/>
     </row>
-    <row r="361" spans="1:27" ht="13.2">
+    <row r="361" spans="1:27" ht="12.75">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="14"/>
@@ -12991,7 +13004,7 @@
       <c r="Z361" s="2"/>
       <c r="AA361" s="2"/>
     </row>
-    <row r="362" spans="1:27" ht="13.2">
+    <row r="362" spans="1:27" ht="12.75">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="14"/>
@@ -13020,7 +13033,7 @@
       <c r="Z362" s="2"/>
       <c r="AA362" s="2"/>
     </row>
-    <row r="363" spans="1:27" ht="13.2">
+    <row r="363" spans="1:27" ht="12.75">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="14"/>
@@ -13049,7 +13062,7 @@
       <c r="Z363" s="2"/>
       <c r="AA363" s="2"/>
     </row>
-    <row r="364" spans="1:27" ht="13.2">
+    <row r="364" spans="1:27" ht="12.75">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="14"/>
@@ -13078,7 +13091,7 @@
       <c r="Z364" s="2"/>
       <c r="AA364" s="2"/>
     </row>
-    <row r="365" spans="1:27" ht="13.2">
+    <row r="365" spans="1:27" ht="12.75">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="14"/>
@@ -13107,7 +13120,7 @@
       <c r="Z365" s="2"/>
       <c r="AA365" s="2"/>
     </row>
-    <row r="366" spans="1:27" ht="13.2">
+    <row r="366" spans="1:27" ht="12.75">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="14"/>
@@ -13136,7 +13149,7 @@
       <c r="Z366" s="2"/>
       <c r="AA366" s="2"/>
     </row>
-    <row r="367" spans="1:27" ht="13.2">
+    <row r="367" spans="1:27" ht="12.75">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="14"/>
@@ -13165,7 +13178,7 @@
       <c r="Z367" s="2"/>
       <c r="AA367" s="2"/>
     </row>
-    <row r="368" spans="1:27" ht="13.2">
+    <row r="368" spans="1:27" ht="12.75">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="14"/>
@@ -13194,7 +13207,7 @@
       <c r="Z368" s="2"/>
       <c r="AA368" s="2"/>
     </row>
-    <row r="369" spans="1:27" ht="13.2">
+    <row r="369" spans="1:27" ht="12.75">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="14"/>
@@ -13223,7 +13236,7 @@
       <c r="Z369" s="2"/>
       <c r="AA369" s="2"/>
     </row>
-    <row r="370" spans="1:27" ht="13.2">
+    <row r="370" spans="1:27" ht="12.75">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="14"/>
@@ -13252,7 +13265,7 @@
       <c r="Z370" s="2"/>
       <c r="AA370" s="2"/>
     </row>
-    <row r="371" spans="1:27" ht="13.2">
+    <row r="371" spans="1:27" ht="12.75">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="14"/>
@@ -13281,7 +13294,7 @@
       <c r="Z371" s="2"/>
       <c r="AA371" s="2"/>
     </row>
-    <row r="372" spans="1:27" ht="13.2">
+    <row r="372" spans="1:27" ht="12.75">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="14"/>
@@ -13310,7 +13323,7 @@
       <c r="Z372" s="2"/>
       <c r="AA372" s="2"/>
     </row>
-    <row r="373" spans="1:27" ht="13.2">
+    <row r="373" spans="1:27" ht="12.75">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="14"/>
@@ -13339,7 +13352,7 @@
       <c r="Z373" s="2"/>
       <c r="AA373" s="2"/>
     </row>
-    <row r="374" spans="1:27" ht="13.2">
+    <row r="374" spans="1:27" ht="12.75">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="14"/>
@@ -13368,7 +13381,7 @@
       <c r="Z374" s="2"/>
       <c r="AA374" s="2"/>
     </row>
-    <row r="375" spans="1:27" ht="13.2">
+    <row r="375" spans="1:27" ht="12.75">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="14"/>
@@ -13397,7 +13410,7 @@
       <c r="Z375" s="2"/>
       <c r="AA375" s="2"/>
     </row>
-    <row r="376" spans="1:27" ht="13.2">
+    <row r="376" spans="1:27" ht="12.75">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="14"/>
@@ -13426,7 +13439,7 @@
       <c r="Z376" s="2"/>
       <c r="AA376" s="2"/>
     </row>
-    <row r="377" spans="1:27" ht="13.2">
+    <row r="377" spans="1:27" ht="12.75">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="14"/>
@@ -13455,7 +13468,7 @@
       <c r="Z377" s="2"/>
       <c r="AA377" s="2"/>
     </row>
-    <row r="378" spans="1:27" ht="13.2">
+    <row r="378" spans="1:27" ht="12.75">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="14"/>
@@ -13484,7 +13497,7 @@
       <c r="Z378" s="2"/>
       <c r="AA378" s="2"/>
     </row>
-    <row r="379" spans="1:27" ht="13.2">
+    <row r="379" spans="1:27" ht="12.75">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="14"/>
@@ -13513,7 +13526,7 @@
       <c r="Z379" s="2"/>
       <c r="AA379" s="2"/>
     </row>
-    <row r="380" spans="1:27" ht="13.2">
+    <row r="380" spans="1:27" ht="12.75">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="14"/>
@@ -13542,7 +13555,7 @@
       <c r="Z380" s="2"/>
       <c r="AA380" s="2"/>
     </row>
-    <row r="381" spans="1:27" ht="13.2">
+    <row r="381" spans="1:27" ht="12.75">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="14"/>
@@ -13571,7 +13584,7 @@
       <c r="Z381" s="2"/>
       <c r="AA381" s="2"/>
     </row>
-    <row r="382" spans="1:27" ht="13.2">
+    <row r="382" spans="1:27" ht="12.75">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="14"/>
@@ -13600,7 +13613,7 @@
       <c r="Z382" s="2"/>
       <c r="AA382" s="2"/>
     </row>
-    <row r="383" spans="1:27" ht="13.2">
+    <row r="383" spans="1:27" ht="12.75">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="14"/>
@@ -13629,7 +13642,7 @@
       <c r="Z383" s="2"/>
       <c r="AA383" s="2"/>
     </row>
-    <row r="384" spans="1:27" ht="13.2">
+    <row r="384" spans="1:27" ht="12.75">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="14"/>
@@ -13658,7 +13671,7 @@
       <c r="Z384" s="2"/>
       <c r="AA384" s="2"/>
     </row>
-    <row r="385" spans="1:27" ht="13.2">
+    <row r="385" spans="1:27" ht="12.75">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="14"/>
@@ -13687,7 +13700,7 @@
       <c r="Z385" s="2"/>
       <c r="AA385" s="2"/>
     </row>
-    <row r="386" spans="1:27" ht="13.2">
+    <row r="386" spans="1:27" ht="12.75">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="14"/>
@@ -13716,7 +13729,7 @@
       <c r="Z386" s="2"/>
       <c r="AA386" s="2"/>
     </row>
-    <row r="387" spans="1:27" ht="13.2">
+    <row r="387" spans="1:27" ht="12.75">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="14"/>
@@ -13745,7 +13758,7 @@
       <c r="Z387" s="2"/>
       <c r="AA387" s="2"/>
     </row>
-    <row r="388" spans="1:27" ht="13.2">
+    <row r="388" spans="1:27" ht="12.75">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="14"/>
@@ -13774,7 +13787,7 @@
       <c r="Z388" s="2"/>
       <c r="AA388" s="2"/>
     </row>
-    <row r="389" spans="1:27" ht="13.2">
+    <row r="389" spans="1:27" ht="12.75">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="14"/>
@@ -13803,7 +13816,7 @@
       <c r="Z389" s="2"/>
       <c r="AA389" s="2"/>
     </row>
-    <row r="390" spans="1:27" ht="13.2">
+    <row r="390" spans="1:27" ht="12.75">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="14"/>
@@ -13832,7 +13845,7 @@
       <c r="Z390" s="2"/>
       <c r="AA390" s="2"/>
     </row>
-    <row r="391" spans="1:27" ht="13.2">
+    <row r="391" spans="1:27" ht="12.75">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="14"/>
@@ -13861,7 +13874,7 @@
       <c r="Z391" s="2"/>
       <c r="AA391" s="2"/>
     </row>
-    <row r="392" spans="1:27" ht="13.2">
+    <row r="392" spans="1:27" ht="12.75">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="14"/>
@@ -13890,7 +13903,7 @@
       <c r="Z392" s="2"/>
       <c r="AA392" s="2"/>
     </row>
-    <row r="393" spans="1:27" ht="13.2">
+    <row r="393" spans="1:27" ht="12.75">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="14"/>
@@ -13919,7 +13932,7 @@
       <c r="Z393" s="2"/>
       <c r="AA393" s="2"/>
     </row>
-    <row r="394" spans="1:27" ht="13.2">
+    <row r="394" spans="1:27" ht="12.75">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="14"/>
@@ -13948,7 +13961,7 @@
       <c r="Z394" s="2"/>
       <c r="AA394" s="2"/>
     </row>
-    <row r="395" spans="1:27" ht="13.2">
+    <row r="395" spans="1:27" ht="12.75">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="14"/>
@@ -13977,7 +13990,7 @@
       <c r="Z395" s="2"/>
       <c r="AA395" s="2"/>
     </row>
-    <row r="396" spans="1:27" ht="13.2">
+    <row r="396" spans="1:27" ht="12.75">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="14"/>
@@ -14006,7 +14019,7 @@
       <c r="Z396" s="2"/>
       <c r="AA396" s="2"/>
     </row>
-    <row r="397" spans="1:27" ht="13.2">
+    <row r="397" spans="1:27" ht="12.75">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="14"/>
@@ -14035,7 +14048,7 @@
       <c r="Z397" s="2"/>
       <c r="AA397" s="2"/>
     </row>
-    <row r="398" spans="1:27" ht="13.2">
+    <row r="398" spans="1:27" ht="12.75">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="14"/>
@@ -14064,7 +14077,7 @@
       <c r="Z398" s="2"/>
       <c r="AA398" s="2"/>
     </row>
-    <row r="399" spans="1:27" ht="13.2">
+    <row r="399" spans="1:27" ht="12.75">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="14"/>
@@ -14093,7 +14106,7 @@
       <c r="Z399" s="2"/>
       <c r="AA399" s="2"/>
     </row>
-    <row r="400" spans="1:27" ht="13.2">
+    <row r="400" spans="1:27" ht="12.75">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="14"/>
@@ -14122,7 +14135,7 @@
       <c r="Z400" s="2"/>
       <c r="AA400" s="2"/>
     </row>
-    <row r="401" spans="1:27" ht="13.2">
+    <row r="401" spans="1:27" ht="12.75">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="14"/>
@@ -14151,7 +14164,7 @@
       <c r="Z401" s="2"/>
       <c r="AA401" s="2"/>
     </row>
-    <row r="402" spans="1:27" ht="13.2">
+    <row r="402" spans="1:27" ht="12.75">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="14"/>
@@ -14180,7 +14193,7 @@
       <c r="Z402" s="2"/>
       <c r="AA402" s="2"/>
     </row>
-    <row r="403" spans="1:27" ht="13.2">
+    <row r="403" spans="1:27" ht="12.75">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="14"/>
@@ -14209,7 +14222,7 @@
       <c r="Z403" s="2"/>
       <c r="AA403" s="2"/>
     </row>
-    <row r="404" spans="1:27" ht="13.2">
+    <row r="404" spans="1:27" ht="12.75">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="14"/>
@@ -14238,7 +14251,7 @@
       <c r="Z404" s="2"/>
       <c r="AA404" s="2"/>
     </row>
-    <row r="405" spans="1:27" ht="13.2">
+    <row r="405" spans="1:27" ht="12.75">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="14"/>
@@ -14267,7 +14280,7 @@
       <c r="Z405" s="2"/>
       <c r="AA405" s="2"/>
     </row>
-    <row r="406" spans="1:27" ht="13.2">
+    <row r="406" spans="1:27" ht="12.75">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="14"/>
@@ -14296,7 +14309,7 @@
       <c r="Z406" s="2"/>
       <c r="AA406" s="2"/>
     </row>
-    <row r="407" spans="1:27" ht="13.2">
+    <row r="407" spans="1:27" ht="12.75">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="14"/>
@@ -14325,7 +14338,7 @@
       <c r="Z407" s="2"/>
       <c r="AA407" s="2"/>
     </row>
-    <row r="408" spans="1:27" ht="13.2">
+    <row r="408" spans="1:27" ht="12.75">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="14"/>
@@ -14354,7 +14367,7 @@
       <c r="Z408" s="2"/>
       <c r="AA408" s="2"/>
     </row>
-    <row r="409" spans="1:27" ht="13.2">
+    <row r="409" spans="1:27" ht="12.75">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="14"/>
@@ -14383,7 +14396,7 @@
       <c r="Z409" s="2"/>
       <c r="AA409" s="2"/>
     </row>
-    <row r="410" spans="1:27" ht="13.2">
+    <row r="410" spans="1:27" ht="12.75">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="14"/>
@@ -14412,7 +14425,7 @@
       <c r="Z410" s="2"/>
       <c r="AA410" s="2"/>
     </row>
-    <row r="411" spans="1:27" ht="13.2">
+    <row r="411" spans="1:27" ht="12.75">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="14"/>
@@ -14441,7 +14454,7 @@
       <c r="Z411" s="2"/>
       <c r="AA411" s="2"/>
     </row>
-    <row r="412" spans="1:27" ht="13.2">
+    <row r="412" spans="1:27" ht="12.75">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="14"/>
@@ -14470,7 +14483,7 @@
       <c r="Z412" s="2"/>
       <c r="AA412" s="2"/>
     </row>
-    <row r="413" spans="1:27" ht="13.2">
+    <row r="413" spans="1:27" ht="12.75">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="14"/>
@@ -14499,7 +14512,7 @@
       <c r="Z413" s="2"/>
       <c r="AA413" s="2"/>
     </row>
-    <row r="414" spans="1:27" ht="13.2">
+    <row r="414" spans="1:27" ht="12.75">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="14"/>
@@ -14528,7 +14541,7 @@
       <c r="Z414" s="2"/>
       <c r="AA414" s="2"/>
     </row>
-    <row r="415" spans="1:27" ht="13.2">
+    <row r="415" spans="1:27" ht="12.75">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="14"/>
@@ -14557,7 +14570,7 @@
       <c r="Z415" s="2"/>
       <c r="AA415" s="2"/>
     </row>
-    <row r="416" spans="1:27" ht="13.2">
+    <row r="416" spans="1:27" ht="12.75">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="14"/>
@@ -14586,7 +14599,7 @@
       <c r="Z416" s="2"/>
       <c r="AA416" s="2"/>
     </row>
-    <row r="417" spans="1:27" ht="13.2">
+    <row r="417" spans="1:27" ht="12.75">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="14"/>
@@ -14615,7 +14628,7 @@
       <c r="Z417" s="2"/>
       <c r="AA417" s="2"/>
     </row>
-    <row r="418" spans="1:27" ht="13.2">
+    <row r="418" spans="1:27" ht="12.75">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="14"/>
@@ -14644,7 +14657,7 @@
       <c r="Z418" s="2"/>
       <c r="AA418" s="2"/>
     </row>
-    <row r="419" spans="1:27" ht="13.2">
+    <row r="419" spans="1:27" ht="12.75">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="14"/>
@@ -14673,7 +14686,7 @@
       <c r="Z419" s="2"/>
       <c r="AA419" s="2"/>
     </row>
-    <row r="420" spans="1:27" ht="13.2">
+    <row r="420" spans="1:27" ht="12.75">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="14"/>
@@ -14702,7 +14715,7 @@
       <c r="Z420" s="2"/>
       <c r="AA420" s="2"/>
     </row>
-    <row r="421" spans="1:27" ht="13.2">
+    <row r="421" spans="1:27" ht="12.75">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="14"/>
@@ -14731,7 +14744,7 @@
       <c r="Z421" s="2"/>
       <c r="AA421" s="2"/>
     </row>
-    <row r="422" spans="1:27" ht="13.2">
+    <row r="422" spans="1:27" ht="12.75">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="14"/>
@@ -14760,7 +14773,7 @@
       <c r="Z422" s="2"/>
       <c r="AA422" s="2"/>
     </row>
-    <row r="423" spans="1:27" ht="13.2">
+    <row r="423" spans="1:27" ht="12.75">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="14"/>
@@ -14789,7 +14802,7 @@
       <c r="Z423" s="2"/>
       <c r="AA423" s="2"/>
     </row>
-    <row r="424" spans="1:27" ht="13.2">
+    <row r="424" spans="1:27" ht="12.75">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="14"/>
@@ -14818,7 +14831,7 @@
       <c r="Z424" s="2"/>
       <c r="AA424" s="2"/>
     </row>
-    <row r="425" spans="1:27" ht="13.2">
+    <row r="425" spans="1:27" ht="12.75">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="14"/>
@@ -14847,7 +14860,7 @@
       <c r="Z425" s="2"/>
       <c r="AA425" s="2"/>
     </row>
-    <row r="426" spans="1:27" ht="13.2">
+    <row r="426" spans="1:27" ht="12.75">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="14"/>
@@ -14876,7 +14889,7 @@
       <c r="Z426" s="2"/>
       <c r="AA426" s="2"/>
     </row>
-    <row r="427" spans="1:27" ht="13.2">
+    <row r="427" spans="1:27" ht="12.75">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="14"/>
@@ -14905,7 +14918,7 @@
       <c r="Z427" s="2"/>
       <c r="AA427" s="2"/>
     </row>
-    <row r="428" spans="1:27" ht="13.2">
+    <row r="428" spans="1:27" ht="12.75">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="14"/>
@@ -14934,7 +14947,7 @@
       <c r="Z428" s="2"/>
       <c r="AA428" s="2"/>
     </row>
-    <row r="429" spans="1:27" ht="13.2">
+    <row r="429" spans="1:27" ht="12.75">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="14"/>
@@ -14963,7 +14976,7 @@
       <c r="Z429" s="2"/>
       <c r="AA429" s="2"/>
     </row>
-    <row r="430" spans="1:27" ht="13.2">
+    <row r="430" spans="1:27" ht="12.75">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="14"/>
@@ -14992,7 +15005,7 @@
       <c r="Z430" s="2"/>
       <c r="AA430" s="2"/>
     </row>
-    <row r="431" spans="1:27" ht="13.2">
+    <row r="431" spans="1:27" ht="12.75">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="14"/>
@@ -15021,7 +15034,7 @@
       <c r="Z431" s="2"/>
       <c r="AA431" s="2"/>
     </row>
-    <row r="432" spans="1:27" ht="13.2">
+    <row r="432" spans="1:27" ht="12.75">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="14"/>
@@ -15050,7 +15063,7 @@
       <c r="Z432" s="2"/>
       <c r="AA432" s="2"/>
     </row>
-    <row r="433" spans="1:27" ht="13.2">
+    <row r="433" spans="1:27" ht="12.75">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="14"/>
@@ -15079,7 +15092,7 @@
       <c r="Z433" s="2"/>
       <c r="AA433" s="2"/>
     </row>
-    <row r="434" spans="1:27" ht="13.2">
+    <row r="434" spans="1:27" ht="12.75">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="14"/>
@@ -15108,7 +15121,7 @@
       <c r="Z434" s="2"/>
       <c r="AA434" s="2"/>
     </row>
-    <row r="435" spans="1:27" ht="13.2">
+    <row r="435" spans="1:27" ht="12.75">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="14"/>
@@ -15137,7 +15150,7 @@
       <c r="Z435" s="2"/>
       <c r="AA435" s="2"/>
     </row>
-    <row r="436" spans="1:27" ht="13.2">
+    <row r="436" spans="1:27" ht="12.75">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="14"/>
@@ -15166,7 +15179,7 @@
       <c r="Z436" s="2"/>
       <c r="AA436" s="2"/>
     </row>
-    <row r="437" spans="1:27" ht="13.2">
+    <row r="437" spans="1:27" ht="12.75">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="14"/>
@@ -15195,7 +15208,7 @@
       <c r="Z437" s="2"/>
       <c r="AA437" s="2"/>
     </row>
-    <row r="438" spans="1:27" ht="13.2">
+    <row r="438" spans="1:27" ht="12.75">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="14"/>
@@ -15224,7 +15237,7 @@
       <c r="Z438" s="2"/>
       <c r="AA438" s="2"/>
     </row>
-    <row r="439" spans="1:27" ht="13.2">
+    <row r="439" spans="1:27" ht="12.75">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="14"/>
@@ -15253,7 +15266,7 @@
       <c r="Z439" s="2"/>
       <c r="AA439" s="2"/>
     </row>
-    <row r="440" spans="1:27" ht="13.2">
+    <row r="440" spans="1:27" ht="12.75">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="14"/>
@@ -15282,7 +15295,7 @@
       <c r="Z440" s="2"/>
       <c r="AA440" s="2"/>
     </row>
-    <row r="441" spans="1:27" ht="13.2">
+    <row r="441" spans="1:27" ht="12.75">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="14"/>
@@ -15311,7 +15324,7 @@
       <c r="Z441" s="2"/>
       <c r="AA441" s="2"/>
     </row>
-    <row r="442" spans="1:27" ht="13.2">
+    <row r="442" spans="1:27" ht="12.75">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="14"/>
@@ -15340,7 +15353,7 @@
       <c r="Z442" s="2"/>
       <c r="AA442" s="2"/>
     </row>
-    <row r="443" spans="1:27" ht="13.2">
+    <row r="443" spans="1:27" ht="12.75">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="14"/>
@@ -15369,7 +15382,7 @@
       <c r="Z443" s="2"/>
       <c r="AA443" s="2"/>
     </row>
-    <row r="444" spans="1:27" ht="13.2">
+    <row r="444" spans="1:27" ht="12.75">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="14"/>
@@ -15398,7 +15411,7 @@
       <c r="Z444" s="2"/>
       <c r="AA444" s="2"/>
     </row>
-    <row r="445" spans="1:27" ht="13.2">
+    <row r="445" spans="1:27" ht="12.75">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="14"/>
@@ -15427,7 +15440,7 @@
       <c r="Z445" s="2"/>
       <c r="AA445" s="2"/>
     </row>
-    <row r="446" spans="1:27" ht="13.2">
+    <row r="446" spans="1:27" ht="12.75">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="14"/>
@@ -15456,7 +15469,7 @@
       <c r="Z446" s="2"/>
       <c r="AA446" s="2"/>
     </row>
-    <row r="447" spans="1:27" ht="13.2">
+    <row r="447" spans="1:27" ht="12.75">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="14"/>
@@ -15485,7 +15498,7 @@
       <c r="Z447" s="2"/>
       <c r="AA447" s="2"/>
     </row>
-    <row r="448" spans="1:27" ht="13.2">
+    <row r="448" spans="1:27" ht="12.75">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="14"/>
@@ -15514,7 +15527,7 @@
       <c r="Z448" s="2"/>
       <c r="AA448" s="2"/>
     </row>
-    <row r="449" spans="1:27" ht="13.2">
+    <row r="449" spans="1:27" ht="12.75">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="14"/>
@@ -15543,7 +15556,7 @@
       <c r="Z449" s="2"/>
       <c r="AA449" s="2"/>
     </row>
-    <row r="450" spans="1:27" ht="13.2">
+    <row r="450" spans="1:27" ht="12.75">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="14"/>
@@ -15572,7 +15585,7 @@
       <c r="Z450" s="2"/>
       <c r="AA450" s="2"/>
     </row>
-    <row r="451" spans="1:27" ht="13.2">
+    <row r="451" spans="1:27" ht="12.75">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="14"/>
@@ -15601,7 +15614,7 @@
       <c r="Z451" s="2"/>
       <c r="AA451" s="2"/>
     </row>
-    <row r="452" spans="1:27" ht="13.2">
+    <row r="452" spans="1:27" ht="12.75">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="14"/>
@@ -15630,7 +15643,7 @@
       <c r="Z452" s="2"/>
       <c r="AA452" s="2"/>
     </row>
-    <row r="453" spans="1:27" ht="13.2">
+    <row r="453" spans="1:27" ht="12.75">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="14"/>
@@ -15659,7 +15672,7 @@
       <c r="Z453" s="2"/>
       <c r="AA453" s="2"/>
     </row>
-    <row r="454" spans="1:27" ht="13.2">
+    <row r="454" spans="1:27" ht="12.75">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="14"/>
@@ -15688,7 +15701,7 @@
       <c r="Z454" s="2"/>
       <c r="AA454" s="2"/>
     </row>
-    <row r="455" spans="1:27" ht="13.2">
+    <row r="455" spans="1:27" ht="12.75">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="14"/>
@@ -15717,7 +15730,7 @@
       <c r="Z455" s="2"/>
       <c r="AA455" s="2"/>
     </row>
-    <row r="456" spans="1:27" ht="13.2">
+    <row r="456" spans="1:27" ht="12.75">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="14"/>
@@ -15746,7 +15759,7 @@
       <c r="Z456" s="2"/>
       <c r="AA456" s="2"/>
     </row>
-    <row r="457" spans="1:27" ht="13.2">
+    <row r="457" spans="1:27" ht="12.75">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="14"/>
@@ -15775,7 +15788,7 @@
       <c r="Z457" s="2"/>
       <c r="AA457" s="2"/>
     </row>
-    <row r="458" spans="1:27" ht="13.2">
+    <row r="458" spans="1:27" ht="12.75">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="14"/>
@@ -15804,7 +15817,7 @@
       <c r="Z458" s="2"/>
       <c r="AA458" s="2"/>
     </row>
-    <row r="459" spans="1:27" ht="13.2">
+    <row r="459" spans="1:27" ht="12.75">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="14"/>
@@ -15833,7 +15846,7 @@
       <c r="Z459" s="2"/>
       <c r="AA459" s="2"/>
     </row>
-    <row r="460" spans="1:27" ht="13.2">
+    <row r="460" spans="1:27" ht="12.75">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="14"/>
@@ -15862,7 +15875,7 @@
       <c r="Z460" s="2"/>
       <c r="AA460" s="2"/>
     </row>
-    <row r="461" spans="1:27" ht="13.2">
+    <row r="461" spans="1:27" ht="12.75">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="14"/>
@@ -15891,7 +15904,7 @@
       <c r="Z461" s="2"/>
       <c r="AA461" s="2"/>
     </row>
-    <row r="462" spans="1:27" ht="13.2">
+    <row r="462" spans="1:27" ht="12.75">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="14"/>
@@ -15920,7 +15933,7 @@
       <c r="Z462" s="2"/>
       <c r="AA462" s="2"/>
     </row>
-    <row r="463" spans="1:27" ht="13.2">
+    <row r="463" spans="1:27" ht="12.75">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="14"/>
@@ -15949,7 +15962,7 @@
       <c r="Z463" s="2"/>
       <c r="AA463" s="2"/>
     </row>
-    <row r="464" spans="1:27" ht="13.2">
+    <row r="464" spans="1:27" ht="12.75">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="14"/>
@@ -15978,7 +15991,7 @@
       <c r="Z464" s="2"/>
       <c r="AA464" s="2"/>
     </row>
-    <row r="465" spans="1:27" ht="13.2">
+    <row r="465" spans="1:27" ht="12.75">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="14"/>
@@ -16007,7 +16020,7 @@
       <c r="Z465" s="2"/>
       <c r="AA465" s="2"/>
     </row>
-    <row r="466" spans="1:27" ht="13.2">
+    <row r="466" spans="1:27" ht="12.75">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="14"/>
@@ -16036,7 +16049,7 @@
       <c r="Z466" s="2"/>
       <c r="AA466" s="2"/>
     </row>
-    <row r="467" spans="1:27" ht="13.2">
+    <row r="467" spans="1:27" ht="12.75">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="14"/>
@@ -16065,7 +16078,7 @@
       <c r="Z467" s="2"/>
       <c r="AA467" s="2"/>
     </row>
-    <row r="468" spans="1:27" ht="13.2">
+    <row r="468" spans="1:27" ht="12.75">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="14"/>
@@ -16094,7 +16107,7 @@
       <c r="Z468" s="2"/>
       <c r="AA468" s="2"/>
     </row>
-    <row r="469" spans="1:27" ht="13.2">
+    <row r="469" spans="1:27" ht="12.75">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="14"/>
@@ -16123,7 +16136,7 @@
       <c r="Z469" s="2"/>
       <c r="AA469" s="2"/>
     </row>
-    <row r="470" spans="1:27" ht="13.2">
+    <row r="470" spans="1:27" ht="12.75">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="14"/>
@@ -16152,7 +16165,7 @@
       <c r="Z470" s="2"/>
       <c r="AA470" s="2"/>
     </row>
-    <row r="471" spans="1:27" ht="13.2">
+    <row r="471" spans="1:27" ht="12.75">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="14"/>
@@ -16181,7 +16194,7 @@
       <c r="Z471" s="2"/>
       <c r="AA471" s="2"/>
     </row>
-    <row r="472" spans="1:27" ht="13.2">
+    <row r="472" spans="1:27" ht="12.75">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="14"/>
@@ -16210,7 +16223,7 @@
       <c r="Z472" s="2"/>
       <c r="AA472" s="2"/>
     </row>
-    <row r="473" spans="1:27" ht="13.2">
+    <row r="473" spans="1:27" ht="12.75">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="14"/>
@@ -16239,7 +16252,7 @@
       <c r="Z473" s="2"/>
       <c r="AA473" s="2"/>
     </row>
-    <row r="474" spans="1:27" ht="13.2">
+    <row r="474" spans="1:27" ht="12.75">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="14"/>
@@ -16268,7 +16281,7 @@
       <c r="Z474" s="2"/>
       <c r="AA474" s="2"/>
     </row>
-    <row r="475" spans="1:27" ht="13.2">
+    <row r="475" spans="1:27" ht="12.75">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="14"/>
@@ -16297,7 +16310,7 @@
       <c r="Z475" s="2"/>
       <c r="AA475" s="2"/>
     </row>
-    <row r="476" spans="1:27" ht="13.2">
+    <row r="476" spans="1:27" ht="12.75">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="14"/>
@@ -16326,7 +16339,7 @@
       <c r="Z476" s="2"/>
       <c r="AA476" s="2"/>
     </row>
-    <row r="477" spans="1:27" ht="13.2">
+    <row r="477" spans="1:27" ht="12.75">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="14"/>
@@ -16355,7 +16368,7 @@
       <c r="Z477" s="2"/>
       <c r="AA477" s="2"/>
     </row>
-    <row r="478" spans="1:27" ht="13.2">
+    <row r="478" spans="1:27" ht="12.75">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="14"/>
@@ -16384,7 +16397,7 @@
       <c r="Z478" s="2"/>
       <c r="AA478" s="2"/>
     </row>
-    <row r="479" spans="1:27" ht="13.2">
+    <row r="479" spans="1:27" ht="12.75">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="14"/>
@@ -16413,7 +16426,7 @@
       <c r="Z479" s="2"/>
       <c r="AA479" s="2"/>
     </row>
-    <row r="480" spans="1:27" ht="13.2">
+    <row r="480" spans="1:27" ht="12.75">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="14"/>
@@ -16442,7 +16455,7 @@
       <c r="Z480" s="2"/>
       <c r="AA480" s="2"/>
     </row>
-    <row r="481" spans="1:27" ht="13.2">
+    <row r="481" spans="1:27" ht="12.75">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="14"/>
@@ -16471,7 +16484,7 @@
       <c r="Z481" s="2"/>
       <c r="AA481" s="2"/>
     </row>
-    <row r="482" spans="1:27" ht="13.2">
+    <row r="482" spans="1:27" ht="12.75">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="14"/>
@@ -16500,7 +16513,7 @@
       <c r="Z482" s="2"/>
       <c r="AA482" s="2"/>
     </row>
-    <row r="483" spans="1:27" ht="13.2">
+    <row r="483" spans="1:27" ht="12.75">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="14"/>
@@ -16529,7 +16542,7 @@
       <c r="Z483" s="2"/>
       <c r="AA483" s="2"/>
     </row>
-    <row r="484" spans="1:27" ht="13.2">
+    <row r="484" spans="1:27" ht="12.75">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="14"/>
@@ -16558,7 +16571,7 @@
       <c r="Z484" s="2"/>
       <c r="AA484" s="2"/>
     </row>
-    <row r="485" spans="1:27" ht="13.2">
+    <row r="485" spans="1:27" ht="12.75">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="14"/>
@@ -16587,7 +16600,7 @@
       <c r="Z485" s="2"/>
       <c r="AA485" s="2"/>
     </row>
-    <row r="486" spans="1:27" ht="13.2">
+    <row r="486" spans="1:27" ht="12.75">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="14"/>
@@ -16616,7 +16629,7 @@
       <c r="Z486" s="2"/>
       <c r="AA486" s="2"/>
     </row>
-    <row r="487" spans="1:27" ht="13.2">
+    <row r="487" spans="1:27" ht="12.75">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="14"/>
@@ -16645,7 +16658,7 @@
       <c r="Z487" s="2"/>
       <c r="AA487" s="2"/>
     </row>
-    <row r="488" spans="1:27" ht="13.2">
+    <row r="488" spans="1:27" ht="12.75">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="14"/>
@@ -16674,7 +16687,7 @@
       <c r="Z488" s="2"/>
       <c r="AA488" s="2"/>
     </row>
-    <row r="489" spans="1:27" ht="13.2">
+    <row r="489" spans="1:27" ht="12.75">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="14"/>
@@ -16703,7 +16716,7 @@
       <c r="Z489" s="2"/>
       <c r="AA489" s="2"/>
     </row>
-    <row r="490" spans="1:27" ht="13.2">
+    <row r="490" spans="1:27" ht="12.75">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="14"/>
@@ -16732,7 +16745,7 @@
       <c r="Z490" s="2"/>
       <c r="AA490" s="2"/>
     </row>
-    <row r="491" spans="1:27" ht="13.2">
+    <row r="491" spans="1:27" ht="12.75">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="14"/>
@@ -16761,7 +16774,7 @@
       <c r="Z491" s="2"/>
       <c r="AA491" s="2"/>
     </row>
-    <row r="492" spans="1:27" ht="13.2">
+    <row r="492" spans="1:27" ht="12.75">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="14"/>
@@ -16790,7 +16803,7 @@
       <c r="Z492" s="2"/>
       <c r="AA492" s="2"/>
     </row>
-    <row r="493" spans="1:27" ht="13.2">
+    <row r="493" spans="1:27" ht="12.75">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="14"/>
@@ -16819,7 +16832,7 @@
       <c r="Z493" s="2"/>
       <c r="AA493" s="2"/>
     </row>
-    <row r="494" spans="1:27" ht="13.2">
+    <row r="494" spans="1:27" ht="12.75">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="14"/>
@@ -16848,7 +16861,7 @@
       <c r="Z494" s="2"/>
       <c r="AA494" s="2"/>
     </row>
-    <row r="495" spans="1:27" ht="13.2">
+    <row r="495" spans="1:27" ht="12.75">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="14"/>
@@ -16877,7 +16890,7 @@
       <c r="Z495" s="2"/>
       <c r="AA495" s="2"/>
     </row>
-    <row r="496" spans="1:27" ht="13.2">
+    <row r="496" spans="1:27" ht="12.75">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="14"/>
@@ -16906,7 +16919,7 @@
       <c r="Z496" s="2"/>
       <c r="AA496" s="2"/>
     </row>
-    <row r="497" spans="1:27" ht="13.2">
+    <row r="497" spans="1:27" ht="12.75">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="14"/>
@@ -16935,7 +16948,7 @@
       <c r="Z497" s="2"/>
       <c r="AA497" s="2"/>
     </row>
-    <row r="498" spans="1:27" ht="13.2">
+    <row r="498" spans="1:27" ht="12.75">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="14"/>
@@ -16964,7 +16977,7 @@
       <c r="Z498" s="2"/>
       <c r="AA498" s="2"/>
     </row>
-    <row r="499" spans="1:27" ht="13.2">
+    <row r="499" spans="1:27" ht="12.75">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="14"/>
@@ -16993,7 +17006,7 @@
       <c r="Z499" s="2"/>
       <c r="AA499" s="2"/>
     </row>
-    <row r="500" spans="1:27" ht="13.2">
+    <row r="500" spans="1:27" ht="12.75">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="14"/>
@@ -17022,7 +17035,7 @@
       <c r="Z500" s="2"/>
       <c r="AA500" s="2"/>
     </row>
-    <row r="501" spans="1:27" ht="13.2">
+    <row r="501" spans="1:27" ht="12.75">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="14"/>
@@ -17051,7 +17064,7 @@
       <c r="Z501" s="2"/>
       <c r="AA501" s="2"/>
     </row>
-    <row r="502" spans="1:27" ht="13.2">
+    <row r="502" spans="1:27" ht="12.75">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="14"/>
@@ -17080,7 +17093,7 @@
       <c r="Z502" s="2"/>
       <c r="AA502" s="2"/>
     </row>
-    <row r="503" spans="1:27" ht="13.2">
+    <row r="503" spans="1:27" ht="12.75">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="14"/>
@@ -17109,7 +17122,7 @@
       <c r="Z503" s="2"/>
       <c r="AA503" s="2"/>
     </row>
-    <row r="504" spans="1:27" ht="13.2">
+    <row r="504" spans="1:27" ht="12.75">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="14"/>
@@ -17138,7 +17151,7 @@
       <c r="Z504" s="2"/>
       <c r="AA504" s="2"/>
     </row>
-    <row r="505" spans="1:27" ht="13.2">
+    <row r="505" spans="1:27" ht="12.75">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="14"/>
@@ -17167,7 +17180,7 @@
       <c r="Z505" s="2"/>
       <c r="AA505" s="2"/>
     </row>
-    <row r="506" spans="1:27" ht="13.2">
+    <row r="506" spans="1:27" ht="12.75">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
       <c r="C506" s="14"/>
@@ -17196,7 +17209,7 @@
       <c r="Z506" s="2"/>
       <c r="AA506" s="2"/>
     </row>
-    <row r="507" spans="1:27" ht="13.2">
+    <row r="507" spans="1:27" ht="12.75">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="14"/>
@@ -17225,7 +17238,7 @@
       <c r="Z507" s="2"/>
       <c r="AA507" s="2"/>
     </row>
-    <row r="508" spans="1:27" ht="13.2">
+    <row r="508" spans="1:27" ht="12.75">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="14"/>
@@ -17254,7 +17267,7 @@
       <c r="Z508" s="2"/>
       <c r="AA508" s="2"/>
     </row>
-    <row r="509" spans="1:27" ht="13.2">
+    <row r="509" spans="1:27" ht="12.75">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="14"/>
@@ -17283,7 +17296,7 @@
       <c r="Z509" s="2"/>
       <c r="AA509" s="2"/>
     </row>
-    <row r="510" spans="1:27" ht="13.2">
+    <row r="510" spans="1:27" ht="12.75">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="14"/>
@@ -17312,7 +17325,7 @@
       <c r="Z510" s="2"/>
       <c r="AA510" s="2"/>
     </row>
-    <row r="511" spans="1:27" ht="13.2">
+    <row r="511" spans="1:27" ht="12.75">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="14"/>
@@ -17341,7 +17354,7 @@
       <c r="Z511" s="2"/>
       <c r="AA511" s="2"/>
     </row>
-    <row r="512" spans="1:27" ht="13.2">
+    <row r="512" spans="1:27" ht="12.75">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
       <c r="C512" s="14"/>
@@ -17370,7 +17383,7 @@
       <c r="Z512" s="2"/>
       <c r="AA512" s="2"/>
     </row>
-    <row r="513" spans="1:27" ht="13.2">
+    <row r="513" spans="1:27" ht="12.75">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="14"/>
@@ -17399,7 +17412,7 @@
       <c r="Z513" s="2"/>
       <c r="AA513" s="2"/>
     </row>
-    <row r="514" spans="1:27" ht="13.2">
+    <row r="514" spans="1:27" ht="12.75">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="14"/>
@@ -17428,7 +17441,7 @@
       <c r="Z514" s="2"/>
       <c r="AA514" s="2"/>
     </row>
-    <row r="515" spans="1:27" ht="13.2">
+    <row r="515" spans="1:27" ht="12.75">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="14"/>
@@ -17457,7 +17470,7 @@
       <c r="Z515" s="2"/>
       <c r="AA515" s="2"/>
     </row>
-    <row r="516" spans="1:27" ht="13.2">
+    <row r="516" spans="1:27" ht="12.75">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="14"/>
@@ -17486,7 +17499,7 @@
       <c r="Z516" s="2"/>
       <c r="AA516" s="2"/>
     </row>
-    <row r="517" spans="1:27" ht="13.2">
+    <row r="517" spans="1:27" ht="12.75">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="14"/>
@@ -17515,7 +17528,7 @@
       <c r="Z517" s="2"/>
       <c r="AA517" s="2"/>
     </row>
-    <row r="518" spans="1:27" ht="13.2">
+    <row r="518" spans="1:27" ht="12.75">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
       <c r="C518" s="14"/>
@@ -17544,7 +17557,7 @@
       <c r="Z518" s="2"/>
       <c r="AA518" s="2"/>
     </row>
-    <row r="519" spans="1:27" ht="13.2">
+    <row r="519" spans="1:27" ht="12.75">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="14"/>
@@ -17573,7 +17586,7 @@
       <c r="Z519" s="2"/>
       <c r="AA519" s="2"/>
     </row>
-    <row r="520" spans="1:27" ht="13.2">
+    <row r="520" spans="1:27" ht="12.75">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="14"/>
@@ -17602,7 +17615,7 @@
       <c r="Z520" s="2"/>
       <c r="AA520" s="2"/>
     </row>
-    <row r="521" spans="1:27" ht="13.2">
+    <row r="521" spans="1:27" ht="12.75">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="14"/>
@@ -17631,7 +17644,7 @@
       <c r="Z521" s="2"/>
       <c r="AA521" s="2"/>
     </row>
-    <row r="522" spans="1:27" ht="13.2">
+    <row r="522" spans="1:27" ht="12.75">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
       <c r="C522" s="14"/>
@@ -17660,7 +17673,7 @@
       <c r="Z522" s="2"/>
       <c r="AA522" s="2"/>
     </row>
-    <row r="523" spans="1:27" ht="13.2">
+    <row r="523" spans="1:27" ht="12.75">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="14"/>
@@ -17689,7 +17702,7 @@
       <c r="Z523" s="2"/>
       <c r="AA523" s="2"/>
     </row>
-    <row r="524" spans="1:27" ht="13.2">
+    <row r="524" spans="1:27" ht="12.75">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="14"/>
@@ -17718,7 +17731,7 @@
       <c r="Z524" s="2"/>
       <c r="AA524" s="2"/>
     </row>
-    <row r="525" spans="1:27" ht="13.2">
+    <row r="525" spans="1:27" ht="12.75">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="14"/>
@@ -17747,7 +17760,7 @@
       <c r="Z525" s="2"/>
       <c r="AA525" s="2"/>
     </row>
-    <row r="526" spans="1:27" ht="13.2">
+    <row r="526" spans="1:27" ht="12.75">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="14"/>
@@ -17776,7 +17789,7 @@
       <c r="Z526" s="2"/>
       <c r="AA526" s="2"/>
     </row>
-    <row r="527" spans="1:27" ht="13.2">
+    <row r="527" spans="1:27" ht="12.75">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
       <c r="C527" s="14"/>
@@ -17805,7 +17818,7 @@
       <c r="Z527" s="2"/>
       <c r="AA527" s="2"/>
     </row>
-    <row r="528" spans="1:27" ht="13.2">
+    <row r="528" spans="1:27" ht="12.75">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="14"/>
@@ -17834,7 +17847,7 @@
       <c r="Z528" s="2"/>
       <c r="AA528" s="2"/>
     </row>
-    <row r="529" spans="1:27" ht="13.2">
+    <row r="529" spans="1:27" ht="12.75">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="14"/>
@@ -17863,7 +17876,7 @@
       <c r="Z529" s="2"/>
       <c r="AA529" s="2"/>
     </row>
-    <row r="530" spans="1:27" ht="13.2">
+    <row r="530" spans="1:27" ht="12.75">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
       <c r="C530" s="14"/>
@@ -17892,7 +17905,7 @@
       <c r="Z530" s="2"/>
       <c r="AA530" s="2"/>
     </row>
-    <row r="531" spans="1:27" ht="13.2">
+    <row r="531" spans="1:27" ht="12.75">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="14"/>
@@ -17921,7 +17934,7 @@
       <c r="Z531" s="2"/>
       <c r="AA531" s="2"/>
     </row>
-    <row r="532" spans="1:27" ht="13.2">
+    <row r="532" spans="1:27" ht="12.75">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="14"/>
@@ -17950,7 +17963,7 @@
       <c r="Z532" s="2"/>
       <c r="AA532" s="2"/>
     </row>
-    <row r="533" spans="1:27" ht="13.2">
+    <row r="533" spans="1:27" ht="12.75">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="14"/>
@@ -17979,7 +17992,7 @@
       <c r="Z533" s="2"/>
       <c r="AA533" s="2"/>
     </row>
-    <row r="534" spans="1:27" ht="13.2">
+    <row r="534" spans="1:27" ht="12.75">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
       <c r="C534" s="14"/>
@@ -18008,7 +18021,7 @@
       <c r="Z534" s="2"/>
       <c r="AA534" s="2"/>
     </row>
-    <row r="535" spans="1:27" ht="13.2">
+    <row r="535" spans="1:27" ht="12.75">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="14"/>
@@ -18037,7 +18050,7 @@
       <c r="Z535" s="2"/>
       <c r="AA535" s="2"/>
     </row>
-    <row r="536" spans="1:27" ht="13.2">
+    <row r="536" spans="1:27" ht="12.75">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="14"/>
@@ -18066,7 +18079,7 @@
       <c r="Z536" s="2"/>
       <c r="AA536" s="2"/>
     </row>
-    <row r="537" spans="1:27" ht="13.2">
+    <row r="537" spans="1:27" ht="12.75">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="14"/>
@@ -18095,7 +18108,7 @@
       <c r="Z537" s="2"/>
       <c r="AA537" s="2"/>
     </row>
-    <row r="538" spans="1:27" ht="13.2">
+    <row r="538" spans="1:27" ht="12.75">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="14"/>
@@ -18124,7 +18137,7 @@
       <c r="Z538" s="2"/>
       <c r="AA538" s="2"/>
     </row>
-    <row r="539" spans="1:27" ht="13.2">
+    <row r="539" spans="1:27" ht="12.75">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="14"/>
@@ -18153,7 +18166,7 @@
       <c r="Z539" s="2"/>
       <c r="AA539" s="2"/>
     </row>
-    <row r="540" spans="1:27" ht="13.2">
+    <row r="540" spans="1:27" ht="12.75">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
       <c r="C540" s="14"/>
@@ -18182,7 +18195,7 @@
       <c r="Z540" s="2"/>
       <c r="AA540" s="2"/>
     </row>
-    <row r="541" spans="1:27" ht="13.2">
+    <row r="541" spans="1:27" ht="12.75">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
       <c r="C541" s="14"/>
@@ -18211,7 +18224,7 @@
       <c r="Z541" s="2"/>
       <c r="AA541" s="2"/>
     </row>
-    <row r="542" spans="1:27" ht="13.2">
+    <row r="542" spans="1:27" ht="12.75">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
       <c r="C542" s="14"/>
@@ -18240,7 +18253,7 @@
       <c r="Z542" s="2"/>
       <c r="AA542" s="2"/>
     </row>
-    <row r="543" spans="1:27" ht="13.2">
+    <row r="543" spans="1:27" ht="12.75">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="14"/>
@@ -18269,7 +18282,7 @@
       <c r="Z543" s="2"/>
       <c r="AA543" s="2"/>
     </row>
-    <row r="544" spans="1:27" ht="13.2">
+    <row r="544" spans="1:27" ht="12.75">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="14"/>
@@ -18298,7 +18311,7 @@
       <c r="Z544" s="2"/>
       <c r="AA544" s="2"/>
     </row>
-    <row r="545" spans="1:27" ht="13.2">
+    <row r="545" spans="1:27" ht="12.75">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="14"/>
@@ -18327,7 +18340,7 @@
       <c r="Z545" s="2"/>
       <c r="AA545" s="2"/>
     </row>
-    <row r="546" spans="1:27" ht="13.2">
+    <row r="546" spans="1:27" ht="12.75">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="14"/>
@@ -18356,7 +18369,7 @@
       <c r="Z546" s="2"/>
       <c r="AA546" s="2"/>
     </row>
-    <row r="547" spans="1:27" ht="13.2">
+    <row r="547" spans="1:27" ht="12.75">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
       <c r="C547" s="14"/>
@@ -18385,7 +18398,7 @@
       <c r="Z547" s="2"/>
       <c r="AA547" s="2"/>
     </row>
-    <row r="548" spans="1:27" ht="13.2">
+    <row r="548" spans="1:27" ht="12.75">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="14"/>
@@ -18414,7 +18427,7 @@
       <c r="Z548" s="2"/>
       <c r="AA548" s="2"/>
     </row>
-    <row r="549" spans="1:27" ht="13.2">
+    <row r="549" spans="1:27" ht="12.75">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
       <c r="C549" s="14"/>
@@ -18443,7 +18456,7 @@
       <c r="Z549" s="2"/>
       <c r="AA549" s="2"/>
     </row>
-    <row r="550" spans="1:27" ht="13.2">
+    <row r="550" spans="1:27" ht="12.75">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="14"/>
@@ -18472,7 +18485,7 @@
       <c r="Z550" s="2"/>
       <c r="AA550" s="2"/>
     </row>
-    <row r="551" spans="1:27" ht="13.2">
+    <row r="551" spans="1:27" ht="12.75">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
       <c r="C551" s="14"/>
@@ -18501,7 +18514,7 @@
       <c r="Z551" s="2"/>
       <c r="AA551" s="2"/>
     </row>
-    <row r="552" spans="1:27" ht="13.2">
+    <row r="552" spans="1:27" ht="12.75">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="14"/>
@@ -18530,7 +18543,7 @@
       <c r="Z552" s="2"/>
       <c r="AA552" s="2"/>
     </row>
-    <row r="553" spans="1:27" ht="13.2">
+    <row r="553" spans="1:27" ht="12.75">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="14"/>
@@ -18559,7 +18572,7 @@
       <c r="Z553" s="2"/>
       <c r="AA553" s="2"/>
     </row>
-    <row r="554" spans="1:27" ht="13.2">
+    <row r="554" spans="1:27" ht="12.75">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="14"/>
@@ -18588,7 +18601,7 @@
       <c r="Z554" s="2"/>
       <c r="AA554" s="2"/>
     </row>
-    <row r="555" spans="1:27" ht="13.2">
+    <row r="555" spans="1:27" ht="12.75">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
       <c r="C555" s="14"/>
@@ -18617,7 +18630,7 @@
       <c r="Z555" s="2"/>
       <c r="AA555" s="2"/>
     </row>
-    <row r="556" spans="1:27" ht="13.2">
+    <row r="556" spans="1:27" ht="12.75">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
       <c r="C556" s="14"/>
@@ -18646,7 +18659,7 @@
       <c r="Z556" s="2"/>
       <c r="AA556" s="2"/>
     </row>
-    <row r="557" spans="1:27" ht="13.2">
+    <row r="557" spans="1:27" ht="12.75">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="14"/>
@@ -18675,7 +18688,7 @@
       <c r="Z557" s="2"/>
       <c r="AA557" s="2"/>
     </row>
-    <row r="558" spans="1:27" ht="13.2">
+    <row r="558" spans="1:27" ht="12.75">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="14"/>
@@ -18704,7 +18717,7 @@
       <c r="Z558" s="2"/>
       <c r="AA558" s="2"/>
     </row>
-    <row r="559" spans="1:27" ht="13.2">
+    <row r="559" spans="1:27" ht="12.75">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
       <c r="C559" s="14"/>
@@ -18733,7 +18746,7 @@
       <c r="Z559" s="2"/>
       <c r="AA559" s="2"/>
     </row>
-    <row r="560" spans="1:27" ht="13.2">
+    <row r="560" spans="1:27" ht="12.75">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="14"/>
@@ -18762,7 +18775,7 @@
       <c r="Z560" s="2"/>
       <c r="AA560" s="2"/>
     </row>
-    <row r="561" spans="1:27" ht="13.2">
+    <row r="561" spans="1:27" ht="12.75">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="14"/>
@@ -18791,7 +18804,7 @@
       <c r="Z561" s="2"/>
       <c r="AA561" s="2"/>
     </row>
-    <row r="562" spans="1:27" ht="13.2">
+    <row r="562" spans="1:27" ht="12.75">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="14"/>
@@ -18820,7 +18833,7 @@
       <c r="Z562" s="2"/>
       <c r="AA562" s="2"/>
     </row>
-    <row r="563" spans="1:27" ht="13.2">
+    <row r="563" spans="1:27" ht="12.75">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="14"/>
@@ -18849,7 +18862,7 @@
       <c r="Z563" s="2"/>
       <c r="AA563" s="2"/>
     </row>
-    <row r="564" spans="1:27" ht="13.2">
+    <row r="564" spans="1:27" ht="12.75">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="14"/>
@@ -18878,7 +18891,7 @@
       <c r="Z564" s="2"/>
       <c r="AA564" s="2"/>
     </row>
-    <row r="565" spans="1:27" ht="13.2">
+    <row r="565" spans="1:27" ht="12.75">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
       <c r="C565" s="14"/>
@@ -18907,7 +18920,7 @@
       <c r="Z565" s="2"/>
       <c r="AA565" s="2"/>
     </row>
-    <row r="566" spans="1:27" ht="13.2">
+    <row r="566" spans="1:27" ht="12.75">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="14"/>
@@ -18936,7 +18949,7 @@
       <c r="Z566" s="2"/>
       <c r="AA566" s="2"/>
     </row>
-    <row r="567" spans="1:27" ht="13.2">
+    <row r="567" spans="1:27" ht="12.75">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="14"/>
@@ -18965,7 +18978,7 @@
       <c r="Z567" s="2"/>
       <c r="AA567" s="2"/>
     </row>
-    <row r="568" spans="1:27" ht="13.2">
+    <row r="568" spans="1:27" ht="12.75">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
       <c r="C568" s="14"/>
@@ -18994,7 +19007,7 @@
       <c r="Z568" s="2"/>
       <c r="AA568" s="2"/>
     </row>
-    <row r="569" spans="1:27" ht="13.2">
+    <row r="569" spans="1:27" ht="12.75">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="14"/>
@@ -19023,7 +19036,7 @@
       <c r="Z569" s="2"/>
       <c r="AA569" s="2"/>
     </row>
-    <row r="570" spans="1:27" ht="13.2">
+    <row r="570" spans="1:27" ht="12.75">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="14"/>
@@ -19052,7 +19065,7 @@
       <c r="Z570" s="2"/>
       <c r="AA570" s="2"/>
     </row>
-    <row r="571" spans="1:27" ht="13.2">
+    <row r="571" spans="1:27" ht="12.75">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="14"/>
@@ -19081,7 +19094,7 @@
       <c r="Z571" s="2"/>
       <c r="AA571" s="2"/>
     </row>
-    <row r="572" spans="1:27" ht="13.2">
+    <row r="572" spans="1:27" ht="12.75">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
       <c r="C572" s="14"/>
@@ -19110,7 +19123,7 @@
       <c r="Z572" s="2"/>
       <c r="AA572" s="2"/>
     </row>
-    <row r="573" spans="1:27" ht="13.2">
+    <row r="573" spans="1:27" ht="12.75">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="14"/>
@@ -19139,7 +19152,7 @@
       <c r="Z573" s="2"/>
       <c r="AA573" s="2"/>
     </row>
-    <row r="574" spans="1:27" ht="13.2">
+    <row r="574" spans="1:27" ht="12.75">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="14"/>
@@ -19168,7 +19181,7 @@
       <c r="Z574" s="2"/>
       <c r="AA574" s="2"/>
     </row>
-    <row r="575" spans="1:27" ht="13.2">
+    <row r="575" spans="1:27" ht="12.75">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="14"/>
@@ -19197,7 +19210,7 @@
       <c r="Z575" s="2"/>
       <c r="AA575" s="2"/>
     </row>
-    <row r="576" spans="1:27" ht="13.2">
+    <row r="576" spans="1:27" ht="12.75">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="14"/>
@@ -19226,7 +19239,7 @@
       <c r="Z576" s="2"/>
       <c r="AA576" s="2"/>
     </row>
-    <row r="577" spans="1:27" ht="13.2">
+    <row r="577" spans="1:27" ht="12.75">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="14"/>
@@ -19255,7 +19268,7 @@
       <c r="Z577" s="2"/>
       <c r="AA577" s="2"/>
     </row>
-    <row r="578" spans="1:27" ht="13.2">
+    <row r="578" spans="1:27" ht="12.75">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
       <c r="C578" s="14"/>
@@ -19284,7 +19297,7 @@
       <c r="Z578" s="2"/>
       <c r="AA578" s="2"/>
     </row>
-    <row r="579" spans="1:27" ht="13.2">
+    <row r="579" spans="1:27" ht="12.75">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
       <c r="C579" s="14"/>
@@ -19313,7 +19326,7 @@
       <c r="Z579" s="2"/>
       <c r="AA579" s="2"/>
     </row>
-    <row r="580" spans="1:27" ht="13.2">
+    <row r="580" spans="1:27" ht="12.75">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="14"/>
@@ -19342,7 +19355,7 @@
       <c r="Z580" s="2"/>
       <c r="AA580" s="2"/>
     </row>
-    <row r="581" spans="1:27" ht="13.2">
+    <row r="581" spans="1:27" ht="12.75">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="14"/>
@@ -19371,7 +19384,7 @@
       <c r="Z581" s="2"/>
       <c r="AA581" s="2"/>
     </row>
-    <row r="582" spans="1:27" ht="13.2">
+    <row r="582" spans="1:27" ht="12.75">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
       <c r="C582" s="14"/>
@@ -19400,7 +19413,7 @@
       <c r="Z582" s="2"/>
       <c r="AA582" s="2"/>
     </row>
-    <row r="583" spans="1:27" ht="13.2">
+    <row r="583" spans="1:27" ht="12.75">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="14"/>
@@ -19429,7 +19442,7 @@
       <c r="Z583" s="2"/>
       <c r="AA583" s="2"/>
     </row>
-    <row r="584" spans="1:27" ht="13.2">
+    <row r="584" spans="1:27" ht="12.75">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
       <c r="C584" s="14"/>
@@ -19458,7 +19471,7 @@
       <c r="Z584" s="2"/>
       <c r="AA584" s="2"/>
     </row>
-    <row r="585" spans="1:27" ht="13.2">
+    <row r="585" spans="1:27" ht="12.75">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="14"/>
@@ -19487,7 +19500,7 @@
       <c r="Z585" s="2"/>
       <c r="AA585" s="2"/>
     </row>
-    <row r="586" spans="1:27" ht="13.2">
+    <row r="586" spans="1:27" ht="12.75">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="14"/>
@@ -19516,7 +19529,7 @@
       <c r="Z586" s="2"/>
       <c r="AA586" s="2"/>
     </row>
-    <row r="587" spans="1:27" ht="13.2">
+    <row r="587" spans="1:27" ht="12.75">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="14"/>
@@ -19545,7 +19558,7 @@
       <c r="Z587" s="2"/>
       <c r="AA587" s="2"/>
     </row>
-    <row r="588" spans="1:27" ht="13.2">
+    <row r="588" spans="1:27" ht="12.75">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
       <c r="C588" s="14"/>
@@ -19574,7 +19587,7 @@
       <c r="Z588" s="2"/>
       <c r="AA588" s="2"/>
     </row>
-    <row r="589" spans="1:27" ht="13.2">
+    <row r="589" spans="1:27" ht="12.75">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="14"/>
@@ -19603,7 +19616,7 @@
       <c r="Z589" s="2"/>
       <c r="AA589" s="2"/>
     </row>
-    <row r="590" spans="1:27" ht="13.2">
+    <row r="590" spans="1:27" ht="12.75">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="14"/>
@@ -19632,7 +19645,7 @@
       <c r="Z590" s="2"/>
       <c r="AA590" s="2"/>
     </row>
-    <row r="591" spans="1:27" ht="13.2">
+    <row r="591" spans="1:27" ht="12.75">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="14"/>
@@ -19661,7 +19674,7 @@
       <c r="Z591" s="2"/>
       <c r="AA591" s="2"/>
     </row>
-    <row r="592" spans="1:27" ht="13.2">
+    <row r="592" spans="1:27" ht="12.75">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="14"/>
@@ -19690,7 +19703,7 @@
       <c r="Z592" s="2"/>
       <c r="AA592" s="2"/>
     </row>
-    <row r="593" spans="1:27" ht="13.2">
+    <row r="593" spans="1:27" ht="12.75">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
       <c r="C593" s="14"/>
@@ -19719,7 +19732,7 @@
       <c r="Z593" s="2"/>
       <c r="AA593" s="2"/>
     </row>
-    <row r="594" spans="1:27" ht="13.2">
+    <row r="594" spans="1:27" ht="12.75">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="14"/>
@@ -19748,7 +19761,7 @@
       <c r="Z594" s="2"/>
       <c r="AA594" s="2"/>
     </row>
-    <row r="595" spans="1:27" ht="13.2">
+    <row r="595" spans="1:27" ht="12.75">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="14"/>
@@ -19777,7 +19790,7 @@
       <c r="Z595" s="2"/>
       <c r="AA595" s="2"/>
     </row>
-    <row r="596" spans="1:27" ht="13.2">
+    <row r="596" spans="1:27" ht="12.75">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="14"/>
@@ -19806,7 +19819,7 @@
       <c r="Z596" s="2"/>
       <c r="AA596" s="2"/>
     </row>
-    <row r="597" spans="1:27" ht="13.2">
+    <row r="597" spans="1:27" ht="12.75">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="14"/>
@@ -19835,7 +19848,7 @@
       <c r="Z597" s="2"/>
       <c r="AA597" s="2"/>
     </row>
-    <row r="598" spans="1:27" ht="13.2">
+    <row r="598" spans="1:27" ht="12.75">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="14"/>
@@ -19864,7 +19877,7 @@
       <c r="Z598" s="2"/>
       <c r="AA598" s="2"/>
     </row>
-    <row r="599" spans="1:27" ht="13.2">
+    <row r="599" spans="1:27" ht="12.75">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
       <c r="C599" s="14"/>
@@ -19893,7 +19906,7 @@
       <c r="Z599" s="2"/>
       <c r="AA599" s="2"/>
     </row>
-    <row r="600" spans="1:27" ht="13.2">
+    <row r="600" spans="1:27" ht="12.75">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="14"/>
@@ -19922,7 +19935,7 @@
       <c r="Z600" s="2"/>
       <c r="AA600" s="2"/>
     </row>
-    <row r="601" spans="1:27" ht="13.2">
+    <row r="601" spans="1:27" ht="12.75">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="14"/>
@@ -19951,7 +19964,7 @@
       <c r="Z601" s="2"/>
       <c r="AA601" s="2"/>
     </row>
-    <row r="602" spans="1:27" ht="13.2">
+    <row r="602" spans="1:27" ht="12.75">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="14"/>
@@ -19980,7 +19993,7 @@
       <c r="Z602" s="2"/>
       <c r="AA602" s="2"/>
     </row>
-    <row r="603" spans="1:27" ht="13.2">
+    <row r="603" spans="1:27" ht="12.75">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="14"/>
@@ -20009,7 +20022,7 @@
       <c r="Z603" s="2"/>
       <c r="AA603" s="2"/>
     </row>
-    <row r="604" spans="1:27" ht="13.2">
+    <row r="604" spans="1:27" ht="12.75">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
       <c r="C604" s="14"/>
@@ -20038,7 +20051,7 @@
       <c r="Z604" s="2"/>
       <c r="AA604" s="2"/>
     </row>
-    <row r="605" spans="1:27" ht="13.2">
+    <row r="605" spans="1:27" ht="12.75">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
       <c r="C605" s="14"/>
@@ -20067,7 +20080,7 @@
       <c r="Z605" s="2"/>
       <c r="AA605" s="2"/>
     </row>
-    <row r="606" spans="1:27" ht="13.2">
+    <row r="606" spans="1:27" ht="12.75">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
       <c r="C606" s="14"/>
@@ -20096,7 +20109,7 @@
       <c r="Z606" s="2"/>
       <c r="AA606" s="2"/>
     </row>
-    <row r="607" spans="1:27" ht="13.2">
+    <row r="607" spans="1:27" ht="12.75">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
       <c r="C607" s="14"/>
@@ -20125,7 +20138,7 @@
       <c r="Z607" s="2"/>
       <c r="AA607" s="2"/>
     </row>
-    <row r="608" spans="1:27" ht="13.2">
+    <row r="608" spans="1:27" ht="12.75">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
       <c r="C608" s="14"/>
@@ -20154,7 +20167,7 @@
       <c r="Z608" s="2"/>
       <c r="AA608" s="2"/>
     </row>
-    <row r="609" spans="1:27" ht="13.2">
+    <row r="609" spans="1:27" ht="12.75">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
       <c r="C609" s="14"/>
@@ -20183,7 +20196,7 @@
       <c r="Z609" s="2"/>
       <c r="AA609" s="2"/>
     </row>
-    <row r="610" spans="1:27" ht="13.2">
+    <row r="610" spans="1:27" ht="12.75">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
       <c r="C610" s="14"/>
@@ -20212,7 +20225,7 @@
       <c r="Z610" s="2"/>
       <c r="AA610" s="2"/>
     </row>
-    <row r="611" spans="1:27" ht="13.2">
+    <row r="611" spans="1:27" ht="12.75">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
       <c r="C611" s="14"/>
@@ -20241,7 +20254,7 @@
       <c r="Z611" s="2"/>
       <c r="AA611" s="2"/>
     </row>
-    <row r="612" spans="1:27" ht="13.2">
+    <row r="612" spans="1:27" ht="12.75">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
       <c r="C612" s="14"/>
@@ -20270,7 +20283,7 @@
       <c r="Z612" s="2"/>
       <c r="AA612" s="2"/>
     </row>
-    <row r="613" spans="1:27" ht="13.2">
+    <row r="613" spans="1:27" ht="12.75">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
       <c r="C613" s="14"/>
@@ -20299,7 +20312,7 @@
       <c r="Z613" s="2"/>
       <c r="AA613" s="2"/>
     </row>
-    <row r="614" spans="1:27" ht="13.2">
+    <row r="614" spans="1:27" ht="12.75">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
       <c r="C614" s="14"/>
@@ -20328,7 +20341,7 @@
       <c r="Z614" s="2"/>
       <c r="AA614" s="2"/>
     </row>
-    <row r="615" spans="1:27" ht="13.2">
+    <row r="615" spans="1:27" ht="12.75">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
       <c r="C615" s="14"/>
@@ -20357,7 +20370,7 @@
       <c r="Z615" s="2"/>
       <c r="AA615" s="2"/>
     </row>
-    <row r="616" spans="1:27" ht="13.2">
+    <row r="616" spans="1:27" ht="12.75">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
       <c r="C616" s="14"/>
@@ -20386,7 +20399,7 @@
       <c r="Z616" s="2"/>
       <c r="AA616" s="2"/>
     </row>
-    <row r="617" spans="1:27" ht="13.2">
+    <row r="617" spans="1:27" ht="12.75">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
       <c r="C617" s="14"/>
@@ -20415,7 +20428,7 @@
       <c r="Z617" s="2"/>
       <c r="AA617" s="2"/>
     </row>
-    <row r="618" spans="1:27" ht="13.2">
+    <row r="618" spans="1:27" ht="12.75">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
       <c r="C618" s="14"/>
@@ -20444,7 +20457,7 @@
       <c r="Z618" s="2"/>
       <c r="AA618" s="2"/>
     </row>
-    <row r="619" spans="1:27" ht="13.2">
+    <row r="619" spans="1:27" ht="12.75">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
       <c r="C619" s="14"/>
@@ -20473,7 +20486,7 @@
       <c r="Z619" s="2"/>
       <c r="AA619" s="2"/>
     </row>
-    <row r="620" spans="1:27" ht="13.2">
+    <row r="620" spans="1:27" ht="12.75">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
       <c r="C620" s="14"/>
@@ -20502,7 +20515,7 @@
       <c r="Z620" s="2"/>
       <c r="AA620" s="2"/>
     </row>
-    <row r="621" spans="1:27" ht="13.2">
+    <row r="621" spans="1:27" ht="12.75">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
       <c r="C621" s="14"/>
@@ -20531,7 +20544,7 @@
       <c r="Z621" s="2"/>
       <c r="AA621" s="2"/>
     </row>
-    <row r="622" spans="1:27" ht="13.2">
+    <row r="622" spans="1:27" ht="12.75">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
       <c r="C622" s="14"/>
@@ -20560,7 +20573,7 @@
       <c r="Z622" s="2"/>
       <c r="AA622" s="2"/>
     </row>
-    <row r="623" spans="1:27" ht="13.2">
+    <row r="623" spans="1:27" ht="12.75">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
       <c r="C623" s="14"/>
@@ -20589,7 +20602,7 @@
       <c r="Z623" s="2"/>
       <c r="AA623" s="2"/>
     </row>
-    <row r="624" spans="1:27" ht="13.2">
+    <row r="624" spans="1:27" ht="12.75">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
       <c r="C624" s="14"/>
@@ -20618,7 +20631,7 @@
       <c r="Z624" s="2"/>
       <c r="AA624" s="2"/>
     </row>
-    <row r="625" spans="1:27" ht="13.2">
+    <row r="625" spans="1:27" ht="12.75">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
       <c r="C625" s="14"/>
@@ -20647,7 +20660,7 @@
       <c r="Z625" s="2"/>
       <c r="AA625" s="2"/>
     </row>
-    <row r="626" spans="1:27" ht="13.2">
+    <row r="626" spans="1:27" ht="12.75">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
       <c r="C626" s="14"/>
@@ -20676,7 +20689,7 @@
       <c r="Z626" s="2"/>
       <c r="AA626" s="2"/>
     </row>
-    <row r="627" spans="1:27" ht="13.2">
+    <row r="627" spans="1:27" ht="12.75">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
       <c r="C627" s="14"/>
@@ -20705,7 +20718,7 @@
       <c r="Z627" s="2"/>
       <c r="AA627" s="2"/>
     </row>
-    <row r="628" spans="1:27" ht="13.2">
+    <row r="628" spans="1:27" ht="12.75">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
       <c r="C628" s="14"/>
@@ -20734,7 +20747,7 @@
       <c r="Z628" s="2"/>
       <c r="AA628" s="2"/>
     </row>
-    <row r="629" spans="1:27" ht="13.2">
+    <row r="629" spans="1:27" ht="12.75">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
       <c r="C629" s="14"/>
@@ -20763,7 +20776,7 @@
       <c r="Z629" s="2"/>
       <c r="AA629" s="2"/>
     </row>
-    <row r="630" spans="1:27" ht="13.2">
+    <row r="630" spans="1:27" ht="12.75">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
       <c r="C630" s="14"/>
@@ -20792,7 +20805,7 @@
       <c r="Z630" s="2"/>
       <c r="AA630" s="2"/>
     </row>
-    <row r="631" spans="1:27" ht="13.2">
+    <row r="631" spans="1:27" ht="12.75">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
       <c r="C631" s="14"/>
@@ -20821,7 +20834,7 @@
       <c r="Z631" s="2"/>
       <c r="AA631" s="2"/>
     </row>
-    <row r="632" spans="1:27" ht="13.2">
+    <row r="632" spans="1:27" ht="12.75">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
       <c r="C632" s="14"/>
@@ -20850,7 +20863,7 @@
       <c r="Z632" s="2"/>
       <c r="AA632" s="2"/>
     </row>
-    <row r="633" spans="1:27" ht="13.2">
+    <row r="633" spans="1:27" ht="12.75">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
       <c r="C633" s="14"/>
@@ -20879,7 +20892,7 @@
       <c r="Z633" s="2"/>
       <c r="AA633" s="2"/>
     </row>
-    <row r="634" spans="1:27" ht="13.2">
+    <row r="634" spans="1:27" ht="12.75">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
       <c r="C634" s="14"/>
@@ -20908,7 +20921,7 @@
       <c r="Z634" s="2"/>
       <c r="AA634" s="2"/>
     </row>
-    <row r="635" spans="1:27" ht="13.2">
+    <row r="635" spans="1:27" ht="12.75">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
       <c r="C635" s="14"/>
@@ -20937,7 +20950,7 @@
       <c r="Z635" s="2"/>
       <c r="AA635" s="2"/>
     </row>
-    <row r="636" spans="1:27" ht="13.2">
+    <row r="636" spans="1:27" ht="12.75">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
       <c r="C636" s="14"/>
@@ -20966,7 +20979,7 @@
       <c r="Z636" s="2"/>
       <c r="AA636" s="2"/>
     </row>
-    <row r="637" spans="1:27" ht="13.2">
+    <row r="637" spans="1:27" ht="12.75">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
       <c r="C637" s="14"/>
@@ -20995,7 +21008,7 @@
       <c r="Z637" s="2"/>
       <c r="AA637" s="2"/>
     </row>
-    <row r="638" spans="1:27" ht="13.2">
+    <row r="638" spans="1:27" ht="12.75">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
       <c r="C638" s="14"/>
@@ -21024,7 +21037,7 @@
       <c r="Z638" s="2"/>
       <c r="AA638" s="2"/>
     </row>
-    <row r="639" spans="1:27" ht="13.2">
+    <row r="639" spans="1:27" ht="12.75">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
       <c r="C639" s="14"/>
@@ -21053,7 +21066,7 @@
       <c r="Z639" s="2"/>
       <c r="AA639" s="2"/>
     </row>
-    <row r="640" spans="1:27" ht="13.2">
+    <row r="640" spans="1:27" ht="12.75">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
       <c r="C640" s="14"/>
@@ -21082,7 +21095,7 @@
       <c r="Z640" s="2"/>
       <c r="AA640" s="2"/>
     </row>
-    <row r="641" spans="1:27" ht="13.2">
+    <row r="641" spans="1:27" ht="12.75">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
       <c r="C641" s="14"/>
@@ -21111,7 +21124,7 @@
       <c r="Z641" s="2"/>
       <c r="AA641" s="2"/>
     </row>
-    <row r="642" spans="1:27" ht="13.2">
+    <row r="642" spans="1:27" ht="12.75">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
       <c r="C642" s="14"/>
@@ -21140,7 +21153,7 @@
       <c r="Z642" s="2"/>
       <c r="AA642" s="2"/>
     </row>
-    <row r="643" spans="1:27" ht="13.2">
+    <row r="643" spans="1:27" ht="12.75">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
       <c r="C643" s="14"/>
@@ -21169,7 +21182,7 @@
       <c r="Z643" s="2"/>
       <c r="AA643" s="2"/>
     </row>
-    <row r="644" spans="1:27" ht="13.2">
+    <row r="644" spans="1:27" ht="12.75">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
       <c r="C644" s="14"/>
@@ -21198,7 +21211,7 @@
       <c r="Z644" s="2"/>
       <c r="AA644" s="2"/>
     </row>
-    <row r="645" spans="1:27" ht="13.2">
+    <row r="645" spans="1:27" ht="12.75">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
       <c r="C645" s="14"/>
@@ -21227,7 +21240,7 @@
       <c r="Z645" s="2"/>
       <c r="AA645" s="2"/>
     </row>
-    <row r="646" spans="1:27" ht="13.2">
+    <row r="646" spans="1:27" ht="12.75">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
       <c r="C646" s="14"/>
@@ -21256,7 +21269,7 @@
       <c r="Z646" s="2"/>
       <c r="AA646" s="2"/>
     </row>
-    <row r="647" spans="1:27" ht="13.2">
+    <row r="647" spans="1:27" ht="12.75">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
       <c r="C647" s="14"/>
@@ -21285,7 +21298,7 @@
       <c r="Z647" s="2"/>
       <c r="AA647" s="2"/>
     </row>
-    <row r="648" spans="1:27" ht="13.2">
+    <row r="648" spans="1:27" ht="12.75">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
       <c r="C648" s="14"/>
@@ -21314,7 +21327,7 @@
       <c r="Z648" s="2"/>
       <c r="AA648" s="2"/>
     </row>
-    <row r="649" spans="1:27" ht="13.2">
+    <row r="649" spans="1:27" ht="12.75">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
       <c r="C649" s="14"/>
@@ -21343,7 +21356,7 @@
       <c r="Z649" s="2"/>
       <c r="AA649" s="2"/>
     </row>
-    <row r="650" spans="1:27" ht="13.2">
+    <row r="650" spans="1:27" ht="12.75">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
       <c r="C650" s="14"/>
@@ -21372,7 +21385,7 @@
       <c r="Z650" s="2"/>
       <c r="AA650" s="2"/>
     </row>
-    <row r="651" spans="1:27" ht="13.2">
+    <row r="651" spans="1:27" ht="12.75">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
       <c r="C651" s="14"/>
@@ -21401,7 +21414,7 @@
       <c r="Z651" s="2"/>
       <c r="AA651" s="2"/>
     </row>
-    <row r="652" spans="1:27" ht="13.2">
+    <row r="652" spans="1:27" ht="12.75">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
       <c r="C652" s="14"/>
@@ -21430,7 +21443,7 @@
       <c r="Z652" s="2"/>
       <c r="AA652" s="2"/>
     </row>
-    <row r="653" spans="1:27" ht="13.2">
+    <row r="653" spans="1:27" ht="12.75">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
       <c r="C653" s="14"/>
@@ -21459,7 +21472,7 @@
       <c r="Z653" s="2"/>
       <c r="AA653" s="2"/>
     </row>
-    <row r="654" spans="1:27" ht="13.2">
+    <row r="654" spans="1:27" ht="12.75">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
       <c r="C654" s="14"/>
@@ -21488,7 +21501,7 @@
       <c r="Z654" s="2"/>
       <c r="AA654" s="2"/>
     </row>
-    <row r="655" spans="1:27" ht="13.2">
+    <row r="655" spans="1:27" ht="12.75">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
       <c r="C655" s="14"/>
@@ -21517,7 +21530,7 @@
       <c r="Z655" s="2"/>
       <c r="AA655" s="2"/>
     </row>
-    <row r="656" spans="1:27" ht="13.2">
+    <row r="656" spans="1:27" ht="12.75">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
       <c r="C656" s="14"/>
@@ -21546,7 +21559,7 @@
       <c r="Z656" s="2"/>
       <c r="AA656" s="2"/>
     </row>
-    <row r="657" spans="1:27" ht="13.2">
+    <row r="657" spans="1:27" ht="12.75">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
       <c r="C657" s="14"/>
@@ -21575,7 +21588,7 @@
       <c r="Z657" s="2"/>
       <c r="AA657" s="2"/>
     </row>
-    <row r="658" spans="1:27" ht="13.2">
+    <row r="658" spans="1:27" ht="12.75">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
       <c r="C658" s="14"/>
@@ -21604,7 +21617,7 @@
       <c r="Z658" s="2"/>
       <c r="AA658" s="2"/>
     </row>
-    <row r="659" spans="1:27" ht="13.2">
+    <row r="659" spans="1:27" ht="12.75">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
       <c r="C659" s="14"/>
@@ -21633,7 +21646,7 @@
       <c r="Z659" s="2"/>
       <c r="AA659" s="2"/>
     </row>
-    <row r="660" spans="1:27" ht="13.2">
+    <row r="660" spans="1:27" ht="12.75">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
       <c r="C660" s="14"/>
@@ -21662,7 +21675,7 @@
       <c r="Z660" s="2"/>
       <c r="AA660" s="2"/>
     </row>
-    <row r="661" spans="1:27" ht="13.2">
+    <row r="661" spans="1:27" ht="12.75">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
       <c r="C661" s="14"/>
@@ -21691,7 +21704,7 @@
       <c r="Z661" s="2"/>
       <c r="AA661" s="2"/>
     </row>
-    <row r="662" spans="1:27" ht="13.2">
+    <row r="662" spans="1:27" ht="12.75">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
       <c r="C662" s="14"/>
@@ -21720,7 +21733,7 @@
       <c r="Z662" s="2"/>
       <c r="AA662" s="2"/>
     </row>
-    <row r="663" spans="1:27" ht="13.2">
+    <row r="663" spans="1:27" ht="12.75">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
       <c r="C663" s="14"/>
@@ -21749,7 +21762,7 @@
       <c r="Z663" s="2"/>
       <c r="AA663" s="2"/>
     </row>
-    <row r="664" spans="1:27" ht="13.2">
+    <row r="664" spans="1:27" ht="12.75">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
       <c r="C664" s="14"/>
@@ -21778,7 +21791,7 @@
       <c r="Z664" s="2"/>
       <c r="AA664" s="2"/>
     </row>
-    <row r="665" spans="1:27" ht="13.2">
+    <row r="665" spans="1:27" ht="12.75">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
       <c r="C665" s="14"/>
@@ -21807,7 +21820,7 @@
       <c r="Z665" s="2"/>
       <c r="AA665" s="2"/>
     </row>
-    <row r="666" spans="1:27" ht="13.2">
+    <row r="666" spans="1:27" ht="12.75">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
       <c r="C666" s="14"/>
@@ -21836,7 +21849,7 @@
       <c r="Z666" s="2"/>
       <c r="AA666" s="2"/>
     </row>
-    <row r="667" spans="1:27" ht="13.2">
+    <row r="667" spans="1:27" ht="12.75">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
       <c r="C667" s="14"/>
@@ -21865,7 +21878,7 @@
       <c r="Z667" s="2"/>
       <c r="AA667" s="2"/>
     </row>
-    <row r="668" spans="1:27" ht="13.2">
+    <row r="668" spans="1:27" ht="12.75">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
       <c r="C668" s="14"/>
@@ -21894,7 +21907,7 @@
       <c r="Z668" s="2"/>
       <c r="AA668" s="2"/>
     </row>
-    <row r="669" spans="1:27" ht="13.2">
+    <row r="669" spans="1:27" ht="12.75">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
       <c r="C669" s="14"/>
@@ -21923,7 +21936,7 @@
       <c r="Z669" s="2"/>
       <c r="AA669" s="2"/>
     </row>
-    <row r="670" spans="1:27" ht="13.2">
+    <row r="670" spans="1:27" ht="12.75">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
       <c r="C670" s="14"/>
@@ -21952,7 +21965,7 @@
       <c r="Z670" s="2"/>
       <c r="AA670" s="2"/>
     </row>
-    <row r="671" spans="1:27" ht="13.2">
+    <row r="671" spans="1:27" ht="12.75">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
       <c r="C671" s="14"/>
@@ -21981,7 +21994,7 @@
       <c r="Z671" s="2"/>
       <c r="AA671" s="2"/>
     </row>
-    <row r="672" spans="1:27" ht="13.2">
+    <row r="672" spans="1:27" ht="12.75">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
       <c r="C672" s="14"/>
@@ -22010,7 +22023,7 @@
       <c r="Z672" s="2"/>
       <c r="AA672" s="2"/>
     </row>
-    <row r="673" spans="1:27" ht="13.2">
+    <row r="673" spans="1:27" ht="12.75">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
       <c r="C673" s="14"/>
@@ -22039,7 +22052,7 @@
       <c r="Z673" s="2"/>
       <c r="AA673" s="2"/>
     </row>
-    <row r="674" spans="1:27" ht="13.2">
+    <row r="674" spans="1:27" ht="12.75">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
       <c r="C674" s="14"/>
@@ -22068,7 +22081,7 @@
       <c r="Z674" s="2"/>
       <c r="AA674" s="2"/>
     </row>
-    <row r="675" spans="1:27" ht="13.2">
+    <row r="675" spans="1:27" ht="12.75">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
       <c r="C675" s="14"/>
@@ -22097,7 +22110,7 @@
       <c r="Z675" s="2"/>
       <c r="AA675" s="2"/>
     </row>
-    <row r="676" spans="1:27" ht="13.2">
+    <row r="676" spans="1:27" ht="12.75">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
       <c r="C676" s="14"/>
@@ -22126,7 +22139,7 @@
       <c r="Z676" s="2"/>
       <c r="AA676" s="2"/>
     </row>
-    <row r="677" spans="1:27" ht="13.2">
+    <row r="677" spans="1:27" ht="12.75">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
       <c r="C677" s="14"/>
@@ -22155,7 +22168,7 @@
       <c r="Z677" s="2"/>
       <c r="AA677" s="2"/>
     </row>
-    <row r="678" spans="1:27" ht="13.2">
+    <row r="678" spans="1:27" ht="12.75">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
       <c r="C678" s="14"/>
@@ -22184,7 +22197,7 @@
       <c r="Z678" s="2"/>
       <c r="AA678" s="2"/>
     </row>
-    <row r="679" spans="1:27" ht="13.2">
+    <row r="679" spans="1:27" ht="12.75">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
       <c r="C679" s="14"/>
@@ -22213,7 +22226,7 @@
       <c r="Z679" s="2"/>
       <c r="AA679" s="2"/>
     </row>
-    <row r="680" spans="1:27" ht="13.2">
+    <row r="680" spans="1:27" ht="12.75">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
       <c r="C680" s="14"/>
@@ -22242,7 +22255,7 @@
       <c r="Z680" s="2"/>
       <c r="AA680" s="2"/>
     </row>
-    <row r="681" spans="1:27" ht="13.2">
+    <row r="681" spans="1:27" ht="12.75">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
       <c r="C681" s="14"/>
@@ -22271,7 +22284,7 @@
       <c r="Z681" s="2"/>
       <c r="AA681" s="2"/>
     </row>
-    <row r="682" spans="1:27" ht="13.2">
+    <row r="682" spans="1:27" ht="12.75">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
       <c r="C682" s="14"/>
@@ -22300,7 +22313,7 @@
       <c r="Z682" s="2"/>
       <c r="AA682" s="2"/>
     </row>
-    <row r="683" spans="1:27" ht="13.2">
+    <row r="683" spans="1:27" ht="12.75">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
       <c r="C683" s="14"/>
@@ -22329,7 +22342,7 @@
       <c r="Z683" s="2"/>
       <c r="AA683" s="2"/>
     </row>
-    <row r="684" spans="1:27" ht="13.2">
+    <row r="684" spans="1:27" ht="12.75">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
       <c r="C684" s="14"/>
@@ -22358,7 +22371,7 @@
       <c r="Z684" s="2"/>
       <c r="AA684" s="2"/>
     </row>
-    <row r="685" spans="1:27" ht="13.2">
+    <row r="685" spans="1:27" ht="12.75">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
       <c r="C685" s="14"/>
@@ -22387,7 +22400,7 @@
       <c r="Z685" s="2"/>
       <c r="AA685" s="2"/>
     </row>
-    <row r="686" spans="1:27" ht="13.2">
+    <row r="686" spans="1:27" ht="12.75">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
       <c r="C686" s="14"/>
@@ -22416,7 +22429,7 @@
       <c r="Z686" s="2"/>
       <c r="AA686" s="2"/>
     </row>
-    <row r="687" spans="1:27" ht="13.2">
+    <row r="687" spans="1:27" ht="12.75">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
       <c r="C687" s="14"/>
@@ -22445,7 +22458,7 @@
       <c r="Z687" s="2"/>
       <c r="AA687" s="2"/>
     </row>
-    <row r="688" spans="1:27" ht="13.2">
+    <row r="688" spans="1:27" ht="12.75">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
       <c r="C688" s="14"/>
@@ -22474,7 +22487,7 @@
       <c r="Z688" s="2"/>
       <c r="AA688" s="2"/>
     </row>
-    <row r="689" spans="1:27" ht="13.2">
+    <row r="689" spans="1:27" ht="12.75">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
       <c r="C689" s="14"/>
@@ -22503,7 +22516,7 @@
       <c r="Z689" s="2"/>
       <c r="AA689" s="2"/>
     </row>
-    <row r="690" spans="1:27" ht="13.2">
+    <row r="690" spans="1:27" ht="12.75">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
       <c r="C690" s="14"/>
@@ -22532,7 +22545,7 @@
       <c r="Z690" s="2"/>
       <c r="AA690" s="2"/>
     </row>
-    <row r="691" spans="1:27" ht="13.2">
+    <row r="691" spans="1:27" ht="12.75">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
       <c r="C691" s="14"/>
@@ -22561,7 +22574,7 @@
       <c r="Z691" s="2"/>
       <c r="AA691" s="2"/>
     </row>
-    <row r="692" spans="1:27" ht="13.2">
+    <row r="692" spans="1:27" ht="12.75">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
       <c r="C692" s="14"/>
@@ -22590,7 +22603,7 @@
       <c r="Z692" s="2"/>
       <c r="AA692" s="2"/>
     </row>
-    <row r="693" spans="1:27" ht="13.2">
+    <row r="693" spans="1:27" ht="12.75">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
       <c r="C693" s="14"/>
@@ -22619,7 +22632,7 @@
       <c r="Z693" s="2"/>
       <c r="AA693" s="2"/>
     </row>
-    <row r="694" spans="1:27" ht="13.2">
+    <row r="694" spans="1:27" ht="12.75">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
       <c r="C694" s="14"/>
@@ -22648,7 +22661,7 @@
       <c r="Z694" s="2"/>
       <c r="AA694" s="2"/>
     </row>
-    <row r="695" spans="1:27" ht="13.2">
+    <row r="695" spans="1:27" ht="12.75">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
       <c r="C695" s="14"/>
@@ -22677,7 +22690,7 @@
       <c r="Z695" s="2"/>
       <c r="AA695" s="2"/>
     </row>
-    <row r="696" spans="1:27" ht="13.2">
+    <row r="696" spans="1:27" ht="12.75">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
       <c r="C696" s="14"/>
@@ -22706,7 +22719,7 @@
       <c r="Z696" s="2"/>
       <c r="AA696" s="2"/>
     </row>
-    <row r="697" spans="1:27" ht="13.2">
+    <row r="697" spans="1:27" ht="12.75">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
       <c r="C697" s="14"/>
@@ -22735,7 +22748,7 @@
       <c r="Z697" s="2"/>
       <c r="AA697" s="2"/>
     </row>
-    <row r="698" spans="1:27" ht="13.2">
+    <row r="698" spans="1:27" ht="12.75">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
       <c r="C698" s="14"/>
@@ -22764,7 +22777,7 @@
       <c r="Z698" s="2"/>
       <c r="AA698" s="2"/>
     </row>
-    <row r="699" spans="1:27" ht="13.2">
+    <row r="699" spans="1:27" ht="12.75">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
       <c r="C699" s="14"/>
@@ -22793,7 +22806,7 @@
       <c r="Z699" s="2"/>
       <c r="AA699" s="2"/>
     </row>
-    <row r="700" spans="1:27" ht="13.2">
+    <row r="700" spans="1:27" ht="12.75">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
       <c r="C700" s="14"/>
@@ -22822,7 +22835,7 @@
       <c r="Z700" s="2"/>
       <c r="AA700" s="2"/>
     </row>
-    <row r="701" spans="1:27" ht="13.2">
+    <row r="701" spans="1:27" ht="12.75">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
       <c r="C701" s="14"/>
@@ -22851,7 +22864,7 @@
       <c r="Z701" s="2"/>
       <c r="AA701" s="2"/>
     </row>
-    <row r="702" spans="1:27" ht="13.2">
+    <row r="702" spans="1:27" ht="12.75">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
       <c r="C702" s="14"/>
@@ -22880,7 +22893,7 @@
       <c r="Z702" s="2"/>
       <c r="AA702" s="2"/>
     </row>
-    <row r="703" spans="1:27" ht="13.2">
+    <row r="703" spans="1:27" ht="12.75">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
       <c r="C703" s="14"/>
@@ -22909,7 +22922,7 @@
       <c r="Z703" s="2"/>
       <c r="AA703" s="2"/>
     </row>
-    <row r="704" spans="1:27" ht="13.2">
+    <row r="704" spans="1:27" ht="12.75">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
       <c r="C704" s="14"/>
@@ -22938,7 +22951,7 @@
       <c r="Z704" s="2"/>
       <c r="AA704" s="2"/>
     </row>
-    <row r="705" spans="1:27" ht="13.2">
+    <row r="705" spans="1:27" ht="12.75">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
       <c r="C705" s="14"/>
@@ -22967,7 +22980,7 @@
       <c r="Z705" s="2"/>
       <c r="AA705" s="2"/>
     </row>
-    <row r="706" spans="1:27" ht="13.2">
+    <row r="706" spans="1:27" ht="12.75">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
       <c r="C706" s="14"/>
@@ -22996,7 +23009,7 @@
       <c r="Z706" s="2"/>
       <c r="AA706" s="2"/>
     </row>
-    <row r="707" spans="1:27" ht="13.2">
+    <row r="707" spans="1:27" ht="12.75">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
       <c r="C707" s="14"/>
@@ -23025,7 +23038,7 @@
       <c r="Z707" s="2"/>
       <c r="AA707" s="2"/>
     </row>
-    <row r="708" spans="1:27" ht="13.2">
+    <row r="708" spans="1:27" ht="12.75">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
       <c r="C708" s="14"/>
@@ -23054,7 +23067,7 @@
       <c r="Z708" s="2"/>
       <c r="AA708" s="2"/>
     </row>
-    <row r="709" spans="1:27" ht="13.2">
+    <row r="709" spans="1:27" ht="12.75">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
       <c r="C709" s="14"/>
@@ -23083,7 +23096,7 @@
       <c r="Z709" s="2"/>
       <c r="AA709" s="2"/>
     </row>
-    <row r="710" spans="1:27" ht="13.2">
+    <row r="710" spans="1:27" ht="12.75">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
       <c r="C710" s="14"/>
@@ -23112,7 +23125,7 @@
       <c r="Z710" s="2"/>
       <c r="AA710" s="2"/>
     </row>
-    <row r="711" spans="1:27" ht="13.2">
+    <row r="711" spans="1:27" ht="12.75">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
       <c r="C711" s="14"/>
@@ -23141,7 +23154,7 @@
       <c r="Z711" s="2"/>
       <c r="AA711" s="2"/>
     </row>
-    <row r="712" spans="1:27" ht="13.2">
+    <row r="712" spans="1:27" ht="12.75">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
       <c r="C712" s="14"/>
@@ -23170,7 +23183,7 @@
       <c r="Z712" s="2"/>
       <c r="AA712" s="2"/>
     </row>
-    <row r="713" spans="1:27" ht="13.2">
+    <row r="713" spans="1:27" ht="12.75">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
       <c r="C713" s="14"/>
@@ -23199,7 +23212,7 @@
       <c r="Z713" s="2"/>
       <c r="AA713" s="2"/>
     </row>
-    <row r="714" spans="1:27" ht="13.2">
+    <row r="714" spans="1:27" ht="12.75">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
       <c r="C714" s="14"/>
@@ -23228,7 +23241,7 @@
       <c r="Z714" s="2"/>
       <c r="AA714" s="2"/>
     </row>
-    <row r="715" spans="1:27" ht="13.2">
+    <row r="715" spans="1:27" ht="12.75">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
       <c r="C715" s="14"/>
@@ -23257,7 +23270,7 @@
       <c r="Z715" s="2"/>
       <c r="AA715" s="2"/>
     </row>
-    <row r="716" spans="1:27" ht="13.2">
+    <row r="716" spans="1:27" ht="12.75">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
       <c r="C716" s="14"/>
@@ -23286,7 +23299,7 @@
       <c r="Z716" s="2"/>
       <c r="AA716" s="2"/>
     </row>
-    <row r="717" spans="1:27" ht="13.2">
+    <row r="717" spans="1:27" ht="12.75">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
       <c r="C717" s="14"/>
@@ -23315,7 +23328,7 @@
       <c r="Z717" s="2"/>
       <c r="AA717" s="2"/>
     </row>
-    <row r="718" spans="1:27" ht="13.2">
+    <row r="718" spans="1:27" ht="12.75">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
       <c r="C718" s="14"/>
@@ -23344,7 +23357,7 @@
       <c r="Z718" s="2"/>
       <c r="AA718" s="2"/>
     </row>
-    <row r="719" spans="1:27" ht="13.2">
+    <row r="719" spans="1:27" ht="12.75">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
       <c r="C719" s="14"/>
@@ -23373,7 +23386,7 @@
       <c r="Z719" s="2"/>
       <c r="AA719" s="2"/>
     </row>
-    <row r="720" spans="1:27" ht="13.2">
+    <row r="720" spans="1:27" ht="12.75">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
       <c r="C720" s="14"/>
@@ -23402,7 +23415,7 @@
       <c r="Z720" s="2"/>
       <c r="AA720" s="2"/>
     </row>
-    <row r="721" spans="1:27" ht="13.2">
+    <row r="721" spans="1:27" ht="12.75">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
       <c r="C721" s="14"/>
@@ -23431,7 +23444,7 @@
       <c r="Z721" s="2"/>
       <c r="AA721" s="2"/>
     </row>
-    <row r="722" spans="1:27" ht="13.2">
+    <row r="722" spans="1:27" ht="12.75">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
       <c r="C722" s="14"/>
@@ -23460,7 +23473,7 @@
       <c r="Z722" s="2"/>
       <c r="AA722" s="2"/>
     </row>
-    <row r="723" spans="1:27" ht="13.2">
+    <row r="723" spans="1:27" ht="12.75">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
       <c r="C723" s="14"/>
@@ -23489,7 +23502,7 @@
       <c r="Z723" s="2"/>
       <c r="AA723" s="2"/>
     </row>
-    <row r="724" spans="1:27" ht="13.2">
+    <row r="724" spans="1:27" ht="12.75">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
       <c r="C724" s="14"/>
@@ -23518,7 +23531,7 @@
       <c r="Z724" s="2"/>
       <c r="AA724" s="2"/>
     </row>
-    <row r="725" spans="1:27" ht="13.2">
+    <row r="725" spans="1:27" ht="12.75">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
       <c r="C725" s="14"/>
@@ -23547,7 +23560,7 @@
       <c r="Z725" s="2"/>
       <c r="AA725" s="2"/>
     </row>
-    <row r="726" spans="1:27" ht="13.2">
+    <row r="726" spans="1:27" ht="12.75">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
       <c r="C726" s="14"/>
@@ -23576,7 +23589,7 @@
       <c r="Z726" s="2"/>
       <c r="AA726" s="2"/>
     </row>
-    <row r="727" spans="1:27" ht="13.2">
+    <row r="727" spans="1:27" ht="12.75">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
       <c r="C727" s="14"/>
@@ -23605,7 +23618,7 @@
       <c r="Z727" s="2"/>
       <c r="AA727" s="2"/>
     </row>
-    <row r="728" spans="1:27" ht="13.2">
+    <row r="728" spans="1:27" ht="12.75">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
       <c r="C728" s="14"/>
@@ -23634,7 +23647,7 @@
       <c r="Z728" s="2"/>
       <c r="AA728" s="2"/>
     </row>
-    <row r="729" spans="1:27" ht="13.2">
+    <row r="729" spans="1:27" ht="12.75">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
       <c r="C729" s="14"/>
@@ -23663,7 +23676,7 @@
       <c r="Z729" s="2"/>
       <c r="AA729" s="2"/>
     </row>
-    <row r="730" spans="1:27" ht="13.2">
+    <row r="730" spans="1:27" ht="12.75">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
       <c r="C730" s="14"/>
@@ -23692,7 +23705,7 @@
       <c r="Z730" s="2"/>
       <c r="AA730" s="2"/>
     </row>
-    <row r="731" spans="1:27" ht="13.2">
+    <row r="731" spans="1:27" ht="12.75">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
       <c r="C731" s="14"/>
@@ -23721,7 +23734,7 @@
       <c r="Z731" s="2"/>
       <c r="AA731" s="2"/>
     </row>
-    <row r="732" spans="1:27" ht="13.2">
+    <row r="732" spans="1:27" ht="12.75">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
       <c r="C732" s="14"/>
@@ -23750,7 +23763,7 @@
       <c r="Z732" s="2"/>
       <c r="AA732" s="2"/>
     </row>
-    <row r="733" spans="1:27" ht="13.2">
+    <row r="733" spans="1:27" ht="12.75">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
       <c r="C733" s="14"/>
@@ -23779,7 +23792,7 @@
       <c r="Z733" s="2"/>
       <c r="AA733" s="2"/>
     </row>
-    <row r="734" spans="1:27" ht="13.2">
+    <row r="734" spans="1:27" ht="12.75">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
       <c r="C734" s="14"/>
@@ -23808,7 +23821,7 @@
       <c r="Z734" s="2"/>
       <c r="AA734" s="2"/>
     </row>
-    <row r="735" spans="1:27" ht="13.2">
+    <row r="735" spans="1:27" ht="12.75">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
       <c r="C735" s="14"/>
@@ -23837,7 +23850,7 @@
       <c r="Z735" s="2"/>
       <c r="AA735" s="2"/>
     </row>
-    <row r="736" spans="1:27" ht="13.2">
+    <row r="736" spans="1:27" ht="12.75">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
       <c r="C736" s="14"/>
@@ -23866,7 +23879,7 @@
       <c r="Z736" s="2"/>
       <c r="AA736" s="2"/>
     </row>
-    <row r="737" spans="1:27" ht="13.2">
+    <row r="737" spans="1:27" ht="12.75">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
       <c r="C737" s="14"/>
@@ -23895,7 +23908,7 @@
       <c r="Z737" s="2"/>
       <c r="AA737" s="2"/>
     </row>
-    <row r="738" spans="1:27" ht="13.2">
+    <row r="738" spans="1:27" ht="12.75">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
       <c r="C738" s="14"/>
@@ -23924,7 +23937,7 @@
       <c r="Z738" s="2"/>
       <c r="AA738" s="2"/>
     </row>
-    <row r="739" spans="1:27" ht="13.2">
+    <row r="739" spans="1:27" ht="12.75">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
       <c r="C739" s="14"/>
@@ -23953,7 +23966,7 @@
       <c r="Z739" s="2"/>
       <c r="AA739" s="2"/>
     </row>
-    <row r="740" spans="1:27" ht="13.2">
+    <row r="740" spans="1:27" ht="12.75">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
       <c r="C740" s="14"/>
@@ -23982,7 +23995,7 @@
       <c r="Z740" s="2"/>
       <c r="AA740" s="2"/>
     </row>
-    <row r="741" spans="1:27" ht="13.2">
+    <row r="741" spans="1:27" ht="12.75">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
       <c r="C741" s="14"/>
@@ -24011,7 +24024,7 @@
       <c r="Z741" s="2"/>
       <c r="AA741" s="2"/>
     </row>
-    <row r="742" spans="1:27" ht="13.2">
+    <row r="742" spans="1:27" ht="12.75">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
       <c r="C742" s="14"/>
@@ -24040,7 +24053,7 @@
       <c r="Z742" s="2"/>
       <c r="AA742" s="2"/>
     </row>
-    <row r="743" spans="1:27" ht="13.2">
+    <row r="743" spans="1:27" ht="12.75">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
       <c r="C743" s="14"/>
@@ -24069,7 +24082,7 @@
       <c r="Z743" s="2"/>
       <c r="AA743" s="2"/>
     </row>
-    <row r="744" spans="1:27" ht="13.2">
+    <row r="744" spans="1:27" ht="12.75">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
       <c r="C744" s="14"/>
@@ -24098,7 +24111,7 @@
       <c r="Z744" s="2"/>
       <c r="AA744" s="2"/>
     </row>
-    <row r="745" spans="1:27" ht="13.2">
+    <row r="745" spans="1:27" ht="12.75">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
       <c r="C745" s="14"/>
@@ -24127,7 +24140,7 @@
       <c r="Z745" s="2"/>
       <c r="AA745" s="2"/>
     </row>
-    <row r="746" spans="1:27" ht="13.2">
+    <row r="746" spans="1:27" ht="12.75">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
       <c r="C746" s="14"/>
@@ -24156,7 +24169,7 @@
       <c r="Z746" s="2"/>
       <c r="AA746" s="2"/>
     </row>
-    <row r="747" spans="1:27" ht="13.2">
+    <row r="747" spans="1:27" ht="12.75">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
       <c r="C747" s="14"/>
@@ -24185,7 +24198,7 @@
       <c r="Z747" s="2"/>
       <c r="AA747" s="2"/>
     </row>
-    <row r="748" spans="1:27" ht="13.2">
+    <row r="748" spans="1:27" ht="12.75">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
       <c r="C748" s="14"/>
@@ -24214,7 +24227,7 @@
       <c r="Z748" s="2"/>
       <c r="AA748" s="2"/>
     </row>
-    <row r="749" spans="1:27" ht="13.2">
+    <row r="749" spans="1:27" ht="12.75">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
       <c r="C749" s="14"/>
@@ -24243,7 +24256,7 @@
       <c r="Z749" s="2"/>
       <c r="AA749" s="2"/>
     </row>
-    <row r="750" spans="1:27" ht="13.2">
+    <row r="750" spans="1:27" ht="12.75">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
       <c r="C750" s="14"/>
@@ -24272,7 +24285,7 @@
       <c r="Z750" s="2"/>
       <c r="AA750" s="2"/>
     </row>
-    <row r="751" spans="1:27" ht="13.2">
+    <row r="751" spans="1:27" ht="12.75">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
       <c r="C751" s="14"/>
@@ -24301,7 +24314,7 @@
       <c r="Z751" s="2"/>
       <c r="AA751" s="2"/>
     </row>
-    <row r="752" spans="1:27" ht="13.2">
+    <row r="752" spans="1:27" ht="12.75">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
       <c r="C752" s="14"/>
@@ -24330,7 +24343,7 @@
       <c r="Z752" s="2"/>
       <c r="AA752" s="2"/>
     </row>
-    <row r="753" spans="1:27" ht="13.2">
+    <row r="753" spans="1:27" ht="12.75">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
       <c r="C753" s="14"/>
@@ -24359,7 +24372,7 @@
       <c r="Z753" s="2"/>
       <c r="AA753" s="2"/>
     </row>
-    <row r="754" spans="1:27" ht="13.2">
+    <row r="754" spans="1:27" ht="12.75">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
       <c r="C754" s="14"/>
@@ -24388,7 +24401,7 @@
       <c r="Z754" s="2"/>
       <c r="AA754" s="2"/>
     </row>
-    <row r="755" spans="1:27" ht="13.2">
+    <row r="755" spans="1:27" ht="12.75">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
       <c r="C755" s="14"/>
@@ -24417,7 +24430,7 @@
       <c r="Z755" s="2"/>
       <c r="AA755" s="2"/>
     </row>
-    <row r="756" spans="1:27" ht="13.2">
+    <row r="756" spans="1:27" ht="12.75">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
       <c r="C756" s="14"/>
@@ -24446,7 +24459,7 @@
       <c r="Z756" s="2"/>
       <c r="AA756" s="2"/>
     </row>
-    <row r="757" spans="1:27" ht="13.2">
+    <row r="757" spans="1:27" ht="12.75">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
       <c r="C757" s="14"/>
@@ -24475,7 +24488,7 @@
       <c r="Z757" s="2"/>
       <c r="AA757" s="2"/>
     </row>
-    <row r="758" spans="1:27" ht="13.2">
+    <row r="758" spans="1:27" ht="12.75">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
       <c r="C758" s="14"/>
@@ -24504,7 +24517,7 @@
       <c r="Z758" s="2"/>
       <c r="AA758" s="2"/>
     </row>
-    <row r="759" spans="1:27" ht="13.2">
+    <row r="759" spans="1:27" ht="12.75">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
       <c r="C759" s="14"/>
@@ -24533,7 +24546,7 @@
       <c r="Z759" s="2"/>
       <c r="AA759" s="2"/>
     </row>
-    <row r="760" spans="1:27" ht="13.2">
+    <row r="760" spans="1:27" ht="12.75">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
       <c r="C760" s="14"/>
@@ -24562,7 +24575,7 @@
       <c r="Z760" s="2"/>
       <c r="AA760" s="2"/>
     </row>
-    <row r="761" spans="1:27" ht="13.2">
+    <row r="761" spans="1:27" ht="12.75">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
       <c r="C761" s="14"/>
@@ -24591,7 +24604,7 @@
       <c r="Z761" s="2"/>
       <c r="AA761" s="2"/>
     </row>
-    <row r="762" spans="1:27" ht="13.2">
+    <row r="762" spans="1:27" ht="12.75">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
       <c r="C762" s="14"/>
@@ -24620,7 +24633,7 @@
       <c r="Z762" s="2"/>
       <c r="AA762" s="2"/>
     </row>
-    <row r="763" spans="1:27" ht="13.2">
+    <row r="763" spans="1:27" ht="12.75">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
       <c r="C763" s="14"/>
@@ -24649,7 +24662,7 @@
       <c r="Z763" s="2"/>
       <c r="AA763" s="2"/>
     </row>
-    <row r="764" spans="1:27" ht="13.2">
+    <row r="764" spans="1:27" ht="12.75">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
       <c r="C764" s="14"/>
@@ -24678,7 +24691,7 @@
       <c r="Z764" s="2"/>
       <c r="AA764" s="2"/>
     </row>
-    <row r="765" spans="1:27" ht="13.2">
+    <row r="765" spans="1:27" ht="12.75">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
       <c r="C765" s="14"/>
@@ -24707,7 +24720,7 @@
       <c r="Z765" s="2"/>
       <c r="AA765" s="2"/>
     </row>
-    <row r="766" spans="1:27" ht="13.2">
+    <row r="766" spans="1:27" ht="12.75">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
       <c r="C766" s="14"/>
@@ -24736,7 +24749,7 @@
       <c r="Z766" s="2"/>
       <c r="AA766" s="2"/>
     </row>
-    <row r="767" spans="1:27" ht="13.2">
+    <row r="767" spans="1:27" ht="12.75">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
       <c r="C767" s="14"/>
@@ -24765,7 +24778,7 @@
       <c r="Z767" s="2"/>
       <c r="AA767" s="2"/>
     </row>
-    <row r="768" spans="1:27" ht="13.2">
+    <row r="768" spans="1:27" ht="12.75">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
       <c r="C768" s="14"/>
@@ -24794,7 +24807,7 @@
       <c r="Z768" s="2"/>
       <c r="AA768" s="2"/>
     </row>
-    <row r="769" spans="1:27" ht="13.2">
+    <row r="769" spans="1:27" ht="12.75">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
       <c r="C769" s="14"/>
@@ -24823,7 +24836,7 @@
       <c r="Z769" s="2"/>
       <c r="AA769" s="2"/>
     </row>
-    <row r="770" spans="1:27" ht="13.2">
+    <row r="770" spans="1:27" ht="12.75">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
       <c r="C770" s="14"/>
@@ -24852,7 +24865,7 @@
       <c r="Z770" s="2"/>
       <c r="AA770" s="2"/>
     </row>
-    <row r="771" spans="1:27" ht="13.2">
+    <row r="771" spans="1:27" ht="12.75">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
       <c r="C771" s="14"/>
@@ -24881,7 +24894,7 @@
       <c r="Z771" s="2"/>
       <c r="AA771" s="2"/>
     </row>
-    <row r="772" spans="1:27" ht="13.2">
+    <row r="772" spans="1:27" ht="12.75">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
       <c r="C772" s="14"/>
@@ -24910,7 +24923,7 @@
       <c r="Z772" s="2"/>
       <c r="AA772" s="2"/>
     </row>
-    <row r="773" spans="1:27" ht="13.2">
+    <row r="773" spans="1:27" ht="12.75">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
       <c r="C773" s="14"/>
@@ -24939,7 +24952,7 @@
       <c r="Z773" s="2"/>
       <c r="AA773" s="2"/>
     </row>
-    <row r="774" spans="1:27" ht="13.2">
+    <row r="774" spans="1:27" ht="12.75">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
       <c r="C774" s="14"/>
@@ -24968,7 +24981,7 @@
       <c r="Z774" s="2"/>
       <c r="AA774" s="2"/>
     </row>
-    <row r="775" spans="1:27" ht="13.2">
+    <row r="775" spans="1:27" ht="12.75">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
       <c r="C775" s="14"/>
@@ -24997,7 +25010,7 @@
       <c r="Z775" s="2"/>
       <c r="AA775" s="2"/>
     </row>
-    <row r="776" spans="1:27" ht="13.2">
+    <row r="776" spans="1:27" ht="12.75">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
       <c r="C776" s="14"/>
@@ -25026,7 +25039,7 @@
       <c r="Z776" s="2"/>
       <c r="AA776" s="2"/>
     </row>
-    <row r="777" spans="1:27" ht="13.2">
+    <row r="777" spans="1:27" ht="12.75">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
       <c r="C777" s="14"/>
@@ -25055,7 +25068,7 @@
       <c r="Z777" s="2"/>
       <c r="AA777" s="2"/>
     </row>
-    <row r="778" spans="1:27" ht="13.2">
+    <row r="778" spans="1:27" ht="12.75">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
       <c r="C778" s="14"/>
@@ -25084,7 +25097,7 @@
       <c r="Z778" s="2"/>
       <c r="AA778" s="2"/>
     </row>
-    <row r="779" spans="1:27" ht="13.2">
+    <row r="779" spans="1:27" ht="12.75">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
       <c r="C779" s="14"/>
@@ -25113,7 +25126,7 @@
       <c r="Z779" s="2"/>
       <c r="AA779" s="2"/>
     </row>
-    <row r="780" spans="1:27" ht="13.2">
+    <row r="780" spans="1:27" ht="12.75">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
       <c r="C780" s="14"/>
@@ -25142,7 +25155,7 @@
       <c r="Z780" s="2"/>
       <c r="AA780" s="2"/>
     </row>
-    <row r="781" spans="1:27" ht="13.2">
+    <row r="781" spans="1:27" ht="12.75">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
       <c r="C781" s="14"/>
@@ -25171,7 +25184,7 @@
       <c r="Z781" s="2"/>
       <c r="AA781" s="2"/>
     </row>
-    <row r="782" spans="1:27" ht="13.2">
+    <row r="782" spans="1:27" ht="12.75">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
       <c r="C782" s="14"/>
@@ -25200,7 +25213,7 @@
       <c r="Z782" s="2"/>
       <c r="AA782" s="2"/>
     </row>
-    <row r="783" spans="1:27" ht="13.2">
+    <row r="783" spans="1:27" ht="12.75">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
       <c r="C783" s="14"/>
@@ -25229,7 +25242,7 @@
       <c r="Z783" s="2"/>
       <c r="AA783" s="2"/>
     </row>
-    <row r="784" spans="1:27" ht="13.2">
+    <row r="784" spans="1:27" ht="12.75">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
       <c r="C784" s="14"/>
@@ -25258,7 +25271,7 @@
       <c r="Z784" s="2"/>
       <c r="AA784" s="2"/>
     </row>
-    <row r="785" spans="1:27" ht="13.2">
+    <row r="785" spans="1:27" ht="12.75">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
       <c r="C785" s="14"/>
@@ -25287,7 +25300,7 @@
       <c r="Z785" s="2"/>
       <c r="AA785" s="2"/>
     </row>
-    <row r="786" spans="1:27" ht="13.2">
+    <row r="786" spans="1:27" ht="12.75">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
       <c r="C786" s="14"/>
@@ -25316,7 +25329,7 @@
       <c r="Z786" s="2"/>
       <c r="AA786" s="2"/>
     </row>
-    <row r="787" spans="1:27" ht="13.2">
+    <row r="787" spans="1:27" ht="12.75">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
       <c r="C787" s="14"/>
@@ -25345,7 +25358,7 @@
       <c r="Z787" s="2"/>
       <c r="AA787" s="2"/>
     </row>
-    <row r="788" spans="1:27" ht="13.2">
+    <row r="788" spans="1:27" ht="12.75">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
       <c r="C788" s="14"/>
@@ -25374,7 +25387,7 @@
       <c r="Z788" s="2"/>
       <c r="AA788" s="2"/>
     </row>
-    <row r="789" spans="1:27" ht="13.2">
+    <row r="789" spans="1:27" ht="12.75">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
       <c r="C789" s="14"/>
@@ -25403,7 +25416,7 @@
       <c r="Z789" s="2"/>
       <c r="AA789" s="2"/>
     </row>
-    <row r="790" spans="1:27" ht="13.2">
+    <row r="790" spans="1:27" ht="12.75">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
       <c r="C790" s="14"/>
@@ -25432,7 +25445,7 @@
       <c r="Z790" s="2"/>
       <c r="AA790" s="2"/>
     </row>
-    <row r="791" spans="1:27" ht="13.2">
+    <row r="791" spans="1:27" ht="12.75">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
       <c r="C791" s="14"/>
@@ -25461,7 +25474,7 @@
       <c r="Z791" s="2"/>
       <c r="AA791" s="2"/>
     </row>
-    <row r="792" spans="1:27" ht="13.2">
+    <row r="792" spans="1:27" ht="12.75">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
       <c r="C792" s="14"/>
@@ -25490,7 +25503,7 @@
       <c r="Z792" s="2"/>
       <c r="AA792" s="2"/>
     </row>
-    <row r="793" spans="1:27" ht="13.2">
+    <row r="793" spans="1:27" ht="12.75">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
       <c r="C793" s="14"/>
@@ -25519,7 +25532,7 @@
       <c r="Z793" s="2"/>
       <c r="AA793" s="2"/>
     </row>
-    <row r="794" spans="1:27" ht="13.2">
+    <row r="794" spans="1:27" ht="12.75">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
       <c r="C794" s="14"/>
@@ -25548,7 +25561,7 @@
       <c r="Z794" s="2"/>
       <c r="AA794" s="2"/>
     </row>
-    <row r="795" spans="1:27" ht="13.2">
+    <row r="795" spans="1:27" ht="12.75">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
       <c r="C795" s="14"/>
@@ -25577,7 +25590,7 @@
       <c r="Z795" s="2"/>
       <c r="AA795" s="2"/>
     </row>
-    <row r="796" spans="1:27" ht="13.2">
+    <row r="796" spans="1:27" ht="12.75">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
       <c r="C796" s="14"/>
@@ -25606,7 +25619,7 @@
       <c r="Z796" s="2"/>
       <c r="AA796" s="2"/>
     </row>
-    <row r="797" spans="1:27" ht="13.2">
+    <row r="797" spans="1:27" ht="12.75">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
       <c r="C797" s="14"/>
@@ -25635,7 +25648,7 @@
       <c r="Z797" s="2"/>
       <c r="AA797" s="2"/>
     </row>
-    <row r="798" spans="1:27" ht="13.2">
+    <row r="798" spans="1:27" ht="12.75">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
       <c r="C798" s="14"/>
@@ -25664,7 +25677,7 @@
       <c r="Z798" s="2"/>
       <c r="AA798" s="2"/>
     </row>
-    <row r="799" spans="1:27" ht="13.2">
+    <row r="799" spans="1:27" ht="12.75">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
       <c r="C799" s="14"/>
@@ -25693,7 +25706,7 @@
       <c r="Z799" s="2"/>
       <c r="AA799" s="2"/>
     </row>
-    <row r="800" spans="1:27" ht="13.2">
+    <row r="800" spans="1:27" ht="12.75">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
       <c r="C800" s="14"/>
@@ -25722,7 +25735,7 @@
       <c r="Z800" s="2"/>
       <c r="AA800" s="2"/>
     </row>
-    <row r="801" spans="1:27" ht="13.2">
+    <row r="801" spans="1:27" ht="12.75">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
       <c r="C801" s="14"/>
@@ -25751,7 +25764,7 @@
       <c r="Z801" s="2"/>
       <c r="AA801" s="2"/>
     </row>
-    <row r="802" spans="1:27" ht="13.2">
+    <row r="802" spans="1:27" ht="12.75">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
       <c r="C802" s="14"/>
@@ -25780,7 +25793,7 @@
       <c r="Z802" s="2"/>
       <c r="AA802" s="2"/>
     </row>
-    <row r="803" spans="1:27" ht="13.2">
+    <row r="803" spans="1:27" ht="12.75">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
       <c r="C803" s="14"/>
@@ -25809,7 +25822,7 @@
       <c r="Z803" s="2"/>
       <c r="AA803" s="2"/>
     </row>
-    <row r="804" spans="1:27" ht="13.2">
+    <row r="804" spans="1:27" ht="12.75">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
       <c r="C804" s="14"/>
@@ -25838,7 +25851,7 @@
       <c r="Z804" s="2"/>
       <c r="AA804" s="2"/>
     </row>
-    <row r="805" spans="1:27" ht="13.2">
+    <row r="805" spans="1:27" ht="12.75">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
       <c r="C805" s="14"/>
@@ -25867,7 +25880,7 @@
       <c r="Z805" s="2"/>
       <c r="AA805" s="2"/>
     </row>
-    <row r="806" spans="1:27" ht="13.2">
+    <row r="806" spans="1:27" ht="12.75">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
       <c r="C806" s="14"/>
@@ -25896,7 +25909,7 @@
       <c r="Z806" s="2"/>
       <c r="AA806" s="2"/>
     </row>
-    <row r="807" spans="1:27" ht="13.2">
+    <row r="807" spans="1:27" ht="12.75">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
       <c r="C807" s="14"/>
@@ -25925,7 +25938,7 @@
       <c r="Z807" s="2"/>
       <c r="AA807" s="2"/>
     </row>
-    <row r="808" spans="1:27" ht="13.2">
+    <row r="808" spans="1:27" ht="12.75">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
       <c r="C808" s="14"/>
@@ -25954,7 +25967,7 @@
       <c r="Z808" s="2"/>
       <c r="AA808" s="2"/>
     </row>
-    <row r="809" spans="1:27" ht="13.2">
+    <row r="809" spans="1:27" ht="12.75">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
       <c r="C809" s="14"/>
@@ -25983,7 +25996,7 @@
       <c r="Z809" s="2"/>
       <c r="AA809" s="2"/>
     </row>
-    <row r="810" spans="1:27" ht="13.2">
+    <row r="810" spans="1:27" ht="12.75">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
       <c r="C810" s="14"/>
@@ -26012,7 +26025,7 @@
       <c r="Z810" s="2"/>
       <c r="AA810" s="2"/>
     </row>
-    <row r="811" spans="1:27" ht="13.2">
+    <row r="811" spans="1:27" ht="12.75">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
       <c r="C811" s="14"/>
@@ -26041,7 +26054,7 @@
       <c r="Z811" s="2"/>
       <c r="AA811" s="2"/>
     </row>
-    <row r="812" spans="1:27" ht="13.2">
+    <row r="812" spans="1:27" ht="12.75">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
       <c r="C812" s="14"/>
@@ -26070,7 +26083,7 @@
       <c r="Z812" s="2"/>
       <c r="AA812" s="2"/>
     </row>
-    <row r="813" spans="1:27" ht="13.2">
+    <row r="813" spans="1:27" ht="12.75">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
       <c r="C813" s="14"/>
@@ -26099,7 +26112,7 @@
       <c r="Z813" s="2"/>
       <c r="AA813" s="2"/>
     </row>
-    <row r="814" spans="1:27" ht="13.2">
+    <row r="814" spans="1:27" ht="12.75">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
       <c r="C814" s="14"/>
@@ -26128,7 +26141,7 @@
       <c r="Z814" s="2"/>
       <c r="AA814" s="2"/>
     </row>
-    <row r="815" spans="1:27" ht="13.2">
+    <row r="815" spans="1:27" ht="12.75">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
       <c r="C815" s="14"/>
@@ -26157,7 +26170,7 @@
       <c r="Z815" s="2"/>
       <c r="AA815" s="2"/>
     </row>
-    <row r="816" spans="1:27" ht="13.2">
+    <row r="816" spans="1:27" ht="12.75">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
       <c r="C816" s="14"/>
@@ -26186,7 +26199,7 @@
       <c r="Z816" s="2"/>
       <c r="AA816" s="2"/>
     </row>
-    <row r="817" spans="1:27" ht="13.2">
+    <row r="817" spans="1:27" ht="12.75">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
       <c r="C817" s="14"/>
@@ -26215,7 +26228,7 @@
       <c r="Z817" s="2"/>
       <c r="AA817" s="2"/>
     </row>
-    <row r="818" spans="1:27" ht="13.2">
+    <row r="818" spans="1:27" ht="12.75">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
       <c r="C818" s="14"/>
@@ -26244,7 +26257,7 @@
       <c r="Z818" s="2"/>
       <c r="AA818" s="2"/>
     </row>
-    <row r="819" spans="1:27" ht="13.2">
+    <row r="819" spans="1:27" ht="12.75">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
       <c r="C819" s="14"/>
@@ -26273,7 +26286,7 @@
       <c r="Z819" s="2"/>
       <c r="AA819" s="2"/>
     </row>
-    <row r="820" spans="1:27" ht="13.2">
+    <row r="820" spans="1:27" ht="12.75">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
       <c r="C820" s="14"/>
@@ -26302,7 +26315,7 @@
       <c r="Z820" s="2"/>
       <c r="AA820" s="2"/>
     </row>
-    <row r="821" spans="1:27" ht="13.2">
+    <row r="821" spans="1:27" ht="12.75">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
       <c r="C821" s="14"/>
@@ -26331,7 +26344,7 @@
       <c r="Z821" s="2"/>
       <c r="AA821" s="2"/>
     </row>
-    <row r="822" spans="1:27" ht="13.2">
+    <row r="822" spans="1:27" ht="12.75">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
       <c r="C822" s="14"/>
@@ -26360,7 +26373,7 @@
       <c r="Z822" s="2"/>
       <c r="AA822" s="2"/>
     </row>
-    <row r="823" spans="1:27" ht="13.2">
+    <row r="823" spans="1:27" ht="12.75">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
       <c r="C823" s="14"/>
@@ -26389,7 +26402,7 @@
       <c r="Z823" s="2"/>
       <c r="AA823" s="2"/>
     </row>
-    <row r="824" spans="1:27" ht="13.2">
+    <row r="824" spans="1:27" ht="12.75">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
       <c r="C824" s="14"/>
@@ -26418,7 +26431,7 @@
       <c r="Z824" s="2"/>
       <c r="AA824" s="2"/>
     </row>
-    <row r="825" spans="1:27" ht="13.2">
+    <row r="825" spans="1:27" ht="12.75">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
       <c r="C825" s="14"/>
@@ -26447,7 +26460,7 @@
       <c r="Z825" s="2"/>
       <c r="AA825" s="2"/>
     </row>
-    <row r="826" spans="1:27" ht="13.2">
+    <row r="826" spans="1:27" ht="12.75">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
       <c r="C826" s="14"/>
@@ -26476,7 +26489,7 @@
       <c r="Z826" s="2"/>
       <c r="AA826" s="2"/>
     </row>
-    <row r="827" spans="1:27" ht="13.2">
+    <row r="827" spans="1:27" ht="12.75">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
       <c r="C827" s="14"/>
@@ -26505,7 +26518,7 @@
       <c r="Z827" s="2"/>
       <c r="AA827" s="2"/>
     </row>
-    <row r="828" spans="1:27" ht="13.2">
+    <row r="828" spans="1:27" ht="12.75">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
       <c r="C828" s="14"/>
@@ -26534,7 +26547,7 @@
       <c r="Z828" s="2"/>
       <c r="AA828" s="2"/>
     </row>
-    <row r="829" spans="1:27" ht="13.2">
+    <row r="829" spans="1:27" ht="12.75">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
       <c r="C829" s="14"/>
@@ -26563,7 +26576,7 @@
       <c r="Z829" s="2"/>
       <c r="AA829" s="2"/>
     </row>
-    <row r="830" spans="1:27" ht="13.2">
+    <row r="830" spans="1:27" ht="12.75">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
       <c r="C830" s="14"/>
@@ -26592,7 +26605,7 @@
       <c r="Z830" s="2"/>
       <c r="AA830" s="2"/>
     </row>
-    <row r="831" spans="1:27" ht="13.2">
+    <row r="831" spans="1:27" ht="12.75">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
       <c r="C831" s="14"/>
@@ -26621,7 +26634,7 @@
       <c r="Z831" s="2"/>
       <c r="AA831" s="2"/>
     </row>
-    <row r="832" spans="1:27" ht="13.2">
+    <row r="832" spans="1:27" ht="12.75">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
       <c r="C832" s="14"/>
@@ -26650,7 +26663,7 @@
       <c r="Z832" s="2"/>
       <c r="AA832" s="2"/>
     </row>
-    <row r="833" spans="1:27" ht="13.2">
+    <row r="833" spans="1:27" ht="12.75">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
       <c r="C833" s="14"/>
@@ -26679,7 +26692,7 @@
       <c r="Z833" s="2"/>
       <c r="AA833" s="2"/>
     </row>
-    <row r="834" spans="1:27" ht="13.2">
+    <row r="834" spans="1:27" ht="12.75">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
       <c r="C834" s="14"/>
@@ -26708,7 +26721,7 @@
       <c r="Z834" s="2"/>
       <c r="AA834" s="2"/>
     </row>
-    <row r="835" spans="1:27" ht="13.2">
+    <row r="835" spans="1:27" ht="12.75">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
       <c r="C835" s="14"/>
@@ -26737,7 +26750,7 @@
       <c r="Z835" s="2"/>
       <c r="AA835" s="2"/>
     </row>
-    <row r="836" spans="1:27" ht="13.2">
+    <row r="836" spans="1:27" ht="12.75">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
       <c r="C836" s="14"/>
@@ -26766,7 +26779,7 @@
       <c r="Z836" s="2"/>
       <c r="AA836" s="2"/>
     </row>
-    <row r="837" spans="1:27" ht="13.2">
+    <row r="837" spans="1:27" ht="12.75">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
       <c r="C837" s="14"/>
@@ -26795,7 +26808,7 @@
       <c r="Z837" s="2"/>
       <c r="AA837" s="2"/>
     </row>
-    <row r="838" spans="1:27" ht="13.2">
+    <row r="838" spans="1:27" ht="12.75">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
       <c r="C838" s="14"/>
@@ -26824,7 +26837,7 @@
       <c r="Z838" s="2"/>
       <c r="AA838" s="2"/>
     </row>
-    <row r="839" spans="1:27" ht="13.2">
+    <row r="839" spans="1:27" ht="12.75">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
       <c r="C839" s="14"/>
@@ -26853,7 +26866,7 @@
       <c r="Z839" s="2"/>
       <c r="AA839" s="2"/>
     </row>
-    <row r="840" spans="1:27" ht="13.2">
+    <row r="840" spans="1:27" ht="12.75">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
       <c r="C840" s="14"/>
@@ -26882,7 +26895,7 @@
       <c r="Z840" s="2"/>
       <c r="AA840" s="2"/>
     </row>
-    <row r="841" spans="1:27" ht="13.2">
+    <row r="841" spans="1:27" ht="12.75">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
       <c r="C841" s="14"/>
@@ -26911,7 +26924,7 @@
       <c r="Z841" s="2"/>
       <c r="AA841" s="2"/>
     </row>
-    <row r="842" spans="1:27" ht="13.2">
+    <row r="842" spans="1:27" ht="12.75">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
       <c r="C842" s="14"/>
@@ -26940,7 +26953,7 @@
       <c r="Z842" s="2"/>
       <c r="AA842" s="2"/>
     </row>
-    <row r="843" spans="1:27" ht="13.2">
+    <row r="843" spans="1:27" ht="12.75">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
       <c r="C843" s="14"/>
@@ -26969,7 +26982,7 @@
       <c r="Z843" s="2"/>
       <c r="AA843" s="2"/>
     </row>
-    <row r="844" spans="1:27" ht="13.2">
+    <row r="844" spans="1:27" ht="12.75">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
       <c r="C844" s="14"/>
@@ -26998,7 +27011,7 @@
       <c r="Z844" s="2"/>
       <c r="AA844" s="2"/>
     </row>
-    <row r="845" spans="1:27" ht="13.2">
+    <row r="845" spans="1:27" ht="12.75">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
       <c r="C845" s="14"/>
@@ -27027,7 +27040,7 @@
       <c r="Z845" s="2"/>
       <c r="AA845" s="2"/>
     </row>
-    <row r="846" spans="1:27" ht="13.2">
+    <row r="846" spans="1:27" ht="12.75">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
       <c r="C846" s="14"/>
@@ -27056,7 +27069,7 @@
       <c r="Z846" s="2"/>
       <c r="AA846" s="2"/>
     </row>
-    <row r="847" spans="1:27" ht="13.2">
+    <row r="847" spans="1:27" ht="12.75">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
       <c r="C847" s="14"/>
@@ -27085,7 +27098,7 @@
       <c r="Z847" s="2"/>
       <c r="AA847" s="2"/>
     </row>
-    <row r="848" spans="1:27" ht="13.2">
+    <row r="848" spans="1:27" ht="12.75">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
       <c r="C848" s="14"/>
@@ -27114,7 +27127,7 @@
       <c r="Z848" s="2"/>
       <c r="AA848" s="2"/>
     </row>
-    <row r="849" spans="1:27" ht="13.2">
+    <row r="849" spans="1:27" ht="12.75">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
       <c r="C849" s="14"/>
@@ -27143,7 +27156,7 @@
       <c r="Z849" s="2"/>
       <c r="AA849" s="2"/>
     </row>
-    <row r="850" spans="1:27" ht="13.2">
+    <row r="850" spans="1:27" ht="12.75">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
       <c r="C850" s="14"/>
@@ -27172,7 +27185,7 @@
       <c r="Z850" s="2"/>
       <c r="AA850" s="2"/>
     </row>
-    <row r="851" spans="1:27" ht="13.2">
+    <row r="851" spans="1:27" ht="12.75">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
       <c r="C851" s="14"/>
@@ -27201,7 +27214,7 @@
       <c r="Z851" s="2"/>
       <c r="AA851" s="2"/>
     </row>
-    <row r="852" spans="1:27" ht="13.2">
+    <row r="852" spans="1:27" ht="12.75">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
       <c r="C852" s="14"/>
@@ -27230,7 +27243,7 @@
       <c r="Z852" s="2"/>
       <c r="AA852" s="2"/>
     </row>
-    <row r="853" spans="1:27" ht="13.2">
+    <row r="853" spans="1:27" ht="12.75">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
       <c r="C853" s="14"/>
@@ -27259,7 +27272,7 @@
       <c r="Z853" s="2"/>
       <c r="AA853" s="2"/>
     </row>
-    <row r="854" spans="1:27" ht="13.2">
+    <row r="854" spans="1:27" ht="12.75">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
       <c r="C854" s="14"/>
@@ -27288,7 +27301,7 @@
       <c r="Z854" s="2"/>
       <c r="AA854" s="2"/>
     </row>
-    <row r="855" spans="1:27" ht="13.2">
+    <row r="855" spans="1:27" ht="12.75">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
       <c r="C855" s="14"/>
@@ -27317,7 +27330,7 @@
       <c r="Z855" s="2"/>
       <c r="AA855" s="2"/>
     </row>
-    <row r="856" spans="1:27" ht="13.2">
+    <row r="856" spans="1:27" ht="12.75">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
       <c r="C856" s="14"/>
@@ -27346,7 +27359,7 @@
       <c r="Z856" s="2"/>
       <c r="AA856" s="2"/>
     </row>
-    <row r="857" spans="1:27" ht="13.2">
+    <row r="857" spans="1:27" ht="12.75">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
       <c r="C857" s="14"/>
@@ -27375,7 +27388,7 @@
       <c r="Z857" s="2"/>
       <c r="AA857" s="2"/>
     </row>
-    <row r="858" spans="1:27" ht="13.2">
+    <row r="858" spans="1:27" ht="12.75">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
       <c r="C858" s="14"/>
@@ -27404,7 +27417,7 @@
       <c r="Z858" s="2"/>
       <c r="AA858" s="2"/>
     </row>
-    <row r="859" spans="1:27" ht="13.2">
+    <row r="859" spans="1:27" ht="12.75">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
       <c r="C859" s="14"/>
@@ -27433,7 +27446,7 @@
       <c r="Z859" s="2"/>
       <c r="AA859" s="2"/>
     </row>
-    <row r="860" spans="1:27" ht="13.2">
+    <row r="860" spans="1:27" ht="12.75">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
       <c r="C860" s="14"/>
@@ -27462,7 +27475,7 @@
       <c r="Z860" s="2"/>
       <c r="AA860" s="2"/>
     </row>
-    <row r="861" spans="1:27" ht="13.2">
+    <row r="861" spans="1:27" ht="12.75">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
       <c r="C861" s="14"/>
@@ -27491,7 +27504,7 @@
       <c r="Z861" s="2"/>
       <c r="AA861" s="2"/>
     </row>
-    <row r="862" spans="1:27" ht="13.2">
+    <row r="862" spans="1:27" ht="12.75">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
       <c r="C862" s="14"/>
@@ -27520,7 +27533,7 @@
       <c r="Z862" s="2"/>
       <c r="AA862" s="2"/>
     </row>
-    <row r="863" spans="1:27" ht="13.2">
+    <row r="863" spans="1:27" ht="12.75">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
       <c r="C863" s="14"/>
@@ -27549,7 +27562,7 @@
       <c r="Z863" s="2"/>
       <c r="AA863" s="2"/>
     </row>
-    <row r="864" spans="1:27" ht="13.2">
+    <row r="864" spans="1:27" ht="12.75">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
       <c r="C864" s="14"/>
@@ -27578,7 +27591,7 @@
       <c r="Z864" s="2"/>
       <c r="AA864" s="2"/>
     </row>
-    <row r="865" spans="1:27" ht="13.2">
+    <row r="865" spans="1:27" ht="12.75">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
       <c r="C865" s="14"/>
@@ -27607,7 +27620,7 @@
       <c r="Z865" s="2"/>
       <c r="AA865" s="2"/>
     </row>
-    <row r="866" spans="1:27" ht="13.2">
+    <row r="866" spans="1:27" ht="12.75">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
       <c r="C866" s="14"/>
@@ -27636,7 +27649,7 @@
       <c r="Z866" s="2"/>
       <c r="AA866" s="2"/>
     </row>
-    <row r="867" spans="1:27" ht="13.2">
+    <row r="867" spans="1:27" ht="12.75">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
       <c r="C867" s="14"/>
@@ -27665,7 +27678,7 @@
       <c r="Z867" s="2"/>
       <c r="AA867" s="2"/>
     </row>
-    <row r="868" spans="1:27" ht="13.2">
+    <row r="868" spans="1:27" ht="12.75">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
       <c r="C868" s="14"/>
@@ -27694,7 +27707,7 @@
       <c r="Z868" s="2"/>
       <c r="AA868" s="2"/>
     </row>
-    <row r="869" spans="1:27" ht="13.2">
+    <row r="869" spans="1:27" ht="12.75">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
       <c r="C869" s="14"/>
@@ -27723,7 +27736,7 @@
       <c r="Z869" s="2"/>
       <c r="AA869" s="2"/>
     </row>
-    <row r="870" spans="1:27" ht="13.2">
+    <row r="870" spans="1:27" ht="12.75">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
       <c r="C870" s="14"/>
@@ -27752,7 +27765,7 @@
       <c r="Z870" s="2"/>
       <c r="AA870" s="2"/>
     </row>
-    <row r="871" spans="1:27" ht="13.2">
+    <row r="871" spans="1:27" ht="12.75">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
       <c r="C871" s="14"/>
@@ -27781,7 +27794,7 @@
       <c r="Z871" s="2"/>
       <c r="AA871" s="2"/>
     </row>
-    <row r="872" spans="1:27" ht="13.2">
+    <row r="872" spans="1:27" ht="12.75">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
       <c r="C872" s="14"/>
@@ -27810,7 +27823,7 @@
       <c r="Z872" s="2"/>
       <c r="AA872" s="2"/>
     </row>
-    <row r="873" spans="1:27" ht="13.2">
+    <row r="873" spans="1:27" ht="12.75">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
       <c r="C873" s="14"/>
@@ -27839,7 +27852,7 @@
       <c r="Z873" s="2"/>
       <c r="AA873" s="2"/>
     </row>
-    <row r="874" spans="1:27" ht="13.2">
+    <row r="874" spans="1:27" ht="12.75">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
       <c r="C874" s="14"/>
@@ -27868,7 +27881,7 @@
       <c r="Z874" s="2"/>
       <c r="AA874" s="2"/>
     </row>
-    <row r="875" spans="1:27" ht="13.2">
+    <row r="875" spans="1:27" ht="12.75">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
       <c r="C875" s="14"/>
@@ -27897,7 +27910,7 @@
       <c r="Z875" s="2"/>
       <c r="AA875" s="2"/>
     </row>
-    <row r="876" spans="1:27" ht="13.2">
+    <row r="876" spans="1:27" ht="12.75">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
       <c r="C876" s="14"/>
@@ -27926,7 +27939,7 @@
       <c r="Z876" s="2"/>
       <c r="AA876" s="2"/>
     </row>
-    <row r="877" spans="1:27" ht="13.2">
+    <row r="877" spans="1:27" ht="12.75">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
       <c r="C877" s="14"/>
@@ -27955,7 +27968,7 @@
       <c r="Z877" s="2"/>
       <c r="AA877" s="2"/>
     </row>
-    <row r="878" spans="1:27" ht="13.2">
+    <row r="878" spans="1:27" ht="12.75">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
       <c r="C878" s="14"/>
@@ -27984,7 +27997,7 @@
       <c r="Z878" s="2"/>
       <c r="AA878" s="2"/>
     </row>
-    <row r="879" spans="1:27" ht="13.2">
+    <row r="879" spans="1:27" ht="12.75">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
       <c r="C879" s="14"/>
@@ -28013,7 +28026,7 @@
       <c r="Z879" s="2"/>
       <c r="AA879" s="2"/>
     </row>
-    <row r="880" spans="1:27" ht="13.2">
+    <row r="880" spans="1:27" ht="12.75">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
       <c r="C880" s="14"/>
@@ -28042,7 +28055,7 @@
       <c r="Z880" s="2"/>
       <c r="AA880" s="2"/>
     </row>
-    <row r="881" spans="1:27" ht="13.2">
+    <row r="881" spans="1:27" ht="12.75">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
       <c r="C881" s="14"/>
@@ -28071,7 +28084,7 @@
       <c r="Z881" s="2"/>
       <c r="AA881" s="2"/>
     </row>
-    <row r="882" spans="1:27" ht="13.2">
+    <row r="882" spans="1:27" ht="12.75">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
       <c r="C882" s="14"/>
@@ -28100,7 +28113,7 @@
       <c r="Z882" s="2"/>
       <c r="AA882" s="2"/>
     </row>
-    <row r="883" spans="1:27" ht="13.2">
+    <row r="883" spans="1:27" ht="12.75">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
       <c r="C883" s="14"/>
@@ -28129,7 +28142,7 @@
       <c r="Z883" s="2"/>
       <c r="AA883" s="2"/>
     </row>
-    <row r="884" spans="1:27" ht="13.2">
+    <row r="884" spans="1:27" ht="12.75">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
       <c r="C884" s="14"/>
@@ -28158,7 +28171,7 @@
       <c r="Z884" s="2"/>
       <c r="AA884" s="2"/>
     </row>
-    <row r="885" spans="1:27" ht="13.2">
+    <row r="885" spans="1:27" ht="12.75">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
       <c r="C885" s="14"/>
@@ -28187,7 +28200,7 @@
       <c r="Z885" s="2"/>
       <c r="AA885" s="2"/>
     </row>
-    <row r="886" spans="1:27" ht="13.2">
+    <row r="886" spans="1:27" ht="12.75">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
       <c r="C886" s="14"/>
@@ -28216,7 +28229,7 @@
       <c r="Z886" s="2"/>
       <c r="AA886" s="2"/>
     </row>
-    <row r="887" spans="1:27" ht="13.2">
+    <row r="887" spans="1:27" ht="12.75">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
       <c r="C887" s="14"/>
@@ -28245,7 +28258,7 @@
       <c r="Z887" s="2"/>
       <c r="AA887" s="2"/>
     </row>
-    <row r="888" spans="1:27" ht="13.2">
+    <row r="888" spans="1:27" ht="12.75">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
       <c r="C888" s="14"/>
@@ -28274,7 +28287,7 @@
       <c r="Z888" s="2"/>
       <c r="AA888" s="2"/>
     </row>
-    <row r="889" spans="1:27" ht="13.2">
+    <row r="889" spans="1:27" ht="12.75">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
       <c r="C889" s="14"/>
@@ -28303,7 +28316,7 @@
       <c r="Z889" s="2"/>
       <c r="AA889" s="2"/>
     </row>
-    <row r="890" spans="1:27" ht="13.2">
+    <row r="890" spans="1:27" ht="12.75">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
       <c r="C890" s="14"/>
@@ -28332,7 +28345,7 @@
       <c r="Z890" s="2"/>
       <c r="AA890" s="2"/>
     </row>
-    <row r="891" spans="1:27" ht="13.2">
+    <row r="891" spans="1:27" ht="12.75">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
       <c r="C891" s="14"/>
@@ -28361,7 +28374,7 @@
       <c r="Z891" s="2"/>
       <c r="AA891" s="2"/>
     </row>
-    <row r="892" spans="1:27" ht="13.2">
+    <row r="892" spans="1:27" ht="12.75">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
       <c r="C892" s="14"/>
@@ -28390,7 +28403,7 @@
       <c r="Z892" s="2"/>
       <c r="AA892" s="2"/>
     </row>
-    <row r="893" spans="1:27" ht="13.2">
+    <row r="893" spans="1:27" ht="12.75">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
       <c r="C893" s="14"/>
@@ -28419,7 +28432,7 @@
       <c r="Z893" s="2"/>
       <c r="AA893" s="2"/>
     </row>
-    <row r="894" spans="1:27" ht="13.2">
+    <row r="894" spans="1:27" ht="12.75">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
       <c r="C894" s="14"/>
@@ -28448,7 +28461,7 @@
       <c r="Z894" s="2"/>
       <c r="AA894" s="2"/>
     </row>
-    <row r="895" spans="1:27" ht="13.2">
+    <row r="895" spans="1:27" ht="12.75">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
       <c r="C895" s="14"/>
@@ -28477,7 +28490,7 @@
       <c r="Z895" s="2"/>
       <c r="AA895" s="2"/>
     </row>
-    <row r="896" spans="1:27" ht="13.2">
+    <row r="896" spans="1:27" ht="12.75">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
       <c r="C896" s="14"/>
@@ -28506,7 +28519,7 @@
       <c r="Z896" s="2"/>
       <c r="AA896" s="2"/>
     </row>
-    <row r="897" spans="1:27" ht="13.2">
+    <row r="897" spans="1:27" ht="12.75">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
       <c r="C897" s="14"/>
@@ -28535,7 +28548,7 @@
       <c r="Z897" s="2"/>
       <c r="AA897" s="2"/>
     </row>
-    <row r="898" spans="1:27" ht="13.2">
+    <row r="898" spans="1:27" ht="12.75">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
       <c r="C898" s="14"/>
@@ -28564,7 +28577,7 @@
       <c r="Z898" s="2"/>
       <c r="AA898" s="2"/>
     </row>
-    <row r="899" spans="1:27" ht="13.2">
+    <row r="899" spans="1:27" ht="12.75">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
       <c r="C899" s="14"/>
@@ -28593,7 +28606,7 @@
       <c r="Z899" s="2"/>
       <c r="AA899" s="2"/>
     </row>
-    <row r="900" spans="1:27" ht="13.2">
+    <row r="900" spans="1:27" ht="12.75">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
       <c r="C900" s="14"/>
@@ -28622,7 +28635,7 @@
       <c r="Z900" s="2"/>
       <c r="AA900" s="2"/>
     </row>
-    <row r="901" spans="1:27" ht="13.2">
+    <row r="901" spans="1:27" ht="12.75">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
       <c r="C901" s="14"/>
@@ -28651,7 +28664,7 @@
       <c r="Z901" s="2"/>
       <c r="AA901" s="2"/>
     </row>
-    <row r="902" spans="1:27" ht="13.2">
+    <row r="902" spans="1:27" ht="12.75">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
       <c r="C902" s="14"/>
@@ -28680,7 +28693,7 @@
       <c r="Z902" s="2"/>
       <c r="AA902" s="2"/>
     </row>
-    <row r="903" spans="1:27" ht="13.2">
+    <row r="903" spans="1:27" ht="12.75">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
       <c r="C903" s="14"/>
@@ -28709,7 +28722,7 @@
       <c r="Z903" s="2"/>
       <c r="AA903" s="2"/>
     </row>
-    <row r="904" spans="1:27" ht="13.2">
+    <row r="904" spans="1:27" ht="12.75">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
       <c r="C904" s="14"/>
@@ -28738,7 +28751,7 @@
       <c r="Z904" s="2"/>
       <c r="AA904" s="2"/>
     </row>
-    <row r="905" spans="1:27" ht="13.2">
+    <row r="905" spans="1:27" ht="12.75">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
       <c r="C905" s="14"/>
@@ -28767,7 +28780,7 @@
       <c r="Z905" s="2"/>
       <c r="AA905" s="2"/>
     </row>
-    <row r="906" spans="1:27" ht="13.2">
+    <row r="906" spans="1:27" ht="12.75">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
       <c r="C906" s="14"/>
@@ -28796,7 +28809,7 @@
       <c r="Z906" s="2"/>
       <c r="AA906" s="2"/>
     </row>
-    <row r="907" spans="1:27" ht="13.2">
+    <row r="907" spans="1:27" ht="12.75">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
       <c r="C907" s="14"/>
@@ -28825,7 +28838,7 @@
       <c r="Z907" s="2"/>
       <c r="AA907" s="2"/>
     </row>
-    <row r="908" spans="1:27" ht="13.2">
+    <row r="908" spans="1:27" ht="12.75">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
       <c r="C908" s="14"/>
@@ -28854,7 +28867,7 @@
       <c r="Z908" s="2"/>
       <c r="AA908" s="2"/>
     </row>
-    <row r="909" spans="1:27" ht="13.2">
+    <row r="909" spans="1:27" ht="12.75">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
       <c r="C909" s="14"/>
@@ -28883,7 +28896,7 @@
       <c r="Z909" s="2"/>
       <c r="AA909" s="2"/>
     </row>
-    <row r="910" spans="1:27" ht="13.2">
+    <row r="910" spans="1:27" ht="12.75">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
       <c r="C910" s="14"/>
@@ -28912,7 +28925,7 @@
       <c r="Z910" s="2"/>
       <c r="AA910" s="2"/>
     </row>
-    <row r="911" spans="1:27" ht="13.2">
+    <row r="911" spans="1:27" ht="12.75">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
       <c r="C911" s="14"/>
@@ -28941,7 +28954,7 @@
       <c r="Z911" s="2"/>
       <c r="AA911" s="2"/>
     </row>
-    <row r="912" spans="1:27" ht="13.2">
+    <row r="912" spans="1:27" ht="12.75">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
       <c r="C912" s="14"/>
@@ -28970,7 +28983,7 @@
       <c r="Z912" s="2"/>
       <c r="AA912" s="2"/>
     </row>
-    <row r="913" spans="1:27" ht="13.2">
+    <row r="913" spans="1:27" ht="12.75">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
       <c r="C913" s="14"/>
@@ -28999,7 +29012,7 @@
       <c r="Z913" s="2"/>
       <c r="AA913" s="2"/>
     </row>
-    <row r="914" spans="1:27" ht="13.2">
+    <row r="914" spans="1:27" ht="12.75">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
       <c r="C914" s="14"/>
@@ -29028,7 +29041,7 @@
       <c r="Z914" s="2"/>
       <c r="AA914" s="2"/>
     </row>
-    <row r="915" spans="1:27" ht="13.2">
+    <row r="915" spans="1:27" ht="12.75">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
       <c r="C915" s="14"/>
@@ -29057,7 +29070,7 @@
       <c r="Z915" s="2"/>
       <c r="AA915" s="2"/>
     </row>
-    <row r="916" spans="1:27" ht="13.2">
+    <row r="916" spans="1:27" ht="12.75">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
       <c r="C916" s="14"/>
@@ -29086,7 +29099,7 @@
       <c r="Z916" s="2"/>
       <c r="AA916" s="2"/>
     </row>
-    <row r="917" spans="1:27" ht="13.2">
+    <row r="917" spans="1:27" ht="12.75">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
       <c r="C917" s="14"/>
@@ -29115,7 +29128,7 @@
       <c r="Z917" s="2"/>
       <c r="AA917" s="2"/>
     </row>
-    <row r="918" spans="1:27" ht="13.2">
+    <row r="918" spans="1:27" ht="12.75">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
       <c r="C918" s="14"/>
@@ -29144,7 +29157,7 @@
       <c r="Z918" s="2"/>
       <c r="AA918" s="2"/>
     </row>
-    <row r="919" spans="1:27" ht="13.2">
+    <row r="919" spans="1:27" ht="12.75">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
       <c r="C919" s="14"/>
@@ -29173,7 +29186,7 @@
       <c r="Z919" s="2"/>
       <c r="AA919" s="2"/>
     </row>
-    <row r="920" spans="1:27" ht="13.2">
+    <row r="920" spans="1:27" ht="12.75">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
       <c r="C920" s="14"/>
@@ -29202,7 +29215,7 @@
       <c r="Z920" s="2"/>
       <c r="AA920" s="2"/>
     </row>
-    <row r="921" spans="1:27" ht="13.2">
+    <row r="921" spans="1:27" ht="12.75">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
       <c r="C921" s="14"/>
@@ -29231,7 +29244,7 @@
       <c r="Z921" s="2"/>
       <c r="AA921" s="2"/>
     </row>
-    <row r="922" spans="1:27" ht="13.2">
+    <row r="922" spans="1:27" ht="12.75">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
       <c r="C922" s="14"/>
@@ -29260,7 +29273,7 @@
       <c r="Z922" s="2"/>
       <c r="AA922" s="2"/>
     </row>
-    <row r="923" spans="1:27" ht="13.2">
+    <row r="923" spans="1:27" ht="12.75">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
       <c r="C923" s="14"/>
@@ -29289,7 +29302,7 @@
       <c r="Z923" s="2"/>
       <c r="AA923" s="2"/>
     </row>
-    <row r="924" spans="1:27" ht="13.2">
+    <row r="924" spans="1:27" ht="12.75">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
       <c r="C924" s="14"/>
@@ -29318,7 +29331,7 @@
       <c r="Z924" s="2"/>
       <c r="AA924" s="2"/>
     </row>
-    <row r="925" spans="1:27" ht="13.2">
+    <row r="925" spans="1:27" ht="12.75">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
       <c r="C925" s="14"/>
@@ -29347,7 +29360,7 @@
       <c r="Z925" s="2"/>
       <c r="AA925" s="2"/>
     </row>
-    <row r="926" spans="1:27" ht="13.2">
+    <row r="926" spans="1:27" ht="12.75">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
       <c r="C926" s="14"/>
@@ -29376,7 +29389,7 @@
       <c r="Z926" s="2"/>
       <c r="AA926" s="2"/>
     </row>
-    <row r="927" spans="1:27" ht="13.2">
+    <row r="927" spans="1:27" ht="12.75">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
       <c r="C927" s="14"/>
@@ -29405,7 +29418,7 @@
       <c r="Z927" s="2"/>
       <c r="AA927" s="2"/>
     </row>
-    <row r="928" spans="1:27" ht="13.2">
+    <row r="928" spans="1:27" ht="12.75">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
       <c r="C928" s="14"/>
@@ -29434,7 +29447,7 @@
       <c r="Z928" s="2"/>
       <c r="AA928" s="2"/>
     </row>
-    <row r="929" spans="1:27" ht="13.2">
+    <row r="929" spans="1:27" ht="12.75">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
       <c r="C929" s="14"/>
@@ -29463,7 +29476,7 @@
       <c r="Z929" s="2"/>
       <c r="AA929" s="2"/>
     </row>
-    <row r="930" spans="1:27" ht="13.2">
+    <row r="930" spans="1:27" ht="12.75">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
       <c r="C930" s="14"/>
@@ -29492,7 +29505,7 @@
       <c r="Z930" s="2"/>
       <c r="AA930" s="2"/>
     </row>
-    <row r="931" spans="1:27" ht="13.2">
+    <row r="931" spans="1:27" ht="12.75">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
       <c r="C931" s="14"/>
@@ -29521,7 +29534,7 @@
       <c r="Z931" s="2"/>
       <c r="AA931" s="2"/>
     </row>
-    <row r="932" spans="1:27" ht="13.2">
+    <row r="932" spans="1:27" ht="12.75">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
       <c r="C932" s="14"/>
@@ -29550,7 +29563,7 @@
       <c r="Z932" s="2"/>
       <c r="AA932" s="2"/>
     </row>
-    <row r="933" spans="1:27" ht="13.2">
+    <row r="933" spans="1:27" ht="12.75">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
       <c r="C933" s="14"/>
@@ -29579,7 +29592,7 @@
       <c r="Z933" s="2"/>
       <c r="AA933" s="2"/>
     </row>
-    <row r="934" spans="1:27" ht="13.2">
+    <row r="934" spans="1:27" ht="12.75">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
       <c r="C934" s="14"/>
@@ -29608,7 +29621,7 @@
       <c r="Z934" s="2"/>
       <c r="AA934" s="2"/>
     </row>
-    <row r="935" spans="1:27" ht="13.2">
+    <row r="935" spans="1:27" ht="12.75">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
       <c r="C935" s="14"/>
@@ -29637,7 +29650,7 @@
       <c r="Z935" s="2"/>
       <c r="AA935" s="2"/>
     </row>
-    <row r="936" spans="1:27" ht="13.2">
+    <row r="936" spans="1:27" ht="12.75">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
       <c r="C936" s="14"/>
@@ -29666,7 +29679,7 @@
       <c r="Z936" s="2"/>
       <c r="AA936" s="2"/>
     </row>
-    <row r="937" spans="1:27" ht="13.2">
+    <row r="937" spans="1:27" ht="12.75">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
       <c r="C937" s="14"/>
@@ -29695,7 +29708,7 @@
       <c r="Z937" s="2"/>
       <c r="AA937" s="2"/>
     </row>
-    <row r="938" spans="1:27" ht="13.2">
+    <row r="938" spans="1:27" ht="12.75">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
       <c r="C938" s="14"/>
@@ -29724,7 +29737,7 @@
       <c r="Z938" s="2"/>
       <c r="AA938" s="2"/>
     </row>
-    <row r="939" spans="1:27" ht="13.2">
+    <row r="939" spans="1:27" ht="12.75">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
       <c r="C939" s="14"/>
@@ -29753,7 +29766,7 @@
       <c r="Z939" s="2"/>
       <c r="AA939" s="2"/>
     </row>
-    <row r="940" spans="1:27" ht="13.2">
+    <row r="940" spans="1:27" ht="12.75">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
       <c r="C940" s="14"/>
@@ -29782,7 +29795,7 @@
       <c r="Z940" s="2"/>
       <c r="AA940" s="2"/>
     </row>
-    <row r="941" spans="1:27" ht="13.2">
+    <row r="941" spans="1:27" ht="12.75">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
       <c r="C941" s="14"/>
@@ -29811,7 +29824,7 @@
       <c r="Z941" s="2"/>
       <c r="AA941" s="2"/>
     </row>
-    <row r="942" spans="1:27" ht="13.2">
+    <row r="942" spans="1:27" ht="12.75">
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
       <c r="C942" s="14"/>
@@ -29840,7 +29853,7 @@
       <c r="Z942" s="2"/>
       <c r="AA942" s="2"/>
     </row>
-    <row r="943" spans="1:27" ht="13.2">
+    <row r="943" spans="1:27" ht="12.75">
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
       <c r="C943" s="14"/>
@@ -29869,7 +29882,7 @@
       <c r="Z943" s="2"/>
       <c r="AA943" s="2"/>
     </row>
-    <row r="944" spans="1:27" ht="13.2">
+    <row r="944" spans="1:27" ht="12.75">
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
       <c r="C944" s="14"/>
@@ -29898,7 +29911,7 @@
       <c r="Z944" s="2"/>
       <c r="AA944" s="2"/>
     </row>
-    <row r="945" spans="1:27" ht="13.2">
+    <row r="945" spans="1:27" ht="12.75">
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
       <c r="C945" s="14"/>
@@ -29927,7 +29940,7 @@
       <c r="Z945" s="2"/>
       <c r="AA945" s="2"/>
     </row>
-    <row r="946" spans="1:27" ht="13.2">
+    <row r="946" spans="1:27" ht="12.75">
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
       <c r="C946" s="14"/>
@@ -29956,7 +29969,7 @@
       <c r="Z946" s="2"/>
       <c r="AA946" s="2"/>
     </row>
-    <row r="947" spans="1:27" ht="13.2">
+    <row r="947" spans="1:27" ht="12.75">
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
       <c r="C947" s="14"/>
@@ -29985,7 +29998,7 @@
       <c r="Z947" s="2"/>
       <c r="AA947" s="2"/>
     </row>
-    <row r="948" spans="1:27" ht="13.2">
+    <row r="948" spans="1:27" ht="12.75">
       <c r="A948" s="2"/>
       <c r="B948" s="2"/>
       <c r="C948" s="14"/>
@@ -30014,7 +30027,7 @@
       <c r="Z948" s="2"/>
       <c r="AA948" s="2"/>
     </row>
-    <row r="949" spans="1:27" ht="13.2">
+    <row r="949" spans="1:27" ht="12.75">
       <c r="A949" s="2"/>
       <c r="B949" s="2"/>
       <c r="C949" s="14"/>
@@ -30043,7 +30056,7 @@
       <c r="Z949" s="2"/>
       <c r="AA949" s="2"/>
     </row>
-    <row r="950" spans="1:27" ht="13.2">
+    <row r="950" spans="1:27" ht="12.75">
       <c r="A950" s="2"/>
       <c r="B950" s="2"/>
       <c r="C950" s="14"/>
@@ -30072,7 +30085,7 @@
       <c r="Z950" s="2"/>
       <c r="AA950" s="2"/>
     </row>
-    <row r="951" spans="1:27" ht="13.2">
+    <row r="951" spans="1:27" ht="12.75">
       <c r="A951" s="2"/>
       <c r="B951" s="2"/>
       <c r="C951" s="14"/>
@@ -30101,7 +30114,7 @@
       <c r="Z951" s="2"/>
       <c r="AA951" s="2"/>
     </row>
-    <row r="952" spans="1:27" ht="13.2">
+    <row r="952" spans="1:27" ht="12.75">
       <c r="A952" s="2"/>
       <c r="B952" s="2"/>
       <c r="C952" s="14"/>
@@ -30130,7 +30143,7 @@
       <c r="Z952" s="2"/>
       <c r="AA952" s="2"/>
     </row>
-    <row r="953" spans="1:27" ht="13.2">
+    <row r="953" spans="1:27" ht="12.75">
       <c r="A953" s="2"/>
       <c r="B953" s="2"/>
       <c r="C953" s="14"/>
@@ -30159,7 +30172,7 @@
       <c r="Z953" s="2"/>
       <c r="AA953" s="2"/>
     </row>
-    <row r="954" spans="1:27" ht="13.2">
+    <row r="954" spans="1:27" ht="12.75">
       <c r="A954" s="2"/>
       <c r="B954" s="2"/>
       <c r="C954" s="14"/>
@@ -30188,7 +30201,7 @@
       <c r="Z954" s="2"/>
       <c r="AA954" s="2"/>
     </row>
-    <row r="955" spans="1:27" ht="13.2">
+    <row r="955" spans="1:27" ht="12.75">
       <c r="A955" s="2"/>
       <c r="B955" s="2"/>
       <c r="C955" s="14"/>
@@ -30217,7 +30230,7 @@
       <c r="Z955" s="2"/>
       <c r="AA955" s="2"/>
     </row>
-    <row r="956" spans="1:27" ht="13.2">
+    <row r="956" spans="1:27" ht="12.75">
       <c r="A956" s="2"/>
       <c r="B956" s="2"/>
       <c r="C956" s="14"/>
@@ -30246,7 +30259,7 @@
       <c r="Z956" s="2"/>
       <c r="AA956" s="2"/>
     </row>
-    <row r="957" spans="1:27" ht="13.2">
+    <row r="957" spans="1:27" ht="12.75">
       <c r="A957" s="2"/>
       <c r="B957" s="2"/>
       <c r="C957" s="14"/>
@@ -30275,7 +30288,7 @@
       <c r="Z957" s="2"/>
       <c r="AA957" s="2"/>
     </row>
-    <row r="958" spans="1:27" ht="13.2">
+    <row r="958" spans="1:27" ht="12.75">
       <c r="A958" s="2"/>
       <c r="B958" s="2"/>
       <c r="C958" s="14"/>
@@ -30304,7 +30317,7 @@
       <c r="Z958" s="2"/>
       <c r="AA958" s="2"/>
     </row>
-    <row r="959" spans="1:27" ht="13.2">
+    <row r="959" spans="1:27" ht="12.75">
       <c r="A959" s="2"/>
       <c r="B959" s="2"/>
       <c r="C959" s="14"/>
@@ -30333,7 +30346,7 @@
       <c r="Z959" s="2"/>
       <c r="AA959" s="2"/>
     </row>
-    <row r="960" spans="1:27" ht="13.2">
+    <row r="960" spans="1:27" ht="12.75">
       <c r="A960" s="2"/>
       <c r="B960" s="2"/>
       <c r="C960" s="14"/>
@@ -30362,7 +30375,7 @@
       <c r="Z960" s="2"/>
       <c r="AA960" s="2"/>
     </row>
-    <row r="961" spans="1:27" ht="13.2">
+    <row r="961" spans="1:27" ht="12.75">
       <c r="A961" s="2"/>
       <c r="B961" s="2"/>
       <c r="C961" s="14"/>
@@ -30391,7 +30404,7 @@
       <c r="Z961" s="2"/>
       <c r="AA961" s="2"/>
     </row>
-    <row r="962" spans="1:27" ht="13.2">
+    <row r="962" spans="1:27" ht="12.75">
       <c r="A962" s="2"/>
       <c r="B962" s="2"/>
       <c r="C962" s="14"/>
@@ -30420,7 +30433,7 @@
       <c r="Z962" s="2"/>
       <c r="AA962" s="2"/>
     </row>
-    <row r="963" spans="1:27" ht="13.2">
+    <row r="963" spans="1:27" ht="12.75">
       <c r="A963" s="2"/>
       <c r="B963" s="2"/>
       <c r="C963" s="14"/>
@@ -30449,7 +30462,7 @@
       <c r="Z963" s="2"/>
       <c r="AA963" s="2"/>
     </row>
-    <row r="964" spans="1:27" ht="13.2">
+    <row r="964" spans="1:27" ht="12.75">
       <c r="A964" s="2"/>
       <c r="B964" s="2"/>
       <c r="C964" s="14"/>
@@ -30478,7 +30491,7 @@
       <c r="Z964" s="2"/>
       <c r="AA964" s="2"/>
     </row>
-    <row r="965" spans="1:27" ht="13.2">
+    <row r="965" spans="1:27" ht="12.75">
       <c r="A965" s="2"/>
       <c r="B965" s="2"/>
       <c r="C965" s="14"/>
@@ -30507,7 +30520,7 @@
       <c r="Z965" s="2"/>
       <c r="AA965" s="2"/>
     </row>
-    <row r="966" spans="1:27" ht="13.2">
+    <row r="966" spans="1:27" ht="12.75">
       <c r="A966" s="2"/>
       <c r="B966" s="2"/>
       <c r="C966" s="14"/>
@@ -30536,7 +30549,7 @@
       <c r="Z966" s="2"/>
       <c r="AA966" s="2"/>
     </row>
-    <row r="967" spans="1:27" ht="13.2">
+    <row r="967" spans="1:27" ht="12.75">
       <c r="A967" s="2"/>
       <c r="B967" s="2"/>
       <c r="C967" s="14"/>
@@ -30565,7 +30578,7 @@
       <c r="Z967" s="2"/>
       <c r="AA967" s="2"/>
     </row>
-    <row r="968" spans="1:27" ht="13.2">
+    <row r="968" spans="1:27" ht="12.75">
       <c r="A968" s="2"/>
       <c r="B968" s="2"/>
       <c r="C968" s="14"/>
@@ -30594,7 +30607,7 @@
       <c r="Z968" s="2"/>
       <c r="AA968" s="2"/>
     </row>
-    <row r="969" spans="1:27" ht="13.2">
+    <row r="969" spans="1:27" ht="12.75">
       <c r="A969" s="2"/>
       <c r="B969" s="2"/>
       <c r="C969" s="14"/>
@@ -30623,7 +30636,7 @@
       <c r="Z969" s="2"/>
       <c r="AA969" s="2"/>
     </row>
-    <row r="970" spans="1:27" ht="13.2">
+    <row r="970" spans="1:27" ht="12.75">
       <c r="A970" s="2"/>
       <c r="B970" s="2"/>
       <c r="C970" s="14"/>
@@ -30652,7 +30665,7 @@
       <c r="Z970" s="2"/>
       <c r="AA970" s="2"/>
     </row>
-    <row r="971" spans="1:27" ht="13.2">
+    <row r="971" spans="1:27" ht="12.75">
       <c r="A971" s="2"/>
       <c r="B971" s="2"/>
       <c r="C971" s="14"/>
@@ -30681,7 +30694,7 @@
       <c r="Z971" s="2"/>
       <c r="AA971" s="2"/>
     </row>
-    <row r="972" spans="1:27" ht="13.2">
+    <row r="972" spans="1:27" ht="12.75">
       <c r="A972" s="2"/>
       <c r="B972" s="2"/>
       <c r="C972" s="14"/>
@@ -30710,7 +30723,7 @@
       <c r="Z972" s="2"/>
       <c r="AA972" s="2"/>
     </row>
-    <row r="973" spans="1:27" ht="13.2">
+    <row r="973" spans="1:27" ht="12.75">
       <c r="A973" s="2"/>
       <c r="B973" s="2"/>
       <c r="C973" s="14"/>
@@ -30739,7 +30752,7 @@
       <c r="Z973" s="2"/>
       <c r="AA973" s="2"/>
     </row>
-    <row r="974" spans="1:27" ht="13.2">
+    <row r="974" spans="1:27" ht="12.75">
       <c r="A974" s="2"/>
       <c r="B974" s="2"/>
       <c r="C974" s="14"/>
@@ -30768,7 +30781,7 @@
       <c r="Z974" s="2"/>
       <c r="AA974" s="2"/>
     </row>
-    <row r="975" spans="1:27" ht="13.2">
+    <row r="975" spans="1:27" ht="12.75">
       <c r="A975" s="2"/>
       <c r="B975" s="2"/>
       <c r="C975" s="14"/>
@@ -30797,7 +30810,7 @@
       <c r="Z975" s="2"/>
       <c r="AA975" s="2"/>
     </row>
-    <row r="976" spans="1:27" ht="13.2">
+    <row r="976" spans="1:27" ht="12.75">
       <c r="A976" s="2"/>
       <c r="B976" s="2"/>
       <c r="C976" s="14"/>
@@ -30826,7 +30839,7 @@
       <c r="Z976" s="2"/>
       <c r="AA976" s="2"/>
     </row>
-    <row r="977" spans="1:27" ht="13.2">
+    <row r="977" spans="1:27" ht="12.75">
       <c r="A977" s="2"/>
       <c r="B977" s="2"/>
       <c r="C977" s="14"/>
@@ -30855,7 +30868,7 @@
       <c r="Z977" s="2"/>
       <c r="AA977" s="2"/>
     </row>
-    <row r="978" spans="1:27" ht="13.2">
+    <row r="978" spans="1:27" ht="12.75">
       <c r="A978" s="2"/>
       <c r="B978" s="2"/>
       <c r="C978" s="14"/>
@@ -30884,7 +30897,7 @@
       <c r="Z978" s="2"/>
       <c r="AA978" s="2"/>
     </row>
-    <row r="979" spans="1:27" ht="13.2">
+    <row r="979" spans="1:27" ht="12.75">
       <c r="A979" s="2"/>
       <c r="B979" s="2"/>
       <c r="C979" s="14"/>
@@ -30913,7 +30926,7 @@
       <c r="Z979" s="2"/>
       <c r="AA979" s="2"/>
     </row>
-    <row r="980" spans="1:27" ht="13.2">
+    <row r="980" spans="1:27" ht="12.75">
       <c r="A980" s="2"/>
       <c r="B980" s="2"/>
       <c r="C980" s="14"/>
@@ -30942,7 +30955,7 @@
       <c r="Z980" s="2"/>
       <c r="AA980" s="2"/>
     </row>
-    <row r="981" spans="1:27" ht="13.2">
+    <row r="981" spans="1:27" ht="12.75">
       <c r="A981" s="2"/>
       <c r="B981" s="2"/>
       <c r="C981" s="14"/>
@@ -30971,7 +30984,7 @@
       <c r="Z981" s="2"/>
       <c r="AA981" s="2"/>
     </row>
-    <row r="982" spans="1:27" ht="13.2">
+    <row r="982" spans="1:27" ht="12.75">
       <c r="A982" s="2"/>
       <c r="B982" s="2"/>
       <c r="C982" s="14"/>
@@ -31000,7 +31013,7 @@
       <c r="Z982" s="2"/>
       <c r="AA982" s="2"/>
     </row>
-    <row r="983" spans="1:27" ht="13.2">
+    <row r="983" spans="1:27" ht="12.75">
       <c r="A983" s="2"/>
       <c r="B983" s="2"/>
       <c r="C983" s="14"/>
@@ -31029,7 +31042,7 @@
       <c r="Z983" s="2"/>
       <c r="AA983" s="2"/>
     </row>
-    <row r="984" spans="1:27" ht="13.2">
+    <row r="984" spans="1:27" ht="12.75">
       <c r="A984" s="2"/>
       <c r="B984" s="2"/>
       <c r="C984" s="14"/>
@@ -31058,7 +31071,7 @@
       <c r="Z984" s="2"/>
       <c r="AA984" s="2"/>
     </row>
-    <row r="985" spans="1:27" ht="13.2">
+    <row r="985" spans="1:27" ht="12.75">
       <c r="A985" s="2"/>
       <c r="B985" s="2"/>
       <c r="C985" s="14"/>
@@ -31087,7 +31100,7 @@
       <c r="Z985" s="2"/>
       <c r="AA985" s="2"/>
     </row>
-    <row r="986" spans="1:27" ht="13.2">
+    <row r="986" spans="1:27" ht="12.75">
       <c r="A986" s="2"/>
       <c r="B986" s="2"/>
       <c r="C986" s="14"/>
@@ -31116,7 +31129,7 @@
       <c r="Z986" s="2"/>
       <c r="AA986" s="2"/>
     </row>
-    <row r="987" spans="1:27" ht="13.2">
+    <row r="987" spans="1:27" ht="12.75">
       <c r="A987" s="2"/>
       <c r="B987" s="2"/>
       <c r="C987" s="14"/>
@@ -31145,7 +31158,7 @@
       <c r="Z987" s="2"/>
       <c r="AA987" s="2"/>
     </row>
-    <row r="988" spans="1:27" ht="13.2">
+    <row r="988" spans="1:27" ht="12.75">
       <c r="A988" s="2"/>
       <c r="B988" s="2"/>
       <c r="C988" s="14"/>
@@ -31174,7 +31187,7 @@
       <c r="Z988" s="2"/>
       <c r="AA988" s="2"/>
     </row>
-    <row r="989" spans="1:27" ht="13.2">
+    <row r="989" spans="1:27" ht="12.75">
       <c r="A989" s="2"/>
       <c r="B989" s="2"/>
       <c r="C989" s="14"/>
@@ -31203,7 +31216,7 @@
       <c r="Z989" s="2"/>
       <c r="AA989" s="2"/>
     </row>
-    <row r="990" spans="1:27" ht="13.2">
+    <row r="990" spans="1:27" ht="12.75">
       <c r="A990" s="2"/>
       <c r="B990" s="2"/>
       <c r="C990" s="14"/>
@@ -31232,7 +31245,7 @@
       <c r="Z990" s="2"/>
       <c r="AA990" s="2"/>
     </row>
-    <row r="991" spans="1:27" ht="13.2">
+    <row r="991" spans="1:27" ht="12.75">
       <c r="A991" s="2"/>
       <c r="B991" s="2"/>
       <c r="C991" s="14"/>
@@ -31261,7 +31274,7 @@
       <c r="Z991" s="2"/>
       <c r="AA991" s="2"/>
     </row>
-    <row r="992" spans="1:27" ht="13.2">
+    <row r="992" spans="1:27" ht="12.75">
       <c r="A992" s="2"/>
       <c r="B992" s="2"/>
       <c r="C992" s="14"/>
@@ -31290,7 +31303,7 @@
       <c r="Z992" s="2"/>
       <c r="AA992" s="2"/>
     </row>
-    <row r="993" spans="1:27" ht="13.2">
+    <row r="993" spans="1:27" ht="12.75">
       <c r="A993" s="2"/>
       <c r="B993" s="2"/>
       <c r="C993" s="14"/>
@@ -31319,7 +31332,7 @@
       <c r="Z993" s="2"/>
       <c r="AA993" s="2"/>
     </row>
-    <row r="994" spans="1:27" ht="13.2">
+    <row r="994" spans="1:27" ht="12.75">
       <c r="A994" s="2"/>
       <c r="B994" s="2"/>
       <c r="C994" s="14"/>
@@ -31348,7 +31361,7 @@
       <c r="Z994" s="2"/>
       <c r="AA994" s="2"/>
     </row>
-    <row r="995" spans="1:27" ht="13.2">
+    <row r="995" spans="1:27" ht="12.75">
       <c r="A995" s="2"/>
       <c r="B995" s="2"/>
       <c r="C995" s="14"/>
@@ -31377,7 +31390,7 @@
       <c r="Z995" s="2"/>
       <c r="AA995" s="2"/>
     </row>
-    <row r="996" spans="1:27" ht="13.2">
+    <row r="996" spans="1:27" ht="12.75">
       <c r="A996" s="2"/>
       <c r="B996" s="2"/>
       <c r="C996" s="14"/>
@@ -31406,7 +31419,7 @@
       <c r="Z996" s="2"/>
       <c r="AA996" s="2"/>
     </row>
-    <row r="997" spans="1:27" ht="13.2">
+    <row r="997" spans="1:27" ht="12.75">
       <c r="A997" s="2"/>
       <c r="B997" s="2"/>
       <c r="C997" s="14"/>
@@ -31435,7 +31448,7 @@
       <c r="Z997" s="2"/>
       <c r="AA997" s="2"/>
     </row>
-    <row r="998" spans="1:27" ht="13.2">
+    <row r="998" spans="1:27" ht="12.75">
       <c r="A998" s="2"/>
       <c r="B998" s="2"/>
       <c r="C998" s="14"/>
@@ -31464,7 +31477,7 @@
       <c r="Z998" s="2"/>
       <c r="AA998" s="2"/>
     </row>
-    <row r="999" spans="1:27" ht="13.2">
+    <row r="999" spans="1:27" ht="12.75">
       <c r="A999" s="2"/>
       <c r="B999" s="2"/>
       <c r="C999" s="14"/>
@@ -31493,7 +31506,7 @@
       <c r="Z999" s="2"/>
       <c r="AA999" s="2"/>
     </row>
-    <row r="1000" spans="1:27" ht="13.2">
+    <row r="1000" spans="1:27" ht="12.75">
       <c r="A1000" s="2"/>
       <c r="B1000" s="2"/>
       <c r="C1000" s="14"/>
@@ -31522,7 +31535,7 @@
       <c r="Z1000" s="2"/>
       <c r="AA1000" s="2"/>
     </row>
-    <row r="1001" spans="1:27" ht="13.2">
+    <row r="1001" spans="1:27" ht="12.75">
       <c r="A1001" s="2"/>
       <c r="B1001" s="2"/>
       <c r="C1001" s="14"/>
@@ -31564,7 +31577,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
@@ -31660,9 +31673,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z5"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
@@ -31783,7 +31796,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1">
       <c r="A1" s="10" t="s">
@@ -31841,19 +31854,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:X1007"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="20.25" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" style="33" customWidth="1"/>
-    <col min="2" max="2" width="61.44140625" style="33" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="33" customWidth="1"/>
-    <col min="4" max="4" width="184.5546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="33" customWidth="1"/>
+    <col min="2" max="2" width="61.42578125" style="33" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="33" customWidth="1"/>
+    <col min="4" max="4" width="184.5703125" style="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="62.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.44140625" style="33" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" style="49" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.5546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.5546875" style="33"/>
+    <col min="6" max="6" width="62.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" style="33" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="49" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="12.5703125" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="20.25" customHeight="1">
@@ -32535,27 +32548,28 @@
       </c>
     </row>
     <row r="18" spans="1:24" ht="20.25" customHeight="1">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="B18" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="C18" s="30">
-        <v>2026</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>345</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>299</v>
-      </c>
-      <c r="I18"/>
-      <c r="J18" s="33" t="s">
-        <v>103</v>
+      <c r="B18" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="C18" s="33">
+        <v>2025</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" s="30"/>
+      <c r="F18" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="46"/>
+      <c r="H18" s="49" t="s">
+        <v>303</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="20.25" customHeight="1">
@@ -32563,75 +32577,76 @@
         <v>216</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>300</v>
-      </c>
-      <c r="C19" s="33">
+        <v>221</v>
+      </c>
+      <c r="C19" s="30">
         <v>2025</v>
       </c>
-      <c r="D19" s="33" t="s">
-        <v>248</v>
+      <c r="D19" s="30" t="s">
+        <v>302</v>
       </c>
       <c r="E19" s="30"/>
-      <c r="F19" s="33" t="s">
+      <c r="F19" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="G19" s="46"/>
-      <c r="H19" s="49" t="s">
-        <v>303</v>
+      <c r="G19" s="45"/>
+      <c r="H19" s="47" t="s">
+        <v>304</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>301</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="J19" s="30"/>
     </row>
     <row r="20" spans="1:24" ht="20.25" customHeight="1">
       <c r="A20" s="33" t="s">
         <v>216</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="C20" s="30">
         <v>2025</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="30"/>
+        <v>325</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>173</v>
+      </c>
       <c r="F20" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" s="45"/>
-      <c r="H20" s="47" t="s">
-        <v>304</v>
-      </c>
-      <c r="I20" s="22" t="s">
-        <v>306</v>
+        <v>108</v>
+      </c>
+      <c r="G20" s="30"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="30" t="s">
+        <v>324</v>
       </c>
       <c r="J20" s="30"/>
     </row>
     <row r="21" spans="1:24" ht="20.25" customHeight="1">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="30" t="s">
         <v>216</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="C21" s="30">
         <v>2025</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>325</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>173</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="E21" s="30"/>
       <c r="F21" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="G21" s="30"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="30" t="s">
-        <v>324</v>
+        <v>223</v>
+      </c>
+      <c r="G21" s="45"/>
+      <c r="H21" s="47" t="s">
+        <v>305</v>
+      </c>
+      <c r="I21" s="22" t="s">
+        <v>270</v>
       </c>
       <c r="J21" s="30"/>
     </row>
@@ -32640,52 +32655,68 @@
         <v>216</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C22" s="30">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="E22" s="30"/>
+        <v>247</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>173</v>
+      </c>
       <c r="F22" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="G22" s="45"/>
-      <c r="H22" s="47" t="s">
-        <v>305</v>
-      </c>
-      <c r="I22" s="22" t="s">
-        <v>270</v>
+        <v>244</v>
+      </c>
+      <c r="G22" s="30"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="52" t="s">
+        <v>326</v>
       </c>
       <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
     </row>
     <row r="23" spans="1:24" ht="20.25" customHeight="1">
       <c r="A23" s="30" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="C23" s="30">
-        <v>2026</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>247</v>
+        <v>2023</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>276</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>244</v>
+        <v>280</v>
+      </c>
+      <c r="F23" s="44" t="s">
+        <v>278</v>
       </c>
       <c r="G23" s="30"/>
       <c r="H23" s="47"/>
-      <c r="I23" s="52" t="s">
-        <v>326</v>
-      </c>
-      <c r="J23" s="30"/>
+      <c r="I23" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="J23" s="30" t="s">
+        <v>279</v>
+      </c>
       <c r="K23" s="30"/>
       <c r="L23" s="30"/>
       <c r="M23" s="30"/>
@@ -32703,64 +32734,50 @@
     </row>
     <row r="24" spans="1:24" ht="20.25" customHeight="1">
       <c r="A24" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>249</v>
+        <v>216</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>307</v>
       </c>
       <c r="C24" s="30">
         <v>2026</v>
       </c>
-      <c r="D24" s="30" t="s">
-        <v>250</v>
+      <c r="D24" s="38" t="s">
+        <v>180</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="F24" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="G24" s="30"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="F24" s="39" t="s">
+        <v>299</v>
+      </c>
+      <c r="I24"/>
+      <c r="J24" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
     </row>
     <row r="25" spans="1:24" ht="20.25" customHeight="1">
       <c r="A25" s="30" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="C25" s="30">
         <v>2026</v>
       </c>
-      <c r="D25" s="30" t="s">
-        <v>335</v>
+      <c r="D25" s="50" t="s">
+        <v>310</v>
       </c>
       <c r="E25" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="F25" s="30"/>
+      <c r="F25" s="44" t="s">
+        <v>327</v>
+      </c>
       <c r="G25" s="30"/>
       <c r="H25" s="47"/>
-      <c r="I25" s="30"/>
+      <c r="I25" s="22"/>
       <c r="J25" s="30"/>
       <c r="K25" s="30"/>
       <c r="L25" s="30"/>
@@ -32782,27 +32799,25 @@
         <v>97</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="C26" s="30">
-        <v>2023</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>276</v>
+        <v>2026</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>250</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="F26" s="44" t="s">
-        <v>278</v>
+        <v>158</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>285</v>
       </c>
       <c r="G26" s="30"/>
       <c r="H26" s="47"/>
-      <c r="I26" s="22" t="s">
-        <v>281</v>
-      </c>
+      <c r="I26" s="30"/>
       <c r="J26" s="30" t="s">
-        <v>279</v>
+        <v>103</v>
       </c>
       <c r="K26" s="30"/>
       <c r="L26" s="30"/>
@@ -32824,23 +32839,21 @@
         <v>97</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="C27" s="30">
         <v>2026</v>
       </c>
-      <c r="D27" s="50" t="s">
-        <v>310</v>
+      <c r="D27" s="30" t="s">
+        <v>335</v>
       </c>
       <c r="E27" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="F27" s="44" t="s">
-        <v>327</v>
-      </c>
+      <c r="F27" s="30"/>
       <c r="G27" s="30"/>
       <c r="H27" s="47"/>
-      <c r="I27" s="22"/>
+      <c r="I27" s="30"/>
       <c r="J27" s="30"/>
       <c r="K27" s="30"/>
       <c r="L27" s="30"/>
@@ -58580,9 +58593,9 @@
       <c r="X1007" s="30"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J21" xr:uid="{00000000-0001-0000-0600-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J39">
-      <sortCondition ref="A1:A21"/>
+  <autoFilter ref="A1:J20" xr:uid="{00000000-0001-0000-0600-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J38">
+      <sortCondition ref="A1:A20"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -58590,10 +58603,10 @@
     <hyperlink ref="I10" r:id="rId1" xr:uid="{EA9A8237-32EE-4828-902C-BF843B0673D1}"/>
     <hyperlink ref="I14" r:id="rId2" xr:uid="{9FA698D4-510B-4E75-A98B-530B9A769900}"/>
     <hyperlink ref="I13" r:id="rId3" xr:uid="{34C7BA2E-AE5E-4AAE-9D97-AF6E732EB65E}"/>
-    <hyperlink ref="I22" r:id="rId4" xr:uid="{944264E1-1A29-4998-BEBB-3E83A3D5A9C7}"/>
-    <hyperlink ref="I26" r:id="rId5" xr:uid="{1E794ED6-3FDC-4A22-8E05-460A0AE97089}"/>
-    <hyperlink ref="I19" r:id="rId6" xr:uid="{FFD2CCEA-C02A-44EA-80A6-FCEF979E484D}"/>
-    <hyperlink ref="I20" r:id="rId7" xr:uid="{6066E855-F357-4FD7-B9F8-6A4FDC938CEC}"/>
+    <hyperlink ref="I21" r:id="rId4" xr:uid="{944264E1-1A29-4998-BEBB-3E83A3D5A9C7}"/>
+    <hyperlink ref="I23" r:id="rId5" xr:uid="{1E794ED6-3FDC-4A22-8E05-460A0AE97089}"/>
+    <hyperlink ref="I18" r:id="rId6" xr:uid="{FFD2CCEA-C02A-44EA-80A6-FCEF979E484D}"/>
+    <hyperlink ref="I19" r:id="rId7" xr:uid="{6066E855-F357-4FD7-B9F8-6A4FDC938CEC}"/>
     <hyperlink ref="I17" r:id="rId8" xr:uid="{EA8E42A0-62C4-4194-A23D-DC3C0A687163}"/>
     <hyperlink ref="I5" r:id="rId9" xr:uid="{55D8A3A6-A30D-4B54-9205-4040973204CE}"/>
     <hyperlink ref="I6" r:id="rId10" xr:uid="{85B44222-3F81-4FEA-8822-38623903E60E}"/>
@@ -58609,9 +58622,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4445EC-8FC5-4E63-800B-686D768A8FCC}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -58664,7 +58677,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
+    <row r="5" spans="1:5" ht="16.5">
       <c r="A5">
         <v>2026</v>
       </c>
@@ -58675,7 +58688,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.8">
+    <row r="6" spans="1:5" ht="13.5">
       <c r="A6" s="42"/>
     </row>
   </sheetData>
@@ -58691,14 +58704,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1"/>
-    <col min="5" max="5" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.7109375" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="13.2">
+    <row r="1" spans="1:21" ht="12.75">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -58735,7 +58748,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:21" ht="13.2">
+    <row r="2" spans="1:21" ht="12.75">
       <c r="A2" s="2" t="s">
         <v>122</v>
       </c>
@@ -58772,7 +58785,7 @@
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
     </row>
-    <row r="3" spans="1:21" ht="13.2">
+    <row r="3" spans="1:21" ht="12.75">
       <c r="A3" s="2" t="s">
         <v>122</v>
       </c>
@@ -58809,7 +58822,7 @@
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
     </row>
-    <row r="4" spans="1:21" ht="13.2">
+    <row r="4" spans="1:21" ht="12.75">
       <c r="A4" s="2" t="s">
         <v>122</v>
       </c>
@@ -58845,7 +58858,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
     </row>
-    <row r="5" spans="1:21" ht="13.2">
+    <row r="5" spans="1:21" ht="12.75">
       <c r="A5" s="2" t="s">
         <v>122</v>
       </c>
@@ -58882,7 +58895,7 @@
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
     </row>
-    <row r="6" spans="1:21" ht="13.8">
+    <row r="6" spans="1:21" ht="14.25">
       <c r="A6" s="2" t="s">
         <v>122</v>
       </c>
@@ -58919,7 +58932,7 @@
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
     </row>
-    <row r="7" spans="1:21" ht="13.8" thickBot="1">
+    <row r="7" spans="1:21" ht="13.5" thickBot="1">
       <c r="A7" s="2" t="s">
         <v>122</v>
       </c>
@@ -58956,7 +58969,7 @@
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
     </row>
-    <row r="8" spans="1:21" ht="13.8" thickBot="1">
+    <row r="8" spans="1:21" ht="13.5" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>122</v>
       </c>

--- a/data/CV_infolist.xlsx
+++ b/data/CV_infolist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lee\Documents\GitHub\sylcv\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sooyo\Documents\github\sylcv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C05310-94AB-4AE8-ABD6-F654A71B0802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA238B8-E062-416D-B9AF-4F5AC7327FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="0" windowWidth="14430" windowHeight="16200" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="14496" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Publication!$A$1:$J$20</definedName>
-    <definedName name="header" localSheetId="6">Publication!$D$29</definedName>
+    <definedName name="header" localSheetId="6">Publication!$D$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="355">
   <si>
     <t>Degree</t>
   </si>
@@ -1117,6 +1117,15 @@
   <si>
     <t>Validity Study for AI-generated Sample and Responses</t>
   </si>
+  <si>
+    <t>The Cultural Continuity Scale: Cross-Validated Item Response Theory Development of a Measure of Perceived Cultural Stability in a Racially and Ethnically Diverse U.S. Sample</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Cory L. Cobb, Sooyong Lee, Lawson Kami, Schwartz Seth, Eddy J. Mark, &amp; Martinez Charles</t>
+  </si>
 </sst>
 </file>
 
@@ -1708,15 +1717,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="136.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="136.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="12.75">
+    <row r="1" spans="1:5" ht="13.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1733,7 +1742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="38.25">
+    <row r="2" spans="1:5" ht="39.6">
       <c r="A2" s="26" t="s">
         <v>165</v>
       </c>
@@ -1750,7 +1759,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="13.5" thickBot="1">
+    <row r="3" spans="1:5" ht="13.8" thickBot="1">
       <c r="A3" s="24" t="s">
         <v>134</v>
       </c>
@@ -1795,9 +1804,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:P18"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="39.140625" customWidth="1"/>
+    <col min="3" max="3" width="39.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1">
@@ -2231,19 +2240,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1001"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" style="16" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.88671875" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="12.75">
+    <row r="1" spans="1:27" ht="13.2">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -2290,7 +2299,7 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:27" ht="12.75">
+    <row r="2" spans="1:27" ht="13.2">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -2335,7 +2344,7 @@
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
     </row>
-    <row r="3" spans="1:27" ht="12.75">
+    <row r="3" spans="1:27" ht="13.2">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -2380,7 +2389,7 @@
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
     </row>
-    <row r="4" spans="1:27" ht="12.75">
+    <row r="4" spans="1:27" ht="13.2">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -2468,7 +2477,7 @@
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
     </row>
-    <row r="6" spans="1:27" ht="12.75">
+    <row r="6" spans="1:27" ht="13.2">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -2511,7 +2520,7 @@
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
     </row>
-    <row r="7" spans="1:27" ht="18">
+    <row r="7" spans="1:27" ht="16.8">
       <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
@@ -2558,7 +2567,7 @@
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
     </row>
-    <row r="8" spans="1:27" ht="18">
+    <row r="8" spans="1:27" ht="16.8">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -2603,7 +2612,7 @@
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:27" ht="18">
+    <row r="9" spans="1:27" ht="16.8">
       <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
@@ -2648,7 +2657,7 @@
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
     </row>
-    <row r="10" spans="1:27" ht="12.75">
+    <row r="10" spans="1:27" ht="13.2">
       <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
@@ -2691,7 +2700,7 @@
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="1:27" ht="12.75">
+    <row r="11" spans="1:27" ht="13.2">
       <c r="A11" s="21" t="s">
         <v>40</v>
       </c>
@@ -2732,7 +2741,7 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" ht="15.6">
       <c r="A12" s="21" t="s">
         <v>19</v>
       </c>
@@ -2773,7 +2782,7 @@
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" ht="15.6">
       <c r="A13" s="21" t="s">
         <v>40</v>
       </c>
@@ -2814,7 +2823,7 @@
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
     </row>
-    <row r="14" spans="1:27" ht="12.75">
+    <row r="14" spans="1:27" ht="13.2">
       <c r="A14" s="21" t="s">
         <v>40</v>
       </c>
@@ -2857,7 +2866,7 @@
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
     </row>
-    <row r="15" spans="1:27" ht="12.75">
+    <row r="15" spans="1:27" ht="13.2">
       <c r="A15" s="21" t="s">
         <v>40</v>
       </c>
@@ -2900,7 +2909,7 @@
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
     </row>
-    <row r="16" spans="1:27" ht="12.75">
+    <row r="16" spans="1:27" ht="13.2">
       <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
@@ -2943,7 +2952,7 @@
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="1:27" ht="12.75">
+    <row r="17" spans="1:27" ht="13.2">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -2986,7 +2995,7 @@
       <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
     </row>
-    <row r="18" spans="1:27" ht="12.75">
+    <row r="18" spans="1:27" ht="13.2">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -3029,7 +3038,7 @@
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
     </row>
-    <row r="19" spans="1:27" ht="12.75">
+    <row r="19" spans="1:27" ht="13.2">
       <c r="A19" s="2" t="s">
         <v>40</v>
       </c>
@@ -3072,7 +3081,7 @@
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" spans="1:27" ht="12.75">
+    <row r="20" spans="1:27" ht="13.2">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -3115,7 +3124,7 @@
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" spans="1:27" ht="12.75">
+    <row r="21" spans="1:27" ht="13.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="14"/>
@@ -3144,7 +3153,7 @@
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
     </row>
-    <row r="22" spans="1:27" ht="12.75">
+    <row r="22" spans="1:27" ht="13.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="14"/>
@@ -3173,7 +3182,7 @@
       <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="1:27" ht="12.75">
+    <row r="23" spans="1:27" ht="13.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="14"/>
@@ -3202,7 +3211,7 @@
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
     </row>
-    <row r="24" spans="1:27" ht="12.75">
+    <row r="24" spans="1:27" ht="13.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="14"/>
@@ -3231,7 +3240,7 @@
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" spans="1:27" ht="12.75">
+    <row r="25" spans="1:27" ht="13.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="14"/>
@@ -3260,7 +3269,7 @@
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
     </row>
-    <row r="26" spans="1:27" ht="12.75">
+    <row r="26" spans="1:27" ht="13.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="14"/>
@@ -3289,7 +3298,7 @@
       <c r="Z26" s="2"/>
       <c r="AA26" s="2"/>
     </row>
-    <row r="27" spans="1:27" ht="12.75">
+    <row r="27" spans="1:27" ht="13.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="14"/>
@@ -3318,7 +3327,7 @@
       <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
     </row>
-    <row r="28" spans="1:27" ht="12.75">
+    <row r="28" spans="1:27" ht="13.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="14"/>
@@ -3347,7 +3356,7 @@
       <c r="Z28" s="2"/>
       <c r="AA28" s="2"/>
     </row>
-    <row r="29" spans="1:27" ht="12.75">
+    <row r="29" spans="1:27" ht="13.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="14"/>
@@ -3376,7 +3385,7 @@
       <c r="Z29" s="2"/>
       <c r="AA29" s="2"/>
     </row>
-    <row r="30" spans="1:27" ht="12.75">
+    <row r="30" spans="1:27" ht="13.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="14"/>
@@ -3405,7 +3414,7 @@
       <c r="Z30" s="2"/>
       <c r="AA30" s="2"/>
     </row>
-    <row r="31" spans="1:27" ht="12.75">
+    <row r="31" spans="1:27" ht="13.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="14"/>
@@ -3434,7 +3443,7 @@
       <c r="Z31" s="2"/>
       <c r="AA31" s="2"/>
     </row>
-    <row r="32" spans="1:27" ht="12.75">
+    <row r="32" spans="1:27" ht="13.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="14"/>
@@ -3463,7 +3472,7 @@
       <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
     </row>
-    <row r="33" spans="1:27" ht="12.75">
+    <row r="33" spans="1:27" ht="13.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="14"/>
@@ -3492,7 +3501,7 @@
       <c r="Z33" s="2"/>
       <c r="AA33" s="2"/>
     </row>
-    <row r="34" spans="1:27" ht="12.75">
+    <row r="34" spans="1:27" ht="13.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="14"/>
@@ -3521,7 +3530,7 @@
       <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
     </row>
-    <row r="35" spans="1:27" ht="12.75">
+    <row r="35" spans="1:27" ht="13.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="14"/>
@@ -3550,7 +3559,7 @@
       <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
     </row>
-    <row r="36" spans="1:27" ht="12.75">
+    <row r="36" spans="1:27" ht="13.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="14"/>
@@ -3579,7 +3588,7 @@
       <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
     </row>
-    <row r="37" spans="1:27" ht="12.75">
+    <row r="37" spans="1:27" ht="13.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="14"/>
@@ -3608,7 +3617,7 @@
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
     </row>
-    <row r="38" spans="1:27" ht="12.75">
+    <row r="38" spans="1:27" ht="13.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="14"/>
@@ -3637,7 +3646,7 @@
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
     </row>
-    <row r="39" spans="1:27" ht="12.75">
+    <row r="39" spans="1:27" ht="13.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="14"/>
@@ -3666,7 +3675,7 @@
       <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
     </row>
-    <row r="40" spans="1:27" ht="12.75">
+    <row r="40" spans="1:27" ht="13.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="14"/>
@@ -3695,7 +3704,7 @@
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
     </row>
-    <row r="41" spans="1:27" ht="12.75">
+    <row r="41" spans="1:27" ht="13.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="14"/>
@@ -3724,7 +3733,7 @@
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="1:27" ht="12.75">
+    <row r="42" spans="1:27" ht="13.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="14"/>
@@ -3753,7 +3762,7 @@
       <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
     </row>
-    <row r="43" spans="1:27" ht="12.75">
+    <row r="43" spans="1:27" ht="13.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="14"/>
@@ -3782,7 +3791,7 @@
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
     </row>
-    <row r="44" spans="1:27" ht="12.75">
+    <row r="44" spans="1:27" ht="13.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="14"/>
@@ -3811,7 +3820,7 @@
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
     </row>
-    <row r="45" spans="1:27" ht="12.75">
+    <row r="45" spans="1:27" ht="13.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="14"/>
@@ -3840,7 +3849,7 @@
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="1:27" ht="12.75">
+    <row r="46" spans="1:27" ht="13.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="14"/>
@@ -3869,7 +3878,7 @@
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
     </row>
-    <row r="47" spans="1:27" ht="12.75">
+    <row r="47" spans="1:27" ht="13.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="14"/>
@@ -3898,7 +3907,7 @@
       <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
     </row>
-    <row r="48" spans="1:27" ht="12.75">
+    <row r="48" spans="1:27" ht="13.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="14"/>
@@ -3927,7 +3936,7 @@
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
     </row>
-    <row r="49" spans="1:27" ht="12.75">
+    <row r="49" spans="1:27" ht="13.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="14"/>
@@ -3956,7 +3965,7 @@
       <c r="Z49" s="2"/>
       <c r="AA49" s="2"/>
     </row>
-    <row r="50" spans="1:27" ht="12.75">
+    <row r="50" spans="1:27" ht="13.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="14"/>
@@ -3985,7 +3994,7 @@
       <c r="Z50" s="2"/>
       <c r="AA50" s="2"/>
     </row>
-    <row r="51" spans="1:27" ht="12.75">
+    <row r="51" spans="1:27" ht="13.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="14"/>
@@ -4014,7 +4023,7 @@
       <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
     </row>
-    <row r="52" spans="1:27" ht="12.75">
+    <row r="52" spans="1:27" ht="13.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="14"/>
@@ -4043,7 +4052,7 @@
       <c r="Z52" s="2"/>
       <c r="AA52" s="2"/>
     </row>
-    <row r="53" spans="1:27" ht="12.75">
+    <row r="53" spans="1:27" ht="13.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="14"/>
@@ -4072,7 +4081,7 @@
       <c r="Z53" s="2"/>
       <c r="AA53" s="2"/>
     </row>
-    <row r="54" spans="1:27" ht="12.75">
+    <row r="54" spans="1:27" ht="13.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="14"/>
@@ -4101,7 +4110,7 @@
       <c r="Z54" s="2"/>
       <c r="AA54" s="2"/>
     </row>
-    <row r="55" spans="1:27" ht="12.75">
+    <row r="55" spans="1:27" ht="13.2">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="14"/>
@@ -4130,7 +4139,7 @@
       <c r="Z55" s="2"/>
       <c r="AA55" s="2"/>
     </row>
-    <row r="56" spans="1:27" ht="12.75">
+    <row r="56" spans="1:27" ht="13.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="14"/>
@@ -4159,7 +4168,7 @@
       <c r="Z56" s="2"/>
       <c r="AA56" s="2"/>
     </row>
-    <row r="57" spans="1:27" ht="12.75">
+    <row r="57" spans="1:27" ht="13.2">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="14"/>
@@ -4188,7 +4197,7 @@
       <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
     </row>
-    <row r="58" spans="1:27" ht="12.75">
+    <row r="58" spans="1:27" ht="13.2">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="14"/>
@@ -4217,7 +4226,7 @@
       <c r="Z58" s="2"/>
       <c r="AA58" s="2"/>
     </row>
-    <row r="59" spans="1:27" ht="12.75">
+    <row r="59" spans="1:27" ht="13.2">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="14"/>
@@ -4246,7 +4255,7 @@
       <c r="Z59" s="2"/>
       <c r="AA59" s="2"/>
     </row>
-    <row r="60" spans="1:27" ht="12.75">
+    <row r="60" spans="1:27" ht="13.2">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="14"/>
@@ -4275,7 +4284,7 @@
       <c r="Z60" s="2"/>
       <c r="AA60" s="2"/>
     </row>
-    <row r="61" spans="1:27" ht="12.75">
+    <row r="61" spans="1:27" ht="13.2">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="14"/>
@@ -4304,7 +4313,7 @@
       <c r="Z61" s="2"/>
       <c r="AA61" s="2"/>
     </row>
-    <row r="62" spans="1:27" ht="12.75">
+    <row r="62" spans="1:27" ht="13.2">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="14"/>
@@ -4333,7 +4342,7 @@
       <c r="Z62" s="2"/>
       <c r="AA62" s="2"/>
     </row>
-    <row r="63" spans="1:27" ht="12.75">
+    <row r="63" spans="1:27" ht="13.2">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="14"/>
@@ -4362,7 +4371,7 @@
       <c r="Z63" s="2"/>
       <c r="AA63" s="2"/>
     </row>
-    <row r="64" spans="1:27" ht="12.75">
+    <row r="64" spans="1:27" ht="13.2">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="14"/>
@@ -4391,7 +4400,7 @@
       <c r="Z64" s="2"/>
       <c r="AA64" s="2"/>
     </row>
-    <row r="65" spans="1:27" ht="12.75">
+    <row r="65" spans="1:27" ht="13.2">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="14"/>
@@ -4420,7 +4429,7 @@
       <c r="Z65" s="2"/>
       <c r="AA65" s="2"/>
     </row>
-    <row r="66" spans="1:27" ht="12.75">
+    <row r="66" spans="1:27" ht="13.2">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="14"/>
@@ -4449,7 +4458,7 @@
       <c r="Z66" s="2"/>
       <c r="AA66" s="2"/>
     </row>
-    <row r="67" spans="1:27" ht="12.75">
+    <row r="67" spans="1:27" ht="13.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="14"/>
@@ -4478,7 +4487,7 @@
       <c r="Z67" s="2"/>
       <c r="AA67" s="2"/>
     </row>
-    <row r="68" spans="1:27" ht="12.75">
+    <row r="68" spans="1:27" ht="13.2">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="14"/>
@@ -4507,7 +4516,7 @@
       <c r="Z68" s="2"/>
       <c r="AA68" s="2"/>
     </row>
-    <row r="69" spans="1:27" ht="12.75">
+    <row r="69" spans="1:27" ht="13.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="14"/>
@@ -4536,7 +4545,7 @@
       <c r="Z69" s="2"/>
       <c r="AA69" s="2"/>
     </row>
-    <row r="70" spans="1:27" ht="12.75">
+    <row r="70" spans="1:27" ht="13.2">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="14"/>
@@ -4565,7 +4574,7 @@
       <c r="Z70" s="2"/>
       <c r="AA70" s="2"/>
     </row>
-    <row r="71" spans="1:27" ht="12.75">
+    <row r="71" spans="1:27" ht="13.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="14"/>
@@ -4594,7 +4603,7 @@
       <c r="Z71" s="2"/>
       <c r="AA71" s="2"/>
     </row>
-    <row r="72" spans="1:27" ht="12.75">
+    <row r="72" spans="1:27" ht="13.2">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="14"/>
@@ -4623,7 +4632,7 @@
       <c r="Z72" s="2"/>
       <c r="AA72" s="2"/>
     </row>
-    <row r="73" spans="1:27" ht="12.75">
+    <row r="73" spans="1:27" ht="13.2">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="14"/>
@@ -4652,7 +4661,7 @@
       <c r="Z73" s="2"/>
       <c r="AA73" s="2"/>
     </row>
-    <row r="74" spans="1:27" ht="12.75">
+    <row r="74" spans="1:27" ht="13.2">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="14"/>
@@ -4681,7 +4690,7 @@
       <c r="Z74" s="2"/>
       <c r="AA74" s="2"/>
     </row>
-    <row r="75" spans="1:27" ht="12.75">
+    <row r="75" spans="1:27" ht="13.2">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="14"/>
@@ -4710,7 +4719,7 @@
       <c r="Z75" s="2"/>
       <c r="AA75" s="2"/>
     </row>
-    <row r="76" spans="1:27" ht="12.75">
+    <row r="76" spans="1:27" ht="13.2">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="14"/>
@@ -4739,7 +4748,7 @@
       <c r="Z76" s="2"/>
       <c r="AA76" s="2"/>
     </row>
-    <row r="77" spans="1:27" ht="12.75">
+    <row r="77" spans="1:27" ht="13.2">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="14"/>
@@ -4768,7 +4777,7 @@
       <c r="Z77" s="2"/>
       <c r="AA77" s="2"/>
     </row>
-    <row r="78" spans="1:27" ht="12.75">
+    <row r="78" spans="1:27" ht="13.2">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="14"/>
@@ -4797,7 +4806,7 @@
       <c r="Z78" s="2"/>
       <c r="AA78" s="2"/>
     </row>
-    <row r="79" spans="1:27" ht="12.75">
+    <row r="79" spans="1:27" ht="13.2">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="14"/>
@@ -4826,7 +4835,7 @@
       <c r="Z79" s="2"/>
       <c r="AA79" s="2"/>
     </row>
-    <row r="80" spans="1:27" ht="12.75">
+    <row r="80" spans="1:27" ht="13.2">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="14"/>
@@ -4855,7 +4864,7 @@
       <c r="Z80" s="2"/>
       <c r="AA80" s="2"/>
     </row>
-    <row r="81" spans="1:27" ht="12.75">
+    <row r="81" spans="1:27" ht="13.2">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="14"/>
@@ -4884,7 +4893,7 @@
       <c r="Z81" s="2"/>
       <c r="AA81" s="2"/>
     </row>
-    <row r="82" spans="1:27" ht="12.75">
+    <row r="82" spans="1:27" ht="13.2">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="14"/>
@@ -4913,7 +4922,7 @@
       <c r="Z82" s="2"/>
       <c r="AA82" s="2"/>
     </row>
-    <row r="83" spans="1:27" ht="12.75">
+    <row r="83" spans="1:27" ht="13.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="14"/>
@@ -4942,7 +4951,7 @@
       <c r="Z83" s="2"/>
       <c r="AA83" s="2"/>
     </row>
-    <row r="84" spans="1:27" ht="12.75">
+    <row r="84" spans="1:27" ht="13.2">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="14"/>
@@ -4971,7 +4980,7 @@
       <c r="Z84" s="2"/>
       <c r="AA84" s="2"/>
     </row>
-    <row r="85" spans="1:27" ht="12.75">
+    <row r="85" spans="1:27" ht="13.2">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="14"/>
@@ -5000,7 +5009,7 @@
       <c r="Z85" s="2"/>
       <c r="AA85" s="2"/>
     </row>
-    <row r="86" spans="1:27" ht="12.75">
+    <row r="86" spans="1:27" ht="13.2">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="14"/>
@@ -5029,7 +5038,7 @@
       <c r="Z86" s="2"/>
       <c r="AA86" s="2"/>
     </row>
-    <row r="87" spans="1:27" ht="12.75">
+    <row r="87" spans="1:27" ht="13.2">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="14"/>
@@ -5058,7 +5067,7 @@
       <c r="Z87" s="2"/>
       <c r="AA87" s="2"/>
     </row>
-    <row r="88" spans="1:27" ht="12.75">
+    <row r="88" spans="1:27" ht="13.2">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="14"/>
@@ -5087,7 +5096,7 @@
       <c r="Z88" s="2"/>
       <c r="AA88" s="2"/>
     </row>
-    <row r="89" spans="1:27" ht="12.75">
+    <row r="89" spans="1:27" ht="13.2">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="14"/>
@@ -5116,7 +5125,7 @@
       <c r="Z89" s="2"/>
       <c r="AA89" s="2"/>
     </row>
-    <row r="90" spans="1:27" ht="12.75">
+    <row r="90" spans="1:27" ht="13.2">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="14"/>
@@ -5145,7 +5154,7 @@
       <c r="Z90" s="2"/>
       <c r="AA90" s="2"/>
     </row>
-    <row r="91" spans="1:27" ht="12.75">
+    <row r="91" spans="1:27" ht="13.2">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="14"/>
@@ -5174,7 +5183,7 @@
       <c r="Z91" s="2"/>
       <c r="AA91" s="2"/>
     </row>
-    <row r="92" spans="1:27" ht="12.75">
+    <row r="92" spans="1:27" ht="13.2">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="14"/>
@@ -5203,7 +5212,7 @@
       <c r="Z92" s="2"/>
       <c r="AA92" s="2"/>
     </row>
-    <row r="93" spans="1:27" ht="12.75">
+    <row r="93" spans="1:27" ht="13.2">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="14"/>
@@ -5232,7 +5241,7 @@
       <c r="Z93" s="2"/>
       <c r="AA93" s="2"/>
     </row>
-    <row r="94" spans="1:27" ht="12.75">
+    <row r="94" spans="1:27" ht="13.2">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="14"/>
@@ -5261,7 +5270,7 @@
       <c r="Z94" s="2"/>
       <c r="AA94" s="2"/>
     </row>
-    <row r="95" spans="1:27" ht="12.75">
+    <row r="95" spans="1:27" ht="13.2">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="14"/>
@@ -5290,7 +5299,7 @@
       <c r="Z95" s="2"/>
       <c r="AA95" s="2"/>
     </row>
-    <row r="96" spans="1:27" ht="12.75">
+    <row r="96" spans="1:27" ht="13.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="14"/>
@@ -5319,7 +5328,7 @@
       <c r="Z96" s="2"/>
       <c r="AA96" s="2"/>
     </row>
-    <row r="97" spans="1:27" ht="12.75">
+    <row r="97" spans="1:27" ht="13.2">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="14"/>
@@ -5348,7 +5357,7 @@
       <c r="Z97" s="2"/>
       <c r="AA97" s="2"/>
     </row>
-    <row r="98" spans="1:27" ht="12.75">
+    <row r="98" spans="1:27" ht="13.2">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="14"/>
@@ -5377,7 +5386,7 @@
       <c r="Z98" s="2"/>
       <c r="AA98" s="2"/>
     </row>
-    <row r="99" spans="1:27" ht="12.75">
+    <row r="99" spans="1:27" ht="13.2">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="14"/>
@@ -5406,7 +5415,7 @@
       <c r="Z99" s="2"/>
       <c r="AA99" s="2"/>
     </row>
-    <row r="100" spans="1:27" ht="12.75">
+    <row r="100" spans="1:27" ht="13.2">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="14"/>
@@ -5435,7 +5444,7 @@
       <c r="Z100" s="2"/>
       <c r="AA100" s="2"/>
     </row>
-    <row r="101" spans="1:27" ht="12.75">
+    <row r="101" spans="1:27" ht="13.2">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="14"/>
@@ -5464,7 +5473,7 @@
       <c r="Z101" s="2"/>
       <c r="AA101" s="2"/>
     </row>
-    <row r="102" spans="1:27" ht="12.75">
+    <row r="102" spans="1:27" ht="13.2">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="14"/>
@@ -5493,7 +5502,7 @@
       <c r="Z102" s="2"/>
       <c r="AA102" s="2"/>
     </row>
-    <row r="103" spans="1:27" ht="12.75">
+    <row r="103" spans="1:27" ht="13.2">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="14"/>
@@ -5522,7 +5531,7 @@
       <c r="Z103" s="2"/>
       <c r="AA103" s="2"/>
     </row>
-    <row r="104" spans="1:27" ht="12.75">
+    <row r="104" spans="1:27" ht="13.2">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="14"/>
@@ -5551,7 +5560,7 @@
       <c r="Z104" s="2"/>
       <c r="AA104" s="2"/>
     </row>
-    <row r="105" spans="1:27" ht="12.75">
+    <row r="105" spans="1:27" ht="13.2">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="14"/>
@@ -5580,7 +5589,7 @@
       <c r="Z105" s="2"/>
       <c r="AA105" s="2"/>
     </row>
-    <row r="106" spans="1:27" ht="12.75">
+    <row r="106" spans="1:27" ht="13.2">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="14"/>
@@ -5609,7 +5618,7 @@
       <c r="Z106" s="2"/>
       <c r="AA106" s="2"/>
     </row>
-    <row r="107" spans="1:27" ht="12.75">
+    <row r="107" spans="1:27" ht="13.2">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="14"/>
@@ -5638,7 +5647,7 @@
       <c r="Z107" s="2"/>
       <c r="AA107" s="2"/>
     </row>
-    <row r="108" spans="1:27" ht="12.75">
+    <row r="108" spans="1:27" ht="13.2">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="14"/>
@@ -5667,7 +5676,7 @@
       <c r="Z108" s="2"/>
       <c r="AA108" s="2"/>
     </row>
-    <row r="109" spans="1:27" ht="12.75">
+    <row r="109" spans="1:27" ht="13.2">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="14"/>
@@ -5696,7 +5705,7 @@
       <c r="Z109" s="2"/>
       <c r="AA109" s="2"/>
     </row>
-    <row r="110" spans="1:27" ht="12.75">
+    <row r="110" spans="1:27" ht="13.2">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="14"/>
@@ -5725,7 +5734,7 @@
       <c r="Z110" s="2"/>
       <c r="AA110" s="2"/>
     </row>
-    <row r="111" spans="1:27" ht="12.75">
+    <row r="111" spans="1:27" ht="13.2">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="14"/>
@@ -5754,7 +5763,7 @@
       <c r="Z111" s="2"/>
       <c r="AA111" s="2"/>
     </row>
-    <row r="112" spans="1:27" ht="12.75">
+    <row r="112" spans="1:27" ht="13.2">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="14"/>
@@ -5783,7 +5792,7 @@
       <c r="Z112" s="2"/>
       <c r="AA112" s="2"/>
     </row>
-    <row r="113" spans="1:27" ht="12.75">
+    <row r="113" spans="1:27" ht="13.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="14"/>
@@ -5812,7 +5821,7 @@
       <c r="Z113" s="2"/>
       <c r="AA113" s="2"/>
     </row>
-    <row r="114" spans="1:27" ht="12.75">
+    <row r="114" spans="1:27" ht="13.2">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="14"/>
@@ -5841,7 +5850,7 @@
       <c r="Z114" s="2"/>
       <c r="AA114" s="2"/>
     </row>
-    <row r="115" spans="1:27" ht="12.75">
+    <row r="115" spans="1:27" ht="13.2">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="14"/>
@@ -5870,7 +5879,7 @@
       <c r="Z115" s="2"/>
       <c r="AA115" s="2"/>
     </row>
-    <row r="116" spans="1:27" ht="12.75">
+    <row r="116" spans="1:27" ht="13.2">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="14"/>
@@ -5899,7 +5908,7 @@
       <c r="Z116" s="2"/>
       <c r="AA116" s="2"/>
     </row>
-    <row r="117" spans="1:27" ht="12.75">
+    <row r="117" spans="1:27" ht="13.2">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="14"/>
@@ -5928,7 +5937,7 @@
       <c r="Z117" s="2"/>
       <c r="AA117" s="2"/>
     </row>
-    <row r="118" spans="1:27" ht="12.75">
+    <row r="118" spans="1:27" ht="13.2">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="14"/>
@@ -5957,7 +5966,7 @@
       <c r="Z118" s="2"/>
       <c r="AA118" s="2"/>
     </row>
-    <row r="119" spans="1:27" ht="12.75">
+    <row r="119" spans="1:27" ht="13.2">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="14"/>
@@ -5986,7 +5995,7 @@
       <c r="Z119" s="2"/>
       <c r="AA119" s="2"/>
     </row>
-    <row r="120" spans="1:27" ht="12.75">
+    <row r="120" spans="1:27" ht="13.2">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="14"/>
@@ -6015,7 +6024,7 @@
       <c r="Z120" s="2"/>
       <c r="AA120" s="2"/>
     </row>
-    <row r="121" spans="1:27" ht="12.75">
+    <row r="121" spans="1:27" ht="13.2">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="14"/>
@@ -6044,7 +6053,7 @@
       <c r="Z121" s="2"/>
       <c r="AA121" s="2"/>
     </row>
-    <row r="122" spans="1:27" ht="12.75">
+    <row r="122" spans="1:27" ht="13.2">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="14"/>
@@ -6073,7 +6082,7 @@
       <c r="Z122" s="2"/>
       <c r="AA122" s="2"/>
     </row>
-    <row r="123" spans="1:27" ht="12.75">
+    <row r="123" spans="1:27" ht="13.2">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="14"/>
@@ -6102,7 +6111,7 @@
       <c r="Z123" s="2"/>
       <c r="AA123" s="2"/>
     </row>
-    <row r="124" spans="1:27" ht="12.75">
+    <row r="124" spans="1:27" ht="13.2">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="14"/>
@@ -6131,7 +6140,7 @@
       <c r="Z124" s="2"/>
       <c r="AA124" s="2"/>
     </row>
-    <row r="125" spans="1:27" ht="12.75">
+    <row r="125" spans="1:27" ht="13.2">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="14"/>
@@ -6160,7 +6169,7 @@
       <c r="Z125" s="2"/>
       <c r="AA125" s="2"/>
     </row>
-    <row r="126" spans="1:27" ht="12.75">
+    <row r="126" spans="1:27" ht="13.2">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="14"/>
@@ -6189,7 +6198,7 @@
       <c r="Z126" s="2"/>
       <c r="AA126" s="2"/>
     </row>
-    <row r="127" spans="1:27" ht="12.75">
+    <row r="127" spans="1:27" ht="13.2">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="14"/>
@@ -6218,7 +6227,7 @@
       <c r="Z127" s="2"/>
       <c r="AA127" s="2"/>
     </row>
-    <row r="128" spans="1:27" ht="12.75">
+    <row r="128" spans="1:27" ht="13.2">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="14"/>
@@ -6247,7 +6256,7 @@
       <c r="Z128" s="2"/>
       <c r="AA128" s="2"/>
     </row>
-    <row r="129" spans="1:27" ht="12.75">
+    <row r="129" spans="1:27" ht="13.2">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="14"/>
@@ -6276,7 +6285,7 @@
       <c r="Z129" s="2"/>
       <c r="AA129" s="2"/>
     </row>
-    <row r="130" spans="1:27" ht="12.75">
+    <row r="130" spans="1:27" ht="13.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="14"/>
@@ -6305,7 +6314,7 @@
       <c r="Z130" s="2"/>
       <c r="AA130" s="2"/>
     </row>
-    <row r="131" spans="1:27" ht="12.75">
+    <row r="131" spans="1:27" ht="13.2">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="14"/>
@@ -6334,7 +6343,7 @@
       <c r="Z131" s="2"/>
       <c r="AA131" s="2"/>
     </row>
-    <row r="132" spans="1:27" ht="12.75">
+    <row r="132" spans="1:27" ht="13.2">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="14"/>
@@ -6363,7 +6372,7 @@
       <c r="Z132" s="2"/>
       <c r="AA132" s="2"/>
     </row>
-    <row r="133" spans="1:27" ht="12.75">
+    <row r="133" spans="1:27" ht="13.2">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="14"/>
@@ -6392,7 +6401,7 @@
       <c r="Z133" s="2"/>
       <c r="AA133" s="2"/>
     </row>
-    <row r="134" spans="1:27" ht="12.75">
+    <row r="134" spans="1:27" ht="13.2">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="14"/>
@@ -6421,7 +6430,7 @@
       <c r="Z134" s="2"/>
       <c r="AA134" s="2"/>
     </row>
-    <row r="135" spans="1:27" ht="12.75">
+    <row r="135" spans="1:27" ht="13.2">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="14"/>
@@ -6450,7 +6459,7 @@
       <c r="Z135" s="2"/>
       <c r="AA135" s="2"/>
     </row>
-    <row r="136" spans="1:27" ht="12.75">
+    <row r="136" spans="1:27" ht="13.2">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="14"/>
@@ -6479,7 +6488,7 @@
       <c r="Z136" s="2"/>
       <c r="AA136" s="2"/>
     </row>
-    <row r="137" spans="1:27" ht="12.75">
+    <row r="137" spans="1:27" ht="13.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="14"/>
@@ -6508,7 +6517,7 @@
       <c r="Z137" s="2"/>
       <c r="AA137" s="2"/>
     </row>
-    <row r="138" spans="1:27" ht="12.75">
+    <row r="138" spans="1:27" ht="13.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="14"/>
@@ -6537,7 +6546,7 @@
       <c r="Z138" s="2"/>
       <c r="AA138" s="2"/>
     </row>
-    <row r="139" spans="1:27" ht="12.75">
+    <row r="139" spans="1:27" ht="13.2">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="14"/>
@@ -6566,7 +6575,7 @@
       <c r="Z139" s="2"/>
       <c r="AA139" s="2"/>
     </row>
-    <row r="140" spans="1:27" ht="12.75">
+    <row r="140" spans="1:27" ht="13.2">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="14"/>
@@ -6595,7 +6604,7 @@
       <c r="Z140" s="2"/>
       <c r="AA140" s="2"/>
     </row>
-    <row r="141" spans="1:27" ht="12.75">
+    <row r="141" spans="1:27" ht="13.2">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="14"/>
@@ -6624,7 +6633,7 @@
       <c r="Z141" s="2"/>
       <c r="AA141" s="2"/>
     </row>
-    <row r="142" spans="1:27" ht="12.75">
+    <row r="142" spans="1:27" ht="13.2">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="14"/>
@@ -6653,7 +6662,7 @@
       <c r="Z142" s="2"/>
       <c r="AA142" s="2"/>
     </row>
-    <row r="143" spans="1:27" ht="12.75">
+    <row r="143" spans="1:27" ht="13.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="14"/>
@@ -6682,7 +6691,7 @@
       <c r="Z143" s="2"/>
       <c r="AA143" s="2"/>
     </row>
-    <row r="144" spans="1:27" ht="12.75">
+    <row r="144" spans="1:27" ht="13.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="14"/>
@@ -6711,7 +6720,7 @@
       <c r="Z144" s="2"/>
       <c r="AA144" s="2"/>
     </row>
-    <row r="145" spans="1:27" ht="12.75">
+    <row r="145" spans="1:27" ht="13.2">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="14"/>
@@ -6740,7 +6749,7 @@
       <c r="Z145" s="2"/>
       <c r="AA145" s="2"/>
     </row>
-    <row r="146" spans="1:27" ht="12.75">
+    <row r="146" spans="1:27" ht="13.2">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="14"/>
@@ -6769,7 +6778,7 @@
       <c r="Z146" s="2"/>
       <c r="AA146" s="2"/>
     </row>
-    <row r="147" spans="1:27" ht="12.75">
+    <row r="147" spans="1:27" ht="13.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="14"/>
@@ -6798,7 +6807,7 @@
       <c r="Z147" s="2"/>
       <c r="AA147" s="2"/>
     </row>
-    <row r="148" spans="1:27" ht="12.75">
+    <row r="148" spans="1:27" ht="13.2">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="14"/>
@@ -6827,7 +6836,7 @@
       <c r="Z148" s="2"/>
       <c r="AA148" s="2"/>
     </row>
-    <row r="149" spans="1:27" ht="12.75">
+    <row r="149" spans="1:27" ht="13.2">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="14"/>
@@ -6856,7 +6865,7 @@
       <c r="Z149" s="2"/>
       <c r="AA149" s="2"/>
     </row>
-    <row r="150" spans="1:27" ht="12.75">
+    <row r="150" spans="1:27" ht="13.2">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="14"/>
@@ -6885,7 +6894,7 @@
       <c r="Z150" s="2"/>
       <c r="AA150" s="2"/>
     </row>
-    <row r="151" spans="1:27" ht="12.75">
+    <row r="151" spans="1:27" ht="13.2">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="14"/>
@@ -6914,7 +6923,7 @@
       <c r="Z151" s="2"/>
       <c r="AA151" s="2"/>
     </row>
-    <row r="152" spans="1:27" ht="12.75">
+    <row r="152" spans="1:27" ht="13.2">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="14"/>
@@ -6943,7 +6952,7 @@
       <c r="Z152" s="2"/>
       <c r="AA152" s="2"/>
     </row>
-    <row r="153" spans="1:27" ht="12.75">
+    <row r="153" spans="1:27" ht="13.2">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="14"/>
@@ -6972,7 +6981,7 @@
       <c r="Z153" s="2"/>
       <c r="AA153" s="2"/>
     </row>
-    <row r="154" spans="1:27" ht="12.75">
+    <row r="154" spans="1:27" ht="13.2">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="14"/>
@@ -7001,7 +7010,7 @@
       <c r="Z154" s="2"/>
       <c r="AA154" s="2"/>
     </row>
-    <row r="155" spans="1:27" ht="12.75">
+    <row r="155" spans="1:27" ht="13.2">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="14"/>
@@ -7030,7 +7039,7 @@
       <c r="Z155" s="2"/>
       <c r="AA155" s="2"/>
     </row>
-    <row r="156" spans="1:27" ht="12.75">
+    <row r="156" spans="1:27" ht="13.2">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="14"/>
@@ -7059,7 +7068,7 @@
       <c r="Z156" s="2"/>
       <c r="AA156" s="2"/>
     </row>
-    <row r="157" spans="1:27" ht="12.75">
+    <row r="157" spans="1:27" ht="13.2">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="14"/>
@@ -7088,7 +7097,7 @@
       <c r="Z157" s="2"/>
       <c r="AA157" s="2"/>
     </row>
-    <row r="158" spans="1:27" ht="12.75">
+    <row r="158" spans="1:27" ht="13.2">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="14"/>
@@ -7117,7 +7126,7 @@
       <c r="Z158" s="2"/>
       <c r="AA158" s="2"/>
     </row>
-    <row r="159" spans="1:27" ht="12.75">
+    <row r="159" spans="1:27" ht="13.2">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="14"/>
@@ -7146,7 +7155,7 @@
       <c r="Z159" s="2"/>
       <c r="AA159" s="2"/>
     </row>
-    <row r="160" spans="1:27" ht="12.75">
+    <row r="160" spans="1:27" ht="13.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="14"/>
@@ -7175,7 +7184,7 @@
       <c r="Z160" s="2"/>
       <c r="AA160" s="2"/>
     </row>
-    <row r="161" spans="1:27" ht="12.75">
+    <row r="161" spans="1:27" ht="13.2">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="14"/>
@@ -7204,7 +7213,7 @@
       <c r="Z161" s="2"/>
       <c r="AA161" s="2"/>
     </row>
-    <row r="162" spans="1:27" ht="12.75">
+    <row r="162" spans="1:27" ht="13.2">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="14"/>
@@ -7233,7 +7242,7 @@
       <c r="Z162" s="2"/>
       <c r="AA162" s="2"/>
     </row>
-    <row r="163" spans="1:27" ht="12.75">
+    <row r="163" spans="1:27" ht="13.2">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="14"/>
@@ -7262,7 +7271,7 @@
       <c r="Z163" s="2"/>
       <c r="AA163" s="2"/>
     </row>
-    <row r="164" spans="1:27" ht="12.75">
+    <row r="164" spans="1:27" ht="13.2">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="14"/>
@@ -7291,7 +7300,7 @@
       <c r="Z164" s="2"/>
       <c r="AA164" s="2"/>
     </row>
-    <row r="165" spans="1:27" ht="12.75">
+    <row r="165" spans="1:27" ht="13.2">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="14"/>
@@ -7320,7 +7329,7 @@
       <c r="Z165" s="2"/>
       <c r="AA165" s="2"/>
     </row>
-    <row r="166" spans="1:27" ht="12.75">
+    <row r="166" spans="1:27" ht="13.2">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="14"/>
@@ -7349,7 +7358,7 @@
       <c r="Z166" s="2"/>
       <c r="AA166" s="2"/>
     </row>
-    <row r="167" spans="1:27" ht="12.75">
+    <row r="167" spans="1:27" ht="13.2">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="14"/>
@@ -7378,7 +7387,7 @@
       <c r="Z167" s="2"/>
       <c r="AA167" s="2"/>
     </row>
-    <row r="168" spans="1:27" ht="12.75">
+    <row r="168" spans="1:27" ht="13.2">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="14"/>
@@ -7407,7 +7416,7 @@
       <c r="Z168" s="2"/>
       <c r="AA168" s="2"/>
     </row>
-    <row r="169" spans="1:27" ht="12.75">
+    <row r="169" spans="1:27" ht="13.2">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="14"/>
@@ -7436,7 +7445,7 @@
       <c r="Z169" s="2"/>
       <c r="AA169" s="2"/>
     </row>
-    <row r="170" spans="1:27" ht="12.75">
+    <row r="170" spans="1:27" ht="13.2">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="14"/>
@@ -7465,7 +7474,7 @@
       <c r="Z170" s="2"/>
       <c r="AA170" s="2"/>
     </row>
-    <row r="171" spans="1:27" ht="12.75">
+    <row r="171" spans="1:27" ht="13.2">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="14"/>
@@ -7494,7 +7503,7 @@
       <c r="Z171" s="2"/>
       <c r="AA171" s="2"/>
     </row>
-    <row r="172" spans="1:27" ht="12.75">
+    <row r="172" spans="1:27" ht="13.2">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="14"/>
@@ -7523,7 +7532,7 @@
       <c r="Z172" s="2"/>
       <c r="AA172" s="2"/>
     </row>
-    <row r="173" spans="1:27" ht="12.75">
+    <row r="173" spans="1:27" ht="13.2">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="14"/>
@@ -7552,7 +7561,7 @@
       <c r="Z173" s="2"/>
       <c r="AA173" s="2"/>
     </row>
-    <row r="174" spans="1:27" ht="12.75">
+    <row r="174" spans="1:27" ht="13.2">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="14"/>
@@ -7581,7 +7590,7 @@
       <c r="Z174" s="2"/>
       <c r="AA174" s="2"/>
     </row>
-    <row r="175" spans="1:27" ht="12.75">
+    <row r="175" spans="1:27" ht="13.2">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="14"/>
@@ -7610,7 +7619,7 @@
       <c r="Z175" s="2"/>
       <c r="AA175" s="2"/>
     </row>
-    <row r="176" spans="1:27" ht="12.75">
+    <row r="176" spans="1:27" ht="13.2">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="14"/>
@@ -7639,7 +7648,7 @@
       <c r="Z176" s="2"/>
       <c r="AA176" s="2"/>
     </row>
-    <row r="177" spans="1:27" ht="12.75">
+    <row r="177" spans="1:27" ht="13.2">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="14"/>
@@ -7668,7 +7677,7 @@
       <c r="Z177" s="2"/>
       <c r="AA177" s="2"/>
     </row>
-    <row r="178" spans="1:27" ht="12.75">
+    <row r="178" spans="1:27" ht="13.2">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="14"/>
@@ -7697,7 +7706,7 @@
       <c r="Z178" s="2"/>
       <c r="AA178" s="2"/>
     </row>
-    <row r="179" spans="1:27" ht="12.75">
+    <row r="179" spans="1:27" ht="13.2">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="14"/>
@@ -7726,7 +7735,7 @@
       <c r="Z179" s="2"/>
       <c r="AA179" s="2"/>
     </row>
-    <row r="180" spans="1:27" ht="12.75">
+    <row r="180" spans="1:27" ht="13.2">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="14"/>
@@ -7755,7 +7764,7 @@
       <c r="Z180" s="2"/>
       <c r="AA180" s="2"/>
     </row>
-    <row r="181" spans="1:27" ht="12.75">
+    <row r="181" spans="1:27" ht="13.2">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="14"/>
@@ -7784,7 +7793,7 @@
       <c r="Z181" s="2"/>
       <c r="AA181" s="2"/>
     </row>
-    <row r="182" spans="1:27" ht="12.75">
+    <row r="182" spans="1:27" ht="13.2">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="14"/>
@@ -7813,7 +7822,7 @@
       <c r="Z182" s="2"/>
       <c r="AA182" s="2"/>
     </row>
-    <row r="183" spans="1:27" ht="12.75">
+    <row r="183" spans="1:27" ht="13.2">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="14"/>
@@ -7842,7 +7851,7 @@
       <c r="Z183" s="2"/>
       <c r="AA183" s="2"/>
     </row>
-    <row r="184" spans="1:27" ht="12.75">
+    <row r="184" spans="1:27" ht="13.2">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="14"/>
@@ -7871,7 +7880,7 @@
       <c r="Z184" s="2"/>
       <c r="AA184" s="2"/>
     </row>
-    <row r="185" spans="1:27" ht="12.75">
+    <row r="185" spans="1:27" ht="13.2">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="14"/>
@@ -7900,7 +7909,7 @@
       <c r="Z185" s="2"/>
       <c r="AA185" s="2"/>
     </row>
-    <row r="186" spans="1:27" ht="12.75">
+    <row r="186" spans="1:27" ht="13.2">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="14"/>
@@ -7929,7 +7938,7 @@
       <c r="Z186" s="2"/>
       <c r="AA186" s="2"/>
     </row>
-    <row r="187" spans="1:27" ht="12.75">
+    <row r="187" spans="1:27" ht="13.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="14"/>
@@ -7958,7 +7967,7 @@
       <c r="Z187" s="2"/>
       <c r="AA187" s="2"/>
     </row>
-    <row r="188" spans="1:27" ht="12.75">
+    <row r="188" spans="1:27" ht="13.2">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="14"/>
@@ -7987,7 +7996,7 @@
       <c r="Z188" s="2"/>
       <c r="AA188" s="2"/>
     </row>
-    <row r="189" spans="1:27" ht="12.75">
+    <row r="189" spans="1:27" ht="13.2">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="14"/>
@@ -8016,7 +8025,7 @@
       <c r="Z189" s="2"/>
       <c r="AA189" s="2"/>
     </row>
-    <row r="190" spans="1:27" ht="12.75">
+    <row r="190" spans="1:27" ht="13.2">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="14"/>
@@ -8045,7 +8054,7 @@
       <c r="Z190" s="2"/>
       <c r="AA190" s="2"/>
     </row>
-    <row r="191" spans="1:27" ht="12.75">
+    <row r="191" spans="1:27" ht="13.2">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="14"/>
@@ -8074,7 +8083,7 @@
       <c r="Z191" s="2"/>
       <c r="AA191" s="2"/>
     </row>
-    <row r="192" spans="1:27" ht="12.75">
+    <row r="192" spans="1:27" ht="13.2">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="14"/>
@@ -8103,7 +8112,7 @@
       <c r="Z192" s="2"/>
       <c r="AA192" s="2"/>
     </row>
-    <row r="193" spans="1:27" ht="12.75">
+    <row r="193" spans="1:27" ht="13.2">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="14"/>
@@ -8132,7 +8141,7 @@
       <c r="Z193" s="2"/>
       <c r="AA193" s="2"/>
     </row>
-    <row r="194" spans="1:27" ht="12.75">
+    <row r="194" spans="1:27" ht="13.2">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="14"/>
@@ -8161,7 +8170,7 @@
       <c r="Z194" s="2"/>
       <c r="AA194" s="2"/>
     </row>
-    <row r="195" spans="1:27" ht="12.75">
+    <row r="195" spans="1:27" ht="13.2">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="14"/>
@@ -8190,7 +8199,7 @@
       <c r="Z195" s="2"/>
       <c r="AA195" s="2"/>
     </row>
-    <row r="196" spans="1:27" ht="12.75">
+    <row r="196" spans="1:27" ht="13.2">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="14"/>
@@ -8219,7 +8228,7 @@
       <c r="Z196" s="2"/>
       <c r="AA196" s="2"/>
     </row>
-    <row r="197" spans="1:27" ht="12.75">
+    <row r="197" spans="1:27" ht="13.2">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="14"/>
@@ -8248,7 +8257,7 @@
       <c r="Z197" s="2"/>
       <c r="AA197" s="2"/>
     </row>
-    <row r="198" spans="1:27" ht="12.75">
+    <row r="198" spans="1:27" ht="13.2">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="14"/>
@@ -8277,7 +8286,7 @@
       <c r="Z198" s="2"/>
       <c r="AA198" s="2"/>
     </row>
-    <row r="199" spans="1:27" ht="12.75">
+    <row r="199" spans="1:27" ht="13.2">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="14"/>
@@ -8306,7 +8315,7 @@
       <c r="Z199" s="2"/>
       <c r="AA199" s="2"/>
     </row>
-    <row r="200" spans="1:27" ht="12.75">
+    <row r="200" spans="1:27" ht="13.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="14"/>
@@ -8335,7 +8344,7 @@
       <c r="Z200" s="2"/>
       <c r="AA200" s="2"/>
     </row>
-    <row r="201" spans="1:27" ht="12.75">
+    <row r="201" spans="1:27" ht="13.2">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="14"/>
@@ -8364,7 +8373,7 @@
       <c r="Z201" s="2"/>
       <c r="AA201" s="2"/>
     </row>
-    <row r="202" spans="1:27" ht="12.75">
+    <row r="202" spans="1:27" ht="13.2">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="14"/>
@@ -8393,7 +8402,7 @@
       <c r="Z202" s="2"/>
       <c r="AA202" s="2"/>
     </row>
-    <row r="203" spans="1:27" ht="12.75">
+    <row r="203" spans="1:27" ht="13.2">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="14"/>
@@ -8422,7 +8431,7 @@
       <c r="Z203" s="2"/>
       <c r="AA203" s="2"/>
     </row>
-    <row r="204" spans="1:27" ht="12.75">
+    <row r="204" spans="1:27" ht="13.2">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="14"/>
@@ -8451,7 +8460,7 @@
       <c r="Z204" s="2"/>
       <c r="AA204" s="2"/>
     </row>
-    <row r="205" spans="1:27" ht="12.75">
+    <row r="205" spans="1:27" ht="13.2">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="14"/>
@@ -8480,7 +8489,7 @@
       <c r="Z205" s="2"/>
       <c r="AA205" s="2"/>
     </row>
-    <row r="206" spans="1:27" ht="12.75">
+    <row r="206" spans="1:27" ht="13.2">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="14"/>
@@ -8509,7 +8518,7 @@
       <c r="Z206" s="2"/>
       <c r="AA206" s="2"/>
     </row>
-    <row r="207" spans="1:27" ht="12.75">
+    <row r="207" spans="1:27" ht="13.2">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="14"/>
@@ -8538,7 +8547,7 @@
       <c r="Z207" s="2"/>
       <c r="AA207" s="2"/>
     </row>
-    <row r="208" spans="1:27" ht="12.75">
+    <row r="208" spans="1:27" ht="13.2">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="14"/>
@@ -8567,7 +8576,7 @@
       <c r="Z208" s="2"/>
       <c r="AA208" s="2"/>
     </row>
-    <row r="209" spans="1:27" ht="12.75">
+    <row r="209" spans="1:27" ht="13.2">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="14"/>
@@ -8596,7 +8605,7 @@
       <c r="Z209" s="2"/>
       <c r="AA209" s="2"/>
     </row>
-    <row r="210" spans="1:27" ht="12.75">
+    <row r="210" spans="1:27" ht="13.2">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="14"/>
@@ -8625,7 +8634,7 @@
       <c r="Z210" s="2"/>
       <c r="AA210" s="2"/>
     </row>
-    <row r="211" spans="1:27" ht="12.75">
+    <row r="211" spans="1:27" ht="13.2">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="14"/>
@@ -8654,7 +8663,7 @@
       <c r="Z211" s="2"/>
       <c r="AA211" s="2"/>
     </row>
-    <row r="212" spans="1:27" ht="12.75">
+    <row r="212" spans="1:27" ht="13.2">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="14"/>
@@ -8683,7 +8692,7 @@
       <c r="Z212" s="2"/>
       <c r="AA212" s="2"/>
     </row>
-    <row r="213" spans="1:27" ht="12.75">
+    <row r="213" spans="1:27" ht="13.2">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="14"/>
@@ -8712,7 +8721,7 @@
       <c r="Z213" s="2"/>
       <c r="AA213" s="2"/>
     </row>
-    <row r="214" spans="1:27" ht="12.75">
+    <row r="214" spans="1:27" ht="13.2">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="14"/>
@@ -8741,7 +8750,7 @@
       <c r="Z214" s="2"/>
       <c r="AA214" s="2"/>
     </row>
-    <row r="215" spans="1:27" ht="12.75">
+    <row r="215" spans="1:27" ht="13.2">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="14"/>
@@ -8770,7 +8779,7 @@
       <c r="Z215" s="2"/>
       <c r="AA215" s="2"/>
     </row>
-    <row r="216" spans="1:27" ht="12.75">
+    <row r="216" spans="1:27" ht="13.2">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="14"/>
@@ -8799,7 +8808,7 @@
       <c r="Z216" s="2"/>
       <c r="AA216" s="2"/>
     </row>
-    <row r="217" spans="1:27" ht="12.75">
+    <row r="217" spans="1:27" ht="13.2">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="14"/>
@@ -8828,7 +8837,7 @@
       <c r="Z217" s="2"/>
       <c r="AA217" s="2"/>
     </row>
-    <row r="218" spans="1:27" ht="12.75">
+    <row r="218" spans="1:27" ht="13.2">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="14"/>
@@ -8857,7 +8866,7 @@
       <c r="Z218" s="2"/>
       <c r="AA218" s="2"/>
     </row>
-    <row r="219" spans="1:27" ht="12.75">
+    <row r="219" spans="1:27" ht="13.2">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="14"/>
@@ -8886,7 +8895,7 @@
       <c r="Z219" s="2"/>
       <c r="AA219" s="2"/>
     </row>
-    <row r="220" spans="1:27" ht="12.75">
+    <row r="220" spans="1:27" ht="13.2">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="14"/>
@@ -8915,7 +8924,7 @@
       <c r="Z220" s="2"/>
       <c r="AA220" s="2"/>
     </row>
-    <row r="221" spans="1:27" ht="12.75">
+    <row r="221" spans="1:27" ht="13.2">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="14"/>
@@ -8944,7 +8953,7 @@
       <c r="Z221" s="2"/>
       <c r="AA221" s="2"/>
     </row>
-    <row r="222" spans="1:27" ht="12.75">
+    <row r="222" spans="1:27" ht="13.2">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="14"/>
@@ -8973,7 +8982,7 @@
       <c r="Z222" s="2"/>
       <c r="AA222" s="2"/>
     </row>
-    <row r="223" spans="1:27" ht="12.75">
+    <row r="223" spans="1:27" ht="13.2">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="14"/>
@@ -9002,7 +9011,7 @@
       <c r="Z223" s="2"/>
       <c r="AA223" s="2"/>
     </row>
-    <row r="224" spans="1:27" ht="12.75">
+    <row r="224" spans="1:27" ht="13.2">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="14"/>
@@ -9031,7 +9040,7 @@
       <c r="Z224" s="2"/>
       <c r="AA224" s="2"/>
     </row>
-    <row r="225" spans="1:27" ht="12.75">
+    <row r="225" spans="1:27" ht="13.2">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="14"/>
@@ -9060,7 +9069,7 @@
       <c r="Z225" s="2"/>
       <c r="AA225" s="2"/>
     </row>
-    <row r="226" spans="1:27" ht="12.75">
+    <row r="226" spans="1:27" ht="13.2">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="14"/>
@@ -9089,7 +9098,7 @@
       <c r="Z226" s="2"/>
       <c r="AA226" s="2"/>
     </row>
-    <row r="227" spans="1:27" ht="12.75">
+    <row r="227" spans="1:27" ht="13.2">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="14"/>
@@ -9118,7 +9127,7 @@
       <c r="Z227" s="2"/>
       <c r="AA227" s="2"/>
     </row>
-    <row r="228" spans="1:27" ht="12.75">
+    <row r="228" spans="1:27" ht="13.2">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="14"/>
@@ -9147,7 +9156,7 @@
       <c r="Z228" s="2"/>
       <c r="AA228" s="2"/>
     </row>
-    <row r="229" spans="1:27" ht="12.75">
+    <row r="229" spans="1:27" ht="13.2">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="14"/>
@@ -9176,7 +9185,7 @@
       <c r="Z229" s="2"/>
       <c r="AA229" s="2"/>
     </row>
-    <row r="230" spans="1:27" ht="12.75">
+    <row r="230" spans="1:27" ht="13.2">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="14"/>
@@ -9205,7 +9214,7 @@
       <c r="Z230" s="2"/>
       <c r="AA230" s="2"/>
     </row>
-    <row r="231" spans="1:27" ht="12.75">
+    <row r="231" spans="1:27" ht="13.2">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="14"/>
@@ -9234,7 +9243,7 @@
       <c r="Z231" s="2"/>
       <c r="AA231" s="2"/>
     </row>
-    <row r="232" spans="1:27" ht="12.75">
+    <row r="232" spans="1:27" ht="13.2">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="14"/>
@@ -9263,7 +9272,7 @@
       <c r="Z232" s="2"/>
       <c r="AA232" s="2"/>
     </row>
-    <row r="233" spans="1:27" ht="12.75">
+    <row r="233" spans="1:27" ht="13.2">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="14"/>
@@ -9292,7 +9301,7 @@
       <c r="Z233" s="2"/>
       <c r="AA233" s="2"/>
     </row>
-    <row r="234" spans="1:27" ht="12.75">
+    <row r="234" spans="1:27" ht="13.2">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="14"/>
@@ -9321,7 +9330,7 @@
       <c r="Z234" s="2"/>
       <c r="AA234" s="2"/>
     </row>
-    <row r="235" spans="1:27" ht="12.75">
+    <row r="235" spans="1:27" ht="13.2">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="14"/>
@@ -9350,7 +9359,7 @@
       <c r="Z235" s="2"/>
       <c r="AA235" s="2"/>
     </row>
-    <row r="236" spans="1:27" ht="12.75">
+    <row r="236" spans="1:27" ht="13.2">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="14"/>
@@ -9379,7 +9388,7 @@
       <c r="Z236" s="2"/>
       <c r="AA236" s="2"/>
     </row>
-    <row r="237" spans="1:27" ht="12.75">
+    <row r="237" spans="1:27" ht="13.2">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="14"/>
@@ -9408,7 +9417,7 @@
       <c r="Z237" s="2"/>
       <c r="AA237" s="2"/>
     </row>
-    <row r="238" spans="1:27" ht="12.75">
+    <row r="238" spans="1:27" ht="13.2">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="14"/>
@@ -9437,7 +9446,7 @@
       <c r="Z238" s="2"/>
       <c r="AA238" s="2"/>
     </row>
-    <row r="239" spans="1:27" ht="12.75">
+    <row r="239" spans="1:27" ht="13.2">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="14"/>
@@ -9466,7 +9475,7 @@
       <c r="Z239" s="2"/>
       <c r="AA239" s="2"/>
     </row>
-    <row r="240" spans="1:27" ht="12.75">
+    <row r="240" spans="1:27" ht="13.2">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="14"/>
@@ -9495,7 +9504,7 @@
       <c r="Z240" s="2"/>
       <c r="AA240" s="2"/>
     </row>
-    <row r="241" spans="1:27" ht="12.75">
+    <row r="241" spans="1:27" ht="13.2">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="14"/>
@@ -9524,7 +9533,7 @@
       <c r="Z241" s="2"/>
       <c r="AA241" s="2"/>
     </row>
-    <row r="242" spans="1:27" ht="12.75">
+    <row r="242" spans="1:27" ht="13.2">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="14"/>
@@ -9553,7 +9562,7 @@
       <c r="Z242" s="2"/>
       <c r="AA242" s="2"/>
     </row>
-    <row r="243" spans="1:27" ht="12.75">
+    <row r="243" spans="1:27" ht="13.2">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="14"/>
@@ -9582,7 +9591,7 @@
       <c r="Z243" s="2"/>
       <c r="AA243" s="2"/>
     </row>
-    <row r="244" spans="1:27" ht="12.75">
+    <row r="244" spans="1:27" ht="13.2">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="14"/>
@@ -9611,7 +9620,7 @@
       <c r="Z244" s="2"/>
       <c r="AA244" s="2"/>
     </row>
-    <row r="245" spans="1:27" ht="12.75">
+    <row r="245" spans="1:27" ht="13.2">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="14"/>
@@ -9640,7 +9649,7 @@
       <c r="Z245" s="2"/>
       <c r="AA245" s="2"/>
     </row>
-    <row r="246" spans="1:27" ht="12.75">
+    <row r="246" spans="1:27" ht="13.2">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="14"/>
@@ -9669,7 +9678,7 @@
       <c r="Z246" s="2"/>
       <c r="AA246" s="2"/>
     </row>
-    <row r="247" spans="1:27" ht="12.75">
+    <row r="247" spans="1:27" ht="13.2">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="14"/>
@@ -9698,7 +9707,7 @@
       <c r="Z247" s="2"/>
       <c r="AA247" s="2"/>
     </row>
-    <row r="248" spans="1:27" ht="12.75">
+    <row r="248" spans="1:27" ht="13.2">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="14"/>
@@ -9727,7 +9736,7 @@
       <c r="Z248" s="2"/>
       <c r="AA248" s="2"/>
     </row>
-    <row r="249" spans="1:27" ht="12.75">
+    <row r="249" spans="1:27" ht="13.2">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="14"/>
@@ -9756,7 +9765,7 @@
       <c r="Z249" s="2"/>
       <c r="AA249" s="2"/>
     </row>
-    <row r="250" spans="1:27" ht="12.75">
+    <row r="250" spans="1:27" ht="13.2">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="14"/>
@@ -9785,7 +9794,7 @@
       <c r="Z250" s="2"/>
       <c r="AA250" s="2"/>
     </row>
-    <row r="251" spans="1:27" ht="12.75">
+    <row r="251" spans="1:27" ht="13.2">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="14"/>
@@ -9814,7 +9823,7 @@
       <c r="Z251" s="2"/>
       <c r="AA251" s="2"/>
     </row>
-    <row r="252" spans="1:27" ht="12.75">
+    <row r="252" spans="1:27" ht="13.2">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="14"/>
@@ -9843,7 +9852,7 @@
       <c r="Z252" s="2"/>
       <c r="AA252" s="2"/>
     </row>
-    <row r="253" spans="1:27" ht="12.75">
+    <row r="253" spans="1:27" ht="13.2">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="14"/>
@@ -9872,7 +9881,7 @@
       <c r="Z253" s="2"/>
       <c r="AA253" s="2"/>
     </row>
-    <row r="254" spans="1:27" ht="12.75">
+    <row r="254" spans="1:27" ht="13.2">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="14"/>
@@ -9901,7 +9910,7 @@
       <c r="Z254" s="2"/>
       <c r="AA254" s="2"/>
     </row>
-    <row r="255" spans="1:27" ht="12.75">
+    <row r="255" spans="1:27" ht="13.2">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="14"/>
@@ -9930,7 +9939,7 @@
       <c r="Z255" s="2"/>
       <c r="AA255" s="2"/>
     </row>
-    <row r="256" spans="1:27" ht="12.75">
+    <row r="256" spans="1:27" ht="13.2">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="14"/>
@@ -9959,7 +9968,7 @@
       <c r="Z256" s="2"/>
       <c r="AA256" s="2"/>
     </row>
-    <row r="257" spans="1:27" ht="12.75">
+    <row r="257" spans="1:27" ht="13.2">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="14"/>
@@ -9988,7 +9997,7 @@
       <c r="Z257" s="2"/>
       <c r="AA257" s="2"/>
     </row>
-    <row r="258" spans="1:27" ht="12.75">
+    <row r="258" spans="1:27" ht="13.2">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="14"/>
@@ -10017,7 +10026,7 @@
       <c r="Z258" s="2"/>
       <c r="AA258" s="2"/>
     </row>
-    <row r="259" spans="1:27" ht="12.75">
+    <row r="259" spans="1:27" ht="13.2">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="14"/>
@@ -10046,7 +10055,7 @@
       <c r="Z259" s="2"/>
       <c r="AA259" s="2"/>
     </row>
-    <row r="260" spans="1:27" ht="12.75">
+    <row r="260" spans="1:27" ht="13.2">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="14"/>
@@ -10075,7 +10084,7 @@
       <c r="Z260" s="2"/>
       <c r="AA260" s="2"/>
     </row>
-    <row r="261" spans="1:27" ht="12.75">
+    <row r="261" spans="1:27" ht="13.2">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="14"/>
@@ -10104,7 +10113,7 @@
       <c r="Z261" s="2"/>
       <c r="AA261" s="2"/>
     </row>
-    <row r="262" spans="1:27" ht="12.75">
+    <row r="262" spans="1:27" ht="13.2">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="14"/>
@@ -10133,7 +10142,7 @@
       <c r="Z262" s="2"/>
       <c r="AA262" s="2"/>
     </row>
-    <row r="263" spans="1:27" ht="12.75">
+    <row r="263" spans="1:27" ht="13.2">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="14"/>
@@ -10162,7 +10171,7 @@
       <c r="Z263" s="2"/>
       <c r="AA263" s="2"/>
     </row>
-    <row r="264" spans="1:27" ht="12.75">
+    <row r="264" spans="1:27" ht="13.2">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="14"/>
@@ -10191,7 +10200,7 @@
       <c r="Z264" s="2"/>
       <c r="AA264" s="2"/>
     </row>
-    <row r="265" spans="1:27" ht="12.75">
+    <row r="265" spans="1:27" ht="13.2">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="14"/>
@@ -10220,7 +10229,7 @@
       <c r="Z265" s="2"/>
       <c r="AA265" s="2"/>
     </row>
-    <row r="266" spans="1:27" ht="12.75">
+    <row r="266" spans="1:27" ht="13.2">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="14"/>
@@ -10249,7 +10258,7 @@
       <c r="Z266" s="2"/>
       <c r="AA266" s="2"/>
     </row>
-    <row r="267" spans="1:27" ht="12.75">
+    <row r="267" spans="1:27" ht="13.2">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="14"/>
@@ -10278,7 +10287,7 @@
       <c r="Z267" s="2"/>
       <c r="AA267" s="2"/>
     </row>
-    <row r="268" spans="1:27" ht="12.75">
+    <row r="268" spans="1:27" ht="13.2">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="14"/>
@@ -10307,7 +10316,7 @@
       <c r="Z268" s="2"/>
       <c r="AA268" s="2"/>
     </row>
-    <row r="269" spans="1:27" ht="12.75">
+    <row r="269" spans="1:27" ht="13.2">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="14"/>
@@ -10336,7 +10345,7 @@
       <c r="Z269" s="2"/>
       <c r="AA269" s="2"/>
     </row>
-    <row r="270" spans="1:27" ht="12.75">
+    <row r="270" spans="1:27" ht="13.2">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="14"/>
@@ -10365,7 +10374,7 @@
       <c r="Z270" s="2"/>
       <c r="AA270" s="2"/>
     </row>
-    <row r="271" spans="1:27" ht="12.75">
+    <row r="271" spans="1:27" ht="13.2">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="14"/>
@@ -10394,7 +10403,7 @@
       <c r="Z271" s="2"/>
       <c r="AA271" s="2"/>
     </row>
-    <row r="272" spans="1:27" ht="12.75">
+    <row r="272" spans="1:27" ht="13.2">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="14"/>
@@ -10423,7 +10432,7 @@
       <c r="Z272" s="2"/>
       <c r="AA272" s="2"/>
     </row>
-    <row r="273" spans="1:27" ht="12.75">
+    <row r="273" spans="1:27" ht="13.2">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="14"/>
@@ -10452,7 +10461,7 @@
       <c r="Z273" s="2"/>
       <c r="AA273" s="2"/>
     </row>
-    <row r="274" spans="1:27" ht="12.75">
+    <row r="274" spans="1:27" ht="13.2">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="14"/>
@@ -10481,7 +10490,7 @@
       <c r="Z274" s="2"/>
       <c r="AA274" s="2"/>
     </row>
-    <row r="275" spans="1:27" ht="12.75">
+    <row r="275" spans="1:27" ht="13.2">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="14"/>
@@ -10510,7 +10519,7 @@
       <c r="Z275" s="2"/>
       <c r="AA275" s="2"/>
     </row>
-    <row r="276" spans="1:27" ht="12.75">
+    <row r="276" spans="1:27" ht="13.2">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="14"/>
@@ -10539,7 +10548,7 @@
       <c r="Z276" s="2"/>
       <c r="AA276" s="2"/>
     </row>
-    <row r="277" spans="1:27" ht="12.75">
+    <row r="277" spans="1:27" ht="13.2">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="14"/>
@@ -10568,7 +10577,7 @@
       <c r="Z277" s="2"/>
       <c r="AA277" s="2"/>
     </row>
-    <row r="278" spans="1:27" ht="12.75">
+    <row r="278" spans="1:27" ht="13.2">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="14"/>
@@ -10597,7 +10606,7 @@
       <c r="Z278" s="2"/>
       <c r="AA278" s="2"/>
     </row>
-    <row r="279" spans="1:27" ht="12.75">
+    <row r="279" spans="1:27" ht="13.2">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="14"/>
@@ -10626,7 +10635,7 @@
       <c r="Z279" s="2"/>
       <c r="AA279" s="2"/>
     </row>
-    <row r="280" spans="1:27" ht="12.75">
+    <row r="280" spans="1:27" ht="13.2">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="14"/>
@@ -10655,7 +10664,7 @@
       <c r="Z280" s="2"/>
       <c r="AA280" s="2"/>
     </row>
-    <row r="281" spans="1:27" ht="12.75">
+    <row r="281" spans="1:27" ht="13.2">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="14"/>
@@ -10684,7 +10693,7 @@
       <c r="Z281" s="2"/>
       <c r="AA281" s="2"/>
     </row>
-    <row r="282" spans="1:27" ht="12.75">
+    <row r="282" spans="1:27" ht="13.2">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="14"/>
@@ -10713,7 +10722,7 @@
       <c r="Z282" s="2"/>
       <c r="AA282" s="2"/>
     </row>
-    <row r="283" spans="1:27" ht="12.75">
+    <row r="283" spans="1:27" ht="13.2">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="14"/>
@@ -10742,7 +10751,7 @@
       <c r="Z283" s="2"/>
       <c r="AA283" s="2"/>
     </row>
-    <row r="284" spans="1:27" ht="12.75">
+    <row r="284" spans="1:27" ht="13.2">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="14"/>
@@ -10771,7 +10780,7 @@
       <c r="Z284" s="2"/>
       <c r="AA284" s="2"/>
     </row>
-    <row r="285" spans="1:27" ht="12.75">
+    <row r="285" spans="1:27" ht="13.2">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="14"/>
@@ -10800,7 +10809,7 @@
       <c r="Z285" s="2"/>
       <c r="AA285" s="2"/>
     </row>
-    <row r="286" spans="1:27" ht="12.75">
+    <row r="286" spans="1:27" ht="13.2">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="14"/>
@@ -10829,7 +10838,7 @@
       <c r="Z286" s="2"/>
       <c r="AA286" s="2"/>
     </row>
-    <row r="287" spans="1:27" ht="12.75">
+    <row r="287" spans="1:27" ht="13.2">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="14"/>
@@ -10858,7 +10867,7 @@
       <c r="Z287" s="2"/>
       <c r="AA287" s="2"/>
     </row>
-    <row r="288" spans="1:27" ht="12.75">
+    <row r="288" spans="1:27" ht="13.2">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="14"/>
@@ -10887,7 +10896,7 @@
       <c r="Z288" s="2"/>
       <c r="AA288" s="2"/>
     </row>
-    <row r="289" spans="1:27" ht="12.75">
+    <row r="289" spans="1:27" ht="13.2">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="14"/>
@@ -10916,7 +10925,7 @@
       <c r="Z289" s="2"/>
       <c r="AA289" s="2"/>
     </row>
-    <row r="290" spans="1:27" ht="12.75">
+    <row r="290" spans="1:27" ht="13.2">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="14"/>
@@ -10945,7 +10954,7 @@
       <c r="Z290" s="2"/>
       <c r="AA290" s="2"/>
     </row>
-    <row r="291" spans="1:27" ht="12.75">
+    <row r="291" spans="1:27" ht="13.2">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="14"/>
@@ -10974,7 +10983,7 @@
       <c r="Z291" s="2"/>
       <c r="AA291" s="2"/>
     </row>
-    <row r="292" spans="1:27" ht="12.75">
+    <row r="292" spans="1:27" ht="13.2">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="14"/>
@@ -11003,7 +11012,7 @@
       <c r="Z292" s="2"/>
       <c r="AA292" s="2"/>
     </row>
-    <row r="293" spans="1:27" ht="12.75">
+    <row r="293" spans="1:27" ht="13.2">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="14"/>
@@ -11032,7 +11041,7 @@
       <c r="Z293" s="2"/>
       <c r="AA293" s="2"/>
     </row>
-    <row r="294" spans="1:27" ht="12.75">
+    <row r="294" spans="1:27" ht="13.2">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="14"/>
@@ -11061,7 +11070,7 @@
       <c r="Z294" s="2"/>
       <c r="AA294" s="2"/>
     </row>
-    <row r="295" spans="1:27" ht="12.75">
+    <row r="295" spans="1:27" ht="13.2">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="14"/>
@@ -11090,7 +11099,7 @@
       <c r="Z295" s="2"/>
       <c r="AA295" s="2"/>
     </row>
-    <row r="296" spans="1:27" ht="12.75">
+    <row r="296" spans="1:27" ht="13.2">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="14"/>
@@ -11119,7 +11128,7 @@
       <c r="Z296" s="2"/>
       <c r="AA296" s="2"/>
     </row>
-    <row r="297" spans="1:27" ht="12.75">
+    <row r="297" spans="1:27" ht="13.2">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="14"/>
@@ -11148,7 +11157,7 @@
       <c r="Z297" s="2"/>
       <c r="AA297" s="2"/>
     </row>
-    <row r="298" spans="1:27" ht="12.75">
+    <row r="298" spans="1:27" ht="13.2">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="14"/>
@@ -11177,7 +11186,7 @@
       <c r="Z298" s="2"/>
       <c r="AA298" s="2"/>
     </row>
-    <row r="299" spans="1:27" ht="12.75">
+    <row r="299" spans="1:27" ht="13.2">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="14"/>
@@ -11206,7 +11215,7 @@
       <c r="Z299" s="2"/>
       <c r="AA299" s="2"/>
     </row>
-    <row r="300" spans="1:27" ht="12.75">
+    <row r="300" spans="1:27" ht="13.2">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="14"/>
@@ -11235,7 +11244,7 @@
       <c r="Z300" s="2"/>
       <c r="AA300" s="2"/>
     </row>
-    <row r="301" spans="1:27" ht="12.75">
+    <row r="301" spans="1:27" ht="13.2">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="14"/>
@@ -11264,7 +11273,7 @@
       <c r="Z301" s="2"/>
       <c r="AA301" s="2"/>
     </row>
-    <row r="302" spans="1:27" ht="12.75">
+    <row r="302" spans="1:27" ht="13.2">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="14"/>
@@ -11293,7 +11302,7 @@
       <c r="Z302" s="2"/>
       <c r="AA302" s="2"/>
     </row>
-    <row r="303" spans="1:27" ht="12.75">
+    <row r="303" spans="1:27" ht="13.2">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="14"/>
@@ -11322,7 +11331,7 @@
       <c r="Z303" s="2"/>
       <c r="AA303" s="2"/>
     </row>
-    <row r="304" spans="1:27" ht="12.75">
+    <row r="304" spans="1:27" ht="13.2">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="14"/>
@@ -11351,7 +11360,7 @@
       <c r="Z304" s="2"/>
       <c r="AA304" s="2"/>
     </row>
-    <row r="305" spans="1:27" ht="12.75">
+    <row r="305" spans="1:27" ht="13.2">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="14"/>
@@ -11380,7 +11389,7 @@
       <c r="Z305" s="2"/>
       <c r="AA305" s="2"/>
     </row>
-    <row r="306" spans="1:27" ht="12.75">
+    <row r="306" spans="1:27" ht="13.2">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="14"/>
@@ -11409,7 +11418,7 @@
       <c r="Z306" s="2"/>
       <c r="AA306" s="2"/>
     </row>
-    <row r="307" spans="1:27" ht="12.75">
+    <row r="307" spans="1:27" ht="13.2">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="14"/>
@@ -11438,7 +11447,7 @@
       <c r="Z307" s="2"/>
       <c r="AA307" s="2"/>
     </row>
-    <row r="308" spans="1:27" ht="12.75">
+    <row r="308" spans="1:27" ht="13.2">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="14"/>
@@ -11467,7 +11476,7 @@
       <c r="Z308" s="2"/>
       <c r="AA308" s="2"/>
     </row>
-    <row r="309" spans="1:27" ht="12.75">
+    <row r="309" spans="1:27" ht="13.2">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="14"/>
@@ -11496,7 +11505,7 @@
       <c r="Z309" s="2"/>
       <c r="AA309" s="2"/>
     </row>
-    <row r="310" spans="1:27" ht="12.75">
+    <row r="310" spans="1:27" ht="13.2">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="14"/>
@@ -11525,7 +11534,7 @@
       <c r="Z310" s="2"/>
       <c r="AA310" s="2"/>
     </row>
-    <row r="311" spans="1:27" ht="12.75">
+    <row r="311" spans="1:27" ht="13.2">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="14"/>
@@ -11554,7 +11563,7 @@
       <c r="Z311" s="2"/>
       <c r="AA311" s="2"/>
     </row>
-    <row r="312" spans="1:27" ht="12.75">
+    <row r="312" spans="1:27" ht="13.2">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="14"/>
@@ -11583,7 +11592,7 @@
       <c r="Z312" s="2"/>
       <c r="AA312" s="2"/>
     </row>
-    <row r="313" spans="1:27" ht="12.75">
+    <row r="313" spans="1:27" ht="13.2">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="14"/>
@@ -11612,7 +11621,7 @@
       <c r="Z313" s="2"/>
       <c r="AA313" s="2"/>
     </row>
-    <row r="314" spans="1:27" ht="12.75">
+    <row r="314" spans="1:27" ht="13.2">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="14"/>
@@ -11641,7 +11650,7 @@
       <c r="Z314" s="2"/>
       <c r="AA314" s="2"/>
     </row>
-    <row r="315" spans="1:27" ht="12.75">
+    <row r="315" spans="1:27" ht="13.2">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="14"/>
@@ -11670,7 +11679,7 @@
       <c r="Z315" s="2"/>
       <c r="AA315" s="2"/>
     </row>
-    <row r="316" spans="1:27" ht="12.75">
+    <row r="316" spans="1:27" ht="13.2">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="14"/>
@@ -11699,7 +11708,7 @@
       <c r="Z316" s="2"/>
       <c r="AA316" s="2"/>
     </row>
-    <row r="317" spans="1:27" ht="12.75">
+    <row r="317" spans="1:27" ht="13.2">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="14"/>
@@ -11728,7 +11737,7 @@
       <c r="Z317" s="2"/>
       <c r="AA317" s="2"/>
     </row>
-    <row r="318" spans="1:27" ht="12.75">
+    <row r="318" spans="1:27" ht="13.2">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="14"/>
@@ -11757,7 +11766,7 @@
       <c r="Z318" s="2"/>
       <c r="AA318" s="2"/>
     </row>
-    <row r="319" spans="1:27" ht="12.75">
+    <row r="319" spans="1:27" ht="13.2">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="14"/>
@@ -11786,7 +11795,7 @@
       <c r="Z319" s="2"/>
       <c r="AA319" s="2"/>
     </row>
-    <row r="320" spans="1:27" ht="12.75">
+    <row r="320" spans="1:27" ht="13.2">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="14"/>
@@ -11815,7 +11824,7 @@
       <c r="Z320" s="2"/>
       <c r="AA320" s="2"/>
     </row>
-    <row r="321" spans="1:27" ht="12.75">
+    <row r="321" spans="1:27" ht="13.2">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="14"/>
@@ -11844,7 +11853,7 @@
       <c r="Z321" s="2"/>
       <c r="AA321" s="2"/>
     </row>
-    <row r="322" spans="1:27" ht="12.75">
+    <row r="322" spans="1:27" ht="13.2">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="14"/>
@@ -11873,7 +11882,7 @@
       <c r="Z322" s="2"/>
       <c r="AA322" s="2"/>
     </row>
-    <row r="323" spans="1:27" ht="12.75">
+    <row r="323" spans="1:27" ht="13.2">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="14"/>
@@ -11902,7 +11911,7 @@
       <c r="Z323" s="2"/>
       <c r="AA323" s="2"/>
     </row>
-    <row r="324" spans="1:27" ht="12.75">
+    <row r="324" spans="1:27" ht="13.2">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="14"/>
@@ -11931,7 +11940,7 @@
       <c r="Z324" s="2"/>
       <c r="AA324" s="2"/>
     </row>
-    <row r="325" spans="1:27" ht="12.75">
+    <row r="325" spans="1:27" ht="13.2">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="14"/>
@@ -11960,7 +11969,7 @@
       <c r="Z325" s="2"/>
       <c r="AA325" s="2"/>
     </row>
-    <row r="326" spans="1:27" ht="12.75">
+    <row r="326" spans="1:27" ht="13.2">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="14"/>
@@ -11989,7 +11998,7 @@
       <c r="Z326" s="2"/>
       <c r="AA326" s="2"/>
     </row>
-    <row r="327" spans="1:27" ht="12.75">
+    <row r="327" spans="1:27" ht="13.2">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="14"/>
@@ -12018,7 +12027,7 @@
       <c r="Z327" s="2"/>
       <c r="AA327" s="2"/>
     </row>
-    <row r="328" spans="1:27" ht="12.75">
+    <row r="328" spans="1:27" ht="13.2">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="14"/>
@@ -12047,7 +12056,7 @@
       <c r="Z328" s="2"/>
       <c r="AA328" s="2"/>
     </row>
-    <row r="329" spans="1:27" ht="12.75">
+    <row r="329" spans="1:27" ht="13.2">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="14"/>
@@ -12076,7 +12085,7 @@
       <c r="Z329" s="2"/>
       <c r="AA329" s="2"/>
     </row>
-    <row r="330" spans="1:27" ht="12.75">
+    <row r="330" spans="1:27" ht="13.2">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="14"/>
@@ -12105,7 +12114,7 @@
       <c r="Z330" s="2"/>
       <c r="AA330" s="2"/>
     </row>
-    <row r="331" spans="1:27" ht="12.75">
+    <row r="331" spans="1:27" ht="13.2">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="14"/>
@@ -12134,7 +12143,7 @@
       <c r="Z331" s="2"/>
       <c r="AA331" s="2"/>
     </row>
-    <row r="332" spans="1:27" ht="12.75">
+    <row r="332" spans="1:27" ht="13.2">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="14"/>
@@ -12163,7 +12172,7 @@
       <c r="Z332" s="2"/>
       <c r="AA332" s="2"/>
     </row>
-    <row r="333" spans="1:27" ht="12.75">
+    <row r="333" spans="1:27" ht="13.2">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="14"/>
@@ -12192,7 +12201,7 @@
       <c r="Z333" s="2"/>
       <c r="AA333" s="2"/>
     </row>
-    <row r="334" spans="1:27" ht="12.75">
+    <row r="334" spans="1:27" ht="13.2">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="14"/>
@@ -12221,7 +12230,7 @@
       <c r="Z334" s="2"/>
       <c r="AA334" s="2"/>
     </row>
-    <row r="335" spans="1:27" ht="12.75">
+    <row r="335" spans="1:27" ht="13.2">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="14"/>
@@ -12250,7 +12259,7 @@
       <c r="Z335" s="2"/>
       <c r="AA335" s="2"/>
     </row>
-    <row r="336" spans="1:27" ht="12.75">
+    <row r="336" spans="1:27" ht="13.2">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="14"/>
@@ -12279,7 +12288,7 @@
       <c r="Z336" s="2"/>
       <c r="AA336" s="2"/>
     </row>
-    <row r="337" spans="1:27" ht="12.75">
+    <row r="337" spans="1:27" ht="13.2">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="14"/>
@@ -12308,7 +12317,7 @@
       <c r="Z337" s="2"/>
       <c r="AA337" s="2"/>
     </row>
-    <row r="338" spans="1:27" ht="12.75">
+    <row r="338" spans="1:27" ht="13.2">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="14"/>
@@ -12337,7 +12346,7 @@
       <c r="Z338" s="2"/>
       <c r="AA338" s="2"/>
     </row>
-    <row r="339" spans="1:27" ht="12.75">
+    <row r="339" spans="1:27" ht="13.2">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="14"/>
@@ -12366,7 +12375,7 @@
       <c r="Z339" s="2"/>
       <c r="AA339" s="2"/>
     </row>
-    <row r="340" spans="1:27" ht="12.75">
+    <row r="340" spans="1:27" ht="13.2">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="14"/>
@@ -12395,7 +12404,7 @@
       <c r="Z340" s="2"/>
       <c r="AA340" s="2"/>
     </row>
-    <row r="341" spans="1:27" ht="12.75">
+    <row r="341" spans="1:27" ht="13.2">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="14"/>
@@ -12424,7 +12433,7 @@
       <c r="Z341" s="2"/>
       <c r="AA341" s="2"/>
     </row>
-    <row r="342" spans="1:27" ht="12.75">
+    <row r="342" spans="1:27" ht="13.2">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="14"/>
@@ -12453,7 +12462,7 @@
       <c r="Z342" s="2"/>
       <c r="AA342" s="2"/>
     </row>
-    <row r="343" spans="1:27" ht="12.75">
+    <row r="343" spans="1:27" ht="13.2">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="14"/>
@@ -12482,7 +12491,7 @@
       <c r="Z343" s="2"/>
       <c r="AA343" s="2"/>
     </row>
-    <row r="344" spans="1:27" ht="12.75">
+    <row r="344" spans="1:27" ht="13.2">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="14"/>
@@ -12511,7 +12520,7 @@
       <c r="Z344" s="2"/>
       <c r="AA344" s="2"/>
     </row>
-    <row r="345" spans="1:27" ht="12.75">
+    <row r="345" spans="1:27" ht="13.2">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="14"/>
@@ -12540,7 +12549,7 @@
       <c r="Z345" s="2"/>
       <c r="AA345" s="2"/>
     </row>
-    <row r="346" spans="1:27" ht="12.75">
+    <row r="346" spans="1:27" ht="13.2">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="14"/>
@@ -12569,7 +12578,7 @@
       <c r="Z346" s="2"/>
       <c r="AA346" s="2"/>
     </row>
-    <row r="347" spans="1:27" ht="12.75">
+    <row r="347" spans="1:27" ht="13.2">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="14"/>
@@ -12598,7 +12607,7 @@
       <c r="Z347" s="2"/>
       <c r="AA347" s="2"/>
     </row>
-    <row r="348" spans="1:27" ht="12.75">
+    <row r="348" spans="1:27" ht="13.2">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="14"/>
@@ -12627,7 +12636,7 @@
       <c r="Z348" s="2"/>
       <c r="AA348" s="2"/>
     </row>
-    <row r="349" spans="1:27" ht="12.75">
+    <row r="349" spans="1:27" ht="13.2">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="14"/>
@@ -12656,7 +12665,7 @@
       <c r="Z349" s="2"/>
       <c r="AA349" s="2"/>
     </row>
-    <row r="350" spans="1:27" ht="12.75">
+    <row r="350" spans="1:27" ht="13.2">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="14"/>
@@ -12685,7 +12694,7 @@
       <c r="Z350" s="2"/>
       <c r="AA350" s="2"/>
     </row>
-    <row r="351" spans="1:27" ht="12.75">
+    <row r="351" spans="1:27" ht="13.2">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="14"/>
@@ -12714,7 +12723,7 @@
       <c r="Z351" s="2"/>
       <c r="AA351" s="2"/>
     </row>
-    <row r="352" spans="1:27" ht="12.75">
+    <row r="352" spans="1:27" ht="13.2">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="14"/>
@@ -12743,7 +12752,7 @@
       <c r="Z352" s="2"/>
       <c r="AA352" s="2"/>
     </row>
-    <row r="353" spans="1:27" ht="12.75">
+    <row r="353" spans="1:27" ht="13.2">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="14"/>
@@ -12772,7 +12781,7 @@
       <c r="Z353" s="2"/>
       <c r="AA353" s="2"/>
     </row>
-    <row r="354" spans="1:27" ht="12.75">
+    <row r="354" spans="1:27" ht="13.2">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="14"/>
@@ -12801,7 +12810,7 @@
       <c r="Z354" s="2"/>
       <c r="AA354" s="2"/>
     </row>
-    <row r="355" spans="1:27" ht="12.75">
+    <row r="355" spans="1:27" ht="13.2">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="14"/>
@@ -12830,7 +12839,7 @@
       <c r="Z355" s="2"/>
       <c r="AA355" s="2"/>
     </row>
-    <row r="356" spans="1:27" ht="12.75">
+    <row r="356" spans="1:27" ht="13.2">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="14"/>
@@ -12859,7 +12868,7 @@
       <c r="Z356" s="2"/>
       <c r="AA356" s="2"/>
     </row>
-    <row r="357" spans="1:27" ht="12.75">
+    <row r="357" spans="1:27" ht="13.2">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="14"/>
@@ -12888,7 +12897,7 @@
       <c r="Z357" s="2"/>
       <c r="AA357" s="2"/>
     </row>
-    <row r="358" spans="1:27" ht="12.75">
+    <row r="358" spans="1:27" ht="13.2">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="14"/>
@@ -12917,7 +12926,7 @@
       <c r="Z358" s="2"/>
       <c r="AA358" s="2"/>
     </row>
-    <row r="359" spans="1:27" ht="12.75">
+    <row r="359" spans="1:27" ht="13.2">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="14"/>
@@ -12946,7 +12955,7 @@
       <c r="Z359" s="2"/>
       <c r="AA359" s="2"/>
     </row>
-    <row r="360" spans="1:27" ht="12.75">
+    <row r="360" spans="1:27" ht="13.2">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="14"/>
@@ -12975,7 +12984,7 @@
       <c r="Z360" s="2"/>
       <c r="AA360" s="2"/>
     </row>
-    <row r="361" spans="1:27" ht="12.75">
+    <row r="361" spans="1:27" ht="13.2">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="14"/>
@@ -13004,7 +13013,7 @@
       <c r="Z361" s="2"/>
       <c r="AA361" s="2"/>
     </row>
-    <row r="362" spans="1:27" ht="12.75">
+    <row r="362" spans="1:27" ht="13.2">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="14"/>
@@ -13033,7 +13042,7 @@
       <c r="Z362" s="2"/>
       <c r="AA362" s="2"/>
     </row>
-    <row r="363" spans="1:27" ht="12.75">
+    <row r="363" spans="1:27" ht="13.2">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="14"/>
@@ -13062,7 +13071,7 @@
       <c r="Z363" s="2"/>
       <c r="AA363" s="2"/>
     </row>
-    <row r="364" spans="1:27" ht="12.75">
+    <row r="364" spans="1:27" ht="13.2">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="14"/>
@@ -13091,7 +13100,7 @@
       <c r="Z364" s="2"/>
       <c r="AA364" s="2"/>
     </row>
-    <row r="365" spans="1:27" ht="12.75">
+    <row r="365" spans="1:27" ht="13.2">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="14"/>
@@ -13120,7 +13129,7 @@
       <c r="Z365" s="2"/>
       <c r="AA365" s="2"/>
     </row>
-    <row r="366" spans="1:27" ht="12.75">
+    <row r="366" spans="1:27" ht="13.2">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="14"/>
@@ -13149,7 +13158,7 @@
       <c r="Z366" s="2"/>
       <c r="AA366" s="2"/>
     </row>
-    <row r="367" spans="1:27" ht="12.75">
+    <row r="367" spans="1:27" ht="13.2">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="14"/>
@@ -13178,7 +13187,7 @@
       <c r="Z367" s="2"/>
       <c r="AA367" s="2"/>
     </row>
-    <row r="368" spans="1:27" ht="12.75">
+    <row r="368" spans="1:27" ht="13.2">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="14"/>
@@ -13207,7 +13216,7 @@
       <c r="Z368" s="2"/>
       <c r="AA368" s="2"/>
     </row>
-    <row r="369" spans="1:27" ht="12.75">
+    <row r="369" spans="1:27" ht="13.2">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="14"/>
@@ -13236,7 +13245,7 @@
       <c r="Z369" s="2"/>
       <c r="AA369" s="2"/>
     </row>
-    <row r="370" spans="1:27" ht="12.75">
+    <row r="370" spans="1:27" ht="13.2">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="14"/>
@@ -13265,7 +13274,7 @@
       <c r="Z370" s="2"/>
       <c r="AA370" s="2"/>
     </row>
-    <row r="371" spans="1:27" ht="12.75">
+    <row r="371" spans="1:27" ht="13.2">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="14"/>
@@ -13294,7 +13303,7 @@
       <c r="Z371" s="2"/>
       <c r="AA371" s="2"/>
     </row>
-    <row r="372" spans="1:27" ht="12.75">
+    <row r="372" spans="1:27" ht="13.2">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="14"/>
@@ -13323,7 +13332,7 @@
       <c r="Z372" s="2"/>
       <c r="AA372" s="2"/>
     </row>
-    <row r="373" spans="1:27" ht="12.75">
+    <row r="373" spans="1:27" ht="13.2">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="14"/>
@@ -13352,7 +13361,7 @@
       <c r="Z373" s="2"/>
       <c r="AA373" s="2"/>
     </row>
-    <row r="374" spans="1:27" ht="12.75">
+    <row r="374" spans="1:27" ht="13.2">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="14"/>
@@ -13381,7 +13390,7 @@
       <c r="Z374" s="2"/>
       <c r="AA374" s="2"/>
     </row>
-    <row r="375" spans="1:27" ht="12.75">
+    <row r="375" spans="1:27" ht="13.2">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="14"/>
@@ -13410,7 +13419,7 @@
       <c r="Z375" s="2"/>
       <c r="AA375" s="2"/>
     </row>
-    <row r="376" spans="1:27" ht="12.75">
+    <row r="376" spans="1:27" ht="13.2">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="14"/>
@@ -13439,7 +13448,7 @@
       <c r="Z376" s="2"/>
       <c r="AA376" s="2"/>
     </row>
-    <row r="377" spans="1:27" ht="12.75">
+    <row r="377" spans="1:27" ht="13.2">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="14"/>
@@ -13468,7 +13477,7 @@
       <c r="Z377" s="2"/>
       <c r="AA377" s="2"/>
     </row>
-    <row r="378" spans="1:27" ht="12.75">
+    <row r="378" spans="1:27" ht="13.2">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="14"/>
@@ -13497,7 +13506,7 @@
       <c r="Z378" s="2"/>
       <c r="AA378" s="2"/>
     </row>
-    <row r="379" spans="1:27" ht="12.75">
+    <row r="379" spans="1:27" ht="13.2">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="14"/>
@@ -13526,7 +13535,7 @@
       <c r="Z379" s="2"/>
       <c r="AA379" s="2"/>
     </row>
-    <row r="380" spans="1:27" ht="12.75">
+    <row r="380" spans="1:27" ht="13.2">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="14"/>
@@ -13555,7 +13564,7 @@
       <c r="Z380" s="2"/>
       <c r="AA380" s="2"/>
     </row>
-    <row r="381" spans="1:27" ht="12.75">
+    <row r="381" spans="1:27" ht="13.2">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="14"/>
@@ -13584,7 +13593,7 @@
       <c r="Z381" s="2"/>
       <c r="AA381" s="2"/>
     </row>
-    <row r="382" spans="1:27" ht="12.75">
+    <row r="382" spans="1:27" ht="13.2">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="14"/>
@@ -13613,7 +13622,7 @@
       <c r="Z382" s="2"/>
       <c r="AA382" s="2"/>
     </row>
-    <row r="383" spans="1:27" ht="12.75">
+    <row r="383" spans="1:27" ht="13.2">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="14"/>
@@ -13642,7 +13651,7 @@
       <c r="Z383" s="2"/>
       <c r="AA383" s="2"/>
     </row>
-    <row r="384" spans="1:27" ht="12.75">
+    <row r="384" spans="1:27" ht="13.2">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="14"/>
@@ -13671,7 +13680,7 @@
       <c r="Z384" s="2"/>
       <c r="AA384" s="2"/>
     </row>
-    <row r="385" spans="1:27" ht="12.75">
+    <row r="385" spans="1:27" ht="13.2">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="14"/>
@@ -13700,7 +13709,7 @@
       <c r="Z385" s="2"/>
       <c r="AA385" s="2"/>
     </row>
-    <row r="386" spans="1:27" ht="12.75">
+    <row r="386" spans="1:27" ht="13.2">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="14"/>
@@ -13729,7 +13738,7 @@
       <c r="Z386" s="2"/>
       <c r="AA386" s="2"/>
     </row>
-    <row r="387" spans="1:27" ht="12.75">
+    <row r="387" spans="1:27" ht="13.2">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="14"/>
@@ -13758,7 +13767,7 @@
       <c r="Z387" s="2"/>
       <c r="AA387" s="2"/>
     </row>
-    <row r="388" spans="1:27" ht="12.75">
+    <row r="388" spans="1:27" ht="13.2">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="14"/>
@@ -13787,7 +13796,7 @@
       <c r="Z388" s="2"/>
       <c r="AA388" s="2"/>
     </row>
-    <row r="389" spans="1:27" ht="12.75">
+    <row r="389" spans="1:27" ht="13.2">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="14"/>
@@ -13816,7 +13825,7 @@
       <c r="Z389" s="2"/>
       <c r="AA389" s="2"/>
     </row>
-    <row r="390" spans="1:27" ht="12.75">
+    <row r="390" spans="1:27" ht="13.2">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="14"/>
@@ -13845,7 +13854,7 @@
       <c r="Z390" s="2"/>
       <c r="AA390" s="2"/>
     </row>
-    <row r="391" spans="1:27" ht="12.75">
+    <row r="391" spans="1:27" ht="13.2">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="14"/>
@@ -13874,7 +13883,7 @@
       <c r="Z391" s="2"/>
       <c r="AA391" s="2"/>
     </row>
-    <row r="392" spans="1:27" ht="12.75">
+    <row r="392" spans="1:27" ht="13.2">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="14"/>
@@ -13903,7 +13912,7 @@
       <c r="Z392" s="2"/>
       <c r="AA392" s="2"/>
     </row>
-    <row r="393" spans="1:27" ht="12.75">
+    <row r="393" spans="1:27" ht="13.2">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="14"/>
@@ -13932,7 +13941,7 @@
       <c r="Z393" s="2"/>
       <c r="AA393" s="2"/>
     </row>
-    <row r="394" spans="1:27" ht="12.75">
+    <row r="394" spans="1:27" ht="13.2">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="14"/>
@@ -13961,7 +13970,7 @@
       <c r="Z394" s="2"/>
       <c r="AA394" s="2"/>
     </row>
-    <row r="395" spans="1:27" ht="12.75">
+    <row r="395" spans="1:27" ht="13.2">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="14"/>
@@ -13990,7 +13999,7 @@
       <c r="Z395" s="2"/>
       <c r="AA395" s="2"/>
     </row>
-    <row r="396" spans="1:27" ht="12.75">
+    <row r="396" spans="1:27" ht="13.2">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="14"/>
@@ -14019,7 +14028,7 @@
       <c r="Z396" s="2"/>
       <c r="AA396" s="2"/>
     </row>
-    <row r="397" spans="1:27" ht="12.75">
+    <row r="397" spans="1:27" ht="13.2">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="14"/>
@@ -14048,7 +14057,7 @@
       <c r="Z397" s="2"/>
       <c r="AA397" s="2"/>
     </row>
-    <row r="398" spans="1:27" ht="12.75">
+    <row r="398" spans="1:27" ht="13.2">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="14"/>
@@ -14077,7 +14086,7 @@
       <c r="Z398" s="2"/>
       <c r="AA398" s="2"/>
     </row>
-    <row r="399" spans="1:27" ht="12.75">
+    <row r="399" spans="1:27" ht="13.2">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="14"/>
@@ -14106,7 +14115,7 @@
       <c r="Z399" s="2"/>
       <c r="AA399" s="2"/>
     </row>
-    <row r="400" spans="1:27" ht="12.75">
+    <row r="400" spans="1:27" ht="13.2">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="14"/>
@@ -14135,7 +14144,7 @@
       <c r="Z400" s="2"/>
       <c r="AA400" s="2"/>
     </row>
-    <row r="401" spans="1:27" ht="12.75">
+    <row r="401" spans="1:27" ht="13.2">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="14"/>
@@ -14164,7 +14173,7 @@
       <c r="Z401" s="2"/>
       <c r="AA401" s="2"/>
     </row>
-    <row r="402" spans="1:27" ht="12.75">
+    <row r="402" spans="1:27" ht="13.2">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="14"/>
@@ -14193,7 +14202,7 @@
       <c r="Z402" s="2"/>
       <c r="AA402" s="2"/>
     </row>
-    <row r="403" spans="1:27" ht="12.75">
+    <row r="403" spans="1:27" ht="13.2">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="14"/>
@@ -14222,7 +14231,7 @@
       <c r="Z403" s="2"/>
       <c r="AA403" s="2"/>
     </row>
-    <row r="404" spans="1:27" ht="12.75">
+    <row r="404" spans="1:27" ht="13.2">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="14"/>
@@ -14251,7 +14260,7 @@
       <c r="Z404" s="2"/>
       <c r="AA404" s="2"/>
     </row>
-    <row r="405" spans="1:27" ht="12.75">
+    <row r="405" spans="1:27" ht="13.2">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="14"/>
@@ -14280,7 +14289,7 @@
       <c r="Z405" s="2"/>
       <c r="AA405" s="2"/>
     </row>
-    <row r="406" spans="1:27" ht="12.75">
+    <row r="406" spans="1:27" ht="13.2">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="14"/>
@@ -14309,7 +14318,7 @@
       <c r="Z406" s="2"/>
       <c r="AA406" s="2"/>
     </row>
-    <row r="407" spans="1:27" ht="12.75">
+    <row r="407" spans="1:27" ht="13.2">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="14"/>
@@ -14338,7 +14347,7 @@
       <c r="Z407" s="2"/>
       <c r="AA407" s="2"/>
     </row>
-    <row r="408" spans="1:27" ht="12.75">
+    <row r="408" spans="1:27" ht="13.2">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="14"/>
@@ -14367,7 +14376,7 @@
       <c r="Z408" s="2"/>
       <c r="AA408" s="2"/>
     </row>
-    <row r="409" spans="1:27" ht="12.75">
+    <row r="409" spans="1:27" ht="13.2">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="14"/>
@@ -14396,7 +14405,7 @@
       <c r="Z409" s="2"/>
       <c r="AA409" s="2"/>
     </row>
-    <row r="410" spans="1:27" ht="12.75">
+    <row r="410" spans="1:27" ht="13.2">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="14"/>
@@ -14425,7 +14434,7 @@
       <c r="Z410" s="2"/>
       <c r="AA410" s="2"/>
     </row>
-    <row r="411" spans="1:27" ht="12.75">
+    <row r="411" spans="1:27" ht="13.2">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="14"/>
@@ -14454,7 +14463,7 @@
       <c r="Z411" s="2"/>
       <c r="AA411" s="2"/>
     </row>
-    <row r="412" spans="1:27" ht="12.75">
+    <row r="412" spans="1:27" ht="13.2">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="14"/>
@@ -14483,7 +14492,7 @@
       <c r="Z412" s="2"/>
       <c r="AA412" s="2"/>
     </row>
-    <row r="413" spans="1:27" ht="12.75">
+    <row r="413" spans="1:27" ht="13.2">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="14"/>
@@ -14512,7 +14521,7 @@
       <c r="Z413" s="2"/>
       <c r="AA413" s="2"/>
     </row>
-    <row r="414" spans="1:27" ht="12.75">
+    <row r="414" spans="1:27" ht="13.2">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="14"/>
@@ -14541,7 +14550,7 @@
       <c r="Z414" s="2"/>
       <c r="AA414" s="2"/>
     </row>
-    <row r="415" spans="1:27" ht="12.75">
+    <row r="415" spans="1:27" ht="13.2">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="14"/>
@@ -14570,7 +14579,7 @@
       <c r="Z415" s="2"/>
       <c r="AA415" s="2"/>
     </row>
-    <row r="416" spans="1:27" ht="12.75">
+    <row r="416" spans="1:27" ht="13.2">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="14"/>
@@ -14599,7 +14608,7 @@
       <c r="Z416" s="2"/>
       <c r="AA416" s="2"/>
     </row>
-    <row r="417" spans="1:27" ht="12.75">
+    <row r="417" spans="1:27" ht="13.2">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="14"/>
@@ -14628,7 +14637,7 @@
       <c r="Z417" s="2"/>
       <c r="AA417" s="2"/>
     </row>
-    <row r="418" spans="1:27" ht="12.75">
+    <row r="418" spans="1:27" ht="13.2">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="14"/>
@@ -14657,7 +14666,7 @@
       <c r="Z418" s="2"/>
       <c r="AA418" s="2"/>
     </row>
-    <row r="419" spans="1:27" ht="12.75">
+    <row r="419" spans="1:27" ht="13.2">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="14"/>
@@ -14686,7 +14695,7 @@
       <c r="Z419" s="2"/>
       <c r="AA419" s="2"/>
     </row>
-    <row r="420" spans="1:27" ht="12.75">
+    <row r="420" spans="1:27" ht="13.2">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="14"/>
@@ -14715,7 +14724,7 @@
       <c r="Z420" s="2"/>
       <c r="AA420" s="2"/>
     </row>
-    <row r="421" spans="1:27" ht="12.75">
+    <row r="421" spans="1:27" ht="13.2">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="14"/>
@@ -14744,7 +14753,7 @@
       <c r="Z421" s="2"/>
       <c r="AA421" s="2"/>
     </row>
-    <row r="422" spans="1:27" ht="12.75">
+    <row r="422" spans="1:27" ht="13.2">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="14"/>
@@ -14773,7 +14782,7 @@
       <c r="Z422" s="2"/>
       <c r="AA422" s="2"/>
     </row>
-    <row r="423" spans="1:27" ht="12.75">
+    <row r="423" spans="1:27" ht="13.2">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="14"/>
@@ -14802,7 +14811,7 @@
       <c r="Z423" s="2"/>
       <c r="AA423" s="2"/>
     </row>
-    <row r="424" spans="1:27" ht="12.75">
+    <row r="424" spans="1:27" ht="13.2">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="14"/>
@@ -14831,7 +14840,7 @@
       <c r="Z424" s="2"/>
       <c r="AA424" s="2"/>
     </row>
-    <row r="425" spans="1:27" ht="12.75">
+    <row r="425" spans="1:27" ht="13.2">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="14"/>
@@ -14860,7 +14869,7 @@
       <c r="Z425" s="2"/>
       <c r="AA425" s="2"/>
     </row>
-    <row r="426" spans="1:27" ht="12.75">
+    <row r="426" spans="1:27" ht="13.2">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="14"/>
@@ -14889,7 +14898,7 @@
       <c r="Z426" s="2"/>
       <c r="AA426" s="2"/>
     </row>
-    <row r="427" spans="1:27" ht="12.75">
+    <row r="427" spans="1:27" ht="13.2">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="14"/>
@@ -14918,7 +14927,7 @@
       <c r="Z427" s="2"/>
       <c r="AA427" s="2"/>
     </row>
-    <row r="428" spans="1:27" ht="12.75">
+    <row r="428" spans="1:27" ht="13.2">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="14"/>
@@ -14947,7 +14956,7 @@
       <c r="Z428" s="2"/>
       <c r="AA428" s="2"/>
     </row>
-    <row r="429" spans="1:27" ht="12.75">
+    <row r="429" spans="1:27" ht="13.2">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="14"/>
@@ -14976,7 +14985,7 @@
       <c r="Z429" s="2"/>
       <c r="AA429" s="2"/>
     </row>
-    <row r="430" spans="1:27" ht="12.75">
+    <row r="430" spans="1:27" ht="13.2">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="14"/>
@@ -15005,7 +15014,7 @@
       <c r="Z430" s="2"/>
       <c r="AA430" s="2"/>
     </row>
-    <row r="431" spans="1:27" ht="12.75">
+    <row r="431" spans="1:27" ht="13.2">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="14"/>
@@ -15034,7 +15043,7 @@
       <c r="Z431" s="2"/>
       <c r="AA431" s="2"/>
     </row>
-    <row r="432" spans="1:27" ht="12.75">
+    <row r="432" spans="1:27" ht="13.2">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="14"/>
@@ -15063,7 +15072,7 @@
       <c r="Z432" s="2"/>
       <c r="AA432" s="2"/>
     </row>
-    <row r="433" spans="1:27" ht="12.75">
+    <row r="433" spans="1:27" ht="13.2">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="14"/>
@@ -15092,7 +15101,7 @@
       <c r="Z433" s="2"/>
       <c r="AA433" s="2"/>
     </row>
-    <row r="434" spans="1:27" ht="12.75">
+    <row r="434" spans="1:27" ht="13.2">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="14"/>
@@ -15121,7 +15130,7 @@
       <c r="Z434" s="2"/>
       <c r="AA434" s="2"/>
     </row>
-    <row r="435" spans="1:27" ht="12.75">
+    <row r="435" spans="1:27" ht="13.2">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="14"/>
@@ -15150,7 +15159,7 @@
       <c r="Z435" s="2"/>
       <c r="AA435" s="2"/>
     </row>
-    <row r="436" spans="1:27" ht="12.75">
+    <row r="436" spans="1:27" ht="13.2">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="14"/>
@@ -15179,7 +15188,7 @@
       <c r="Z436" s="2"/>
       <c r="AA436" s="2"/>
     </row>
-    <row r="437" spans="1:27" ht="12.75">
+    <row r="437" spans="1:27" ht="13.2">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="14"/>
@@ -15208,7 +15217,7 @@
       <c r="Z437" s="2"/>
       <c r="AA437" s="2"/>
     </row>
-    <row r="438" spans="1:27" ht="12.75">
+    <row r="438" spans="1:27" ht="13.2">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="14"/>
@@ -15237,7 +15246,7 @@
       <c r="Z438" s="2"/>
       <c r="AA438" s="2"/>
     </row>
-    <row r="439" spans="1:27" ht="12.75">
+    <row r="439" spans="1:27" ht="13.2">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="14"/>
@@ -15266,7 +15275,7 @@
       <c r="Z439" s="2"/>
       <c r="AA439" s="2"/>
     </row>
-    <row r="440" spans="1:27" ht="12.75">
+    <row r="440" spans="1:27" ht="13.2">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="14"/>
@@ -15295,7 +15304,7 @@
       <c r="Z440" s="2"/>
       <c r="AA440" s="2"/>
     </row>
-    <row r="441" spans="1:27" ht="12.75">
+    <row r="441" spans="1:27" ht="13.2">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="14"/>
@@ -15324,7 +15333,7 @@
       <c r="Z441" s="2"/>
       <c r="AA441" s="2"/>
     </row>
-    <row r="442" spans="1:27" ht="12.75">
+    <row r="442" spans="1:27" ht="13.2">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="14"/>
@@ -15353,7 +15362,7 @@
       <c r="Z442" s="2"/>
       <c r="AA442" s="2"/>
     </row>
-    <row r="443" spans="1:27" ht="12.75">
+    <row r="443" spans="1:27" ht="13.2">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="14"/>
@@ -15382,7 +15391,7 @@
       <c r="Z443" s="2"/>
       <c r="AA443" s="2"/>
     </row>
-    <row r="444" spans="1:27" ht="12.75">
+    <row r="444" spans="1:27" ht="13.2">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="14"/>
@@ -15411,7 +15420,7 @@
       <c r="Z444" s="2"/>
       <c r="AA444" s="2"/>
     </row>
-    <row r="445" spans="1:27" ht="12.75">
+    <row r="445" spans="1:27" ht="13.2">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="14"/>
@@ -15440,7 +15449,7 @@
       <c r="Z445" s="2"/>
       <c r="AA445" s="2"/>
     </row>
-    <row r="446" spans="1:27" ht="12.75">
+    <row r="446" spans="1:27" ht="13.2">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="14"/>
@@ -15469,7 +15478,7 @@
       <c r="Z446" s="2"/>
       <c r="AA446" s="2"/>
     </row>
-    <row r="447" spans="1:27" ht="12.75">
+    <row r="447" spans="1:27" ht="13.2">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="14"/>
@@ -15498,7 +15507,7 @@
       <c r="Z447" s="2"/>
       <c r="AA447" s="2"/>
     </row>
-    <row r="448" spans="1:27" ht="12.75">
+    <row r="448" spans="1:27" ht="13.2">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="14"/>
@@ -15527,7 +15536,7 @@
       <c r="Z448" s="2"/>
       <c r="AA448" s="2"/>
     </row>
-    <row r="449" spans="1:27" ht="12.75">
+    <row r="449" spans="1:27" ht="13.2">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="14"/>
@@ -15556,7 +15565,7 @@
       <c r="Z449" s="2"/>
       <c r="AA449" s="2"/>
     </row>
-    <row r="450" spans="1:27" ht="12.75">
+    <row r="450" spans="1:27" ht="13.2">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="14"/>
@@ -15585,7 +15594,7 @@
       <c r="Z450" s="2"/>
       <c r="AA450" s="2"/>
     </row>
-    <row r="451" spans="1:27" ht="12.75">
+    <row r="451" spans="1:27" ht="13.2">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="14"/>
@@ -15614,7 +15623,7 @@
       <c r="Z451" s="2"/>
       <c r="AA451" s="2"/>
     </row>
-    <row r="452" spans="1:27" ht="12.75">
+    <row r="452" spans="1:27" ht="13.2">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="14"/>
@@ -15643,7 +15652,7 @@
       <c r="Z452" s="2"/>
       <c r="AA452" s="2"/>
     </row>
-    <row r="453" spans="1:27" ht="12.75">
+    <row r="453" spans="1:27" ht="13.2">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="14"/>
@@ -15672,7 +15681,7 @@
       <c r="Z453" s="2"/>
       <c r="AA453" s="2"/>
     </row>
-    <row r="454" spans="1:27" ht="12.75">
+    <row r="454" spans="1:27" ht="13.2">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="14"/>
@@ -15701,7 +15710,7 @@
       <c r="Z454" s="2"/>
       <c r="AA454" s="2"/>
     </row>
-    <row r="455" spans="1:27" ht="12.75">
+    <row r="455" spans="1:27" ht="13.2">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="14"/>
@@ -15730,7 +15739,7 @@
       <c r="Z455" s="2"/>
       <c r="AA455" s="2"/>
     </row>
-    <row r="456" spans="1:27" ht="12.75">
+    <row r="456" spans="1:27" ht="13.2">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="14"/>
@@ -15759,7 +15768,7 @@
       <c r="Z456" s="2"/>
       <c r="AA456" s="2"/>
     </row>
-    <row r="457" spans="1:27" ht="12.75">
+    <row r="457" spans="1:27" ht="13.2">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="14"/>
@@ -15788,7 +15797,7 @@
       <c r="Z457" s="2"/>
       <c r="AA457" s="2"/>
     </row>
-    <row r="458" spans="1:27" ht="12.75">
+    <row r="458" spans="1:27" ht="13.2">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="14"/>
@@ -15817,7 +15826,7 @@
       <c r="Z458" s="2"/>
       <c r="AA458" s="2"/>
     </row>
-    <row r="459" spans="1:27" ht="12.75">
+    <row r="459" spans="1:27" ht="13.2">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="14"/>
@@ -15846,7 +15855,7 @@
       <c r="Z459" s="2"/>
       <c r="AA459" s="2"/>
     </row>
-    <row r="460" spans="1:27" ht="12.75">
+    <row r="460" spans="1:27" ht="13.2">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="14"/>
@@ -15875,7 +15884,7 @@
       <c r="Z460" s="2"/>
       <c r="AA460" s="2"/>
     </row>
-    <row r="461" spans="1:27" ht="12.75">
+    <row r="461" spans="1:27" ht="13.2">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="14"/>
@@ -15904,7 +15913,7 @@
       <c r="Z461" s="2"/>
       <c r="AA461" s="2"/>
     </row>
-    <row r="462" spans="1:27" ht="12.75">
+    <row r="462" spans="1:27" ht="13.2">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="14"/>
@@ -15933,7 +15942,7 @@
       <c r="Z462" s="2"/>
       <c r="AA462" s="2"/>
     </row>
-    <row r="463" spans="1:27" ht="12.75">
+    <row r="463" spans="1:27" ht="13.2">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="14"/>
@@ -15962,7 +15971,7 @@
       <c r="Z463" s="2"/>
       <c r="AA463" s="2"/>
     </row>
-    <row r="464" spans="1:27" ht="12.75">
+    <row r="464" spans="1:27" ht="13.2">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="14"/>
@@ -15991,7 +16000,7 @@
       <c r="Z464" s="2"/>
       <c r="AA464" s="2"/>
     </row>
-    <row r="465" spans="1:27" ht="12.75">
+    <row r="465" spans="1:27" ht="13.2">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="14"/>
@@ -16020,7 +16029,7 @@
       <c r="Z465" s="2"/>
       <c r="AA465" s="2"/>
     </row>
-    <row r="466" spans="1:27" ht="12.75">
+    <row r="466" spans="1:27" ht="13.2">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="14"/>
@@ -16049,7 +16058,7 @@
       <c r="Z466" s="2"/>
       <c r="AA466" s="2"/>
     </row>
-    <row r="467" spans="1:27" ht="12.75">
+    <row r="467" spans="1:27" ht="13.2">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="14"/>
@@ -16078,7 +16087,7 @@
       <c r="Z467" s="2"/>
       <c r="AA467" s="2"/>
     </row>
-    <row r="468" spans="1:27" ht="12.75">
+    <row r="468" spans="1:27" ht="13.2">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="14"/>
@@ -16107,7 +16116,7 @@
       <c r="Z468" s="2"/>
       <c r="AA468" s="2"/>
     </row>
-    <row r="469" spans="1:27" ht="12.75">
+    <row r="469" spans="1:27" ht="13.2">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="14"/>
@@ -16136,7 +16145,7 @@
       <c r="Z469" s="2"/>
       <c r="AA469" s="2"/>
     </row>
-    <row r="470" spans="1:27" ht="12.75">
+    <row r="470" spans="1:27" ht="13.2">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="14"/>
@@ -16165,7 +16174,7 @@
       <c r="Z470" s="2"/>
       <c r="AA470" s="2"/>
     </row>
-    <row r="471" spans="1:27" ht="12.75">
+    <row r="471" spans="1:27" ht="13.2">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="14"/>
@@ -16194,7 +16203,7 @@
       <c r="Z471" s="2"/>
       <c r="AA471" s="2"/>
     </row>
-    <row r="472" spans="1:27" ht="12.75">
+    <row r="472" spans="1:27" ht="13.2">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="14"/>
@@ -16223,7 +16232,7 @@
       <c r="Z472" s="2"/>
       <c r="AA472" s="2"/>
     </row>
-    <row r="473" spans="1:27" ht="12.75">
+    <row r="473" spans="1:27" ht="13.2">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="14"/>
@@ -16252,7 +16261,7 @@
       <c r="Z473" s="2"/>
       <c r="AA473" s="2"/>
     </row>
-    <row r="474" spans="1:27" ht="12.75">
+    <row r="474" spans="1:27" ht="13.2">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="14"/>
@@ -16281,7 +16290,7 @@
       <c r="Z474" s="2"/>
       <c r="AA474" s="2"/>
     </row>
-    <row r="475" spans="1:27" ht="12.75">
+    <row r="475" spans="1:27" ht="13.2">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="14"/>
@@ -16310,7 +16319,7 @@
       <c r="Z475" s="2"/>
       <c r="AA475" s="2"/>
     </row>
-    <row r="476" spans="1:27" ht="12.75">
+    <row r="476" spans="1:27" ht="13.2">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="14"/>
@@ -16339,7 +16348,7 @@
       <c r="Z476" s="2"/>
       <c r="AA476" s="2"/>
     </row>
-    <row r="477" spans="1:27" ht="12.75">
+    <row r="477" spans="1:27" ht="13.2">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="14"/>
@@ -16368,7 +16377,7 @@
       <c r="Z477" s="2"/>
       <c r="AA477" s="2"/>
     </row>
-    <row r="478" spans="1:27" ht="12.75">
+    <row r="478" spans="1:27" ht="13.2">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="14"/>
@@ -16397,7 +16406,7 @@
       <c r="Z478" s="2"/>
       <c r="AA478" s="2"/>
     </row>
-    <row r="479" spans="1:27" ht="12.75">
+    <row r="479" spans="1:27" ht="13.2">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="14"/>
@@ -16426,7 +16435,7 @@
       <c r="Z479" s="2"/>
       <c r="AA479" s="2"/>
     </row>
-    <row r="480" spans="1:27" ht="12.75">
+    <row r="480" spans="1:27" ht="13.2">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="14"/>
@@ -16455,7 +16464,7 @@
       <c r="Z480" s="2"/>
       <c r="AA480" s="2"/>
     </row>
-    <row r="481" spans="1:27" ht="12.75">
+    <row r="481" spans="1:27" ht="13.2">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="14"/>
@@ -16484,7 +16493,7 @@
       <c r="Z481" s="2"/>
       <c r="AA481" s="2"/>
     </row>
-    <row r="482" spans="1:27" ht="12.75">
+    <row r="482" spans="1:27" ht="13.2">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="14"/>
@@ -16513,7 +16522,7 @@
       <c r="Z482" s="2"/>
       <c r="AA482" s="2"/>
     </row>
-    <row r="483" spans="1:27" ht="12.75">
+    <row r="483" spans="1:27" ht="13.2">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="14"/>
@@ -16542,7 +16551,7 @@
       <c r="Z483" s="2"/>
       <c r="AA483" s="2"/>
     </row>
-    <row r="484" spans="1:27" ht="12.75">
+    <row r="484" spans="1:27" ht="13.2">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="14"/>
@@ -16571,7 +16580,7 @@
       <c r="Z484" s="2"/>
       <c r="AA484" s="2"/>
     </row>
-    <row r="485" spans="1:27" ht="12.75">
+    <row r="485" spans="1:27" ht="13.2">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="14"/>
@@ -16600,7 +16609,7 @@
       <c r="Z485" s="2"/>
       <c r="AA485" s="2"/>
     </row>
-    <row r="486" spans="1:27" ht="12.75">
+    <row r="486" spans="1:27" ht="13.2">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="14"/>
@@ -16629,7 +16638,7 @@
       <c r="Z486" s="2"/>
       <c r="AA486" s="2"/>
     </row>
-    <row r="487" spans="1:27" ht="12.75">
+    <row r="487" spans="1:27" ht="13.2">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="14"/>
@@ -16658,7 +16667,7 @@
       <c r="Z487" s="2"/>
       <c r="AA487" s="2"/>
     </row>
-    <row r="488" spans="1:27" ht="12.75">
+    <row r="488" spans="1:27" ht="13.2">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="14"/>
@@ -16687,7 +16696,7 @@
       <c r="Z488" s="2"/>
       <c r="AA488" s="2"/>
     </row>
-    <row r="489" spans="1:27" ht="12.75">
+    <row r="489" spans="1:27" ht="13.2">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="14"/>
@@ -16716,7 +16725,7 @@
       <c r="Z489" s="2"/>
       <c r="AA489" s="2"/>
     </row>
-    <row r="490" spans="1:27" ht="12.75">
+    <row r="490" spans="1:27" ht="13.2">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="14"/>
@@ -16745,7 +16754,7 @@
       <c r="Z490" s="2"/>
       <c r="AA490" s="2"/>
     </row>
-    <row r="491" spans="1:27" ht="12.75">
+    <row r="491" spans="1:27" ht="13.2">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="14"/>
@@ -16774,7 +16783,7 @@
       <c r="Z491" s="2"/>
       <c r="AA491" s="2"/>
     </row>
-    <row r="492" spans="1:27" ht="12.75">
+    <row r="492" spans="1:27" ht="13.2">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="14"/>
@@ -16803,7 +16812,7 @@
       <c r="Z492" s="2"/>
       <c r="AA492" s="2"/>
     </row>
-    <row r="493" spans="1:27" ht="12.75">
+    <row r="493" spans="1:27" ht="13.2">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="14"/>
@@ -16832,7 +16841,7 @@
       <c r="Z493" s="2"/>
       <c r="AA493" s="2"/>
     </row>
-    <row r="494" spans="1:27" ht="12.75">
+    <row r="494" spans="1:27" ht="13.2">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="14"/>
@@ -16861,7 +16870,7 @@
       <c r="Z494" s="2"/>
       <c r="AA494" s="2"/>
     </row>
-    <row r="495" spans="1:27" ht="12.75">
+    <row r="495" spans="1:27" ht="13.2">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="14"/>
@@ -16890,7 +16899,7 @@
       <c r="Z495" s="2"/>
       <c r="AA495" s="2"/>
     </row>
-    <row r="496" spans="1:27" ht="12.75">
+    <row r="496" spans="1:27" ht="13.2">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="14"/>
@@ -16919,7 +16928,7 @@
       <c r="Z496" s="2"/>
       <c r="AA496" s="2"/>
     </row>
-    <row r="497" spans="1:27" ht="12.75">
+    <row r="497" spans="1:27" ht="13.2">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="14"/>
@@ -16948,7 +16957,7 @@
       <c r="Z497" s="2"/>
       <c r="AA497" s="2"/>
     </row>
-    <row r="498" spans="1:27" ht="12.75">
+    <row r="498" spans="1:27" ht="13.2">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="14"/>
@@ -16977,7 +16986,7 @@
       <c r="Z498" s="2"/>
       <c r="AA498" s="2"/>
     </row>
-    <row r="499" spans="1:27" ht="12.75">
+    <row r="499" spans="1:27" ht="13.2">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="14"/>
@@ -17006,7 +17015,7 @@
       <c r="Z499" s="2"/>
       <c r="AA499" s="2"/>
     </row>
-    <row r="500" spans="1:27" ht="12.75">
+    <row r="500" spans="1:27" ht="13.2">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="14"/>
@@ -17035,7 +17044,7 @@
       <c r="Z500" s="2"/>
       <c r="AA500" s="2"/>
     </row>
-    <row r="501" spans="1:27" ht="12.75">
+    <row r="501" spans="1:27" ht="13.2">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="14"/>
@@ -17064,7 +17073,7 @@
       <c r="Z501" s="2"/>
       <c r="AA501" s="2"/>
     </row>
-    <row r="502" spans="1:27" ht="12.75">
+    <row r="502" spans="1:27" ht="13.2">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="14"/>
@@ -17093,7 +17102,7 @@
       <c r="Z502" s="2"/>
       <c r="AA502" s="2"/>
     </row>
-    <row r="503" spans="1:27" ht="12.75">
+    <row r="503" spans="1:27" ht="13.2">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="14"/>
@@ -17122,7 +17131,7 @@
       <c r="Z503" s="2"/>
       <c r="AA503" s="2"/>
     </row>
-    <row r="504" spans="1:27" ht="12.75">
+    <row r="504" spans="1:27" ht="13.2">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="14"/>
@@ -17151,7 +17160,7 @@
       <c r="Z504" s="2"/>
       <c r="AA504" s="2"/>
     </row>
-    <row r="505" spans="1:27" ht="12.75">
+    <row r="505" spans="1:27" ht="13.2">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="14"/>
@@ -17180,7 +17189,7 @@
       <c r="Z505" s="2"/>
       <c r="AA505" s="2"/>
     </row>
-    <row r="506" spans="1:27" ht="12.75">
+    <row r="506" spans="1:27" ht="13.2">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
       <c r="C506" s="14"/>
@@ -17209,7 +17218,7 @@
       <c r="Z506" s="2"/>
       <c r="AA506" s="2"/>
     </row>
-    <row r="507" spans="1:27" ht="12.75">
+    <row r="507" spans="1:27" ht="13.2">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="14"/>
@@ -17238,7 +17247,7 @@
       <c r="Z507" s="2"/>
       <c r="AA507" s="2"/>
     </row>
-    <row r="508" spans="1:27" ht="12.75">
+    <row r="508" spans="1:27" ht="13.2">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="14"/>
@@ -17267,7 +17276,7 @@
       <c r="Z508" s="2"/>
       <c r="AA508" s="2"/>
     </row>
-    <row r="509" spans="1:27" ht="12.75">
+    <row r="509" spans="1:27" ht="13.2">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="14"/>
@@ -17296,7 +17305,7 @@
       <c r="Z509" s="2"/>
       <c r="AA509" s="2"/>
     </row>
-    <row r="510" spans="1:27" ht="12.75">
+    <row r="510" spans="1:27" ht="13.2">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="14"/>
@@ -17325,7 +17334,7 @@
       <c r="Z510" s="2"/>
       <c r="AA510" s="2"/>
     </row>
-    <row r="511" spans="1:27" ht="12.75">
+    <row r="511" spans="1:27" ht="13.2">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="14"/>
@@ -17354,7 +17363,7 @@
       <c r="Z511" s="2"/>
       <c r="AA511" s="2"/>
     </row>
-    <row r="512" spans="1:27" ht="12.75">
+    <row r="512" spans="1:27" ht="13.2">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
       <c r="C512" s="14"/>
@@ -17383,7 +17392,7 @@
       <c r="Z512" s="2"/>
       <c r="AA512" s="2"/>
     </row>
-    <row r="513" spans="1:27" ht="12.75">
+    <row r="513" spans="1:27" ht="13.2">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="14"/>
@@ -17412,7 +17421,7 @@
       <c r="Z513" s="2"/>
       <c r="AA513" s="2"/>
     </row>
-    <row r="514" spans="1:27" ht="12.75">
+    <row r="514" spans="1:27" ht="13.2">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="14"/>
@@ -17441,7 +17450,7 @@
       <c r="Z514" s="2"/>
       <c r="AA514" s="2"/>
     </row>
-    <row r="515" spans="1:27" ht="12.75">
+    <row r="515" spans="1:27" ht="13.2">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="14"/>
@@ -17470,7 +17479,7 @@
       <c r="Z515" s="2"/>
       <c r="AA515" s="2"/>
     </row>
-    <row r="516" spans="1:27" ht="12.75">
+    <row r="516" spans="1:27" ht="13.2">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="14"/>
@@ -17499,7 +17508,7 @@
       <c r="Z516" s="2"/>
       <c r="AA516" s="2"/>
     </row>
-    <row r="517" spans="1:27" ht="12.75">
+    <row r="517" spans="1:27" ht="13.2">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="14"/>
@@ -17528,7 +17537,7 @@
       <c r="Z517" s="2"/>
       <c r="AA517" s="2"/>
     </row>
-    <row r="518" spans="1:27" ht="12.75">
+    <row r="518" spans="1:27" ht="13.2">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
       <c r="C518" s="14"/>
@@ -17557,7 +17566,7 @@
       <c r="Z518" s="2"/>
       <c r="AA518" s="2"/>
     </row>
-    <row r="519" spans="1:27" ht="12.75">
+    <row r="519" spans="1:27" ht="13.2">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="14"/>
@@ -17586,7 +17595,7 @@
       <c r="Z519" s="2"/>
       <c r="AA519" s="2"/>
     </row>
-    <row r="520" spans="1:27" ht="12.75">
+    <row r="520" spans="1:27" ht="13.2">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="14"/>
@@ -17615,7 +17624,7 @@
       <c r="Z520" s="2"/>
       <c r="AA520" s="2"/>
     </row>
-    <row r="521" spans="1:27" ht="12.75">
+    <row r="521" spans="1:27" ht="13.2">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="14"/>
@@ -17644,7 +17653,7 @@
       <c r="Z521" s="2"/>
       <c r="AA521" s="2"/>
     </row>
-    <row r="522" spans="1:27" ht="12.75">
+    <row r="522" spans="1:27" ht="13.2">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
       <c r="C522" s="14"/>
@@ -17673,7 +17682,7 @@
       <c r="Z522" s="2"/>
       <c r="AA522" s="2"/>
     </row>
-    <row r="523" spans="1:27" ht="12.75">
+    <row r="523" spans="1:27" ht="13.2">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="14"/>
@@ -17702,7 +17711,7 @@
       <c r="Z523" s="2"/>
       <c r="AA523" s="2"/>
     </row>
-    <row r="524" spans="1:27" ht="12.75">
+    <row r="524" spans="1:27" ht="13.2">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="14"/>
@@ -17731,7 +17740,7 @@
       <c r="Z524" s="2"/>
       <c r="AA524" s="2"/>
     </row>
-    <row r="525" spans="1:27" ht="12.75">
+    <row r="525" spans="1:27" ht="13.2">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="14"/>
@@ -17760,7 +17769,7 @@
       <c r="Z525" s="2"/>
       <c r="AA525" s="2"/>
     </row>
-    <row r="526" spans="1:27" ht="12.75">
+    <row r="526" spans="1:27" ht="13.2">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="14"/>
@@ -17789,7 +17798,7 @@
       <c r="Z526" s="2"/>
       <c r="AA526" s="2"/>
     </row>
-    <row r="527" spans="1:27" ht="12.75">
+    <row r="527" spans="1:27" ht="13.2">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
       <c r="C527" s="14"/>
@@ -17818,7 +17827,7 @@
       <c r="Z527" s="2"/>
       <c r="AA527" s="2"/>
     </row>
-    <row r="528" spans="1:27" ht="12.75">
+    <row r="528" spans="1:27" ht="13.2">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="14"/>
@@ -17847,7 +17856,7 @@
       <c r="Z528" s="2"/>
       <c r="AA528" s="2"/>
     </row>
-    <row r="529" spans="1:27" ht="12.75">
+    <row r="529" spans="1:27" ht="13.2">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="14"/>
@@ -17876,7 +17885,7 @@
       <c r="Z529" s="2"/>
       <c r="AA529" s="2"/>
     </row>
-    <row r="530" spans="1:27" ht="12.75">
+    <row r="530" spans="1:27" ht="13.2">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
       <c r="C530" s="14"/>
@@ -17905,7 +17914,7 @@
       <c r="Z530" s="2"/>
       <c r="AA530" s="2"/>
     </row>
-    <row r="531" spans="1:27" ht="12.75">
+    <row r="531" spans="1:27" ht="13.2">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="14"/>
@@ -17934,7 +17943,7 @@
       <c r="Z531" s="2"/>
       <c r="AA531" s="2"/>
     </row>
-    <row r="532" spans="1:27" ht="12.75">
+    <row r="532" spans="1:27" ht="13.2">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="14"/>
@@ -17963,7 +17972,7 @@
       <c r="Z532" s="2"/>
       <c r="AA532" s="2"/>
     </row>
-    <row r="533" spans="1:27" ht="12.75">
+    <row r="533" spans="1:27" ht="13.2">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="14"/>
@@ -17992,7 +18001,7 @@
       <c r="Z533" s="2"/>
       <c r="AA533" s="2"/>
     </row>
-    <row r="534" spans="1:27" ht="12.75">
+    <row r="534" spans="1:27" ht="13.2">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
       <c r="C534" s="14"/>
@@ -18021,7 +18030,7 @@
       <c r="Z534" s="2"/>
       <c r="AA534" s="2"/>
     </row>
-    <row r="535" spans="1:27" ht="12.75">
+    <row r="535" spans="1:27" ht="13.2">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="14"/>
@@ -18050,7 +18059,7 @@
       <c r="Z535" s="2"/>
       <c r="AA535" s="2"/>
     </row>
-    <row r="536" spans="1:27" ht="12.75">
+    <row r="536" spans="1:27" ht="13.2">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="14"/>
@@ -18079,7 +18088,7 @@
       <c r="Z536" s="2"/>
       <c r="AA536" s="2"/>
     </row>
-    <row r="537" spans="1:27" ht="12.75">
+    <row r="537" spans="1:27" ht="13.2">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="14"/>
@@ -18108,7 +18117,7 @@
       <c r="Z537" s="2"/>
       <c r="AA537" s="2"/>
     </row>
-    <row r="538" spans="1:27" ht="12.75">
+    <row r="538" spans="1:27" ht="13.2">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="14"/>
@@ -18137,7 +18146,7 @@
       <c r="Z538" s="2"/>
       <c r="AA538" s="2"/>
     </row>
-    <row r="539" spans="1:27" ht="12.75">
+    <row r="539" spans="1:27" ht="13.2">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="14"/>
@@ -18166,7 +18175,7 @@
       <c r="Z539" s="2"/>
       <c r="AA539" s="2"/>
     </row>
-    <row r="540" spans="1:27" ht="12.75">
+    <row r="540" spans="1:27" ht="13.2">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
       <c r="C540" s="14"/>
@@ -18195,7 +18204,7 @@
       <c r="Z540" s="2"/>
       <c r="AA540" s="2"/>
     </row>
-    <row r="541" spans="1:27" ht="12.75">
+    <row r="541" spans="1:27" ht="13.2">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
       <c r="C541" s="14"/>
@@ -18224,7 +18233,7 @@
       <c r="Z541" s="2"/>
       <c r="AA541" s="2"/>
     </row>
-    <row r="542" spans="1:27" ht="12.75">
+    <row r="542" spans="1:27" ht="13.2">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
       <c r="C542" s="14"/>
@@ -18253,7 +18262,7 @@
       <c r="Z542" s="2"/>
       <c r="AA542" s="2"/>
     </row>
-    <row r="543" spans="1:27" ht="12.75">
+    <row r="543" spans="1:27" ht="13.2">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="14"/>
@@ -18282,7 +18291,7 @@
       <c r="Z543" s="2"/>
       <c r="AA543" s="2"/>
     </row>
-    <row r="544" spans="1:27" ht="12.75">
+    <row r="544" spans="1:27" ht="13.2">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="14"/>
@@ -18311,7 +18320,7 @@
       <c r="Z544" s="2"/>
       <c r="AA544" s="2"/>
     </row>
-    <row r="545" spans="1:27" ht="12.75">
+    <row r="545" spans="1:27" ht="13.2">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="14"/>
@@ -18340,7 +18349,7 @@
       <c r="Z545" s="2"/>
       <c r="AA545" s="2"/>
     </row>
-    <row r="546" spans="1:27" ht="12.75">
+    <row r="546" spans="1:27" ht="13.2">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="14"/>
@@ -18369,7 +18378,7 @@
       <c r="Z546" s="2"/>
       <c r="AA546" s="2"/>
     </row>
-    <row r="547" spans="1:27" ht="12.75">
+    <row r="547" spans="1:27" ht="13.2">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
       <c r="C547" s="14"/>
@@ -18398,7 +18407,7 @@
       <c r="Z547" s="2"/>
       <c r="AA547" s="2"/>
     </row>
-    <row r="548" spans="1:27" ht="12.75">
+    <row r="548" spans="1:27" ht="13.2">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="14"/>
@@ -18427,7 +18436,7 @@
       <c r="Z548" s="2"/>
       <c r="AA548" s="2"/>
     </row>
-    <row r="549" spans="1:27" ht="12.75">
+    <row r="549" spans="1:27" ht="13.2">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
       <c r="C549" s="14"/>
@@ -18456,7 +18465,7 @@
       <c r="Z549" s="2"/>
       <c r="AA549" s="2"/>
     </row>
-    <row r="550" spans="1:27" ht="12.75">
+    <row r="550" spans="1:27" ht="13.2">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="14"/>
@@ -18485,7 +18494,7 @@
       <c r="Z550" s="2"/>
       <c r="AA550" s="2"/>
     </row>
-    <row r="551" spans="1:27" ht="12.75">
+    <row r="551" spans="1:27" ht="13.2">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
       <c r="C551" s="14"/>
@@ -18514,7 +18523,7 @@
       <c r="Z551" s="2"/>
       <c r="AA551" s="2"/>
     </row>
-    <row r="552" spans="1:27" ht="12.75">
+    <row r="552" spans="1:27" ht="13.2">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="14"/>
@@ -18543,7 +18552,7 @@
       <c r="Z552" s="2"/>
       <c r="AA552" s="2"/>
     </row>
-    <row r="553" spans="1:27" ht="12.75">
+    <row r="553" spans="1:27" ht="13.2">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="14"/>
@@ -18572,7 +18581,7 @@
       <c r="Z553" s="2"/>
       <c r="AA553" s="2"/>
     </row>
-    <row r="554" spans="1:27" ht="12.75">
+    <row r="554" spans="1:27" ht="13.2">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="14"/>
@@ -18601,7 +18610,7 @@
       <c r="Z554" s="2"/>
       <c r="AA554" s="2"/>
     </row>
-    <row r="555" spans="1:27" ht="12.75">
+    <row r="555" spans="1:27" ht="13.2">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
       <c r="C555" s="14"/>
@@ -18630,7 +18639,7 @@
       <c r="Z555" s="2"/>
       <c r="AA555" s="2"/>
     </row>
-    <row r="556" spans="1:27" ht="12.75">
+    <row r="556" spans="1:27" ht="13.2">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
       <c r="C556" s="14"/>
@@ -18659,7 +18668,7 @@
       <c r="Z556" s="2"/>
       <c r="AA556" s="2"/>
     </row>
-    <row r="557" spans="1:27" ht="12.75">
+    <row r="557" spans="1:27" ht="13.2">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="14"/>
@@ -18688,7 +18697,7 @@
       <c r="Z557" s="2"/>
       <c r="AA557" s="2"/>
     </row>
-    <row r="558" spans="1:27" ht="12.75">
+    <row r="558" spans="1:27" ht="13.2">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="14"/>
@@ -18717,7 +18726,7 @@
       <c r="Z558" s="2"/>
       <c r="AA558" s="2"/>
     </row>
-    <row r="559" spans="1:27" ht="12.75">
+    <row r="559" spans="1:27" ht="13.2">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
       <c r="C559" s="14"/>
@@ -18746,7 +18755,7 @@
       <c r="Z559" s="2"/>
       <c r="AA559" s="2"/>
     </row>
-    <row r="560" spans="1:27" ht="12.75">
+    <row r="560" spans="1:27" ht="13.2">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="14"/>
@@ -18775,7 +18784,7 @@
       <c r="Z560" s="2"/>
       <c r="AA560" s="2"/>
     </row>
-    <row r="561" spans="1:27" ht="12.75">
+    <row r="561" spans="1:27" ht="13.2">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="14"/>
@@ -18804,7 +18813,7 @@
       <c r="Z561" s="2"/>
       <c r="AA561" s="2"/>
     </row>
-    <row r="562" spans="1:27" ht="12.75">
+    <row r="562" spans="1:27" ht="13.2">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="14"/>
@@ -18833,7 +18842,7 @@
       <c r="Z562" s="2"/>
       <c r="AA562" s="2"/>
     </row>
-    <row r="563" spans="1:27" ht="12.75">
+    <row r="563" spans="1:27" ht="13.2">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="14"/>
@@ -18862,7 +18871,7 @@
       <c r="Z563" s="2"/>
       <c r="AA563" s="2"/>
     </row>
-    <row r="564" spans="1:27" ht="12.75">
+    <row r="564" spans="1:27" ht="13.2">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="14"/>
@@ -18891,7 +18900,7 @@
       <c r="Z564" s="2"/>
       <c r="AA564" s="2"/>
     </row>
-    <row r="565" spans="1:27" ht="12.75">
+    <row r="565" spans="1:27" ht="13.2">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
       <c r="C565" s="14"/>
@@ -18920,7 +18929,7 @@
       <c r="Z565" s="2"/>
       <c r="AA565" s="2"/>
     </row>
-    <row r="566" spans="1:27" ht="12.75">
+    <row r="566" spans="1:27" ht="13.2">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="14"/>
@@ -18949,7 +18958,7 @@
       <c r="Z566" s="2"/>
       <c r="AA566" s="2"/>
     </row>
-    <row r="567" spans="1:27" ht="12.75">
+    <row r="567" spans="1:27" ht="13.2">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="14"/>
@@ -18978,7 +18987,7 @@
       <c r="Z567" s="2"/>
       <c r="AA567" s="2"/>
     </row>
-    <row r="568" spans="1:27" ht="12.75">
+    <row r="568" spans="1:27" ht="13.2">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
       <c r="C568" s="14"/>
@@ -19007,7 +19016,7 @@
       <c r="Z568" s="2"/>
       <c r="AA568" s="2"/>
     </row>
-    <row r="569" spans="1:27" ht="12.75">
+    <row r="569" spans="1:27" ht="13.2">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="14"/>
@@ -19036,7 +19045,7 @@
       <c r="Z569" s="2"/>
       <c r="AA569" s="2"/>
     </row>
-    <row r="570" spans="1:27" ht="12.75">
+    <row r="570" spans="1:27" ht="13.2">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="14"/>
@@ -19065,7 +19074,7 @@
       <c r="Z570" s="2"/>
       <c r="AA570" s="2"/>
     </row>
-    <row r="571" spans="1:27" ht="12.75">
+    <row r="571" spans="1:27" ht="13.2">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="14"/>
@@ -19094,7 +19103,7 @@
       <c r="Z571" s="2"/>
       <c r="AA571" s="2"/>
     </row>
-    <row r="572" spans="1:27" ht="12.75">
+    <row r="572" spans="1:27" ht="13.2">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
       <c r="C572" s="14"/>
@@ -19123,7 +19132,7 @@
       <c r="Z572" s="2"/>
       <c r="AA572" s="2"/>
     </row>
-    <row r="573" spans="1:27" ht="12.75">
+    <row r="573" spans="1:27" ht="13.2">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="14"/>
@@ -19152,7 +19161,7 @@
       <c r="Z573" s="2"/>
       <c r="AA573" s="2"/>
     </row>
-    <row r="574" spans="1:27" ht="12.75">
+    <row r="574" spans="1:27" ht="13.2">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="14"/>
@@ -19181,7 +19190,7 @@
       <c r="Z574" s="2"/>
       <c r="AA574" s="2"/>
     </row>
-    <row r="575" spans="1:27" ht="12.75">
+    <row r="575" spans="1:27" ht="13.2">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="14"/>
@@ -19210,7 +19219,7 @@
       <c r="Z575" s="2"/>
       <c r="AA575" s="2"/>
     </row>
-    <row r="576" spans="1:27" ht="12.75">
+    <row r="576" spans="1:27" ht="13.2">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="14"/>
@@ -19239,7 +19248,7 @@
       <c r="Z576" s="2"/>
       <c r="AA576" s="2"/>
     </row>
-    <row r="577" spans="1:27" ht="12.75">
+    <row r="577" spans="1:27" ht="13.2">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="14"/>
@@ -19268,7 +19277,7 @@
       <c r="Z577" s="2"/>
       <c r="AA577" s="2"/>
     </row>
-    <row r="578" spans="1:27" ht="12.75">
+    <row r="578" spans="1:27" ht="13.2">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
       <c r="C578" s="14"/>
@@ -19297,7 +19306,7 @@
       <c r="Z578" s="2"/>
       <c r="AA578" s="2"/>
     </row>
-    <row r="579" spans="1:27" ht="12.75">
+    <row r="579" spans="1:27" ht="13.2">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
       <c r="C579" s="14"/>
@@ -19326,7 +19335,7 @@
       <c r="Z579" s="2"/>
       <c r="AA579" s="2"/>
     </row>
-    <row r="580" spans="1:27" ht="12.75">
+    <row r="580" spans="1:27" ht="13.2">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="14"/>
@@ -19355,7 +19364,7 @@
       <c r="Z580" s="2"/>
       <c r="AA580" s="2"/>
     </row>
-    <row r="581" spans="1:27" ht="12.75">
+    <row r="581" spans="1:27" ht="13.2">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="14"/>
@@ -19384,7 +19393,7 @@
       <c r="Z581" s="2"/>
       <c r="AA581" s="2"/>
     </row>
-    <row r="582" spans="1:27" ht="12.75">
+    <row r="582" spans="1:27" ht="13.2">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
       <c r="C582" s="14"/>
@@ -19413,7 +19422,7 @@
       <c r="Z582" s="2"/>
       <c r="AA582" s="2"/>
     </row>
-    <row r="583" spans="1:27" ht="12.75">
+    <row r="583" spans="1:27" ht="13.2">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="14"/>
@@ -19442,7 +19451,7 @@
       <c r="Z583" s="2"/>
       <c r="AA583" s="2"/>
     </row>
-    <row r="584" spans="1:27" ht="12.75">
+    <row r="584" spans="1:27" ht="13.2">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
       <c r="C584" s="14"/>
@@ -19471,7 +19480,7 @@
       <c r="Z584" s="2"/>
       <c r="AA584" s="2"/>
     </row>
-    <row r="585" spans="1:27" ht="12.75">
+    <row r="585" spans="1:27" ht="13.2">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="14"/>
@@ -19500,7 +19509,7 @@
       <c r="Z585" s="2"/>
       <c r="AA585" s="2"/>
     </row>
-    <row r="586" spans="1:27" ht="12.75">
+    <row r="586" spans="1:27" ht="13.2">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="14"/>
@@ -19529,7 +19538,7 @@
       <c r="Z586" s="2"/>
       <c r="AA586" s="2"/>
     </row>
-    <row r="587" spans="1:27" ht="12.75">
+    <row r="587" spans="1:27" ht="13.2">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="14"/>
@@ -19558,7 +19567,7 @@
       <c r="Z587" s="2"/>
       <c r="AA587" s="2"/>
     </row>
-    <row r="588" spans="1:27" ht="12.75">
+    <row r="588" spans="1:27" ht="13.2">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
       <c r="C588" s="14"/>
@@ -19587,7 +19596,7 @@
       <c r="Z588" s="2"/>
       <c r="AA588" s="2"/>
     </row>
-    <row r="589" spans="1:27" ht="12.75">
+    <row r="589" spans="1:27" ht="13.2">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="14"/>
@@ -19616,7 +19625,7 @@
       <c r="Z589" s="2"/>
       <c r="AA589" s="2"/>
     </row>
-    <row r="590" spans="1:27" ht="12.75">
+    <row r="590" spans="1:27" ht="13.2">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="14"/>
@@ -19645,7 +19654,7 @@
       <c r="Z590" s="2"/>
       <c r="AA590" s="2"/>
     </row>
-    <row r="591" spans="1:27" ht="12.75">
+    <row r="591" spans="1:27" ht="13.2">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="14"/>
@@ -19674,7 +19683,7 @@
       <c r="Z591" s="2"/>
       <c r="AA591" s="2"/>
     </row>
-    <row r="592" spans="1:27" ht="12.75">
+    <row r="592" spans="1:27" ht="13.2">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="14"/>
@@ -19703,7 +19712,7 @@
       <c r="Z592" s="2"/>
       <c r="AA592" s="2"/>
     </row>
-    <row r="593" spans="1:27" ht="12.75">
+    <row r="593" spans="1:27" ht="13.2">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
       <c r="C593" s="14"/>
@@ -19732,7 +19741,7 @@
       <c r="Z593" s="2"/>
       <c r="AA593" s="2"/>
     </row>
-    <row r="594" spans="1:27" ht="12.75">
+    <row r="594" spans="1:27" ht="13.2">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="14"/>
@@ -19761,7 +19770,7 @@
       <c r="Z594" s="2"/>
       <c r="AA594" s="2"/>
     </row>
-    <row r="595" spans="1:27" ht="12.75">
+    <row r="595" spans="1:27" ht="13.2">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="14"/>
@@ -19790,7 +19799,7 @@
       <c r="Z595" s="2"/>
       <c r="AA595" s="2"/>
     </row>
-    <row r="596" spans="1:27" ht="12.75">
+    <row r="596" spans="1:27" ht="13.2">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="14"/>
@@ -19819,7 +19828,7 @@
       <c r="Z596" s="2"/>
       <c r="AA596" s="2"/>
     </row>
-    <row r="597" spans="1:27" ht="12.75">
+    <row r="597" spans="1:27" ht="13.2">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="14"/>
@@ -19848,7 +19857,7 @@
       <c r="Z597" s="2"/>
       <c r="AA597" s="2"/>
     </row>
-    <row r="598" spans="1:27" ht="12.75">
+    <row r="598" spans="1:27" ht="13.2">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="14"/>
@@ -19877,7 +19886,7 @@
       <c r="Z598" s="2"/>
       <c r="AA598" s="2"/>
     </row>
-    <row r="599" spans="1:27" ht="12.75">
+    <row r="599" spans="1:27" ht="13.2">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
       <c r="C599" s="14"/>
@@ -19906,7 +19915,7 @@
       <c r="Z599" s="2"/>
       <c r="AA599" s="2"/>
     </row>
-    <row r="600" spans="1:27" ht="12.75">
+    <row r="600" spans="1:27" ht="13.2">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="14"/>
@@ -19935,7 +19944,7 @@
       <c r="Z600" s="2"/>
       <c r="AA600" s="2"/>
     </row>
-    <row r="601" spans="1:27" ht="12.75">
+    <row r="601" spans="1:27" ht="13.2">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="14"/>
@@ -19964,7 +19973,7 @@
       <c r="Z601" s="2"/>
       <c r="AA601" s="2"/>
     </row>
-    <row r="602" spans="1:27" ht="12.75">
+    <row r="602" spans="1:27" ht="13.2">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="14"/>
@@ -19993,7 +20002,7 @@
       <c r="Z602" s="2"/>
       <c r="AA602" s="2"/>
     </row>
-    <row r="603" spans="1:27" ht="12.75">
+    <row r="603" spans="1:27" ht="13.2">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="14"/>
@@ -20022,7 +20031,7 @@
       <c r="Z603" s="2"/>
       <c r="AA603" s="2"/>
     </row>
-    <row r="604" spans="1:27" ht="12.75">
+    <row r="604" spans="1:27" ht="13.2">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
       <c r="C604" s="14"/>
@@ -20051,7 +20060,7 @@
       <c r="Z604" s="2"/>
       <c r="AA604" s="2"/>
     </row>
-    <row r="605" spans="1:27" ht="12.75">
+    <row r="605" spans="1:27" ht="13.2">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
       <c r="C605" s="14"/>
@@ -20080,7 +20089,7 @@
       <c r="Z605" s="2"/>
       <c r="AA605" s="2"/>
     </row>
-    <row r="606" spans="1:27" ht="12.75">
+    <row r="606" spans="1:27" ht="13.2">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
       <c r="C606" s="14"/>
@@ -20109,7 +20118,7 @@
       <c r="Z606" s="2"/>
       <c r="AA606" s="2"/>
     </row>
-    <row r="607" spans="1:27" ht="12.75">
+    <row r="607" spans="1:27" ht="13.2">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
       <c r="C607" s="14"/>
@@ -20138,7 +20147,7 @@
       <c r="Z607" s="2"/>
       <c r="AA607" s="2"/>
     </row>
-    <row r="608" spans="1:27" ht="12.75">
+    <row r="608" spans="1:27" ht="13.2">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
       <c r="C608" s="14"/>
@@ -20167,7 +20176,7 @@
       <c r="Z608" s="2"/>
       <c r="AA608" s="2"/>
     </row>
-    <row r="609" spans="1:27" ht="12.75">
+    <row r="609" spans="1:27" ht="13.2">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
       <c r="C609" s="14"/>
@@ -20196,7 +20205,7 @@
       <c r="Z609" s="2"/>
       <c r="AA609" s="2"/>
     </row>
-    <row r="610" spans="1:27" ht="12.75">
+    <row r="610" spans="1:27" ht="13.2">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
       <c r="C610" s="14"/>
@@ -20225,7 +20234,7 @@
       <c r="Z610" s="2"/>
       <c r="AA610" s="2"/>
     </row>
-    <row r="611" spans="1:27" ht="12.75">
+    <row r="611" spans="1:27" ht="13.2">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
       <c r="C611" s="14"/>
@@ -20254,7 +20263,7 @@
       <c r="Z611" s="2"/>
       <c r="AA611" s="2"/>
     </row>
-    <row r="612" spans="1:27" ht="12.75">
+    <row r="612" spans="1:27" ht="13.2">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
       <c r="C612" s="14"/>
@@ -20283,7 +20292,7 @@
       <c r="Z612" s="2"/>
       <c r="AA612" s="2"/>
     </row>
-    <row r="613" spans="1:27" ht="12.75">
+    <row r="613" spans="1:27" ht="13.2">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
       <c r="C613" s="14"/>
@@ -20312,7 +20321,7 @@
       <c r="Z613" s="2"/>
       <c r="AA613" s="2"/>
     </row>
-    <row r="614" spans="1:27" ht="12.75">
+    <row r="614" spans="1:27" ht="13.2">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
       <c r="C614" s="14"/>
@@ -20341,7 +20350,7 @@
       <c r="Z614" s="2"/>
       <c r="AA614" s="2"/>
     </row>
-    <row r="615" spans="1:27" ht="12.75">
+    <row r="615" spans="1:27" ht="13.2">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
       <c r="C615" s="14"/>
@@ -20370,7 +20379,7 @@
       <c r="Z615" s="2"/>
       <c r="AA615" s="2"/>
     </row>
-    <row r="616" spans="1:27" ht="12.75">
+    <row r="616" spans="1:27" ht="13.2">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
       <c r="C616" s="14"/>
@@ -20399,7 +20408,7 @@
       <c r="Z616" s="2"/>
       <c r="AA616" s="2"/>
     </row>
-    <row r="617" spans="1:27" ht="12.75">
+    <row r="617" spans="1:27" ht="13.2">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
       <c r="C617" s="14"/>
@@ -20428,7 +20437,7 @@
       <c r="Z617" s="2"/>
       <c r="AA617" s="2"/>
     </row>
-    <row r="618" spans="1:27" ht="12.75">
+    <row r="618" spans="1:27" ht="13.2">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
       <c r="C618" s="14"/>
@@ -20457,7 +20466,7 @@
       <c r="Z618" s="2"/>
       <c r="AA618" s="2"/>
     </row>
-    <row r="619" spans="1:27" ht="12.75">
+    <row r="619" spans="1:27" ht="13.2">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
       <c r="C619" s="14"/>
@@ -20486,7 +20495,7 @@
       <c r="Z619" s="2"/>
       <c r="AA619" s="2"/>
     </row>
-    <row r="620" spans="1:27" ht="12.75">
+    <row r="620" spans="1:27" ht="13.2">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
       <c r="C620" s="14"/>
@@ -20515,7 +20524,7 @@
       <c r="Z620" s="2"/>
       <c r="AA620" s="2"/>
     </row>
-    <row r="621" spans="1:27" ht="12.75">
+    <row r="621" spans="1:27" ht="13.2">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
       <c r="C621" s="14"/>
@@ -20544,7 +20553,7 @@
       <c r="Z621" s="2"/>
       <c r="AA621" s="2"/>
     </row>
-    <row r="622" spans="1:27" ht="12.75">
+    <row r="622" spans="1:27" ht="13.2">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
       <c r="C622" s="14"/>
@@ -20573,7 +20582,7 @@
       <c r="Z622" s="2"/>
       <c r="AA622" s="2"/>
     </row>
-    <row r="623" spans="1:27" ht="12.75">
+    <row r="623" spans="1:27" ht="13.2">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
       <c r="C623" s="14"/>
@@ -20602,7 +20611,7 @@
       <c r="Z623" s="2"/>
       <c r="AA623" s="2"/>
     </row>
-    <row r="624" spans="1:27" ht="12.75">
+    <row r="624" spans="1:27" ht="13.2">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
       <c r="C624" s="14"/>
@@ -20631,7 +20640,7 @@
       <c r="Z624" s="2"/>
       <c r="AA624" s="2"/>
     </row>
-    <row r="625" spans="1:27" ht="12.75">
+    <row r="625" spans="1:27" ht="13.2">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
       <c r="C625" s="14"/>
@@ -20660,7 +20669,7 @@
       <c r="Z625" s="2"/>
       <c r="AA625" s="2"/>
     </row>
-    <row r="626" spans="1:27" ht="12.75">
+    <row r="626" spans="1:27" ht="13.2">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
       <c r="C626" s="14"/>
@@ -20689,7 +20698,7 @@
       <c r="Z626" s="2"/>
       <c r="AA626" s="2"/>
     </row>
-    <row r="627" spans="1:27" ht="12.75">
+    <row r="627" spans="1:27" ht="13.2">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
       <c r="C627" s="14"/>
@@ -20718,7 +20727,7 @@
       <c r="Z627" s="2"/>
       <c r="AA627" s="2"/>
     </row>
-    <row r="628" spans="1:27" ht="12.75">
+    <row r="628" spans="1:27" ht="13.2">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
       <c r="C628" s="14"/>
@@ -20747,7 +20756,7 @@
       <c r="Z628" s="2"/>
       <c r="AA628" s="2"/>
     </row>
-    <row r="629" spans="1:27" ht="12.75">
+    <row r="629" spans="1:27" ht="13.2">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
       <c r="C629" s="14"/>
@@ -20776,7 +20785,7 @@
       <c r="Z629" s="2"/>
       <c r="AA629" s="2"/>
     </row>
-    <row r="630" spans="1:27" ht="12.75">
+    <row r="630" spans="1:27" ht="13.2">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
       <c r="C630" s="14"/>
@@ -20805,7 +20814,7 @@
       <c r="Z630" s="2"/>
       <c r="AA630" s="2"/>
     </row>
-    <row r="631" spans="1:27" ht="12.75">
+    <row r="631" spans="1:27" ht="13.2">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
       <c r="C631" s="14"/>
@@ -20834,7 +20843,7 @@
       <c r="Z631" s="2"/>
       <c r="AA631" s="2"/>
     </row>
-    <row r="632" spans="1:27" ht="12.75">
+    <row r="632" spans="1:27" ht="13.2">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
       <c r="C632" s="14"/>
@@ -20863,7 +20872,7 @@
       <c r="Z632" s="2"/>
       <c r="AA632" s="2"/>
     </row>
-    <row r="633" spans="1:27" ht="12.75">
+    <row r="633" spans="1:27" ht="13.2">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
       <c r="C633" s="14"/>
@@ -20892,7 +20901,7 @@
       <c r="Z633" s="2"/>
       <c r="AA633" s="2"/>
     </row>
-    <row r="634" spans="1:27" ht="12.75">
+    <row r="634" spans="1:27" ht="13.2">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
       <c r="C634" s="14"/>
@@ -20921,7 +20930,7 @@
       <c r="Z634" s="2"/>
       <c r="AA634" s="2"/>
     </row>
-    <row r="635" spans="1:27" ht="12.75">
+    <row r="635" spans="1:27" ht="13.2">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
       <c r="C635" s="14"/>
@@ -20950,7 +20959,7 @@
       <c r="Z635" s="2"/>
       <c r="AA635" s="2"/>
     </row>
-    <row r="636" spans="1:27" ht="12.75">
+    <row r="636" spans="1:27" ht="13.2">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
       <c r="C636" s="14"/>
@@ -20979,7 +20988,7 @@
       <c r="Z636" s="2"/>
       <c r="AA636" s="2"/>
     </row>
-    <row r="637" spans="1:27" ht="12.75">
+    <row r="637" spans="1:27" ht="13.2">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
       <c r="C637" s="14"/>
@@ -21008,7 +21017,7 @@
       <c r="Z637" s="2"/>
       <c r="AA637" s="2"/>
     </row>
-    <row r="638" spans="1:27" ht="12.75">
+    <row r="638" spans="1:27" ht="13.2">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
       <c r="C638" s="14"/>
@@ -21037,7 +21046,7 @@
       <c r="Z638" s="2"/>
       <c r="AA638" s="2"/>
     </row>
-    <row r="639" spans="1:27" ht="12.75">
+    <row r="639" spans="1:27" ht="13.2">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
       <c r="C639" s="14"/>
@@ -21066,7 +21075,7 @@
       <c r="Z639" s="2"/>
       <c r="AA639" s="2"/>
     </row>
-    <row r="640" spans="1:27" ht="12.75">
+    <row r="640" spans="1:27" ht="13.2">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
       <c r="C640" s="14"/>
@@ -21095,7 +21104,7 @@
       <c r="Z640" s="2"/>
       <c r="AA640" s="2"/>
     </row>
-    <row r="641" spans="1:27" ht="12.75">
+    <row r="641" spans="1:27" ht="13.2">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
       <c r="C641" s="14"/>
@@ -21124,7 +21133,7 @@
       <c r="Z641" s="2"/>
       <c r="AA641" s="2"/>
     </row>
-    <row r="642" spans="1:27" ht="12.75">
+    <row r="642" spans="1:27" ht="13.2">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
       <c r="C642" s="14"/>
@@ -21153,7 +21162,7 @@
       <c r="Z642" s="2"/>
       <c r="AA642" s="2"/>
     </row>
-    <row r="643" spans="1:27" ht="12.75">
+    <row r="643" spans="1:27" ht="13.2">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
       <c r="C643" s="14"/>
@@ -21182,7 +21191,7 @@
       <c r="Z643" s="2"/>
       <c r="AA643" s="2"/>
     </row>
-    <row r="644" spans="1:27" ht="12.75">
+    <row r="644" spans="1:27" ht="13.2">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
       <c r="C644" s="14"/>
@@ -21211,7 +21220,7 @@
       <c r="Z644" s="2"/>
       <c r="AA644" s="2"/>
     </row>
-    <row r="645" spans="1:27" ht="12.75">
+    <row r="645" spans="1:27" ht="13.2">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
       <c r="C645" s="14"/>
@@ -21240,7 +21249,7 @@
       <c r="Z645" s="2"/>
       <c r="AA645" s="2"/>
     </row>
-    <row r="646" spans="1:27" ht="12.75">
+    <row r="646" spans="1:27" ht="13.2">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
       <c r="C646" s="14"/>
@@ -21269,7 +21278,7 @@
       <c r="Z646" s="2"/>
       <c r="AA646" s="2"/>
     </row>
-    <row r="647" spans="1:27" ht="12.75">
+    <row r="647" spans="1:27" ht="13.2">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
       <c r="C647" s="14"/>
@@ -21298,7 +21307,7 @@
       <c r="Z647" s="2"/>
       <c r="AA647" s="2"/>
     </row>
-    <row r="648" spans="1:27" ht="12.75">
+    <row r="648" spans="1:27" ht="13.2">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
       <c r="C648" s="14"/>
@@ -21327,7 +21336,7 @@
       <c r="Z648" s="2"/>
       <c r="AA648" s="2"/>
     </row>
-    <row r="649" spans="1:27" ht="12.75">
+    <row r="649" spans="1:27" ht="13.2">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
       <c r="C649" s="14"/>
@@ -21356,7 +21365,7 @@
       <c r="Z649" s="2"/>
       <c r="AA649" s="2"/>
     </row>
-    <row r="650" spans="1:27" ht="12.75">
+    <row r="650" spans="1:27" ht="13.2">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
       <c r="C650" s="14"/>
@@ -21385,7 +21394,7 @@
       <c r="Z650" s="2"/>
       <c r="AA650" s="2"/>
     </row>
-    <row r="651" spans="1:27" ht="12.75">
+    <row r="651" spans="1:27" ht="13.2">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
       <c r="C651" s="14"/>
@@ -21414,7 +21423,7 @@
       <c r="Z651" s="2"/>
       <c r="AA651" s="2"/>
     </row>
-    <row r="652" spans="1:27" ht="12.75">
+    <row r="652" spans="1:27" ht="13.2">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
       <c r="C652" s="14"/>
@@ -21443,7 +21452,7 @@
       <c r="Z652" s="2"/>
       <c r="AA652" s="2"/>
     </row>
-    <row r="653" spans="1:27" ht="12.75">
+    <row r="653" spans="1:27" ht="13.2">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
       <c r="C653" s="14"/>
@@ -21472,7 +21481,7 @@
       <c r="Z653" s="2"/>
       <c r="AA653" s="2"/>
     </row>
-    <row r="654" spans="1:27" ht="12.75">
+    <row r="654" spans="1:27" ht="13.2">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
       <c r="C654" s="14"/>
@@ -21501,7 +21510,7 @@
       <c r="Z654" s="2"/>
       <c r="AA654" s="2"/>
     </row>
-    <row r="655" spans="1:27" ht="12.75">
+    <row r="655" spans="1:27" ht="13.2">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
       <c r="C655" s="14"/>
@@ -21530,7 +21539,7 @@
       <c r="Z655" s="2"/>
       <c r="AA655" s="2"/>
     </row>
-    <row r="656" spans="1:27" ht="12.75">
+    <row r="656" spans="1:27" ht="13.2">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
       <c r="C656" s="14"/>
@@ -21559,7 +21568,7 @@
       <c r="Z656" s="2"/>
       <c r="AA656" s="2"/>
     </row>
-    <row r="657" spans="1:27" ht="12.75">
+    <row r="657" spans="1:27" ht="13.2">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
       <c r="C657" s="14"/>
@@ -21588,7 +21597,7 @@
       <c r="Z657" s="2"/>
       <c r="AA657" s="2"/>
     </row>
-    <row r="658" spans="1:27" ht="12.75">
+    <row r="658" spans="1:27" ht="13.2">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
       <c r="C658" s="14"/>
@@ -21617,7 +21626,7 @@
       <c r="Z658" s="2"/>
       <c r="AA658" s="2"/>
     </row>
-    <row r="659" spans="1:27" ht="12.75">
+    <row r="659" spans="1:27" ht="13.2">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
       <c r="C659" s="14"/>
@@ -21646,7 +21655,7 @@
       <c r="Z659" s="2"/>
       <c r="AA659" s="2"/>
     </row>
-    <row r="660" spans="1:27" ht="12.75">
+    <row r="660" spans="1:27" ht="13.2">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
       <c r="C660" s="14"/>
@@ -21675,7 +21684,7 @@
       <c r="Z660" s="2"/>
       <c r="AA660" s="2"/>
     </row>
-    <row r="661" spans="1:27" ht="12.75">
+    <row r="661" spans="1:27" ht="13.2">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
       <c r="C661" s="14"/>
@@ -21704,7 +21713,7 @@
       <c r="Z661" s="2"/>
       <c r="AA661" s="2"/>
     </row>
-    <row r="662" spans="1:27" ht="12.75">
+    <row r="662" spans="1:27" ht="13.2">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
       <c r="C662" s="14"/>
@@ -21733,7 +21742,7 @@
       <c r="Z662" s="2"/>
       <c r="AA662" s="2"/>
     </row>
-    <row r="663" spans="1:27" ht="12.75">
+    <row r="663" spans="1:27" ht="13.2">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
       <c r="C663" s="14"/>
@@ -21762,7 +21771,7 @@
       <c r="Z663" s="2"/>
       <c r="AA663" s="2"/>
     </row>
-    <row r="664" spans="1:27" ht="12.75">
+    <row r="664" spans="1:27" ht="13.2">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
       <c r="C664" s="14"/>
@@ -21791,7 +21800,7 @@
       <c r="Z664" s="2"/>
       <c r="AA664" s="2"/>
     </row>
-    <row r="665" spans="1:27" ht="12.75">
+    <row r="665" spans="1:27" ht="13.2">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
       <c r="C665" s="14"/>
@@ -21820,7 +21829,7 @@
       <c r="Z665" s="2"/>
       <c r="AA665" s="2"/>
     </row>
-    <row r="666" spans="1:27" ht="12.75">
+    <row r="666" spans="1:27" ht="13.2">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
       <c r="C666" s="14"/>
@@ -21849,7 +21858,7 @@
       <c r="Z666" s="2"/>
       <c r="AA666" s="2"/>
     </row>
-    <row r="667" spans="1:27" ht="12.75">
+    <row r="667" spans="1:27" ht="13.2">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
       <c r="C667" s="14"/>
@@ -21878,7 +21887,7 @@
       <c r="Z667" s="2"/>
       <c r="AA667" s="2"/>
     </row>
-    <row r="668" spans="1:27" ht="12.75">
+    <row r="668" spans="1:27" ht="13.2">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
       <c r="C668" s="14"/>
@@ -21907,7 +21916,7 @@
       <c r="Z668" s="2"/>
       <c r="AA668" s="2"/>
     </row>
-    <row r="669" spans="1:27" ht="12.75">
+    <row r="669" spans="1:27" ht="13.2">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
       <c r="C669" s="14"/>
@@ -21936,7 +21945,7 @@
       <c r="Z669" s="2"/>
       <c r="AA669" s="2"/>
     </row>
-    <row r="670" spans="1:27" ht="12.75">
+    <row r="670" spans="1:27" ht="13.2">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
       <c r="C670" s="14"/>
@@ -21965,7 +21974,7 @@
       <c r="Z670" s="2"/>
       <c r="AA670" s="2"/>
     </row>
-    <row r="671" spans="1:27" ht="12.75">
+    <row r="671" spans="1:27" ht="13.2">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
       <c r="C671" s="14"/>
@@ -21994,7 +22003,7 @@
       <c r="Z671" s="2"/>
       <c r="AA671" s="2"/>
     </row>
-    <row r="672" spans="1:27" ht="12.75">
+    <row r="672" spans="1:27" ht="13.2">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
       <c r="C672" s="14"/>
@@ -22023,7 +22032,7 @@
       <c r="Z672" s="2"/>
       <c r="AA672" s="2"/>
     </row>
-    <row r="673" spans="1:27" ht="12.75">
+    <row r="673" spans="1:27" ht="13.2">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
       <c r="C673" s="14"/>
@@ -22052,7 +22061,7 @@
       <c r="Z673" s="2"/>
       <c r="AA673" s="2"/>
     </row>
-    <row r="674" spans="1:27" ht="12.75">
+    <row r="674" spans="1:27" ht="13.2">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
       <c r="C674" s="14"/>
@@ -22081,7 +22090,7 @@
       <c r="Z674" s="2"/>
       <c r="AA674" s="2"/>
     </row>
-    <row r="675" spans="1:27" ht="12.75">
+    <row r="675" spans="1:27" ht="13.2">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
       <c r="C675" s="14"/>
@@ -22110,7 +22119,7 @@
       <c r="Z675" s="2"/>
       <c r="AA675" s="2"/>
     </row>
-    <row r="676" spans="1:27" ht="12.75">
+    <row r="676" spans="1:27" ht="13.2">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
       <c r="C676" s="14"/>
@@ -22139,7 +22148,7 @@
       <c r="Z676" s="2"/>
       <c r="AA676" s="2"/>
     </row>
-    <row r="677" spans="1:27" ht="12.75">
+    <row r="677" spans="1:27" ht="13.2">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
       <c r="C677" s="14"/>
@@ -22168,7 +22177,7 @@
       <c r="Z677" s="2"/>
       <c r="AA677" s="2"/>
     </row>
-    <row r="678" spans="1:27" ht="12.75">
+    <row r="678" spans="1:27" ht="13.2">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
       <c r="C678" s="14"/>
@@ -22197,7 +22206,7 @@
       <c r="Z678" s="2"/>
       <c r="AA678" s="2"/>
     </row>
-    <row r="679" spans="1:27" ht="12.75">
+    <row r="679" spans="1:27" ht="13.2">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
       <c r="C679" s="14"/>
@@ -22226,7 +22235,7 @@
       <c r="Z679" s="2"/>
       <c r="AA679" s="2"/>
     </row>
-    <row r="680" spans="1:27" ht="12.75">
+    <row r="680" spans="1:27" ht="13.2">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
       <c r="C680" s="14"/>
@@ -22255,7 +22264,7 @@
       <c r="Z680" s="2"/>
       <c r="AA680" s="2"/>
     </row>
-    <row r="681" spans="1:27" ht="12.75">
+    <row r="681" spans="1:27" ht="13.2">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
       <c r="C681" s="14"/>
@@ -22284,7 +22293,7 @@
       <c r="Z681" s="2"/>
       <c r="AA681" s="2"/>
     </row>
-    <row r="682" spans="1:27" ht="12.75">
+    <row r="682" spans="1:27" ht="13.2">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
       <c r="C682" s="14"/>
@@ -22313,7 +22322,7 @@
       <c r="Z682" s="2"/>
       <c r="AA682" s="2"/>
     </row>
-    <row r="683" spans="1:27" ht="12.75">
+    <row r="683" spans="1:27" ht="13.2">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
       <c r="C683" s="14"/>
@@ -22342,7 +22351,7 @@
       <c r="Z683" s="2"/>
       <c r="AA683" s="2"/>
     </row>
-    <row r="684" spans="1:27" ht="12.75">
+    <row r="684" spans="1:27" ht="13.2">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
       <c r="C684" s="14"/>
@@ -22371,7 +22380,7 @@
       <c r="Z684" s="2"/>
       <c r="AA684" s="2"/>
     </row>
-    <row r="685" spans="1:27" ht="12.75">
+    <row r="685" spans="1:27" ht="13.2">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
       <c r="C685" s="14"/>
@@ -22400,7 +22409,7 @@
       <c r="Z685" s="2"/>
       <c r="AA685" s="2"/>
     </row>
-    <row r="686" spans="1:27" ht="12.75">
+    <row r="686" spans="1:27" ht="13.2">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
       <c r="C686" s="14"/>
@@ -22429,7 +22438,7 @@
       <c r="Z686" s="2"/>
       <c r="AA686" s="2"/>
     </row>
-    <row r="687" spans="1:27" ht="12.75">
+    <row r="687" spans="1:27" ht="13.2">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
       <c r="C687" s="14"/>
@@ -22458,7 +22467,7 @@
       <c r="Z687" s="2"/>
       <c r="AA687" s="2"/>
     </row>
-    <row r="688" spans="1:27" ht="12.75">
+    <row r="688" spans="1:27" ht="13.2">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
       <c r="C688" s="14"/>
@@ -22487,7 +22496,7 @@
       <c r="Z688" s="2"/>
       <c r="AA688" s="2"/>
     </row>
-    <row r="689" spans="1:27" ht="12.75">
+    <row r="689" spans="1:27" ht="13.2">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
       <c r="C689" s="14"/>
@@ -22516,7 +22525,7 @@
       <c r="Z689" s="2"/>
       <c r="AA689" s="2"/>
     </row>
-    <row r="690" spans="1:27" ht="12.75">
+    <row r="690" spans="1:27" ht="13.2">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
       <c r="C690" s="14"/>
@@ -22545,7 +22554,7 @@
       <c r="Z690" s="2"/>
       <c r="AA690" s="2"/>
     </row>
-    <row r="691" spans="1:27" ht="12.75">
+    <row r="691" spans="1:27" ht="13.2">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
       <c r="C691" s="14"/>
@@ -22574,7 +22583,7 @@
       <c r="Z691" s="2"/>
       <c r="AA691" s="2"/>
     </row>
-    <row r="692" spans="1:27" ht="12.75">
+    <row r="692" spans="1:27" ht="13.2">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
       <c r="C692" s="14"/>
@@ -22603,7 +22612,7 @@
       <c r="Z692" s="2"/>
       <c r="AA692" s="2"/>
     </row>
-    <row r="693" spans="1:27" ht="12.75">
+    <row r="693" spans="1:27" ht="13.2">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
       <c r="C693" s="14"/>
@@ -22632,7 +22641,7 @@
       <c r="Z693" s="2"/>
       <c r="AA693" s="2"/>
     </row>
-    <row r="694" spans="1:27" ht="12.75">
+    <row r="694" spans="1:27" ht="13.2">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
       <c r="C694" s="14"/>
@@ -22661,7 +22670,7 @@
       <c r="Z694" s="2"/>
       <c r="AA694" s="2"/>
     </row>
-    <row r="695" spans="1:27" ht="12.75">
+    <row r="695" spans="1:27" ht="13.2">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
       <c r="C695" s="14"/>
@@ -22690,7 +22699,7 @@
       <c r="Z695" s="2"/>
       <c r="AA695" s="2"/>
     </row>
-    <row r="696" spans="1:27" ht="12.75">
+    <row r="696" spans="1:27" ht="13.2">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
       <c r="C696" s="14"/>
@@ -22719,7 +22728,7 @@
       <c r="Z696" s="2"/>
       <c r="AA696" s="2"/>
     </row>
-    <row r="697" spans="1:27" ht="12.75">
+    <row r="697" spans="1:27" ht="13.2">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
       <c r="C697" s="14"/>
@@ -22748,7 +22757,7 @@
       <c r="Z697" s="2"/>
       <c r="AA697" s="2"/>
     </row>
-    <row r="698" spans="1:27" ht="12.75">
+    <row r="698" spans="1:27" ht="13.2">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
       <c r="C698" s="14"/>
@@ -22777,7 +22786,7 @@
       <c r="Z698" s="2"/>
       <c r="AA698" s="2"/>
     </row>
-    <row r="699" spans="1:27" ht="12.75">
+    <row r="699" spans="1:27" ht="13.2">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
       <c r="C699" s="14"/>
@@ -22806,7 +22815,7 @@
       <c r="Z699" s="2"/>
       <c r="AA699" s="2"/>
     </row>
-    <row r="700" spans="1:27" ht="12.75">
+    <row r="700" spans="1:27" ht="13.2">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
       <c r="C700" s="14"/>
@@ -22835,7 +22844,7 @@
       <c r="Z700" s="2"/>
       <c r="AA700" s="2"/>
     </row>
-    <row r="701" spans="1:27" ht="12.75">
+    <row r="701" spans="1:27" ht="13.2">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
       <c r="C701" s="14"/>
@@ -22864,7 +22873,7 @@
       <c r="Z701" s="2"/>
       <c r="AA701" s="2"/>
     </row>
-    <row r="702" spans="1:27" ht="12.75">
+    <row r="702" spans="1:27" ht="13.2">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
       <c r="C702" s="14"/>
@@ -22893,7 +22902,7 @@
       <c r="Z702" s="2"/>
       <c r="AA702" s="2"/>
     </row>
-    <row r="703" spans="1:27" ht="12.75">
+    <row r="703" spans="1:27" ht="13.2">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
       <c r="C703" s="14"/>
@@ -22922,7 +22931,7 @@
       <c r="Z703" s="2"/>
       <c r="AA703" s="2"/>
     </row>
-    <row r="704" spans="1:27" ht="12.75">
+    <row r="704" spans="1:27" ht="13.2">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
       <c r="C704" s="14"/>
@@ -22951,7 +22960,7 @@
       <c r="Z704" s="2"/>
       <c r="AA704" s="2"/>
     </row>
-    <row r="705" spans="1:27" ht="12.75">
+    <row r="705" spans="1:27" ht="13.2">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
       <c r="C705" s="14"/>
@@ -22980,7 +22989,7 @@
       <c r="Z705" s="2"/>
       <c r="AA705" s="2"/>
     </row>
-    <row r="706" spans="1:27" ht="12.75">
+    <row r="706" spans="1:27" ht="13.2">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
       <c r="C706" s="14"/>
@@ -23009,7 +23018,7 @@
       <c r="Z706" s="2"/>
       <c r="AA706" s="2"/>
     </row>
-    <row r="707" spans="1:27" ht="12.75">
+    <row r="707" spans="1:27" ht="13.2">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
       <c r="C707" s="14"/>
@@ -23038,7 +23047,7 @@
       <c r="Z707" s="2"/>
       <c r="AA707" s="2"/>
     </row>
-    <row r="708" spans="1:27" ht="12.75">
+    <row r="708" spans="1:27" ht="13.2">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
       <c r="C708" s="14"/>
@@ -23067,7 +23076,7 @@
       <c r="Z708" s="2"/>
       <c r="AA708" s="2"/>
     </row>
-    <row r="709" spans="1:27" ht="12.75">
+    <row r="709" spans="1:27" ht="13.2">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
       <c r="C709" s="14"/>
@@ -23096,7 +23105,7 @@
       <c r="Z709" s="2"/>
       <c r="AA709" s="2"/>
     </row>
-    <row r="710" spans="1:27" ht="12.75">
+    <row r="710" spans="1:27" ht="13.2">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
       <c r="C710" s="14"/>
@@ -23125,7 +23134,7 @@
       <c r="Z710" s="2"/>
       <c r="AA710" s="2"/>
     </row>
-    <row r="711" spans="1:27" ht="12.75">
+    <row r="711" spans="1:27" ht="13.2">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
       <c r="C711" s="14"/>
@@ -23154,7 +23163,7 @@
       <c r="Z711" s="2"/>
       <c r="AA711" s="2"/>
     </row>
-    <row r="712" spans="1:27" ht="12.75">
+    <row r="712" spans="1:27" ht="13.2">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
       <c r="C712" s="14"/>
@@ -23183,7 +23192,7 @@
       <c r="Z712" s="2"/>
       <c r="AA712" s="2"/>
     </row>
-    <row r="713" spans="1:27" ht="12.75">
+    <row r="713" spans="1:27" ht="13.2">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
       <c r="C713" s="14"/>
@@ -23212,7 +23221,7 @@
       <c r="Z713" s="2"/>
       <c r="AA713" s="2"/>
     </row>
-    <row r="714" spans="1:27" ht="12.75">
+    <row r="714" spans="1:27" ht="13.2">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
       <c r="C714" s="14"/>
@@ -23241,7 +23250,7 @@
       <c r="Z714" s="2"/>
       <c r="AA714" s="2"/>
     </row>
-    <row r="715" spans="1:27" ht="12.75">
+    <row r="715" spans="1:27" ht="13.2">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
       <c r="C715" s="14"/>
@@ -23270,7 +23279,7 @@
       <c r="Z715" s="2"/>
       <c r="AA715" s="2"/>
     </row>
-    <row r="716" spans="1:27" ht="12.75">
+    <row r="716" spans="1:27" ht="13.2">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
       <c r="C716" s="14"/>
@@ -23299,7 +23308,7 @@
       <c r="Z716" s="2"/>
       <c r="AA716" s="2"/>
     </row>
-    <row r="717" spans="1:27" ht="12.75">
+    <row r="717" spans="1:27" ht="13.2">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
       <c r="C717" s="14"/>
@@ -23328,7 +23337,7 @@
       <c r="Z717" s="2"/>
       <c r="AA717" s="2"/>
     </row>
-    <row r="718" spans="1:27" ht="12.75">
+    <row r="718" spans="1:27" ht="13.2">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
       <c r="C718" s="14"/>
@@ -23357,7 +23366,7 @@
       <c r="Z718" s="2"/>
       <c r="AA718" s="2"/>
     </row>
-    <row r="719" spans="1:27" ht="12.75">
+    <row r="719" spans="1:27" ht="13.2">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
       <c r="C719" s="14"/>
@@ -23386,7 +23395,7 @@
       <c r="Z719" s="2"/>
       <c r="AA719" s="2"/>
     </row>
-    <row r="720" spans="1:27" ht="12.75">
+    <row r="720" spans="1:27" ht="13.2">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
       <c r="C720" s="14"/>
@@ -23415,7 +23424,7 @@
       <c r="Z720" s="2"/>
       <c r="AA720" s="2"/>
     </row>
-    <row r="721" spans="1:27" ht="12.75">
+    <row r="721" spans="1:27" ht="13.2">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
       <c r="C721" s="14"/>
@@ -23444,7 +23453,7 @@
       <c r="Z721" s="2"/>
       <c r="AA721" s="2"/>
     </row>
-    <row r="722" spans="1:27" ht="12.75">
+    <row r="722" spans="1:27" ht="13.2">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
       <c r="C722" s="14"/>
@@ -23473,7 +23482,7 @@
       <c r="Z722" s="2"/>
       <c r="AA722" s="2"/>
     </row>
-    <row r="723" spans="1:27" ht="12.75">
+    <row r="723" spans="1:27" ht="13.2">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
       <c r="C723" s="14"/>
@@ -23502,7 +23511,7 @@
       <c r="Z723" s="2"/>
       <c r="AA723" s="2"/>
     </row>
-    <row r="724" spans="1:27" ht="12.75">
+    <row r="724" spans="1:27" ht="13.2">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
       <c r="C724" s="14"/>
@@ -23531,7 +23540,7 @@
       <c r="Z724" s="2"/>
       <c r="AA724" s="2"/>
     </row>
-    <row r="725" spans="1:27" ht="12.75">
+    <row r="725" spans="1:27" ht="13.2">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
       <c r="C725" s="14"/>
@@ -23560,7 +23569,7 @@
       <c r="Z725" s="2"/>
       <c r="AA725" s="2"/>
     </row>
-    <row r="726" spans="1:27" ht="12.75">
+    <row r="726" spans="1:27" ht="13.2">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
       <c r="C726" s="14"/>
@@ -23589,7 +23598,7 @@
       <c r="Z726" s="2"/>
       <c r="AA726" s="2"/>
     </row>
-    <row r="727" spans="1:27" ht="12.75">
+    <row r="727" spans="1:27" ht="13.2">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
       <c r="C727" s="14"/>
@@ -23618,7 +23627,7 @@
       <c r="Z727" s="2"/>
       <c r="AA727" s="2"/>
     </row>
-    <row r="728" spans="1:27" ht="12.75">
+    <row r="728" spans="1:27" ht="13.2">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
       <c r="C728" s="14"/>
@@ -23647,7 +23656,7 @@
       <c r="Z728" s="2"/>
       <c r="AA728" s="2"/>
     </row>
-    <row r="729" spans="1:27" ht="12.75">
+    <row r="729" spans="1:27" ht="13.2">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
       <c r="C729" s="14"/>
@@ -23676,7 +23685,7 @@
       <c r="Z729" s="2"/>
       <c r="AA729" s="2"/>
     </row>
-    <row r="730" spans="1:27" ht="12.75">
+    <row r="730" spans="1:27" ht="13.2">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
       <c r="C730" s="14"/>
@@ -23705,7 +23714,7 @@
       <c r="Z730" s="2"/>
       <c r="AA730" s="2"/>
     </row>
-    <row r="731" spans="1:27" ht="12.75">
+    <row r="731" spans="1:27" ht="13.2">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
       <c r="C731" s="14"/>
@@ -23734,7 +23743,7 @@
       <c r="Z731" s="2"/>
       <c r="AA731" s="2"/>
     </row>
-    <row r="732" spans="1:27" ht="12.75">
+    <row r="732" spans="1:27" ht="13.2">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
       <c r="C732" s="14"/>
@@ -23763,7 +23772,7 @@
       <c r="Z732" s="2"/>
       <c r="AA732" s="2"/>
     </row>
-    <row r="733" spans="1:27" ht="12.75">
+    <row r="733" spans="1:27" ht="13.2">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
       <c r="C733" s="14"/>
@@ -23792,7 +23801,7 @@
       <c r="Z733" s="2"/>
       <c r="AA733" s="2"/>
     </row>
-    <row r="734" spans="1:27" ht="12.75">
+    <row r="734" spans="1:27" ht="13.2">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
       <c r="C734" s="14"/>
@@ -23821,7 +23830,7 @@
       <c r="Z734" s="2"/>
       <c r="AA734" s="2"/>
     </row>
-    <row r="735" spans="1:27" ht="12.75">
+    <row r="735" spans="1:27" ht="13.2">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
       <c r="C735" s="14"/>
@@ -23850,7 +23859,7 @@
       <c r="Z735" s="2"/>
       <c r="AA735" s="2"/>
     </row>
-    <row r="736" spans="1:27" ht="12.75">
+    <row r="736" spans="1:27" ht="13.2">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
       <c r="C736" s="14"/>
@@ -23879,7 +23888,7 @@
       <c r="Z736" s="2"/>
       <c r="AA736" s="2"/>
     </row>
-    <row r="737" spans="1:27" ht="12.75">
+    <row r="737" spans="1:27" ht="13.2">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
       <c r="C737" s="14"/>
@@ -23908,7 +23917,7 @@
       <c r="Z737" s="2"/>
       <c r="AA737" s="2"/>
     </row>
-    <row r="738" spans="1:27" ht="12.75">
+    <row r="738" spans="1:27" ht="13.2">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
       <c r="C738" s="14"/>
@@ -23937,7 +23946,7 @@
       <c r="Z738" s="2"/>
       <c r="AA738" s="2"/>
     </row>
-    <row r="739" spans="1:27" ht="12.75">
+    <row r="739" spans="1:27" ht="13.2">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
       <c r="C739" s="14"/>
@@ -23966,7 +23975,7 @@
       <c r="Z739" s="2"/>
       <c r="AA739" s="2"/>
     </row>
-    <row r="740" spans="1:27" ht="12.75">
+    <row r="740" spans="1:27" ht="13.2">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
       <c r="C740" s="14"/>
@@ -23995,7 +24004,7 @@
       <c r="Z740" s="2"/>
       <c r="AA740" s="2"/>
     </row>
-    <row r="741" spans="1:27" ht="12.75">
+    <row r="741" spans="1:27" ht="13.2">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
       <c r="C741" s="14"/>
@@ -24024,7 +24033,7 @@
       <c r="Z741" s="2"/>
       <c r="AA741" s="2"/>
     </row>
-    <row r="742" spans="1:27" ht="12.75">
+    <row r="742" spans="1:27" ht="13.2">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
       <c r="C742" s="14"/>
@@ -24053,7 +24062,7 @@
       <c r="Z742" s="2"/>
       <c r="AA742" s="2"/>
     </row>
-    <row r="743" spans="1:27" ht="12.75">
+    <row r="743" spans="1:27" ht="13.2">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
       <c r="C743" s="14"/>
@@ -24082,7 +24091,7 @@
       <c r="Z743" s="2"/>
       <c r="AA743" s="2"/>
     </row>
-    <row r="744" spans="1:27" ht="12.75">
+    <row r="744" spans="1:27" ht="13.2">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
       <c r="C744" s="14"/>
@@ -24111,7 +24120,7 @@
       <c r="Z744" s="2"/>
       <c r="AA744" s="2"/>
     </row>
-    <row r="745" spans="1:27" ht="12.75">
+    <row r="745" spans="1:27" ht="13.2">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
       <c r="C745" s="14"/>
@@ -24140,7 +24149,7 @@
       <c r="Z745" s="2"/>
       <c r="AA745" s="2"/>
     </row>
-    <row r="746" spans="1:27" ht="12.75">
+    <row r="746" spans="1:27" ht="13.2">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
       <c r="C746" s="14"/>
@@ -24169,7 +24178,7 @@
       <c r="Z746" s="2"/>
       <c r="AA746" s="2"/>
     </row>
-    <row r="747" spans="1:27" ht="12.75">
+    <row r="747" spans="1:27" ht="13.2">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
       <c r="C747" s="14"/>
@@ -24198,7 +24207,7 @@
       <c r="Z747" s="2"/>
       <c r="AA747" s="2"/>
     </row>
-    <row r="748" spans="1:27" ht="12.75">
+    <row r="748" spans="1:27" ht="13.2">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
       <c r="C748" s="14"/>
@@ -24227,7 +24236,7 @@
       <c r="Z748" s="2"/>
       <c r="AA748" s="2"/>
     </row>
-    <row r="749" spans="1:27" ht="12.75">
+    <row r="749" spans="1:27" ht="13.2">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
       <c r="C749" s="14"/>
@@ -24256,7 +24265,7 @@
       <c r="Z749" s="2"/>
       <c r="AA749" s="2"/>
     </row>
-    <row r="750" spans="1:27" ht="12.75">
+    <row r="750" spans="1:27" ht="13.2">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
       <c r="C750" s="14"/>
@@ -24285,7 +24294,7 @@
       <c r="Z750" s="2"/>
       <c r="AA750" s="2"/>
     </row>
-    <row r="751" spans="1:27" ht="12.75">
+    <row r="751" spans="1:27" ht="13.2">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
       <c r="C751" s="14"/>
@@ -24314,7 +24323,7 @@
       <c r="Z751" s="2"/>
       <c r="AA751" s="2"/>
     </row>
-    <row r="752" spans="1:27" ht="12.75">
+    <row r="752" spans="1:27" ht="13.2">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
       <c r="C752" s="14"/>
@@ -24343,7 +24352,7 @@
       <c r="Z752" s="2"/>
       <c r="AA752" s="2"/>
     </row>
-    <row r="753" spans="1:27" ht="12.75">
+    <row r="753" spans="1:27" ht="13.2">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
       <c r="C753" s="14"/>
@@ -24372,7 +24381,7 @@
       <c r="Z753" s="2"/>
       <c r="AA753" s="2"/>
     </row>
-    <row r="754" spans="1:27" ht="12.75">
+    <row r="754" spans="1:27" ht="13.2">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
       <c r="C754" s="14"/>
@@ -24401,7 +24410,7 @@
       <c r="Z754" s="2"/>
       <c r="AA754" s="2"/>
     </row>
-    <row r="755" spans="1:27" ht="12.75">
+    <row r="755" spans="1:27" ht="13.2">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
       <c r="C755" s="14"/>
@@ -24430,7 +24439,7 @@
       <c r="Z755" s="2"/>
       <c r="AA755" s="2"/>
     </row>
-    <row r="756" spans="1:27" ht="12.75">
+    <row r="756" spans="1:27" ht="13.2">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
       <c r="C756" s="14"/>
@@ -24459,7 +24468,7 @@
       <c r="Z756" s="2"/>
       <c r="AA756" s="2"/>
     </row>
-    <row r="757" spans="1:27" ht="12.75">
+    <row r="757" spans="1:27" ht="13.2">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
       <c r="C757" s="14"/>
@@ -24488,7 +24497,7 @@
       <c r="Z757" s="2"/>
       <c r="AA757" s="2"/>
     </row>
-    <row r="758" spans="1:27" ht="12.75">
+    <row r="758" spans="1:27" ht="13.2">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
       <c r="C758" s="14"/>
@@ -24517,7 +24526,7 @@
       <c r="Z758" s="2"/>
       <c r="AA758" s="2"/>
     </row>
-    <row r="759" spans="1:27" ht="12.75">
+    <row r="759" spans="1:27" ht="13.2">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
       <c r="C759" s="14"/>
@@ -24546,7 +24555,7 @@
       <c r="Z759" s="2"/>
       <c r="AA759" s="2"/>
     </row>
-    <row r="760" spans="1:27" ht="12.75">
+    <row r="760" spans="1:27" ht="13.2">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
       <c r="C760" s="14"/>
@@ -24575,7 +24584,7 @@
       <c r="Z760" s="2"/>
       <c r="AA760" s="2"/>
     </row>
-    <row r="761" spans="1:27" ht="12.75">
+    <row r="761" spans="1:27" ht="13.2">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
       <c r="C761" s="14"/>
@@ -24604,7 +24613,7 @@
       <c r="Z761" s="2"/>
       <c r="AA761" s="2"/>
     </row>
-    <row r="762" spans="1:27" ht="12.75">
+    <row r="762" spans="1:27" ht="13.2">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
       <c r="C762" s="14"/>
@@ -24633,7 +24642,7 @@
       <c r="Z762" s="2"/>
       <c r="AA762" s="2"/>
     </row>
-    <row r="763" spans="1:27" ht="12.75">
+    <row r="763" spans="1:27" ht="13.2">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
       <c r="C763" s="14"/>
@@ -24662,7 +24671,7 @@
       <c r="Z763" s="2"/>
       <c r="AA763" s="2"/>
     </row>
-    <row r="764" spans="1:27" ht="12.75">
+    <row r="764" spans="1:27" ht="13.2">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
       <c r="C764" s="14"/>
@@ -24691,7 +24700,7 @@
       <c r="Z764" s="2"/>
       <c r="AA764" s="2"/>
     </row>
-    <row r="765" spans="1:27" ht="12.75">
+    <row r="765" spans="1:27" ht="13.2">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
       <c r="C765" s="14"/>
@@ -24720,7 +24729,7 @@
       <c r="Z765" s="2"/>
       <c r="AA765" s="2"/>
     </row>
-    <row r="766" spans="1:27" ht="12.75">
+    <row r="766" spans="1:27" ht="13.2">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
       <c r="C766" s="14"/>
@@ -24749,7 +24758,7 @@
       <c r="Z766" s="2"/>
       <c r="AA766" s="2"/>
     </row>
-    <row r="767" spans="1:27" ht="12.75">
+    <row r="767" spans="1:27" ht="13.2">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
       <c r="C767" s="14"/>
@@ -24778,7 +24787,7 @@
       <c r="Z767" s="2"/>
       <c r="AA767" s="2"/>
     </row>
-    <row r="768" spans="1:27" ht="12.75">
+    <row r="768" spans="1:27" ht="13.2">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
       <c r="C768" s="14"/>
@@ -24807,7 +24816,7 @@
       <c r="Z768" s="2"/>
       <c r="AA768" s="2"/>
     </row>
-    <row r="769" spans="1:27" ht="12.75">
+    <row r="769" spans="1:27" ht="13.2">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
       <c r="C769" s="14"/>
@@ -24836,7 +24845,7 @@
       <c r="Z769" s="2"/>
       <c r="AA769" s="2"/>
     </row>
-    <row r="770" spans="1:27" ht="12.75">
+    <row r="770" spans="1:27" ht="13.2">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
       <c r="C770" s="14"/>
@@ -24865,7 +24874,7 @@
       <c r="Z770" s="2"/>
       <c r="AA770" s="2"/>
     </row>
-    <row r="771" spans="1:27" ht="12.75">
+    <row r="771" spans="1:27" ht="13.2">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
       <c r="C771" s="14"/>
@@ -24894,7 +24903,7 @@
       <c r="Z771" s="2"/>
       <c r="AA771" s="2"/>
     </row>
-    <row r="772" spans="1:27" ht="12.75">
+    <row r="772" spans="1:27" ht="13.2">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
       <c r="C772" s="14"/>
@@ -24923,7 +24932,7 @@
       <c r="Z772" s="2"/>
       <c r="AA772" s="2"/>
     </row>
-    <row r="773" spans="1:27" ht="12.75">
+    <row r="773" spans="1:27" ht="13.2">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
       <c r="C773" s="14"/>
@@ -24952,7 +24961,7 @@
       <c r="Z773" s="2"/>
       <c r="AA773" s="2"/>
     </row>
-    <row r="774" spans="1:27" ht="12.75">
+    <row r="774" spans="1:27" ht="13.2">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
       <c r="C774" s="14"/>
@@ -24981,7 +24990,7 @@
       <c r="Z774" s="2"/>
       <c r="AA774" s="2"/>
     </row>
-    <row r="775" spans="1:27" ht="12.75">
+    <row r="775" spans="1:27" ht="13.2">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
       <c r="C775" s="14"/>
@@ -25010,7 +25019,7 @@
       <c r="Z775" s="2"/>
       <c r="AA775" s="2"/>
     </row>
-    <row r="776" spans="1:27" ht="12.75">
+    <row r="776" spans="1:27" ht="13.2">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
       <c r="C776" s="14"/>
@@ -25039,7 +25048,7 @@
       <c r="Z776" s="2"/>
       <c r="AA776" s="2"/>
     </row>
-    <row r="777" spans="1:27" ht="12.75">
+    <row r="777" spans="1:27" ht="13.2">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
       <c r="C777" s="14"/>
@@ -25068,7 +25077,7 @@
       <c r="Z777" s="2"/>
       <c r="AA777" s="2"/>
     </row>
-    <row r="778" spans="1:27" ht="12.75">
+    <row r="778" spans="1:27" ht="13.2">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
       <c r="C778" s="14"/>
@@ -25097,7 +25106,7 @@
       <c r="Z778" s="2"/>
       <c r="AA778" s="2"/>
     </row>
-    <row r="779" spans="1:27" ht="12.75">
+    <row r="779" spans="1:27" ht="13.2">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
       <c r="C779" s="14"/>
@@ -25126,7 +25135,7 @@
       <c r="Z779" s="2"/>
       <c r="AA779" s="2"/>
     </row>
-    <row r="780" spans="1:27" ht="12.75">
+    <row r="780" spans="1:27" ht="13.2">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
       <c r="C780" s="14"/>
@@ -25155,7 +25164,7 @@
       <c r="Z780" s="2"/>
       <c r="AA780" s="2"/>
     </row>
-    <row r="781" spans="1:27" ht="12.75">
+    <row r="781" spans="1:27" ht="13.2">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
       <c r="C781" s="14"/>
@@ -25184,7 +25193,7 @@
       <c r="Z781" s="2"/>
       <c r="AA781" s="2"/>
     </row>
-    <row r="782" spans="1:27" ht="12.75">
+    <row r="782" spans="1:27" ht="13.2">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
       <c r="C782" s="14"/>
@@ -25213,7 +25222,7 @@
       <c r="Z782" s="2"/>
       <c r="AA782" s="2"/>
     </row>
-    <row r="783" spans="1:27" ht="12.75">
+    <row r="783" spans="1:27" ht="13.2">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
       <c r="C783" s="14"/>
@@ -25242,7 +25251,7 @@
       <c r="Z783" s="2"/>
       <c r="AA783" s="2"/>
     </row>
-    <row r="784" spans="1:27" ht="12.75">
+    <row r="784" spans="1:27" ht="13.2">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
       <c r="C784" s="14"/>
@@ -25271,7 +25280,7 @@
       <c r="Z784" s="2"/>
       <c r="AA784" s="2"/>
     </row>
-    <row r="785" spans="1:27" ht="12.75">
+    <row r="785" spans="1:27" ht="13.2">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
       <c r="C785" s="14"/>
@@ -25300,7 +25309,7 @@
       <c r="Z785" s="2"/>
       <c r="AA785" s="2"/>
     </row>
-    <row r="786" spans="1:27" ht="12.75">
+    <row r="786" spans="1:27" ht="13.2">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
       <c r="C786" s="14"/>
@@ -25329,7 +25338,7 @@
       <c r="Z786" s="2"/>
       <c r="AA786" s="2"/>
     </row>
-    <row r="787" spans="1:27" ht="12.75">
+    <row r="787" spans="1:27" ht="13.2">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
       <c r="C787" s="14"/>
@@ -25358,7 +25367,7 @@
       <c r="Z787" s="2"/>
       <c r="AA787" s="2"/>
     </row>
-    <row r="788" spans="1:27" ht="12.75">
+    <row r="788" spans="1:27" ht="13.2">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
       <c r="C788" s="14"/>
@@ -25387,7 +25396,7 @@
       <c r="Z788" s="2"/>
       <c r="AA788" s="2"/>
     </row>
-    <row r="789" spans="1:27" ht="12.75">
+    <row r="789" spans="1:27" ht="13.2">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
       <c r="C789" s="14"/>
@@ -25416,7 +25425,7 @@
       <c r="Z789" s="2"/>
       <c r="AA789" s="2"/>
     </row>
-    <row r="790" spans="1:27" ht="12.75">
+    <row r="790" spans="1:27" ht="13.2">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
       <c r="C790" s="14"/>
@@ -25445,7 +25454,7 @@
       <c r="Z790" s="2"/>
       <c r="AA790" s="2"/>
     </row>
-    <row r="791" spans="1:27" ht="12.75">
+    <row r="791" spans="1:27" ht="13.2">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
       <c r="C791" s="14"/>
@@ -25474,7 +25483,7 @@
       <c r="Z791" s="2"/>
       <c r="AA791" s="2"/>
     </row>
-    <row r="792" spans="1:27" ht="12.75">
+    <row r="792" spans="1:27" ht="13.2">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
       <c r="C792" s="14"/>
@@ -25503,7 +25512,7 @@
       <c r="Z792" s="2"/>
       <c r="AA792" s="2"/>
     </row>
-    <row r="793" spans="1:27" ht="12.75">
+    <row r="793" spans="1:27" ht="13.2">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
       <c r="C793" s="14"/>
@@ -25532,7 +25541,7 @@
       <c r="Z793" s="2"/>
       <c r="AA793" s="2"/>
     </row>
-    <row r="794" spans="1:27" ht="12.75">
+    <row r="794" spans="1:27" ht="13.2">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
       <c r="C794" s="14"/>
@@ -25561,7 +25570,7 @@
       <c r="Z794" s="2"/>
       <c r="AA794" s="2"/>
     </row>
-    <row r="795" spans="1:27" ht="12.75">
+    <row r="795" spans="1:27" ht="13.2">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
       <c r="C795" s="14"/>
@@ -25590,7 +25599,7 @@
       <c r="Z795" s="2"/>
       <c r="AA795" s="2"/>
     </row>
-    <row r="796" spans="1:27" ht="12.75">
+    <row r="796" spans="1:27" ht="13.2">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
       <c r="C796" s="14"/>
@@ -25619,7 +25628,7 @@
       <c r="Z796" s="2"/>
       <c r="AA796" s="2"/>
     </row>
-    <row r="797" spans="1:27" ht="12.75">
+    <row r="797" spans="1:27" ht="13.2">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
       <c r="C797" s="14"/>
@@ -25648,7 +25657,7 @@
       <c r="Z797" s="2"/>
       <c r="AA797" s="2"/>
     </row>
-    <row r="798" spans="1:27" ht="12.75">
+    <row r="798" spans="1:27" ht="13.2">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
       <c r="C798" s="14"/>
@@ -25677,7 +25686,7 @@
       <c r="Z798" s="2"/>
       <c r="AA798" s="2"/>
     </row>
-    <row r="799" spans="1:27" ht="12.75">
+    <row r="799" spans="1:27" ht="13.2">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
       <c r="C799" s="14"/>
@@ -25706,7 +25715,7 @@
       <c r="Z799" s="2"/>
       <c r="AA799" s="2"/>
     </row>
-    <row r="800" spans="1:27" ht="12.75">
+    <row r="800" spans="1:27" ht="13.2">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
       <c r="C800" s="14"/>
@@ -25735,7 +25744,7 @@
       <c r="Z800" s="2"/>
       <c r="AA800" s="2"/>
     </row>
-    <row r="801" spans="1:27" ht="12.75">
+    <row r="801" spans="1:27" ht="13.2">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
       <c r="C801" s="14"/>
@@ -25764,7 +25773,7 @@
       <c r="Z801" s="2"/>
       <c r="AA801" s="2"/>
     </row>
-    <row r="802" spans="1:27" ht="12.75">
+    <row r="802" spans="1:27" ht="13.2">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
       <c r="C802" s="14"/>
@@ -25793,7 +25802,7 @@
       <c r="Z802" s="2"/>
       <c r="AA802" s="2"/>
     </row>
-    <row r="803" spans="1:27" ht="12.75">
+    <row r="803" spans="1:27" ht="13.2">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
       <c r="C803" s="14"/>
@@ -25822,7 +25831,7 @@
       <c r="Z803" s="2"/>
       <c r="AA803" s="2"/>
     </row>
-    <row r="804" spans="1:27" ht="12.75">
+    <row r="804" spans="1:27" ht="13.2">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
       <c r="C804" s="14"/>
@@ -25851,7 +25860,7 @@
       <c r="Z804" s="2"/>
       <c r="AA804" s="2"/>
     </row>
-    <row r="805" spans="1:27" ht="12.75">
+    <row r="805" spans="1:27" ht="13.2">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
       <c r="C805" s="14"/>
@@ -25880,7 +25889,7 @@
       <c r="Z805" s="2"/>
       <c r="AA805" s="2"/>
     </row>
-    <row r="806" spans="1:27" ht="12.75">
+    <row r="806" spans="1:27" ht="13.2">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
       <c r="C806" s="14"/>
@@ -25909,7 +25918,7 @@
       <c r="Z806" s="2"/>
       <c r="AA806" s="2"/>
     </row>
-    <row r="807" spans="1:27" ht="12.75">
+    <row r="807" spans="1:27" ht="13.2">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
       <c r="C807" s="14"/>
@@ -25938,7 +25947,7 @@
       <c r="Z807" s="2"/>
       <c r="AA807" s="2"/>
     </row>
-    <row r="808" spans="1:27" ht="12.75">
+    <row r="808" spans="1:27" ht="13.2">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
       <c r="C808" s="14"/>
@@ -25967,7 +25976,7 @@
       <c r="Z808" s="2"/>
       <c r="AA808" s="2"/>
     </row>
-    <row r="809" spans="1:27" ht="12.75">
+    <row r="809" spans="1:27" ht="13.2">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
       <c r="C809" s="14"/>
@@ -25996,7 +26005,7 @@
       <c r="Z809" s="2"/>
       <c r="AA809" s="2"/>
     </row>
-    <row r="810" spans="1:27" ht="12.75">
+    <row r="810" spans="1:27" ht="13.2">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
       <c r="C810" s="14"/>
@@ -26025,7 +26034,7 @@
       <c r="Z810" s="2"/>
       <c r="AA810" s="2"/>
     </row>
-    <row r="811" spans="1:27" ht="12.75">
+    <row r="811" spans="1:27" ht="13.2">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
       <c r="C811" s="14"/>
@@ -26054,7 +26063,7 @@
       <c r="Z811" s="2"/>
       <c r="AA811" s="2"/>
     </row>
-    <row r="812" spans="1:27" ht="12.75">
+    <row r="812" spans="1:27" ht="13.2">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
       <c r="C812" s="14"/>
@@ -26083,7 +26092,7 @@
       <c r="Z812" s="2"/>
       <c r="AA812" s="2"/>
     </row>
-    <row r="813" spans="1:27" ht="12.75">
+    <row r="813" spans="1:27" ht="13.2">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
       <c r="C813" s="14"/>
@@ -26112,7 +26121,7 @@
       <c r="Z813" s="2"/>
       <c r="AA813" s="2"/>
     </row>
-    <row r="814" spans="1:27" ht="12.75">
+    <row r="814" spans="1:27" ht="13.2">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
       <c r="C814" s="14"/>
@@ -26141,7 +26150,7 @@
       <c r="Z814" s="2"/>
       <c r="AA814" s="2"/>
     </row>
-    <row r="815" spans="1:27" ht="12.75">
+    <row r="815" spans="1:27" ht="13.2">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
       <c r="C815" s="14"/>
@@ -26170,7 +26179,7 @@
       <c r="Z815" s="2"/>
       <c r="AA815" s="2"/>
     </row>
-    <row r="816" spans="1:27" ht="12.75">
+    <row r="816" spans="1:27" ht="13.2">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
       <c r="C816" s="14"/>
@@ -26199,7 +26208,7 @@
       <c r="Z816" s="2"/>
       <c r="AA816" s="2"/>
     </row>
-    <row r="817" spans="1:27" ht="12.75">
+    <row r="817" spans="1:27" ht="13.2">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
       <c r="C817" s="14"/>
@@ -26228,7 +26237,7 @@
       <c r="Z817" s="2"/>
       <c r="AA817" s="2"/>
     </row>
-    <row r="818" spans="1:27" ht="12.75">
+    <row r="818" spans="1:27" ht="13.2">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
       <c r="C818" s="14"/>
@@ -26257,7 +26266,7 @@
       <c r="Z818" s="2"/>
       <c r="AA818" s="2"/>
     </row>
-    <row r="819" spans="1:27" ht="12.75">
+    <row r="819" spans="1:27" ht="13.2">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
       <c r="C819" s="14"/>
@@ -26286,7 +26295,7 @@
       <c r="Z819" s="2"/>
       <c r="AA819" s="2"/>
     </row>
-    <row r="820" spans="1:27" ht="12.75">
+    <row r="820" spans="1:27" ht="13.2">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
       <c r="C820" s="14"/>
@@ -26315,7 +26324,7 @@
       <c r="Z820" s="2"/>
       <c r="AA820" s="2"/>
     </row>
-    <row r="821" spans="1:27" ht="12.75">
+    <row r="821" spans="1:27" ht="13.2">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
       <c r="C821" s="14"/>
@@ -26344,7 +26353,7 @@
       <c r="Z821" s="2"/>
       <c r="AA821" s="2"/>
     </row>
-    <row r="822" spans="1:27" ht="12.75">
+    <row r="822" spans="1:27" ht="13.2">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
       <c r="C822" s="14"/>
@@ -26373,7 +26382,7 @@
       <c r="Z822" s="2"/>
       <c r="AA822" s="2"/>
     </row>
-    <row r="823" spans="1:27" ht="12.75">
+    <row r="823" spans="1:27" ht="13.2">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
       <c r="C823" s="14"/>
@@ -26402,7 +26411,7 @@
       <c r="Z823" s="2"/>
       <c r="AA823" s="2"/>
     </row>
-    <row r="824" spans="1:27" ht="12.75">
+    <row r="824" spans="1:27" ht="13.2">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
       <c r="C824" s="14"/>
@@ -26431,7 +26440,7 @@
       <c r="Z824" s="2"/>
       <c r="AA824" s="2"/>
     </row>
-    <row r="825" spans="1:27" ht="12.75">
+    <row r="825" spans="1:27" ht="13.2">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
       <c r="C825" s="14"/>
@@ -26460,7 +26469,7 @@
       <c r="Z825" s="2"/>
       <c r="AA825" s="2"/>
     </row>
-    <row r="826" spans="1:27" ht="12.75">
+    <row r="826" spans="1:27" ht="13.2">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
       <c r="C826" s="14"/>
@@ -26489,7 +26498,7 @@
       <c r="Z826" s="2"/>
       <c r="AA826" s="2"/>
     </row>
-    <row r="827" spans="1:27" ht="12.75">
+    <row r="827" spans="1:27" ht="13.2">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
       <c r="C827" s="14"/>
@@ -26518,7 +26527,7 @@
       <c r="Z827" s="2"/>
       <c r="AA827" s="2"/>
     </row>
-    <row r="828" spans="1:27" ht="12.75">
+    <row r="828" spans="1:27" ht="13.2">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
       <c r="C828" s="14"/>
@@ -26547,7 +26556,7 @@
       <c r="Z828" s="2"/>
       <c r="AA828" s="2"/>
     </row>
-    <row r="829" spans="1:27" ht="12.75">
+    <row r="829" spans="1:27" ht="13.2">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
       <c r="C829" s="14"/>
@@ -26576,7 +26585,7 @@
       <c r="Z829" s="2"/>
       <c r="AA829" s="2"/>
     </row>
-    <row r="830" spans="1:27" ht="12.75">
+    <row r="830" spans="1:27" ht="13.2">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
       <c r="C830" s="14"/>
@@ -26605,7 +26614,7 @@
       <c r="Z830" s="2"/>
       <c r="AA830" s="2"/>
     </row>
-    <row r="831" spans="1:27" ht="12.75">
+    <row r="831" spans="1:27" ht="13.2">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
       <c r="C831" s="14"/>
@@ -26634,7 +26643,7 @@
       <c r="Z831" s="2"/>
       <c r="AA831" s="2"/>
     </row>
-    <row r="832" spans="1:27" ht="12.75">
+    <row r="832" spans="1:27" ht="13.2">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
       <c r="C832" s="14"/>
@@ -26663,7 +26672,7 @@
       <c r="Z832" s="2"/>
       <c r="AA832" s="2"/>
     </row>
-    <row r="833" spans="1:27" ht="12.75">
+    <row r="833" spans="1:27" ht="13.2">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
       <c r="C833" s="14"/>
@@ -26692,7 +26701,7 @@
       <c r="Z833" s="2"/>
       <c r="AA833" s="2"/>
     </row>
-    <row r="834" spans="1:27" ht="12.75">
+    <row r="834" spans="1:27" ht="13.2">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
       <c r="C834" s="14"/>
@@ -26721,7 +26730,7 @@
       <c r="Z834" s="2"/>
       <c r="AA834" s="2"/>
     </row>
-    <row r="835" spans="1:27" ht="12.75">
+    <row r="835" spans="1:27" ht="13.2">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
       <c r="C835" s="14"/>
@@ -26750,7 +26759,7 @@
       <c r="Z835" s="2"/>
       <c r="AA835" s="2"/>
     </row>
-    <row r="836" spans="1:27" ht="12.75">
+    <row r="836" spans="1:27" ht="13.2">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
       <c r="C836" s="14"/>
@@ -26779,7 +26788,7 @@
       <c r="Z836" s="2"/>
       <c r="AA836" s="2"/>
     </row>
-    <row r="837" spans="1:27" ht="12.75">
+    <row r="837" spans="1:27" ht="13.2">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
       <c r="C837" s="14"/>
@@ -26808,7 +26817,7 @@
       <c r="Z837" s="2"/>
       <c r="AA837" s="2"/>
     </row>
-    <row r="838" spans="1:27" ht="12.75">
+    <row r="838" spans="1:27" ht="13.2">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
       <c r="C838" s="14"/>
@@ -26837,7 +26846,7 @@
       <c r="Z838" s="2"/>
       <c r="AA838" s="2"/>
     </row>
-    <row r="839" spans="1:27" ht="12.75">
+    <row r="839" spans="1:27" ht="13.2">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
       <c r="C839" s="14"/>
@@ -26866,7 +26875,7 @@
       <c r="Z839" s="2"/>
       <c r="AA839" s="2"/>
     </row>
-    <row r="840" spans="1:27" ht="12.75">
+    <row r="840" spans="1:27" ht="13.2">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
       <c r="C840" s="14"/>
@@ -26895,7 +26904,7 @@
       <c r="Z840" s="2"/>
       <c r="AA840" s="2"/>
     </row>
-    <row r="841" spans="1:27" ht="12.75">
+    <row r="841" spans="1:27" ht="13.2">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
       <c r="C841" s="14"/>
@@ -26924,7 +26933,7 @@
       <c r="Z841" s="2"/>
       <c r="AA841" s="2"/>
     </row>
-    <row r="842" spans="1:27" ht="12.75">
+    <row r="842" spans="1:27" ht="13.2">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
       <c r="C842" s="14"/>
@@ -26953,7 +26962,7 @@
       <c r="Z842" s="2"/>
       <c r="AA842" s="2"/>
     </row>
-    <row r="843" spans="1:27" ht="12.75">
+    <row r="843" spans="1:27" ht="13.2">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
       <c r="C843" s="14"/>
@@ -26982,7 +26991,7 @@
       <c r="Z843" s="2"/>
       <c r="AA843" s="2"/>
     </row>
-    <row r="844" spans="1:27" ht="12.75">
+    <row r="844" spans="1:27" ht="13.2">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
       <c r="C844" s="14"/>
@@ -27011,7 +27020,7 @@
       <c r="Z844" s="2"/>
       <c r="AA844" s="2"/>
     </row>
-    <row r="845" spans="1:27" ht="12.75">
+    <row r="845" spans="1:27" ht="13.2">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
       <c r="C845" s="14"/>
@@ -27040,7 +27049,7 @@
       <c r="Z845" s="2"/>
       <c r="AA845" s="2"/>
     </row>
-    <row r="846" spans="1:27" ht="12.75">
+    <row r="846" spans="1:27" ht="13.2">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
       <c r="C846" s="14"/>
@@ -27069,7 +27078,7 @@
       <c r="Z846" s="2"/>
       <c r="AA846" s="2"/>
     </row>
-    <row r="847" spans="1:27" ht="12.75">
+    <row r="847" spans="1:27" ht="13.2">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
       <c r="C847" s="14"/>
@@ -27098,7 +27107,7 @@
       <c r="Z847" s="2"/>
       <c r="AA847" s="2"/>
     </row>
-    <row r="848" spans="1:27" ht="12.75">
+    <row r="848" spans="1:27" ht="13.2">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
       <c r="C848" s="14"/>
@@ -27127,7 +27136,7 @@
       <c r="Z848" s="2"/>
       <c r="AA848" s="2"/>
     </row>
-    <row r="849" spans="1:27" ht="12.75">
+    <row r="849" spans="1:27" ht="13.2">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
       <c r="C849" s="14"/>
@@ -27156,7 +27165,7 @@
       <c r="Z849" s="2"/>
       <c r="AA849" s="2"/>
     </row>
-    <row r="850" spans="1:27" ht="12.75">
+    <row r="850" spans="1:27" ht="13.2">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
       <c r="C850" s="14"/>
@@ -27185,7 +27194,7 @@
       <c r="Z850" s="2"/>
       <c r="AA850" s="2"/>
     </row>
-    <row r="851" spans="1:27" ht="12.75">
+    <row r="851" spans="1:27" ht="13.2">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
       <c r="C851" s="14"/>
@@ -27214,7 +27223,7 @@
       <c r="Z851" s="2"/>
       <c r="AA851" s="2"/>
     </row>
-    <row r="852" spans="1:27" ht="12.75">
+    <row r="852" spans="1:27" ht="13.2">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
       <c r="C852" s="14"/>
@@ -27243,7 +27252,7 @@
       <c r="Z852" s="2"/>
       <c r="AA852" s="2"/>
     </row>
-    <row r="853" spans="1:27" ht="12.75">
+    <row r="853" spans="1:27" ht="13.2">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
       <c r="C853" s="14"/>
@@ -27272,7 +27281,7 @@
       <c r="Z853" s="2"/>
       <c r="AA853" s="2"/>
     </row>
-    <row r="854" spans="1:27" ht="12.75">
+    <row r="854" spans="1:27" ht="13.2">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
       <c r="C854" s="14"/>
@@ -27301,7 +27310,7 @@
       <c r="Z854" s="2"/>
       <c r="AA854" s="2"/>
     </row>
-    <row r="855" spans="1:27" ht="12.75">
+    <row r="855" spans="1:27" ht="13.2">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
       <c r="C855" s="14"/>
@@ -27330,7 +27339,7 @@
       <c r="Z855" s="2"/>
       <c r="AA855" s="2"/>
     </row>
-    <row r="856" spans="1:27" ht="12.75">
+    <row r="856" spans="1:27" ht="13.2">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
       <c r="C856" s="14"/>
@@ -27359,7 +27368,7 @@
       <c r="Z856" s="2"/>
       <c r="AA856" s="2"/>
     </row>
-    <row r="857" spans="1:27" ht="12.75">
+    <row r="857" spans="1:27" ht="13.2">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
       <c r="C857" s="14"/>
@@ -27388,7 +27397,7 @@
       <c r="Z857" s="2"/>
       <c r="AA857" s="2"/>
     </row>
-    <row r="858" spans="1:27" ht="12.75">
+    <row r="858" spans="1:27" ht="13.2">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
       <c r="C858" s="14"/>
@@ -27417,7 +27426,7 @@
       <c r="Z858" s="2"/>
       <c r="AA858" s="2"/>
     </row>
-    <row r="859" spans="1:27" ht="12.75">
+    <row r="859" spans="1:27" ht="13.2">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
       <c r="C859" s="14"/>
@@ -27446,7 +27455,7 @@
       <c r="Z859" s="2"/>
       <c r="AA859" s="2"/>
     </row>
-    <row r="860" spans="1:27" ht="12.75">
+    <row r="860" spans="1:27" ht="13.2">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
       <c r="C860" s="14"/>
@@ -27475,7 +27484,7 @@
       <c r="Z860" s="2"/>
       <c r="AA860" s="2"/>
     </row>
-    <row r="861" spans="1:27" ht="12.75">
+    <row r="861" spans="1:27" ht="13.2">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
       <c r="C861" s="14"/>
@@ -27504,7 +27513,7 @@
       <c r="Z861" s="2"/>
       <c r="AA861" s="2"/>
     </row>
-    <row r="862" spans="1:27" ht="12.75">
+    <row r="862" spans="1:27" ht="13.2">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
       <c r="C862" s="14"/>
@@ -27533,7 +27542,7 @@
       <c r="Z862" s="2"/>
       <c r="AA862" s="2"/>
     </row>
-    <row r="863" spans="1:27" ht="12.75">
+    <row r="863" spans="1:27" ht="13.2">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
       <c r="C863" s="14"/>
@@ -27562,7 +27571,7 @@
       <c r="Z863" s="2"/>
       <c r="AA863" s="2"/>
     </row>
-    <row r="864" spans="1:27" ht="12.75">
+    <row r="864" spans="1:27" ht="13.2">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
       <c r="C864" s="14"/>
@@ -27591,7 +27600,7 @@
       <c r="Z864" s="2"/>
       <c r="AA864" s="2"/>
     </row>
-    <row r="865" spans="1:27" ht="12.75">
+    <row r="865" spans="1:27" ht="13.2">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
       <c r="C865" s="14"/>
@@ -27620,7 +27629,7 @@
       <c r="Z865" s="2"/>
       <c r="AA865" s="2"/>
     </row>
-    <row r="866" spans="1:27" ht="12.75">
+    <row r="866" spans="1:27" ht="13.2">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
       <c r="C866" s="14"/>
@@ -27649,7 +27658,7 @@
       <c r="Z866" s="2"/>
       <c r="AA866" s="2"/>
     </row>
-    <row r="867" spans="1:27" ht="12.75">
+    <row r="867" spans="1:27" ht="13.2">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
       <c r="C867" s="14"/>
@@ -27678,7 +27687,7 @@
       <c r="Z867" s="2"/>
       <c r="AA867" s="2"/>
     </row>
-    <row r="868" spans="1:27" ht="12.75">
+    <row r="868" spans="1:27" ht="13.2">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
       <c r="C868" s="14"/>
@@ -27707,7 +27716,7 @@
       <c r="Z868" s="2"/>
       <c r="AA868" s="2"/>
     </row>
-    <row r="869" spans="1:27" ht="12.75">
+    <row r="869" spans="1:27" ht="13.2">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
       <c r="C869" s="14"/>
@@ -27736,7 +27745,7 @@
       <c r="Z869" s="2"/>
       <c r="AA869" s="2"/>
     </row>
-    <row r="870" spans="1:27" ht="12.75">
+    <row r="870" spans="1:27" ht="13.2">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
       <c r="C870" s="14"/>
@@ -27765,7 +27774,7 @@
       <c r="Z870" s="2"/>
       <c r="AA870" s="2"/>
     </row>
-    <row r="871" spans="1:27" ht="12.75">
+    <row r="871" spans="1:27" ht="13.2">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
       <c r="C871" s="14"/>
@@ -27794,7 +27803,7 @@
       <c r="Z871" s="2"/>
       <c r="AA871" s="2"/>
     </row>
-    <row r="872" spans="1:27" ht="12.75">
+    <row r="872" spans="1:27" ht="13.2">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
       <c r="C872" s="14"/>
@@ -27823,7 +27832,7 @@
       <c r="Z872" s="2"/>
       <c r="AA872" s="2"/>
     </row>
-    <row r="873" spans="1:27" ht="12.75">
+    <row r="873" spans="1:27" ht="13.2">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
       <c r="C873" s="14"/>
@@ -27852,7 +27861,7 @@
       <c r="Z873" s="2"/>
       <c r="AA873" s="2"/>
     </row>
-    <row r="874" spans="1:27" ht="12.75">
+    <row r="874" spans="1:27" ht="13.2">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
       <c r="C874" s="14"/>
@@ -27881,7 +27890,7 @@
       <c r="Z874" s="2"/>
       <c r="AA874" s="2"/>
     </row>
-    <row r="875" spans="1:27" ht="12.75">
+    <row r="875" spans="1:27" ht="13.2">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
       <c r="C875" s="14"/>
@@ -27910,7 +27919,7 @@
       <c r="Z875" s="2"/>
       <c r="AA875" s="2"/>
     </row>
-    <row r="876" spans="1:27" ht="12.75">
+    <row r="876" spans="1:27" ht="13.2">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
       <c r="C876" s="14"/>
@@ -27939,7 +27948,7 @@
       <c r="Z876" s="2"/>
       <c r="AA876" s="2"/>
     </row>
-    <row r="877" spans="1:27" ht="12.75">
+    <row r="877" spans="1:27" ht="13.2">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
       <c r="C877" s="14"/>
@@ -27968,7 +27977,7 @@
       <c r="Z877" s="2"/>
       <c r="AA877" s="2"/>
     </row>
-    <row r="878" spans="1:27" ht="12.75">
+    <row r="878" spans="1:27" ht="13.2">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
       <c r="C878" s="14"/>
@@ -27997,7 +28006,7 @@
       <c r="Z878" s="2"/>
       <c r="AA878" s="2"/>
     </row>
-    <row r="879" spans="1:27" ht="12.75">
+    <row r="879" spans="1:27" ht="13.2">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
       <c r="C879" s="14"/>
@@ -28026,7 +28035,7 @@
       <c r="Z879" s="2"/>
       <c r="AA879" s="2"/>
     </row>
-    <row r="880" spans="1:27" ht="12.75">
+    <row r="880" spans="1:27" ht="13.2">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
       <c r="C880" s="14"/>
@@ -28055,7 +28064,7 @@
       <c r="Z880" s="2"/>
       <c r="AA880" s="2"/>
     </row>
-    <row r="881" spans="1:27" ht="12.75">
+    <row r="881" spans="1:27" ht="13.2">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
       <c r="C881" s="14"/>
@@ -28084,7 +28093,7 @@
       <c r="Z881" s="2"/>
       <c r="AA881" s="2"/>
     </row>
-    <row r="882" spans="1:27" ht="12.75">
+    <row r="882" spans="1:27" ht="13.2">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
       <c r="C882" s="14"/>
@@ -28113,7 +28122,7 @@
       <c r="Z882" s="2"/>
       <c r="AA882" s="2"/>
     </row>
-    <row r="883" spans="1:27" ht="12.75">
+    <row r="883" spans="1:27" ht="13.2">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
       <c r="C883" s="14"/>
@@ -28142,7 +28151,7 @@
       <c r="Z883" s="2"/>
       <c r="AA883" s="2"/>
     </row>
-    <row r="884" spans="1:27" ht="12.75">
+    <row r="884" spans="1:27" ht="13.2">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
       <c r="C884" s="14"/>
@@ -28171,7 +28180,7 @@
       <c r="Z884" s="2"/>
       <c r="AA884" s="2"/>
     </row>
-    <row r="885" spans="1:27" ht="12.75">
+    <row r="885" spans="1:27" ht="13.2">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
       <c r="C885" s="14"/>
@@ -28200,7 +28209,7 @@
       <c r="Z885" s="2"/>
       <c r="AA885" s="2"/>
     </row>
-    <row r="886" spans="1:27" ht="12.75">
+    <row r="886" spans="1:27" ht="13.2">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
       <c r="C886" s="14"/>
@@ -28229,7 +28238,7 @@
       <c r="Z886" s="2"/>
       <c r="AA886" s="2"/>
     </row>
-    <row r="887" spans="1:27" ht="12.75">
+    <row r="887" spans="1:27" ht="13.2">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
       <c r="C887" s="14"/>
@@ -28258,7 +28267,7 @@
       <c r="Z887" s="2"/>
       <c r="AA887" s="2"/>
     </row>
-    <row r="888" spans="1:27" ht="12.75">
+    <row r="888" spans="1:27" ht="13.2">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
       <c r="C888" s="14"/>
@@ -28287,7 +28296,7 @@
       <c r="Z888" s="2"/>
       <c r="AA888" s="2"/>
     </row>
-    <row r="889" spans="1:27" ht="12.75">
+    <row r="889" spans="1:27" ht="13.2">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
       <c r="C889" s="14"/>
@@ -28316,7 +28325,7 @@
       <c r="Z889" s="2"/>
       <c r="AA889" s="2"/>
     </row>
-    <row r="890" spans="1:27" ht="12.75">
+    <row r="890" spans="1:27" ht="13.2">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
       <c r="C890" s="14"/>
@@ -28345,7 +28354,7 @@
       <c r="Z890" s="2"/>
       <c r="AA890" s="2"/>
     </row>
-    <row r="891" spans="1:27" ht="12.75">
+    <row r="891" spans="1:27" ht="13.2">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
       <c r="C891" s="14"/>
@@ -28374,7 +28383,7 @@
       <c r="Z891" s="2"/>
       <c r="AA891" s="2"/>
     </row>
-    <row r="892" spans="1:27" ht="12.75">
+    <row r="892" spans="1:27" ht="13.2">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
       <c r="C892" s="14"/>
@@ -28403,7 +28412,7 @@
       <c r="Z892" s="2"/>
       <c r="AA892" s="2"/>
     </row>
-    <row r="893" spans="1:27" ht="12.75">
+    <row r="893" spans="1:27" ht="13.2">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
       <c r="C893" s="14"/>
@@ -28432,7 +28441,7 @@
       <c r="Z893" s="2"/>
       <c r="AA893" s="2"/>
     </row>
-    <row r="894" spans="1:27" ht="12.75">
+    <row r="894" spans="1:27" ht="13.2">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
       <c r="C894" s="14"/>
@@ -28461,7 +28470,7 @@
       <c r="Z894" s="2"/>
       <c r="AA894" s="2"/>
     </row>
-    <row r="895" spans="1:27" ht="12.75">
+    <row r="895" spans="1:27" ht="13.2">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
       <c r="C895" s="14"/>
@@ -28490,7 +28499,7 @@
       <c r="Z895" s="2"/>
       <c r="AA895" s="2"/>
     </row>
-    <row r="896" spans="1:27" ht="12.75">
+    <row r="896" spans="1:27" ht="13.2">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
       <c r="C896" s="14"/>
@@ -28519,7 +28528,7 @@
       <c r="Z896" s="2"/>
       <c r="AA896" s="2"/>
     </row>
-    <row r="897" spans="1:27" ht="12.75">
+    <row r="897" spans="1:27" ht="13.2">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
       <c r="C897" s="14"/>
@@ -28548,7 +28557,7 @@
       <c r="Z897" s="2"/>
       <c r="AA897" s="2"/>
     </row>
-    <row r="898" spans="1:27" ht="12.75">
+    <row r="898" spans="1:27" ht="13.2">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
       <c r="C898" s="14"/>
@@ -28577,7 +28586,7 @@
       <c r="Z898" s="2"/>
       <c r="AA898" s="2"/>
     </row>
-    <row r="899" spans="1:27" ht="12.75">
+    <row r="899" spans="1:27" ht="13.2">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
       <c r="C899" s="14"/>
@@ -28606,7 +28615,7 @@
       <c r="Z899" s="2"/>
       <c r="AA899" s="2"/>
     </row>
-    <row r="900" spans="1:27" ht="12.75">
+    <row r="900" spans="1:27" ht="13.2">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
       <c r="C900" s="14"/>
@@ -28635,7 +28644,7 @@
       <c r="Z900" s="2"/>
       <c r="AA900" s="2"/>
     </row>
-    <row r="901" spans="1:27" ht="12.75">
+    <row r="901" spans="1:27" ht="13.2">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
       <c r="C901" s="14"/>
@@ -28664,7 +28673,7 @@
       <c r="Z901" s="2"/>
       <c r="AA901" s="2"/>
     </row>
-    <row r="902" spans="1:27" ht="12.75">
+    <row r="902" spans="1:27" ht="13.2">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
       <c r="C902" s="14"/>
@@ -28693,7 +28702,7 @@
       <c r="Z902" s="2"/>
       <c r="AA902" s="2"/>
     </row>
-    <row r="903" spans="1:27" ht="12.75">
+    <row r="903" spans="1:27" ht="13.2">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
       <c r="C903" s="14"/>
@@ -28722,7 +28731,7 @@
       <c r="Z903" s="2"/>
       <c r="AA903" s="2"/>
     </row>
-    <row r="904" spans="1:27" ht="12.75">
+    <row r="904" spans="1:27" ht="13.2">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
       <c r="C904" s="14"/>
@@ -28751,7 +28760,7 @@
       <c r="Z904" s="2"/>
       <c r="AA904" s="2"/>
     </row>
-    <row r="905" spans="1:27" ht="12.75">
+    <row r="905" spans="1:27" ht="13.2">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
       <c r="C905" s="14"/>
@@ -28780,7 +28789,7 @@
       <c r="Z905" s="2"/>
       <c r="AA905" s="2"/>
     </row>
-    <row r="906" spans="1:27" ht="12.75">
+    <row r="906" spans="1:27" ht="13.2">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
       <c r="C906" s="14"/>
@@ -28809,7 +28818,7 @@
       <c r="Z906" s="2"/>
       <c r="AA906" s="2"/>
     </row>
-    <row r="907" spans="1:27" ht="12.75">
+    <row r="907" spans="1:27" ht="13.2">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
       <c r="C907" s="14"/>
@@ -28838,7 +28847,7 @@
       <c r="Z907" s="2"/>
       <c r="AA907" s="2"/>
     </row>
-    <row r="908" spans="1:27" ht="12.75">
+    <row r="908" spans="1:27" ht="13.2">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
       <c r="C908" s="14"/>
@@ -28867,7 +28876,7 @@
       <c r="Z908" s="2"/>
       <c r="AA908" s="2"/>
     </row>
-    <row r="909" spans="1:27" ht="12.75">
+    <row r="909" spans="1:27" ht="13.2">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
       <c r="C909" s="14"/>
@@ -28896,7 +28905,7 @@
       <c r="Z909" s="2"/>
       <c r="AA909" s="2"/>
     </row>
-    <row r="910" spans="1:27" ht="12.75">
+    <row r="910" spans="1:27" ht="13.2">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
       <c r="C910" s="14"/>
@@ -28925,7 +28934,7 @@
       <c r="Z910" s="2"/>
       <c r="AA910" s="2"/>
     </row>
-    <row r="911" spans="1:27" ht="12.75">
+    <row r="911" spans="1:27" ht="13.2">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
       <c r="C911" s="14"/>
@@ -28954,7 +28963,7 @@
       <c r="Z911" s="2"/>
       <c r="AA911" s="2"/>
     </row>
-    <row r="912" spans="1:27" ht="12.75">
+    <row r="912" spans="1:27" ht="13.2">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
       <c r="C912" s="14"/>
@@ -28983,7 +28992,7 @@
       <c r="Z912" s="2"/>
       <c r="AA912" s="2"/>
     </row>
-    <row r="913" spans="1:27" ht="12.75">
+    <row r="913" spans="1:27" ht="13.2">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
       <c r="C913" s="14"/>
@@ -29012,7 +29021,7 @@
       <c r="Z913" s="2"/>
       <c r="AA913" s="2"/>
     </row>
-    <row r="914" spans="1:27" ht="12.75">
+    <row r="914" spans="1:27" ht="13.2">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
       <c r="C914" s="14"/>
@@ -29041,7 +29050,7 @@
       <c r="Z914" s="2"/>
       <c r="AA914" s="2"/>
     </row>
-    <row r="915" spans="1:27" ht="12.75">
+    <row r="915" spans="1:27" ht="13.2">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
       <c r="C915" s="14"/>
@@ -29070,7 +29079,7 @@
       <c r="Z915" s="2"/>
       <c r="AA915" s="2"/>
     </row>
-    <row r="916" spans="1:27" ht="12.75">
+    <row r="916" spans="1:27" ht="13.2">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
       <c r="C916" s="14"/>
@@ -29099,7 +29108,7 @@
       <c r="Z916" s="2"/>
       <c r="AA916" s="2"/>
     </row>
-    <row r="917" spans="1:27" ht="12.75">
+    <row r="917" spans="1:27" ht="13.2">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
       <c r="C917" s="14"/>
@@ -29128,7 +29137,7 @@
       <c r="Z917" s="2"/>
       <c r="AA917" s="2"/>
     </row>
-    <row r="918" spans="1:27" ht="12.75">
+    <row r="918" spans="1:27" ht="13.2">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
       <c r="C918" s="14"/>
@@ -29157,7 +29166,7 @@
       <c r="Z918" s="2"/>
       <c r="AA918" s="2"/>
     </row>
-    <row r="919" spans="1:27" ht="12.75">
+    <row r="919" spans="1:27" ht="13.2">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
       <c r="C919" s="14"/>
@@ -29186,7 +29195,7 @@
       <c r="Z919" s="2"/>
       <c r="AA919" s="2"/>
     </row>
-    <row r="920" spans="1:27" ht="12.75">
+    <row r="920" spans="1:27" ht="13.2">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
       <c r="C920" s="14"/>
@@ -29215,7 +29224,7 @@
       <c r="Z920" s="2"/>
       <c r="AA920" s="2"/>
     </row>
-    <row r="921" spans="1:27" ht="12.75">
+    <row r="921" spans="1:27" ht="13.2">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
       <c r="C921" s="14"/>
@@ -29244,7 +29253,7 @@
       <c r="Z921" s="2"/>
       <c r="AA921" s="2"/>
     </row>
-    <row r="922" spans="1:27" ht="12.75">
+    <row r="922" spans="1:27" ht="13.2">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
       <c r="C922" s="14"/>
@@ -29273,7 +29282,7 @@
       <c r="Z922" s="2"/>
       <c r="AA922" s="2"/>
     </row>
-    <row r="923" spans="1:27" ht="12.75">
+    <row r="923" spans="1:27" ht="13.2">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
       <c r="C923" s="14"/>
@@ -29302,7 +29311,7 @@
       <c r="Z923" s="2"/>
       <c r="AA923" s="2"/>
     </row>
-    <row r="924" spans="1:27" ht="12.75">
+    <row r="924" spans="1:27" ht="13.2">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
       <c r="C924" s="14"/>
@@ -29331,7 +29340,7 @@
       <c r="Z924" s="2"/>
       <c r="AA924" s="2"/>
     </row>
-    <row r="925" spans="1:27" ht="12.75">
+    <row r="925" spans="1:27" ht="13.2">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
       <c r="C925" s="14"/>
@@ -29360,7 +29369,7 @@
       <c r="Z925" s="2"/>
       <c r="AA925" s="2"/>
     </row>
-    <row r="926" spans="1:27" ht="12.75">
+    <row r="926" spans="1:27" ht="13.2">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
       <c r="C926" s="14"/>
@@ -29389,7 +29398,7 @@
       <c r="Z926" s="2"/>
       <c r="AA926" s="2"/>
     </row>
-    <row r="927" spans="1:27" ht="12.75">
+    <row r="927" spans="1:27" ht="13.2">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
       <c r="C927" s="14"/>
@@ -29418,7 +29427,7 @@
       <c r="Z927" s="2"/>
       <c r="AA927" s="2"/>
     </row>
-    <row r="928" spans="1:27" ht="12.75">
+    <row r="928" spans="1:27" ht="13.2">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
       <c r="C928" s="14"/>
@@ -29447,7 +29456,7 @@
       <c r="Z928" s="2"/>
       <c r="AA928" s="2"/>
     </row>
-    <row r="929" spans="1:27" ht="12.75">
+    <row r="929" spans="1:27" ht="13.2">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
       <c r="C929" s="14"/>
@@ -29476,7 +29485,7 @@
       <c r="Z929" s="2"/>
       <c r="AA929" s="2"/>
     </row>
-    <row r="930" spans="1:27" ht="12.75">
+    <row r="930" spans="1:27" ht="13.2">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
       <c r="C930" s="14"/>
@@ -29505,7 +29514,7 @@
       <c r="Z930" s="2"/>
       <c r="AA930" s="2"/>
     </row>
-    <row r="931" spans="1:27" ht="12.75">
+    <row r="931" spans="1:27" ht="13.2">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
       <c r="C931" s="14"/>
@@ -29534,7 +29543,7 @@
       <c r="Z931" s="2"/>
       <c r="AA931" s="2"/>
     </row>
-    <row r="932" spans="1:27" ht="12.75">
+    <row r="932" spans="1:27" ht="13.2">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
       <c r="C932" s="14"/>
@@ -29563,7 +29572,7 @@
       <c r="Z932" s="2"/>
       <c r="AA932" s="2"/>
     </row>
-    <row r="933" spans="1:27" ht="12.75">
+    <row r="933" spans="1:27" ht="13.2">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
       <c r="C933" s="14"/>
@@ -29592,7 +29601,7 @@
       <c r="Z933" s="2"/>
       <c r="AA933" s="2"/>
     </row>
-    <row r="934" spans="1:27" ht="12.75">
+    <row r="934" spans="1:27" ht="13.2">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
       <c r="C934" s="14"/>
@@ -29621,7 +29630,7 @@
       <c r="Z934" s="2"/>
       <c r="AA934" s="2"/>
     </row>
-    <row r="935" spans="1:27" ht="12.75">
+    <row r="935" spans="1:27" ht="13.2">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
       <c r="C935" s="14"/>
@@ -29650,7 +29659,7 @@
       <c r="Z935" s="2"/>
       <c r="AA935" s="2"/>
     </row>
-    <row r="936" spans="1:27" ht="12.75">
+    <row r="936" spans="1:27" ht="13.2">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
       <c r="C936" s="14"/>
@@ -29679,7 +29688,7 @@
       <c r="Z936" s="2"/>
       <c r="AA936" s="2"/>
     </row>
-    <row r="937" spans="1:27" ht="12.75">
+    <row r="937" spans="1:27" ht="13.2">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
       <c r="C937" s="14"/>
@@ -29708,7 +29717,7 @@
       <c r="Z937" s="2"/>
       <c r="AA937" s="2"/>
     </row>
-    <row r="938" spans="1:27" ht="12.75">
+    <row r="938" spans="1:27" ht="13.2">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
       <c r="C938" s="14"/>
@@ -29737,7 +29746,7 @@
       <c r="Z938" s="2"/>
       <c r="AA938" s="2"/>
     </row>
-    <row r="939" spans="1:27" ht="12.75">
+    <row r="939" spans="1:27" ht="13.2">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
       <c r="C939" s="14"/>
@@ -29766,7 +29775,7 @@
       <c r="Z939" s="2"/>
       <c r="AA939" s="2"/>
     </row>
-    <row r="940" spans="1:27" ht="12.75">
+    <row r="940" spans="1:27" ht="13.2">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
       <c r="C940" s="14"/>
@@ -29795,7 +29804,7 @@
       <c r="Z940" s="2"/>
       <c r="AA940" s="2"/>
     </row>
-    <row r="941" spans="1:27" ht="12.75">
+    <row r="941" spans="1:27" ht="13.2">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
       <c r="C941" s="14"/>
@@ -29824,7 +29833,7 @@
       <c r="Z941" s="2"/>
       <c r="AA941" s="2"/>
     </row>
-    <row r="942" spans="1:27" ht="12.75">
+    <row r="942" spans="1:27" ht="13.2">
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
       <c r="C942" s="14"/>
@@ -29853,7 +29862,7 @@
       <c r="Z942" s="2"/>
       <c r="AA942" s="2"/>
     </row>
-    <row r="943" spans="1:27" ht="12.75">
+    <row r="943" spans="1:27" ht="13.2">
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
       <c r="C943" s="14"/>
@@ -29882,7 +29891,7 @@
       <c r="Z943" s="2"/>
       <c r="AA943" s="2"/>
     </row>
-    <row r="944" spans="1:27" ht="12.75">
+    <row r="944" spans="1:27" ht="13.2">
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
       <c r="C944" s="14"/>
@@ -29911,7 +29920,7 @@
       <c r="Z944" s="2"/>
       <c r="AA944" s="2"/>
     </row>
-    <row r="945" spans="1:27" ht="12.75">
+    <row r="945" spans="1:27" ht="13.2">
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
       <c r="C945" s="14"/>
@@ -29940,7 +29949,7 @@
       <c r="Z945" s="2"/>
       <c r="AA945" s="2"/>
     </row>
-    <row r="946" spans="1:27" ht="12.75">
+    <row r="946" spans="1:27" ht="13.2">
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
       <c r="C946" s="14"/>
@@ -29969,7 +29978,7 @@
       <c r="Z946" s="2"/>
       <c r="AA946" s="2"/>
     </row>
-    <row r="947" spans="1:27" ht="12.75">
+    <row r="947" spans="1:27" ht="13.2">
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
       <c r="C947" s="14"/>
@@ -29998,7 +30007,7 @@
       <c r="Z947" s="2"/>
       <c r="AA947" s="2"/>
     </row>
-    <row r="948" spans="1:27" ht="12.75">
+    <row r="948" spans="1:27" ht="13.2">
       <c r="A948" s="2"/>
       <c r="B948" s="2"/>
       <c r="C948" s="14"/>
@@ -30027,7 +30036,7 @@
       <c r="Z948" s="2"/>
       <c r="AA948" s="2"/>
     </row>
-    <row r="949" spans="1:27" ht="12.75">
+    <row r="949" spans="1:27" ht="13.2">
       <c r="A949" s="2"/>
       <c r="B949" s="2"/>
       <c r="C949" s="14"/>
@@ -30056,7 +30065,7 @@
       <c r="Z949" s="2"/>
       <c r="AA949" s="2"/>
     </row>
-    <row r="950" spans="1:27" ht="12.75">
+    <row r="950" spans="1:27" ht="13.2">
       <c r="A950" s="2"/>
       <c r="B950" s="2"/>
       <c r="C950" s="14"/>
@@ -30085,7 +30094,7 @@
       <c r="Z950" s="2"/>
       <c r="AA950" s="2"/>
     </row>
-    <row r="951" spans="1:27" ht="12.75">
+    <row r="951" spans="1:27" ht="13.2">
       <c r="A951" s="2"/>
       <c r="B951" s="2"/>
       <c r="C951" s="14"/>
@@ -30114,7 +30123,7 @@
       <c r="Z951" s="2"/>
       <c r="AA951" s="2"/>
     </row>
-    <row r="952" spans="1:27" ht="12.75">
+    <row r="952" spans="1:27" ht="13.2">
       <c r="A952" s="2"/>
       <c r="B952" s="2"/>
       <c r="C952" s="14"/>
@@ -30143,7 +30152,7 @@
       <c r="Z952" s="2"/>
       <c r="AA952" s="2"/>
     </row>
-    <row r="953" spans="1:27" ht="12.75">
+    <row r="953" spans="1:27" ht="13.2">
       <c r="A953" s="2"/>
       <c r="B953" s="2"/>
       <c r="C953" s="14"/>
@@ -30172,7 +30181,7 @@
       <c r="Z953" s="2"/>
       <c r="AA953" s="2"/>
     </row>
-    <row r="954" spans="1:27" ht="12.75">
+    <row r="954" spans="1:27" ht="13.2">
       <c r="A954" s="2"/>
       <c r="B954" s="2"/>
       <c r="C954" s="14"/>
@@ -30201,7 +30210,7 @@
       <c r="Z954" s="2"/>
       <c r="AA954" s="2"/>
     </row>
-    <row r="955" spans="1:27" ht="12.75">
+    <row r="955" spans="1:27" ht="13.2">
       <c r="A955" s="2"/>
       <c r="B955" s="2"/>
       <c r="C955" s="14"/>
@@ -30230,7 +30239,7 @@
       <c r="Z955" s="2"/>
       <c r="AA955" s="2"/>
     </row>
-    <row r="956" spans="1:27" ht="12.75">
+    <row r="956" spans="1:27" ht="13.2">
       <c r="A956" s="2"/>
       <c r="B956" s="2"/>
       <c r="C956" s="14"/>
@@ -30259,7 +30268,7 @@
       <c r="Z956" s="2"/>
       <c r="AA956" s="2"/>
     </row>
-    <row r="957" spans="1:27" ht="12.75">
+    <row r="957" spans="1:27" ht="13.2">
       <c r="A957" s="2"/>
       <c r="B957" s="2"/>
       <c r="C957" s="14"/>
@@ -30288,7 +30297,7 @@
       <c r="Z957" s="2"/>
       <c r="AA957" s="2"/>
     </row>
-    <row r="958" spans="1:27" ht="12.75">
+    <row r="958" spans="1:27" ht="13.2">
       <c r="A958" s="2"/>
       <c r="B958" s="2"/>
       <c r="C958" s="14"/>
@@ -30317,7 +30326,7 @@
       <c r="Z958" s="2"/>
       <c r="AA958" s="2"/>
     </row>
-    <row r="959" spans="1:27" ht="12.75">
+    <row r="959" spans="1:27" ht="13.2">
       <c r="A959" s="2"/>
       <c r="B959" s="2"/>
       <c r="C959" s="14"/>
@@ -30346,7 +30355,7 @@
       <c r="Z959" s="2"/>
       <c r="AA959" s="2"/>
     </row>
-    <row r="960" spans="1:27" ht="12.75">
+    <row r="960" spans="1:27" ht="13.2">
       <c r="A960" s="2"/>
       <c r="B960" s="2"/>
       <c r="C960" s="14"/>
@@ -30375,7 +30384,7 @@
       <c r="Z960" s="2"/>
       <c r="AA960" s="2"/>
     </row>
-    <row r="961" spans="1:27" ht="12.75">
+    <row r="961" spans="1:27" ht="13.2">
       <c r="A961" s="2"/>
       <c r="B961" s="2"/>
       <c r="C961" s="14"/>
@@ -30404,7 +30413,7 @@
       <c r="Z961" s="2"/>
       <c r="AA961" s="2"/>
     </row>
-    <row r="962" spans="1:27" ht="12.75">
+    <row r="962" spans="1:27" ht="13.2">
       <c r="A962" s="2"/>
       <c r="B962" s="2"/>
       <c r="C962" s="14"/>
@@ -30433,7 +30442,7 @@
       <c r="Z962" s="2"/>
       <c r="AA962" s="2"/>
     </row>
-    <row r="963" spans="1:27" ht="12.75">
+    <row r="963" spans="1:27" ht="13.2">
       <c r="A963" s="2"/>
       <c r="B963" s="2"/>
       <c r="C963" s="14"/>
@@ -30462,7 +30471,7 @@
       <c r="Z963" s="2"/>
       <c r="AA963" s="2"/>
     </row>
-    <row r="964" spans="1:27" ht="12.75">
+    <row r="964" spans="1:27" ht="13.2">
       <c r="A964" s="2"/>
       <c r="B964" s="2"/>
       <c r="C964" s="14"/>
@@ -30491,7 +30500,7 @@
       <c r="Z964" s="2"/>
       <c r="AA964" s="2"/>
     </row>
-    <row r="965" spans="1:27" ht="12.75">
+    <row r="965" spans="1:27" ht="13.2">
       <c r="A965" s="2"/>
       <c r="B965" s="2"/>
       <c r="C965" s="14"/>
@@ -30520,7 +30529,7 @@
       <c r="Z965" s="2"/>
       <c r="AA965" s="2"/>
     </row>
-    <row r="966" spans="1:27" ht="12.75">
+    <row r="966" spans="1:27" ht="13.2">
       <c r="A966" s="2"/>
       <c r="B966" s="2"/>
       <c r="C966" s="14"/>
@@ -30549,7 +30558,7 @@
       <c r="Z966" s="2"/>
       <c r="AA966" s="2"/>
     </row>
-    <row r="967" spans="1:27" ht="12.75">
+    <row r="967" spans="1:27" ht="13.2">
       <c r="A967" s="2"/>
       <c r="B967" s="2"/>
       <c r="C967" s="14"/>
@@ -30578,7 +30587,7 @@
       <c r="Z967" s="2"/>
       <c r="AA967" s="2"/>
     </row>
-    <row r="968" spans="1:27" ht="12.75">
+    <row r="968" spans="1:27" ht="13.2">
       <c r="A968" s="2"/>
       <c r="B968" s="2"/>
       <c r="C968" s="14"/>
@@ -30607,7 +30616,7 @@
       <c r="Z968" s="2"/>
       <c r="AA968" s="2"/>
     </row>
-    <row r="969" spans="1:27" ht="12.75">
+    <row r="969" spans="1:27" ht="13.2">
       <c r="A969" s="2"/>
       <c r="B969" s="2"/>
       <c r="C969" s="14"/>
@@ -30636,7 +30645,7 @@
       <c r="Z969" s="2"/>
       <c r="AA969" s="2"/>
     </row>
-    <row r="970" spans="1:27" ht="12.75">
+    <row r="970" spans="1:27" ht="13.2">
       <c r="A970" s="2"/>
       <c r="B970" s="2"/>
       <c r="C970" s="14"/>
@@ -30665,7 +30674,7 @@
       <c r="Z970" s="2"/>
       <c r="AA970" s="2"/>
     </row>
-    <row r="971" spans="1:27" ht="12.75">
+    <row r="971" spans="1:27" ht="13.2">
       <c r="A971" s="2"/>
       <c r="B971" s="2"/>
       <c r="C971" s="14"/>
@@ -30694,7 +30703,7 @@
       <c r="Z971" s="2"/>
       <c r="AA971" s="2"/>
     </row>
-    <row r="972" spans="1:27" ht="12.75">
+    <row r="972" spans="1:27" ht="13.2">
       <c r="A972" s="2"/>
       <c r="B972" s="2"/>
       <c r="C972" s="14"/>
@@ -30723,7 +30732,7 @@
       <c r="Z972" s="2"/>
       <c r="AA972" s="2"/>
     </row>
-    <row r="973" spans="1:27" ht="12.75">
+    <row r="973" spans="1:27" ht="13.2">
       <c r="A973" s="2"/>
       <c r="B973" s="2"/>
       <c r="C973" s="14"/>
@@ -30752,7 +30761,7 @@
       <c r="Z973" s="2"/>
       <c r="AA973" s="2"/>
     </row>
-    <row r="974" spans="1:27" ht="12.75">
+    <row r="974" spans="1:27" ht="13.2">
       <c r="A974" s="2"/>
       <c r="B974" s="2"/>
       <c r="C974" s="14"/>
@@ -30781,7 +30790,7 @@
       <c r="Z974" s="2"/>
       <c r="AA974" s="2"/>
     </row>
-    <row r="975" spans="1:27" ht="12.75">
+    <row r="975" spans="1:27" ht="13.2">
       <c r="A975" s="2"/>
       <c r="B975" s="2"/>
       <c r="C975" s="14"/>
@@ -30810,7 +30819,7 @@
       <c r="Z975" s="2"/>
       <c r="AA975" s="2"/>
     </row>
-    <row r="976" spans="1:27" ht="12.75">
+    <row r="976" spans="1:27" ht="13.2">
       <c r="A976" s="2"/>
       <c r="B976" s="2"/>
       <c r="C976" s="14"/>
@@ -30839,7 +30848,7 @@
       <c r="Z976" s="2"/>
       <c r="AA976" s="2"/>
     </row>
-    <row r="977" spans="1:27" ht="12.75">
+    <row r="977" spans="1:27" ht="13.2">
       <c r="A977" s="2"/>
       <c r="B977" s="2"/>
       <c r="C977" s="14"/>
@@ -30868,7 +30877,7 @@
       <c r="Z977" s="2"/>
       <c r="AA977" s="2"/>
     </row>
-    <row r="978" spans="1:27" ht="12.75">
+    <row r="978" spans="1:27" ht="13.2">
       <c r="A978" s="2"/>
       <c r="B978" s="2"/>
       <c r="C978" s="14"/>
@@ -30897,7 +30906,7 @@
       <c r="Z978" s="2"/>
       <c r="AA978" s="2"/>
     </row>
-    <row r="979" spans="1:27" ht="12.75">
+    <row r="979" spans="1:27" ht="13.2">
       <c r="A979" s="2"/>
       <c r="B979" s="2"/>
       <c r="C979" s="14"/>
@@ -30926,7 +30935,7 @@
       <c r="Z979" s="2"/>
       <c r="AA979" s="2"/>
     </row>
-    <row r="980" spans="1:27" ht="12.75">
+    <row r="980" spans="1:27" ht="13.2">
       <c r="A980" s="2"/>
       <c r="B980" s="2"/>
       <c r="C980" s="14"/>
@@ -30955,7 +30964,7 @@
       <c r="Z980" s="2"/>
       <c r="AA980" s="2"/>
     </row>
-    <row r="981" spans="1:27" ht="12.75">
+    <row r="981" spans="1:27" ht="13.2">
       <c r="A981" s="2"/>
       <c r="B981" s="2"/>
       <c r="C981" s="14"/>
@@ -30984,7 +30993,7 @@
       <c r="Z981" s="2"/>
       <c r="AA981" s="2"/>
     </row>
-    <row r="982" spans="1:27" ht="12.75">
+    <row r="982" spans="1:27" ht="13.2">
       <c r="A982" s="2"/>
       <c r="B982" s="2"/>
       <c r="C982" s="14"/>
@@ -31013,7 +31022,7 @@
       <c r="Z982" s="2"/>
       <c r="AA982" s="2"/>
     </row>
-    <row r="983" spans="1:27" ht="12.75">
+    <row r="983" spans="1:27" ht="13.2">
       <c r="A983" s="2"/>
       <c r="B983" s="2"/>
       <c r="C983" s="14"/>
@@ -31042,7 +31051,7 @@
       <c r="Z983" s="2"/>
       <c r="AA983" s="2"/>
     </row>
-    <row r="984" spans="1:27" ht="12.75">
+    <row r="984" spans="1:27" ht="13.2">
       <c r="A984" s="2"/>
       <c r="B984" s="2"/>
       <c r="C984" s="14"/>
@@ -31071,7 +31080,7 @@
       <c r="Z984" s="2"/>
       <c r="AA984" s="2"/>
     </row>
-    <row r="985" spans="1:27" ht="12.75">
+    <row r="985" spans="1:27" ht="13.2">
       <c r="A985" s="2"/>
       <c r="B985" s="2"/>
       <c r="C985" s="14"/>
@@ -31100,7 +31109,7 @@
       <c r="Z985" s="2"/>
       <c r="AA985" s="2"/>
     </row>
-    <row r="986" spans="1:27" ht="12.75">
+    <row r="986" spans="1:27" ht="13.2">
       <c r="A986" s="2"/>
       <c r="B986" s="2"/>
       <c r="C986" s="14"/>
@@ -31129,7 +31138,7 @@
       <c r="Z986" s="2"/>
       <c r="AA986" s="2"/>
     </row>
-    <row r="987" spans="1:27" ht="12.75">
+    <row r="987" spans="1:27" ht="13.2">
       <c r="A987" s="2"/>
       <c r="B987" s="2"/>
       <c r="C987" s="14"/>
@@ -31158,7 +31167,7 @@
       <c r="Z987" s="2"/>
       <c r="AA987" s="2"/>
     </row>
-    <row r="988" spans="1:27" ht="12.75">
+    <row r="988" spans="1:27" ht="13.2">
       <c r="A988" s="2"/>
       <c r="B988" s="2"/>
       <c r="C988" s="14"/>
@@ -31187,7 +31196,7 @@
       <c r="Z988" s="2"/>
       <c r="AA988" s="2"/>
     </row>
-    <row r="989" spans="1:27" ht="12.75">
+    <row r="989" spans="1:27" ht="13.2">
       <c r="A989" s="2"/>
       <c r="B989" s="2"/>
       <c r="C989" s="14"/>
@@ -31216,7 +31225,7 @@
       <c r="Z989" s="2"/>
       <c r="AA989" s="2"/>
     </row>
-    <row r="990" spans="1:27" ht="12.75">
+    <row r="990" spans="1:27" ht="13.2">
       <c r="A990" s="2"/>
       <c r="B990" s="2"/>
       <c r="C990" s="14"/>
@@ -31245,7 +31254,7 @@
       <c r="Z990" s="2"/>
       <c r="AA990" s="2"/>
     </row>
-    <row r="991" spans="1:27" ht="12.75">
+    <row r="991" spans="1:27" ht="13.2">
       <c r="A991" s="2"/>
       <c r="B991" s="2"/>
       <c r="C991" s="14"/>
@@ -31274,7 +31283,7 @@
       <c r="Z991" s="2"/>
       <c r="AA991" s="2"/>
     </row>
-    <row r="992" spans="1:27" ht="12.75">
+    <row r="992" spans="1:27" ht="13.2">
       <c r="A992" s="2"/>
       <c r="B992" s="2"/>
       <c r="C992" s="14"/>
@@ -31303,7 +31312,7 @@
       <c r="Z992" s="2"/>
       <c r="AA992" s="2"/>
     </row>
-    <row r="993" spans="1:27" ht="12.75">
+    <row r="993" spans="1:27" ht="13.2">
       <c r="A993" s="2"/>
       <c r="B993" s="2"/>
       <c r="C993" s="14"/>
@@ -31332,7 +31341,7 @@
       <c r="Z993" s="2"/>
       <c r="AA993" s="2"/>
     </row>
-    <row r="994" spans="1:27" ht="12.75">
+    <row r="994" spans="1:27" ht="13.2">
       <c r="A994" s="2"/>
       <c r="B994" s="2"/>
       <c r="C994" s="14"/>
@@ -31361,7 +31370,7 @@
       <c r="Z994" s="2"/>
       <c r="AA994" s="2"/>
     </row>
-    <row r="995" spans="1:27" ht="12.75">
+    <row r="995" spans="1:27" ht="13.2">
       <c r="A995" s="2"/>
       <c r="B995" s="2"/>
       <c r="C995" s="14"/>
@@ -31390,7 +31399,7 @@
       <c r="Z995" s="2"/>
       <c r="AA995" s="2"/>
     </row>
-    <row r="996" spans="1:27" ht="12.75">
+    <row r="996" spans="1:27" ht="13.2">
       <c r="A996" s="2"/>
       <c r="B996" s="2"/>
       <c r="C996" s="14"/>
@@ -31419,7 +31428,7 @@
       <c r="Z996" s="2"/>
       <c r="AA996" s="2"/>
     </row>
-    <row r="997" spans="1:27" ht="12.75">
+    <row r="997" spans="1:27" ht="13.2">
       <c r="A997" s="2"/>
       <c r="B997" s="2"/>
       <c r="C997" s="14"/>
@@ -31448,7 +31457,7 @@
       <c r="Z997" s="2"/>
       <c r="AA997" s="2"/>
     </row>
-    <row r="998" spans="1:27" ht="12.75">
+    <row r="998" spans="1:27" ht="13.2">
       <c r="A998" s="2"/>
       <c r="B998" s="2"/>
       <c r="C998" s="14"/>
@@ -31477,7 +31486,7 @@
       <c r="Z998" s="2"/>
       <c r="AA998" s="2"/>
     </row>
-    <row r="999" spans="1:27" ht="12.75">
+    <row r="999" spans="1:27" ht="13.2">
       <c r="A999" s="2"/>
       <c r="B999" s="2"/>
       <c r="C999" s="14"/>
@@ -31506,7 +31515,7 @@
       <c r="Z999" s="2"/>
       <c r="AA999" s="2"/>
     </row>
-    <row r="1000" spans="1:27" ht="12.75">
+    <row r="1000" spans="1:27" ht="13.2">
       <c r="A1000" s="2"/>
       <c r="B1000" s="2"/>
       <c r="C1000" s="14"/>
@@ -31535,7 +31544,7 @@
       <c r="Z1000" s="2"/>
       <c r="AA1000" s="2"/>
     </row>
-    <row r="1001" spans="1:27" ht="12.75">
+    <row r="1001" spans="1:27" ht="13.2">
       <c r="A1001" s="2"/>
       <c r="B1001" s="2"/>
       <c r="C1001" s="14"/>
@@ -31577,7 +31586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
@@ -31673,9 +31682,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z5"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
@@ -31796,7 +31805,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1">
       <c r="A1" s="10" t="s">
@@ -31853,20 +31862,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:X1007"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="20.25" customHeight="1"/>
+  <dimension ref="A1:X1008"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="33" customWidth="1"/>
-    <col min="2" max="2" width="61.42578125" style="33" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="33" customWidth="1"/>
-    <col min="4" max="4" width="184.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" style="33" customWidth="1"/>
+    <col min="2" max="2" width="61.44140625" style="33" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="33" customWidth="1"/>
+    <col min="4" max="4" width="184.5546875" style="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="62.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" style="33" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="49" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.5703125" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.5703125" style="33"/>
+    <col min="6" max="6" width="62.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" style="33" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" style="49" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.5546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="12.5546875" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="20.25" customHeight="1">
@@ -32875,21 +32884,23 @@
         <v>97</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="C28" s="30">
         <v>2026</v>
       </c>
-      <c r="D28" s="23" t="s">
-        <v>328</v>
+      <c r="D28" s="30" t="s">
+        <v>352</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="F28" s="44"/>
+        <v>158</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>353</v>
+      </c>
       <c r="G28" s="30"/>
       <c r="H28" s="47"/>
-      <c r="I28" s="22"/>
+      <c r="I28" s="30"/>
       <c r="J28" s="30"/>
       <c r="K28" s="30"/>
       <c r="L28" s="30"/>
@@ -32916,8 +32927,8 @@
       <c r="C29" s="30">
         <v>2026</v>
       </c>
-      <c r="D29" s="51" t="s">
-        <v>312</v>
+      <c r="D29" s="23" t="s">
+        <v>328</v>
       </c>
       <c r="E29" s="30" t="s">
         <v>152</v>
@@ -32947,20 +32958,18 @@
         <v>97</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="C30" s="30">
         <v>2026</v>
       </c>
-      <c r="D30" s="53" t="s">
-        <v>336</v>
+      <c r="D30" s="51" t="s">
+        <v>312</v>
       </c>
       <c r="E30" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="F30" s="44" t="s">
-        <v>337</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="F30" s="44"/>
       <c r="G30" s="30"/>
       <c r="H30" s="47"/>
       <c r="I30" s="22"/>
@@ -32985,18 +32994,20 @@
         <v>97</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C31" s="30">
         <v>2026</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="F31" s="44"/>
+        <v>158</v>
+      </c>
+      <c r="F31" s="44" t="s">
+        <v>337</v>
+      </c>
       <c r="G31" s="30"/>
       <c r="H31" s="47"/>
       <c r="I31" s="22"/>
@@ -33021,15 +33032,17 @@
         <v>97</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>251</v>
+        <v>347</v>
       </c>
       <c r="C32" s="30">
         <v>2026</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>348</v>
-      </c>
-      <c r="E32" s="30"/>
+        <v>339</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="F32" s="44"/>
       <c r="G32" s="30"/>
       <c r="H32" s="47"/>
@@ -33061,7 +33074,7 @@
         <v>2026</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E33" s="30"/>
       <c r="F33" s="44"/>
@@ -33095,7 +33108,7 @@
         <v>2026</v>
       </c>
       <c r="D34" s="53" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E34" s="30"/>
       <c r="F34" s="44"/>
@@ -33129,7 +33142,7 @@
         <v>2026</v>
       </c>
       <c r="D35" s="53" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E35" s="30"/>
       <c r="F35" s="44"/>
@@ -33154,16 +33167,16 @@
     </row>
     <row r="36" spans="1:24" ht="20.25" customHeight="1">
       <c r="A36" s="30" t="s">
-        <v>258</v>
+        <v>97</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>344</v>
+        <v>251</v>
       </c>
       <c r="C36" s="30">
         <v>2026</v>
       </c>
       <c r="D36" s="53" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E36" s="30"/>
       <c r="F36" s="44"/>
@@ -33191,13 +33204,13 @@
         <v>258</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C37" s="30">
         <v>2026</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="44"/>
@@ -33225,13 +33238,13 @@
         <v>258</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>251</v>
+        <v>341</v>
       </c>
       <c r="C38" s="30">
         <v>2026</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E38" s="30"/>
       <c r="F38" s="44"/>
@@ -33259,21 +33272,19 @@
         <v>258</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="C39" s="30">
-        <v>2025</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="E39" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="F39" s="30"/>
+        <v>2026</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>340</v>
+      </c>
+      <c r="E39" s="30"/>
+      <c r="F39" s="44"/>
       <c r="G39" s="30"/>
       <c r="H39" s="47"/>
-      <c r="I39" s="30"/>
+      <c r="I39" s="22"/>
       <c r="J39" s="30"/>
       <c r="K39" s="30"/>
       <c r="L39" s="30"/>
@@ -33295,13 +33306,13 @@
         <v>258</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C40" s="30">
         <v>2025</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E40" s="30" t="s">
         <v>225</v>
@@ -33310,9 +33321,7 @@
       <c r="G40" s="30"/>
       <c r="H40" s="47"/>
       <c r="I40" s="30"/>
-      <c r="J40" s="30" t="s">
-        <v>103</v>
-      </c>
+      <c r="J40" s="30"/>
       <c r="K40" s="30"/>
       <c r="L40" s="30"/>
       <c r="M40" s="30"/>
@@ -33333,18 +33342,24 @@
         <v>258</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="C41" s="30"/>
+        <v>229</v>
+      </c>
+      <c r="C41" s="30">
+        <v>2025</v>
+      </c>
       <c r="D41" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="E41" s="30"/>
+        <v>228</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>225</v>
+      </c>
       <c r="F41" s="30"/>
       <c r="G41" s="30"/>
       <c r="H41" s="47"/>
       <c r="I41" s="30"/>
-      <c r="J41" s="30"/>
+      <c r="J41" s="30" t="s">
+        <v>103</v>
+      </c>
       <c r="K41" s="30"/>
       <c r="L41" s="30"/>
       <c r="M41" s="30"/>
@@ -33369,7 +33384,7 @@
       </c>
       <c r="C42" s="30"/>
       <c r="D42" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E42" s="30"/>
       <c r="F42" s="30"/>
@@ -33401,7 +33416,7 @@
       </c>
       <c r="C43" s="30"/>
       <c r="D43" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E43" s="30"/>
       <c r="F43" s="30"/>
@@ -33433,7 +33448,7 @@
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E44" s="30"/>
       <c r="F44" s="30"/>
@@ -33465,7 +33480,7 @@
       </c>
       <c r="C45" s="30"/>
       <c r="D45" s="30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E45" s="30"/>
       <c r="F45" s="30"/>
@@ -33497,7 +33512,7 @@
       </c>
       <c r="C46" s="30"/>
       <c r="D46" s="30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E46" s="30"/>
       <c r="F46" s="30"/>
@@ -33525,11 +33540,11 @@
         <v>258</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C47" s="30"/>
       <c r="D47" s="30" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="30"/>
@@ -33556,10 +33571,12 @@
       <c r="A48" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="B48" s="30"/>
+      <c r="B48" s="30" t="s">
+        <v>259</v>
+      </c>
       <c r="C48" s="30"/>
       <c r="D48" s="30" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="E48" s="30"/>
       <c r="F48" s="30"/>
@@ -33589,7 +33606,7 @@
       <c r="B49" s="30"/>
       <c r="C49" s="30"/>
       <c r="D49" s="30" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
@@ -33619,7 +33636,7 @@
       <c r="B50" s="30"/>
       <c r="C50" s="30"/>
       <c r="D50" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="30"/>
@@ -33649,7 +33666,7 @@
       <c r="B51" s="30"/>
       <c r="C51" s="30"/>
       <c r="D51" s="30" t="s">
-        <v>319</v>
+        <v>288</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="30"/>
@@ -33679,7 +33696,7 @@
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
       <c r="D52" s="30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E52" s="30"/>
       <c r="F52" s="30"/>
@@ -33709,7 +33726,7 @@
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
       <c r="D53" s="30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E53" s="30"/>
       <c r="F53" s="30"/>
@@ -33739,7 +33756,7 @@
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
       <c r="D54" s="30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E54" s="30"/>
       <c r="F54" s="30"/>
@@ -33769,7 +33786,7 @@
       <c r="B55" s="30"/>
       <c r="C55" s="30"/>
       <c r="D55" s="30" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E55" s="30"/>
       <c r="F55" s="30"/>
@@ -33799,11 +33816,9 @@
       <c r="B56" s="30"/>
       <c r="C56" s="30"/>
       <c r="D56" s="30" t="s">
-        <v>334</v>
-      </c>
-      <c r="E56" s="30" t="s">
-        <v>333</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="E56" s="30"/>
       <c r="F56" s="30"/>
       <c r="G56" s="30"/>
       <c r="H56" s="47"/>
@@ -33830,8 +33845,12 @@
       </c>
       <c r="B57" s="30"/>
       <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
+      <c r="D57" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="E57" s="30" t="s">
+        <v>333</v>
+      </c>
       <c r="F57" s="30"/>
       <c r="G57" s="30"/>
       <c r="H57" s="47"/>
@@ -33854,24 +33873,16 @@
     </row>
     <row r="58" spans="1:24" ht="20.25" customHeight="1">
       <c r="A58" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="B58" s="30" t="s">
-        <v>318</v>
-      </c>
-      <c r="C58" s="30">
-        <v>2025</v>
-      </c>
-      <c r="D58" s="50" t="s">
-        <v>311</v>
-      </c>
-      <c r="E58" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="F58" s="44"/>
+        <v>258</v>
+      </c>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
       <c r="G58" s="30"/>
       <c r="H58" s="47"/>
-      <c r="I58" s="22"/>
+      <c r="I58" s="30"/>
       <c r="J58" s="30"/>
       <c r="K58" s="30"/>
       <c r="L58" s="30"/>
@@ -33890,22 +33901,25 @@
     </row>
     <row r="59" spans="1:24" ht="20.25" customHeight="1">
       <c r="A59" s="30" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30" t="s">
-        <v>120</v>
+        <v>318</v>
+      </c>
+      <c r="C59" s="30">
+        <v>2025</v>
+      </c>
+      <c r="D59" s="50" t="s">
+        <v>311</v>
       </c>
       <c r="E59" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="F59" s="30"/>
+      <c r="F59" s="44"/>
       <c r="G59" s="30"/>
       <c r="H59" s="47"/>
-      <c r="I59" s="30"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="30"/>
       <c r="K59" s="30"/>
       <c r="L59" s="30"/>
       <c r="M59" s="30"/>
@@ -33923,22 +33937,22 @@
     </row>
     <row r="60" spans="1:24" ht="20.25" customHeight="1">
       <c r="A60" s="30" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="C60" s="30"/>
-      <c r="D60" s="35" t="s">
-        <v>154</v>
+      <c r="D60" s="30" t="s">
+        <v>120</v>
       </c>
       <c r="E60" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="I60"/>
-      <c r="J60" s="33" t="s">
-        <v>103</v>
-      </c>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="47"/>
+      <c r="I60" s="30"/>
       <c r="K60" s="30"/>
       <c r="L60" s="30"/>
       <c r="M60" s="30"/>
@@ -33962,12 +33976,13 @@
         <v>153</v>
       </c>
       <c r="C61" s="30"/>
-      <c r="D61" s="33" t="s">
-        <v>207</v>
+      <c r="D61" s="35" t="s">
+        <v>154</v>
       </c>
       <c r="E61" s="30" t="s">
         <v>152</v>
       </c>
+      <c r="I61"/>
       <c r="J61" s="33" t="s">
         <v>103</v>
       </c>
@@ -33988,22 +34003,18 @@
     </row>
     <row r="62" spans="1:24" ht="20.25" customHeight="1">
       <c r="A62" s="30" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B62" s="30" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="C62" s="30"/>
-      <c r="D62" s="30" t="s">
-        <v>155</v>
+      <c r="D62" s="33" t="s">
+        <v>207</v>
       </c>
       <c r="E62" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="F62" s="30"/>
-      <c r="G62" s="30"/>
-      <c r="H62" s="47"/>
-      <c r="I62" s="30"/>
       <c r="J62" s="33" t="s">
         <v>103</v>
       </c>
@@ -34023,16 +34034,26 @@
       <c r="X62" s="30"/>
     </row>
     <row r="63" spans="1:24" ht="20.25" customHeight="1">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="B63" s="30" t="s">
+        <v>52</v>
+      </c>
       <c r="C63" s="30"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
+      <c r="D63" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E63" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="F63" s="30"/>
       <c r="G63" s="30"/>
       <c r="H63" s="47"/>
       <c r="I63" s="30"/>
-      <c r="J63" s="30"/>
+      <c r="J63" s="33" t="s">
+        <v>103</v>
+      </c>
       <c r="K63" s="30"/>
       <c r="L63" s="30"/>
       <c r="M63" s="30"/>
@@ -58591,6 +58612,32 @@
       <c r="V1007" s="30"/>
       <c r="W1007" s="30"/>
       <c r="X1007" s="30"/>
+    </row>
+    <row r="1008" spans="1:24" ht="20.25" customHeight="1">
+      <c r="A1008" s="30"/>
+      <c r="B1008" s="30"/>
+      <c r="C1008" s="30"/>
+      <c r="D1008" s="30"/>
+      <c r="E1008" s="30"/>
+      <c r="F1008" s="30"/>
+      <c r="G1008" s="30"/>
+      <c r="H1008" s="47"/>
+      <c r="I1008" s="30"/>
+      <c r="J1008" s="30"/>
+      <c r="K1008" s="30"/>
+      <c r="L1008" s="30"/>
+      <c r="M1008" s="30"/>
+      <c r="N1008" s="30"/>
+      <c r="O1008" s="30"/>
+      <c r="P1008" s="30"/>
+      <c r="Q1008" s="30"/>
+      <c r="R1008" s="30"/>
+      <c r="S1008" s="30"/>
+      <c r="T1008" s="30"/>
+      <c r="U1008" s="30"/>
+      <c r="V1008" s="30"/>
+      <c r="W1008" s="30"/>
+      <c r="X1008" s="30"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J20" xr:uid="{00000000-0001-0000-0600-000000000000}">
@@ -58622,9 +58669,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4445EC-8FC5-4E63-800B-686D768A8FCC}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -58677,7 +58724,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16.5">
+    <row r="5" spans="1:5" ht="17.399999999999999">
       <c r="A5">
         <v>2026</v>
       </c>
@@ -58688,7 +58735,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.5">
+    <row r="6" spans="1:5" ht="13.8">
       <c r="A6" s="42"/>
     </row>
   </sheetData>
@@ -58704,14 +58751,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.7109375" customWidth="1"/>
-    <col min="5" max="5" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1"/>
+    <col min="5" max="5" width="46.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.75">
+    <row r="1" spans="1:21" ht="13.2">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -58748,7 +58795,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:21" ht="12.75">
+    <row r="2" spans="1:21" ht="13.2">
       <c r="A2" s="2" t="s">
         <v>122</v>
       </c>
@@ -58785,7 +58832,7 @@
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
     </row>
-    <row r="3" spans="1:21" ht="12.75">
+    <row r="3" spans="1:21" ht="13.2">
       <c r="A3" s="2" t="s">
         <v>122</v>
       </c>
@@ -58822,7 +58869,7 @@
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
     </row>
-    <row r="4" spans="1:21" ht="12.75">
+    <row r="4" spans="1:21" ht="13.2">
       <c r="A4" s="2" t="s">
         <v>122</v>
       </c>
@@ -58858,7 +58905,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
     </row>
-    <row r="5" spans="1:21" ht="12.75">
+    <row r="5" spans="1:21" ht="13.2">
       <c r="A5" s="2" t="s">
         <v>122</v>
       </c>
@@ -58895,7 +58942,7 @@
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
     </row>
-    <row r="6" spans="1:21" ht="14.25">
+    <row r="6" spans="1:21" ht="13.8">
       <c r="A6" s="2" t="s">
         <v>122</v>
       </c>
@@ -58932,7 +58979,7 @@
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
     </row>
-    <row r="7" spans="1:21" ht="13.5" thickBot="1">
+    <row r="7" spans="1:21" ht="13.8" thickBot="1">
       <c r="A7" s="2" t="s">
         <v>122</v>
       </c>
@@ -58969,7 +59016,7 @@
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
     </row>
-    <row r="8" spans="1:21" ht="13.5" thickBot="1">
+    <row r="8" spans="1:21" ht="13.8" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>122</v>
       </c>

--- a/data/CV_infolist.xlsx
+++ b/data/CV_infolist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sooyo\Documents\github\sylcv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA238B8-E062-416D-B9AF-4F5AC7327FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582A43AE-EC7F-4CB4-8B3C-22E5DA81B1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="14496" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
@@ -33065,7 +33065,7 @@
     </row>
     <row r="33" spans="1:24" ht="20.25" customHeight="1">
       <c r="A33" s="30" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="B33" s="30" t="s">
         <v>251</v>
@@ -33099,7 +33099,7 @@
     </row>
     <row r="34" spans="1:24" ht="20.25" customHeight="1">
       <c r="A34" s="30" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="B34" s="30" t="s">
         <v>251</v>
@@ -33133,7 +33133,7 @@
     </row>
     <row r="35" spans="1:24" ht="20.25" customHeight="1">
       <c r="A35" s="30" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="B35" s="30" t="s">
         <v>251</v>
@@ -33167,7 +33167,7 @@
     </row>
     <row r="36" spans="1:24" ht="20.25" customHeight="1">
       <c r="A36" s="30" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="B36" s="30" t="s">
         <v>251</v>

--- a/data/CV_infolist.xlsx
+++ b/data/CV_infolist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sooyo\Documents\github\sylcv\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slee2462\Documents\github\sylcv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582A43AE-EC7F-4CB4-8B3C-22E5DA81B1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE38B6E-F2F2-4380-980D-BC4CFE3125A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7992" yWindow="0" windowWidth="13968" windowHeight="12336" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="357">
   <si>
     <t>Degree</t>
   </si>
@@ -1103,9 +1103,6 @@
     <t>BMC Medical Research Methodology</t>
   </si>
   <si>
-    <t>Sooyong Lee, Myoungsung Lee, Sehee Hong</t>
-  </si>
-  <si>
     <t>How to Generate Data for Simulation-based Power Analysis</t>
   </si>
   <si>
@@ -1125,6 +1122,15 @@
   </si>
   <si>
     <t>Cory L. Cobb, Sooyong Lee, Lawson Kami, Schwartz Seth, Eddy J. Mark, &amp; Martinez Charles</t>
+  </si>
+  <si>
+    <t>Validity Study for AI-generated Sample and Responses for STEM gender stereotype</t>
+  </si>
+  <si>
+    <t>Sooyong Lee, Kahyun Lee, &amp; Allison Masters</t>
+  </si>
+  <si>
+    <t>Sooyong Lee, Myoungsung Lee, &amp; Sehee Hong</t>
   </si>
 </sst>
 </file>
@@ -1347,16 +1353,16 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="7"/>
+      <sz val="13"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="4">
@@ -31862,7 +31868,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:X1008"/>
+  <dimension ref="A1:X1009"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.44140625" style="33" customWidth="1"/>
@@ -32884,19 +32890,19 @@
         <v>97</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C28" s="30">
         <v>2026</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E28" s="30" t="s">
         <v>158</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G28" s="30"/>
       <c r="H28" s="47"/>
@@ -32999,7 +33005,7 @@
       <c r="C31" s="30">
         <v>2026</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="D31" s="54" t="s">
         <v>336</v>
       </c>
       <c r="E31" s="30" t="s">
@@ -33032,12 +33038,12 @@
         <v>97</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C32" s="30">
         <v>2026</v>
       </c>
-      <c r="D32" s="53" t="s">
+      <c r="D32" s="54" t="s">
         <v>339</v>
       </c>
       <c r="E32" s="30" t="s">
@@ -33065,18 +33071,20 @@
     </row>
     <row r="33" spans="1:24" ht="20.25" customHeight="1">
       <c r="A33" s="30" t="s">
-        <v>258</v>
+        <v>97</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>251</v>
+        <v>355</v>
       </c>
       <c r="C33" s="30">
         <v>2026</v>
       </c>
-      <c r="D33" s="53" t="s">
-        <v>348</v>
-      </c>
-      <c r="E33" s="30"/>
+      <c r="D33" s="54" t="s">
+        <v>354</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="F33" s="44"/>
       <c r="G33" s="30"/>
       <c r="H33" s="47"/>
@@ -33107,8 +33115,8 @@
       <c r="C34" s="30">
         <v>2026</v>
       </c>
-      <c r="D34" s="53" t="s">
-        <v>349</v>
+      <c r="D34" s="54" t="s">
+        <v>347</v>
       </c>
       <c r="E34" s="30"/>
       <c r="F34" s="44"/>
@@ -33141,8 +33149,8 @@
       <c r="C35" s="30">
         <v>2026</v>
       </c>
-      <c r="D35" s="53" t="s">
-        <v>350</v>
+      <c r="D35" s="54" t="s">
+        <v>348</v>
       </c>
       <c r="E35" s="30"/>
       <c r="F35" s="44"/>
@@ -33175,8 +33183,8 @@
       <c r="C36" s="30">
         <v>2026</v>
       </c>
-      <c r="D36" s="53" t="s">
-        <v>351</v>
+      <c r="D36" s="54" t="s">
+        <v>349</v>
       </c>
       <c r="E36" s="30"/>
       <c r="F36" s="44"/>
@@ -33204,13 +33212,13 @@
         <v>258</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>344</v>
+        <v>251</v>
       </c>
       <c r="C37" s="30">
         <v>2026</v>
       </c>
-      <c r="D37" s="53" t="s">
-        <v>343</v>
+      <c r="D37" s="54" t="s">
+        <v>350</v>
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="44"/>
@@ -33238,13 +33246,13 @@
         <v>258</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C38" s="30">
         <v>2026</v>
       </c>
-      <c r="D38" s="53" t="s">
-        <v>342</v>
+      <c r="D38" s="54" t="s">
+        <v>343</v>
       </c>
       <c r="E38" s="30"/>
       <c r="F38" s="44"/>
@@ -33272,13 +33280,13 @@
         <v>258</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>251</v>
+        <v>341</v>
       </c>
       <c r="C39" s="30">
         <v>2026</v>
       </c>
-      <c r="D39" s="53" t="s">
-        <v>340</v>
+      <c r="D39" s="54" t="s">
+        <v>342</v>
       </c>
       <c r="E39" s="30"/>
       <c r="F39" s="44"/>
@@ -33306,21 +33314,19 @@
         <v>258</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="C40" s="30">
-        <v>2025</v>
-      </c>
-      <c r="D40" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="E40" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="F40" s="30"/>
+        <v>2026</v>
+      </c>
+      <c r="D40" s="54" t="s">
+        <v>340</v>
+      </c>
+      <c r="E40" s="30"/>
+      <c r="F40" s="44"/>
       <c r="G40" s="30"/>
       <c r="H40" s="47"/>
-      <c r="I40" s="30"/>
+      <c r="I40" s="22"/>
       <c r="J40" s="30"/>
       <c r="K40" s="30"/>
       <c r="L40" s="30"/>
@@ -33342,13 +33348,13 @@
         <v>258</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C41" s="30">
         <v>2025</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E41" s="30" t="s">
         <v>225</v>
@@ -33357,9 +33363,7 @@
       <c r="G41" s="30"/>
       <c r="H41" s="47"/>
       <c r="I41" s="30"/>
-      <c r="J41" s="30" t="s">
-        <v>103</v>
-      </c>
+      <c r="J41" s="30"/>
       <c r="K41" s="30"/>
       <c r="L41" s="30"/>
       <c r="M41" s="30"/>
@@ -33380,18 +33384,24 @@
         <v>258</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="C42" s="30"/>
+        <v>229</v>
+      </c>
+      <c r="C42" s="30">
+        <v>2025</v>
+      </c>
       <c r="D42" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="E42" s="30"/>
+        <v>228</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>225</v>
+      </c>
       <c r="F42" s="30"/>
       <c r="G42" s="30"/>
       <c r="H42" s="47"/>
       <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
+      <c r="J42" s="30" t="s">
+        <v>103</v>
+      </c>
       <c r="K42" s="30"/>
       <c r="L42" s="30"/>
       <c r="M42" s="30"/>
@@ -33416,7 +33426,7 @@
       </c>
       <c r="C43" s="30"/>
       <c r="D43" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E43" s="30"/>
       <c r="F43" s="30"/>
@@ -33448,7 +33458,7 @@
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E44" s="30"/>
       <c r="F44" s="30"/>
@@ -33480,7 +33490,7 @@
       </c>
       <c r="C45" s="30"/>
       <c r="D45" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E45" s="30"/>
       <c r="F45" s="30"/>
@@ -33512,7 +33522,7 @@
       </c>
       <c r="C46" s="30"/>
       <c r="D46" s="30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E46" s="30"/>
       <c r="F46" s="30"/>
@@ -33544,7 +33554,7 @@
       </c>
       <c r="C47" s="30"/>
       <c r="D47" s="30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="30"/>
@@ -33572,11 +33582,11 @@
         <v>258</v>
       </c>
       <c r="B48" s="30" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C48" s="30"/>
       <c r="D48" s="30" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E48" s="30"/>
       <c r="F48" s="30"/>
@@ -33603,10 +33613,12 @@
       <c r="A49" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="B49" s="30"/>
+      <c r="B49" s="30" t="s">
+        <v>259</v>
+      </c>
       <c r="C49" s="30"/>
       <c r="D49" s="30" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
@@ -33636,7 +33648,7 @@
       <c r="B50" s="30"/>
       <c r="C50" s="30"/>
       <c r="D50" s="30" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="30"/>
@@ -33666,7 +33678,7 @@
       <c r="B51" s="30"/>
       <c r="C51" s="30"/>
       <c r="D51" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="30"/>
@@ -33696,7 +33708,7 @@
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
       <c r="D52" s="30" t="s">
-        <v>319</v>
+        <v>288</v>
       </c>
       <c r="E52" s="30"/>
       <c r="F52" s="30"/>
@@ -33726,7 +33738,7 @@
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
       <c r="D53" s="30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E53" s="30"/>
       <c r="F53" s="30"/>
@@ -33756,7 +33768,7 @@
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
       <c r="D54" s="30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E54" s="30"/>
       <c r="F54" s="30"/>
@@ -33786,7 +33798,7 @@
       <c r="B55" s="30"/>
       <c r="C55" s="30"/>
       <c r="D55" s="30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E55" s="30"/>
       <c r="F55" s="30"/>
@@ -33816,7 +33828,7 @@
       <c r="B56" s="30"/>
       <c r="C56" s="30"/>
       <c r="D56" s="30" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E56" s="30"/>
       <c r="F56" s="30"/>
@@ -33846,11 +33858,9 @@
       <c r="B57" s="30"/>
       <c r="C57" s="30"/>
       <c r="D57" s="30" t="s">
-        <v>334</v>
-      </c>
-      <c r="E57" s="30" t="s">
-        <v>333</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="E57" s="30"/>
       <c r="F57" s="30"/>
       <c r="G57" s="30"/>
       <c r="H57" s="47"/>
@@ -33877,8 +33887,12 @@
       </c>
       <c r="B58" s="30"/>
       <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
+      <c r="D58" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>333</v>
+      </c>
       <c r="F58" s="30"/>
       <c r="G58" s="30"/>
       <c r="H58" s="47"/>
@@ -33901,24 +33915,16 @@
     </row>
     <row r="59" spans="1:24" ht="20.25" customHeight="1">
       <c r="A59" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="B59" s="30" t="s">
-        <v>318</v>
-      </c>
-      <c r="C59" s="30">
-        <v>2025</v>
-      </c>
-      <c r="D59" s="50" t="s">
-        <v>311</v>
-      </c>
-      <c r="E59" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="F59" s="44"/>
+        <v>258</v>
+      </c>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
       <c r="G59" s="30"/>
       <c r="H59" s="47"/>
-      <c r="I59" s="22"/>
+      <c r="I59" s="30"/>
       <c r="J59" s="30"/>
       <c r="K59" s="30"/>
       <c r="L59" s="30"/>
@@ -33937,22 +33943,25 @@
     </row>
     <row r="60" spans="1:24" ht="20.25" customHeight="1">
       <c r="A60" s="30" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30" t="s">
-        <v>120</v>
+        <v>318</v>
+      </c>
+      <c r="C60" s="30">
+        <v>2025</v>
+      </c>
+      <c r="D60" s="50" t="s">
+        <v>311</v>
       </c>
       <c r="E60" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="F60" s="30"/>
+      <c r="F60" s="44"/>
       <c r="G60" s="30"/>
       <c r="H60" s="47"/>
-      <c r="I60" s="30"/>
+      <c r="I60" s="22"/>
+      <c r="J60" s="30"/>
       <c r="K60" s="30"/>
       <c r="L60" s="30"/>
       <c r="M60" s="30"/>
@@ -33970,22 +33979,22 @@
     </row>
     <row r="61" spans="1:24" ht="20.25" customHeight="1">
       <c r="A61" s="30" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="C61" s="30"/>
-      <c r="D61" s="35" t="s">
-        <v>154</v>
+      <c r="D61" s="30" t="s">
+        <v>120</v>
       </c>
       <c r="E61" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="I61"/>
-      <c r="J61" s="33" t="s">
-        <v>103</v>
-      </c>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="47"/>
+      <c r="I61" s="30"/>
       <c r="K61" s="30"/>
       <c r="L61" s="30"/>
       <c r="M61" s="30"/>
@@ -34009,12 +34018,13 @@
         <v>153</v>
       </c>
       <c r="C62" s="30"/>
-      <c r="D62" s="33" t="s">
-        <v>207</v>
+      <c r="D62" s="35" t="s">
+        <v>154</v>
       </c>
       <c r="E62" s="30" t="s">
         <v>152</v>
       </c>
+      <c r="I62"/>
       <c r="J62" s="33" t="s">
         <v>103</v>
       </c>
@@ -34035,22 +34045,18 @@
     </row>
     <row r="63" spans="1:24" ht="20.25" customHeight="1">
       <c r="A63" s="30" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B63" s="30" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="C63" s="30"/>
-      <c r="D63" s="30" t="s">
-        <v>155</v>
+      <c r="D63" s="33" t="s">
+        <v>207</v>
       </c>
       <c r="E63" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="F63" s="30"/>
-      <c r="G63" s="30"/>
-      <c r="H63" s="47"/>
-      <c r="I63" s="30"/>
       <c r="J63" s="33" t="s">
         <v>103</v>
       </c>
@@ -34070,16 +34076,26 @@
       <c r="X63" s="30"/>
     </row>
     <row r="64" spans="1:24" ht="20.25" customHeight="1">
-      <c r="A64" s="30"/>
-      <c r="B64" s="30"/>
+      <c r="A64" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" s="30" t="s">
+        <v>52</v>
+      </c>
       <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
+      <c r="D64" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E64" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="F64" s="30"/>
       <c r="G64" s="30"/>
       <c r="H64" s="47"/>
       <c r="I64" s="30"/>
-      <c r="J64" s="30"/>
+      <c r="J64" s="33" t="s">
+        <v>103</v>
+      </c>
       <c r="K64" s="30"/>
       <c r="L64" s="30"/>
       <c r="M64" s="30"/>
@@ -58638,6 +58654,32 @@
       <c r="V1008" s="30"/>
       <c r="W1008" s="30"/>
       <c r="X1008" s="30"/>
+    </row>
+    <row r="1009" spans="1:24" ht="20.25" customHeight="1">
+      <c r="A1009" s="30"/>
+      <c r="B1009" s="30"/>
+      <c r="C1009" s="30"/>
+      <c r="D1009" s="30"/>
+      <c r="E1009" s="30"/>
+      <c r="F1009" s="30"/>
+      <c r="G1009" s="30"/>
+      <c r="H1009" s="47"/>
+      <c r="I1009" s="30"/>
+      <c r="J1009" s="30"/>
+      <c r="K1009" s="30"/>
+      <c r="L1009" s="30"/>
+      <c r="M1009" s="30"/>
+      <c r="N1009" s="30"/>
+      <c r="O1009" s="30"/>
+      <c r="P1009" s="30"/>
+      <c r="Q1009" s="30"/>
+      <c r="R1009" s="30"/>
+      <c r="S1009" s="30"/>
+      <c r="T1009" s="30"/>
+      <c r="U1009" s="30"/>
+      <c r="V1009" s="30"/>
+      <c r="W1009" s="30"/>
+      <c r="X1009" s="30"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J20" xr:uid="{00000000-0001-0000-0600-000000000000}">
@@ -58731,7 +58773,7 @@
       <c r="B5" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="53" t="s">
         <v>346</v>
       </c>
     </row>

--- a/data/CV_infolist.xlsx
+++ b/data/CV_infolist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slee2462\Documents\github\sylcv\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sooyo\Documents\github\sylcv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE38B6E-F2F2-4380-980D-BC4CFE3125A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32810AB0-670A-459E-B062-C01C716C7106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7992" yWindow="0" windowWidth="13968" windowHeight="12336" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
@@ -938,9 +938,6 @@
     <t>Kei Bishop, Hacer Karamese, Syed Abdul Hadi, &amp; Sooyong Lee</t>
   </si>
   <si>
-    <t>International Objective Measurement Workshio</t>
-  </si>
-  <si>
     <t>Sooyong Lee, Kei Bishop, Hacer Karamese, &amp; Syed Abdul Hadi</t>
   </si>
   <si>
@@ -1124,13 +1121,16 @@
     <t>Cory L. Cobb, Sooyong Lee, Lawson Kami, Schwartz Seth, Eddy J. Mark, &amp; Martinez Charles</t>
   </si>
   <si>
-    <t>Validity Study for AI-generated Sample and Responses for STEM gender stereotype</t>
-  </si>
-  <si>
     <t>Sooyong Lee, Kahyun Lee, &amp; Allison Masters</t>
   </si>
   <si>
     <t>Sooyong Lee, Myoungsung Lee, &amp; Sehee Hong</t>
+  </si>
+  <si>
+    <t>Validity Study for AI-generated Sample and Responses for gender stereotype in STEM</t>
+  </si>
+  <si>
+    <t>International Objective Measurement Workshop</t>
   </si>
 </sst>
 </file>
@@ -2454,7 +2454,7 @@
         <v>35</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>37</v>
@@ -2929,10 +2929,10 @@
         <v>290</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>292</v>
+        <v>356</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -2963,16 +2963,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>289</v>
       </c>
       <c r="D17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>44</v>
@@ -3006,16 +3006,16 @@
         <v>19</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>289</v>
       </c>
       <c r="D18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>44</v>
@@ -3055,10 +3055,10 @@
         <v>289</v>
       </c>
       <c r="D19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>44</v>
@@ -3092,16 +3092,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="D20" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E20" s="21" t="s">
         <v>330</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>331</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>44</v>
@@ -32081,7 +32081,7 @@
         <v>105</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J5" s="30" t="s">
         <v>103</v>
@@ -32125,7 +32125,7 @@
         <v>110</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J6" s="30" t="s">
         <v>103</v>
@@ -32169,7 +32169,7 @@
         <v>114</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J7" s="30" t="s">
         <v>103</v>
@@ -32213,7 +32213,7 @@
         <v>183</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J8" s="30" t="s">
         <v>103</v>
@@ -32257,7 +32257,7 @@
         <v>272</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J9" s="30" t="s">
         <v>103</v>
@@ -32556,7 +32556,7 @@
       <c r="G17" s="30"/>
       <c r="H17" s="34"/>
       <c r="I17" s="22" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J17" s="33" t="s">
         <v>103</v>
@@ -32567,7 +32567,7 @@
         <v>216</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C18" s="33">
         <v>2025</v>
@@ -32581,10 +32581,10 @@
       </c>
       <c r="G18" s="46"/>
       <c r="H18" s="49" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="20.25" customHeight="1">
@@ -32598,7 +32598,7 @@
         <v>2025</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E19" s="30"/>
       <c r="F19" s="30" t="s">
@@ -32606,10 +32606,10 @@
       </c>
       <c r="G19" s="45"/>
       <c r="H19" s="47" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J19" s="30"/>
     </row>
@@ -32624,7 +32624,7 @@
         <v>2025</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E20" s="30" t="s">
         <v>173</v>
@@ -32635,7 +32635,7 @@
       <c r="G20" s="30"/>
       <c r="H20" s="47"/>
       <c r="I20" s="30" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J20" s="30"/>
     </row>
@@ -32658,7 +32658,7 @@
       </c>
       <c r="G21" s="45"/>
       <c r="H21" s="47" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I21" s="22" t="s">
         <v>270</v>
@@ -32687,7 +32687,7 @@
       <c r="G22" s="30"/>
       <c r="H22" s="47"/>
       <c r="I22" s="52" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J22" s="30"/>
       <c r="K22" s="30"/>
@@ -32752,7 +32752,7 @@
         <v>216</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C24" s="30">
         <v>2026</v>
@@ -32761,10 +32761,10 @@
         <v>180</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I24"/>
       <c r="J24" s="33" t="s">
@@ -32776,19 +32776,19 @@
         <v>97</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C25" s="30">
         <v>2026</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E25" s="30" t="s">
         <v>158</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G25" s="30"/>
       <c r="H25" s="47"/>
@@ -32860,7 +32860,7 @@
         <v>2026</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E27" s="30" t="s">
         <v>158</v>
@@ -32890,19 +32890,19 @@
         <v>97</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C28" s="30">
         <v>2026</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E28" s="30" t="s">
         <v>158</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G28" s="30"/>
       <c r="H28" s="47"/>
@@ -32928,13 +32928,13 @@
         <v>97</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C29" s="30">
         <v>2026</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E29" s="30" t="s">
         <v>152</v>
@@ -32964,13 +32964,13 @@
         <v>97</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C30" s="30">
         <v>2026</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E30" s="30" t="s">
         <v>152</v>
@@ -33000,19 +33000,19 @@
         <v>97</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C31" s="30">
         <v>2026</v>
       </c>
       <c r="D31" s="54" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E31" s="30" t="s">
         <v>158</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G31" s="30"/>
       <c r="H31" s="47"/>
@@ -33038,13 +33038,13 @@
         <v>97</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C32" s="30">
         <v>2026</v>
       </c>
       <c r="D32" s="54" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E32" s="30" t="s">
         <v>152</v>
@@ -33074,13 +33074,13 @@
         <v>97</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C33" s="30">
         <v>2026</v>
       </c>
       <c r="D33" s="54" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E33" s="30" t="s">
         <v>152</v>
@@ -33116,7 +33116,7 @@
         <v>2026</v>
       </c>
       <c r="D34" s="54" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E34" s="30"/>
       <c r="F34" s="44"/>
@@ -33150,7 +33150,7 @@
         <v>2026</v>
       </c>
       <c r="D35" s="54" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E35" s="30"/>
       <c r="F35" s="44"/>
@@ -33184,7 +33184,7 @@
         <v>2026</v>
       </c>
       <c r="D36" s="54" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E36" s="30"/>
       <c r="F36" s="44"/>
@@ -33218,7 +33218,7 @@
         <v>2026</v>
       </c>
       <c r="D37" s="54" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="44"/>
@@ -33246,13 +33246,13 @@
         <v>258</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C38" s="30">
         <v>2026</v>
       </c>
       <c r="D38" s="54" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E38" s="30"/>
       <c r="F38" s="44"/>
@@ -33280,13 +33280,13 @@
         <v>258</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C39" s="30">
         <v>2026</v>
       </c>
       <c r="D39" s="54" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E39" s="30"/>
       <c r="F39" s="44"/>
@@ -33320,7 +33320,7 @@
         <v>2026</v>
       </c>
       <c r="D40" s="54" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E40" s="30"/>
       <c r="F40" s="44"/>
@@ -33738,7 +33738,7 @@
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
       <c r="D53" s="30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E53" s="30"/>
       <c r="F53" s="30"/>
@@ -33768,7 +33768,7 @@
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
       <c r="D54" s="30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E54" s="30"/>
       <c r="F54" s="30"/>
@@ -33798,7 +33798,7 @@
       <c r="B55" s="30"/>
       <c r="C55" s="30"/>
       <c r="D55" s="30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E55" s="30"/>
       <c r="F55" s="30"/>
@@ -33828,7 +33828,7 @@
       <c r="B56" s="30"/>
       <c r="C56" s="30"/>
       <c r="D56" s="30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E56" s="30"/>
       <c r="F56" s="30"/>
@@ -33858,7 +33858,7 @@
       <c r="B57" s="30"/>
       <c r="C57" s="30"/>
       <c r="D57" s="30" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E57" s="30"/>
       <c r="F57" s="30"/>
@@ -33888,10 +33888,10 @@
       <c r="B58" s="30"/>
       <c r="C58" s="30"/>
       <c r="D58" s="30" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F58" s="30"/>
       <c r="G58" s="30"/>
@@ -33946,13 +33946,13 @@
         <v>230</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C60" s="30">
         <v>2025</v>
       </c>
       <c r="D60" s="50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E60" s="30" t="s">
         <v>152</v>
@@ -58774,7 +58774,7 @@
         <v>234</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="13.8">

--- a/data/CV_infolist.xlsx
+++ b/data/CV_infolist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sooyo\Documents\github\sylcv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9924FA93-EF42-40FD-821B-9B34CBAF637B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857C42C7-AAEA-49FA-910F-D6F0B17D47F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="438">
   <si>
     <t>Degree</t>
   </si>
@@ -285,9 +285,6 @@
   </si>
   <si>
     <t>2020/6-2020/8</t>
-  </si>
-  <si>
-    <t>Intern</t>
   </si>
   <si>
     <t>Embedded Standard Setting (ESS)</t>
@@ -1211,33 +1208,6 @@
     <t>2024/09</t>
   </si>
   <si>
-    <t>고급 통계를 위한 선형대수 기초 강의</t>
-  </si>
-  <si>
-    <t>잠재집단분석에 대한 기초 수업</t>
-  </si>
-  <si>
-    <t>R 패키지를 통한 통계 시뮬레이션 분석 소개</t>
-  </si>
-  <si>
-    <t>R을 활용하여 응용연구하는 법 소개</t>
-  </si>
-  <si>
-    <t>lavaan 패키지를 사용하여 잠재성장모형 분석 소개</t>
-  </si>
-  <si>
-    <t>통계 시뮬레이션을 위한 데이터 생성 강의</t>
-  </si>
-  <si>
-    <t>Shiny app 기초 수업</t>
-  </si>
-  <si>
-    <t>ggplot2 패키지를 활용한 데이터 시각화 강의</t>
-  </si>
-  <si>
-    <t>구조방정식 모형 분석 소프트웨어인 Mplus 활용법을 주제로 실습 세션을 운영</t>
-  </si>
-  <si>
     <t>visulization with ggplot2</t>
   </si>
   <si>
@@ -1301,9 +1271,6 @@
     <t>College of Education</t>
   </si>
   <si>
-    <t>Wisconsin Center for Education Research</t>
-  </si>
-  <si>
     <t>Institute of Educational Sciences (IES) grant
 \$891,895
 2021–2025 
@@ -1311,9 +1278,6 @@
   </si>
   <si>
     <t>대규모 무선할당실험(RCT) 데이터에서 발생하는 행동 로그를 인과 모형에 통합하는 FLPS(Fully Latent Principal Stratification) 방법론을 개발하는 프로젝트에 RA 로 참여하여 연구에 기여했습니다.</t>
-  </si>
-  <si>
-    <t>교육 평가 분야의 주요 기준 설정(Standard Setting) 기법인 Embedded Standard Setting의 창시자 Dr. Daniel Lewis와 협력하여, 해당 방법론을 웹 애플리케이션으로 구현하였습니다. 이 작업은 CreativeMeasurementSolution LLC 인턴십을 통해 수행되었으며, 전문가만 활용 가능했던 방법론을 실용적인 도구로 전환하여 현장 접근성을 높이는 데 기여하였습니다.</t>
   </si>
   <si>
     <t>컴퓨터 적응형 검사(CAT)를 학기 단위 종단 설계로 확장한 Multiple Administration Adaptive Testing(MAAT) 프로젝트에 참여하였습니다. 이 방법론은 가을·봄·여름 학기에 걸쳐 반복 시행되는 적응형 검사 환경에 최적화된 것으로, Dr. Seung Choi(UT Austin), Dr. Sangdon Lim(Cambium), Dr. Luping Niu(NCSBN)와 공동으로 R 패키지 maat를 개발·배포하였습니다.</t>
@@ -1328,25 +1292,94 @@
     <t>UT Austin 교육학과 졸업생의 진로 경로(career path)를 조사하고 기초 통계 분석을 수행하는 연구에 조교로 참여하였습니다.</t>
   </si>
   <si>
-    <t>성균관대학교 이태경 교수와 함께 협업</t>
+    <t>Cory L. Cobb, Sooyong Lee, &amp; Tae Kyoung Lee</t>
   </si>
   <si>
-    <t>부산대학교 이계진 교수와 함께 협업</t>
+    <t>성균관대학교 아동복지학 이태경 교수와 함께 협업</t>
   </si>
   <si>
-    <t>가천대학교 김수영 교수와 함께 협업</t>
+    <t>가천대학교 심리학 김수영 교수와 함께 협업</t>
   </si>
   <si>
-    <t>연세대학교 김한조 교수와 함께 협업</t>
+    <t>부산대학교 교육학과 이계진 교수와 함께 협업</t>
   </si>
   <si>
-    <t>전남대학교 김소영 교수와 함께 협업</t>
+    <t>가천대학교 심리학과 김수영 교수와 함께 협업</t>
   </si>
   <si>
-    <t>성균관대학교 장승민 교수와 협업</t>
+    <t>연세대학교 심리학과 김한조 교수와 함께 협업</t>
   </si>
   <si>
-    <t>Cory L. Cobb, Sooyong Lee, &amp; Tae Kyoung Lee</t>
+    <t>전남대학교 심리학과 김소영 교수와 함께 협업</t>
+  </si>
+  <si>
+    <t>성균관대학교 아동복지학과 이태경 교수와 함께 협업</t>
+  </si>
+  <si>
+    <t>성균관대학교 심리학과 장승민 교수와 협업</t>
+  </si>
+  <si>
+    <t>고려대학교 교육학과 홍세희 교수와 함께 협업</t>
+  </si>
+  <si>
+    <t>교육 평가 분야의 주요 기준 설정(Standard Setting) 기법인 Embedded Standard Setting의 창시자 Dr. Daniel Lewis와 협력하여, 해당 방법론을 웹 애플리케이션으로 구현하였습니다. CreativeMeasurementSolution LLC 에서 Research Follow로 일하며, 전문가만 활용 가능했던 방법론을 실용적인 도구로 전환하여 현장 접근성을 높이는 데 기여하였습니다.</t>
+  </si>
+  <si>
+    <t>직전 연도의 Research Followship을 이어 동일한 프로젝트에 기여했습니다.</t>
+  </si>
+  <si>
+    <t>Research Fellow</t>
+  </si>
+  <si>
+    <t>Wisconsin Center for Education Research
+Revenue: \$90M</t>
+  </si>
+  <si>
+    <t>구조방정식 모형 분석 소프트웨어인 Mplus 활용법을 주제로 실습 세션을 운영 (대학원생 대상)</t>
+  </si>
+  <si>
+    <t>구조방정식 모형 분석 소프트웨어인 Mplus 활용법을 주제로 실습 세션을 운영(대학원생 대상)</t>
+  </si>
+  <si>
+    <t>ggplot2 패키지를 활용한 데이터 시각화 강의(대학원생 대상)</t>
+  </si>
+  <si>
+    <t>Shiny app 기초 수업(대학원생 대상)</t>
+  </si>
+  <si>
+    <t>통계 시뮬레이션을 위한 데이터 생성 강의(대학원생 대상)</t>
+  </si>
+  <si>
+    <t>lavaan 패키지를 사용하여 잠재성장모형 분석 소개(대학원생 대상)</t>
+  </si>
+  <si>
+    <t>R을 활용하여 응용연구하는 법 소개(대학원생 대상)</t>
+  </si>
+  <si>
+    <t>R 패키지를 통한 통계 시뮬레이션 분석 소개(대학원생 대상)</t>
+  </si>
+  <si>
+    <t>고급 통계를 위한 선형대수 기초 강의(대학원생 대상)</t>
+  </si>
+  <si>
+    <t>잠재집단분석에 대한 기초 수업(대학원생 대상)</t>
+  </si>
+  <si>
+    <t>2020 - present</t>
+  </si>
+  <si>
+    <t>2023 - present</t>
+  </si>
+  <si>
+    <t>Professional 
+membership</t>
+  </si>
+  <si>
+    <t>Professional
+membership</t>
+  </si>
+  <si>
+    <t>Sooyong Lee &amp; Cory L. Cobb</t>
   </si>
 </sst>
 </file>
@@ -1629,7 +1662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1720,6 +1753,12 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1969,10 +2008,10 @@
     </row>
     <row r="2" spans="1:5" ht="39.6">
       <c r="A2" s="26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -1981,12 +2020,12 @@
         <v>6</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="13.8" thickBot="1">
       <c r="A3" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -1998,18 +2037,18 @@
         <v>9</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B4" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>134</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>135</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>9</v>
@@ -2051,7 +2090,7 @@
         <v>17</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -2069,7 +2108,7 @@
         <v>68</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>69</v>
@@ -2078,10 +2117,10 @@
         <v>70</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2099,7 +2138,7 @@
         <v>71</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>72</v>
@@ -2111,7 +2150,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -2129,19 +2168,19 @@
         <v>74</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -2159,19 +2198,19 @@
         <v>76</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -2186,22 +2225,22 @@
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E6" s="55" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -2219,19 +2258,19 @@
         <v>79</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -2245,22 +2284,22 @@
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -2275,22 +2314,22 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -2305,22 +2344,22 @@
     </row>
     <row r="10" spans="1:16" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="D10" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>413</v>
+        <v>216</v>
+      </c>
+      <c r="E10" s="56" t="s">
+        <v>422</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -2557,7 +2596,7 @@
         <v>20</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>21</v>
@@ -2602,7 +2641,7 @@
         <v>25</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>26</v>
@@ -2647,7 +2686,7 @@
         <v>30</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>31</v>
@@ -2692,13 +2731,13 @@
         <v>34</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>37</v>
@@ -2735,7 +2774,7 @@
         <v>38</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>39</v>
@@ -2775,13 +2814,13 @@
         <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>41</v>
@@ -2825,7 +2864,7 @@
         <v>44</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>45</v>
@@ -2870,7 +2909,7 @@
         <v>48</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>49</v>
@@ -2915,7 +2954,7 @@
         <v>50</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>51</v>
@@ -2955,16 +2994,16 @@
         <v>40</v>
       </c>
       <c r="B11" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" s="21" t="s">
         <v>148</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>149</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>42</v>
@@ -2996,19 +3035,19 @@
         <v>19</v>
       </c>
       <c r="B12" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="D12" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="E12" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="F12" s="27" t="s">
         <v>186</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>187</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -3040,16 +3079,16 @@
         <v>50</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E13" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" s="27" t="s">
         <v>186</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>187</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -3078,19 +3117,19 @@
         <v>40</v>
       </c>
       <c r="B14" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" t="s">
+        <v>231</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C14" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" s="21" t="s">
         <v>232</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>233</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -3121,19 +3160,19 @@
         <v>40</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C15" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>235</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -3164,19 +3203,19 @@
         <v>40</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C16" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="E16" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -3207,16 +3246,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>42</v>
@@ -3250,16 +3289,16 @@
         <v>19</v>
       </c>
       <c r="B18" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="D18" t="s">
         <v>290</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="D18" t="s">
-        <v>291</v>
-      </c>
       <c r="E18" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>42</v>
@@ -3293,16 +3332,16 @@
         <v>40</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>42</v>
@@ -3336,16 +3375,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="D20" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E20" s="21" t="s">
         <v>325</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>326</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>42</v>
@@ -31955,13 +31994,13 @@
         <v>17</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -31984,16 +32023,16 @@
         <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>391</v>
+        <v>423</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -32027,16 +32066,16 @@
         <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -32061,187 +32100,187 @@
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D4" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C5" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="D5" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C6" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D6" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="F6" t="s">
-        <v>388</v>
+        <v>427</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1">
       <c r="A7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D7" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="F7" t="s">
-        <v>387</v>
+        <v>428</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1">
       <c r="A8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D8" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="F8" t="s">
-        <v>386</v>
+        <v>429</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1">
       <c r="A9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D9" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="F9" t="s">
-        <v>385</v>
+        <v>430</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1">
       <c r="A10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C10" t="s">
+        <v>369</v>
+      </c>
+      <c r="D10" t="s">
+        <v>397</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F10" t="s">
+        <v>431</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H10" s="22" t="s">
         <v>370</v>
-      </c>
-      <c r="D10" t="s">
-        <v>407</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F10" t="s">
-        <v>383</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1">
       <c r="A11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C11" t="s">
+        <v>371</v>
+      </c>
+      <c r="D11" t="s">
+        <v>398</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F11" t="s">
+        <v>432</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H11" s="22" t="s">
         <v>372</v>
-      </c>
-      <c r="D11" t="s">
-        <v>408</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F11" t="s">
-        <v>384</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="H11" s="22" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1">
@@ -32279,21 +32318,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C2" s="1">
         <v>5</v>
@@ -32301,10 +32340,10 @@
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -32312,10 +32351,10 @@
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -32366,25 +32405,25 @@
         <v>17</v>
       </c>
       <c r="F1" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="H1" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="47" t="s">
+      <c r="I1" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="30" t="s">
-        <v>94</v>
-      </c>
       <c r="J1" s="30" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="K1" s="30" t="s">
         <v>55</v>
       </c>
       <c r="L1" s="30" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="M1" s="30" t="s">
         <v>18</v>
@@ -32406,34 +32445,34 @@
     </row>
     <row r="2" spans="1:27" ht="20.25" customHeight="1">
       <c r="A2" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C2" s="30">
         <v>2016</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G2" s="33">
         <v>50</v>
       </c>
       <c r="H2" s="47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N2" s="30"/>
       <c r="O2" s="30"/>
@@ -32452,35 +32491,35 @@
     </row>
     <row r="3" spans="1:27" ht="20.25" customHeight="1">
       <c r="A3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C3" s="30">
         <v>2016</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E3" s="30"/>
       <c r="F3" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="H3" s="47" t="s">
         <v>145</v>
-      </c>
-      <c r="H3" s="47" t="s">
-        <v>146</v>
       </c>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="K3"/>
       <c r="L3"/>
       <c r="M3" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N3" s="30"/>
       <c r="O3" s="30"/>
@@ -32499,39 +32538,39 @@
     </row>
     <row r="4" spans="1:27" ht="20.25" customHeight="1">
       <c r="A4" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="30" t="s">
         <v>95</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>96</v>
       </c>
       <c r="C4" s="31">
         <v>2021</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E4" s="30"/>
       <c r="F4" s="30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G4" s="31">
         <v>81</v>
       </c>
       <c r="H4" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="I4" t="s">
         <v>99</v>
       </c>
-      <c r="I4" t="s">
-        <v>100</v>
-      </c>
       <c r="J4" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="K4"/>
       <c r="L4" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="M4" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N4" s="30"/>
       <c r="O4" s="30"/>
@@ -32550,7 +32589,7 @@
     </row>
     <row r="5" spans="1:27" ht="20.25" customHeight="1">
       <c r="A5" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B5" s="30" t="s">
         <v>34</v>
@@ -32563,24 +32602,24 @@
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G5" s="31">
         <v>29</v>
       </c>
       <c r="H5" s="47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K5" s="22"/>
       <c r="L5" s="22"/>
       <c r="M5" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N5" s="30"/>
       <c r="O5" s="30"/>
@@ -32599,37 +32638,37 @@
     </row>
     <row r="6" spans="1:27" ht="20.25" customHeight="1">
       <c r="A6" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="31">
         <v>2022</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="H6" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="H6" s="47" t="s">
-        <v>108</v>
-      </c>
       <c r="I6" s="22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="22"/>
       <c r="M6" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N6" s="30"/>
       <c r="O6" s="30"/>
@@ -32648,7 +32687,7 @@
     </row>
     <row r="7" spans="1:27" ht="20.25" customHeight="1">
       <c r="A7" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B7" s="30" t="s">
         <v>38</v>
@@ -32657,28 +32696,28 @@
         <v>2022</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="H7" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="H7" s="47" t="s">
-        <v>112</v>
-      </c>
       <c r="I7" s="22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="22"/>
       <c r="M7" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N7" s="30"/>
       <c r="O7" s="30"/>
@@ -32697,7 +32736,7 @@
     </row>
     <row r="8" spans="1:27" ht="20.25" customHeight="1">
       <c r="A8" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B8" s="30" t="s">
         <v>34</v>
@@ -32706,28 +32745,28 @@
         <v>2023</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E8" s="30"/>
       <c r="F8" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G8" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="H8" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="H8" s="34" t="s">
-        <v>181</v>
-      </c>
       <c r="I8" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K8" s="22"/>
       <c r="L8" s="22"/>
       <c r="M8" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N8" s="30"/>
       <c r="O8" s="30"/>
@@ -32746,37 +32785,37 @@
     </row>
     <row r="9" spans="1:27" ht="20.25" customHeight="1">
       <c r="A9" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C9" s="31">
         <v>2023</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G9" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="H9" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="H9" s="34" t="s">
-        <v>269</v>
-      </c>
       <c r="I9" s="22" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K9" s="22"/>
       <c r="L9" s="22"/>
       <c r="M9" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N9" s="30"/>
       <c r="O9" s="30"/>
@@ -32795,7 +32834,7 @@
     </row>
     <row r="10" spans="1:27" ht="20.25" customHeight="1">
       <c r="A10" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10" s="30" t="s">
         <v>50</v>
@@ -32804,28 +32843,28 @@
         <v>2023</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G10" s="30"/>
       <c r="H10" s="34" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K10" s="22"/>
       <c r="L10" s="22"/>
       <c r="M10" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N10" s="30"/>
       <c r="O10" s="30"/>
@@ -32844,7 +32883,7 @@
     </row>
     <row r="11" spans="1:27" ht="20.25" customHeight="1">
       <c r="A11" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B11" s="30" t="s">
         <v>38</v>
@@ -32853,28 +32892,28 @@
         <v>2024</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G11" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="H11" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="H11" s="47" t="s">
-        <v>230</v>
-      </c>
       <c r="I11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K11" s="22"/>
       <c r="L11" s="22"/>
       <c r="M11" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N11" s="30"/>
       <c r="O11" s="30"/>
@@ -32893,7 +32932,7 @@
     </row>
     <row r="12" spans="1:27" ht="20.25" customHeight="1">
       <c r="A12" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="30" t="s">
         <v>50</v>
@@ -32902,28 +32941,28 @@
         <v>2025</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G12" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="H12" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="H12" s="47" t="s">
-        <v>281</v>
-      </c>
       <c r="I12" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
       <c r="M12" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N12" s="30"/>
       <c r="O12" s="30"/>
@@ -32942,39 +32981,39 @@
     </row>
     <row r="13" spans="1:27" ht="20.25" customHeight="1">
       <c r="A13" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C13" s="30">
         <v>2024</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G13" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="H13" s="48" t="s">
         <v>270</v>
       </c>
-      <c r="H13" s="48" t="s">
-        <v>271</v>
-      </c>
       <c r="I13" s="22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K13" s="22"/>
       <c r="L13" s="30" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="M13" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N13" s="30"/>
       <c r="P13" s="30"/>
@@ -32992,100 +33031,100 @@
     </row>
     <row r="14" spans="1:27" ht="20.25" customHeight="1">
       <c r="A14" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" s="33" t="s">
         <v>213</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>214</v>
       </c>
       <c r="C14" s="33">
         <v>2024</v>
       </c>
       <c r="D14" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="I14" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="E14" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>243</v>
-      </c>
       <c r="J14" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K14" s="22"/>
       <c r="L14" s="22" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="M14" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="20.25" customHeight="1">
       <c r="A15" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C15" s="30">
         <v>2025</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G15" s="33">
         <v>12</v>
       </c>
       <c r="H15" s="49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K15" s="22"/>
       <c r="L15" s="22"/>
       <c r="M15" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="20.25" customHeight="1">
       <c r="A16" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C16" s="30">
         <v>2025</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E16" s="30"/>
       <c r="F16" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G16" s="30">
         <v>12</v>
       </c>
       <c r="H16" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K16" s="22"/>
       <c r="L16" s="22"/>
@@ -33093,7 +33132,7 @@
     </row>
     <row r="17" spans="1:27" ht="20.25" customHeight="1">
       <c r="A17" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17" s="30" t="s">
         <v>50</v>
@@ -33102,150 +33141,150 @@
         <v>2025</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E17" s="30"/>
       <c r="F17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G17" s="30"/>
       <c r="H17" s="34"/>
       <c r="I17" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K17" s="22"/>
       <c r="L17" s="22"/>
       <c r="M17" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="20.25" customHeight="1">
       <c r="A18" s="33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C18" s="33">
         <v>2025</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E18" s="30"/>
       <c r="F18" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G18" s="46"/>
       <c r="H18" s="49" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K18" s="22"/>
       <c r="L18" s="22" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="20.25" customHeight="1">
       <c r="A19" s="33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C19" s="30">
         <v>2025</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E19" s="30"/>
       <c r="F19" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G19" s="45"/>
       <c r="H19" s="47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K19" s="22"/>
       <c r="L19" s="22" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="M19" s="30"/>
     </row>
     <row r="20" spans="1:27" ht="20.25" customHeight="1">
       <c r="A20" s="33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C20" s="30">
         <v>2025</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G20" s="30"/>
       <c r="H20" s="47"/>
       <c r="I20" s="30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J20" s="30" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K20" s="30"/>
       <c r="L20" s="30" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="M20" s="30"/>
     </row>
     <row r="21" spans="1:27" ht="20.25" customHeight="1">
       <c r="A21" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C21" s="30">
         <v>2025</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E21" s="30"/>
       <c r="F21" s="30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G21" s="45"/>
       <c r="H21" s="47" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K21" s="22"/>
       <c r="L21" s="22"/>
@@ -33253,34 +33292,34 @@
     </row>
     <row r="22" spans="1:27" ht="20.25" customHeight="1">
       <c r="A22" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C22" s="30">
         <v>2026</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G22" s="30"/>
       <c r="H22" s="47"/>
       <c r="I22" s="52" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J22" s="52" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K22" s="52"/>
       <c r="L22" s="52" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M22" s="30"/>
       <c r="N22" s="30"/>
@@ -33300,35 +33339,35 @@
     </row>
     <row r="23" spans="1:27" ht="20.25" customHeight="1">
       <c r="A23" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C23" s="30">
         <v>2023</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G23" s="30"/>
       <c r="H23" s="47"/>
       <c r="I23" s="22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
       <c r="M23" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N23" s="30"/>
       <c r="O23" s="30"/>
@@ -33347,61 +33386,61 @@
     </row>
     <row r="24" spans="1:27" ht="20.25" customHeight="1">
       <c r="A24" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C24" s="30">
         <v>2026</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I24"/>
       <c r="J24" s="22" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
       <c r="M24" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="20.25" customHeight="1">
       <c r="A25" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C25" s="30">
         <v>2026</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G25" s="30"/>
       <c r="H25" s="47"/>
       <c r="I25" s="22"/>
       <c r="J25" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K25" s="22"/>
       <c r="L25" s="22" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M25" s="30"/>
       <c r="N25" s="30"/>
@@ -33421,35 +33460,35 @@
     </row>
     <row r="26" spans="1:27" ht="20.25" customHeight="1">
       <c r="A26" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="C26" s="30">
         <v>2026</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G26" s="30"/>
       <c r="H26" s="47"/>
       <c r="I26" s="30"/>
       <c r="J26" s="30" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="K26" s="30"/>
       <c r="L26" s="30" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="M26" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N26" s="30"/>
       <c r="O26" s="30"/>
@@ -33468,26 +33507,26 @@
     </row>
     <row r="27" spans="1:27" ht="20.25" customHeight="1">
       <c r="A27" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C27" s="30">
         <v>2026</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F27" s="30"/>
       <c r="G27" s="30"/>
       <c r="H27" s="47"/>
       <c r="I27" s="30"/>
       <c r="J27" s="30" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="K27" s="30"/>
       <c r="L27" s="30"/>
@@ -33509,28 +33548,28 @@
     </row>
     <row r="28" spans="1:27" ht="20.25" customHeight="1">
       <c r="A28" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C28" s="30">
         <v>2026</v>
       </c>
       <c r="D28" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" s="30" t="s">
         <v>346</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="F28" s="30" t="s">
-        <v>347</v>
       </c>
       <c r="G28" s="30"/>
       <c r="H28" s="47"/>
       <c r="I28" s="30"/>
       <c r="J28" s="30" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="K28" s="30"/>
       <c r="L28" s="30"/>
@@ -33552,26 +33591,26 @@
     </row>
     <row r="29" spans="1:27" ht="20.25" customHeight="1">
       <c r="A29" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C29" s="30">
         <v>2026</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F29" s="44"/>
       <c r="G29" s="30"/>
       <c r="H29" s="47"/>
       <c r="I29" s="22"/>
       <c r="J29" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
@@ -33593,26 +33632,26 @@
     </row>
     <row r="30" spans="1:27" ht="20.25" customHeight="1">
       <c r="A30" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C30" s="30">
         <v>2026</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="E30" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F30" s="44"/>
       <c r="G30" s="30"/>
       <c r="H30" s="47"/>
       <c r="I30" s="22"/>
       <c r="J30" s="22" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
@@ -33634,28 +33673,28 @@
     </row>
     <row r="31" spans="1:27" ht="20.25" customHeight="1">
       <c r="A31" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C31" s="30">
         <v>2026</v>
       </c>
       <c r="D31" s="54" t="s">
+        <v>330</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="F31" s="44" t="s">
         <v>331</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="F31" s="44" t="s">
-        <v>332</v>
       </c>
       <c r="G31" s="30"/>
       <c r="H31" s="47"/>
       <c r="I31" s="22"/>
       <c r="J31" s="22" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
@@ -33677,31 +33716,33 @@
     </row>
     <row r="32" spans="1:27" ht="20.25" customHeight="1">
       <c r="A32" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C32" s="30">
         <v>2026</v>
       </c>
       <c r="D32" s="54" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E32" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F32" s="44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G32" s="30"/>
       <c r="H32" s="47"/>
       <c r="I32" s="22"/>
       <c r="J32" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
+      <c r="L32" s="22" t="s">
+        <v>418</v>
+      </c>
       <c r="M32" s="30"/>
       <c r="N32" s="30"/>
       <c r="O32" s="30"/>
@@ -33720,26 +33761,26 @@
     </row>
     <row r="33" spans="1:27" ht="20.25" customHeight="1">
       <c r="A33" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C33" s="30">
         <v>2026</v>
       </c>
       <c r="D33" s="54" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E33" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F33" s="44"/>
       <c r="G33" s="30"/>
       <c r="H33" s="47"/>
       <c r="I33" s="22"/>
       <c r="J33" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K33" s="22"/>
       <c r="L33" s="22"/>
@@ -33761,26 +33802,26 @@
     </row>
     <row r="34" spans="1:27" ht="20.25" customHeight="1">
       <c r="A34" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C34" s="30">
         <v>2026</v>
       </c>
       <c r="D34" s="54" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F34" s="44"/>
       <c r="G34" s="30"/>
       <c r="H34" s="47"/>
       <c r="I34" s="22"/>
       <c r="J34" s="22" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
@@ -33802,31 +33843,31 @@
     </row>
     <row r="35" spans="1:27" ht="20.25" customHeight="1">
       <c r="A35" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C35" s="30">
         <v>2026</v>
       </c>
       <c r="D35" s="54" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F35" s="44" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G35" s="30"/>
       <c r="H35" s="47"/>
       <c r="J35" s="22" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="K35" s="22"/>
       <c r="L35" s="22" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="M35" s="30"/>
       <c r="N35" s="30"/>
@@ -33846,28 +33887,28 @@
     </row>
     <row r="36" spans="1:27" ht="20.25" customHeight="1">
       <c r="A36" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C36" s="30">
         <v>2026</v>
       </c>
       <c r="D36" s="54" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E36" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F36" s="44" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G36" s="30"/>
       <c r="H36" s="47"/>
       <c r="I36" s="22"/>
       <c r="J36" s="22" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="K36" s="22"/>
       <c r="L36" s="22"/>
@@ -33889,23 +33930,27 @@
     </row>
     <row r="37" spans="1:27" ht="20.25" customHeight="1">
       <c r="A37" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>248</v>
+        <v>437</v>
       </c>
       <c r="C37" s="30">
         <v>2026</v>
       </c>
       <c r="D37" s="54" t="s">
-        <v>343</v>
-      </c>
-      <c r="E37" s="30"/>
+        <v>342</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>149</v>
+      </c>
       <c r="F37" s="44"/>
       <c r="G37" s="30"/>
       <c r="H37" s="47"/>
       <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
+      <c r="J37" s="22" t="s">
+        <v>388</v>
+      </c>
       <c r="K37" s="22"/>
       <c r="L37" s="22"/>
       <c r="M37" s="30"/>
@@ -33926,16 +33971,16 @@
     </row>
     <row r="38" spans="1:27" ht="20.25" customHeight="1">
       <c r="A38" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C38" s="30">
         <v>2026</v>
       </c>
       <c r="D38" s="54" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E38" s="30"/>
       <c r="F38" s="44"/>
@@ -33963,16 +34008,16 @@
     </row>
     <row r="39" spans="1:27" ht="20.25" customHeight="1">
       <c r="A39" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C39" s="30">
         <v>2026</v>
       </c>
       <c r="D39" s="54" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E39" s="30"/>
       <c r="F39" s="44"/>
@@ -34000,16 +34045,16 @@
     </row>
     <row r="40" spans="1:27" ht="20.25" customHeight="1">
       <c r="A40" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C40" s="30">
         <v>2026</v>
       </c>
       <c r="D40" s="54" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E40" s="30"/>
       <c r="F40" s="44"/>
@@ -34037,16 +34082,16 @@
     </row>
     <row r="41" spans="1:27" ht="20.25" customHeight="1">
       <c r="A41" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C41" s="30">
         <v>2026</v>
       </c>
       <c r="D41" s="54" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E41" s="30"/>
       <c r="F41" s="44"/>
@@ -34074,23 +34119,27 @@
     </row>
     <row r="42" spans="1:27" ht="20.25" customHeight="1">
       <c r="A42" s="30" t="s">
-        <v>255</v>
+        <v>94</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C42" s="30">
         <v>2026</v>
       </c>
       <c r="D42" s="54" t="s">
-        <v>335</v>
-      </c>
-      <c r="E42" s="30"/>
+        <v>334</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>149</v>
+      </c>
       <c r="F42" s="44"/>
       <c r="G42" s="30"/>
       <c r="H42" s="47"/>
       <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
+      <c r="J42" s="22" t="s">
+        <v>388</v>
+      </c>
       <c r="K42" s="22"/>
       <c r="L42" s="22"/>
       <c r="M42" s="30"/>
@@ -34111,25 +34160,27 @@
     </row>
     <row r="43" spans="1:27" ht="20.25" customHeight="1">
       <c r="A43" s="30" t="s">
-        <v>255</v>
+        <v>94</v>
       </c>
       <c r="B43" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C43" s="30">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F43" s="30"/>
       <c r="G43" s="30"/>
       <c r="H43" s="47"/>
       <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
+      <c r="J43" s="30" t="s">
+        <v>388</v>
+      </c>
       <c r="K43" s="30"/>
       <c r="L43" s="30"/>
       <c r="M43" s="30"/>
@@ -34150,19 +34201,19 @@
     </row>
     <row r="44" spans="1:27" ht="20.25" customHeight="1">
       <c r="A44" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B44" s="30" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C44" s="30">
         <v>2025</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F44" s="30"/>
       <c r="G44" s="30"/>
@@ -34172,7 +34223,7 @@
       <c r="K44" s="30"/>
       <c r="L44" s="30"/>
       <c r="M44" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N44" s="30"/>
       <c r="O44" s="30"/>
@@ -34191,14 +34242,14 @@
     </row>
     <row r="45" spans="1:27" ht="20.25" customHeight="1">
       <c r="A45" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C45" s="30"/>
       <c r="D45" s="30" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E45" s="30"/>
       <c r="F45" s="30"/>
@@ -34226,14 +34277,14 @@
     </row>
     <row r="46" spans="1:27" ht="20.25" customHeight="1">
       <c r="A46" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C46" s="30"/>
       <c r="D46" s="30" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E46" s="30"/>
       <c r="F46" s="30"/>
@@ -34261,14 +34312,14 @@
     </row>
     <row r="47" spans="1:27" ht="20.25" customHeight="1">
       <c r="A47" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C47" s="30"/>
       <c r="D47" s="30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="30"/>
@@ -34296,14 +34347,14 @@
     </row>
     <row r="48" spans="1:27" ht="20.25" customHeight="1">
       <c r="A48" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B48" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C48" s="30"/>
       <c r="D48" s="30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E48" s="30"/>
       <c r="F48" s="30"/>
@@ -34331,14 +34382,14 @@
     </row>
     <row r="49" spans="1:27" ht="20.25" customHeight="1">
       <c r="A49" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C49" s="30"/>
       <c r="D49" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
@@ -34366,14 +34417,14 @@
     </row>
     <row r="50" spans="1:27" ht="20.25" customHeight="1">
       <c r="A50" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B50" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C50" s="30"/>
       <c r="D50" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="30"/>
@@ -34401,14 +34452,14 @@
     </row>
     <row r="51" spans="1:27" ht="20.25" customHeight="1">
       <c r="A51" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B51" s="30" t="s">
         <v>255</v>
-      </c>
-      <c r="B51" s="30" t="s">
-        <v>256</v>
       </c>
       <c r="C51" s="30"/>
       <c r="D51" s="30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="30"/>
@@ -34436,12 +34487,12 @@
     </row>
     <row r="52" spans="1:27" ht="20.25" customHeight="1">
       <c r="A52" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
       <c r="D52" s="30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E52" s="30"/>
       <c r="F52" s="30"/>
@@ -34469,12 +34520,12 @@
     </row>
     <row r="53" spans="1:27" ht="20.25" customHeight="1">
       <c r="A53" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
       <c r="D53" s="30" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E53" s="30"/>
       <c r="F53" s="30"/>
@@ -34502,12 +34553,12 @@
     </row>
     <row r="54" spans="1:27" ht="20.25" customHeight="1">
       <c r="A54" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
       <c r="D54" s="30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E54" s="30"/>
       <c r="F54" s="30"/>
@@ -34535,12 +34586,12 @@
     </row>
     <row r="55" spans="1:27" ht="20.25" customHeight="1">
       <c r="A55" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="30"/>
       <c r="D55" s="30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E55" s="30"/>
       <c r="F55" s="30"/>
@@ -34568,12 +34619,12 @@
     </row>
     <row r="56" spans="1:27" ht="20.25" customHeight="1">
       <c r="A56" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B56" s="30"/>
       <c r="C56" s="30"/>
       <c r="D56" s="30" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E56" s="30"/>
       <c r="F56" s="30"/>
@@ -34601,12 +34652,12 @@
     </row>
     <row r="57" spans="1:27" ht="20.25" customHeight="1">
       <c r="A57" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B57" s="30"/>
       <c r="C57" s="30"/>
       <c r="D57" s="30" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E57" s="30"/>
       <c r="F57" s="30"/>
@@ -34634,12 +34685,12 @@
     </row>
     <row r="58" spans="1:27" ht="20.25" customHeight="1">
       <c r="A58" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B58" s="30"/>
       <c r="C58" s="30"/>
       <c r="D58" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E58" s="30"/>
       <c r="F58" s="30"/>
@@ -34667,12 +34718,12 @@
     </row>
     <row r="59" spans="1:27" ht="20.25" customHeight="1">
       <c r="A59" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B59" s="30"/>
       <c r="C59" s="30"/>
       <c r="D59" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E59" s="30"/>
       <c r="F59" s="30"/>
@@ -34700,15 +34751,15 @@
     </row>
     <row r="60" spans="1:27" ht="20.25" customHeight="1">
       <c r="A60" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B60" s="30"/>
       <c r="C60" s="30"/>
       <c r="D60" s="30" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E60" s="30" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F60" s="30"/>
       <c r="G60" s="30"/>
@@ -34735,7 +34786,7 @@
     </row>
     <row r="61" spans="1:27" ht="20.25" customHeight="1">
       <c r="A61" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B61" s="30"/>
       <c r="C61" s="30"/>
@@ -34766,19 +34817,19 @@
     </row>
     <row r="62" spans="1:27" ht="20.25" customHeight="1">
       <c r="A62" s="30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B62" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C62" s="30">
         <v>2025</v>
       </c>
       <c r="D62" s="50" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E62" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F62" s="44"/>
       <c r="G62" s="30"/>
@@ -34805,17 +34856,17 @@
     </row>
     <row r="63" spans="1:27" ht="20.25" customHeight="1">
       <c r="A63" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B63" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C63" s="30"/>
       <c r="D63" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E63" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F63" s="30"/>
       <c r="G63" s="30"/>
@@ -34841,24 +34892,24 @@
     </row>
     <row r="64" spans="1:27" ht="20.25" customHeight="1">
       <c r="A64" s="30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B64" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C64" s="30"/>
       <c r="D64" s="35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I64"/>
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64"/>
       <c r="M64" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N64" s="30"/>
       <c r="O64" s="30"/>
@@ -34877,20 +34928,20 @@
     </row>
     <row r="65" spans="1:27" ht="20.25" customHeight="1">
       <c r="A65" s="30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B65" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C65" s="30"/>
       <c r="D65" s="33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E65" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M65" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N65" s="30"/>
       <c r="O65" s="30"/>
@@ -34909,17 +34960,17 @@
     </row>
     <row r="66" spans="1:27" ht="20.25" customHeight="1">
       <c r="A66" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B66" s="30" t="s">
         <v>50</v>
       </c>
       <c r="C66" s="30"/>
       <c r="D66" s="30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E66" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F66" s="30"/>
       <c r="G66" s="30"/>
@@ -34929,7 +34980,7 @@
       <c r="K66" s="30"/>
       <c r="L66" s="30"/>
       <c r="M66" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N66" s="30"/>
       <c r="O66" s="30"/>
@@ -62380,7 +62431,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4445EC-8FC5-4E63-800B-686D768A8FCC}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -62405,13 +62456,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -62419,10 +62470,10 @@
         <v>2024</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -62430,10 +62481,10 @@
         <v>2024</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="17.399999999999999">
@@ -62441,14 +62492,33 @@
         <v>2026</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="13.8">
-      <c r="A6" s="42"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="41.4">
+      <c r="A6" s="42" t="s">
+        <v>433</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>436</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="26.4">
+      <c r="A7" t="s">
+        <v>434</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>435</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="27" type="noConversion"/>
@@ -62484,7 +62554,7 @@
         <v>13</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>17</v>
@@ -62509,25 +62579,25 @@
     </row>
     <row r="2" spans="1:21" ht="13.2">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C2" s="2">
         <v>2023</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E2" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="E2" s="22" t="s">
-        <v>160</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -62546,25 +62616,25 @@
     </row>
     <row r="3" spans="1:21" ht="13.2">
       <c r="A3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="C3" s="11">
         <v>2022</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -62583,25 +62653,25 @@
     </row>
     <row r="4" spans="1:21" ht="13.2">
       <c r="A4" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C4" s="11">
         <v>2021</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="H4" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="1"/>
@@ -62619,25 +62689,25 @@
     </row>
     <row r="5" spans="1:21" ht="13.2">
       <c r="A5" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="11">
         <v>2022</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -62656,25 +62726,25 @@
     </row>
     <row r="6" spans="1:21" ht="13.8">
       <c r="A6" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C6" s="11">
         <v>2022</v>
       </c>
       <c r="D6" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -62693,25 +62763,25 @@
     </row>
     <row r="7" spans="1:21" ht="13.8" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C7" s="11">
         <v>2022</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -62730,25 +62800,25 @@
     </row>
     <row r="8" spans="1:21" ht="13.8" thickBot="1">
       <c r="A8" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" s="11">
         <v>2023</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>

--- a/data/CV_infolist.xlsx
+++ b/data/CV_infolist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sooyo\Documents\github\sylcv\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lee\Documents\GitHub\sylcv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857C42C7-AAEA-49FA-910F-D6F0B17D47F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FC78B7-25BB-4745-9C59-DCABFD46A573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="-120" windowWidth="37710" windowHeight="16440" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="441">
   <si>
     <t>Degree</t>
   </si>
@@ -1381,6 +1381,15 @@
   <si>
     <t>Sooyong Lee &amp; Cory L. Cobb</t>
   </si>
+  <si>
+    <t>https://doi.org/10.1080/00273171.2026.2699709</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/00273171.2025.2699709</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/00273171..2699709</t>
+  </si>
 </sst>
 </file>
 
@@ -1981,15 +1990,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="29.44140625" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="136.6640625" customWidth="1"/>
+    <col min="1" max="1" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="136.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.2">
+    <row r="1" spans="1:5" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2006,7 +2015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="39.6">
+    <row r="2" spans="1:5" ht="38.25">
       <c r="A2" s="26" t="s">
         <v>162</v>
       </c>
@@ -2023,7 +2032,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="13.8" thickBot="1">
+    <row r="3" spans="1:5" ht="13.5" thickBot="1">
       <c r="A3" s="24" t="s">
         <v>131</v>
       </c>
@@ -2068,9 +2077,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:P18"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="39.109375" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1">
@@ -2529,19 +2538,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1001"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.88671875" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" style="16" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="13.2">
+    <row r="1" spans="1:27" ht="12.75">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -2588,7 +2597,7 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:27" ht="13.2">
+    <row r="2" spans="1:27" ht="12.75">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -2633,7 +2642,7 @@
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
     </row>
-    <row r="3" spans="1:27" ht="13.2">
+    <row r="3" spans="1:27" ht="12.75">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -2678,7 +2687,7 @@
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
     </row>
-    <row r="4" spans="1:27" ht="13.2">
+    <row r="4" spans="1:27" ht="12.75">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -2766,7 +2775,7 @@
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
     </row>
-    <row r="6" spans="1:27" ht="13.2">
+    <row r="6" spans="1:27" ht="12.75">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -2809,7 +2818,7 @@
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
     </row>
-    <row r="7" spans="1:27" ht="16.8">
+    <row r="7" spans="1:27" ht="18">
       <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
@@ -2856,7 +2865,7 @@
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
     </row>
-    <row r="8" spans="1:27" ht="16.8">
+    <row r="8" spans="1:27" ht="18">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -2901,7 +2910,7 @@
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:27" ht="16.8">
+    <row r="9" spans="1:27" ht="18">
       <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
@@ -2946,7 +2955,7 @@
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
     </row>
-    <row r="10" spans="1:27" ht="13.2">
+    <row r="10" spans="1:27" ht="12.75">
       <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
@@ -2989,7 +2998,7 @@
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="1:27" ht="13.2">
+    <row r="11" spans="1:27" ht="12.75">
       <c r="A11" s="21" t="s">
         <v>40</v>
       </c>
@@ -3030,7 +3039,7 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="1:27" ht="15.6">
+    <row r="12" spans="1:27">
       <c r="A12" s="21" t="s">
         <v>19</v>
       </c>
@@ -3071,7 +3080,7 @@
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
     </row>
-    <row r="13" spans="1:27" ht="15.6">
+    <row r="13" spans="1:27">
       <c r="A13" s="21" t="s">
         <v>40</v>
       </c>
@@ -3112,7 +3121,7 @@
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
     </row>
-    <row r="14" spans="1:27" ht="13.2">
+    <row r="14" spans="1:27" ht="12.75">
       <c r="A14" s="21" t="s">
         <v>40</v>
       </c>
@@ -3155,7 +3164,7 @@
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
     </row>
-    <row r="15" spans="1:27" ht="13.2">
+    <row r="15" spans="1:27" ht="12.75">
       <c r="A15" s="21" t="s">
         <v>40</v>
       </c>
@@ -3198,7 +3207,7 @@
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
     </row>
-    <row r="16" spans="1:27" ht="13.2">
+    <row r="16" spans="1:27" ht="12.75">
       <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
@@ -3241,7 +3250,7 @@
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="1:27" ht="13.2">
+    <row r="17" spans="1:27" ht="12.75">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -3284,7 +3293,7 @@
       <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
     </row>
-    <row r="18" spans="1:27" ht="13.2">
+    <row r="18" spans="1:27" ht="12.75">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -3327,7 +3336,7 @@
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
     </row>
-    <row r="19" spans="1:27" ht="13.2">
+    <row r="19" spans="1:27" ht="12.75">
       <c r="A19" s="2" t="s">
         <v>40</v>
       </c>
@@ -3370,7 +3379,7 @@
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" spans="1:27" ht="13.2">
+    <row r="20" spans="1:27" ht="12.75">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -3413,7 +3422,7 @@
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" spans="1:27" ht="13.2">
+    <row r="21" spans="1:27" ht="12.75">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="14"/>
@@ -3442,7 +3451,7 @@
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
     </row>
-    <row r="22" spans="1:27" ht="13.2">
+    <row r="22" spans="1:27" ht="12.75">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="14"/>
@@ -3471,7 +3480,7 @@
       <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="1:27" ht="13.2">
+    <row r="23" spans="1:27" ht="12.75">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="14"/>
@@ -3500,7 +3509,7 @@
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
     </row>
-    <row r="24" spans="1:27" ht="13.2">
+    <row r="24" spans="1:27" ht="12.75">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="14"/>
@@ -3529,7 +3538,7 @@
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" spans="1:27" ht="13.2">
+    <row r="25" spans="1:27" ht="12.75">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="14"/>
@@ -3558,7 +3567,7 @@
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
     </row>
-    <row r="26" spans="1:27" ht="13.2">
+    <row r="26" spans="1:27" ht="12.75">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="14"/>
@@ -3587,7 +3596,7 @@
       <c r="Z26" s="2"/>
       <c r="AA26" s="2"/>
     </row>
-    <row r="27" spans="1:27" ht="13.2">
+    <row r="27" spans="1:27" ht="12.75">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="14"/>
@@ -3616,7 +3625,7 @@
       <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
     </row>
-    <row r="28" spans="1:27" ht="13.2">
+    <row r="28" spans="1:27" ht="12.75">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="14"/>
@@ -3645,7 +3654,7 @@
       <c r="Z28" s="2"/>
       <c r="AA28" s="2"/>
     </row>
-    <row r="29" spans="1:27" ht="13.2">
+    <row r="29" spans="1:27" ht="12.75">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="14"/>
@@ -3674,7 +3683,7 @@
       <c r="Z29" s="2"/>
       <c r="AA29" s="2"/>
     </row>
-    <row r="30" spans="1:27" ht="13.2">
+    <row r="30" spans="1:27" ht="12.75">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="14"/>
@@ -3703,7 +3712,7 @@
       <c r="Z30" s="2"/>
       <c r="AA30" s="2"/>
     </row>
-    <row r="31" spans="1:27" ht="13.2">
+    <row r="31" spans="1:27" ht="12.75">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="14"/>
@@ -3732,7 +3741,7 @@
       <c r="Z31" s="2"/>
       <c r="AA31" s="2"/>
     </row>
-    <row r="32" spans="1:27" ht="13.2">
+    <row r="32" spans="1:27" ht="12.75">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="14"/>
@@ -3761,7 +3770,7 @@
       <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
     </row>
-    <row r="33" spans="1:27" ht="13.2">
+    <row r="33" spans="1:27" ht="12.75">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="14"/>
@@ -3790,7 +3799,7 @@
       <c r="Z33" s="2"/>
       <c r="AA33" s="2"/>
     </row>
-    <row r="34" spans="1:27" ht="13.2">
+    <row r="34" spans="1:27" ht="12.75">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="14"/>
@@ -3819,7 +3828,7 @@
       <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
     </row>
-    <row r="35" spans="1:27" ht="13.2">
+    <row r="35" spans="1:27" ht="12.75">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="14"/>
@@ -3848,7 +3857,7 @@
       <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
     </row>
-    <row r="36" spans="1:27" ht="13.2">
+    <row r="36" spans="1:27" ht="12.75">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="14"/>
@@ -3877,7 +3886,7 @@
       <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
     </row>
-    <row r="37" spans="1:27" ht="13.2">
+    <row r="37" spans="1:27" ht="12.75">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="14"/>
@@ -3906,7 +3915,7 @@
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
     </row>
-    <row r="38" spans="1:27" ht="13.2">
+    <row r="38" spans="1:27" ht="12.75">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="14"/>
@@ -3935,7 +3944,7 @@
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
     </row>
-    <row r="39" spans="1:27" ht="13.2">
+    <row r="39" spans="1:27" ht="12.75">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="14"/>
@@ -3964,7 +3973,7 @@
       <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
     </row>
-    <row r="40" spans="1:27" ht="13.2">
+    <row r="40" spans="1:27" ht="12.75">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="14"/>
@@ -3993,7 +4002,7 @@
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
     </row>
-    <row r="41" spans="1:27" ht="13.2">
+    <row r="41" spans="1:27" ht="12.75">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="14"/>
@@ -4022,7 +4031,7 @@
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="1:27" ht="13.2">
+    <row r="42" spans="1:27" ht="12.75">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="14"/>
@@ -4051,7 +4060,7 @@
       <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
     </row>
-    <row r="43" spans="1:27" ht="13.2">
+    <row r="43" spans="1:27" ht="12.75">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="14"/>
@@ -4080,7 +4089,7 @@
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
     </row>
-    <row r="44" spans="1:27" ht="13.2">
+    <row r="44" spans="1:27" ht="12.75">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="14"/>
@@ -4109,7 +4118,7 @@
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
     </row>
-    <row r="45" spans="1:27" ht="13.2">
+    <row r="45" spans="1:27" ht="12.75">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="14"/>
@@ -4138,7 +4147,7 @@
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="1:27" ht="13.2">
+    <row r="46" spans="1:27" ht="12.75">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="14"/>
@@ -4167,7 +4176,7 @@
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
     </row>
-    <row r="47" spans="1:27" ht="13.2">
+    <row r="47" spans="1:27" ht="12.75">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="14"/>
@@ -4196,7 +4205,7 @@
       <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
     </row>
-    <row r="48" spans="1:27" ht="13.2">
+    <row r="48" spans="1:27" ht="12.75">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="14"/>
@@ -4225,7 +4234,7 @@
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
     </row>
-    <row r="49" spans="1:27" ht="13.2">
+    <row r="49" spans="1:27" ht="12.75">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="14"/>
@@ -4254,7 +4263,7 @@
       <c r="Z49" s="2"/>
       <c r="AA49" s="2"/>
     </row>
-    <row r="50" spans="1:27" ht="13.2">
+    <row r="50" spans="1:27" ht="12.75">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="14"/>
@@ -4283,7 +4292,7 @@
       <c r="Z50" s="2"/>
       <c r="AA50" s="2"/>
     </row>
-    <row r="51" spans="1:27" ht="13.2">
+    <row r="51" spans="1:27" ht="12.75">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="14"/>
@@ -4312,7 +4321,7 @@
       <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
     </row>
-    <row r="52" spans="1:27" ht="13.2">
+    <row r="52" spans="1:27" ht="12.75">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="14"/>
@@ -4341,7 +4350,7 @@
       <c r="Z52" s="2"/>
       <c r="AA52" s="2"/>
     </row>
-    <row r="53" spans="1:27" ht="13.2">
+    <row r="53" spans="1:27" ht="12.75">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="14"/>
@@ -4370,7 +4379,7 @@
       <c r="Z53" s="2"/>
       <c r="AA53" s="2"/>
     </row>
-    <row r="54" spans="1:27" ht="13.2">
+    <row r="54" spans="1:27" ht="12.75">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="14"/>
@@ -4399,7 +4408,7 @@
       <c r="Z54" s="2"/>
       <c r="AA54" s="2"/>
     </row>
-    <row r="55" spans="1:27" ht="13.2">
+    <row r="55" spans="1:27" ht="12.75">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="14"/>
@@ -4428,7 +4437,7 @@
       <c r="Z55" s="2"/>
       <c r="AA55" s="2"/>
     </row>
-    <row r="56" spans="1:27" ht="13.2">
+    <row r="56" spans="1:27" ht="12.75">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="14"/>
@@ -4457,7 +4466,7 @@
       <c r="Z56" s="2"/>
       <c r="AA56" s="2"/>
     </row>
-    <row r="57" spans="1:27" ht="13.2">
+    <row r="57" spans="1:27" ht="12.75">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="14"/>
@@ -4486,7 +4495,7 @@
       <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
     </row>
-    <row r="58" spans="1:27" ht="13.2">
+    <row r="58" spans="1:27" ht="12.75">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="14"/>
@@ -4515,7 +4524,7 @@
       <c r="Z58" s="2"/>
       <c r="AA58" s="2"/>
     </row>
-    <row r="59" spans="1:27" ht="13.2">
+    <row r="59" spans="1:27" ht="12.75">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="14"/>
@@ -4544,7 +4553,7 @@
       <c r="Z59" s="2"/>
       <c r="AA59" s="2"/>
     </row>
-    <row r="60" spans="1:27" ht="13.2">
+    <row r="60" spans="1:27" ht="12.75">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="14"/>
@@ -4573,7 +4582,7 @@
       <c r="Z60" s="2"/>
       <c r="AA60" s="2"/>
     </row>
-    <row r="61" spans="1:27" ht="13.2">
+    <row r="61" spans="1:27" ht="12.75">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="14"/>
@@ -4602,7 +4611,7 @@
       <c r="Z61" s="2"/>
       <c r="AA61" s="2"/>
     </row>
-    <row r="62" spans="1:27" ht="13.2">
+    <row r="62" spans="1:27" ht="12.75">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="14"/>
@@ -4631,7 +4640,7 @@
       <c r="Z62" s="2"/>
       <c r="AA62" s="2"/>
     </row>
-    <row r="63" spans="1:27" ht="13.2">
+    <row r="63" spans="1:27" ht="12.75">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="14"/>
@@ -4660,7 +4669,7 @@
       <c r="Z63" s="2"/>
       <c r="AA63" s="2"/>
     </row>
-    <row r="64" spans="1:27" ht="13.2">
+    <row r="64" spans="1:27" ht="12.75">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="14"/>
@@ -4689,7 +4698,7 @@
       <c r="Z64" s="2"/>
       <c r="AA64" s="2"/>
     </row>
-    <row r="65" spans="1:27" ht="13.2">
+    <row r="65" spans="1:27" ht="12.75">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="14"/>
@@ -4718,7 +4727,7 @@
       <c r="Z65" s="2"/>
       <c r="AA65" s="2"/>
     </row>
-    <row r="66" spans="1:27" ht="13.2">
+    <row r="66" spans="1:27" ht="12.75">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="14"/>
@@ -4747,7 +4756,7 @@
       <c r="Z66" s="2"/>
       <c r="AA66" s="2"/>
     </row>
-    <row r="67" spans="1:27" ht="13.2">
+    <row r="67" spans="1:27" ht="12.75">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="14"/>
@@ -4776,7 +4785,7 @@
       <c r="Z67" s="2"/>
       <c r="AA67" s="2"/>
     </row>
-    <row r="68" spans="1:27" ht="13.2">
+    <row r="68" spans="1:27" ht="12.75">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="14"/>
@@ -4805,7 +4814,7 @@
       <c r="Z68" s="2"/>
       <c r="AA68" s="2"/>
     </row>
-    <row r="69" spans="1:27" ht="13.2">
+    <row r="69" spans="1:27" ht="12.75">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="14"/>
@@ -4834,7 +4843,7 @@
       <c r="Z69" s="2"/>
       <c r="AA69" s="2"/>
     </row>
-    <row r="70" spans="1:27" ht="13.2">
+    <row r="70" spans="1:27" ht="12.75">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="14"/>
@@ -4863,7 +4872,7 @@
       <c r="Z70" s="2"/>
       <c r="AA70" s="2"/>
     </row>
-    <row r="71" spans="1:27" ht="13.2">
+    <row r="71" spans="1:27" ht="12.75">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="14"/>
@@ -4892,7 +4901,7 @@
       <c r="Z71" s="2"/>
       <c r="AA71" s="2"/>
     </row>
-    <row r="72" spans="1:27" ht="13.2">
+    <row r="72" spans="1:27" ht="12.75">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="14"/>
@@ -4921,7 +4930,7 @@
       <c r="Z72" s="2"/>
       <c r="AA72" s="2"/>
     </row>
-    <row r="73" spans="1:27" ht="13.2">
+    <row r="73" spans="1:27" ht="12.75">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="14"/>
@@ -4950,7 +4959,7 @@
       <c r="Z73" s="2"/>
       <c r="AA73" s="2"/>
     </row>
-    <row r="74" spans="1:27" ht="13.2">
+    <row r="74" spans="1:27" ht="12.75">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="14"/>
@@ -4979,7 +4988,7 @@
       <c r="Z74" s="2"/>
       <c r="AA74" s="2"/>
     </row>
-    <row r="75" spans="1:27" ht="13.2">
+    <row r="75" spans="1:27" ht="12.75">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="14"/>
@@ -5008,7 +5017,7 @@
       <c r="Z75" s="2"/>
       <c r="AA75" s="2"/>
     </row>
-    <row r="76" spans="1:27" ht="13.2">
+    <row r="76" spans="1:27" ht="12.75">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="14"/>
@@ -5037,7 +5046,7 @@
       <c r="Z76" s="2"/>
       <c r="AA76" s="2"/>
     </row>
-    <row r="77" spans="1:27" ht="13.2">
+    <row r="77" spans="1:27" ht="12.75">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="14"/>
@@ -5066,7 +5075,7 @@
       <c r="Z77" s="2"/>
       <c r="AA77" s="2"/>
     </row>
-    <row r="78" spans="1:27" ht="13.2">
+    <row r="78" spans="1:27" ht="12.75">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="14"/>
@@ -5095,7 +5104,7 @@
       <c r="Z78" s="2"/>
       <c r="AA78" s="2"/>
     </row>
-    <row r="79" spans="1:27" ht="13.2">
+    <row r="79" spans="1:27" ht="12.75">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="14"/>
@@ -5124,7 +5133,7 @@
       <c r="Z79" s="2"/>
       <c r="AA79" s="2"/>
     </row>
-    <row r="80" spans="1:27" ht="13.2">
+    <row r="80" spans="1:27" ht="12.75">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="14"/>
@@ -5153,7 +5162,7 @@
       <c r="Z80" s="2"/>
       <c r="AA80" s="2"/>
     </row>
-    <row r="81" spans="1:27" ht="13.2">
+    <row r="81" spans="1:27" ht="12.75">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="14"/>
@@ -5182,7 +5191,7 @@
       <c r="Z81" s="2"/>
       <c r="AA81" s="2"/>
     </row>
-    <row r="82" spans="1:27" ht="13.2">
+    <row r="82" spans="1:27" ht="12.75">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="14"/>
@@ -5211,7 +5220,7 @@
       <c r="Z82" s="2"/>
       <c r="AA82" s="2"/>
     </row>
-    <row r="83" spans="1:27" ht="13.2">
+    <row r="83" spans="1:27" ht="12.75">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="14"/>
@@ -5240,7 +5249,7 @@
       <c r="Z83" s="2"/>
       <c r="AA83" s="2"/>
     </row>
-    <row r="84" spans="1:27" ht="13.2">
+    <row r="84" spans="1:27" ht="12.75">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="14"/>
@@ -5269,7 +5278,7 @@
       <c r="Z84" s="2"/>
       <c r="AA84" s="2"/>
     </row>
-    <row r="85" spans="1:27" ht="13.2">
+    <row r="85" spans="1:27" ht="12.75">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="14"/>
@@ -5298,7 +5307,7 @@
       <c r="Z85" s="2"/>
       <c r="AA85" s="2"/>
     </row>
-    <row r="86" spans="1:27" ht="13.2">
+    <row r="86" spans="1:27" ht="12.75">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="14"/>
@@ -5327,7 +5336,7 @@
       <c r="Z86" s="2"/>
       <c r="AA86" s="2"/>
     </row>
-    <row r="87" spans="1:27" ht="13.2">
+    <row r="87" spans="1:27" ht="12.75">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="14"/>
@@ -5356,7 +5365,7 @@
       <c r="Z87" s="2"/>
       <c r="AA87" s="2"/>
     </row>
-    <row r="88" spans="1:27" ht="13.2">
+    <row r="88" spans="1:27" ht="12.75">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="14"/>
@@ -5385,7 +5394,7 @@
       <c r="Z88" s="2"/>
       <c r="AA88" s="2"/>
     </row>
-    <row r="89" spans="1:27" ht="13.2">
+    <row r="89" spans="1:27" ht="12.75">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="14"/>
@@ -5414,7 +5423,7 @@
       <c r="Z89" s="2"/>
       <c r="AA89" s="2"/>
     </row>
-    <row r="90" spans="1:27" ht="13.2">
+    <row r="90" spans="1:27" ht="12.75">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="14"/>
@@ -5443,7 +5452,7 @@
       <c r="Z90" s="2"/>
       <c r="AA90" s="2"/>
     </row>
-    <row r="91" spans="1:27" ht="13.2">
+    <row r="91" spans="1:27" ht="12.75">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="14"/>
@@ -5472,7 +5481,7 @@
       <c r="Z91" s="2"/>
       <c r="AA91" s="2"/>
     </row>
-    <row r="92" spans="1:27" ht="13.2">
+    <row r="92" spans="1:27" ht="12.75">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="14"/>
@@ -5501,7 +5510,7 @@
       <c r="Z92" s="2"/>
       <c r="AA92" s="2"/>
     </row>
-    <row r="93" spans="1:27" ht="13.2">
+    <row r="93" spans="1:27" ht="12.75">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="14"/>
@@ -5530,7 +5539,7 @@
       <c r="Z93" s="2"/>
       <c r="AA93" s="2"/>
     </row>
-    <row r="94" spans="1:27" ht="13.2">
+    <row r="94" spans="1:27" ht="12.75">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="14"/>
@@ -5559,7 +5568,7 @@
       <c r="Z94" s="2"/>
       <c r="AA94" s="2"/>
     </row>
-    <row r="95" spans="1:27" ht="13.2">
+    <row r="95" spans="1:27" ht="12.75">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="14"/>
@@ -5588,7 +5597,7 @@
       <c r="Z95" s="2"/>
       <c r="AA95" s="2"/>
     </row>
-    <row r="96" spans="1:27" ht="13.2">
+    <row r="96" spans="1:27" ht="12.75">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="14"/>
@@ -5617,7 +5626,7 @@
       <c r="Z96" s="2"/>
       <c r="AA96" s="2"/>
     </row>
-    <row r="97" spans="1:27" ht="13.2">
+    <row r="97" spans="1:27" ht="12.75">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="14"/>
@@ -5646,7 +5655,7 @@
       <c r="Z97" s="2"/>
       <c r="AA97" s="2"/>
     </row>
-    <row r="98" spans="1:27" ht="13.2">
+    <row r="98" spans="1:27" ht="12.75">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="14"/>
@@ -5675,7 +5684,7 @@
       <c r="Z98" s="2"/>
       <c r="AA98" s="2"/>
     </row>
-    <row r="99" spans="1:27" ht="13.2">
+    <row r="99" spans="1:27" ht="12.75">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="14"/>
@@ -5704,7 +5713,7 @@
       <c r="Z99" s="2"/>
       <c r="AA99" s="2"/>
     </row>
-    <row r="100" spans="1:27" ht="13.2">
+    <row r="100" spans="1:27" ht="12.75">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="14"/>
@@ -5733,7 +5742,7 @@
       <c r="Z100" s="2"/>
       <c r="AA100" s="2"/>
     </row>
-    <row r="101" spans="1:27" ht="13.2">
+    <row r="101" spans="1:27" ht="12.75">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="14"/>
@@ -5762,7 +5771,7 @@
       <c r="Z101" s="2"/>
       <c r="AA101" s="2"/>
     </row>
-    <row r="102" spans="1:27" ht="13.2">
+    <row r="102" spans="1:27" ht="12.75">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="14"/>
@@ -5791,7 +5800,7 @@
       <c r="Z102" s="2"/>
       <c r="AA102" s="2"/>
     </row>
-    <row r="103" spans="1:27" ht="13.2">
+    <row r="103" spans="1:27" ht="12.75">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="14"/>
@@ -5820,7 +5829,7 @@
       <c r="Z103" s="2"/>
       <c r="AA103" s="2"/>
     </row>
-    <row r="104" spans="1:27" ht="13.2">
+    <row r="104" spans="1:27" ht="12.75">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="14"/>
@@ -5849,7 +5858,7 @@
       <c r="Z104" s="2"/>
       <c r="AA104" s="2"/>
     </row>
-    <row r="105" spans="1:27" ht="13.2">
+    <row r="105" spans="1:27" ht="12.75">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="14"/>
@@ -5878,7 +5887,7 @@
       <c r="Z105" s="2"/>
       <c r="AA105" s="2"/>
     </row>
-    <row r="106" spans="1:27" ht="13.2">
+    <row r="106" spans="1:27" ht="12.75">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="14"/>
@@ -5907,7 +5916,7 @@
       <c r="Z106" s="2"/>
       <c r="AA106" s="2"/>
     </row>
-    <row r="107" spans="1:27" ht="13.2">
+    <row r="107" spans="1:27" ht="12.75">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="14"/>
@@ -5936,7 +5945,7 @@
       <c r="Z107" s="2"/>
       <c r="AA107" s="2"/>
     </row>
-    <row r="108" spans="1:27" ht="13.2">
+    <row r="108" spans="1:27" ht="12.75">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="14"/>
@@ -5965,7 +5974,7 @@
       <c r="Z108" s="2"/>
       <c r="AA108" s="2"/>
     </row>
-    <row r="109" spans="1:27" ht="13.2">
+    <row r="109" spans="1:27" ht="12.75">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="14"/>
@@ -5994,7 +6003,7 @@
       <c r="Z109" s="2"/>
       <c r="AA109" s="2"/>
     </row>
-    <row r="110" spans="1:27" ht="13.2">
+    <row r="110" spans="1:27" ht="12.75">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="14"/>
@@ -6023,7 +6032,7 @@
       <c r="Z110" s="2"/>
       <c r="AA110" s="2"/>
     </row>
-    <row r="111" spans="1:27" ht="13.2">
+    <row r="111" spans="1:27" ht="12.75">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="14"/>
@@ -6052,7 +6061,7 @@
       <c r="Z111" s="2"/>
       <c r="AA111" s="2"/>
     </row>
-    <row r="112" spans="1:27" ht="13.2">
+    <row r="112" spans="1:27" ht="12.75">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="14"/>
@@ -6081,7 +6090,7 @@
       <c r="Z112" s="2"/>
       <c r="AA112" s="2"/>
     </row>
-    <row r="113" spans="1:27" ht="13.2">
+    <row r="113" spans="1:27" ht="12.75">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="14"/>
@@ -6110,7 +6119,7 @@
       <c r="Z113" s="2"/>
       <c r="AA113" s="2"/>
     </row>
-    <row r="114" spans="1:27" ht="13.2">
+    <row r="114" spans="1:27" ht="12.75">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="14"/>
@@ -6139,7 +6148,7 @@
       <c r="Z114" s="2"/>
       <c r="AA114" s="2"/>
     </row>
-    <row r="115" spans="1:27" ht="13.2">
+    <row r="115" spans="1:27" ht="12.75">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="14"/>
@@ -6168,7 +6177,7 @@
       <c r="Z115" s="2"/>
       <c r="AA115" s="2"/>
     </row>
-    <row r="116" spans="1:27" ht="13.2">
+    <row r="116" spans="1:27" ht="12.75">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="14"/>
@@ -6197,7 +6206,7 @@
       <c r="Z116" s="2"/>
       <c r="AA116" s="2"/>
     </row>
-    <row r="117" spans="1:27" ht="13.2">
+    <row r="117" spans="1:27" ht="12.75">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="14"/>
@@ -6226,7 +6235,7 @@
       <c r="Z117" s="2"/>
       <c r="AA117" s="2"/>
     </row>
-    <row r="118" spans="1:27" ht="13.2">
+    <row r="118" spans="1:27" ht="12.75">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="14"/>
@@ -6255,7 +6264,7 @@
       <c r="Z118" s="2"/>
       <c r="AA118" s="2"/>
     </row>
-    <row r="119" spans="1:27" ht="13.2">
+    <row r="119" spans="1:27" ht="12.75">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="14"/>
@@ -6284,7 +6293,7 @@
       <c r="Z119" s="2"/>
       <c r="AA119" s="2"/>
     </row>
-    <row r="120" spans="1:27" ht="13.2">
+    <row r="120" spans="1:27" ht="12.75">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="14"/>
@@ -6313,7 +6322,7 @@
       <c r="Z120" s="2"/>
       <c r="AA120" s="2"/>
     </row>
-    <row r="121" spans="1:27" ht="13.2">
+    <row r="121" spans="1:27" ht="12.75">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="14"/>
@@ -6342,7 +6351,7 @@
       <c r="Z121" s="2"/>
       <c r="AA121" s="2"/>
     </row>
-    <row r="122" spans="1:27" ht="13.2">
+    <row r="122" spans="1:27" ht="12.75">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="14"/>
@@ -6371,7 +6380,7 @@
       <c r="Z122" s="2"/>
       <c r="AA122" s="2"/>
     </row>
-    <row r="123" spans="1:27" ht="13.2">
+    <row r="123" spans="1:27" ht="12.75">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="14"/>
@@ -6400,7 +6409,7 @@
       <c r="Z123" s="2"/>
       <c r="AA123" s="2"/>
     </row>
-    <row r="124" spans="1:27" ht="13.2">
+    <row r="124" spans="1:27" ht="12.75">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="14"/>
@@ -6429,7 +6438,7 @@
       <c r="Z124" s="2"/>
       <c r="AA124" s="2"/>
     </row>
-    <row r="125" spans="1:27" ht="13.2">
+    <row r="125" spans="1:27" ht="12.75">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="14"/>
@@ -6458,7 +6467,7 @@
       <c r="Z125" s="2"/>
       <c r="AA125" s="2"/>
     </row>
-    <row r="126" spans="1:27" ht="13.2">
+    <row r="126" spans="1:27" ht="12.75">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="14"/>
@@ -6487,7 +6496,7 @@
       <c r="Z126" s="2"/>
       <c r="AA126" s="2"/>
     </row>
-    <row r="127" spans="1:27" ht="13.2">
+    <row r="127" spans="1:27" ht="12.75">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="14"/>
@@ -6516,7 +6525,7 @@
       <c r="Z127" s="2"/>
       <c r="AA127" s="2"/>
     </row>
-    <row r="128" spans="1:27" ht="13.2">
+    <row r="128" spans="1:27" ht="12.75">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="14"/>
@@ -6545,7 +6554,7 @@
       <c r="Z128" s="2"/>
       <c r="AA128" s="2"/>
     </row>
-    <row r="129" spans="1:27" ht="13.2">
+    <row r="129" spans="1:27" ht="12.75">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="14"/>
@@ -6574,7 +6583,7 @@
       <c r="Z129" s="2"/>
       <c r="AA129" s="2"/>
     </row>
-    <row r="130" spans="1:27" ht="13.2">
+    <row r="130" spans="1:27" ht="12.75">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="14"/>
@@ -6603,7 +6612,7 @@
       <c r="Z130" s="2"/>
       <c r="AA130" s="2"/>
     </row>
-    <row r="131" spans="1:27" ht="13.2">
+    <row r="131" spans="1:27" ht="12.75">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="14"/>
@@ -6632,7 +6641,7 @@
       <c r="Z131" s="2"/>
       <c r="AA131" s="2"/>
     </row>
-    <row r="132" spans="1:27" ht="13.2">
+    <row r="132" spans="1:27" ht="12.75">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="14"/>
@@ -6661,7 +6670,7 @@
       <c r="Z132" s="2"/>
       <c r="AA132" s="2"/>
     </row>
-    <row r="133" spans="1:27" ht="13.2">
+    <row r="133" spans="1:27" ht="12.75">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="14"/>
@@ -6690,7 +6699,7 @@
       <c r="Z133" s="2"/>
       <c r="AA133" s="2"/>
     </row>
-    <row r="134" spans="1:27" ht="13.2">
+    <row r="134" spans="1:27" ht="12.75">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="14"/>
@@ -6719,7 +6728,7 @@
       <c r="Z134" s="2"/>
       <c r="AA134" s="2"/>
     </row>
-    <row r="135" spans="1:27" ht="13.2">
+    <row r="135" spans="1:27" ht="12.75">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="14"/>
@@ -6748,7 +6757,7 @@
       <c r="Z135" s="2"/>
       <c r="AA135" s="2"/>
     </row>
-    <row r="136" spans="1:27" ht="13.2">
+    <row r="136" spans="1:27" ht="12.75">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="14"/>
@@ -6777,7 +6786,7 @@
       <c r="Z136" s="2"/>
       <c r="AA136" s="2"/>
     </row>
-    <row r="137" spans="1:27" ht="13.2">
+    <row r="137" spans="1:27" ht="12.75">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="14"/>
@@ -6806,7 +6815,7 @@
       <c r="Z137" s="2"/>
       <c r="AA137" s="2"/>
     </row>
-    <row r="138" spans="1:27" ht="13.2">
+    <row r="138" spans="1:27" ht="12.75">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="14"/>
@@ -6835,7 +6844,7 @@
       <c r="Z138" s="2"/>
       <c r="AA138" s="2"/>
     </row>
-    <row r="139" spans="1:27" ht="13.2">
+    <row r="139" spans="1:27" ht="12.75">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="14"/>
@@ -6864,7 +6873,7 @@
       <c r="Z139" s="2"/>
       <c r="AA139" s="2"/>
     </row>
-    <row r="140" spans="1:27" ht="13.2">
+    <row r="140" spans="1:27" ht="12.75">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="14"/>
@@ -6893,7 +6902,7 @@
       <c r="Z140" s="2"/>
       <c r="AA140" s="2"/>
     </row>
-    <row r="141" spans="1:27" ht="13.2">
+    <row r="141" spans="1:27" ht="12.75">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="14"/>
@@ -6922,7 +6931,7 @@
       <c r="Z141" s="2"/>
       <c r="AA141" s="2"/>
     </row>
-    <row r="142" spans="1:27" ht="13.2">
+    <row r="142" spans="1:27" ht="12.75">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="14"/>
@@ -6951,7 +6960,7 @@
       <c r="Z142" s="2"/>
       <c r="AA142" s="2"/>
     </row>
-    <row r="143" spans="1:27" ht="13.2">
+    <row r="143" spans="1:27" ht="12.75">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="14"/>
@@ -6980,7 +6989,7 @@
       <c r="Z143" s="2"/>
       <c r="AA143" s="2"/>
     </row>
-    <row r="144" spans="1:27" ht="13.2">
+    <row r="144" spans="1:27" ht="12.75">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="14"/>
@@ -7009,7 +7018,7 @@
       <c r="Z144" s="2"/>
       <c r="AA144" s="2"/>
     </row>
-    <row r="145" spans="1:27" ht="13.2">
+    <row r="145" spans="1:27" ht="12.75">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="14"/>
@@ -7038,7 +7047,7 @@
       <c r="Z145" s="2"/>
       <c r="AA145" s="2"/>
     </row>
-    <row r="146" spans="1:27" ht="13.2">
+    <row r="146" spans="1:27" ht="12.75">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="14"/>
@@ -7067,7 +7076,7 @@
       <c r="Z146" s="2"/>
       <c r="AA146" s="2"/>
     </row>
-    <row r="147" spans="1:27" ht="13.2">
+    <row r="147" spans="1:27" ht="12.75">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="14"/>
@@ -7096,7 +7105,7 @@
       <c r="Z147" s="2"/>
       <c r="AA147" s="2"/>
     </row>
-    <row r="148" spans="1:27" ht="13.2">
+    <row r="148" spans="1:27" ht="12.75">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="14"/>
@@ -7125,7 +7134,7 @@
       <c r="Z148" s="2"/>
       <c r="AA148" s="2"/>
     </row>
-    <row r="149" spans="1:27" ht="13.2">
+    <row r="149" spans="1:27" ht="12.75">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="14"/>
@@ -7154,7 +7163,7 @@
       <c r="Z149" s="2"/>
       <c r="AA149" s="2"/>
     </row>
-    <row r="150" spans="1:27" ht="13.2">
+    <row r="150" spans="1:27" ht="12.75">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="14"/>
@@ -7183,7 +7192,7 @@
       <c r="Z150" s="2"/>
       <c r="AA150" s="2"/>
     </row>
-    <row r="151" spans="1:27" ht="13.2">
+    <row r="151" spans="1:27" ht="12.75">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="14"/>
@@ -7212,7 +7221,7 @@
       <c r="Z151" s="2"/>
       <c r="AA151" s="2"/>
     </row>
-    <row r="152" spans="1:27" ht="13.2">
+    <row r="152" spans="1:27" ht="12.75">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="14"/>
@@ -7241,7 +7250,7 @@
       <c r="Z152" s="2"/>
       <c r="AA152" s="2"/>
     </row>
-    <row r="153" spans="1:27" ht="13.2">
+    <row r="153" spans="1:27" ht="12.75">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="14"/>
@@ -7270,7 +7279,7 @@
       <c r="Z153" s="2"/>
       <c r="AA153" s="2"/>
     </row>
-    <row r="154" spans="1:27" ht="13.2">
+    <row r="154" spans="1:27" ht="12.75">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="14"/>
@@ -7299,7 +7308,7 @@
       <c r="Z154" s="2"/>
       <c r="AA154" s="2"/>
     </row>
-    <row r="155" spans="1:27" ht="13.2">
+    <row r="155" spans="1:27" ht="12.75">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="14"/>
@@ -7328,7 +7337,7 @@
       <c r="Z155" s="2"/>
       <c r="AA155" s="2"/>
     </row>
-    <row r="156" spans="1:27" ht="13.2">
+    <row r="156" spans="1:27" ht="12.75">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="14"/>
@@ -7357,7 +7366,7 @@
       <c r="Z156" s="2"/>
       <c r="AA156" s="2"/>
     </row>
-    <row r="157" spans="1:27" ht="13.2">
+    <row r="157" spans="1:27" ht="12.75">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="14"/>
@@ -7386,7 +7395,7 @@
       <c r="Z157" s="2"/>
       <c r="AA157" s="2"/>
     </row>
-    <row r="158" spans="1:27" ht="13.2">
+    <row r="158" spans="1:27" ht="12.75">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="14"/>
@@ -7415,7 +7424,7 @@
       <c r="Z158" s="2"/>
       <c r="AA158" s="2"/>
     </row>
-    <row r="159" spans="1:27" ht="13.2">
+    <row r="159" spans="1:27" ht="12.75">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="14"/>
@@ -7444,7 +7453,7 @@
       <c r="Z159" s="2"/>
       <c r="AA159" s="2"/>
     </row>
-    <row r="160" spans="1:27" ht="13.2">
+    <row r="160" spans="1:27" ht="12.75">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="14"/>
@@ -7473,7 +7482,7 @@
       <c r="Z160" s="2"/>
       <c r="AA160" s="2"/>
     </row>
-    <row r="161" spans="1:27" ht="13.2">
+    <row r="161" spans="1:27" ht="12.75">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="14"/>
@@ -7502,7 +7511,7 @@
       <c r="Z161" s="2"/>
       <c r="AA161" s="2"/>
     </row>
-    <row r="162" spans="1:27" ht="13.2">
+    <row r="162" spans="1:27" ht="12.75">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="14"/>
@@ -7531,7 +7540,7 @@
       <c r="Z162" s="2"/>
       <c r="AA162" s="2"/>
     </row>
-    <row r="163" spans="1:27" ht="13.2">
+    <row r="163" spans="1:27" ht="12.75">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="14"/>
@@ -7560,7 +7569,7 @@
       <c r="Z163" s="2"/>
       <c r="AA163" s="2"/>
     </row>
-    <row r="164" spans="1:27" ht="13.2">
+    <row r="164" spans="1:27" ht="12.75">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="14"/>
@@ -7589,7 +7598,7 @@
       <c r="Z164" s="2"/>
       <c r="AA164" s="2"/>
     </row>
-    <row r="165" spans="1:27" ht="13.2">
+    <row r="165" spans="1:27" ht="12.75">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="14"/>
@@ -7618,7 +7627,7 @@
       <c r="Z165" s="2"/>
       <c r="AA165" s="2"/>
     </row>
-    <row r="166" spans="1:27" ht="13.2">
+    <row r="166" spans="1:27" ht="12.75">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="14"/>
@@ -7647,7 +7656,7 @@
       <c r="Z166" s="2"/>
       <c r="AA166" s="2"/>
     </row>
-    <row r="167" spans="1:27" ht="13.2">
+    <row r="167" spans="1:27" ht="12.75">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="14"/>
@@ -7676,7 +7685,7 @@
       <c r="Z167" s="2"/>
       <c r="AA167" s="2"/>
     </row>
-    <row r="168" spans="1:27" ht="13.2">
+    <row r="168" spans="1:27" ht="12.75">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="14"/>
@@ -7705,7 +7714,7 @@
       <c r="Z168" s="2"/>
       <c r="AA168" s="2"/>
     </row>
-    <row r="169" spans="1:27" ht="13.2">
+    <row r="169" spans="1:27" ht="12.75">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="14"/>
@@ -7734,7 +7743,7 @@
       <c r="Z169" s="2"/>
       <c r="AA169" s="2"/>
     </row>
-    <row r="170" spans="1:27" ht="13.2">
+    <row r="170" spans="1:27" ht="12.75">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="14"/>
@@ -7763,7 +7772,7 @@
       <c r="Z170" s="2"/>
       <c r="AA170" s="2"/>
     </row>
-    <row r="171" spans="1:27" ht="13.2">
+    <row r="171" spans="1:27" ht="12.75">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="14"/>
@@ -7792,7 +7801,7 @@
       <c r="Z171" s="2"/>
       <c r="AA171" s="2"/>
     </row>
-    <row r="172" spans="1:27" ht="13.2">
+    <row r="172" spans="1:27" ht="12.75">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="14"/>
@@ -7821,7 +7830,7 @@
       <c r="Z172" s="2"/>
       <c r="AA172" s="2"/>
     </row>
-    <row r="173" spans="1:27" ht="13.2">
+    <row r="173" spans="1:27" ht="12.75">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="14"/>
@@ -7850,7 +7859,7 @@
       <c r="Z173" s="2"/>
       <c r="AA173" s="2"/>
     </row>
-    <row r="174" spans="1:27" ht="13.2">
+    <row r="174" spans="1:27" ht="12.75">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="14"/>
@@ -7879,7 +7888,7 @@
       <c r="Z174" s="2"/>
       <c r="AA174" s="2"/>
     </row>
-    <row r="175" spans="1:27" ht="13.2">
+    <row r="175" spans="1:27" ht="12.75">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="14"/>
@@ -7908,7 +7917,7 @@
       <c r="Z175" s="2"/>
       <c r="AA175" s="2"/>
     </row>
-    <row r="176" spans="1:27" ht="13.2">
+    <row r="176" spans="1:27" ht="12.75">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="14"/>
@@ -7937,7 +7946,7 @@
       <c r="Z176" s="2"/>
       <c r="AA176" s="2"/>
     </row>
-    <row r="177" spans="1:27" ht="13.2">
+    <row r="177" spans="1:27" ht="12.75">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="14"/>
@@ -7966,7 +7975,7 @@
       <c r="Z177" s="2"/>
       <c r="AA177" s="2"/>
     </row>
-    <row r="178" spans="1:27" ht="13.2">
+    <row r="178" spans="1:27" ht="12.75">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="14"/>
@@ -7995,7 +8004,7 @@
       <c r="Z178" s="2"/>
       <c r="AA178" s="2"/>
     </row>
-    <row r="179" spans="1:27" ht="13.2">
+    <row r="179" spans="1:27" ht="12.75">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="14"/>
@@ -8024,7 +8033,7 @@
       <c r="Z179" s="2"/>
       <c r="AA179" s="2"/>
     </row>
-    <row r="180" spans="1:27" ht="13.2">
+    <row r="180" spans="1:27" ht="12.75">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="14"/>
@@ -8053,7 +8062,7 @@
       <c r="Z180" s="2"/>
       <c r="AA180" s="2"/>
     </row>
-    <row r="181" spans="1:27" ht="13.2">
+    <row r="181" spans="1:27" ht="12.75">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="14"/>
@@ -8082,7 +8091,7 @@
       <c r="Z181" s="2"/>
       <c r="AA181" s="2"/>
     </row>
-    <row r="182" spans="1:27" ht="13.2">
+    <row r="182" spans="1:27" ht="12.75">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="14"/>
@@ -8111,7 +8120,7 @@
       <c r="Z182" s="2"/>
       <c r="AA182" s="2"/>
     </row>
-    <row r="183" spans="1:27" ht="13.2">
+    <row r="183" spans="1:27" ht="12.75">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="14"/>
@@ -8140,7 +8149,7 @@
       <c r="Z183" s="2"/>
       <c r="AA183" s="2"/>
     </row>
-    <row r="184" spans="1:27" ht="13.2">
+    <row r="184" spans="1:27" ht="12.75">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="14"/>
@@ -8169,7 +8178,7 @@
       <c r="Z184" s="2"/>
       <c r="AA184" s="2"/>
     </row>
-    <row r="185" spans="1:27" ht="13.2">
+    <row r="185" spans="1:27" ht="12.75">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="14"/>
@@ -8198,7 +8207,7 @@
       <c r="Z185" s="2"/>
       <c r="AA185" s="2"/>
     </row>
-    <row r="186" spans="1:27" ht="13.2">
+    <row r="186" spans="1:27" ht="12.75">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="14"/>
@@ -8227,7 +8236,7 @@
       <c r="Z186" s="2"/>
       <c r="AA186" s="2"/>
     </row>
-    <row r="187" spans="1:27" ht="13.2">
+    <row r="187" spans="1:27" ht="12.75">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="14"/>
@@ -8256,7 +8265,7 @@
       <c r="Z187" s="2"/>
       <c r="AA187" s="2"/>
     </row>
-    <row r="188" spans="1:27" ht="13.2">
+    <row r="188" spans="1:27" ht="12.75">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="14"/>
@@ -8285,7 +8294,7 @@
       <c r="Z188" s="2"/>
       <c r="AA188" s="2"/>
     </row>
-    <row r="189" spans="1:27" ht="13.2">
+    <row r="189" spans="1:27" ht="12.75">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="14"/>
@@ -8314,7 +8323,7 @@
       <c r="Z189" s="2"/>
       <c r="AA189" s="2"/>
     </row>
-    <row r="190" spans="1:27" ht="13.2">
+    <row r="190" spans="1:27" ht="12.75">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="14"/>
@@ -8343,7 +8352,7 @@
       <c r="Z190" s="2"/>
       <c r="AA190" s="2"/>
     </row>
-    <row r="191" spans="1:27" ht="13.2">
+    <row r="191" spans="1:27" ht="12.75">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="14"/>
@@ -8372,7 +8381,7 @@
       <c r="Z191" s="2"/>
       <c r="AA191" s="2"/>
     </row>
-    <row r="192" spans="1:27" ht="13.2">
+    <row r="192" spans="1:27" ht="12.75">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="14"/>
@@ -8401,7 +8410,7 @@
       <c r="Z192" s="2"/>
       <c r="AA192" s="2"/>
     </row>
-    <row r="193" spans="1:27" ht="13.2">
+    <row r="193" spans="1:27" ht="12.75">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="14"/>
@@ -8430,7 +8439,7 @@
       <c r="Z193" s="2"/>
       <c r="AA193" s="2"/>
     </row>
-    <row r="194" spans="1:27" ht="13.2">
+    <row r="194" spans="1:27" ht="12.75">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="14"/>
@@ -8459,7 +8468,7 @@
       <c r="Z194" s="2"/>
       <c r="AA194" s="2"/>
     </row>
-    <row r="195" spans="1:27" ht="13.2">
+    <row r="195" spans="1:27" ht="12.75">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="14"/>
@@ -8488,7 +8497,7 @@
       <c r="Z195" s="2"/>
       <c r="AA195" s="2"/>
     </row>
-    <row r="196" spans="1:27" ht="13.2">
+    <row r="196" spans="1:27" ht="12.75">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="14"/>
@@ -8517,7 +8526,7 @@
       <c r="Z196" s="2"/>
       <c r="AA196" s="2"/>
     </row>
-    <row r="197" spans="1:27" ht="13.2">
+    <row r="197" spans="1:27" ht="12.75">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="14"/>
@@ -8546,7 +8555,7 @@
       <c r="Z197" s="2"/>
       <c r="AA197" s="2"/>
     </row>
-    <row r="198" spans="1:27" ht="13.2">
+    <row r="198" spans="1:27" ht="12.75">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="14"/>
@@ -8575,7 +8584,7 @@
       <c r="Z198" s="2"/>
       <c r="AA198" s="2"/>
     </row>
-    <row r="199" spans="1:27" ht="13.2">
+    <row r="199" spans="1:27" ht="12.75">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="14"/>
@@ -8604,7 +8613,7 @@
       <c r="Z199" s="2"/>
       <c r="AA199" s="2"/>
     </row>
-    <row r="200" spans="1:27" ht="13.2">
+    <row r="200" spans="1:27" ht="12.75">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="14"/>
@@ -8633,7 +8642,7 @@
       <c r="Z200" s="2"/>
       <c r="AA200" s="2"/>
     </row>
-    <row r="201" spans="1:27" ht="13.2">
+    <row r="201" spans="1:27" ht="12.75">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="14"/>
@@ -8662,7 +8671,7 @@
       <c r="Z201" s="2"/>
       <c r="AA201" s="2"/>
     </row>
-    <row r="202" spans="1:27" ht="13.2">
+    <row r="202" spans="1:27" ht="12.75">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="14"/>
@@ -8691,7 +8700,7 @@
       <c r="Z202" s="2"/>
       <c r="AA202" s="2"/>
     </row>
-    <row r="203" spans="1:27" ht="13.2">
+    <row r="203" spans="1:27" ht="12.75">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="14"/>
@@ -8720,7 +8729,7 @@
       <c r="Z203" s="2"/>
       <c r="AA203" s="2"/>
     </row>
-    <row r="204" spans="1:27" ht="13.2">
+    <row r="204" spans="1:27" ht="12.75">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="14"/>
@@ -8749,7 +8758,7 @@
       <c r="Z204" s="2"/>
       <c r="AA204" s="2"/>
     </row>
-    <row r="205" spans="1:27" ht="13.2">
+    <row r="205" spans="1:27" ht="12.75">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="14"/>
@@ -8778,7 +8787,7 @@
       <c r="Z205" s="2"/>
       <c r="AA205" s="2"/>
     </row>
-    <row r="206" spans="1:27" ht="13.2">
+    <row r="206" spans="1:27" ht="12.75">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="14"/>
@@ -8807,7 +8816,7 @@
       <c r="Z206" s="2"/>
       <c r="AA206" s="2"/>
     </row>
-    <row r="207" spans="1:27" ht="13.2">
+    <row r="207" spans="1:27" ht="12.75">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="14"/>
@@ -8836,7 +8845,7 @@
       <c r="Z207" s="2"/>
       <c r="AA207" s="2"/>
     </row>
-    <row r="208" spans="1:27" ht="13.2">
+    <row r="208" spans="1:27" ht="12.75">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="14"/>
@@ -8865,7 +8874,7 @@
       <c r="Z208" s="2"/>
       <c r="AA208" s="2"/>
     </row>
-    <row r="209" spans="1:27" ht="13.2">
+    <row r="209" spans="1:27" ht="12.75">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="14"/>
@@ -8894,7 +8903,7 @@
       <c r="Z209" s="2"/>
       <c r="AA209" s="2"/>
     </row>
-    <row r="210" spans="1:27" ht="13.2">
+    <row r="210" spans="1:27" ht="12.75">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="14"/>
@@ -8923,7 +8932,7 @@
       <c r="Z210" s="2"/>
       <c r="AA210" s="2"/>
     </row>
-    <row r="211" spans="1:27" ht="13.2">
+    <row r="211" spans="1:27" ht="12.75">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="14"/>
@@ -8952,7 +8961,7 @@
       <c r="Z211" s="2"/>
       <c r="AA211" s="2"/>
     </row>
-    <row r="212" spans="1:27" ht="13.2">
+    <row r="212" spans="1:27" ht="12.75">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="14"/>
@@ -8981,7 +8990,7 @@
       <c r="Z212" s="2"/>
       <c r="AA212" s="2"/>
     </row>
-    <row r="213" spans="1:27" ht="13.2">
+    <row r="213" spans="1:27" ht="12.75">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="14"/>
@@ -9010,7 +9019,7 @@
       <c r="Z213" s="2"/>
       <c r="AA213" s="2"/>
     </row>
-    <row r="214" spans="1:27" ht="13.2">
+    <row r="214" spans="1:27" ht="12.75">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="14"/>
@@ -9039,7 +9048,7 @@
       <c r="Z214" s="2"/>
       <c r="AA214" s="2"/>
     </row>
-    <row r="215" spans="1:27" ht="13.2">
+    <row r="215" spans="1:27" ht="12.75">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="14"/>
@@ -9068,7 +9077,7 @@
       <c r="Z215" s="2"/>
       <c r="AA215" s="2"/>
     </row>
-    <row r="216" spans="1:27" ht="13.2">
+    <row r="216" spans="1:27" ht="12.75">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="14"/>
@@ -9097,7 +9106,7 @@
       <c r="Z216" s="2"/>
       <c r="AA216" s="2"/>
     </row>
-    <row r="217" spans="1:27" ht="13.2">
+    <row r="217" spans="1:27" ht="12.75">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="14"/>
@@ -9126,7 +9135,7 @@
       <c r="Z217" s="2"/>
       <c r="AA217" s="2"/>
     </row>
-    <row r="218" spans="1:27" ht="13.2">
+    <row r="218" spans="1:27" ht="12.75">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="14"/>
@@ -9155,7 +9164,7 @@
       <c r="Z218" s="2"/>
       <c r="AA218" s="2"/>
     </row>
-    <row r="219" spans="1:27" ht="13.2">
+    <row r="219" spans="1:27" ht="12.75">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="14"/>
@@ -9184,7 +9193,7 @@
       <c r="Z219" s="2"/>
       <c r="AA219" s="2"/>
     </row>
-    <row r="220" spans="1:27" ht="13.2">
+    <row r="220" spans="1:27" ht="12.75">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="14"/>
@@ -9213,7 +9222,7 @@
       <c r="Z220" s="2"/>
       <c r="AA220" s="2"/>
     </row>
-    <row r="221" spans="1:27" ht="13.2">
+    <row r="221" spans="1:27" ht="12.75">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="14"/>
@@ -9242,7 +9251,7 @@
       <c r="Z221" s="2"/>
       <c r="AA221" s="2"/>
     </row>
-    <row r="222" spans="1:27" ht="13.2">
+    <row r="222" spans="1:27" ht="12.75">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="14"/>
@@ -9271,7 +9280,7 @@
       <c r="Z222" s="2"/>
       <c r="AA222" s="2"/>
     </row>
-    <row r="223" spans="1:27" ht="13.2">
+    <row r="223" spans="1:27" ht="12.75">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="14"/>
@@ -9300,7 +9309,7 @@
       <c r="Z223" s="2"/>
       <c r="AA223" s="2"/>
     </row>
-    <row r="224" spans="1:27" ht="13.2">
+    <row r="224" spans="1:27" ht="12.75">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="14"/>
@@ -9329,7 +9338,7 @@
       <c r="Z224" s="2"/>
       <c r="AA224" s="2"/>
     </row>
-    <row r="225" spans="1:27" ht="13.2">
+    <row r="225" spans="1:27" ht="12.75">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="14"/>
@@ -9358,7 +9367,7 @@
       <c r="Z225" s="2"/>
       <c r="AA225" s="2"/>
     </row>
-    <row r="226" spans="1:27" ht="13.2">
+    <row r="226" spans="1:27" ht="12.75">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="14"/>
@@ -9387,7 +9396,7 @@
       <c r="Z226" s="2"/>
       <c r="AA226" s="2"/>
     </row>
-    <row r="227" spans="1:27" ht="13.2">
+    <row r="227" spans="1:27" ht="12.75">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="14"/>
@@ -9416,7 +9425,7 @@
       <c r="Z227" s="2"/>
       <c r="AA227" s="2"/>
     </row>
-    <row r="228" spans="1:27" ht="13.2">
+    <row r="228" spans="1:27" ht="12.75">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="14"/>
@@ -9445,7 +9454,7 @@
       <c r="Z228" s="2"/>
       <c r="AA228" s="2"/>
     </row>
-    <row r="229" spans="1:27" ht="13.2">
+    <row r="229" spans="1:27" ht="12.75">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="14"/>
@@ -9474,7 +9483,7 @@
       <c r="Z229" s="2"/>
       <c r="AA229" s="2"/>
     </row>
-    <row r="230" spans="1:27" ht="13.2">
+    <row r="230" spans="1:27" ht="12.75">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="14"/>
@@ -9503,7 +9512,7 @@
       <c r="Z230" s="2"/>
       <c r="AA230" s="2"/>
     </row>
-    <row r="231" spans="1:27" ht="13.2">
+    <row r="231" spans="1:27" ht="12.75">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="14"/>
@@ -9532,7 +9541,7 @@
       <c r="Z231" s="2"/>
       <c r="AA231" s="2"/>
     </row>
-    <row r="232" spans="1:27" ht="13.2">
+    <row r="232" spans="1:27" ht="12.75">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="14"/>
@@ -9561,7 +9570,7 @@
       <c r="Z232" s="2"/>
       <c r="AA232" s="2"/>
     </row>
-    <row r="233" spans="1:27" ht="13.2">
+    <row r="233" spans="1:27" ht="12.75">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="14"/>
@@ -9590,7 +9599,7 @@
       <c r="Z233" s="2"/>
       <c r="AA233" s="2"/>
     </row>
-    <row r="234" spans="1:27" ht="13.2">
+    <row r="234" spans="1:27" ht="12.75">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="14"/>
@@ -9619,7 +9628,7 @@
       <c r="Z234" s="2"/>
       <c r="AA234" s="2"/>
     </row>
-    <row r="235" spans="1:27" ht="13.2">
+    <row r="235" spans="1:27" ht="12.75">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="14"/>
@@ -9648,7 +9657,7 @@
       <c r="Z235" s="2"/>
       <c r="AA235" s="2"/>
     </row>
-    <row r="236" spans="1:27" ht="13.2">
+    <row r="236" spans="1:27" ht="12.75">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="14"/>
@@ -9677,7 +9686,7 @@
       <c r="Z236" s="2"/>
       <c r="AA236" s="2"/>
     </row>
-    <row r="237" spans="1:27" ht="13.2">
+    <row r="237" spans="1:27" ht="12.75">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="14"/>
@@ -9706,7 +9715,7 @@
       <c r="Z237" s="2"/>
       <c r="AA237" s="2"/>
     </row>
-    <row r="238" spans="1:27" ht="13.2">
+    <row r="238" spans="1:27" ht="12.75">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="14"/>
@@ -9735,7 +9744,7 @@
       <c r="Z238" s="2"/>
       <c r="AA238" s="2"/>
     </row>
-    <row r="239" spans="1:27" ht="13.2">
+    <row r="239" spans="1:27" ht="12.75">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="14"/>
@@ -9764,7 +9773,7 @@
       <c r="Z239" s="2"/>
       <c r="AA239" s="2"/>
     </row>
-    <row r="240" spans="1:27" ht="13.2">
+    <row r="240" spans="1:27" ht="12.75">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="14"/>
@@ -9793,7 +9802,7 @@
       <c r="Z240" s="2"/>
       <c r="AA240" s="2"/>
     </row>
-    <row r="241" spans="1:27" ht="13.2">
+    <row r="241" spans="1:27" ht="12.75">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="14"/>
@@ -9822,7 +9831,7 @@
       <c r="Z241" s="2"/>
       <c r="AA241" s="2"/>
     </row>
-    <row r="242" spans="1:27" ht="13.2">
+    <row r="242" spans="1:27" ht="12.75">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="14"/>
@@ -9851,7 +9860,7 @@
       <c r="Z242" s="2"/>
       <c r="AA242" s="2"/>
     </row>
-    <row r="243" spans="1:27" ht="13.2">
+    <row r="243" spans="1:27" ht="12.75">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="14"/>
@@ -9880,7 +9889,7 @@
       <c r="Z243" s="2"/>
       <c r="AA243" s="2"/>
     </row>
-    <row r="244" spans="1:27" ht="13.2">
+    <row r="244" spans="1:27" ht="12.75">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="14"/>
@@ -9909,7 +9918,7 @@
       <c r="Z244" s="2"/>
       <c r="AA244" s="2"/>
     </row>
-    <row r="245" spans="1:27" ht="13.2">
+    <row r="245" spans="1:27" ht="12.75">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="14"/>
@@ -9938,7 +9947,7 @@
       <c r="Z245" s="2"/>
       <c r="AA245" s="2"/>
     </row>
-    <row r="246" spans="1:27" ht="13.2">
+    <row r="246" spans="1:27" ht="12.75">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="14"/>
@@ -9967,7 +9976,7 @@
       <c r="Z246" s="2"/>
       <c r="AA246" s="2"/>
     </row>
-    <row r="247" spans="1:27" ht="13.2">
+    <row r="247" spans="1:27" ht="12.75">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="14"/>
@@ -9996,7 +10005,7 @@
       <c r="Z247" s="2"/>
       <c r="AA247" s="2"/>
     </row>
-    <row r="248" spans="1:27" ht="13.2">
+    <row r="248" spans="1:27" ht="12.75">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="14"/>
@@ -10025,7 +10034,7 @@
       <c r="Z248" s="2"/>
       <c r="AA248" s="2"/>
     </row>
-    <row r="249" spans="1:27" ht="13.2">
+    <row r="249" spans="1:27" ht="12.75">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="14"/>
@@ -10054,7 +10063,7 @@
       <c r="Z249" s="2"/>
       <c r="AA249" s="2"/>
     </row>
-    <row r="250" spans="1:27" ht="13.2">
+    <row r="250" spans="1:27" ht="12.75">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="14"/>
@@ -10083,7 +10092,7 @@
       <c r="Z250" s="2"/>
       <c r="AA250" s="2"/>
     </row>
-    <row r="251" spans="1:27" ht="13.2">
+    <row r="251" spans="1:27" ht="12.75">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="14"/>
@@ -10112,7 +10121,7 @@
       <c r="Z251" s="2"/>
       <c r="AA251" s="2"/>
     </row>
-    <row r="252" spans="1:27" ht="13.2">
+    <row r="252" spans="1:27" ht="12.75">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="14"/>
@@ -10141,7 +10150,7 @@
       <c r="Z252" s="2"/>
       <c r="AA252" s="2"/>
     </row>
-    <row r="253" spans="1:27" ht="13.2">
+    <row r="253" spans="1:27" ht="12.75">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="14"/>
@@ -10170,7 +10179,7 @@
       <c r="Z253" s="2"/>
       <c r="AA253" s="2"/>
     </row>
-    <row r="254" spans="1:27" ht="13.2">
+    <row r="254" spans="1:27" ht="12.75">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="14"/>
@@ -10199,7 +10208,7 @@
       <c r="Z254" s="2"/>
       <c r="AA254" s="2"/>
     </row>
-    <row r="255" spans="1:27" ht="13.2">
+    <row r="255" spans="1:27" ht="12.75">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="14"/>
@@ -10228,7 +10237,7 @@
       <c r="Z255" s="2"/>
       <c r="AA255" s="2"/>
     </row>
-    <row r="256" spans="1:27" ht="13.2">
+    <row r="256" spans="1:27" ht="12.75">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="14"/>
@@ -10257,7 +10266,7 @@
       <c r="Z256" s="2"/>
       <c r="AA256" s="2"/>
     </row>
-    <row r="257" spans="1:27" ht="13.2">
+    <row r="257" spans="1:27" ht="12.75">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="14"/>
@@ -10286,7 +10295,7 @@
       <c r="Z257" s="2"/>
       <c r="AA257" s="2"/>
     </row>
-    <row r="258" spans="1:27" ht="13.2">
+    <row r="258" spans="1:27" ht="12.75">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="14"/>
@@ -10315,7 +10324,7 @@
       <c r="Z258" s="2"/>
       <c r="AA258" s="2"/>
     </row>
-    <row r="259" spans="1:27" ht="13.2">
+    <row r="259" spans="1:27" ht="12.75">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="14"/>
@@ -10344,7 +10353,7 @@
       <c r="Z259" s="2"/>
       <c r="AA259" s="2"/>
     </row>
-    <row r="260" spans="1:27" ht="13.2">
+    <row r="260" spans="1:27" ht="12.75">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="14"/>
@@ -10373,7 +10382,7 @@
       <c r="Z260" s="2"/>
       <c r="AA260" s="2"/>
     </row>
-    <row r="261" spans="1:27" ht="13.2">
+    <row r="261" spans="1:27" ht="12.75">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="14"/>
@@ -10402,7 +10411,7 @@
       <c r="Z261" s="2"/>
       <c r="AA261" s="2"/>
     </row>
-    <row r="262" spans="1:27" ht="13.2">
+    <row r="262" spans="1:27" ht="12.75">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="14"/>
@@ -10431,7 +10440,7 @@
       <c r="Z262" s="2"/>
       <c r="AA262" s="2"/>
     </row>
-    <row r="263" spans="1:27" ht="13.2">
+    <row r="263" spans="1:27" ht="12.75">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="14"/>
@@ -10460,7 +10469,7 @@
       <c r="Z263" s="2"/>
       <c r="AA263" s="2"/>
     </row>
-    <row r="264" spans="1:27" ht="13.2">
+    <row r="264" spans="1:27" ht="12.75">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="14"/>
@@ -10489,7 +10498,7 @@
       <c r="Z264" s="2"/>
       <c r="AA264" s="2"/>
     </row>
-    <row r="265" spans="1:27" ht="13.2">
+    <row r="265" spans="1:27" ht="12.75">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="14"/>
@@ -10518,7 +10527,7 @@
       <c r="Z265" s="2"/>
       <c r="AA265" s="2"/>
     </row>
-    <row r="266" spans="1:27" ht="13.2">
+    <row r="266" spans="1:27" ht="12.75">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="14"/>
@@ -10547,7 +10556,7 @@
       <c r="Z266" s="2"/>
       <c r="AA266" s="2"/>
     </row>
-    <row r="267" spans="1:27" ht="13.2">
+    <row r="267" spans="1:27" ht="12.75">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="14"/>
@@ -10576,7 +10585,7 @@
       <c r="Z267" s="2"/>
       <c r="AA267" s="2"/>
     </row>
-    <row r="268" spans="1:27" ht="13.2">
+    <row r="268" spans="1:27" ht="12.75">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="14"/>
@@ -10605,7 +10614,7 @@
       <c r="Z268" s="2"/>
       <c r="AA268" s="2"/>
     </row>
-    <row r="269" spans="1:27" ht="13.2">
+    <row r="269" spans="1:27" ht="12.75">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="14"/>
@@ -10634,7 +10643,7 @@
       <c r="Z269" s="2"/>
       <c r="AA269" s="2"/>
     </row>
-    <row r="270" spans="1:27" ht="13.2">
+    <row r="270" spans="1:27" ht="12.75">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="14"/>
@@ -10663,7 +10672,7 @@
       <c r="Z270" s="2"/>
       <c r="AA270" s="2"/>
     </row>
-    <row r="271" spans="1:27" ht="13.2">
+    <row r="271" spans="1:27" ht="12.75">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="14"/>
@@ -10692,7 +10701,7 @@
       <c r="Z271" s="2"/>
       <c r="AA271" s="2"/>
     </row>
-    <row r="272" spans="1:27" ht="13.2">
+    <row r="272" spans="1:27" ht="12.75">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="14"/>
@@ -10721,7 +10730,7 @@
       <c r="Z272" s="2"/>
       <c r="AA272" s="2"/>
     </row>
-    <row r="273" spans="1:27" ht="13.2">
+    <row r="273" spans="1:27" ht="12.75">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="14"/>
@@ -10750,7 +10759,7 @@
       <c r="Z273" s="2"/>
       <c r="AA273" s="2"/>
     </row>
-    <row r="274" spans="1:27" ht="13.2">
+    <row r="274" spans="1:27" ht="12.75">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="14"/>
@@ -10779,7 +10788,7 @@
       <c r="Z274" s="2"/>
       <c r="AA274" s="2"/>
     </row>
-    <row r="275" spans="1:27" ht="13.2">
+    <row r="275" spans="1:27" ht="12.75">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="14"/>
@@ -10808,7 +10817,7 @@
       <c r="Z275" s="2"/>
       <c r="AA275" s="2"/>
     </row>
-    <row r="276" spans="1:27" ht="13.2">
+    <row r="276" spans="1:27" ht="12.75">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="14"/>
@@ -10837,7 +10846,7 @@
       <c r="Z276" s="2"/>
       <c r="AA276" s="2"/>
     </row>
-    <row r="277" spans="1:27" ht="13.2">
+    <row r="277" spans="1:27" ht="12.75">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="14"/>
@@ -10866,7 +10875,7 @@
       <c r="Z277" s="2"/>
       <c r="AA277" s="2"/>
     </row>
-    <row r="278" spans="1:27" ht="13.2">
+    <row r="278" spans="1:27" ht="12.75">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="14"/>
@@ -10895,7 +10904,7 @@
       <c r="Z278" s="2"/>
       <c r="AA278" s="2"/>
     </row>
-    <row r="279" spans="1:27" ht="13.2">
+    <row r="279" spans="1:27" ht="12.75">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="14"/>
@@ -10924,7 +10933,7 @@
       <c r="Z279" s="2"/>
       <c r="AA279" s="2"/>
     </row>
-    <row r="280" spans="1:27" ht="13.2">
+    <row r="280" spans="1:27" ht="12.75">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="14"/>
@@ -10953,7 +10962,7 @@
       <c r="Z280" s="2"/>
       <c r="AA280" s="2"/>
     </row>
-    <row r="281" spans="1:27" ht="13.2">
+    <row r="281" spans="1:27" ht="12.75">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="14"/>
@@ -10982,7 +10991,7 @@
       <c r="Z281" s="2"/>
       <c r="AA281" s="2"/>
     </row>
-    <row r="282" spans="1:27" ht="13.2">
+    <row r="282" spans="1:27" ht="12.75">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="14"/>
@@ -11011,7 +11020,7 @@
       <c r="Z282" s="2"/>
       <c r="AA282" s="2"/>
     </row>
-    <row r="283" spans="1:27" ht="13.2">
+    <row r="283" spans="1:27" ht="12.75">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="14"/>
@@ -11040,7 +11049,7 @@
       <c r="Z283" s="2"/>
       <c r="AA283" s="2"/>
     </row>
-    <row r="284" spans="1:27" ht="13.2">
+    <row r="284" spans="1:27" ht="12.75">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="14"/>
@@ -11069,7 +11078,7 @@
       <c r="Z284" s="2"/>
       <c r="AA284" s="2"/>
     </row>
-    <row r="285" spans="1:27" ht="13.2">
+    <row r="285" spans="1:27" ht="12.75">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="14"/>
@@ -11098,7 +11107,7 @@
       <c r="Z285" s="2"/>
       <c r="AA285" s="2"/>
     </row>
-    <row r="286" spans="1:27" ht="13.2">
+    <row r="286" spans="1:27" ht="12.75">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="14"/>
@@ -11127,7 +11136,7 @@
       <c r="Z286" s="2"/>
       <c r="AA286" s="2"/>
     </row>
-    <row r="287" spans="1:27" ht="13.2">
+    <row r="287" spans="1:27" ht="12.75">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="14"/>
@@ -11156,7 +11165,7 @@
       <c r="Z287" s="2"/>
       <c r="AA287" s="2"/>
     </row>
-    <row r="288" spans="1:27" ht="13.2">
+    <row r="288" spans="1:27" ht="12.75">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="14"/>
@@ -11185,7 +11194,7 @@
       <c r="Z288" s="2"/>
       <c r="AA288" s="2"/>
     </row>
-    <row r="289" spans="1:27" ht="13.2">
+    <row r="289" spans="1:27" ht="12.75">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="14"/>
@@ -11214,7 +11223,7 @@
       <c r="Z289" s="2"/>
       <c r="AA289" s="2"/>
     </row>
-    <row r="290" spans="1:27" ht="13.2">
+    <row r="290" spans="1:27" ht="12.75">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="14"/>
@@ -11243,7 +11252,7 @@
       <c r="Z290" s="2"/>
       <c r="AA290" s="2"/>
     </row>
-    <row r="291" spans="1:27" ht="13.2">
+    <row r="291" spans="1:27" ht="12.75">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="14"/>
@@ -11272,7 +11281,7 @@
       <c r="Z291" s="2"/>
       <c r="AA291" s="2"/>
     </row>
-    <row r="292" spans="1:27" ht="13.2">
+    <row r="292" spans="1:27" ht="12.75">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="14"/>
@@ -11301,7 +11310,7 @@
       <c r="Z292" s="2"/>
       <c r="AA292" s="2"/>
     </row>
-    <row r="293" spans="1:27" ht="13.2">
+    <row r="293" spans="1:27" ht="12.75">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="14"/>
@@ -11330,7 +11339,7 @@
       <c r="Z293" s="2"/>
       <c r="AA293" s="2"/>
     </row>
-    <row r="294" spans="1:27" ht="13.2">
+    <row r="294" spans="1:27" ht="12.75">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="14"/>
@@ -11359,7 +11368,7 @@
       <c r="Z294" s="2"/>
       <c r="AA294" s="2"/>
     </row>
-    <row r="295" spans="1:27" ht="13.2">
+    <row r="295" spans="1:27" ht="12.75">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="14"/>
@@ -11388,7 +11397,7 @@
       <c r="Z295" s="2"/>
       <c r="AA295" s="2"/>
     </row>
-    <row r="296" spans="1:27" ht="13.2">
+    <row r="296" spans="1:27" ht="12.75">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="14"/>
@@ -11417,7 +11426,7 @@
       <c r="Z296" s="2"/>
       <c r="AA296" s="2"/>
     </row>
-    <row r="297" spans="1:27" ht="13.2">
+    <row r="297" spans="1:27" ht="12.75">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="14"/>
@@ -11446,7 +11455,7 @@
       <c r="Z297" s="2"/>
       <c r="AA297" s="2"/>
     </row>
-    <row r="298" spans="1:27" ht="13.2">
+    <row r="298" spans="1:27" ht="12.75">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="14"/>
@@ -11475,7 +11484,7 @@
       <c r="Z298" s="2"/>
       <c r="AA298" s="2"/>
     </row>
-    <row r="299" spans="1:27" ht="13.2">
+    <row r="299" spans="1:27" ht="12.75">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="14"/>
@@ -11504,7 +11513,7 @@
       <c r="Z299" s="2"/>
       <c r="AA299" s="2"/>
     </row>
-    <row r="300" spans="1:27" ht="13.2">
+    <row r="300" spans="1:27" ht="12.75">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="14"/>
@@ -11533,7 +11542,7 @@
       <c r="Z300" s="2"/>
       <c r="AA300" s="2"/>
     </row>
-    <row r="301" spans="1:27" ht="13.2">
+    <row r="301" spans="1:27" ht="12.75">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="14"/>
@@ -11562,7 +11571,7 @@
       <c r="Z301" s="2"/>
       <c r="AA301" s="2"/>
     </row>
-    <row r="302" spans="1:27" ht="13.2">
+    <row r="302" spans="1:27" ht="12.75">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="14"/>
@@ -11591,7 +11600,7 @@
       <c r="Z302" s="2"/>
       <c r="AA302" s="2"/>
     </row>
-    <row r="303" spans="1:27" ht="13.2">
+    <row r="303" spans="1:27" ht="12.75">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="14"/>
@@ -11620,7 +11629,7 @@
       <c r="Z303" s="2"/>
       <c r="AA303" s="2"/>
     </row>
-    <row r="304" spans="1:27" ht="13.2">
+    <row r="304" spans="1:27" ht="12.75">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="14"/>
@@ -11649,7 +11658,7 @@
       <c r="Z304" s="2"/>
       <c r="AA304" s="2"/>
     </row>
-    <row r="305" spans="1:27" ht="13.2">
+    <row r="305" spans="1:27" ht="12.75">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="14"/>
@@ -11678,7 +11687,7 @@
       <c r="Z305" s="2"/>
       <c r="AA305" s="2"/>
     </row>
-    <row r="306" spans="1:27" ht="13.2">
+    <row r="306" spans="1:27" ht="12.75">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="14"/>
@@ -11707,7 +11716,7 @@
       <c r="Z306" s="2"/>
       <c r="AA306" s="2"/>
     </row>
-    <row r="307" spans="1:27" ht="13.2">
+    <row r="307" spans="1:27" ht="12.75">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="14"/>
@@ -11736,7 +11745,7 @@
       <c r="Z307" s="2"/>
       <c r="AA307" s="2"/>
     </row>
-    <row r="308" spans="1:27" ht="13.2">
+    <row r="308" spans="1:27" ht="12.75">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="14"/>
@@ -11765,7 +11774,7 @@
       <c r="Z308" s="2"/>
       <c r="AA308" s="2"/>
     </row>
-    <row r="309" spans="1:27" ht="13.2">
+    <row r="309" spans="1:27" ht="12.75">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="14"/>
@@ -11794,7 +11803,7 @@
       <c r="Z309" s="2"/>
       <c r="AA309" s="2"/>
     </row>
-    <row r="310" spans="1:27" ht="13.2">
+    <row r="310" spans="1:27" ht="12.75">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="14"/>
@@ -11823,7 +11832,7 @@
       <c r="Z310" s="2"/>
       <c r="AA310" s="2"/>
     </row>
-    <row r="311" spans="1:27" ht="13.2">
+    <row r="311" spans="1:27" ht="12.75">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="14"/>
@@ -11852,7 +11861,7 @@
       <c r="Z311" s="2"/>
       <c r="AA311" s="2"/>
     </row>
-    <row r="312" spans="1:27" ht="13.2">
+    <row r="312" spans="1:27" ht="12.75">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="14"/>
@@ -11881,7 +11890,7 @@
       <c r="Z312" s="2"/>
       <c r="AA312" s="2"/>
     </row>
-    <row r="313" spans="1:27" ht="13.2">
+    <row r="313" spans="1:27" ht="12.75">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="14"/>
@@ -11910,7 +11919,7 @@
       <c r="Z313" s="2"/>
       <c r="AA313" s="2"/>
     </row>
-    <row r="314" spans="1:27" ht="13.2">
+    <row r="314" spans="1:27" ht="12.75">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="14"/>
@@ -11939,7 +11948,7 @@
       <c r="Z314" s="2"/>
       <c r="AA314" s="2"/>
     </row>
-    <row r="315" spans="1:27" ht="13.2">
+    <row r="315" spans="1:27" ht="12.75">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="14"/>
@@ -11968,7 +11977,7 @@
       <c r="Z315" s="2"/>
       <c r="AA315" s="2"/>
     </row>
-    <row r="316" spans="1:27" ht="13.2">
+    <row r="316" spans="1:27" ht="12.75">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="14"/>
@@ -11997,7 +12006,7 @@
       <c r="Z316" s="2"/>
       <c r="AA316" s="2"/>
     </row>
-    <row r="317" spans="1:27" ht="13.2">
+    <row r="317" spans="1:27" ht="12.75">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="14"/>
@@ -12026,7 +12035,7 @@
       <c r="Z317" s="2"/>
       <c r="AA317" s="2"/>
     </row>
-    <row r="318" spans="1:27" ht="13.2">
+    <row r="318" spans="1:27" ht="12.75">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="14"/>
@@ -12055,7 +12064,7 @@
       <c r="Z318" s="2"/>
       <c r="AA318" s="2"/>
     </row>
-    <row r="319" spans="1:27" ht="13.2">
+    <row r="319" spans="1:27" ht="12.75">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="14"/>
@@ -12084,7 +12093,7 @@
       <c r="Z319" s="2"/>
       <c r="AA319" s="2"/>
     </row>
-    <row r="320" spans="1:27" ht="13.2">
+    <row r="320" spans="1:27" ht="12.75">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="14"/>
@@ -12113,7 +12122,7 @@
       <c r="Z320" s="2"/>
       <c r="AA320" s="2"/>
     </row>
-    <row r="321" spans="1:27" ht="13.2">
+    <row r="321" spans="1:27" ht="12.75">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="14"/>
@@ -12142,7 +12151,7 @@
       <c r="Z321" s="2"/>
       <c r="AA321" s="2"/>
     </row>
-    <row r="322" spans="1:27" ht="13.2">
+    <row r="322" spans="1:27" ht="12.75">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="14"/>
@@ -12171,7 +12180,7 @@
       <c r="Z322" s="2"/>
       <c r="AA322" s="2"/>
     </row>
-    <row r="323" spans="1:27" ht="13.2">
+    <row r="323" spans="1:27" ht="12.75">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="14"/>
@@ -12200,7 +12209,7 @@
       <c r="Z323" s="2"/>
       <c r="AA323" s="2"/>
     </row>
-    <row r="324" spans="1:27" ht="13.2">
+    <row r="324" spans="1:27" ht="12.75">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="14"/>
@@ -12229,7 +12238,7 @@
       <c r="Z324" s="2"/>
       <c r="AA324" s="2"/>
     </row>
-    <row r="325" spans="1:27" ht="13.2">
+    <row r="325" spans="1:27" ht="12.75">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="14"/>
@@ -12258,7 +12267,7 @@
       <c r="Z325" s="2"/>
       <c r="AA325" s="2"/>
     </row>
-    <row r="326" spans="1:27" ht="13.2">
+    <row r="326" spans="1:27" ht="12.75">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="14"/>
@@ -12287,7 +12296,7 @@
       <c r="Z326" s="2"/>
       <c r="AA326" s="2"/>
     </row>
-    <row r="327" spans="1:27" ht="13.2">
+    <row r="327" spans="1:27" ht="12.75">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="14"/>
@@ -12316,7 +12325,7 @@
       <c r="Z327" s="2"/>
       <c r="AA327" s="2"/>
     </row>
-    <row r="328" spans="1:27" ht="13.2">
+    <row r="328" spans="1:27" ht="12.75">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="14"/>
@@ -12345,7 +12354,7 @@
       <c r="Z328" s="2"/>
       <c r="AA328" s="2"/>
     </row>
-    <row r="329" spans="1:27" ht="13.2">
+    <row r="329" spans="1:27" ht="12.75">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="14"/>
@@ -12374,7 +12383,7 @@
       <c r="Z329" s="2"/>
       <c r="AA329" s="2"/>
     </row>
-    <row r="330" spans="1:27" ht="13.2">
+    <row r="330" spans="1:27" ht="12.75">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="14"/>
@@ -12403,7 +12412,7 @@
       <c r="Z330" s="2"/>
       <c r="AA330" s="2"/>
     </row>
-    <row r="331" spans="1:27" ht="13.2">
+    <row r="331" spans="1:27" ht="12.75">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="14"/>
@@ -12432,7 +12441,7 @@
       <c r="Z331" s="2"/>
       <c r="AA331" s="2"/>
     </row>
-    <row r="332" spans="1:27" ht="13.2">
+    <row r="332" spans="1:27" ht="12.75">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="14"/>
@@ -12461,7 +12470,7 @@
       <c r="Z332" s="2"/>
       <c r="AA332" s="2"/>
     </row>
-    <row r="333" spans="1:27" ht="13.2">
+    <row r="333" spans="1:27" ht="12.75">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="14"/>
@@ -12490,7 +12499,7 @@
       <c r="Z333" s="2"/>
       <c r="AA333" s="2"/>
     </row>
-    <row r="334" spans="1:27" ht="13.2">
+    <row r="334" spans="1:27" ht="12.75">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="14"/>
@@ -12519,7 +12528,7 @@
       <c r="Z334" s="2"/>
       <c r="AA334" s="2"/>
     </row>
-    <row r="335" spans="1:27" ht="13.2">
+    <row r="335" spans="1:27" ht="12.75">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="14"/>
@@ -12548,7 +12557,7 @@
       <c r="Z335" s="2"/>
       <c r="AA335" s="2"/>
     </row>
-    <row r="336" spans="1:27" ht="13.2">
+    <row r="336" spans="1:27" ht="12.75">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="14"/>
@@ -12577,7 +12586,7 @@
       <c r="Z336" s="2"/>
       <c r="AA336" s="2"/>
     </row>
-    <row r="337" spans="1:27" ht="13.2">
+    <row r="337" spans="1:27" ht="12.75">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="14"/>
@@ -12606,7 +12615,7 @@
       <c r="Z337" s="2"/>
       <c r="AA337" s="2"/>
     </row>
-    <row r="338" spans="1:27" ht="13.2">
+    <row r="338" spans="1:27" ht="12.75">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="14"/>
@@ -12635,7 +12644,7 @@
       <c r="Z338" s="2"/>
       <c r="AA338" s="2"/>
     </row>
-    <row r="339" spans="1:27" ht="13.2">
+    <row r="339" spans="1:27" ht="12.75">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="14"/>
@@ -12664,7 +12673,7 @@
       <c r="Z339" s="2"/>
       <c r="AA339" s="2"/>
     </row>
-    <row r="340" spans="1:27" ht="13.2">
+    <row r="340" spans="1:27" ht="12.75">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="14"/>
@@ -12693,7 +12702,7 @@
       <c r="Z340" s="2"/>
       <c r="AA340" s="2"/>
     </row>
-    <row r="341" spans="1:27" ht="13.2">
+    <row r="341" spans="1:27" ht="12.75">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="14"/>
@@ -12722,7 +12731,7 @@
       <c r="Z341" s="2"/>
       <c r="AA341" s="2"/>
     </row>
-    <row r="342" spans="1:27" ht="13.2">
+    <row r="342" spans="1:27" ht="12.75">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="14"/>
@@ -12751,7 +12760,7 @@
       <c r="Z342" s="2"/>
       <c r="AA342" s="2"/>
     </row>
-    <row r="343" spans="1:27" ht="13.2">
+    <row r="343" spans="1:27" ht="12.75">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="14"/>
@@ -12780,7 +12789,7 @@
       <c r="Z343" s="2"/>
       <c r="AA343" s="2"/>
     </row>
-    <row r="344" spans="1:27" ht="13.2">
+    <row r="344" spans="1:27" ht="12.75">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="14"/>
@@ -12809,7 +12818,7 @@
       <c r="Z344" s="2"/>
       <c r="AA344" s="2"/>
     </row>
-    <row r="345" spans="1:27" ht="13.2">
+    <row r="345" spans="1:27" ht="12.75">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="14"/>
@@ -12838,7 +12847,7 @@
       <c r="Z345" s="2"/>
       <c r="AA345" s="2"/>
     </row>
-    <row r="346" spans="1:27" ht="13.2">
+    <row r="346" spans="1:27" ht="12.75">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="14"/>
@@ -12867,7 +12876,7 @@
       <c r="Z346" s="2"/>
       <c r="AA346" s="2"/>
     </row>
-    <row r="347" spans="1:27" ht="13.2">
+    <row r="347" spans="1:27" ht="12.75">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="14"/>
@@ -12896,7 +12905,7 @@
       <c r="Z347" s="2"/>
       <c r="AA347" s="2"/>
     </row>
-    <row r="348" spans="1:27" ht="13.2">
+    <row r="348" spans="1:27" ht="12.75">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="14"/>
@@ -12925,7 +12934,7 @@
       <c r="Z348" s="2"/>
       <c r="AA348" s="2"/>
     </row>
-    <row r="349" spans="1:27" ht="13.2">
+    <row r="349" spans="1:27" ht="12.75">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="14"/>
@@ -12954,7 +12963,7 @@
       <c r="Z349" s="2"/>
       <c r="AA349" s="2"/>
     </row>
-    <row r="350" spans="1:27" ht="13.2">
+    <row r="350" spans="1:27" ht="12.75">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="14"/>
@@ -12983,7 +12992,7 @@
       <c r="Z350" s="2"/>
       <c r="AA350" s="2"/>
     </row>
-    <row r="351" spans="1:27" ht="13.2">
+    <row r="351" spans="1:27" ht="12.75">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="14"/>
@@ -13012,7 +13021,7 @@
       <c r="Z351" s="2"/>
       <c r="AA351" s="2"/>
     </row>
-    <row r="352" spans="1:27" ht="13.2">
+    <row r="352" spans="1:27" ht="12.75">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="14"/>
@@ -13041,7 +13050,7 @@
       <c r="Z352" s="2"/>
       <c r="AA352" s="2"/>
     </row>
-    <row r="353" spans="1:27" ht="13.2">
+    <row r="353" spans="1:27" ht="12.75">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="14"/>
@@ -13070,7 +13079,7 @@
       <c r="Z353" s="2"/>
       <c r="AA353" s="2"/>
     </row>
-    <row r="354" spans="1:27" ht="13.2">
+    <row r="354" spans="1:27" ht="12.75">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="14"/>
@@ -13099,7 +13108,7 @@
       <c r="Z354" s="2"/>
       <c r="AA354" s="2"/>
     </row>
-    <row r="355" spans="1:27" ht="13.2">
+    <row r="355" spans="1:27" ht="12.75">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="14"/>
@@ -13128,7 +13137,7 @@
       <c r="Z355" s="2"/>
       <c r="AA355" s="2"/>
     </row>
-    <row r="356" spans="1:27" ht="13.2">
+    <row r="356" spans="1:27" ht="12.75">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="14"/>
@@ -13157,7 +13166,7 @@
       <c r="Z356" s="2"/>
       <c r="AA356" s="2"/>
     </row>
-    <row r="357" spans="1:27" ht="13.2">
+    <row r="357" spans="1:27" ht="12.75">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="14"/>
@@ -13186,7 +13195,7 @@
       <c r="Z357" s="2"/>
       <c r="AA357" s="2"/>
     </row>
-    <row r="358" spans="1:27" ht="13.2">
+    <row r="358" spans="1:27" ht="12.75">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="14"/>
@@ -13215,7 +13224,7 @@
       <c r="Z358" s="2"/>
       <c r="AA358" s="2"/>
     </row>
-    <row r="359" spans="1:27" ht="13.2">
+    <row r="359" spans="1:27" ht="12.75">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="14"/>
@@ -13244,7 +13253,7 @@
       <c r="Z359" s="2"/>
       <c r="AA359" s="2"/>
     </row>
-    <row r="360" spans="1:27" ht="13.2">
+    <row r="360" spans="1:27" ht="12.75">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="14"/>
@@ -13273,7 +13282,7 @@
       <c r="Z360" s="2"/>
       <c r="AA360" s="2"/>
     </row>
-    <row r="361" spans="1:27" ht="13.2">
+    <row r="361" spans="1:27" ht="12.75">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="14"/>
@@ -13302,7 +13311,7 @@
       <c r="Z361" s="2"/>
       <c r="AA361" s="2"/>
     </row>
-    <row r="362" spans="1:27" ht="13.2">
+    <row r="362" spans="1:27" ht="12.75">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="14"/>
@@ -13331,7 +13340,7 @@
       <c r="Z362" s="2"/>
       <c r="AA362" s="2"/>
     </row>
-    <row r="363" spans="1:27" ht="13.2">
+    <row r="363" spans="1:27" ht="12.75">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="14"/>
@@ -13360,7 +13369,7 @@
       <c r="Z363" s="2"/>
       <c r="AA363" s="2"/>
     </row>
-    <row r="364" spans="1:27" ht="13.2">
+    <row r="364" spans="1:27" ht="12.75">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="14"/>
@@ -13389,7 +13398,7 @@
       <c r="Z364" s="2"/>
       <c r="AA364" s="2"/>
     </row>
-    <row r="365" spans="1:27" ht="13.2">
+    <row r="365" spans="1:27" ht="12.75">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="14"/>
@@ -13418,7 +13427,7 @@
       <c r="Z365" s="2"/>
       <c r="AA365" s="2"/>
     </row>
-    <row r="366" spans="1:27" ht="13.2">
+    <row r="366" spans="1:27" ht="12.75">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="14"/>
@@ -13447,7 +13456,7 @@
       <c r="Z366" s="2"/>
       <c r="AA366" s="2"/>
     </row>
-    <row r="367" spans="1:27" ht="13.2">
+    <row r="367" spans="1:27" ht="12.75">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="14"/>
@@ -13476,7 +13485,7 @@
       <c r="Z367" s="2"/>
       <c r="AA367" s="2"/>
     </row>
-    <row r="368" spans="1:27" ht="13.2">
+    <row r="368" spans="1:27" ht="12.75">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="14"/>
@@ -13505,7 +13514,7 @@
       <c r="Z368" s="2"/>
       <c r="AA368" s="2"/>
     </row>
-    <row r="369" spans="1:27" ht="13.2">
+    <row r="369" spans="1:27" ht="12.75">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="14"/>
@@ -13534,7 +13543,7 @@
       <c r="Z369" s="2"/>
       <c r="AA369" s="2"/>
     </row>
-    <row r="370" spans="1:27" ht="13.2">
+    <row r="370" spans="1:27" ht="12.75">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="14"/>
@@ -13563,7 +13572,7 @@
       <c r="Z370" s="2"/>
       <c r="AA370" s="2"/>
     </row>
-    <row r="371" spans="1:27" ht="13.2">
+    <row r="371" spans="1:27" ht="12.75">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="14"/>
@@ -13592,7 +13601,7 @@
       <c r="Z371" s="2"/>
       <c r="AA371" s="2"/>
     </row>
-    <row r="372" spans="1:27" ht="13.2">
+    <row r="372" spans="1:27" ht="12.75">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="14"/>
@@ -13621,7 +13630,7 @@
       <c r="Z372" s="2"/>
       <c r="AA372" s="2"/>
     </row>
-    <row r="373" spans="1:27" ht="13.2">
+    <row r="373" spans="1:27" ht="12.75">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="14"/>
@@ -13650,7 +13659,7 @@
       <c r="Z373" s="2"/>
       <c r="AA373" s="2"/>
     </row>
-    <row r="374" spans="1:27" ht="13.2">
+    <row r="374" spans="1:27" ht="12.75">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="14"/>
@@ -13679,7 +13688,7 @@
       <c r="Z374" s="2"/>
       <c r="AA374" s="2"/>
     </row>
-    <row r="375" spans="1:27" ht="13.2">
+    <row r="375" spans="1:27" ht="12.75">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="14"/>
@@ -13708,7 +13717,7 @@
       <c r="Z375" s="2"/>
       <c r="AA375" s="2"/>
     </row>
-    <row r="376" spans="1:27" ht="13.2">
+    <row r="376" spans="1:27" ht="12.75">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="14"/>
@@ -13737,7 +13746,7 @@
       <c r="Z376" s="2"/>
       <c r="AA376" s="2"/>
     </row>
-    <row r="377" spans="1:27" ht="13.2">
+    <row r="377" spans="1:27" ht="12.75">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="14"/>
@@ -13766,7 +13775,7 @@
       <c r="Z377" s="2"/>
       <c r="AA377" s="2"/>
     </row>
-    <row r="378" spans="1:27" ht="13.2">
+    <row r="378" spans="1:27" ht="12.75">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="14"/>
@@ -13795,7 +13804,7 @@
       <c r="Z378" s="2"/>
       <c r="AA378" s="2"/>
     </row>
-    <row r="379" spans="1:27" ht="13.2">
+    <row r="379" spans="1:27" ht="12.75">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="14"/>
@@ -13824,7 +13833,7 @@
       <c r="Z379" s="2"/>
       <c r="AA379" s="2"/>
     </row>
-    <row r="380" spans="1:27" ht="13.2">
+    <row r="380" spans="1:27" ht="12.75">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="14"/>
@@ -13853,7 +13862,7 @@
       <c r="Z380" s="2"/>
       <c r="AA380" s="2"/>
     </row>
-    <row r="381" spans="1:27" ht="13.2">
+    <row r="381" spans="1:27" ht="12.75">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="14"/>
@@ -13882,7 +13891,7 @@
       <c r="Z381" s="2"/>
       <c r="AA381" s="2"/>
     </row>
-    <row r="382" spans="1:27" ht="13.2">
+    <row r="382" spans="1:27" ht="12.75">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="14"/>
@@ -13911,7 +13920,7 @@
       <c r="Z382" s="2"/>
       <c r="AA382" s="2"/>
     </row>
-    <row r="383" spans="1:27" ht="13.2">
+    <row r="383" spans="1:27" ht="12.75">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="14"/>
@@ -13940,7 +13949,7 @@
       <c r="Z383" s="2"/>
       <c r="AA383" s="2"/>
     </row>
-    <row r="384" spans="1:27" ht="13.2">
+    <row r="384" spans="1:27" ht="12.75">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="14"/>
@@ -13969,7 +13978,7 @@
       <c r="Z384" s="2"/>
       <c r="AA384" s="2"/>
     </row>
-    <row r="385" spans="1:27" ht="13.2">
+    <row r="385" spans="1:27" ht="12.75">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="14"/>
@@ -13998,7 +14007,7 @@
       <c r="Z385" s="2"/>
       <c r="AA385" s="2"/>
     </row>
-    <row r="386" spans="1:27" ht="13.2">
+    <row r="386" spans="1:27" ht="12.75">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="14"/>
@@ -14027,7 +14036,7 @@
       <c r="Z386" s="2"/>
       <c r="AA386" s="2"/>
     </row>
-    <row r="387" spans="1:27" ht="13.2">
+    <row r="387" spans="1:27" ht="12.75">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="14"/>
@@ -14056,7 +14065,7 @@
       <c r="Z387" s="2"/>
       <c r="AA387" s="2"/>
     </row>
-    <row r="388" spans="1:27" ht="13.2">
+    <row r="388" spans="1:27" ht="12.75">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="14"/>
@@ -14085,7 +14094,7 @@
       <c r="Z388" s="2"/>
       <c r="AA388" s="2"/>
     </row>
-    <row r="389" spans="1:27" ht="13.2">
+    <row r="389" spans="1:27" ht="12.75">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="14"/>
@@ -14114,7 +14123,7 @@
       <c r="Z389" s="2"/>
       <c r="AA389" s="2"/>
     </row>
-    <row r="390" spans="1:27" ht="13.2">
+    <row r="390" spans="1:27" ht="12.75">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="14"/>
@@ -14143,7 +14152,7 @@
       <c r="Z390" s="2"/>
       <c r="AA390" s="2"/>
     </row>
-    <row r="391" spans="1:27" ht="13.2">
+    <row r="391" spans="1:27" ht="12.75">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="14"/>
@@ -14172,7 +14181,7 @@
       <c r="Z391" s="2"/>
       <c r="AA391" s="2"/>
     </row>
-    <row r="392" spans="1:27" ht="13.2">
+    <row r="392" spans="1:27" ht="12.75">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="14"/>
@@ -14201,7 +14210,7 @@
       <c r="Z392" s="2"/>
       <c r="AA392" s="2"/>
     </row>
-    <row r="393" spans="1:27" ht="13.2">
+    <row r="393" spans="1:27" ht="12.75">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="14"/>
@@ -14230,7 +14239,7 @@
       <c r="Z393" s="2"/>
       <c r="AA393" s="2"/>
     </row>
-    <row r="394" spans="1:27" ht="13.2">
+    <row r="394" spans="1:27" ht="12.75">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="14"/>
@@ -14259,7 +14268,7 @@
       <c r="Z394" s="2"/>
       <c r="AA394" s="2"/>
     </row>
-    <row r="395" spans="1:27" ht="13.2">
+    <row r="395" spans="1:27" ht="12.75">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="14"/>
@@ -14288,7 +14297,7 @@
       <c r="Z395" s="2"/>
       <c r="AA395" s="2"/>
     </row>
-    <row r="396" spans="1:27" ht="13.2">
+    <row r="396" spans="1:27" ht="12.75">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="14"/>
@@ -14317,7 +14326,7 @@
       <c r="Z396" s="2"/>
       <c r="AA396" s="2"/>
     </row>
-    <row r="397" spans="1:27" ht="13.2">
+    <row r="397" spans="1:27" ht="12.75">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="14"/>
@@ -14346,7 +14355,7 @@
       <c r="Z397" s="2"/>
       <c r="AA397" s="2"/>
     </row>
-    <row r="398" spans="1:27" ht="13.2">
+    <row r="398" spans="1:27" ht="12.75">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="14"/>
@@ -14375,7 +14384,7 @@
       <c r="Z398" s="2"/>
       <c r="AA398" s="2"/>
     </row>
-    <row r="399" spans="1:27" ht="13.2">
+    <row r="399" spans="1:27" ht="12.75">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="14"/>
@@ -14404,7 +14413,7 @@
       <c r="Z399" s="2"/>
       <c r="AA399" s="2"/>
     </row>
-    <row r="400" spans="1:27" ht="13.2">
+    <row r="400" spans="1:27" ht="12.75">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="14"/>
@@ -14433,7 +14442,7 @@
       <c r="Z400" s="2"/>
       <c r="AA400" s="2"/>
     </row>
-    <row r="401" spans="1:27" ht="13.2">
+    <row r="401" spans="1:27" ht="12.75">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="14"/>
@@ -14462,7 +14471,7 @@
       <c r="Z401" s="2"/>
       <c r="AA401" s="2"/>
     </row>
-    <row r="402" spans="1:27" ht="13.2">
+    <row r="402" spans="1:27" ht="12.75">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="14"/>
@@ -14491,7 +14500,7 @@
       <c r="Z402" s="2"/>
       <c r="AA402" s="2"/>
     </row>
-    <row r="403" spans="1:27" ht="13.2">
+    <row r="403" spans="1:27" ht="12.75">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="14"/>
@@ -14520,7 +14529,7 @@
       <c r="Z403" s="2"/>
       <c r="AA403" s="2"/>
     </row>
-    <row r="404" spans="1:27" ht="13.2">
+    <row r="404" spans="1:27" ht="12.75">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="14"/>
@@ -14549,7 +14558,7 @@
       <c r="Z404" s="2"/>
       <c r="AA404" s="2"/>
     </row>
-    <row r="405" spans="1:27" ht="13.2">
+    <row r="405" spans="1:27" ht="12.75">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="14"/>
@@ -14578,7 +14587,7 @@
       <c r="Z405" s="2"/>
       <c r="AA405" s="2"/>
     </row>
-    <row r="406" spans="1:27" ht="13.2">
+    <row r="406" spans="1:27" ht="12.75">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="14"/>
@@ -14607,7 +14616,7 @@
       <c r="Z406" s="2"/>
       <c r="AA406" s="2"/>
     </row>
-    <row r="407" spans="1:27" ht="13.2">
+    <row r="407" spans="1:27" ht="12.75">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="14"/>
@@ -14636,7 +14645,7 @@
       <c r="Z407" s="2"/>
       <c r="AA407" s="2"/>
     </row>
-    <row r="408" spans="1:27" ht="13.2">
+    <row r="408" spans="1:27" ht="12.75">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="14"/>
@@ -14665,7 +14674,7 @@
       <c r="Z408" s="2"/>
       <c r="AA408" s="2"/>
     </row>
-    <row r="409" spans="1:27" ht="13.2">
+    <row r="409" spans="1:27" ht="12.75">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="14"/>
@@ -14694,7 +14703,7 @@
       <c r="Z409" s="2"/>
       <c r="AA409" s="2"/>
     </row>
-    <row r="410" spans="1:27" ht="13.2">
+    <row r="410" spans="1:27" ht="12.75">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="14"/>
@@ -14723,7 +14732,7 @@
       <c r="Z410" s="2"/>
       <c r="AA410" s="2"/>
     </row>
-    <row r="411" spans="1:27" ht="13.2">
+    <row r="411" spans="1:27" ht="12.75">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="14"/>
@@ -14752,7 +14761,7 @@
       <c r="Z411" s="2"/>
       <c r="AA411" s="2"/>
     </row>
-    <row r="412" spans="1:27" ht="13.2">
+    <row r="412" spans="1:27" ht="12.75">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="14"/>
@@ -14781,7 +14790,7 @@
       <c r="Z412" s="2"/>
       <c r="AA412" s="2"/>
     </row>
-    <row r="413" spans="1:27" ht="13.2">
+    <row r="413" spans="1:27" ht="12.75">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="14"/>
@@ -14810,7 +14819,7 @@
       <c r="Z413" s="2"/>
       <c r="AA413" s="2"/>
     </row>
-    <row r="414" spans="1:27" ht="13.2">
+    <row r="414" spans="1:27" ht="12.75">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="14"/>
@@ -14839,7 +14848,7 @@
       <c r="Z414" s="2"/>
       <c r="AA414" s="2"/>
     </row>
-    <row r="415" spans="1:27" ht="13.2">
+    <row r="415" spans="1:27" ht="12.75">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="14"/>
@@ -14868,7 +14877,7 @@
       <c r="Z415" s="2"/>
       <c r="AA415" s="2"/>
     </row>
-    <row r="416" spans="1:27" ht="13.2">
+    <row r="416" spans="1:27" ht="12.75">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="14"/>
@@ -14897,7 +14906,7 @@
       <c r="Z416" s="2"/>
       <c r="AA416" s="2"/>
     </row>
-    <row r="417" spans="1:27" ht="13.2">
+    <row r="417" spans="1:27" ht="12.75">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="14"/>
@@ -14926,7 +14935,7 @@
       <c r="Z417" s="2"/>
       <c r="AA417" s="2"/>
     </row>
-    <row r="418" spans="1:27" ht="13.2">
+    <row r="418" spans="1:27" ht="12.75">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="14"/>
@@ -14955,7 +14964,7 @@
       <c r="Z418" s="2"/>
       <c r="AA418" s="2"/>
     </row>
-    <row r="419" spans="1:27" ht="13.2">
+    <row r="419" spans="1:27" ht="12.75">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="14"/>
@@ -14984,7 +14993,7 @@
       <c r="Z419" s="2"/>
       <c r="AA419" s="2"/>
     </row>
-    <row r="420" spans="1:27" ht="13.2">
+    <row r="420" spans="1:27" ht="12.75">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="14"/>
@@ -15013,7 +15022,7 @@
       <c r="Z420" s="2"/>
       <c r="AA420" s="2"/>
     </row>
-    <row r="421" spans="1:27" ht="13.2">
+    <row r="421" spans="1:27" ht="12.75">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="14"/>
@@ -15042,7 +15051,7 @@
       <c r="Z421" s="2"/>
       <c r="AA421" s="2"/>
     </row>
-    <row r="422" spans="1:27" ht="13.2">
+    <row r="422" spans="1:27" ht="12.75">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="14"/>
@@ -15071,7 +15080,7 @@
       <c r="Z422" s="2"/>
       <c r="AA422" s="2"/>
     </row>
-    <row r="423" spans="1:27" ht="13.2">
+    <row r="423" spans="1:27" ht="12.75">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="14"/>
@@ -15100,7 +15109,7 @@
       <c r="Z423" s="2"/>
       <c r="AA423" s="2"/>
     </row>
-    <row r="424" spans="1:27" ht="13.2">
+    <row r="424" spans="1:27" ht="12.75">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="14"/>
@@ -15129,7 +15138,7 @@
       <c r="Z424" s="2"/>
       <c r="AA424" s="2"/>
     </row>
-    <row r="425" spans="1:27" ht="13.2">
+    <row r="425" spans="1:27" ht="12.75">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="14"/>
@@ -15158,7 +15167,7 @@
       <c r="Z425" s="2"/>
       <c r="AA425" s="2"/>
     </row>
-    <row r="426" spans="1:27" ht="13.2">
+    <row r="426" spans="1:27" ht="12.75">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="14"/>
@@ -15187,7 +15196,7 @@
       <c r="Z426" s="2"/>
       <c r="AA426" s="2"/>
     </row>
-    <row r="427" spans="1:27" ht="13.2">
+    <row r="427" spans="1:27" ht="12.75">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="14"/>
@@ -15216,7 +15225,7 @@
       <c r="Z427" s="2"/>
       <c r="AA427" s="2"/>
     </row>
-    <row r="428" spans="1:27" ht="13.2">
+    <row r="428" spans="1:27" ht="12.75">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="14"/>
@@ -15245,7 +15254,7 @@
       <c r="Z428" s="2"/>
       <c r="AA428" s="2"/>
     </row>
-    <row r="429" spans="1:27" ht="13.2">
+    <row r="429" spans="1:27" ht="12.75">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="14"/>
@@ -15274,7 +15283,7 @@
       <c r="Z429" s="2"/>
       <c r="AA429" s="2"/>
     </row>
-    <row r="430" spans="1:27" ht="13.2">
+    <row r="430" spans="1:27" ht="12.75">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="14"/>
@@ -15303,7 +15312,7 @@
       <c r="Z430" s="2"/>
       <c r="AA430" s="2"/>
     </row>
-    <row r="431" spans="1:27" ht="13.2">
+    <row r="431" spans="1:27" ht="12.75">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="14"/>
@@ -15332,7 +15341,7 @@
       <c r="Z431" s="2"/>
       <c r="AA431" s="2"/>
     </row>
-    <row r="432" spans="1:27" ht="13.2">
+    <row r="432" spans="1:27" ht="12.75">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="14"/>
@@ -15361,7 +15370,7 @@
       <c r="Z432" s="2"/>
       <c r="AA432" s="2"/>
     </row>
-    <row r="433" spans="1:27" ht="13.2">
+    <row r="433" spans="1:27" ht="12.75">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="14"/>
@@ -15390,7 +15399,7 @@
       <c r="Z433" s="2"/>
       <c r="AA433" s="2"/>
     </row>
-    <row r="434" spans="1:27" ht="13.2">
+    <row r="434" spans="1:27" ht="12.75">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="14"/>
@@ -15419,7 +15428,7 @@
       <c r="Z434" s="2"/>
       <c r="AA434" s="2"/>
     </row>
-    <row r="435" spans="1:27" ht="13.2">
+    <row r="435" spans="1:27" ht="12.75">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="14"/>
@@ -15448,7 +15457,7 @@
       <c r="Z435" s="2"/>
       <c r="AA435" s="2"/>
     </row>
-    <row r="436" spans="1:27" ht="13.2">
+    <row r="436" spans="1:27" ht="12.75">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="14"/>
@@ -15477,7 +15486,7 @@
       <c r="Z436" s="2"/>
       <c r="AA436" s="2"/>
     </row>
-    <row r="437" spans="1:27" ht="13.2">
+    <row r="437" spans="1:27" ht="12.75">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="14"/>
@@ -15506,7 +15515,7 @@
       <c r="Z437" s="2"/>
       <c r="AA437" s="2"/>
     </row>
-    <row r="438" spans="1:27" ht="13.2">
+    <row r="438" spans="1:27" ht="12.75">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="14"/>
@@ -15535,7 +15544,7 @@
       <c r="Z438" s="2"/>
       <c r="AA438" s="2"/>
     </row>
-    <row r="439" spans="1:27" ht="13.2">
+    <row r="439" spans="1:27" ht="12.75">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="14"/>
@@ -15564,7 +15573,7 @@
       <c r="Z439" s="2"/>
       <c r="AA439" s="2"/>
     </row>
-    <row r="440" spans="1:27" ht="13.2">
+    <row r="440" spans="1:27" ht="12.75">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="14"/>
@@ -15593,7 +15602,7 @@
       <c r="Z440" s="2"/>
       <c r="AA440" s="2"/>
     </row>
-    <row r="441" spans="1:27" ht="13.2">
+    <row r="441" spans="1:27" ht="12.75">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="14"/>
@@ -15622,7 +15631,7 @@
       <c r="Z441" s="2"/>
       <c r="AA441" s="2"/>
     </row>
-    <row r="442" spans="1:27" ht="13.2">
+    <row r="442" spans="1:27" ht="12.75">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="14"/>
@@ -15651,7 +15660,7 @@
       <c r="Z442" s="2"/>
       <c r="AA442" s="2"/>
     </row>
-    <row r="443" spans="1:27" ht="13.2">
+    <row r="443" spans="1:27" ht="12.75">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="14"/>
@@ -15680,7 +15689,7 @@
       <c r="Z443" s="2"/>
       <c r="AA443" s="2"/>
     </row>
-    <row r="444" spans="1:27" ht="13.2">
+    <row r="444" spans="1:27" ht="12.75">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="14"/>
@@ -15709,7 +15718,7 @@
       <c r="Z444" s="2"/>
       <c r="AA444" s="2"/>
     </row>
-    <row r="445" spans="1:27" ht="13.2">
+    <row r="445" spans="1:27" ht="12.75">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="14"/>
@@ -15738,7 +15747,7 @@
       <c r="Z445" s="2"/>
       <c r="AA445" s="2"/>
     </row>
-    <row r="446" spans="1:27" ht="13.2">
+    <row r="446" spans="1:27" ht="12.75">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="14"/>
@@ -15767,7 +15776,7 @@
       <c r="Z446" s="2"/>
       <c r="AA446" s="2"/>
     </row>
-    <row r="447" spans="1:27" ht="13.2">
+    <row r="447" spans="1:27" ht="12.75">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="14"/>
@@ -15796,7 +15805,7 @@
       <c r="Z447" s="2"/>
       <c r="AA447" s="2"/>
     </row>
-    <row r="448" spans="1:27" ht="13.2">
+    <row r="448" spans="1:27" ht="12.75">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="14"/>
@@ -15825,7 +15834,7 @@
       <c r="Z448" s="2"/>
       <c r="AA448" s="2"/>
     </row>
-    <row r="449" spans="1:27" ht="13.2">
+    <row r="449" spans="1:27" ht="12.75">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="14"/>
@@ -15854,7 +15863,7 @@
       <c r="Z449" s="2"/>
       <c r="AA449" s="2"/>
     </row>
-    <row r="450" spans="1:27" ht="13.2">
+    <row r="450" spans="1:27" ht="12.75">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="14"/>
@@ -15883,7 +15892,7 @@
       <c r="Z450" s="2"/>
       <c r="AA450" s="2"/>
     </row>
-    <row r="451" spans="1:27" ht="13.2">
+    <row r="451" spans="1:27" ht="12.75">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="14"/>
@@ -15912,7 +15921,7 @@
       <c r="Z451" s="2"/>
       <c r="AA451" s="2"/>
     </row>
-    <row r="452" spans="1:27" ht="13.2">
+    <row r="452" spans="1:27" ht="12.75">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="14"/>
@@ -15941,7 +15950,7 @@
       <c r="Z452" s="2"/>
       <c r="AA452" s="2"/>
     </row>
-    <row r="453" spans="1:27" ht="13.2">
+    <row r="453" spans="1:27" ht="12.75">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="14"/>
@@ -15970,7 +15979,7 @@
       <c r="Z453" s="2"/>
       <c r="AA453" s="2"/>
     </row>
-    <row r="454" spans="1:27" ht="13.2">
+    <row r="454" spans="1:27" ht="12.75">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="14"/>
@@ -15999,7 +16008,7 @@
       <c r="Z454" s="2"/>
       <c r="AA454" s="2"/>
     </row>
-    <row r="455" spans="1:27" ht="13.2">
+    <row r="455" spans="1:27" ht="12.75">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="14"/>
@@ -16028,7 +16037,7 @@
       <c r="Z455" s="2"/>
       <c r="AA455" s="2"/>
     </row>
-    <row r="456" spans="1:27" ht="13.2">
+    <row r="456" spans="1:27" ht="12.75">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="14"/>
@@ -16057,7 +16066,7 @@
       <c r="Z456" s="2"/>
       <c r="AA456" s="2"/>
     </row>
-    <row r="457" spans="1:27" ht="13.2">
+    <row r="457" spans="1:27" ht="12.75">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="14"/>
@@ -16086,7 +16095,7 @@
       <c r="Z457" s="2"/>
       <c r="AA457" s="2"/>
     </row>
-    <row r="458" spans="1:27" ht="13.2">
+    <row r="458" spans="1:27" ht="12.75">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="14"/>
@@ -16115,7 +16124,7 @@
       <c r="Z458" s="2"/>
       <c r="AA458" s="2"/>
     </row>
-    <row r="459" spans="1:27" ht="13.2">
+    <row r="459" spans="1:27" ht="12.75">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="14"/>
@@ -16144,7 +16153,7 @@
       <c r="Z459" s="2"/>
       <c r="AA459" s="2"/>
     </row>
-    <row r="460" spans="1:27" ht="13.2">
+    <row r="460" spans="1:27" ht="12.75">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="14"/>
@@ -16173,7 +16182,7 @@
       <c r="Z460" s="2"/>
       <c r="AA460" s="2"/>
     </row>
-    <row r="461" spans="1:27" ht="13.2">
+    <row r="461" spans="1:27" ht="12.75">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="14"/>
@@ -16202,7 +16211,7 @@
       <c r="Z461" s="2"/>
       <c r="AA461" s="2"/>
     </row>
-    <row r="462" spans="1:27" ht="13.2">
+    <row r="462" spans="1:27" ht="12.75">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="14"/>
@@ -16231,7 +16240,7 @@
       <c r="Z462" s="2"/>
       <c r="AA462" s="2"/>
     </row>
-    <row r="463" spans="1:27" ht="13.2">
+    <row r="463" spans="1:27" ht="12.75">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="14"/>
@@ -16260,7 +16269,7 @@
       <c r="Z463" s="2"/>
       <c r="AA463" s="2"/>
     </row>
-    <row r="464" spans="1:27" ht="13.2">
+    <row r="464" spans="1:27" ht="12.75">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="14"/>
@@ -16289,7 +16298,7 @@
       <c r="Z464" s="2"/>
       <c r="AA464" s="2"/>
     </row>
-    <row r="465" spans="1:27" ht="13.2">
+    <row r="465" spans="1:27" ht="12.75">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="14"/>
@@ -16318,7 +16327,7 @@
       <c r="Z465" s="2"/>
       <c r="AA465" s="2"/>
     </row>
-    <row r="466" spans="1:27" ht="13.2">
+    <row r="466" spans="1:27" ht="12.75">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="14"/>
@@ -16347,7 +16356,7 @@
       <c r="Z466" s="2"/>
       <c r="AA466" s="2"/>
     </row>
-    <row r="467" spans="1:27" ht="13.2">
+    <row r="467" spans="1:27" ht="12.75">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="14"/>
@@ -16376,7 +16385,7 @@
       <c r="Z467" s="2"/>
       <c r="AA467" s="2"/>
     </row>
-    <row r="468" spans="1:27" ht="13.2">
+    <row r="468" spans="1:27" ht="12.75">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="14"/>
@@ -16405,7 +16414,7 @@
       <c r="Z468" s="2"/>
       <c r="AA468" s="2"/>
     </row>
-    <row r="469" spans="1:27" ht="13.2">
+    <row r="469" spans="1:27" ht="12.75">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="14"/>
@@ -16434,7 +16443,7 @@
       <c r="Z469" s="2"/>
       <c r="AA469" s="2"/>
     </row>
-    <row r="470" spans="1:27" ht="13.2">
+    <row r="470" spans="1:27" ht="12.75">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="14"/>
@@ -16463,7 +16472,7 @@
       <c r="Z470" s="2"/>
       <c r="AA470" s="2"/>
     </row>
-    <row r="471" spans="1:27" ht="13.2">
+    <row r="471" spans="1:27" ht="12.75">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="14"/>
@@ -16492,7 +16501,7 @@
       <c r="Z471" s="2"/>
       <c r="AA471" s="2"/>
     </row>
-    <row r="472" spans="1:27" ht="13.2">
+    <row r="472" spans="1:27" ht="12.75">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="14"/>
@@ -16521,7 +16530,7 @@
       <c r="Z472" s="2"/>
       <c r="AA472" s="2"/>
     </row>
-    <row r="473" spans="1:27" ht="13.2">
+    <row r="473" spans="1:27" ht="12.75">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="14"/>
@@ -16550,7 +16559,7 @@
       <c r="Z473" s="2"/>
       <c r="AA473" s="2"/>
     </row>
-    <row r="474" spans="1:27" ht="13.2">
+    <row r="474" spans="1:27" ht="12.75">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="14"/>
@@ -16579,7 +16588,7 @@
       <c r="Z474" s="2"/>
       <c r="AA474" s="2"/>
     </row>
-    <row r="475" spans="1:27" ht="13.2">
+    <row r="475" spans="1:27" ht="12.75">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="14"/>
@@ -16608,7 +16617,7 @@
       <c r="Z475" s="2"/>
       <c r="AA475" s="2"/>
     </row>
-    <row r="476" spans="1:27" ht="13.2">
+    <row r="476" spans="1:27" ht="12.75">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="14"/>
@@ -16637,7 +16646,7 @@
       <c r="Z476" s="2"/>
       <c r="AA476" s="2"/>
     </row>
-    <row r="477" spans="1:27" ht="13.2">
+    <row r="477" spans="1:27" ht="12.75">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="14"/>
@@ -16666,7 +16675,7 @@
       <c r="Z477" s="2"/>
       <c r="AA477" s="2"/>
     </row>
-    <row r="478" spans="1:27" ht="13.2">
+    <row r="478" spans="1:27" ht="12.75">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="14"/>
@@ -16695,7 +16704,7 @@
       <c r="Z478" s="2"/>
       <c r="AA478" s="2"/>
     </row>
-    <row r="479" spans="1:27" ht="13.2">
+    <row r="479" spans="1:27" ht="12.75">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="14"/>
@@ -16724,7 +16733,7 @@
       <c r="Z479" s="2"/>
       <c r="AA479" s="2"/>
     </row>
-    <row r="480" spans="1:27" ht="13.2">
+    <row r="480" spans="1:27" ht="12.75">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="14"/>
@@ -16753,7 +16762,7 @@
       <c r="Z480" s="2"/>
       <c r="AA480" s="2"/>
     </row>
-    <row r="481" spans="1:27" ht="13.2">
+    <row r="481" spans="1:27" ht="12.75">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="14"/>
@@ -16782,7 +16791,7 @@
       <c r="Z481" s="2"/>
       <c r="AA481" s="2"/>
     </row>
-    <row r="482" spans="1:27" ht="13.2">
+    <row r="482" spans="1:27" ht="12.75">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="14"/>
@@ -16811,7 +16820,7 @@
       <c r="Z482" s="2"/>
       <c r="AA482" s="2"/>
     </row>
-    <row r="483" spans="1:27" ht="13.2">
+    <row r="483" spans="1:27" ht="12.75">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="14"/>
@@ -16840,7 +16849,7 @@
       <c r="Z483" s="2"/>
       <c r="AA483" s="2"/>
     </row>
-    <row r="484" spans="1:27" ht="13.2">
+    <row r="484" spans="1:27" ht="12.75">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="14"/>
@@ -16869,7 +16878,7 @@
       <c r="Z484" s="2"/>
       <c r="AA484" s="2"/>
     </row>
-    <row r="485" spans="1:27" ht="13.2">
+    <row r="485" spans="1:27" ht="12.75">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="14"/>
@@ -16898,7 +16907,7 @@
       <c r="Z485" s="2"/>
       <c r="AA485" s="2"/>
     </row>
-    <row r="486" spans="1:27" ht="13.2">
+    <row r="486" spans="1:27" ht="12.75">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="14"/>
@@ -16927,7 +16936,7 @@
       <c r="Z486" s="2"/>
       <c r="AA486" s="2"/>
     </row>
-    <row r="487" spans="1:27" ht="13.2">
+    <row r="487" spans="1:27" ht="12.75">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="14"/>
@@ -16956,7 +16965,7 @@
       <c r="Z487" s="2"/>
       <c r="AA487" s="2"/>
     </row>
-    <row r="488" spans="1:27" ht="13.2">
+    <row r="488" spans="1:27" ht="12.75">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="14"/>
@@ -16985,7 +16994,7 @@
       <c r="Z488" s="2"/>
       <c r="AA488" s="2"/>
     </row>
-    <row r="489" spans="1:27" ht="13.2">
+    <row r="489" spans="1:27" ht="12.75">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="14"/>
@@ -17014,7 +17023,7 @@
       <c r="Z489" s="2"/>
       <c r="AA489" s="2"/>
     </row>
-    <row r="490" spans="1:27" ht="13.2">
+    <row r="490" spans="1:27" ht="12.75">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="14"/>
@@ -17043,7 +17052,7 @@
       <c r="Z490" s="2"/>
       <c r="AA490" s="2"/>
     </row>
-    <row r="491" spans="1:27" ht="13.2">
+    <row r="491" spans="1:27" ht="12.75">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="14"/>
@@ -17072,7 +17081,7 @@
       <c r="Z491" s="2"/>
       <c r="AA491" s="2"/>
     </row>
-    <row r="492" spans="1:27" ht="13.2">
+    <row r="492" spans="1:27" ht="12.75">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="14"/>
@@ -17101,7 +17110,7 @@
       <c r="Z492" s="2"/>
       <c r="AA492" s="2"/>
     </row>
-    <row r="493" spans="1:27" ht="13.2">
+    <row r="493" spans="1:27" ht="12.75">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="14"/>
@@ -17130,7 +17139,7 @@
       <c r="Z493" s="2"/>
       <c r="AA493" s="2"/>
     </row>
-    <row r="494" spans="1:27" ht="13.2">
+    <row r="494" spans="1:27" ht="12.75">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="14"/>
@@ -17159,7 +17168,7 @@
       <c r="Z494" s="2"/>
       <c r="AA494" s="2"/>
     </row>
-    <row r="495" spans="1:27" ht="13.2">
+    <row r="495" spans="1:27" ht="12.75">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="14"/>
@@ -17188,7 +17197,7 @@
       <c r="Z495" s="2"/>
       <c r="AA495" s="2"/>
     </row>
-    <row r="496" spans="1:27" ht="13.2">
+    <row r="496" spans="1:27" ht="12.75">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="14"/>
@@ -17217,7 +17226,7 @@
       <c r="Z496" s="2"/>
       <c r="AA496" s="2"/>
     </row>
-    <row r="497" spans="1:27" ht="13.2">
+    <row r="497" spans="1:27" ht="12.75">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="14"/>
@@ -17246,7 +17255,7 @@
       <c r="Z497" s="2"/>
       <c r="AA497" s="2"/>
     </row>
-    <row r="498" spans="1:27" ht="13.2">
+    <row r="498" spans="1:27" ht="12.75">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="14"/>
@@ -17275,7 +17284,7 @@
       <c r="Z498" s="2"/>
       <c r="AA498" s="2"/>
     </row>
-    <row r="499" spans="1:27" ht="13.2">
+    <row r="499" spans="1:27" ht="12.75">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="14"/>
@@ -17304,7 +17313,7 @@
       <c r="Z499" s="2"/>
       <c r="AA499" s="2"/>
     </row>
-    <row r="500" spans="1:27" ht="13.2">
+    <row r="500" spans="1:27" ht="12.75">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="14"/>
@@ -17333,7 +17342,7 @@
       <c r="Z500" s="2"/>
       <c r="AA500" s="2"/>
     </row>
-    <row r="501" spans="1:27" ht="13.2">
+    <row r="501" spans="1:27" ht="12.75">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="14"/>
@@ -17362,7 +17371,7 @@
       <c r="Z501" s="2"/>
       <c r="AA501" s="2"/>
     </row>
-    <row r="502" spans="1:27" ht="13.2">
+    <row r="502" spans="1:27" ht="12.75">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="14"/>
@@ -17391,7 +17400,7 @@
       <c r="Z502" s="2"/>
       <c r="AA502" s="2"/>
     </row>
-    <row r="503" spans="1:27" ht="13.2">
+    <row r="503" spans="1:27" ht="12.75">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="14"/>
@@ -17420,7 +17429,7 @@
       <c r="Z503" s="2"/>
       <c r="AA503" s="2"/>
     </row>
-    <row r="504" spans="1:27" ht="13.2">
+    <row r="504" spans="1:27" ht="12.75">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="14"/>
@@ -17449,7 +17458,7 @@
       <c r="Z504" s="2"/>
       <c r="AA504" s="2"/>
     </row>
-    <row r="505" spans="1:27" ht="13.2">
+    <row r="505" spans="1:27" ht="12.75">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="14"/>
@@ -17478,7 +17487,7 @@
       <c r="Z505" s="2"/>
       <c r="AA505" s="2"/>
     </row>
-    <row r="506" spans="1:27" ht="13.2">
+    <row r="506" spans="1:27" ht="12.75">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
       <c r="C506" s="14"/>
@@ -17507,7 +17516,7 @@
       <c r="Z506" s="2"/>
       <c r="AA506" s="2"/>
     </row>
-    <row r="507" spans="1:27" ht="13.2">
+    <row r="507" spans="1:27" ht="12.75">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="14"/>
@@ -17536,7 +17545,7 @@
       <c r="Z507" s="2"/>
       <c r="AA507" s="2"/>
     </row>
-    <row r="508" spans="1:27" ht="13.2">
+    <row r="508" spans="1:27" ht="12.75">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="14"/>
@@ -17565,7 +17574,7 @@
       <c r="Z508" s="2"/>
       <c r="AA508" s="2"/>
     </row>
-    <row r="509" spans="1:27" ht="13.2">
+    <row r="509" spans="1:27" ht="12.75">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="14"/>
@@ -17594,7 +17603,7 @@
       <c r="Z509" s="2"/>
       <c r="AA509" s="2"/>
     </row>
-    <row r="510" spans="1:27" ht="13.2">
+    <row r="510" spans="1:27" ht="12.75">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="14"/>
@@ -17623,7 +17632,7 @@
       <c r="Z510" s="2"/>
       <c r="AA510" s="2"/>
     </row>
-    <row r="511" spans="1:27" ht="13.2">
+    <row r="511" spans="1:27" ht="12.75">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="14"/>
@@ -17652,7 +17661,7 @@
       <c r="Z511" s="2"/>
       <c r="AA511" s="2"/>
     </row>
-    <row r="512" spans="1:27" ht="13.2">
+    <row r="512" spans="1:27" ht="12.75">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
       <c r="C512" s="14"/>
@@ -17681,7 +17690,7 @@
       <c r="Z512" s="2"/>
       <c r="AA512" s="2"/>
     </row>
-    <row r="513" spans="1:27" ht="13.2">
+    <row r="513" spans="1:27" ht="12.75">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="14"/>
@@ -17710,7 +17719,7 @@
       <c r="Z513" s="2"/>
       <c r="AA513" s="2"/>
     </row>
-    <row r="514" spans="1:27" ht="13.2">
+    <row r="514" spans="1:27" ht="12.75">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="14"/>
@@ -17739,7 +17748,7 @@
       <c r="Z514" s="2"/>
       <c r="AA514" s="2"/>
     </row>
-    <row r="515" spans="1:27" ht="13.2">
+    <row r="515" spans="1:27" ht="12.75">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="14"/>
@@ -17768,7 +17777,7 @@
       <c r="Z515" s="2"/>
       <c r="AA515" s="2"/>
     </row>
-    <row r="516" spans="1:27" ht="13.2">
+    <row r="516" spans="1:27" ht="12.75">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="14"/>
@@ -17797,7 +17806,7 @@
       <c r="Z516" s="2"/>
       <c r="AA516" s="2"/>
     </row>
-    <row r="517" spans="1:27" ht="13.2">
+    <row r="517" spans="1:27" ht="12.75">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="14"/>
@@ -17826,7 +17835,7 @@
       <c r="Z517" s="2"/>
       <c r="AA517" s="2"/>
     </row>
-    <row r="518" spans="1:27" ht="13.2">
+    <row r="518" spans="1:27" ht="12.75">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
       <c r="C518" s="14"/>
@@ -17855,7 +17864,7 @@
       <c r="Z518" s="2"/>
       <c r="AA518" s="2"/>
     </row>
-    <row r="519" spans="1:27" ht="13.2">
+    <row r="519" spans="1:27" ht="12.75">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="14"/>
@@ -17884,7 +17893,7 @@
       <c r="Z519" s="2"/>
       <c r="AA519" s="2"/>
     </row>
-    <row r="520" spans="1:27" ht="13.2">
+    <row r="520" spans="1:27" ht="12.75">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="14"/>
@@ -17913,7 +17922,7 @@
       <c r="Z520" s="2"/>
       <c r="AA520" s="2"/>
     </row>
-    <row r="521" spans="1:27" ht="13.2">
+    <row r="521" spans="1:27" ht="12.75">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="14"/>
@@ -17942,7 +17951,7 @@
       <c r="Z521" s="2"/>
       <c r="AA521" s="2"/>
     </row>
-    <row r="522" spans="1:27" ht="13.2">
+    <row r="522" spans="1:27" ht="12.75">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
       <c r="C522" s="14"/>
@@ -17971,7 +17980,7 @@
       <c r="Z522" s="2"/>
       <c r="AA522" s="2"/>
     </row>
-    <row r="523" spans="1:27" ht="13.2">
+    <row r="523" spans="1:27" ht="12.75">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="14"/>
@@ -18000,7 +18009,7 @@
       <c r="Z523" s="2"/>
       <c r="AA523" s="2"/>
     </row>
-    <row r="524" spans="1:27" ht="13.2">
+    <row r="524" spans="1:27" ht="12.75">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="14"/>
@@ -18029,7 +18038,7 @@
       <c r="Z524" s="2"/>
       <c r="AA524" s="2"/>
     </row>
-    <row r="525" spans="1:27" ht="13.2">
+    <row r="525" spans="1:27" ht="12.75">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="14"/>
@@ -18058,7 +18067,7 @@
       <c r="Z525" s="2"/>
       <c r="AA525" s="2"/>
     </row>
-    <row r="526" spans="1:27" ht="13.2">
+    <row r="526" spans="1:27" ht="12.75">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="14"/>
@@ -18087,7 +18096,7 @@
       <c r="Z526" s="2"/>
       <c r="AA526" s="2"/>
     </row>
-    <row r="527" spans="1:27" ht="13.2">
+    <row r="527" spans="1:27" ht="12.75">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
       <c r="C527" s="14"/>
@@ -18116,7 +18125,7 @@
       <c r="Z527" s="2"/>
       <c r="AA527" s="2"/>
     </row>
-    <row r="528" spans="1:27" ht="13.2">
+    <row r="528" spans="1:27" ht="12.75">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="14"/>
@@ -18145,7 +18154,7 @@
       <c r="Z528" s="2"/>
       <c r="AA528" s="2"/>
     </row>
-    <row r="529" spans="1:27" ht="13.2">
+    <row r="529" spans="1:27" ht="12.75">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="14"/>
@@ -18174,7 +18183,7 @@
       <c r="Z529" s="2"/>
       <c r="AA529" s="2"/>
     </row>
-    <row r="530" spans="1:27" ht="13.2">
+    <row r="530" spans="1:27" ht="12.75">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
       <c r="C530" s="14"/>
@@ -18203,7 +18212,7 @@
       <c r="Z530" s="2"/>
       <c r="AA530" s="2"/>
     </row>
-    <row r="531" spans="1:27" ht="13.2">
+    <row r="531" spans="1:27" ht="12.75">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="14"/>
@@ -18232,7 +18241,7 @@
       <c r="Z531" s="2"/>
       <c r="AA531" s="2"/>
     </row>
-    <row r="532" spans="1:27" ht="13.2">
+    <row r="532" spans="1:27" ht="12.75">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="14"/>
@@ -18261,7 +18270,7 @@
       <c r="Z532" s="2"/>
       <c r="AA532" s="2"/>
     </row>
-    <row r="533" spans="1:27" ht="13.2">
+    <row r="533" spans="1:27" ht="12.75">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="14"/>
@@ -18290,7 +18299,7 @@
       <c r="Z533" s="2"/>
       <c r="AA533" s="2"/>
     </row>
-    <row r="534" spans="1:27" ht="13.2">
+    <row r="534" spans="1:27" ht="12.75">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
       <c r="C534" s="14"/>
@@ -18319,7 +18328,7 @@
       <c r="Z534" s="2"/>
       <c r="AA534" s="2"/>
     </row>
-    <row r="535" spans="1:27" ht="13.2">
+    <row r="535" spans="1:27" ht="12.75">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="14"/>
@@ -18348,7 +18357,7 @@
       <c r="Z535" s="2"/>
       <c r="AA535" s="2"/>
     </row>
-    <row r="536" spans="1:27" ht="13.2">
+    <row r="536" spans="1:27" ht="12.75">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="14"/>
@@ -18377,7 +18386,7 @@
       <c r="Z536" s="2"/>
       <c r="AA536" s="2"/>
     </row>
-    <row r="537" spans="1:27" ht="13.2">
+    <row r="537" spans="1:27" ht="12.75">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="14"/>
@@ -18406,7 +18415,7 @@
       <c r="Z537" s="2"/>
       <c r="AA537" s="2"/>
     </row>
-    <row r="538" spans="1:27" ht="13.2">
+    <row r="538" spans="1:27" ht="12.75">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="14"/>
@@ -18435,7 +18444,7 @@
       <c r="Z538" s="2"/>
       <c r="AA538" s="2"/>
     </row>
-    <row r="539" spans="1:27" ht="13.2">
+    <row r="539" spans="1:27" ht="12.75">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="14"/>
@@ -18464,7 +18473,7 @@
       <c r="Z539" s="2"/>
       <c r="AA539" s="2"/>
     </row>
-    <row r="540" spans="1:27" ht="13.2">
+    <row r="540" spans="1:27" ht="12.75">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
       <c r="C540" s="14"/>
@@ -18493,7 +18502,7 @@
       <c r="Z540" s="2"/>
       <c r="AA540" s="2"/>
     </row>
-    <row r="541" spans="1:27" ht="13.2">
+    <row r="541" spans="1:27" ht="12.75">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
       <c r="C541" s="14"/>
@@ -18522,7 +18531,7 @@
       <c r="Z541" s="2"/>
       <c r="AA541" s="2"/>
     </row>
-    <row r="542" spans="1:27" ht="13.2">
+    <row r="542" spans="1:27" ht="12.75">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
       <c r="C542" s="14"/>
@@ -18551,7 +18560,7 @@
       <c r="Z542" s="2"/>
       <c r="AA542" s="2"/>
     </row>
-    <row r="543" spans="1:27" ht="13.2">
+    <row r="543" spans="1:27" ht="12.75">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="14"/>
@@ -18580,7 +18589,7 @@
       <c r="Z543" s="2"/>
       <c r="AA543" s="2"/>
     </row>
-    <row r="544" spans="1:27" ht="13.2">
+    <row r="544" spans="1:27" ht="12.75">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="14"/>
@@ -18609,7 +18618,7 @@
       <c r="Z544" s="2"/>
       <c r="AA544" s="2"/>
     </row>
-    <row r="545" spans="1:27" ht="13.2">
+    <row r="545" spans="1:27" ht="12.75">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="14"/>
@@ -18638,7 +18647,7 @@
       <c r="Z545" s="2"/>
       <c r="AA545" s="2"/>
     </row>
-    <row r="546" spans="1:27" ht="13.2">
+    <row r="546" spans="1:27" ht="12.75">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="14"/>
@@ -18667,7 +18676,7 @@
       <c r="Z546" s="2"/>
       <c r="AA546" s="2"/>
     </row>
-    <row r="547" spans="1:27" ht="13.2">
+    <row r="547" spans="1:27" ht="12.75">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
       <c r="C547" s="14"/>
@@ -18696,7 +18705,7 @@
       <c r="Z547" s="2"/>
       <c r="AA547" s="2"/>
     </row>
-    <row r="548" spans="1:27" ht="13.2">
+    <row r="548" spans="1:27" ht="12.75">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="14"/>
@@ -18725,7 +18734,7 @@
       <c r="Z548" s="2"/>
       <c r="AA548" s="2"/>
     </row>
-    <row r="549" spans="1:27" ht="13.2">
+    <row r="549" spans="1:27" ht="12.75">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
       <c r="C549" s="14"/>
@@ -18754,7 +18763,7 @@
       <c r="Z549" s="2"/>
       <c r="AA549" s="2"/>
     </row>
-    <row r="550" spans="1:27" ht="13.2">
+    <row r="550" spans="1:27" ht="12.75">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="14"/>
@@ -18783,7 +18792,7 @@
       <c r="Z550" s="2"/>
       <c r="AA550" s="2"/>
     </row>
-    <row r="551" spans="1:27" ht="13.2">
+    <row r="551" spans="1:27" ht="12.75">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
       <c r="C551" s="14"/>
@@ -18812,7 +18821,7 @@
       <c r="Z551" s="2"/>
       <c r="AA551" s="2"/>
     </row>
-    <row r="552" spans="1:27" ht="13.2">
+    <row r="552" spans="1:27" ht="12.75">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="14"/>
@@ -18841,7 +18850,7 @@
       <c r="Z552" s="2"/>
       <c r="AA552" s="2"/>
     </row>
-    <row r="553" spans="1:27" ht="13.2">
+    <row r="553" spans="1:27" ht="12.75">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="14"/>
@@ -18870,7 +18879,7 @@
       <c r="Z553" s="2"/>
       <c r="AA553" s="2"/>
     </row>
-    <row r="554" spans="1:27" ht="13.2">
+    <row r="554" spans="1:27" ht="12.75">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="14"/>
@@ -18899,7 +18908,7 @@
       <c r="Z554" s="2"/>
       <c r="AA554" s="2"/>
     </row>
-    <row r="555" spans="1:27" ht="13.2">
+    <row r="555" spans="1:27" ht="12.75">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
       <c r="C555" s="14"/>
@@ -18928,7 +18937,7 @@
       <c r="Z555" s="2"/>
       <c r="AA555" s="2"/>
     </row>
-    <row r="556" spans="1:27" ht="13.2">
+    <row r="556" spans="1:27" ht="12.75">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
       <c r="C556" s="14"/>
@@ -18957,7 +18966,7 @@
       <c r="Z556" s="2"/>
       <c r="AA556" s="2"/>
     </row>
-    <row r="557" spans="1:27" ht="13.2">
+    <row r="557" spans="1:27" ht="12.75">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="14"/>
@@ -18986,7 +18995,7 @@
       <c r="Z557" s="2"/>
       <c r="AA557" s="2"/>
     </row>
-    <row r="558" spans="1:27" ht="13.2">
+    <row r="558" spans="1:27" ht="12.75">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="14"/>
@@ -19015,7 +19024,7 @@
       <c r="Z558" s="2"/>
       <c r="AA558" s="2"/>
     </row>
-    <row r="559" spans="1:27" ht="13.2">
+    <row r="559" spans="1:27" ht="12.75">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
       <c r="C559" s="14"/>
@@ -19044,7 +19053,7 @@
       <c r="Z559" s="2"/>
       <c r="AA559" s="2"/>
     </row>
-    <row r="560" spans="1:27" ht="13.2">
+    <row r="560" spans="1:27" ht="12.75">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="14"/>
@@ -19073,7 +19082,7 @@
       <c r="Z560" s="2"/>
       <c r="AA560" s="2"/>
     </row>
-    <row r="561" spans="1:27" ht="13.2">
+    <row r="561" spans="1:27" ht="12.75">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="14"/>
@@ -19102,7 +19111,7 @@
       <c r="Z561" s="2"/>
       <c r="AA561" s="2"/>
     </row>
-    <row r="562" spans="1:27" ht="13.2">
+    <row r="562" spans="1:27" ht="12.75">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="14"/>
@@ -19131,7 +19140,7 @@
       <c r="Z562" s="2"/>
       <c r="AA562" s="2"/>
     </row>
-    <row r="563" spans="1:27" ht="13.2">
+    <row r="563" spans="1:27" ht="12.75">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="14"/>
@@ -19160,7 +19169,7 @@
       <c r="Z563" s="2"/>
       <c r="AA563" s="2"/>
     </row>
-    <row r="564" spans="1:27" ht="13.2">
+    <row r="564" spans="1:27" ht="12.75">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="14"/>
@@ -19189,7 +19198,7 @@
       <c r="Z564" s="2"/>
       <c r="AA564" s="2"/>
     </row>
-    <row r="565" spans="1:27" ht="13.2">
+    <row r="565" spans="1:27" ht="12.75">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
       <c r="C565" s="14"/>
@@ -19218,7 +19227,7 @@
       <c r="Z565" s="2"/>
       <c r="AA565" s="2"/>
     </row>
-    <row r="566" spans="1:27" ht="13.2">
+    <row r="566" spans="1:27" ht="12.75">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="14"/>
@@ -19247,7 +19256,7 @@
       <c r="Z566" s="2"/>
       <c r="AA566" s="2"/>
     </row>
-    <row r="567" spans="1:27" ht="13.2">
+    <row r="567" spans="1:27" ht="12.75">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="14"/>
@@ -19276,7 +19285,7 @@
       <c r="Z567" s="2"/>
       <c r="AA567" s="2"/>
     </row>
-    <row r="568" spans="1:27" ht="13.2">
+    <row r="568" spans="1:27" ht="12.75">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
       <c r="C568" s="14"/>
@@ -19305,7 +19314,7 @@
       <c r="Z568" s="2"/>
       <c r="AA568" s="2"/>
     </row>
-    <row r="569" spans="1:27" ht="13.2">
+    <row r="569" spans="1:27" ht="12.75">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="14"/>
@@ -19334,7 +19343,7 @@
       <c r="Z569" s="2"/>
       <c r="AA569" s="2"/>
     </row>
-    <row r="570" spans="1:27" ht="13.2">
+    <row r="570" spans="1:27" ht="12.75">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="14"/>
@@ -19363,7 +19372,7 @@
       <c r="Z570" s="2"/>
       <c r="AA570" s="2"/>
     </row>
-    <row r="571" spans="1:27" ht="13.2">
+    <row r="571" spans="1:27" ht="12.75">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="14"/>
@@ -19392,7 +19401,7 @@
       <c r="Z571" s="2"/>
       <c r="AA571" s="2"/>
     </row>
-    <row r="572" spans="1:27" ht="13.2">
+    <row r="572" spans="1:27" ht="12.75">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
       <c r="C572" s="14"/>
@@ -19421,7 +19430,7 @@
       <c r="Z572" s="2"/>
       <c r="AA572" s="2"/>
     </row>
-    <row r="573" spans="1:27" ht="13.2">
+    <row r="573" spans="1:27" ht="12.75">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="14"/>
@@ -19450,7 +19459,7 @@
       <c r="Z573" s="2"/>
       <c r="AA573" s="2"/>
     </row>
-    <row r="574" spans="1:27" ht="13.2">
+    <row r="574" spans="1:27" ht="12.75">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="14"/>
@@ -19479,7 +19488,7 @@
       <c r="Z574" s="2"/>
       <c r="AA574" s="2"/>
     </row>
-    <row r="575" spans="1:27" ht="13.2">
+    <row r="575" spans="1:27" ht="12.75">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="14"/>
@@ -19508,7 +19517,7 @@
       <c r="Z575" s="2"/>
       <c r="AA575" s="2"/>
     </row>
-    <row r="576" spans="1:27" ht="13.2">
+    <row r="576" spans="1:27" ht="12.75">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="14"/>
@@ -19537,7 +19546,7 @@
       <c r="Z576" s="2"/>
       <c r="AA576" s="2"/>
     </row>
-    <row r="577" spans="1:27" ht="13.2">
+    <row r="577" spans="1:27" ht="12.75">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="14"/>
@@ -19566,7 +19575,7 @@
       <c r="Z577" s="2"/>
       <c r="AA577" s="2"/>
     </row>
-    <row r="578" spans="1:27" ht="13.2">
+    <row r="578" spans="1:27" ht="12.75">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
       <c r="C578" s="14"/>
@@ -19595,7 +19604,7 @@
       <c r="Z578" s="2"/>
       <c r="AA578" s="2"/>
     </row>
-    <row r="579" spans="1:27" ht="13.2">
+    <row r="579" spans="1:27" ht="12.75">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
       <c r="C579" s="14"/>
@@ -19624,7 +19633,7 @@
       <c r="Z579" s="2"/>
       <c r="AA579" s="2"/>
     </row>
-    <row r="580" spans="1:27" ht="13.2">
+    <row r="580" spans="1:27" ht="12.75">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="14"/>
@@ -19653,7 +19662,7 @@
       <c r="Z580" s="2"/>
       <c r="AA580" s="2"/>
     </row>
-    <row r="581" spans="1:27" ht="13.2">
+    <row r="581" spans="1:27" ht="12.75">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="14"/>
@@ -19682,7 +19691,7 @@
       <c r="Z581" s="2"/>
       <c r="AA581" s="2"/>
     </row>
-    <row r="582" spans="1:27" ht="13.2">
+    <row r="582" spans="1:27" ht="12.75">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
       <c r="C582" s="14"/>
@@ -19711,7 +19720,7 @@
       <c r="Z582" s="2"/>
       <c r="AA582" s="2"/>
     </row>
-    <row r="583" spans="1:27" ht="13.2">
+    <row r="583" spans="1:27" ht="12.75">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="14"/>
@@ -19740,7 +19749,7 @@
       <c r="Z583" s="2"/>
       <c r="AA583" s="2"/>
     </row>
-    <row r="584" spans="1:27" ht="13.2">
+    <row r="584" spans="1:27" ht="12.75">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
       <c r="C584" s="14"/>
@@ -19769,7 +19778,7 @@
       <c r="Z584" s="2"/>
       <c r="AA584" s="2"/>
     </row>
-    <row r="585" spans="1:27" ht="13.2">
+    <row r="585" spans="1:27" ht="12.75">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="14"/>
@@ -19798,7 +19807,7 @@
       <c r="Z585" s="2"/>
       <c r="AA585" s="2"/>
     </row>
-    <row r="586" spans="1:27" ht="13.2">
+    <row r="586" spans="1:27" ht="12.75">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="14"/>
@@ -19827,7 +19836,7 @@
       <c r="Z586" s="2"/>
       <c r="AA586" s="2"/>
     </row>
-    <row r="587" spans="1:27" ht="13.2">
+    <row r="587" spans="1:27" ht="12.75">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="14"/>
@@ -19856,7 +19865,7 @@
       <c r="Z587" s="2"/>
       <c r="AA587" s="2"/>
     </row>
-    <row r="588" spans="1:27" ht="13.2">
+    <row r="588" spans="1:27" ht="12.75">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
       <c r="C588" s="14"/>
@@ -19885,7 +19894,7 @@
       <c r="Z588" s="2"/>
       <c r="AA588" s="2"/>
     </row>
-    <row r="589" spans="1:27" ht="13.2">
+    <row r="589" spans="1:27" ht="12.75">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="14"/>
@@ -19914,7 +19923,7 @@
       <c r="Z589" s="2"/>
       <c r="AA589" s="2"/>
     </row>
-    <row r="590" spans="1:27" ht="13.2">
+    <row r="590" spans="1:27" ht="12.75">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="14"/>
@@ -19943,7 +19952,7 @@
       <c r="Z590" s="2"/>
       <c r="AA590" s="2"/>
     </row>
-    <row r="591" spans="1:27" ht="13.2">
+    <row r="591" spans="1:27" ht="12.75">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="14"/>
@@ -19972,7 +19981,7 @@
       <c r="Z591" s="2"/>
       <c r="AA591" s="2"/>
     </row>
-    <row r="592" spans="1:27" ht="13.2">
+    <row r="592" spans="1:27" ht="12.75">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="14"/>
@@ -20001,7 +20010,7 @@
       <c r="Z592" s="2"/>
       <c r="AA592" s="2"/>
     </row>
-    <row r="593" spans="1:27" ht="13.2">
+    <row r="593" spans="1:27" ht="12.75">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
       <c r="C593" s="14"/>
@@ -20030,7 +20039,7 @@
       <c r="Z593" s="2"/>
       <c r="AA593" s="2"/>
     </row>
-    <row r="594" spans="1:27" ht="13.2">
+    <row r="594" spans="1:27" ht="12.75">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="14"/>
@@ -20059,7 +20068,7 @@
       <c r="Z594" s="2"/>
       <c r="AA594" s="2"/>
     </row>
-    <row r="595" spans="1:27" ht="13.2">
+    <row r="595" spans="1:27" ht="12.75">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="14"/>
@@ -20088,7 +20097,7 @@
       <c r="Z595" s="2"/>
       <c r="AA595" s="2"/>
     </row>
-    <row r="596" spans="1:27" ht="13.2">
+    <row r="596" spans="1:27" ht="12.75">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="14"/>
@@ -20117,7 +20126,7 @@
       <c r="Z596" s="2"/>
       <c r="AA596" s="2"/>
     </row>
-    <row r="597" spans="1:27" ht="13.2">
+    <row r="597" spans="1:27" ht="12.75">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="14"/>
@@ -20146,7 +20155,7 @@
       <c r="Z597" s="2"/>
       <c r="AA597" s="2"/>
     </row>
-    <row r="598" spans="1:27" ht="13.2">
+    <row r="598" spans="1:27" ht="12.75">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="14"/>
@@ -20175,7 +20184,7 @@
       <c r="Z598" s="2"/>
       <c r="AA598" s="2"/>
     </row>
-    <row r="599" spans="1:27" ht="13.2">
+    <row r="599" spans="1:27" ht="12.75">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
       <c r="C599" s="14"/>
@@ -20204,7 +20213,7 @@
       <c r="Z599" s="2"/>
       <c r="AA599" s="2"/>
     </row>
-    <row r="600" spans="1:27" ht="13.2">
+    <row r="600" spans="1:27" ht="12.75">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="14"/>
@@ -20233,7 +20242,7 @@
       <c r="Z600" s="2"/>
       <c r="AA600" s="2"/>
     </row>
-    <row r="601" spans="1:27" ht="13.2">
+    <row r="601" spans="1:27" ht="12.75">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="14"/>
@@ -20262,7 +20271,7 @@
       <c r="Z601" s="2"/>
       <c r="AA601" s="2"/>
     </row>
-    <row r="602" spans="1:27" ht="13.2">
+    <row r="602" spans="1:27" ht="12.75">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="14"/>
@@ -20291,7 +20300,7 @@
       <c r="Z602" s="2"/>
       <c r="AA602" s="2"/>
     </row>
-    <row r="603" spans="1:27" ht="13.2">
+    <row r="603" spans="1:27" ht="12.75">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="14"/>
@@ -20320,7 +20329,7 @@
       <c r="Z603" s="2"/>
       <c r="AA603" s="2"/>
     </row>
-    <row r="604" spans="1:27" ht="13.2">
+    <row r="604" spans="1:27" ht="12.75">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
       <c r="C604" s="14"/>
@@ -20349,7 +20358,7 @@
       <c r="Z604" s="2"/>
       <c r="AA604" s="2"/>
     </row>
-    <row r="605" spans="1:27" ht="13.2">
+    <row r="605" spans="1:27" ht="12.75">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
       <c r="C605" s="14"/>
@@ -20378,7 +20387,7 @@
       <c r="Z605" s="2"/>
       <c r="AA605" s="2"/>
     </row>
-    <row r="606" spans="1:27" ht="13.2">
+    <row r="606" spans="1:27" ht="12.75">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
       <c r="C606" s="14"/>
@@ -20407,7 +20416,7 @@
       <c r="Z606" s="2"/>
       <c r="AA606" s="2"/>
     </row>
-    <row r="607" spans="1:27" ht="13.2">
+    <row r="607" spans="1:27" ht="12.75">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
       <c r="C607" s="14"/>
@@ -20436,7 +20445,7 @@
       <c r="Z607" s="2"/>
       <c r="AA607" s="2"/>
     </row>
-    <row r="608" spans="1:27" ht="13.2">
+    <row r="608" spans="1:27" ht="12.75">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
       <c r="C608" s="14"/>
@@ -20465,7 +20474,7 @@
       <c r="Z608" s="2"/>
       <c r="AA608" s="2"/>
     </row>
-    <row r="609" spans="1:27" ht="13.2">
+    <row r="609" spans="1:27" ht="12.75">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
       <c r="C609" s="14"/>
@@ -20494,7 +20503,7 @@
       <c r="Z609" s="2"/>
       <c r="AA609" s="2"/>
     </row>
-    <row r="610" spans="1:27" ht="13.2">
+    <row r="610" spans="1:27" ht="12.75">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
       <c r="C610" s="14"/>
@@ -20523,7 +20532,7 @@
       <c r="Z610" s="2"/>
       <c r="AA610" s="2"/>
     </row>
-    <row r="611" spans="1:27" ht="13.2">
+    <row r="611" spans="1:27" ht="12.75">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
       <c r="C611" s="14"/>
@@ -20552,7 +20561,7 @@
       <c r="Z611" s="2"/>
       <c r="AA611" s="2"/>
     </row>
-    <row r="612" spans="1:27" ht="13.2">
+    <row r="612" spans="1:27" ht="12.75">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
       <c r="C612" s="14"/>
@@ -20581,7 +20590,7 @@
       <c r="Z612" s="2"/>
       <c r="AA612" s="2"/>
     </row>
-    <row r="613" spans="1:27" ht="13.2">
+    <row r="613" spans="1:27" ht="12.75">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
       <c r="C613" s="14"/>
@@ -20610,7 +20619,7 @@
       <c r="Z613" s="2"/>
       <c r="AA613" s="2"/>
     </row>
-    <row r="614" spans="1:27" ht="13.2">
+    <row r="614" spans="1:27" ht="12.75">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
       <c r="C614" s="14"/>
@@ -20639,7 +20648,7 @@
       <c r="Z614" s="2"/>
       <c r="AA614" s="2"/>
     </row>
-    <row r="615" spans="1:27" ht="13.2">
+    <row r="615" spans="1:27" ht="12.75">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
       <c r="C615" s="14"/>
@@ -20668,7 +20677,7 @@
       <c r="Z615" s="2"/>
       <c r="AA615" s="2"/>
     </row>
-    <row r="616" spans="1:27" ht="13.2">
+    <row r="616" spans="1:27" ht="12.75">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
       <c r="C616" s="14"/>
@@ -20697,7 +20706,7 @@
       <c r="Z616" s="2"/>
       <c r="AA616" s="2"/>
     </row>
-    <row r="617" spans="1:27" ht="13.2">
+    <row r="617" spans="1:27" ht="12.75">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
       <c r="C617" s="14"/>
@@ -20726,7 +20735,7 @@
       <c r="Z617" s="2"/>
       <c r="AA617" s="2"/>
     </row>
-    <row r="618" spans="1:27" ht="13.2">
+    <row r="618" spans="1:27" ht="12.75">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
       <c r="C618" s="14"/>
@@ -20755,7 +20764,7 @@
       <c r="Z618" s="2"/>
       <c r="AA618" s="2"/>
     </row>
-    <row r="619" spans="1:27" ht="13.2">
+    <row r="619" spans="1:27" ht="12.75">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
       <c r="C619" s="14"/>
@@ -20784,7 +20793,7 @@
       <c r="Z619" s="2"/>
       <c r="AA619" s="2"/>
     </row>
-    <row r="620" spans="1:27" ht="13.2">
+    <row r="620" spans="1:27" ht="12.75">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
       <c r="C620" s="14"/>
@@ -20813,7 +20822,7 @@
       <c r="Z620" s="2"/>
       <c r="AA620" s="2"/>
     </row>
-    <row r="621" spans="1:27" ht="13.2">
+    <row r="621" spans="1:27" ht="12.75">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
       <c r="C621" s="14"/>
@@ -20842,7 +20851,7 @@
       <c r="Z621" s="2"/>
       <c r="AA621" s="2"/>
     </row>
-    <row r="622" spans="1:27" ht="13.2">
+    <row r="622" spans="1:27" ht="12.75">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
       <c r="C622" s="14"/>
@@ -20871,7 +20880,7 @@
       <c r="Z622" s="2"/>
       <c r="AA622" s="2"/>
     </row>
-    <row r="623" spans="1:27" ht="13.2">
+    <row r="623" spans="1:27" ht="12.75">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
       <c r="C623" s="14"/>
@@ -20900,7 +20909,7 @@
       <c r="Z623" s="2"/>
       <c r="AA623" s="2"/>
     </row>
-    <row r="624" spans="1:27" ht="13.2">
+    <row r="624" spans="1:27" ht="12.75">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
       <c r="C624" s="14"/>
@@ -20929,7 +20938,7 @@
       <c r="Z624" s="2"/>
       <c r="AA624" s="2"/>
     </row>
-    <row r="625" spans="1:27" ht="13.2">
+    <row r="625" spans="1:27" ht="12.75">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
       <c r="C625" s="14"/>
@@ -20958,7 +20967,7 @@
       <c r="Z625" s="2"/>
       <c r="AA625" s="2"/>
     </row>
-    <row r="626" spans="1:27" ht="13.2">
+    <row r="626" spans="1:27" ht="12.75">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
       <c r="C626" s="14"/>
@@ -20987,7 +20996,7 @@
       <c r="Z626" s="2"/>
       <c r="AA626" s="2"/>
     </row>
-    <row r="627" spans="1:27" ht="13.2">
+    <row r="627" spans="1:27" ht="12.75">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
       <c r="C627" s="14"/>
@@ -21016,7 +21025,7 @@
       <c r="Z627" s="2"/>
       <c r="AA627" s="2"/>
     </row>
-    <row r="628" spans="1:27" ht="13.2">
+    <row r="628" spans="1:27" ht="12.75">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
       <c r="C628" s="14"/>
@@ -21045,7 +21054,7 @@
       <c r="Z628" s="2"/>
       <c r="AA628" s="2"/>
     </row>
-    <row r="629" spans="1:27" ht="13.2">
+    <row r="629" spans="1:27" ht="12.75">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
       <c r="C629" s="14"/>
@@ -21074,7 +21083,7 @@
       <c r="Z629" s="2"/>
       <c r="AA629" s="2"/>
     </row>
-    <row r="630" spans="1:27" ht="13.2">
+    <row r="630" spans="1:27" ht="12.75">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
       <c r="C630" s="14"/>
@@ -21103,7 +21112,7 @@
       <c r="Z630" s="2"/>
       <c r="AA630" s="2"/>
     </row>
-    <row r="631" spans="1:27" ht="13.2">
+    <row r="631" spans="1:27" ht="12.75">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
       <c r="C631" s="14"/>
@@ -21132,7 +21141,7 @@
       <c r="Z631" s="2"/>
       <c r="AA631" s="2"/>
     </row>
-    <row r="632" spans="1:27" ht="13.2">
+    <row r="632" spans="1:27" ht="12.75">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
       <c r="C632" s="14"/>
@@ -21161,7 +21170,7 @@
       <c r="Z632" s="2"/>
       <c r="AA632" s="2"/>
     </row>
-    <row r="633" spans="1:27" ht="13.2">
+    <row r="633" spans="1:27" ht="12.75">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
       <c r="C633" s="14"/>
@@ -21190,7 +21199,7 @@
       <c r="Z633" s="2"/>
       <c r="AA633" s="2"/>
     </row>
-    <row r="634" spans="1:27" ht="13.2">
+    <row r="634" spans="1:27" ht="12.75">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
       <c r="C634" s="14"/>
@@ -21219,7 +21228,7 @@
       <c r="Z634" s="2"/>
       <c r="AA634" s="2"/>
     </row>
-    <row r="635" spans="1:27" ht="13.2">
+    <row r="635" spans="1:27" ht="12.75">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
       <c r="C635" s="14"/>
@@ -21248,7 +21257,7 @@
       <c r="Z635" s="2"/>
       <c r="AA635" s="2"/>
     </row>
-    <row r="636" spans="1:27" ht="13.2">
+    <row r="636" spans="1:27" ht="12.75">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
       <c r="C636" s="14"/>
@@ -21277,7 +21286,7 @@
       <c r="Z636" s="2"/>
       <c r="AA636" s="2"/>
     </row>
-    <row r="637" spans="1:27" ht="13.2">
+    <row r="637" spans="1:27" ht="12.75">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
       <c r="C637" s="14"/>
@@ -21306,7 +21315,7 @@
       <c r="Z637" s="2"/>
       <c r="AA637" s="2"/>
     </row>
-    <row r="638" spans="1:27" ht="13.2">
+    <row r="638" spans="1:27" ht="12.75">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
       <c r="C638" s="14"/>
@@ -21335,7 +21344,7 @@
       <c r="Z638" s="2"/>
       <c r="AA638" s="2"/>
     </row>
-    <row r="639" spans="1:27" ht="13.2">
+    <row r="639" spans="1:27" ht="12.75">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
       <c r="C639" s="14"/>
@@ -21364,7 +21373,7 @@
       <c r="Z639" s="2"/>
       <c r="AA639" s="2"/>
     </row>
-    <row r="640" spans="1:27" ht="13.2">
+    <row r="640" spans="1:27" ht="12.75">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
       <c r="C640" s="14"/>
@@ -21393,7 +21402,7 @@
       <c r="Z640" s="2"/>
       <c r="AA640" s="2"/>
     </row>
-    <row r="641" spans="1:27" ht="13.2">
+    <row r="641" spans="1:27" ht="12.75">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
       <c r="C641" s="14"/>
@@ -21422,7 +21431,7 @@
       <c r="Z641" s="2"/>
       <c r="AA641" s="2"/>
     </row>
-    <row r="642" spans="1:27" ht="13.2">
+    <row r="642" spans="1:27" ht="12.75">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
       <c r="C642" s="14"/>
@@ -21451,7 +21460,7 @@
       <c r="Z642" s="2"/>
       <c r="AA642" s="2"/>
     </row>
-    <row r="643" spans="1:27" ht="13.2">
+    <row r="643" spans="1:27" ht="12.75">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
       <c r="C643" s="14"/>
@@ -21480,7 +21489,7 @@
       <c r="Z643" s="2"/>
       <c r="AA643" s="2"/>
     </row>
-    <row r="644" spans="1:27" ht="13.2">
+    <row r="644" spans="1:27" ht="12.75">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
       <c r="C644" s="14"/>
@@ -21509,7 +21518,7 @@
       <c r="Z644" s="2"/>
       <c r="AA644" s="2"/>
     </row>
-    <row r="645" spans="1:27" ht="13.2">
+    <row r="645" spans="1:27" ht="12.75">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
       <c r="C645" s="14"/>
@@ -21538,7 +21547,7 @@
       <c r="Z645" s="2"/>
       <c r="AA645" s="2"/>
     </row>
-    <row r="646" spans="1:27" ht="13.2">
+    <row r="646" spans="1:27" ht="12.75">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
       <c r="C646" s="14"/>
@@ -21567,7 +21576,7 @@
       <c r="Z646" s="2"/>
       <c r="AA646" s="2"/>
     </row>
-    <row r="647" spans="1:27" ht="13.2">
+    <row r="647" spans="1:27" ht="12.75">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
       <c r="C647" s="14"/>
@@ -21596,7 +21605,7 @@
       <c r="Z647" s="2"/>
       <c r="AA647" s="2"/>
     </row>
-    <row r="648" spans="1:27" ht="13.2">
+    <row r="648" spans="1:27" ht="12.75">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
       <c r="C648" s="14"/>
@@ -21625,7 +21634,7 @@
       <c r="Z648" s="2"/>
       <c r="AA648" s="2"/>
     </row>
-    <row r="649" spans="1:27" ht="13.2">
+    <row r="649" spans="1:27" ht="12.75">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
       <c r="C649" s="14"/>
@@ -21654,7 +21663,7 @@
       <c r="Z649" s="2"/>
       <c r="AA649" s="2"/>
     </row>
-    <row r="650" spans="1:27" ht="13.2">
+    <row r="650" spans="1:27" ht="12.75">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
       <c r="C650" s="14"/>
@@ -21683,7 +21692,7 @@
       <c r="Z650" s="2"/>
       <c r="AA650" s="2"/>
     </row>
-    <row r="651" spans="1:27" ht="13.2">
+    <row r="651" spans="1:27" ht="12.75">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
       <c r="C651" s="14"/>
@@ -21712,7 +21721,7 @@
       <c r="Z651" s="2"/>
       <c r="AA651" s="2"/>
     </row>
-    <row r="652" spans="1:27" ht="13.2">
+    <row r="652" spans="1:27" ht="12.75">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
       <c r="C652" s="14"/>
@@ -21741,7 +21750,7 @@
       <c r="Z652" s="2"/>
       <c r="AA652" s="2"/>
     </row>
-    <row r="653" spans="1:27" ht="13.2">
+    <row r="653" spans="1:27" ht="12.75">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
       <c r="C653" s="14"/>
@@ -21770,7 +21779,7 @@
       <c r="Z653" s="2"/>
       <c r="AA653" s="2"/>
     </row>
-    <row r="654" spans="1:27" ht="13.2">
+    <row r="654" spans="1:27" ht="12.75">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
       <c r="C654" s="14"/>
@@ -21799,7 +21808,7 @@
       <c r="Z654" s="2"/>
       <c r="AA654" s="2"/>
     </row>
-    <row r="655" spans="1:27" ht="13.2">
+    <row r="655" spans="1:27" ht="12.75">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
       <c r="C655" s="14"/>
@@ -21828,7 +21837,7 @@
       <c r="Z655" s="2"/>
       <c r="AA655" s="2"/>
     </row>
-    <row r="656" spans="1:27" ht="13.2">
+    <row r="656" spans="1:27" ht="12.75">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
       <c r="C656" s="14"/>
@@ -21857,7 +21866,7 @@
       <c r="Z656" s="2"/>
       <c r="AA656" s="2"/>
     </row>
-    <row r="657" spans="1:27" ht="13.2">
+    <row r="657" spans="1:27" ht="12.75">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
       <c r="C657" s="14"/>
@@ -21886,7 +21895,7 @@
       <c r="Z657" s="2"/>
       <c r="AA657" s="2"/>
     </row>
-    <row r="658" spans="1:27" ht="13.2">
+    <row r="658" spans="1:27" ht="12.75">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
       <c r="C658" s="14"/>
@@ -21915,7 +21924,7 @@
       <c r="Z658" s="2"/>
       <c r="AA658" s="2"/>
     </row>
-    <row r="659" spans="1:27" ht="13.2">
+    <row r="659" spans="1:27" ht="12.75">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
       <c r="C659" s="14"/>
@@ -21944,7 +21953,7 @@
       <c r="Z659" s="2"/>
       <c r="AA659" s="2"/>
     </row>
-    <row r="660" spans="1:27" ht="13.2">
+    <row r="660" spans="1:27" ht="12.75">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
       <c r="C660" s="14"/>
@@ -21973,7 +21982,7 @@
       <c r="Z660" s="2"/>
       <c r="AA660" s="2"/>
     </row>
-    <row r="661" spans="1:27" ht="13.2">
+    <row r="661" spans="1:27" ht="12.75">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
       <c r="C661" s="14"/>
@@ -22002,7 +22011,7 @@
       <c r="Z661" s="2"/>
       <c r="AA661" s="2"/>
     </row>
-    <row r="662" spans="1:27" ht="13.2">
+    <row r="662" spans="1:27" ht="12.75">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
       <c r="C662" s="14"/>
@@ -22031,7 +22040,7 @@
       <c r="Z662" s="2"/>
       <c r="AA662" s="2"/>
     </row>
-    <row r="663" spans="1:27" ht="13.2">
+    <row r="663" spans="1:27" ht="12.75">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
       <c r="C663" s="14"/>
@@ -22060,7 +22069,7 @@
       <c r="Z663" s="2"/>
       <c r="AA663" s="2"/>
     </row>
-    <row r="664" spans="1:27" ht="13.2">
+    <row r="664" spans="1:27" ht="12.75">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
       <c r="C664" s="14"/>
@@ -22089,7 +22098,7 @@
       <c r="Z664" s="2"/>
       <c r="AA664" s="2"/>
     </row>
-    <row r="665" spans="1:27" ht="13.2">
+    <row r="665" spans="1:27" ht="12.75">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
       <c r="C665" s="14"/>
@@ -22118,7 +22127,7 @@
       <c r="Z665" s="2"/>
       <c r="AA665" s="2"/>
     </row>
-    <row r="666" spans="1:27" ht="13.2">
+    <row r="666" spans="1:27" ht="12.75">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
       <c r="C666" s="14"/>
@@ -22147,7 +22156,7 @@
       <c r="Z666" s="2"/>
       <c r="AA666" s="2"/>
     </row>
-    <row r="667" spans="1:27" ht="13.2">
+    <row r="667" spans="1:27" ht="12.75">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
       <c r="C667" s="14"/>
@@ -22176,7 +22185,7 @@
       <c r="Z667" s="2"/>
       <c r="AA667" s="2"/>
     </row>
-    <row r="668" spans="1:27" ht="13.2">
+    <row r="668" spans="1:27" ht="12.75">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
       <c r="C668" s="14"/>
@@ -22205,7 +22214,7 @@
       <c r="Z668" s="2"/>
       <c r="AA668" s="2"/>
     </row>
-    <row r="669" spans="1:27" ht="13.2">
+    <row r="669" spans="1:27" ht="12.75">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
       <c r="C669" s="14"/>
@@ -22234,7 +22243,7 @@
       <c r="Z669" s="2"/>
       <c r="AA669" s="2"/>
     </row>
-    <row r="670" spans="1:27" ht="13.2">
+    <row r="670" spans="1:27" ht="12.75">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
       <c r="C670" s="14"/>
@@ -22263,7 +22272,7 @@
       <c r="Z670" s="2"/>
       <c r="AA670" s="2"/>
     </row>
-    <row r="671" spans="1:27" ht="13.2">
+    <row r="671" spans="1:27" ht="12.75">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
       <c r="C671" s="14"/>
@@ -22292,7 +22301,7 @@
       <c r="Z671" s="2"/>
       <c r="AA671" s="2"/>
     </row>
-    <row r="672" spans="1:27" ht="13.2">
+    <row r="672" spans="1:27" ht="12.75">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
       <c r="C672" s="14"/>
@@ -22321,7 +22330,7 @@
       <c r="Z672" s="2"/>
       <c r="AA672" s="2"/>
     </row>
-    <row r="673" spans="1:27" ht="13.2">
+    <row r="673" spans="1:27" ht="12.75">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
       <c r="C673" s="14"/>
@@ -22350,7 +22359,7 @@
       <c r="Z673" s="2"/>
       <c r="AA673" s="2"/>
     </row>
-    <row r="674" spans="1:27" ht="13.2">
+    <row r="674" spans="1:27" ht="12.75">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
       <c r="C674" s="14"/>
@@ -22379,7 +22388,7 @@
       <c r="Z674" s="2"/>
       <c r="AA674" s="2"/>
     </row>
-    <row r="675" spans="1:27" ht="13.2">
+    <row r="675" spans="1:27" ht="12.75">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
       <c r="C675" s="14"/>
@@ -22408,7 +22417,7 @@
       <c r="Z675" s="2"/>
       <c r="AA675" s="2"/>
     </row>
-    <row r="676" spans="1:27" ht="13.2">
+    <row r="676" spans="1:27" ht="12.75">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
       <c r="C676" s="14"/>
@@ -22437,7 +22446,7 @@
       <c r="Z676" s="2"/>
       <c r="AA676" s="2"/>
     </row>
-    <row r="677" spans="1:27" ht="13.2">
+    <row r="677" spans="1:27" ht="12.75">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
       <c r="C677" s="14"/>
@@ -22466,7 +22475,7 @@
       <c r="Z677" s="2"/>
       <c r="AA677" s="2"/>
     </row>
-    <row r="678" spans="1:27" ht="13.2">
+    <row r="678" spans="1:27" ht="12.75">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
       <c r="C678" s="14"/>
@@ -22495,7 +22504,7 @@
       <c r="Z678" s="2"/>
       <c r="AA678" s="2"/>
     </row>
-    <row r="679" spans="1:27" ht="13.2">
+    <row r="679" spans="1:27" ht="12.75">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
       <c r="C679" s="14"/>
@@ -22524,7 +22533,7 @@
       <c r="Z679" s="2"/>
       <c r="AA679" s="2"/>
     </row>
-    <row r="680" spans="1:27" ht="13.2">
+    <row r="680" spans="1:27" ht="12.75">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
       <c r="C680" s="14"/>
@@ -22553,7 +22562,7 @@
       <c r="Z680" s="2"/>
       <c r="AA680" s="2"/>
     </row>
-    <row r="681" spans="1:27" ht="13.2">
+    <row r="681" spans="1:27" ht="12.75">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
       <c r="C681" s="14"/>
@@ -22582,7 +22591,7 @@
       <c r="Z681" s="2"/>
       <c r="AA681" s="2"/>
     </row>
-    <row r="682" spans="1:27" ht="13.2">
+    <row r="682" spans="1:27" ht="12.75">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
       <c r="C682" s="14"/>
@@ -22611,7 +22620,7 @@
       <c r="Z682" s="2"/>
       <c r="AA682" s="2"/>
     </row>
-    <row r="683" spans="1:27" ht="13.2">
+    <row r="683" spans="1:27" ht="12.75">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
       <c r="C683" s="14"/>
@@ -22640,7 +22649,7 @@
       <c r="Z683" s="2"/>
       <c r="AA683" s="2"/>
     </row>
-    <row r="684" spans="1:27" ht="13.2">
+    <row r="684" spans="1:27" ht="12.75">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
       <c r="C684" s="14"/>
@@ -22669,7 +22678,7 @@
       <c r="Z684" s="2"/>
       <c r="AA684" s="2"/>
     </row>
-    <row r="685" spans="1:27" ht="13.2">
+    <row r="685" spans="1:27" ht="12.75">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
       <c r="C685" s="14"/>
@@ -22698,7 +22707,7 @@
       <c r="Z685" s="2"/>
       <c r="AA685" s="2"/>
     </row>
-    <row r="686" spans="1:27" ht="13.2">
+    <row r="686" spans="1:27" ht="12.75">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
       <c r="C686" s="14"/>
@@ -22727,7 +22736,7 @@
       <c r="Z686" s="2"/>
       <c r="AA686" s="2"/>
     </row>
-    <row r="687" spans="1:27" ht="13.2">
+    <row r="687" spans="1:27" ht="12.75">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
       <c r="C687" s="14"/>
@@ -22756,7 +22765,7 @@
       <c r="Z687" s="2"/>
       <c r="AA687" s="2"/>
     </row>
-    <row r="688" spans="1:27" ht="13.2">
+    <row r="688" spans="1:27" ht="12.75">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
       <c r="C688" s="14"/>
@@ -22785,7 +22794,7 @@
       <c r="Z688" s="2"/>
       <c r="AA688" s="2"/>
     </row>
-    <row r="689" spans="1:27" ht="13.2">
+    <row r="689" spans="1:27" ht="12.75">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
       <c r="C689" s="14"/>
@@ -22814,7 +22823,7 @@
       <c r="Z689" s="2"/>
       <c r="AA689" s="2"/>
     </row>
-    <row r="690" spans="1:27" ht="13.2">
+    <row r="690" spans="1:27" ht="12.75">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
       <c r="C690" s="14"/>
@@ -22843,7 +22852,7 @@
       <c r="Z690" s="2"/>
       <c r="AA690" s="2"/>
     </row>
-    <row r="691" spans="1:27" ht="13.2">
+    <row r="691" spans="1:27" ht="12.75">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
       <c r="C691" s="14"/>
@@ -22872,7 +22881,7 @@
       <c r="Z691" s="2"/>
       <c r="AA691" s="2"/>
     </row>
-    <row r="692" spans="1:27" ht="13.2">
+    <row r="692" spans="1:27" ht="12.75">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
       <c r="C692" s="14"/>
@@ -22901,7 +22910,7 @@
       <c r="Z692" s="2"/>
       <c r="AA692" s="2"/>
     </row>
-    <row r="693" spans="1:27" ht="13.2">
+    <row r="693" spans="1:27" ht="12.75">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
       <c r="C693" s="14"/>
@@ -22930,7 +22939,7 @@
       <c r="Z693" s="2"/>
       <c r="AA693" s="2"/>
     </row>
-    <row r="694" spans="1:27" ht="13.2">
+    <row r="694" spans="1:27" ht="12.75">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
       <c r="C694" s="14"/>
@@ -22959,7 +22968,7 @@
       <c r="Z694" s="2"/>
       <c r="AA694" s="2"/>
     </row>
-    <row r="695" spans="1:27" ht="13.2">
+    <row r="695" spans="1:27" ht="12.75">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
       <c r="C695" s="14"/>
@@ -22988,7 +22997,7 @@
       <c r="Z695" s="2"/>
       <c r="AA695" s="2"/>
     </row>
-    <row r="696" spans="1:27" ht="13.2">
+    <row r="696" spans="1:27" ht="12.75">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
       <c r="C696" s="14"/>
@@ -23017,7 +23026,7 @@
       <c r="Z696" s="2"/>
       <c r="AA696" s="2"/>
     </row>
-    <row r="697" spans="1:27" ht="13.2">
+    <row r="697" spans="1:27" ht="12.75">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
       <c r="C697" s="14"/>
@@ -23046,7 +23055,7 @@
       <c r="Z697" s="2"/>
       <c r="AA697" s="2"/>
     </row>
-    <row r="698" spans="1:27" ht="13.2">
+    <row r="698" spans="1:27" ht="12.75">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
       <c r="C698" s="14"/>
@@ -23075,7 +23084,7 @@
       <c r="Z698" s="2"/>
       <c r="AA698" s="2"/>
     </row>
-    <row r="699" spans="1:27" ht="13.2">
+    <row r="699" spans="1:27" ht="12.75">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
       <c r="C699" s="14"/>
@@ -23104,7 +23113,7 @@
       <c r="Z699" s="2"/>
       <c r="AA699" s="2"/>
     </row>
-    <row r="700" spans="1:27" ht="13.2">
+    <row r="700" spans="1:27" ht="12.75">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
       <c r="C700" s="14"/>
@@ -23133,7 +23142,7 @@
       <c r="Z700" s="2"/>
       <c r="AA700" s="2"/>
     </row>
-    <row r="701" spans="1:27" ht="13.2">
+    <row r="701" spans="1:27" ht="12.75">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
       <c r="C701" s="14"/>
@@ -23162,7 +23171,7 @@
       <c r="Z701" s="2"/>
       <c r="AA701" s="2"/>
     </row>
-    <row r="702" spans="1:27" ht="13.2">
+    <row r="702" spans="1:27" ht="12.75">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
       <c r="C702" s="14"/>
@@ -23191,7 +23200,7 @@
       <c r="Z702" s="2"/>
       <c r="AA702" s="2"/>
     </row>
-    <row r="703" spans="1:27" ht="13.2">
+    <row r="703" spans="1:27" ht="12.75">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
       <c r="C703" s="14"/>
@@ -23220,7 +23229,7 @@
       <c r="Z703" s="2"/>
       <c r="AA703" s="2"/>
     </row>
-    <row r="704" spans="1:27" ht="13.2">
+    <row r="704" spans="1:27" ht="12.75">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
       <c r="C704" s="14"/>
@@ -23249,7 +23258,7 @@
       <c r="Z704" s="2"/>
       <c r="AA704" s="2"/>
     </row>
-    <row r="705" spans="1:27" ht="13.2">
+    <row r="705" spans="1:27" ht="12.75">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
       <c r="C705" s="14"/>
@@ -23278,7 +23287,7 @@
       <c r="Z705" s="2"/>
       <c r="AA705" s="2"/>
     </row>
-    <row r="706" spans="1:27" ht="13.2">
+    <row r="706" spans="1:27" ht="12.75">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
       <c r="C706" s="14"/>
@@ -23307,7 +23316,7 @@
       <c r="Z706" s="2"/>
       <c r="AA706" s="2"/>
     </row>
-    <row r="707" spans="1:27" ht="13.2">
+    <row r="707" spans="1:27" ht="12.75">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
       <c r="C707" s="14"/>
@@ -23336,7 +23345,7 @@
       <c r="Z707" s="2"/>
       <c r="AA707" s="2"/>
     </row>
-    <row r="708" spans="1:27" ht="13.2">
+    <row r="708" spans="1:27" ht="12.75">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
       <c r="C708" s="14"/>
@@ -23365,7 +23374,7 @@
       <c r="Z708" s="2"/>
       <c r="AA708" s="2"/>
     </row>
-    <row r="709" spans="1:27" ht="13.2">
+    <row r="709" spans="1:27" ht="12.75">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
       <c r="C709" s="14"/>
@@ -23394,7 +23403,7 @@
       <c r="Z709" s="2"/>
       <c r="AA709" s="2"/>
     </row>
-    <row r="710" spans="1:27" ht="13.2">
+    <row r="710" spans="1:27" ht="12.75">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
       <c r="C710" s="14"/>
@@ -23423,7 +23432,7 @@
       <c r="Z710" s="2"/>
       <c r="AA710" s="2"/>
     </row>
-    <row r="711" spans="1:27" ht="13.2">
+    <row r="711" spans="1:27" ht="12.75">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
       <c r="C711" s="14"/>
@@ -23452,7 +23461,7 @@
       <c r="Z711" s="2"/>
       <c r="AA711" s="2"/>
     </row>
-    <row r="712" spans="1:27" ht="13.2">
+    <row r="712" spans="1:27" ht="12.75">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
       <c r="C712" s="14"/>
@@ -23481,7 +23490,7 @@
       <c r="Z712" s="2"/>
       <c r="AA712" s="2"/>
     </row>
-    <row r="713" spans="1:27" ht="13.2">
+    <row r="713" spans="1:27" ht="12.75">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
       <c r="C713" s="14"/>
@@ -23510,7 +23519,7 @@
       <c r="Z713" s="2"/>
       <c r="AA713" s="2"/>
     </row>
-    <row r="714" spans="1:27" ht="13.2">
+    <row r="714" spans="1:27" ht="12.75">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
       <c r="C714" s="14"/>
@@ -23539,7 +23548,7 @@
       <c r="Z714" s="2"/>
       <c r="AA714" s="2"/>
     </row>
-    <row r="715" spans="1:27" ht="13.2">
+    <row r="715" spans="1:27" ht="12.75">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
       <c r="C715" s="14"/>
@@ -23568,7 +23577,7 @@
       <c r="Z715" s="2"/>
       <c r="AA715" s="2"/>
     </row>
-    <row r="716" spans="1:27" ht="13.2">
+    <row r="716" spans="1:27" ht="12.75">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
       <c r="C716" s="14"/>
@@ -23597,7 +23606,7 @@
       <c r="Z716" s="2"/>
       <c r="AA716" s="2"/>
     </row>
-    <row r="717" spans="1:27" ht="13.2">
+    <row r="717" spans="1:27" ht="12.75">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
       <c r="C717" s="14"/>
@@ -23626,7 +23635,7 @@
       <c r="Z717" s="2"/>
       <c r="AA717" s="2"/>
     </row>
-    <row r="718" spans="1:27" ht="13.2">
+    <row r="718" spans="1:27" ht="12.75">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
       <c r="C718" s="14"/>
@@ -23655,7 +23664,7 @@
       <c r="Z718" s="2"/>
       <c r="AA718" s="2"/>
     </row>
-    <row r="719" spans="1:27" ht="13.2">
+    <row r="719" spans="1:27" ht="12.75">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
       <c r="C719" s="14"/>
@@ -23684,7 +23693,7 @@
       <c r="Z719" s="2"/>
       <c r="AA719" s="2"/>
     </row>
-    <row r="720" spans="1:27" ht="13.2">
+    <row r="720" spans="1:27" ht="12.75">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
       <c r="C720" s="14"/>
@@ -23713,7 +23722,7 @@
       <c r="Z720" s="2"/>
       <c r="AA720" s="2"/>
     </row>
-    <row r="721" spans="1:27" ht="13.2">
+    <row r="721" spans="1:27" ht="12.75">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
       <c r="C721" s="14"/>
@@ -23742,7 +23751,7 @@
       <c r="Z721" s="2"/>
       <c r="AA721" s="2"/>
     </row>
-    <row r="722" spans="1:27" ht="13.2">
+    <row r="722" spans="1:27" ht="12.75">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
       <c r="C722" s="14"/>
@@ -23771,7 +23780,7 @@
       <c r="Z722" s="2"/>
       <c r="AA722" s="2"/>
     </row>
-    <row r="723" spans="1:27" ht="13.2">
+    <row r="723" spans="1:27" ht="12.75">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
       <c r="C723" s="14"/>
@@ -23800,7 +23809,7 @@
       <c r="Z723" s="2"/>
       <c r="AA723" s="2"/>
     </row>
-    <row r="724" spans="1:27" ht="13.2">
+    <row r="724" spans="1:27" ht="12.75">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
       <c r="C724" s="14"/>
@@ -23829,7 +23838,7 @@
       <c r="Z724" s="2"/>
       <c r="AA724" s="2"/>
     </row>
-    <row r="725" spans="1:27" ht="13.2">
+    <row r="725" spans="1:27" ht="12.75">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
       <c r="C725" s="14"/>
@@ -23858,7 +23867,7 @@
       <c r="Z725" s="2"/>
       <c r="AA725" s="2"/>
     </row>
-    <row r="726" spans="1:27" ht="13.2">
+    <row r="726" spans="1:27" ht="12.75">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
       <c r="C726" s="14"/>
@@ -23887,7 +23896,7 @@
       <c r="Z726" s="2"/>
       <c r="AA726" s="2"/>
     </row>
-    <row r="727" spans="1:27" ht="13.2">
+    <row r="727" spans="1:27" ht="12.75">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
       <c r="C727" s="14"/>
@@ -23916,7 +23925,7 @@
       <c r="Z727" s="2"/>
       <c r="AA727" s="2"/>
     </row>
-    <row r="728" spans="1:27" ht="13.2">
+    <row r="728" spans="1:27" ht="12.75">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
       <c r="C728" s="14"/>
@@ -23945,7 +23954,7 @@
       <c r="Z728" s="2"/>
       <c r="AA728" s="2"/>
     </row>
-    <row r="729" spans="1:27" ht="13.2">
+    <row r="729" spans="1:27" ht="12.75">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
       <c r="C729" s="14"/>
@@ -23974,7 +23983,7 @@
       <c r="Z729" s="2"/>
       <c r="AA729" s="2"/>
     </row>
-    <row r="730" spans="1:27" ht="13.2">
+    <row r="730" spans="1:27" ht="12.75">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
       <c r="C730" s="14"/>
@@ -24003,7 +24012,7 @@
       <c r="Z730" s="2"/>
       <c r="AA730" s="2"/>
     </row>
-    <row r="731" spans="1:27" ht="13.2">
+    <row r="731" spans="1:27" ht="12.75">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
       <c r="C731" s="14"/>
@@ -24032,7 +24041,7 @@
       <c r="Z731" s="2"/>
       <c r="AA731" s="2"/>
     </row>
-    <row r="732" spans="1:27" ht="13.2">
+    <row r="732" spans="1:27" ht="12.75">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
       <c r="C732" s="14"/>
@@ -24061,7 +24070,7 @@
       <c r="Z732" s="2"/>
       <c r="AA732" s="2"/>
     </row>
-    <row r="733" spans="1:27" ht="13.2">
+    <row r="733" spans="1:27" ht="12.75">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
       <c r="C733" s="14"/>
@@ -24090,7 +24099,7 @@
       <c r="Z733" s="2"/>
       <c r="AA733" s="2"/>
     </row>
-    <row r="734" spans="1:27" ht="13.2">
+    <row r="734" spans="1:27" ht="12.75">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
       <c r="C734" s="14"/>
@@ -24119,7 +24128,7 @@
       <c r="Z734" s="2"/>
       <c r="AA734" s="2"/>
     </row>
-    <row r="735" spans="1:27" ht="13.2">
+    <row r="735" spans="1:27" ht="12.75">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
       <c r="C735" s="14"/>
@@ -24148,7 +24157,7 @@
       <c r="Z735" s="2"/>
       <c r="AA735" s="2"/>
     </row>
-    <row r="736" spans="1:27" ht="13.2">
+    <row r="736" spans="1:27" ht="12.75">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
       <c r="C736" s="14"/>
@@ -24177,7 +24186,7 @@
       <c r="Z736" s="2"/>
       <c r="AA736" s="2"/>
     </row>
-    <row r="737" spans="1:27" ht="13.2">
+    <row r="737" spans="1:27" ht="12.75">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
       <c r="C737" s="14"/>
@@ -24206,7 +24215,7 @@
       <c r="Z737" s="2"/>
       <c r="AA737" s="2"/>
     </row>
-    <row r="738" spans="1:27" ht="13.2">
+    <row r="738" spans="1:27" ht="12.75">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
       <c r="C738" s="14"/>
@@ -24235,7 +24244,7 @@
       <c r="Z738" s="2"/>
       <c r="AA738" s="2"/>
     </row>
-    <row r="739" spans="1:27" ht="13.2">
+    <row r="739" spans="1:27" ht="12.75">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
       <c r="C739" s="14"/>
@@ -24264,7 +24273,7 @@
       <c r="Z739" s="2"/>
       <c r="AA739" s="2"/>
     </row>
-    <row r="740" spans="1:27" ht="13.2">
+    <row r="740" spans="1:27" ht="12.75">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
       <c r="C740" s="14"/>
@@ -24293,7 +24302,7 @@
       <c r="Z740" s="2"/>
       <c r="AA740" s="2"/>
     </row>
-    <row r="741" spans="1:27" ht="13.2">
+    <row r="741" spans="1:27" ht="12.75">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
       <c r="C741" s="14"/>
@@ -24322,7 +24331,7 @@
       <c r="Z741" s="2"/>
       <c r="AA741" s="2"/>
     </row>
-    <row r="742" spans="1:27" ht="13.2">
+    <row r="742" spans="1:27" ht="12.75">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
       <c r="C742" s="14"/>
@@ -24351,7 +24360,7 @@
       <c r="Z742" s="2"/>
       <c r="AA742" s="2"/>
     </row>
-    <row r="743" spans="1:27" ht="13.2">
+    <row r="743" spans="1:27" ht="12.75">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
       <c r="C743" s="14"/>
@@ -24380,7 +24389,7 @@
       <c r="Z743" s="2"/>
       <c r="AA743" s="2"/>
     </row>
-    <row r="744" spans="1:27" ht="13.2">
+    <row r="744" spans="1:27" ht="12.75">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
       <c r="C744" s="14"/>
@@ -24409,7 +24418,7 @@
       <c r="Z744" s="2"/>
       <c r="AA744" s="2"/>
     </row>
-    <row r="745" spans="1:27" ht="13.2">
+    <row r="745" spans="1:27" ht="12.75">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
       <c r="C745" s="14"/>
@@ -24438,7 +24447,7 @@
       <c r="Z745" s="2"/>
       <c r="AA745" s="2"/>
     </row>
-    <row r="746" spans="1:27" ht="13.2">
+    <row r="746" spans="1:27" ht="12.75">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
       <c r="C746" s="14"/>
@@ -24467,7 +24476,7 @@
       <c r="Z746" s="2"/>
       <c r="AA746" s="2"/>
     </row>
-    <row r="747" spans="1:27" ht="13.2">
+    <row r="747" spans="1:27" ht="12.75">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
       <c r="C747" s="14"/>
@@ -24496,7 +24505,7 @@
       <c r="Z747" s="2"/>
       <c r="AA747" s="2"/>
     </row>
-    <row r="748" spans="1:27" ht="13.2">
+    <row r="748" spans="1:27" ht="12.75">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
       <c r="C748" s="14"/>
@@ -24525,7 +24534,7 @@
       <c r="Z748" s="2"/>
       <c r="AA748" s="2"/>
     </row>
-    <row r="749" spans="1:27" ht="13.2">
+    <row r="749" spans="1:27" ht="12.75">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
       <c r="C749" s="14"/>
@@ -24554,7 +24563,7 @@
       <c r="Z749" s="2"/>
       <c r="AA749" s="2"/>
     </row>
-    <row r="750" spans="1:27" ht="13.2">
+    <row r="750" spans="1:27" ht="12.75">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
       <c r="C750" s="14"/>
@@ -24583,7 +24592,7 @@
       <c r="Z750" s="2"/>
       <c r="AA750" s="2"/>
     </row>
-    <row r="751" spans="1:27" ht="13.2">
+    <row r="751" spans="1:27" ht="12.75">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
       <c r="C751" s="14"/>
@@ -24612,7 +24621,7 @@
       <c r="Z751" s="2"/>
       <c r="AA751" s="2"/>
     </row>
-    <row r="752" spans="1:27" ht="13.2">
+    <row r="752" spans="1:27" ht="12.75">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
       <c r="C752" s="14"/>
@@ -24641,7 +24650,7 @@
       <c r="Z752" s="2"/>
       <c r="AA752" s="2"/>
     </row>
-    <row r="753" spans="1:27" ht="13.2">
+    <row r="753" spans="1:27" ht="12.75">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
       <c r="C753" s="14"/>
@@ -24670,7 +24679,7 @@
       <c r="Z753" s="2"/>
       <c r="AA753" s="2"/>
     </row>
-    <row r="754" spans="1:27" ht="13.2">
+    <row r="754" spans="1:27" ht="12.75">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
       <c r="C754" s="14"/>
@@ -24699,7 +24708,7 @@
       <c r="Z754" s="2"/>
       <c r="AA754" s="2"/>
     </row>
-    <row r="755" spans="1:27" ht="13.2">
+    <row r="755" spans="1:27" ht="12.75">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
       <c r="C755" s="14"/>
@@ -24728,7 +24737,7 @@
       <c r="Z755" s="2"/>
       <c r="AA755" s="2"/>
     </row>
-    <row r="756" spans="1:27" ht="13.2">
+    <row r="756" spans="1:27" ht="12.75">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
       <c r="C756" s="14"/>
@@ -24757,7 +24766,7 @@
       <c r="Z756" s="2"/>
       <c r="AA756" s="2"/>
     </row>
-    <row r="757" spans="1:27" ht="13.2">
+    <row r="757" spans="1:27" ht="12.75">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
       <c r="C757" s="14"/>
@@ -24786,7 +24795,7 @@
       <c r="Z757" s="2"/>
       <c r="AA757" s="2"/>
     </row>
-    <row r="758" spans="1:27" ht="13.2">
+    <row r="758" spans="1:27" ht="12.75">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
       <c r="C758" s="14"/>
@@ -24815,7 +24824,7 @@
       <c r="Z758" s="2"/>
       <c r="AA758" s="2"/>
     </row>
-    <row r="759" spans="1:27" ht="13.2">
+    <row r="759" spans="1:27" ht="12.75">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
       <c r="C759" s="14"/>
@@ -24844,7 +24853,7 @@
       <c r="Z759" s="2"/>
       <c r="AA759" s="2"/>
     </row>
-    <row r="760" spans="1:27" ht="13.2">
+    <row r="760" spans="1:27" ht="12.75">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
       <c r="C760" s="14"/>
@@ -24873,7 +24882,7 @@
       <c r="Z760" s="2"/>
       <c r="AA760" s="2"/>
     </row>
-    <row r="761" spans="1:27" ht="13.2">
+    <row r="761" spans="1:27" ht="12.75">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
       <c r="C761" s="14"/>
@@ -24902,7 +24911,7 @@
       <c r="Z761" s="2"/>
       <c r="AA761" s="2"/>
     </row>
-    <row r="762" spans="1:27" ht="13.2">
+    <row r="762" spans="1:27" ht="12.75">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
       <c r="C762" s="14"/>
@@ -24931,7 +24940,7 @@
       <c r="Z762" s="2"/>
       <c r="AA762" s="2"/>
     </row>
-    <row r="763" spans="1:27" ht="13.2">
+    <row r="763" spans="1:27" ht="12.75">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
       <c r="C763" s="14"/>
@@ -24960,7 +24969,7 @@
       <c r="Z763" s="2"/>
       <c r="AA763" s="2"/>
     </row>
-    <row r="764" spans="1:27" ht="13.2">
+    <row r="764" spans="1:27" ht="12.75">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
       <c r="C764" s="14"/>
@@ -24989,7 +24998,7 @@
       <c r="Z764" s="2"/>
       <c r="AA764" s="2"/>
     </row>
-    <row r="765" spans="1:27" ht="13.2">
+    <row r="765" spans="1:27" ht="12.75">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
       <c r="C765" s="14"/>
@@ -25018,7 +25027,7 @@
       <c r="Z765" s="2"/>
       <c r="AA765" s="2"/>
     </row>
-    <row r="766" spans="1:27" ht="13.2">
+    <row r="766" spans="1:27" ht="12.75">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
       <c r="C766" s="14"/>
@@ -25047,7 +25056,7 @@
       <c r="Z766" s="2"/>
       <c r="AA766" s="2"/>
     </row>
-    <row r="767" spans="1:27" ht="13.2">
+    <row r="767" spans="1:27" ht="12.75">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
       <c r="C767" s="14"/>
@@ -25076,7 +25085,7 @@
       <c r="Z767" s="2"/>
       <c r="AA767" s="2"/>
     </row>
-    <row r="768" spans="1:27" ht="13.2">
+    <row r="768" spans="1:27" ht="12.75">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
       <c r="C768" s="14"/>
@@ -25105,7 +25114,7 @@
       <c r="Z768" s="2"/>
       <c r="AA768" s="2"/>
     </row>
-    <row r="769" spans="1:27" ht="13.2">
+    <row r="769" spans="1:27" ht="12.75">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
       <c r="C769" s="14"/>
@@ -25134,7 +25143,7 @@
       <c r="Z769" s="2"/>
       <c r="AA769" s="2"/>
     </row>
-    <row r="770" spans="1:27" ht="13.2">
+    <row r="770" spans="1:27" ht="12.75">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
       <c r="C770" s="14"/>
@@ -25163,7 +25172,7 @@
       <c r="Z770" s="2"/>
       <c r="AA770" s="2"/>
     </row>
-    <row r="771" spans="1:27" ht="13.2">
+    <row r="771" spans="1:27" ht="12.75">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
       <c r="C771" s="14"/>
@@ -25192,7 +25201,7 @@
       <c r="Z771" s="2"/>
       <c r="AA771" s="2"/>
     </row>
-    <row r="772" spans="1:27" ht="13.2">
+    <row r="772" spans="1:27" ht="12.75">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
       <c r="C772" s="14"/>
@@ -25221,7 +25230,7 @@
       <c r="Z772" s="2"/>
       <c r="AA772" s="2"/>
     </row>
-    <row r="773" spans="1:27" ht="13.2">
+    <row r="773" spans="1:27" ht="12.75">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
       <c r="C773" s="14"/>
@@ -25250,7 +25259,7 @@
       <c r="Z773" s="2"/>
       <c r="AA773" s="2"/>
     </row>
-    <row r="774" spans="1:27" ht="13.2">
+    <row r="774" spans="1:27" ht="12.75">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
       <c r="C774" s="14"/>
@@ -25279,7 +25288,7 @@
       <c r="Z774" s="2"/>
       <c r="AA774" s="2"/>
     </row>
-    <row r="775" spans="1:27" ht="13.2">
+    <row r="775" spans="1:27" ht="12.75">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
       <c r="C775" s="14"/>
@@ -25308,7 +25317,7 @@
       <c r="Z775" s="2"/>
       <c r="AA775" s="2"/>
     </row>
-    <row r="776" spans="1:27" ht="13.2">
+    <row r="776" spans="1:27" ht="12.75">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
       <c r="C776" s="14"/>
@@ -25337,7 +25346,7 @@
       <c r="Z776" s="2"/>
       <c r="AA776" s="2"/>
     </row>
-    <row r="777" spans="1:27" ht="13.2">
+    <row r="777" spans="1:27" ht="12.75">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
       <c r="C777" s="14"/>
@@ -25366,7 +25375,7 @@
       <c r="Z777" s="2"/>
       <c r="AA777" s="2"/>
     </row>
-    <row r="778" spans="1:27" ht="13.2">
+    <row r="778" spans="1:27" ht="12.75">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
       <c r="C778" s="14"/>
@@ -25395,7 +25404,7 @@
       <c r="Z778" s="2"/>
       <c r="AA778" s="2"/>
     </row>
-    <row r="779" spans="1:27" ht="13.2">
+    <row r="779" spans="1:27" ht="12.75">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
       <c r="C779" s="14"/>
@@ -25424,7 +25433,7 @@
       <c r="Z779" s="2"/>
       <c r="AA779" s="2"/>
     </row>
-    <row r="780" spans="1:27" ht="13.2">
+    <row r="780" spans="1:27" ht="12.75">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
       <c r="C780" s="14"/>
@@ -25453,7 +25462,7 @@
       <c r="Z780" s="2"/>
       <c r="AA780" s="2"/>
     </row>
-    <row r="781" spans="1:27" ht="13.2">
+    <row r="781" spans="1:27" ht="12.75">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
       <c r="C781" s="14"/>
@@ -25482,7 +25491,7 @@
       <c r="Z781" s="2"/>
       <c r="AA781" s="2"/>
     </row>
-    <row r="782" spans="1:27" ht="13.2">
+    <row r="782" spans="1:27" ht="12.75">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
       <c r="C782" s="14"/>
@@ -25511,7 +25520,7 @@
       <c r="Z782" s="2"/>
       <c r="AA782" s="2"/>
     </row>
-    <row r="783" spans="1:27" ht="13.2">
+    <row r="783" spans="1:27" ht="12.75">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
       <c r="C783" s="14"/>
@@ -25540,7 +25549,7 @@
       <c r="Z783" s="2"/>
       <c r="AA783" s="2"/>
     </row>
-    <row r="784" spans="1:27" ht="13.2">
+    <row r="784" spans="1:27" ht="12.75">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
       <c r="C784" s="14"/>
@@ -25569,7 +25578,7 @@
       <c r="Z784" s="2"/>
       <c r="AA784" s="2"/>
     </row>
-    <row r="785" spans="1:27" ht="13.2">
+    <row r="785" spans="1:27" ht="12.75">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
       <c r="C785" s="14"/>
@@ -25598,7 +25607,7 @@
       <c r="Z785" s="2"/>
       <c r="AA785" s="2"/>
     </row>
-    <row r="786" spans="1:27" ht="13.2">
+    <row r="786" spans="1:27" ht="12.75">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
       <c r="C786" s="14"/>
@@ -25627,7 +25636,7 @@
       <c r="Z786" s="2"/>
       <c r="AA786" s="2"/>
     </row>
-    <row r="787" spans="1:27" ht="13.2">
+    <row r="787" spans="1:27" ht="12.75">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
       <c r="C787" s="14"/>
@@ -25656,7 +25665,7 @@
       <c r="Z787" s="2"/>
       <c r="AA787" s="2"/>
     </row>
-    <row r="788" spans="1:27" ht="13.2">
+    <row r="788" spans="1:27" ht="12.75">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
       <c r="C788" s="14"/>
@@ -25685,7 +25694,7 @@
       <c r="Z788" s="2"/>
       <c r="AA788" s="2"/>
     </row>
-    <row r="789" spans="1:27" ht="13.2">
+    <row r="789" spans="1:27" ht="12.75">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
       <c r="C789" s="14"/>
@@ -25714,7 +25723,7 @@
       <c r="Z789" s="2"/>
       <c r="AA789" s="2"/>
     </row>
-    <row r="790" spans="1:27" ht="13.2">
+    <row r="790" spans="1:27" ht="12.75">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
       <c r="C790" s="14"/>
@@ -25743,7 +25752,7 @@
       <c r="Z790" s="2"/>
       <c r="AA790" s="2"/>
     </row>
-    <row r="791" spans="1:27" ht="13.2">
+    <row r="791" spans="1:27" ht="12.75">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
       <c r="C791" s="14"/>
@@ -25772,7 +25781,7 @@
       <c r="Z791" s="2"/>
       <c r="AA791" s="2"/>
     </row>
-    <row r="792" spans="1:27" ht="13.2">
+    <row r="792" spans="1:27" ht="12.75">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
       <c r="C792" s="14"/>
@@ -25801,7 +25810,7 @@
       <c r="Z792" s="2"/>
       <c r="AA792" s="2"/>
     </row>
-    <row r="793" spans="1:27" ht="13.2">
+    <row r="793" spans="1:27" ht="12.75">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
       <c r="C793" s="14"/>
@@ -25830,7 +25839,7 @@
       <c r="Z793" s="2"/>
       <c r="AA793" s="2"/>
     </row>
-    <row r="794" spans="1:27" ht="13.2">
+    <row r="794" spans="1:27" ht="12.75">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
       <c r="C794" s="14"/>
@@ -25859,7 +25868,7 @@
       <c r="Z794" s="2"/>
       <c r="AA794" s="2"/>
     </row>
-    <row r="795" spans="1:27" ht="13.2">
+    <row r="795" spans="1:27" ht="12.75">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
       <c r="C795" s="14"/>
@@ -25888,7 +25897,7 @@
       <c r="Z795" s="2"/>
       <c r="AA795" s="2"/>
     </row>
-    <row r="796" spans="1:27" ht="13.2">
+    <row r="796" spans="1:27" ht="12.75">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
       <c r="C796" s="14"/>
@@ -25917,7 +25926,7 @@
       <c r="Z796" s="2"/>
       <c r="AA796" s="2"/>
     </row>
-    <row r="797" spans="1:27" ht="13.2">
+    <row r="797" spans="1:27" ht="12.75">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
       <c r="C797" s="14"/>
@@ -25946,7 +25955,7 @@
       <c r="Z797" s="2"/>
       <c r="AA797" s="2"/>
     </row>
-    <row r="798" spans="1:27" ht="13.2">
+    <row r="798" spans="1:27" ht="12.75">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
       <c r="C798" s="14"/>
@@ -25975,7 +25984,7 @@
       <c r="Z798" s="2"/>
       <c r="AA798" s="2"/>
     </row>
-    <row r="799" spans="1:27" ht="13.2">
+    <row r="799" spans="1:27" ht="12.75">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
       <c r="C799" s="14"/>
@@ -26004,7 +26013,7 @@
       <c r="Z799" s="2"/>
       <c r="AA799" s="2"/>
     </row>
-    <row r="800" spans="1:27" ht="13.2">
+    <row r="800" spans="1:27" ht="12.75">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
       <c r="C800" s="14"/>
@@ -26033,7 +26042,7 @@
       <c r="Z800" s="2"/>
       <c r="AA800" s="2"/>
     </row>
-    <row r="801" spans="1:27" ht="13.2">
+    <row r="801" spans="1:27" ht="12.75">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
       <c r="C801" s="14"/>
@@ -26062,7 +26071,7 @@
       <c r="Z801" s="2"/>
       <c r="AA801" s="2"/>
     </row>
-    <row r="802" spans="1:27" ht="13.2">
+    <row r="802" spans="1:27" ht="12.75">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
       <c r="C802" s="14"/>
@@ -26091,7 +26100,7 @@
       <c r="Z802" s="2"/>
       <c r="AA802" s="2"/>
     </row>
-    <row r="803" spans="1:27" ht="13.2">
+    <row r="803" spans="1:27" ht="12.75">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
       <c r="C803" s="14"/>
@@ -26120,7 +26129,7 @@
       <c r="Z803" s="2"/>
       <c r="AA803" s="2"/>
     </row>
-    <row r="804" spans="1:27" ht="13.2">
+    <row r="804" spans="1:27" ht="12.75">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
       <c r="C804" s="14"/>
@@ -26149,7 +26158,7 @@
       <c r="Z804" s="2"/>
       <c r="AA804" s="2"/>
     </row>
-    <row r="805" spans="1:27" ht="13.2">
+    <row r="805" spans="1:27" ht="12.75">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
       <c r="C805" s="14"/>
@@ -26178,7 +26187,7 @@
       <c r="Z805" s="2"/>
       <c r="AA805" s="2"/>
     </row>
-    <row r="806" spans="1:27" ht="13.2">
+    <row r="806" spans="1:27" ht="12.75">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
       <c r="C806" s="14"/>
@@ -26207,7 +26216,7 @@
       <c r="Z806" s="2"/>
       <c r="AA806" s="2"/>
     </row>
-    <row r="807" spans="1:27" ht="13.2">
+    <row r="807" spans="1:27" ht="12.75">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
       <c r="C807" s="14"/>
@@ -26236,7 +26245,7 @@
       <c r="Z807" s="2"/>
       <c r="AA807" s="2"/>
     </row>
-    <row r="808" spans="1:27" ht="13.2">
+    <row r="808" spans="1:27" ht="12.75">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
       <c r="C808" s="14"/>
@@ -26265,7 +26274,7 @@
       <c r="Z808" s="2"/>
       <c r="AA808" s="2"/>
     </row>
-    <row r="809" spans="1:27" ht="13.2">
+    <row r="809" spans="1:27" ht="12.75">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
       <c r="C809" s="14"/>
@@ -26294,7 +26303,7 @@
       <c r="Z809" s="2"/>
       <c r="AA809" s="2"/>
     </row>
-    <row r="810" spans="1:27" ht="13.2">
+    <row r="810" spans="1:27" ht="12.75">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
       <c r="C810" s="14"/>
@@ -26323,7 +26332,7 @@
       <c r="Z810" s="2"/>
       <c r="AA810" s="2"/>
     </row>
-    <row r="811" spans="1:27" ht="13.2">
+    <row r="811" spans="1:27" ht="12.75">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
       <c r="C811" s="14"/>
@@ -26352,7 +26361,7 @@
       <c r="Z811" s="2"/>
       <c r="AA811" s="2"/>
     </row>
-    <row r="812" spans="1:27" ht="13.2">
+    <row r="812" spans="1:27" ht="12.75">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
       <c r="C812" s="14"/>
@@ -26381,7 +26390,7 @@
       <c r="Z812" s="2"/>
       <c r="AA812" s="2"/>
     </row>
-    <row r="813" spans="1:27" ht="13.2">
+    <row r="813" spans="1:27" ht="12.75">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
       <c r="C813" s="14"/>
@@ -26410,7 +26419,7 @@
       <c r="Z813" s="2"/>
       <c r="AA813" s="2"/>
     </row>
-    <row r="814" spans="1:27" ht="13.2">
+    <row r="814" spans="1:27" ht="12.75">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
       <c r="C814" s="14"/>
@@ -26439,7 +26448,7 @@
       <c r="Z814" s="2"/>
       <c r="AA814" s="2"/>
     </row>
-    <row r="815" spans="1:27" ht="13.2">
+    <row r="815" spans="1:27" ht="12.75">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
       <c r="C815" s="14"/>
@@ -26468,7 +26477,7 @@
       <c r="Z815" s="2"/>
       <c r="AA815" s="2"/>
     </row>
-    <row r="816" spans="1:27" ht="13.2">
+    <row r="816" spans="1:27" ht="12.75">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
       <c r="C816" s="14"/>
@@ -26497,7 +26506,7 @@
       <c r="Z816" s="2"/>
       <c r="AA816" s="2"/>
     </row>
-    <row r="817" spans="1:27" ht="13.2">
+    <row r="817" spans="1:27" ht="12.75">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
       <c r="C817" s="14"/>
@@ -26526,7 +26535,7 @@
       <c r="Z817" s="2"/>
       <c r="AA817" s="2"/>
     </row>
-    <row r="818" spans="1:27" ht="13.2">
+    <row r="818" spans="1:27" ht="12.75">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
       <c r="C818" s="14"/>
@@ -26555,7 +26564,7 @@
       <c r="Z818" s="2"/>
       <c r="AA818" s="2"/>
     </row>
-    <row r="819" spans="1:27" ht="13.2">
+    <row r="819" spans="1:27" ht="12.75">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
       <c r="C819" s="14"/>
@@ -26584,7 +26593,7 @@
       <c r="Z819" s="2"/>
       <c r="AA819" s="2"/>
     </row>
-    <row r="820" spans="1:27" ht="13.2">
+    <row r="820" spans="1:27" ht="12.75">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
       <c r="C820" s="14"/>
@@ -26613,7 +26622,7 @@
       <c r="Z820" s="2"/>
       <c r="AA820" s="2"/>
     </row>
-    <row r="821" spans="1:27" ht="13.2">
+    <row r="821" spans="1:27" ht="12.75">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
       <c r="C821" s="14"/>
@@ -26642,7 +26651,7 @@
       <c r="Z821" s="2"/>
       <c r="AA821" s="2"/>
     </row>
-    <row r="822" spans="1:27" ht="13.2">
+    <row r="822" spans="1:27" ht="12.75">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
       <c r="C822" s="14"/>
@@ -26671,7 +26680,7 @@
       <c r="Z822" s="2"/>
       <c r="AA822" s="2"/>
     </row>
-    <row r="823" spans="1:27" ht="13.2">
+    <row r="823" spans="1:27" ht="12.75">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
       <c r="C823" s="14"/>
@@ -26700,7 +26709,7 @@
       <c r="Z823" s="2"/>
       <c r="AA823" s="2"/>
     </row>
-    <row r="824" spans="1:27" ht="13.2">
+    <row r="824" spans="1:27" ht="12.75">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
       <c r="C824" s="14"/>
@@ -26729,7 +26738,7 @@
       <c r="Z824" s="2"/>
       <c r="AA824" s="2"/>
     </row>
-    <row r="825" spans="1:27" ht="13.2">
+    <row r="825" spans="1:27" ht="12.75">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
       <c r="C825" s="14"/>
@@ -26758,7 +26767,7 @@
       <c r="Z825" s="2"/>
       <c r="AA825" s="2"/>
     </row>
-    <row r="826" spans="1:27" ht="13.2">
+    <row r="826" spans="1:27" ht="12.75">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
       <c r="C826" s="14"/>
@@ -26787,7 +26796,7 @@
       <c r="Z826" s="2"/>
       <c r="AA826" s="2"/>
     </row>
-    <row r="827" spans="1:27" ht="13.2">
+    <row r="827" spans="1:27" ht="12.75">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
       <c r="C827" s="14"/>
@@ -26816,7 +26825,7 @@
       <c r="Z827" s="2"/>
       <c r="AA827" s="2"/>
     </row>
-    <row r="828" spans="1:27" ht="13.2">
+    <row r="828" spans="1:27" ht="12.75">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
       <c r="C828" s="14"/>
@@ -26845,7 +26854,7 @@
       <c r="Z828" s="2"/>
       <c r="AA828" s="2"/>
     </row>
-    <row r="829" spans="1:27" ht="13.2">
+    <row r="829" spans="1:27" ht="12.75">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
       <c r="C829" s="14"/>
@@ -26874,7 +26883,7 @@
       <c r="Z829" s="2"/>
       <c r="AA829" s="2"/>
     </row>
-    <row r="830" spans="1:27" ht="13.2">
+    <row r="830" spans="1:27" ht="12.75">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
       <c r="C830" s="14"/>
@@ -26903,7 +26912,7 @@
       <c r="Z830" s="2"/>
       <c r="AA830" s="2"/>
     </row>
-    <row r="831" spans="1:27" ht="13.2">
+    <row r="831" spans="1:27" ht="12.75">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
       <c r="C831" s="14"/>
@@ -26932,7 +26941,7 @@
       <c r="Z831" s="2"/>
       <c r="AA831" s="2"/>
     </row>
-    <row r="832" spans="1:27" ht="13.2">
+    <row r="832" spans="1:27" ht="12.75">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
       <c r="C832" s="14"/>
@@ -26961,7 +26970,7 @@
       <c r="Z832" s="2"/>
       <c r="AA832" s="2"/>
     </row>
-    <row r="833" spans="1:27" ht="13.2">
+    <row r="833" spans="1:27" ht="12.75">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
       <c r="C833" s="14"/>
@@ -26990,7 +26999,7 @@
       <c r="Z833" s="2"/>
       <c r="AA833" s="2"/>
     </row>
-    <row r="834" spans="1:27" ht="13.2">
+    <row r="834" spans="1:27" ht="12.75">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
       <c r="C834" s="14"/>
@@ -27019,7 +27028,7 @@
       <c r="Z834" s="2"/>
       <c r="AA834" s="2"/>
     </row>
-    <row r="835" spans="1:27" ht="13.2">
+    <row r="835" spans="1:27" ht="12.75">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
       <c r="C835" s="14"/>
@@ -27048,7 +27057,7 @@
       <c r="Z835" s="2"/>
       <c r="AA835" s="2"/>
     </row>
-    <row r="836" spans="1:27" ht="13.2">
+    <row r="836" spans="1:27" ht="12.75">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
       <c r="C836" s="14"/>
@@ -27077,7 +27086,7 @@
       <c r="Z836" s="2"/>
       <c r="AA836" s="2"/>
     </row>
-    <row r="837" spans="1:27" ht="13.2">
+    <row r="837" spans="1:27" ht="12.75">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
       <c r="C837" s="14"/>
@@ -27106,7 +27115,7 @@
       <c r="Z837" s="2"/>
       <c r="AA837" s="2"/>
     </row>
-    <row r="838" spans="1:27" ht="13.2">
+    <row r="838" spans="1:27" ht="12.75">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
       <c r="C838" s="14"/>
@@ -27135,7 +27144,7 @@
       <c r="Z838" s="2"/>
       <c r="AA838" s="2"/>
     </row>
-    <row r="839" spans="1:27" ht="13.2">
+    <row r="839" spans="1:27" ht="12.75">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
       <c r="C839" s="14"/>
@@ -27164,7 +27173,7 @@
       <c r="Z839" s="2"/>
       <c r="AA839" s="2"/>
     </row>
-    <row r="840" spans="1:27" ht="13.2">
+    <row r="840" spans="1:27" ht="12.75">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
       <c r="C840" s="14"/>
@@ -27193,7 +27202,7 @@
       <c r="Z840" s="2"/>
       <c r="AA840" s="2"/>
     </row>
-    <row r="841" spans="1:27" ht="13.2">
+    <row r="841" spans="1:27" ht="12.75">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
       <c r="C841" s="14"/>
@@ -27222,7 +27231,7 @@
       <c r="Z841" s="2"/>
       <c r="AA841" s="2"/>
     </row>
-    <row r="842" spans="1:27" ht="13.2">
+    <row r="842" spans="1:27" ht="12.75">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
       <c r="C842" s="14"/>
@@ -27251,7 +27260,7 @@
       <c r="Z842" s="2"/>
       <c r="AA842" s="2"/>
     </row>
-    <row r="843" spans="1:27" ht="13.2">
+    <row r="843" spans="1:27" ht="12.75">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
       <c r="C843" s="14"/>
@@ -27280,7 +27289,7 @@
       <c r="Z843" s="2"/>
       <c r="AA843" s="2"/>
     </row>
-    <row r="844" spans="1:27" ht="13.2">
+    <row r="844" spans="1:27" ht="12.75">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
       <c r="C844" s="14"/>
@@ -27309,7 +27318,7 @@
       <c r="Z844" s="2"/>
       <c r="AA844" s="2"/>
     </row>
-    <row r="845" spans="1:27" ht="13.2">
+    <row r="845" spans="1:27" ht="12.75">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
       <c r="C845" s="14"/>
@@ -27338,7 +27347,7 @@
       <c r="Z845" s="2"/>
       <c r="AA845" s="2"/>
     </row>
-    <row r="846" spans="1:27" ht="13.2">
+    <row r="846" spans="1:27" ht="12.75">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
       <c r="C846" s="14"/>
@@ -27367,7 +27376,7 @@
       <c r="Z846" s="2"/>
       <c r="AA846" s="2"/>
     </row>
-    <row r="847" spans="1:27" ht="13.2">
+    <row r="847" spans="1:27" ht="12.75">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
       <c r="C847" s="14"/>
@@ -27396,7 +27405,7 @@
       <c r="Z847" s="2"/>
       <c r="AA847" s="2"/>
     </row>
-    <row r="848" spans="1:27" ht="13.2">
+    <row r="848" spans="1:27" ht="12.75">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
       <c r="C848" s="14"/>
@@ -27425,7 +27434,7 @@
       <c r="Z848" s="2"/>
       <c r="AA848" s="2"/>
     </row>
-    <row r="849" spans="1:27" ht="13.2">
+    <row r="849" spans="1:27" ht="12.75">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
       <c r="C849" s="14"/>
@@ -27454,7 +27463,7 @@
       <c r="Z849" s="2"/>
       <c r="AA849" s="2"/>
     </row>
-    <row r="850" spans="1:27" ht="13.2">
+    <row r="850" spans="1:27" ht="12.75">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
       <c r="C850" s="14"/>
@@ -27483,7 +27492,7 @@
       <c r="Z850" s="2"/>
       <c r="AA850" s="2"/>
     </row>
-    <row r="851" spans="1:27" ht="13.2">
+    <row r="851" spans="1:27" ht="12.75">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
       <c r="C851" s="14"/>
@@ -27512,7 +27521,7 @@
       <c r="Z851" s="2"/>
       <c r="AA851" s="2"/>
     </row>
-    <row r="852" spans="1:27" ht="13.2">
+    <row r="852" spans="1:27" ht="12.75">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
       <c r="C852" s="14"/>
@@ -27541,7 +27550,7 @@
       <c r="Z852" s="2"/>
       <c r="AA852" s="2"/>
     </row>
-    <row r="853" spans="1:27" ht="13.2">
+    <row r="853" spans="1:27" ht="12.75">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
       <c r="C853" s="14"/>
@@ -27570,7 +27579,7 @@
       <c r="Z853" s="2"/>
       <c r="AA853" s="2"/>
     </row>
-    <row r="854" spans="1:27" ht="13.2">
+    <row r="854" spans="1:27" ht="12.75">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
       <c r="C854" s="14"/>
@@ -27599,7 +27608,7 @@
       <c r="Z854" s="2"/>
       <c r="AA854" s="2"/>
     </row>
-    <row r="855" spans="1:27" ht="13.2">
+    <row r="855" spans="1:27" ht="12.75">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
       <c r="C855" s="14"/>
@@ -27628,7 +27637,7 @@
       <c r="Z855" s="2"/>
       <c r="AA855" s="2"/>
     </row>
-    <row r="856" spans="1:27" ht="13.2">
+    <row r="856" spans="1:27" ht="12.75">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
       <c r="C856" s="14"/>
@@ -27657,7 +27666,7 @@
       <c r="Z856" s="2"/>
       <c r="AA856" s="2"/>
     </row>
-    <row r="857" spans="1:27" ht="13.2">
+    <row r="857" spans="1:27" ht="12.75">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
       <c r="C857" s="14"/>
@@ -27686,7 +27695,7 @@
       <c r="Z857" s="2"/>
       <c r="AA857" s="2"/>
     </row>
-    <row r="858" spans="1:27" ht="13.2">
+    <row r="858" spans="1:27" ht="12.75">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
       <c r="C858" s="14"/>
@@ -27715,7 +27724,7 @@
       <c r="Z858" s="2"/>
       <c r="AA858" s="2"/>
     </row>
-    <row r="859" spans="1:27" ht="13.2">
+    <row r="859" spans="1:27" ht="12.75">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
       <c r="C859" s="14"/>
@@ -27744,7 +27753,7 @@
       <c r="Z859" s="2"/>
       <c r="AA859" s="2"/>
     </row>
-    <row r="860" spans="1:27" ht="13.2">
+    <row r="860" spans="1:27" ht="12.75">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
       <c r="C860" s="14"/>
@@ -27773,7 +27782,7 @@
       <c r="Z860" s="2"/>
       <c r="AA860" s="2"/>
     </row>
-    <row r="861" spans="1:27" ht="13.2">
+    <row r="861" spans="1:27" ht="12.75">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
       <c r="C861" s="14"/>
@@ -27802,7 +27811,7 @@
       <c r="Z861" s="2"/>
       <c r="AA861" s="2"/>
     </row>
-    <row r="862" spans="1:27" ht="13.2">
+    <row r="862" spans="1:27" ht="12.75">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
       <c r="C862" s="14"/>
@@ -27831,7 +27840,7 @@
       <c r="Z862" s="2"/>
       <c r="AA862" s="2"/>
     </row>
-    <row r="863" spans="1:27" ht="13.2">
+    <row r="863" spans="1:27" ht="12.75">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
       <c r="C863" s="14"/>
@@ -27860,7 +27869,7 @@
       <c r="Z863" s="2"/>
       <c r="AA863" s="2"/>
     </row>
-    <row r="864" spans="1:27" ht="13.2">
+    <row r="864" spans="1:27" ht="12.75">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
       <c r="C864" s="14"/>
@@ -27889,7 +27898,7 @@
       <c r="Z864" s="2"/>
       <c r="AA864" s="2"/>
     </row>
-    <row r="865" spans="1:27" ht="13.2">
+    <row r="865" spans="1:27" ht="12.75">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
       <c r="C865" s="14"/>
@@ -27918,7 +27927,7 @@
       <c r="Z865" s="2"/>
       <c r="AA865" s="2"/>
     </row>
-    <row r="866" spans="1:27" ht="13.2">
+    <row r="866" spans="1:27" ht="12.75">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
       <c r="C866" s="14"/>
@@ -27947,7 +27956,7 @@
       <c r="Z866" s="2"/>
       <c r="AA866" s="2"/>
     </row>
-    <row r="867" spans="1:27" ht="13.2">
+    <row r="867" spans="1:27" ht="12.75">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
       <c r="C867" s="14"/>
@@ -27976,7 +27985,7 @@
       <c r="Z867" s="2"/>
       <c r="AA867" s="2"/>
     </row>
-    <row r="868" spans="1:27" ht="13.2">
+    <row r="868" spans="1:27" ht="12.75">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
       <c r="C868" s="14"/>
@@ -28005,7 +28014,7 @@
       <c r="Z868" s="2"/>
       <c r="AA868" s="2"/>
     </row>
-    <row r="869" spans="1:27" ht="13.2">
+    <row r="869" spans="1:27" ht="12.75">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
       <c r="C869" s="14"/>
@@ -28034,7 +28043,7 @@
       <c r="Z869" s="2"/>
       <c r="AA869" s="2"/>
     </row>
-    <row r="870" spans="1:27" ht="13.2">
+    <row r="870" spans="1:27" ht="12.75">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
       <c r="C870" s="14"/>
@@ -28063,7 +28072,7 @@
       <c r="Z870" s="2"/>
       <c r="AA870" s="2"/>
     </row>
-    <row r="871" spans="1:27" ht="13.2">
+    <row r="871" spans="1:27" ht="12.75">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
       <c r="C871" s="14"/>
@@ -28092,7 +28101,7 @@
       <c r="Z871" s="2"/>
       <c r="AA871" s="2"/>
     </row>
-    <row r="872" spans="1:27" ht="13.2">
+    <row r="872" spans="1:27" ht="12.75">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
       <c r="C872" s="14"/>
@@ -28121,7 +28130,7 @@
       <c r="Z872" s="2"/>
       <c r="AA872" s="2"/>
     </row>
-    <row r="873" spans="1:27" ht="13.2">
+    <row r="873" spans="1:27" ht="12.75">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
       <c r="C873" s="14"/>
@@ -28150,7 +28159,7 @@
       <c r="Z873" s="2"/>
       <c r="AA873" s="2"/>
     </row>
-    <row r="874" spans="1:27" ht="13.2">
+    <row r="874" spans="1:27" ht="12.75">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
       <c r="C874" s="14"/>
@@ -28179,7 +28188,7 @@
       <c r="Z874" s="2"/>
       <c r="AA874" s="2"/>
     </row>
-    <row r="875" spans="1:27" ht="13.2">
+    <row r="875" spans="1:27" ht="12.75">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
       <c r="C875" s="14"/>
@@ -28208,7 +28217,7 @@
       <c r="Z875" s="2"/>
       <c r="AA875" s="2"/>
     </row>
-    <row r="876" spans="1:27" ht="13.2">
+    <row r="876" spans="1:27" ht="12.75">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
       <c r="C876" s="14"/>
@@ -28237,7 +28246,7 @@
       <c r="Z876" s="2"/>
       <c r="AA876" s="2"/>
     </row>
-    <row r="877" spans="1:27" ht="13.2">
+    <row r="877" spans="1:27" ht="12.75">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
       <c r="C877" s="14"/>
@@ -28266,7 +28275,7 @@
       <c r="Z877" s="2"/>
       <c r="AA877" s="2"/>
     </row>
-    <row r="878" spans="1:27" ht="13.2">
+    <row r="878" spans="1:27" ht="12.75">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
       <c r="C878" s="14"/>
@@ -28295,7 +28304,7 @@
       <c r="Z878" s="2"/>
       <c r="AA878" s="2"/>
     </row>
-    <row r="879" spans="1:27" ht="13.2">
+    <row r="879" spans="1:27" ht="12.75">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
       <c r="C879" s="14"/>
@@ -28324,7 +28333,7 @@
       <c r="Z879" s="2"/>
       <c r="AA879" s="2"/>
     </row>
-    <row r="880" spans="1:27" ht="13.2">
+    <row r="880" spans="1:27" ht="12.75">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
       <c r="C880" s="14"/>
@@ -28353,7 +28362,7 @@
       <c r="Z880" s="2"/>
       <c r="AA880" s="2"/>
     </row>
-    <row r="881" spans="1:27" ht="13.2">
+    <row r="881" spans="1:27" ht="12.75">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
       <c r="C881" s="14"/>
@@ -28382,7 +28391,7 @@
       <c r="Z881" s="2"/>
       <c r="AA881" s="2"/>
     </row>
-    <row r="882" spans="1:27" ht="13.2">
+    <row r="882" spans="1:27" ht="12.75">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
       <c r="C882" s="14"/>
@@ -28411,7 +28420,7 @@
       <c r="Z882" s="2"/>
       <c r="AA882" s="2"/>
     </row>
-    <row r="883" spans="1:27" ht="13.2">
+    <row r="883" spans="1:27" ht="12.75">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
       <c r="C883" s="14"/>
@@ -28440,7 +28449,7 @@
       <c r="Z883" s="2"/>
       <c r="AA883" s="2"/>
     </row>
-    <row r="884" spans="1:27" ht="13.2">
+    <row r="884" spans="1:27" ht="12.75">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
       <c r="C884" s="14"/>
@@ -28469,7 +28478,7 @@
       <c r="Z884" s="2"/>
       <c r="AA884" s="2"/>
     </row>
-    <row r="885" spans="1:27" ht="13.2">
+    <row r="885" spans="1:27" ht="12.75">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
       <c r="C885" s="14"/>
@@ -28498,7 +28507,7 @@
       <c r="Z885" s="2"/>
       <c r="AA885" s="2"/>
     </row>
-    <row r="886" spans="1:27" ht="13.2">
+    <row r="886" spans="1:27" ht="12.75">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
       <c r="C886" s="14"/>
@@ -28527,7 +28536,7 @@
       <c r="Z886" s="2"/>
       <c r="AA886" s="2"/>
     </row>
-    <row r="887" spans="1:27" ht="13.2">
+    <row r="887" spans="1:27" ht="12.75">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
       <c r="C887" s="14"/>
@@ -28556,7 +28565,7 @@
       <c r="Z887" s="2"/>
       <c r="AA887" s="2"/>
     </row>
-    <row r="888" spans="1:27" ht="13.2">
+    <row r="888" spans="1:27" ht="12.75">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
       <c r="C888" s="14"/>
@@ -28585,7 +28594,7 @@
       <c r="Z888" s="2"/>
       <c r="AA888" s="2"/>
     </row>
-    <row r="889" spans="1:27" ht="13.2">
+    <row r="889" spans="1:27" ht="12.75">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
       <c r="C889" s="14"/>
@@ -28614,7 +28623,7 @@
       <c r="Z889" s="2"/>
       <c r="AA889" s="2"/>
     </row>
-    <row r="890" spans="1:27" ht="13.2">
+    <row r="890" spans="1:27" ht="12.75">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
       <c r="C890" s="14"/>
@@ -28643,7 +28652,7 @@
       <c r="Z890" s="2"/>
       <c r="AA890" s="2"/>
     </row>
-    <row r="891" spans="1:27" ht="13.2">
+    <row r="891" spans="1:27" ht="12.75">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
       <c r="C891" s="14"/>
@@ -28672,7 +28681,7 @@
       <c r="Z891" s="2"/>
       <c r="AA891" s="2"/>
     </row>
-    <row r="892" spans="1:27" ht="13.2">
+    <row r="892" spans="1:27" ht="12.75">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
       <c r="C892" s="14"/>
@@ -28701,7 +28710,7 @@
       <c r="Z892" s="2"/>
       <c r="AA892" s="2"/>
     </row>
-    <row r="893" spans="1:27" ht="13.2">
+    <row r="893" spans="1:27" ht="12.75">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
       <c r="C893" s="14"/>
@@ -28730,7 +28739,7 @@
       <c r="Z893" s="2"/>
       <c r="AA893" s="2"/>
     </row>
-    <row r="894" spans="1:27" ht="13.2">
+    <row r="894" spans="1:27" ht="12.75">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
       <c r="C894" s="14"/>
@@ -28759,7 +28768,7 @@
       <c r="Z894" s="2"/>
       <c r="AA894" s="2"/>
     </row>
-    <row r="895" spans="1:27" ht="13.2">
+    <row r="895" spans="1:27" ht="12.75">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
       <c r="C895" s="14"/>
@@ -28788,7 +28797,7 @@
       <c r="Z895" s="2"/>
       <c r="AA895" s="2"/>
     </row>
-    <row r="896" spans="1:27" ht="13.2">
+    <row r="896" spans="1:27" ht="12.75">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
       <c r="C896" s="14"/>
@@ -28817,7 +28826,7 @@
       <c r="Z896" s="2"/>
       <c r="AA896" s="2"/>
     </row>
-    <row r="897" spans="1:27" ht="13.2">
+    <row r="897" spans="1:27" ht="12.75">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
       <c r="C897" s="14"/>
@@ -28846,7 +28855,7 @@
       <c r="Z897" s="2"/>
       <c r="AA897" s="2"/>
     </row>
-    <row r="898" spans="1:27" ht="13.2">
+    <row r="898" spans="1:27" ht="12.75">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
       <c r="C898" s="14"/>
@@ -28875,7 +28884,7 @@
       <c r="Z898" s="2"/>
       <c r="AA898" s="2"/>
     </row>
-    <row r="899" spans="1:27" ht="13.2">
+    <row r="899" spans="1:27" ht="12.75">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
       <c r="C899" s="14"/>
@@ -28904,7 +28913,7 @@
       <c r="Z899" s="2"/>
       <c r="AA899" s="2"/>
     </row>
-    <row r="900" spans="1:27" ht="13.2">
+    <row r="900" spans="1:27" ht="12.75">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
       <c r="C900" s="14"/>
@@ -28933,7 +28942,7 @@
       <c r="Z900" s="2"/>
       <c r="AA900" s="2"/>
     </row>
-    <row r="901" spans="1:27" ht="13.2">
+    <row r="901" spans="1:27" ht="12.75">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
       <c r="C901" s="14"/>
@@ -28962,7 +28971,7 @@
       <c r="Z901" s="2"/>
       <c r="AA901" s="2"/>
     </row>
-    <row r="902" spans="1:27" ht="13.2">
+    <row r="902" spans="1:27" ht="12.75">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
       <c r="C902" s="14"/>
@@ -28991,7 +29000,7 @@
       <c r="Z902" s="2"/>
       <c r="AA902" s="2"/>
     </row>
-    <row r="903" spans="1:27" ht="13.2">
+    <row r="903" spans="1:27" ht="12.75">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
       <c r="C903" s="14"/>
@@ -29020,7 +29029,7 @@
       <c r="Z903" s="2"/>
       <c r="AA903" s="2"/>
     </row>
-    <row r="904" spans="1:27" ht="13.2">
+    <row r="904" spans="1:27" ht="12.75">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
       <c r="C904" s="14"/>
@@ -29049,7 +29058,7 @@
       <c r="Z904" s="2"/>
       <c r="AA904" s="2"/>
     </row>
-    <row r="905" spans="1:27" ht="13.2">
+    <row r="905" spans="1:27" ht="12.75">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
       <c r="C905" s="14"/>
@@ -29078,7 +29087,7 @@
       <c r="Z905" s="2"/>
       <c r="AA905" s="2"/>
     </row>
-    <row r="906" spans="1:27" ht="13.2">
+    <row r="906" spans="1:27" ht="12.75">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
       <c r="C906" s="14"/>
@@ -29107,7 +29116,7 @@
       <c r="Z906" s="2"/>
       <c r="AA906" s="2"/>
     </row>
-    <row r="907" spans="1:27" ht="13.2">
+    <row r="907" spans="1:27" ht="12.75">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
       <c r="C907" s="14"/>
@@ -29136,7 +29145,7 @@
       <c r="Z907" s="2"/>
       <c r="AA907" s="2"/>
     </row>
-    <row r="908" spans="1:27" ht="13.2">
+    <row r="908" spans="1:27" ht="12.75">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
       <c r="C908" s="14"/>
@@ -29165,7 +29174,7 @@
       <c r="Z908" s="2"/>
       <c r="AA908" s="2"/>
     </row>
-    <row r="909" spans="1:27" ht="13.2">
+    <row r="909" spans="1:27" ht="12.75">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
       <c r="C909" s="14"/>
@@ -29194,7 +29203,7 @@
       <c r="Z909" s="2"/>
       <c r="AA909" s="2"/>
     </row>
-    <row r="910" spans="1:27" ht="13.2">
+    <row r="910" spans="1:27" ht="12.75">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
       <c r="C910" s="14"/>
@@ -29223,7 +29232,7 @@
       <c r="Z910" s="2"/>
       <c r="AA910" s="2"/>
     </row>
-    <row r="911" spans="1:27" ht="13.2">
+    <row r="911" spans="1:27" ht="12.75">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
       <c r="C911" s="14"/>
@@ -29252,7 +29261,7 @@
       <c r="Z911" s="2"/>
       <c r="AA911" s="2"/>
     </row>
-    <row r="912" spans="1:27" ht="13.2">
+    <row r="912" spans="1:27" ht="12.75">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
       <c r="C912" s="14"/>
@@ -29281,7 +29290,7 @@
       <c r="Z912" s="2"/>
       <c r="AA912" s="2"/>
     </row>
-    <row r="913" spans="1:27" ht="13.2">
+    <row r="913" spans="1:27" ht="12.75">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
       <c r="C913" s="14"/>
@@ -29310,7 +29319,7 @@
       <c r="Z913" s="2"/>
       <c r="AA913" s="2"/>
     </row>
-    <row r="914" spans="1:27" ht="13.2">
+    <row r="914" spans="1:27" ht="12.75">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
       <c r="C914" s="14"/>
@@ -29339,7 +29348,7 @@
       <c r="Z914" s="2"/>
       <c r="AA914" s="2"/>
     </row>
-    <row r="915" spans="1:27" ht="13.2">
+    <row r="915" spans="1:27" ht="12.75">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
       <c r="C915" s="14"/>
@@ -29368,7 +29377,7 @@
       <c r="Z915" s="2"/>
       <c r="AA915" s="2"/>
     </row>
-    <row r="916" spans="1:27" ht="13.2">
+    <row r="916" spans="1:27" ht="12.75">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
       <c r="C916" s="14"/>
@@ -29397,7 +29406,7 @@
       <c r="Z916" s="2"/>
       <c r="AA916" s="2"/>
     </row>
-    <row r="917" spans="1:27" ht="13.2">
+    <row r="917" spans="1:27" ht="12.75">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
       <c r="C917" s="14"/>
@@ -29426,7 +29435,7 @@
       <c r="Z917" s="2"/>
       <c r="AA917" s="2"/>
     </row>
-    <row r="918" spans="1:27" ht="13.2">
+    <row r="918" spans="1:27" ht="12.75">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
       <c r="C918" s="14"/>
@@ -29455,7 +29464,7 @@
       <c r="Z918" s="2"/>
       <c r="AA918" s="2"/>
     </row>
-    <row r="919" spans="1:27" ht="13.2">
+    <row r="919" spans="1:27" ht="12.75">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
       <c r="C919" s="14"/>
@@ -29484,7 +29493,7 @@
       <c r="Z919" s="2"/>
       <c r="AA919" s="2"/>
     </row>
-    <row r="920" spans="1:27" ht="13.2">
+    <row r="920" spans="1:27" ht="12.75">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
       <c r="C920" s="14"/>
@@ -29513,7 +29522,7 @@
       <c r="Z920" s="2"/>
       <c r="AA920" s="2"/>
     </row>
-    <row r="921" spans="1:27" ht="13.2">
+    <row r="921" spans="1:27" ht="12.75">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
       <c r="C921" s="14"/>
@@ -29542,7 +29551,7 @@
       <c r="Z921" s="2"/>
       <c r="AA921" s="2"/>
     </row>
-    <row r="922" spans="1:27" ht="13.2">
+    <row r="922" spans="1:27" ht="12.75">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
       <c r="C922" s="14"/>
@@ -29571,7 +29580,7 @@
       <c r="Z922" s="2"/>
       <c r="AA922" s="2"/>
     </row>
-    <row r="923" spans="1:27" ht="13.2">
+    <row r="923" spans="1:27" ht="12.75">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
       <c r="C923" s="14"/>
@@ -29600,7 +29609,7 @@
       <c r="Z923" s="2"/>
       <c r="AA923" s="2"/>
     </row>
-    <row r="924" spans="1:27" ht="13.2">
+    <row r="924" spans="1:27" ht="12.75">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
       <c r="C924" s="14"/>
@@ -29629,7 +29638,7 @@
       <c r="Z924" s="2"/>
       <c r="AA924" s="2"/>
     </row>
-    <row r="925" spans="1:27" ht="13.2">
+    <row r="925" spans="1:27" ht="12.75">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
       <c r="C925" s="14"/>
@@ -29658,7 +29667,7 @@
       <c r="Z925" s="2"/>
       <c r="AA925" s="2"/>
     </row>
-    <row r="926" spans="1:27" ht="13.2">
+    <row r="926" spans="1:27" ht="12.75">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
       <c r="C926" s="14"/>
@@ -29687,7 +29696,7 @@
       <c r="Z926" s="2"/>
       <c r="AA926" s="2"/>
     </row>
-    <row r="927" spans="1:27" ht="13.2">
+    <row r="927" spans="1:27" ht="12.75">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
       <c r="C927" s="14"/>
@@ -29716,7 +29725,7 @@
       <c r="Z927" s="2"/>
       <c r="AA927" s="2"/>
     </row>
-    <row r="928" spans="1:27" ht="13.2">
+    <row r="928" spans="1:27" ht="12.75">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
       <c r="C928" s="14"/>
@@ -29745,7 +29754,7 @@
       <c r="Z928" s="2"/>
       <c r="AA928" s="2"/>
     </row>
-    <row r="929" spans="1:27" ht="13.2">
+    <row r="929" spans="1:27" ht="12.75">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
       <c r="C929" s="14"/>
@@ -29774,7 +29783,7 @@
       <c r="Z929" s="2"/>
       <c r="AA929" s="2"/>
     </row>
-    <row r="930" spans="1:27" ht="13.2">
+    <row r="930" spans="1:27" ht="12.75">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
       <c r="C930" s="14"/>
@@ -29803,7 +29812,7 @@
       <c r="Z930" s="2"/>
       <c r="AA930" s="2"/>
     </row>
-    <row r="931" spans="1:27" ht="13.2">
+    <row r="931" spans="1:27" ht="12.75">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
       <c r="C931" s="14"/>
@@ -29832,7 +29841,7 @@
       <c r="Z931" s="2"/>
       <c r="AA931" s="2"/>
     </row>
-    <row r="932" spans="1:27" ht="13.2">
+    <row r="932" spans="1:27" ht="12.75">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
       <c r="C932" s="14"/>
@@ -29861,7 +29870,7 @@
       <c r="Z932" s="2"/>
       <c r="AA932" s="2"/>
     </row>
-    <row r="933" spans="1:27" ht="13.2">
+    <row r="933" spans="1:27" ht="12.75">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
       <c r="C933" s="14"/>
@@ -29890,7 +29899,7 @@
       <c r="Z933" s="2"/>
       <c r="AA933" s="2"/>
     </row>
-    <row r="934" spans="1:27" ht="13.2">
+    <row r="934" spans="1:27" ht="12.75">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
       <c r="C934" s="14"/>
@@ -29919,7 +29928,7 @@
       <c r="Z934" s="2"/>
       <c r="AA934" s="2"/>
     </row>
-    <row r="935" spans="1:27" ht="13.2">
+    <row r="935" spans="1:27" ht="12.75">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
       <c r="C935" s="14"/>
@@ -29948,7 +29957,7 @@
       <c r="Z935" s="2"/>
       <c r="AA935" s="2"/>
     </row>
-    <row r="936" spans="1:27" ht="13.2">
+    <row r="936" spans="1:27" ht="12.75">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
       <c r="C936" s="14"/>
@@ -29977,7 +29986,7 @@
       <c r="Z936" s="2"/>
       <c r="AA936" s="2"/>
     </row>
-    <row r="937" spans="1:27" ht="13.2">
+    <row r="937" spans="1:27" ht="12.75">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
       <c r="C937" s="14"/>
@@ -30006,7 +30015,7 @@
       <c r="Z937" s="2"/>
       <c r="AA937" s="2"/>
     </row>
-    <row r="938" spans="1:27" ht="13.2">
+    <row r="938" spans="1:27" ht="12.75">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
       <c r="C938" s="14"/>
@@ -30035,7 +30044,7 @@
       <c r="Z938" s="2"/>
       <c r="AA938" s="2"/>
     </row>
-    <row r="939" spans="1:27" ht="13.2">
+    <row r="939" spans="1:27" ht="12.75">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
       <c r="C939" s="14"/>
@@ -30064,7 +30073,7 @@
       <c r="Z939" s="2"/>
       <c r="AA939" s="2"/>
     </row>
-    <row r="940" spans="1:27" ht="13.2">
+    <row r="940" spans="1:27" ht="12.75">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
       <c r="C940" s="14"/>
@@ -30093,7 +30102,7 @@
       <c r="Z940" s="2"/>
       <c r="AA940" s="2"/>
     </row>
-    <row r="941" spans="1:27" ht="13.2">
+    <row r="941" spans="1:27" ht="12.75">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
       <c r="C941" s="14"/>
@@ -30122,7 +30131,7 @@
       <c r="Z941" s="2"/>
       <c r="AA941" s="2"/>
     </row>
-    <row r="942" spans="1:27" ht="13.2">
+    <row r="942" spans="1:27" ht="12.75">
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
       <c r="C942" s="14"/>
@@ -30151,7 +30160,7 @@
       <c r="Z942" s="2"/>
       <c r="AA942" s="2"/>
     </row>
-    <row r="943" spans="1:27" ht="13.2">
+    <row r="943" spans="1:27" ht="12.75">
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
       <c r="C943" s="14"/>
@@ -30180,7 +30189,7 @@
       <c r="Z943" s="2"/>
       <c r="AA943" s="2"/>
     </row>
-    <row r="944" spans="1:27" ht="13.2">
+    <row r="944" spans="1:27" ht="12.75">
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
       <c r="C944" s="14"/>
@@ -30209,7 +30218,7 @@
       <c r="Z944" s="2"/>
       <c r="AA944" s="2"/>
     </row>
-    <row r="945" spans="1:27" ht="13.2">
+    <row r="945" spans="1:27" ht="12.75">
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
       <c r="C945" s="14"/>
@@ -30238,7 +30247,7 @@
       <c r="Z945" s="2"/>
       <c r="AA945" s="2"/>
     </row>
-    <row r="946" spans="1:27" ht="13.2">
+    <row r="946" spans="1:27" ht="12.75">
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
       <c r="C946" s="14"/>
@@ -30267,7 +30276,7 @@
       <c r="Z946" s="2"/>
       <c r="AA946" s="2"/>
     </row>
-    <row r="947" spans="1:27" ht="13.2">
+    <row r="947" spans="1:27" ht="12.75">
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
       <c r="C947" s="14"/>
@@ -30296,7 +30305,7 @@
       <c r="Z947" s="2"/>
       <c r="AA947" s="2"/>
     </row>
-    <row r="948" spans="1:27" ht="13.2">
+    <row r="948" spans="1:27" ht="12.75">
       <c r="A948" s="2"/>
       <c r="B948" s="2"/>
       <c r="C948" s="14"/>
@@ -30325,7 +30334,7 @@
       <c r="Z948" s="2"/>
       <c r="AA948" s="2"/>
     </row>
-    <row r="949" spans="1:27" ht="13.2">
+    <row r="949" spans="1:27" ht="12.75">
       <c r="A949" s="2"/>
       <c r="B949" s="2"/>
       <c r="C949" s="14"/>
@@ -30354,7 +30363,7 @@
       <c r="Z949" s="2"/>
       <c r="AA949" s="2"/>
     </row>
-    <row r="950" spans="1:27" ht="13.2">
+    <row r="950" spans="1:27" ht="12.75">
       <c r="A950" s="2"/>
       <c r="B950" s="2"/>
       <c r="C950" s="14"/>
@@ -30383,7 +30392,7 @@
       <c r="Z950" s="2"/>
       <c r="AA950" s="2"/>
     </row>
-    <row r="951" spans="1:27" ht="13.2">
+    <row r="951" spans="1:27" ht="12.75">
       <c r="A951" s="2"/>
       <c r="B951" s="2"/>
       <c r="C951" s="14"/>
@@ -30412,7 +30421,7 @@
       <c r="Z951" s="2"/>
       <c r="AA951" s="2"/>
     </row>
-    <row r="952" spans="1:27" ht="13.2">
+    <row r="952" spans="1:27" ht="12.75">
       <c r="A952" s="2"/>
       <c r="B952" s="2"/>
       <c r="C952" s="14"/>
@@ -30441,7 +30450,7 @@
       <c r="Z952" s="2"/>
       <c r="AA952" s="2"/>
     </row>
-    <row r="953" spans="1:27" ht="13.2">
+    <row r="953" spans="1:27" ht="12.75">
       <c r="A953" s="2"/>
       <c r="B953" s="2"/>
       <c r="C953" s="14"/>
@@ -30470,7 +30479,7 @@
       <c r="Z953" s="2"/>
       <c r="AA953" s="2"/>
     </row>
-    <row r="954" spans="1:27" ht="13.2">
+    <row r="954" spans="1:27" ht="12.75">
       <c r="A954" s="2"/>
       <c r="B954" s="2"/>
       <c r="C954" s="14"/>
@@ -30499,7 +30508,7 @@
       <c r="Z954" s="2"/>
       <c r="AA954" s="2"/>
     </row>
-    <row r="955" spans="1:27" ht="13.2">
+    <row r="955" spans="1:27" ht="12.75">
       <c r="A955" s="2"/>
       <c r="B955" s="2"/>
       <c r="C955" s="14"/>
@@ -30528,7 +30537,7 @@
       <c r="Z955" s="2"/>
       <c r="AA955" s="2"/>
     </row>
-    <row r="956" spans="1:27" ht="13.2">
+    <row r="956" spans="1:27" ht="12.75">
       <c r="A956" s="2"/>
       <c r="B956" s="2"/>
       <c r="C956" s="14"/>
@@ -30557,7 +30566,7 @@
       <c r="Z956" s="2"/>
       <c r="AA956" s="2"/>
     </row>
-    <row r="957" spans="1:27" ht="13.2">
+    <row r="957" spans="1:27" ht="12.75">
       <c r="A957" s="2"/>
       <c r="B957" s="2"/>
       <c r="C957" s="14"/>
@@ -30586,7 +30595,7 @@
       <c r="Z957" s="2"/>
       <c r="AA957" s="2"/>
     </row>
-    <row r="958" spans="1:27" ht="13.2">
+    <row r="958" spans="1:27" ht="12.75">
       <c r="A958" s="2"/>
       <c r="B958" s="2"/>
       <c r="C958" s="14"/>
@@ -30615,7 +30624,7 @@
       <c r="Z958" s="2"/>
       <c r="AA958" s="2"/>
     </row>
-    <row r="959" spans="1:27" ht="13.2">
+    <row r="959" spans="1:27" ht="12.75">
       <c r="A959" s="2"/>
       <c r="B959" s="2"/>
       <c r="C959" s="14"/>
@@ -30644,7 +30653,7 @@
       <c r="Z959" s="2"/>
       <c r="AA959" s="2"/>
     </row>
-    <row r="960" spans="1:27" ht="13.2">
+    <row r="960" spans="1:27" ht="12.75">
       <c r="A960" s="2"/>
       <c r="B960" s="2"/>
       <c r="C960" s="14"/>
@@ -30673,7 +30682,7 @@
       <c r="Z960" s="2"/>
       <c r="AA960" s="2"/>
     </row>
-    <row r="961" spans="1:27" ht="13.2">
+    <row r="961" spans="1:27" ht="12.75">
       <c r="A961" s="2"/>
       <c r="B961" s="2"/>
       <c r="C961" s="14"/>
@@ -30702,7 +30711,7 @@
       <c r="Z961" s="2"/>
       <c r="AA961" s="2"/>
     </row>
-    <row r="962" spans="1:27" ht="13.2">
+    <row r="962" spans="1:27" ht="12.75">
       <c r="A962" s="2"/>
       <c r="B962" s="2"/>
       <c r="C962" s="14"/>
@@ -30731,7 +30740,7 @@
       <c r="Z962" s="2"/>
       <c r="AA962" s="2"/>
     </row>
-    <row r="963" spans="1:27" ht="13.2">
+    <row r="963" spans="1:27" ht="12.75">
       <c r="A963" s="2"/>
       <c r="B963" s="2"/>
       <c r="C963" s="14"/>
@@ -30760,7 +30769,7 @@
       <c r="Z963" s="2"/>
       <c r="AA963" s="2"/>
     </row>
-    <row r="964" spans="1:27" ht="13.2">
+    <row r="964" spans="1:27" ht="12.75">
       <c r="A964" s="2"/>
       <c r="B964" s="2"/>
       <c r="C964" s="14"/>
@@ -30789,7 +30798,7 @@
       <c r="Z964" s="2"/>
       <c r="AA964" s="2"/>
     </row>
-    <row r="965" spans="1:27" ht="13.2">
+    <row r="965" spans="1:27" ht="12.75">
       <c r="A965" s="2"/>
       <c r="B965" s="2"/>
       <c r="C965" s="14"/>
@@ -30818,7 +30827,7 @@
       <c r="Z965" s="2"/>
       <c r="AA965" s="2"/>
     </row>
-    <row r="966" spans="1:27" ht="13.2">
+    <row r="966" spans="1:27" ht="12.75">
       <c r="A966" s="2"/>
       <c r="B966" s="2"/>
       <c r="C966" s="14"/>
@@ -30847,7 +30856,7 @@
       <c r="Z966" s="2"/>
       <c r="AA966" s="2"/>
     </row>
-    <row r="967" spans="1:27" ht="13.2">
+    <row r="967" spans="1:27" ht="12.75">
       <c r="A967" s="2"/>
       <c r="B967" s="2"/>
       <c r="C967" s="14"/>
@@ -30876,7 +30885,7 @@
       <c r="Z967" s="2"/>
       <c r="AA967" s="2"/>
     </row>
-    <row r="968" spans="1:27" ht="13.2">
+    <row r="968" spans="1:27" ht="12.75">
       <c r="A968" s="2"/>
       <c r="B968" s="2"/>
       <c r="C968" s="14"/>
@@ -30905,7 +30914,7 @@
       <c r="Z968" s="2"/>
       <c r="AA968" s="2"/>
     </row>
-    <row r="969" spans="1:27" ht="13.2">
+    <row r="969" spans="1:27" ht="12.75">
       <c r="A969" s="2"/>
       <c r="B969" s="2"/>
       <c r="C969" s="14"/>
@@ -30934,7 +30943,7 @@
       <c r="Z969" s="2"/>
       <c r="AA969" s="2"/>
     </row>
-    <row r="970" spans="1:27" ht="13.2">
+    <row r="970" spans="1:27" ht="12.75">
       <c r="A970" s="2"/>
       <c r="B970" s="2"/>
       <c r="C970" s="14"/>
@@ -30963,7 +30972,7 @@
       <c r="Z970" s="2"/>
       <c r="AA970" s="2"/>
     </row>
-    <row r="971" spans="1:27" ht="13.2">
+    <row r="971" spans="1:27" ht="12.75">
       <c r="A971" s="2"/>
       <c r="B971" s="2"/>
       <c r="C971" s="14"/>
@@ -30992,7 +31001,7 @@
       <c r="Z971" s="2"/>
       <c r="AA971" s="2"/>
     </row>
-    <row r="972" spans="1:27" ht="13.2">
+    <row r="972" spans="1:27" ht="12.75">
       <c r="A972" s="2"/>
       <c r="B972" s="2"/>
       <c r="C972" s="14"/>
@@ -31021,7 +31030,7 @@
       <c r="Z972" s="2"/>
       <c r="AA972" s="2"/>
     </row>
-    <row r="973" spans="1:27" ht="13.2">
+    <row r="973" spans="1:27" ht="12.75">
       <c r="A973" s="2"/>
       <c r="B973" s="2"/>
       <c r="C973" s="14"/>
@@ -31050,7 +31059,7 @@
       <c r="Z973" s="2"/>
       <c r="AA973" s="2"/>
     </row>
-    <row r="974" spans="1:27" ht="13.2">
+    <row r="974" spans="1:27" ht="12.75">
       <c r="A974" s="2"/>
       <c r="B974" s="2"/>
       <c r="C974" s="14"/>
@@ -31079,7 +31088,7 @@
       <c r="Z974" s="2"/>
       <c r="AA974" s="2"/>
     </row>
-    <row r="975" spans="1:27" ht="13.2">
+    <row r="975" spans="1:27" ht="12.75">
       <c r="A975" s="2"/>
       <c r="B975" s="2"/>
       <c r="C975" s="14"/>
@@ -31108,7 +31117,7 @@
       <c r="Z975" s="2"/>
       <c r="AA975" s="2"/>
     </row>
-    <row r="976" spans="1:27" ht="13.2">
+    <row r="976" spans="1:27" ht="12.75">
       <c r="A976" s="2"/>
       <c r="B976" s="2"/>
       <c r="C976" s="14"/>
@@ -31137,7 +31146,7 @@
       <c r="Z976" s="2"/>
       <c r="AA976" s="2"/>
     </row>
-    <row r="977" spans="1:27" ht="13.2">
+    <row r="977" spans="1:27" ht="12.75">
       <c r="A977" s="2"/>
       <c r="B977" s="2"/>
       <c r="C977" s="14"/>
@@ -31166,7 +31175,7 @@
       <c r="Z977" s="2"/>
       <c r="AA977" s="2"/>
     </row>
-    <row r="978" spans="1:27" ht="13.2">
+    <row r="978" spans="1:27" ht="12.75">
       <c r="A978" s="2"/>
       <c r="B978" s="2"/>
       <c r="C978" s="14"/>
@@ -31195,7 +31204,7 @@
       <c r="Z978" s="2"/>
       <c r="AA978" s="2"/>
     </row>
-    <row r="979" spans="1:27" ht="13.2">
+    <row r="979" spans="1:27" ht="12.75">
       <c r="A979" s="2"/>
       <c r="B979" s="2"/>
       <c r="C979" s="14"/>
@@ -31224,7 +31233,7 @@
       <c r="Z979" s="2"/>
       <c r="AA979" s="2"/>
     </row>
-    <row r="980" spans="1:27" ht="13.2">
+    <row r="980" spans="1:27" ht="12.75">
       <c r="A980" s="2"/>
       <c r="B980" s="2"/>
       <c r="C980" s="14"/>
@@ -31253,7 +31262,7 @@
       <c r="Z980" s="2"/>
       <c r="AA980" s="2"/>
     </row>
-    <row r="981" spans="1:27" ht="13.2">
+    <row r="981" spans="1:27" ht="12.75">
       <c r="A981" s="2"/>
       <c r="B981" s="2"/>
       <c r="C981" s="14"/>
@@ -31282,7 +31291,7 @@
       <c r="Z981" s="2"/>
       <c r="AA981" s="2"/>
     </row>
-    <row r="982" spans="1:27" ht="13.2">
+    <row r="982" spans="1:27" ht="12.75">
       <c r="A982" s="2"/>
       <c r="B982" s="2"/>
       <c r="C982" s="14"/>
@@ -31311,7 +31320,7 @@
       <c r="Z982" s="2"/>
       <c r="AA982" s="2"/>
     </row>
-    <row r="983" spans="1:27" ht="13.2">
+    <row r="983" spans="1:27" ht="12.75">
       <c r="A983" s="2"/>
       <c r="B983" s="2"/>
       <c r="C983" s="14"/>
@@ -31340,7 +31349,7 @@
       <c r="Z983" s="2"/>
       <c r="AA983" s="2"/>
     </row>
-    <row r="984" spans="1:27" ht="13.2">
+    <row r="984" spans="1:27" ht="12.75">
       <c r="A984" s="2"/>
       <c r="B984" s="2"/>
       <c r="C984" s="14"/>
@@ -31369,7 +31378,7 @@
       <c r="Z984" s="2"/>
       <c r="AA984" s="2"/>
     </row>
-    <row r="985" spans="1:27" ht="13.2">
+    <row r="985" spans="1:27" ht="12.75">
       <c r="A985" s="2"/>
       <c r="B985" s="2"/>
       <c r="C985" s="14"/>
@@ -31398,7 +31407,7 @@
       <c r="Z985" s="2"/>
       <c r="AA985" s="2"/>
     </row>
-    <row r="986" spans="1:27" ht="13.2">
+    <row r="986" spans="1:27" ht="12.75">
       <c r="A986" s="2"/>
       <c r="B986" s="2"/>
       <c r="C986" s="14"/>
@@ -31427,7 +31436,7 @@
       <c r="Z986" s="2"/>
       <c r="AA986" s="2"/>
     </row>
-    <row r="987" spans="1:27" ht="13.2">
+    <row r="987" spans="1:27" ht="12.75">
       <c r="A987" s="2"/>
       <c r="B987" s="2"/>
       <c r="C987" s="14"/>
@@ -31456,7 +31465,7 @@
       <c r="Z987" s="2"/>
       <c r="AA987" s="2"/>
     </row>
-    <row r="988" spans="1:27" ht="13.2">
+    <row r="988" spans="1:27" ht="12.75">
       <c r="A988" s="2"/>
       <c r="B988" s="2"/>
       <c r="C988" s="14"/>
@@ -31485,7 +31494,7 @@
       <c r="Z988" s="2"/>
       <c r="AA988" s="2"/>
     </row>
-    <row r="989" spans="1:27" ht="13.2">
+    <row r="989" spans="1:27" ht="12.75">
       <c r="A989" s="2"/>
       <c r="B989" s="2"/>
       <c r="C989" s="14"/>
@@ -31514,7 +31523,7 @@
       <c r="Z989" s="2"/>
       <c r="AA989" s="2"/>
     </row>
-    <row r="990" spans="1:27" ht="13.2">
+    <row r="990" spans="1:27" ht="12.75">
       <c r="A990" s="2"/>
       <c r="B990" s="2"/>
       <c r="C990" s="14"/>
@@ -31543,7 +31552,7 @@
       <c r="Z990" s="2"/>
       <c r="AA990" s="2"/>
     </row>
-    <row r="991" spans="1:27" ht="13.2">
+    <row r="991" spans="1:27" ht="12.75">
       <c r="A991" s="2"/>
       <c r="B991" s="2"/>
       <c r="C991" s="14"/>
@@ -31572,7 +31581,7 @@
       <c r="Z991" s="2"/>
       <c r="AA991" s="2"/>
     </row>
-    <row r="992" spans="1:27" ht="13.2">
+    <row r="992" spans="1:27" ht="12.75">
       <c r="A992" s="2"/>
       <c r="B992" s="2"/>
       <c r="C992" s="14"/>
@@ -31601,7 +31610,7 @@
       <c r="Z992" s="2"/>
       <c r="AA992" s="2"/>
     </row>
-    <row r="993" spans="1:27" ht="13.2">
+    <row r="993" spans="1:27" ht="12.75">
       <c r="A993" s="2"/>
       <c r="B993" s="2"/>
       <c r="C993" s="14"/>
@@ -31630,7 +31639,7 @@
       <c r="Z993" s="2"/>
       <c r="AA993" s="2"/>
     </row>
-    <row r="994" spans="1:27" ht="13.2">
+    <row r="994" spans="1:27" ht="12.75">
       <c r="A994" s="2"/>
       <c r="B994" s="2"/>
       <c r="C994" s="14"/>
@@ -31659,7 +31668,7 @@
       <c r="Z994" s="2"/>
       <c r="AA994" s="2"/>
     </row>
-    <row r="995" spans="1:27" ht="13.2">
+    <row r="995" spans="1:27" ht="12.75">
       <c r="A995" s="2"/>
       <c r="B995" s="2"/>
       <c r="C995" s="14"/>
@@ -31688,7 +31697,7 @@
       <c r="Z995" s="2"/>
       <c r="AA995" s="2"/>
     </row>
-    <row r="996" spans="1:27" ht="13.2">
+    <row r="996" spans="1:27" ht="12.75">
       <c r="A996" s="2"/>
       <c r="B996" s="2"/>
       <c r="C996" s="14"/>
@@ -31717,7 +31726,7 @@
       <c r="Z996" s="2"/>
       <c r="AA996" s="2"/>
     </row>
-    <row r="997" spans="1:27" ht="13.2">
+    <row r="997" spans="1:27" ht="12.75">
       <c r="A997" s="2"/>
       <c r="B997" s="2"/>
       <c r="C997" s="14"/>
@@ -31746,7 +31755,7 @@
       <c r="Z997" s="2"/>
       <c r="AA997" s="2"/>
     </row>
-    <row r="998" spans="1:27" ht="13.2">
+    <row r="998" spans="1:27" ht="12.75">
       <c r="A998" s="2"/>
       <c r="B998" s="2"/>
       <c r="C998" s="14"/>
@@ -31775,7 +31784,7 @@
       <c r="Z998" s="2"/>
       <c r="AA998" s="2"/>
     </row>
-    <row r="999" spans="1:27" ht="13.2">
+    <row r="999" spans="1:27" ht="12.75">
       <c r="A999" s="2"/>
       <c r="B999" s="2"/>
       <c r="C999" s="14"/>
@@ -31804,7 +31813,7 @@
       <c r="Z999" s="2"/>
       <c r="AA999" s="2"/>
     </row>
-    <row r="1000" spans="1:27" ht="13.2">
+    <row r="1000" spans="1:27" ht="12.75">
       <c r="A1000" s="2"/>
       <c r="B1000" s="2"/>
       <c r="C1000" s="14"/>
@@ -31833,7 +31842,7 @@
       <c r="Z1000" s="2"/>
       <c r="AA1000" s="2"/>
     </row>
-    <row r="1001" spans="1:27" ht="13.2">
+    <row r="1001" spans="1:27" ht="12.75">
       <c r="A1001" s="2"/>
       <c r="B1001" s="2"/>
       <c r="C1001" s="14"/>
@@ -31875,7 +31884,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
@@ -31971,10 +31980,10 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA14"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="22.44140625" customWidth="1"/>
-    <col min="4" max="4" width="41.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1">
@@ -32314,7 +32323,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1">
       <c r="A1" s="10" t="s">
@@ -32372,20 +32381,20 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1011"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="20.25" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" style="33" customWidth="1"/>
-    <col min="2" max="2" width="61.44140625" style="33" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="33" customWidth="1"/>
-    <col min="4" max="4" width="184.5546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="33" customWidth="1"/>
+    <col min="2" max="2" width="61.42578125" style="33" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="33" customWidth="1"/>
+    <col min="4" max="4" width="184.5703125" style="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="62.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.44140625" style="33" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" style="49" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.5546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="38.5546875" style="33" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="12.5546875" style="33"/>
+    <col min="6" max="6" width="62.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" style="33" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="49" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="38.5703125" style="33" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="12.5703125" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.25" customHeight="1">
@@ -33427,14 +33436,16 @@
         <v>305</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="F25" s="44" t="s">
         <v>321</v>
       </c>
       <c r="G25" s="30"/>
       <c r="H25" s="47"/>
-      <c r="I25" s="22"/>
+      <c r="I25" s="22" t="s">
+        <v>438</v>
+      </c>
       <c r="J25" s="22" t="s">
         <v>388</v>
       </c>
@@ -62423,18 +62434,19 @@
     <hyperlink ref="I7" r:id="rId11" xr:uid="{90D33C5E-F624-4F4F-8831-53B87B192937}"/>
     <hyperlink ref="I8" r:id="rId12" xr:uid="{46192688-A117-4E2C-95A0-0FB00628B7D3}"/>
     <hyperlink ref="I9" r:id="rId13" xr:uid="{17C5E153-35DA-4A38-9F10-48DF09B9259B}"/>
+    <hyperlink ref="I25" r:id="rId14" xr:uid="{FF4179C3-21A8-4C08-BC82-5B9623A375E3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4445EC-8FC5-4E63-800B-686D768A8FCC}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -62487,7 +62499,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
+    <row r="5" spans="1:5" ht="16.5">
       <c r="A5">
         <v>2026</v>
       </c>
@@ -62498,7 +62510,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="41.4">
+    <row r="6" spans="1:5" ht="40.5">
       <c r="A6" s="42" t="s">
         <v>433</v>
       </c>
@@ -62509,7 +62521,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="26.4">
+    <row r="7" spans="1:5" ht="25.5">
       <c r="A7" t="s">
         <v>434</v>
       </c>
@@ -62533,14 +62545,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1"/>
-    <col min="5" max="5" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.7109375" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="13.2">
+    <row r="1" spans="1:21" ht="12.75">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -62577,7 +62589,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:21" ht="13.2">
+    <row r="2" spans="1:21" ht="12.75">
       <c r="A2" s="2" t="s">
         <v>119</v>
       </c>
@@ -62614,7 +62626,7 @@
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
     </row>
-    <row r="3" spans="1:21" ht="13.2">
+    <row r="3" spans="1:21" ht="12.75">
       <c r="A3" s="2" t="s">
         <v>119</v>
       </c>
@@ -62651,7 +62663,7 @@
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
     </row>
-    <row r="4" spans="1:21" ht="13.2">
+    <row r="4" spans="1:21" ht="12.75">
       <c r="A4" s="2" t="s">
         <v>119</v>
       </c>
@@ -62687,7 +62699,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
     </row>
-    <row r="5" spans="1:21" ht="13.2">
+    <row r="5" spans="1:21" ht="12.75">
       <c r="A5" s="2" t="s">
         <v>119</v>
       </c>
@@ -62724,7 +62736,7 @@
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
     </row>
-    <row r="6" spans="1:21" ht="13.8">
+    <row r="6" spans="1:21" ht="14.25">
       <c r="A6" s="2" t="s">
         <v>119</v>
       </c>
@@ -62761,7 +62773,7 @@
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
     </row>
-    <row r="7" spans="1:21" ht="13.8" thickBot="1">
+    <row r="7" spans="1:21" ht="13.5" thickBot="1">
       <c r="A7" s="2" t="s">
         <v>119</v>
       </c>
@@ -62798,7 +62810,7 @@
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
     </row>
-    <row r="8" spans="1:21" ht="13.8" thickBot="1">
+    <row r="8" spans="1:21" ht="13.5" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>119</v>
       </c>
